--- a/testrail-import/filters-v1-testrail-import.xlsx
+++ b/testrail-import/filters-v1-testrail-import.xlsx
@@ -3032,7 +3032,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>On the Estimates tab the Status filter is not offered; the other four filters work on top of the Estimates pre-filter</t>
+          <t>On the Estimates tab the Status chip is shown greyed out, pre-filled with 'Status: Estimate', and cannot be changed; the other four filters work on top of the Estimates pre-filter</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3061,20 +3061,21 @@
         <is>
           <t>1. Click the Estimates tab.
 2. Look at the filter bar.
-3. Open the Customer filter and select one customer.
-4. Look at the table.</t>
+3. Try to click the Status chip.
+4. Open the Customer filter and select one customer.
+5. Look at the table.</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>1. The Status filter is not offered as a usable filter on this tab (per the spec the chip is hidden; the tab already pre-filters to Estimate).
+          <t>1. The Status chip is shown but greyed out, already filled in as 'Status: Estimate', and cannot be clicked or changed - the tab already pre-filters the list to Estimate.
 2. Customer, Lead Technician, Service Advisor and Asset on site chips are shown and usable.
-3. After step 3 the table shows only that customer's ESTIMATE work orders - the customer filter narrows the pre-filtered Estimates list.</t>
+3. After step 4 the table shows only that customer's ESTIMATE work orders - the customer filter narrows the pre-filtered Estimates list.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 9 S9-R2; Story 2 S2-N1; §4 Key Decisions</t>
+          <t>requirements.md Story 9 S9-R2; Story 2 S2-N1 (chip-hidden wording superseded by PO ruling 2026-07-17: chip shown disabled); §4 Key Decisions</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -3083,7 +3084,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>On the Completed tab the Status filter is not offered; the other four filters work on top of the Completed pre-filter</t>
+          <t>On the Completed tab the Status chip is shown greyed out, pre-filled with the tab's status, and cannot be changed; the other four filters work on top of the Completed pre-filter</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3112,20 +3113,21 @@
         <is>
           <t>1. Click the Completed tab.
 2. Look at the filter bar.
-3. Open the Customer filter and select one customer.
-4. Look at the table.</t>
+3. Try to click the Status chip.
+4. Open the Customer filter and select one customer.
+5. Look at the table.</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>1. The Status filter is not offered as a usable filter on this tab (the tab already pre-filters to Complete).
+          <t>1. The Status chip is shown but greyed out, already filled in with this tab's status, and cannot be clicked or changed - the tab already pre-filters the list to Complete.
 2. Customer, Lead Technician, Service Advisor and Asset on site chips are shown and usable.
-3. After step 3 the table shows only that customer's COMPLETE work orders.</t>
+3. After step 4 the table shows only that customer's COMPLETE work orders.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 9 S9-R3; Story 2 S2-N2; §4 Key Decisions</t>
+          <t>requirements.md Story 9 S9-R3; Story 2 S2-N2 (chip-hidden wording superseded by PO ruling 2026-07-17: chip shown disabled); §4 Key Decisions</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
@@ -3283,7 +3285,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Filter selections persist while the browser session lasts, wherever you go in the app</t>
+          <t>Filter selections are remembered for you permanently - still applied after moving around the app and even after closing the browser and signing back in</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3310,18 +3312,21 @@
       <c r="F59" s="2" t="inlineStr">
         <is>
           <t>1. Visit several other areas of the app (Customers, Parts, Reports) and use them briefly.
-2. Return to the Work Orders page.
-3. Look at the chips and the table.</t>
+2. Return to the Work Orders page and look at the chips and the table.
+3. Close the browser completely (all windows).
+4. Open the browser again, sign in as the same person, and go to the Work Orders page.
+5. Look at the chips and the table.</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>1. The filter selections are still applied after moving around the app - you do not have to re-apply them within the same browser session.</t>
+          <t>1. After moving around the app (step 2) the filter selections are still applied - you do not have to re-apply them.
+2. After closing the browser completely and signing back in (step 5) the same filter selections are still applied - the app remembers your filters for you permanently, not just for one browser session.</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 10 S10-R2; §2/§4 (persist across navigation, saved per user)</t>
+          <t>requirements.md Story 10 S10-R2 (session-only wording superseded by PO ruling 2026-07-17: permanent per-user persistence); §2/§4 (persist across navigation, saved per user)</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr"/>

--- a/testrail-import/filters-v1-testrail-import.xlsx
+++ b/testrail-import/filters-v1-testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J80"/>
+  <dimension ref="A1:J123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -4118,243 +4118,2304 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>Parts Inventory page shows Bin Location, Category, Supply and Vendor filters</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Parts Page Filters</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Parts area of the app with some sample data present.</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Parts area and go to the Inventory page.
+2. Look at the filter buttons shown above the parts table.</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>1. The Inventory page shows four filter buttons in a row: Bin Location, Category, Supply and Vendor (each with a small icon and a down arrow).
+2. The table below shows the columns: Description, Part number, Tags, Category, Manufacturer, Vendor, Bin Location / Quantity and Action.
+3. A blue New Inventory Part button is shown at the top right.</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5 #1</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Parts Part Sales page shows Status, Customer, Created by and Date filters</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Parts Page Filters</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Parts area of the app with some sample data present.</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Parts area and go to the Part Sales page.
+2. Look at the filter buttons shown above the part sales table.</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>1. The Part Sales page shows four filter buttons: Status, Customer, Created by and Date.
+2. The table shows the columns: Number, Status, Customer, Asset, VIN/Serial #, Created By, Total Price, Created On, Parts and Returns.
+3. A blue New Part Sale button is shown at the top right.</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5 #2</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Parts Catalog page shows Manufacturer and Category filters</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Parts Page Filters</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Parts area of the app with some sample data present.</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Parts area and go to the Catalog page.
+2. Look at the filter buttons shown above the catalog table.</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>1. The Catalog page shows two filter buttons: Manufacturer and Category.
+2. The table shows the columns: (row checkbox), Description, Part Number, Tags and Category.
+3. A blue New Catalog Part button is shown at the top right.</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5 #3</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Parts Returns tab shows Vendor, Category and Part Type filters</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Parts Page Filters</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Parts area of the app with some sample data present.</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Parts area and go to the Returns page.
+2. Make sure the Returns tab is selected (the page has Returns and Credits tabs).
+3. Look at the filter buttons shown above the returns table.</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>1. The Returns tab shows three filter buttons: Vendor, Category and Part Type.
+2. The table shows the columns: Work Order, Vendor Invoice, Vendor, Part Number, Description, Quantity, Cost, Total Cost, Return Reason, Status and Requested.
+3. A blue Create Return button is shown at the top right.</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5 #4</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Parts Credits tab shows Vendor, Date and Processed by filters</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Parts Page Filters</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Parts area of the app with some sample data present.</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Parts area and go to the Returns page.
+2. Select the Credits tab.
+3. Look at the filter buttons shown above the credits table.</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>1. The Credits tab shows three filter buttons: Vendor, Date and Processed by.
+2. The table shows the columns: Credit Memo Number, Vendor, Work Order, Vendor Invoice, Date, Processed By, Total Cost and Notes.
+3. A blue Create Credit button is shown at the top right.</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5 #5</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Parts Purchase Orders page shows Vendor, Status, Date and Ordered by filters</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Parts Page Filters</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Parts area of the app with some sample data present.</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Parts area and go to the Purchase Orders page.
+2. Look at the filter buttons shown above the purchase orders table.</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>1. The Purchase Orders page shows four filter buttons: Vendor, Status, Date and Ordered by.
+2. The table shows the columns: Work Order, Purchase Order Number, Vendor, Order Status, Created On, Ordered By, Total Price and Note.
+3. A blue New Purchase Order button is shown at the top right.</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5 #6</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Vendor Invoices page shows Vendor, Invoice date, Date received, Received by</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Parts Page Filters</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Parts area of the app with some sample data present.</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Parts area and go to the Vendor Invoices page.
+2. Look at the filter buttons shown above the vendor invoices table.</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>1. The Vendor Invoices page shows four filter buttons: Vendor, Invoice date, Date received and Received by.
+2. The table shows the columns: Work Order, Invoice Number, Order Number, Received By, Vendor Name, Date Received, Invoice Date, Due Date, Total Cost and Note.
+3. There is no New button on this page (only the search and filter icons).</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5 #7</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Parts Vendors list page shows Vendor and State/Province filters</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Parts Page Filters</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Parts area of the app with some sample data present.</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Parts area and go to the Vendors list page.
+2. Look at the filter buttons shown above the vendors table.</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>1. The Vendors page shows two filter buttons: Vendor and State/Province.
+2. The table shows the columns: Name, Telephone, Email, Address 1, Address 2, City, State/Province and Zip/Postal Code.
+3. A blue New Vendor button is shown at the top right.</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5 #8</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Part Type filter opens a Core / Non Core list with Clear selection</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Parts Page Filters</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Parts area of the app with some sample data present.</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>1. On the Parts Returns tab, click the Part Type filter button.
+2. Look at the small menu that opens.</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>1. A small menu opens with two options: Core and Non Core.
+2. A Clear selection action is shown at the bottom of the menu.
+3. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (whether the options are single- or multi-select, and how the list is filtered after choosing).</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5 #9</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Parts pages show the shared search and filter toolbar icons</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Parts Page Filters</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Parts area of the app with some sample data present.</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>1. Open any Parts list page (for example Inventory).
+2. Look at the small icons on the right side of the toolbar.</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>1. The toolbar shows a Search (magnifier) icon and a filter (funnel) icon on every Parts list page.
+2. Some pages also show a column/layout toggle icon (for example Inventory).
+3. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (what the funnel and column icons do).</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5 shared shell</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Choosing a Parts filter narrows the list on that page</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Parts Page Filters</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Parts area of the app with some sample data present.</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a Parts list page that has a filter button (for example Inventory).
+2. Open a filter button and choose one value.
+3. Watch the table below.</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>1. The table updates to show only the rows that match the chosen filter value.
+2. The chosen value is shown on the filter button so you can see what is applied.
+3. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (exactly which filters apply on which Parts page, the full option lists, and whether results update immediately).</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Parts filters support multiple choices and can be cleared</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Parts Page Filters</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Parts area of the app with some sample data present.</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a Parts filter button that shows a list of choices.
+2. Try selecting more than one choice.
+3. Use the Clear selection action, then look at the filter bar for a way to clear all filters.</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>1. More than one value can be chosen inside a filter (to be checked live once available).
+2. Clear selection removes the choices for that one filter.
+3. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (whether multi-select, per-filter Clear selection, and an overall Clear filters action all work the same as on the Work Orders page).</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Timesheet Activities report shows Staff, Date, Status, Modified by filters</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Reports Page Filters</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Reports area of the app with some sample data present.</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Reports area and go to the Timesheet Activities report.
+2. Look at the filter buttons shown above the report table.</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>1. The Timesheet Activities report shows four filter buttons: Staff, Date, Status and Modified by.
+2. The table shows columns including Date, Employee, Work Order, Clock In Activity, Clock In, Clock Out, Total Hours, WO Hours, Internal Hours, Modified By and Modified Date/Time.</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #1</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Payroll Timesheet report shows Employee and Date filters</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Reports Page Filters</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Reports area of the app with some sample data present.</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Reports area and go to the Timesheets (Payroll Timesheet) report.
+2. Look at the filter buttons shown above the report table.</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>1. The Payroll Timesheet report shows two filter buttons: Employee and Date.
+2. The table shows columns: Employee Name, Date, Clock In Time, Lunch, Clock Out Time and Hours.</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #2</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Sales report shows Customer and Date filters</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Reports Page Filters</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Reports area of the app with some sample data present.</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Reports area and go to the Sales report.
+2. Look at the filter buttons shown above the report table.</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>1. The Sales report shows two filter buttons: Customer and Date.
+2. The table shows columns including Invoice Date, Invoice, Customer, Inv. Hrs, Billing Efficiency, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Cost, Parts Margin, Profit and Subtotal.</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #3</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Technician Efficiency report shows Customer, Technician and Date filters</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Reports Page Filters</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Reports area of the app with some sample data present.</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Reports area and go to the Technician Efficiency report.
+2. Look at the filter buttons shown above the report table.</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>1. The Technician Efficiency report shows three filter buttons: Customer, Technician and Date, on both the Invoiced and Completed tabs.
+2. The report has two view tabs: Invoiced and Completed; the same three filter buttons appear on each.
+3. 'Technician' is spelled correctly here (unlike the Work Orders list, see the spelling note).</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #4 and #5</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Advisor Analysis report shows Customer, Date and Advisor filters</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Reports Page Filters</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Reports area of the app with some sample data present.</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Reports area and go to the Advisor Analysis report.
+2. Look at the filter buttons shown above the report table.</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>1. The Advisor Analysis report shows three filter buttons: Customer, Date and Advisor.
+2. The table shows columns including Date, Invoice, Customer, Advisor, Days Open, Lines, Hrs Worked, Hrs Invoiced, Hrs Profit, Billing Efficiency, ELR, Parts Cost, Parts Invoiced, Parts Margin and Subtotal.</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #6</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Shop Efficiency report shows only a Date filter</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Reports Page Filters</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Reports area of the app with some sample data present.</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Reports area and go to the Shop Efficiency report.
+2. Look at the filter buttons shown above the report table.</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>1. The Shop Efficiency report shows a single filter button: Date.
+2. The table shows columns: Total Clocked Hours, Total Invoiced Hours, Difference and Efficiency.</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #7</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Work in Progress report shows Status, Date and Customer filters</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Reports Page Filters</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Reports area of the app with some sample data present.</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Reports area and go to the Work in Progress report.
+2. Look at the filter buttons shown above the report table.</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>1. The Work in Progress report shows three filter buttons: Status, Date and Customer.
+2. The table groups rows by status (Pending Authorization, In Progress, Ready To Invoice) with columns Sales, Cost, Profit $ and Profit %.</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #8</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Sales Follow Up report shows Customer, Date and Contact filters</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Reports Page Filters</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Reports area of the app with some sample data present.</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Reports area and go to the Sales Follow Up report.
+2. Look at the filter buttons shown above the report table.</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>1. The Sales Follow Up report shows three filter buttons: Customer, Date and Contact.
+2. The table shows columns: Customer, Sales Representative, Number Of Work Orders, Total Spend and Last Visit.</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #9</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Sales Tax Collected tab shows Date, Invoice Status and Customer filters</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Reports Page Filters</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Reports area of the app with some sample data present.</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Reports area and go to the Sales Tax (Collected tab) report.
+2. Look at the filter buttons shown above the report table.</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>1. On the Sales Tax report's Collected tab, three filter buttons are shown: Date, Invoice Status and Customer.
+2. The report has two view tabs: Collected and All Tax Rates.
+2. Note: in the design the report body uses a sample placeholder table, so only the title, tabs and filter buttons are design-confirmed here; the real report columns come from Branko's PRD.</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #10</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Sales Tax All Tax Rates tab shows only an Invoice Status filter</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Reports Page Filters</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Reports area of the app with some sample data present.</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Reports area and go to the Sales Tax (All Tax Rates tab) report.
+2. Look at the filter buttons shown above the report table.</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>1. On the Sales Tax report's All Tax Rates tab, a single filter button is shown: Invoice Status.
+2. Note: in the design the report body uses a sample placeholder table, so only the title, tabs and filter buttons are design-confirmed here; the real report columns come from Branko's PRD.</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #11</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>A/R Aging Summary report shows Customer and Date filters</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Reports Page Filters</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Reports area of the app with some sample data present.</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Reports area and go to the A/R Aging Summary report.
+2. Look at the filter buttons shown above the report table.</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>1. The A/R Aging Summary report shows two filter buttons: Customer and Date.
+2. A print icon is shown in the toolbar.
+2. Note: in the design the report body uses a sample placeholder table, so only the title, tabs and filter buttons are design-confirmed here; the real report columns come from Branko's PRD.</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #12</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>A/R Aging Detail shows Customer, Date, Location, Transaction Type filters</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Reports Page Filters</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Reports area of the app with some sample data present.</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Reports area and go to the A/R Aging Detail report.
+2. Look at the filter buttons shown above the report table.</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>1. The A/R Aging Detail report shows four filter buttons: Customer, Date, Location and Transaction Type.
+2. A print icon is shown in the toolbar.
+3. Location and Transaction Type are new filter types not on the Work Orders page — Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available.
+2. Note: in the design the report body uses a sample placeholder table, so only the title, tabs and filter buttons are design-confirmed here; the real report columns come from Branko's PRD.</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #13</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>A/R Aging Collection shows Customer, Date, Location, Transaction Type</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Reports Page Filters</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Reports area of the app with some sample data present.</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Reports area and go to the A/R Aging Collection report.
+2. Look at the filter buttons shown above the report table.</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>1. The A/R Aging Collection report shows four filter buttons: Customer, Date, Location and Transaction Type.
+2. A print icon is shown in the toolbar.
+2. Note: in the design the report body uses a sample placeholder table, so only the title, tabs and filter buttons are design-confirmed here; the real report columns come from Branko's PRD.</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #14</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>A/P Aging Summary report shows Vendor and Date filters</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Reports Page Filters</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Reports area of the app with some sample data present.</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Reports area and go to the A/P Aging Summary report.
+2. Look at the filter buttons shown above the report table.</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>1. The A/P Aging Summary report shows two filter buttons: Vendor and Date.
+2. A print icon is shown in the toolbar.
+2. Note: in the design the report body uses a sample placeholder table, so only the title, tabs and filter buttons are design-confirmed here; the real report columns come from Branko's PRD.</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #15</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>A/P Aging Detail shows Vendor, Date, Location, Transaction Type filters</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Reports Page Filters</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Reports area of the app with some sample data present.</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Reports area and go to the A/P Aging Detail report.
+2. Look at the filter buttons shown above the report table.</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>1. The A/P Aging Detail report shows four filter buttons: Vendor, Date, Location and Transaction Type.
+2. A print icon is shown in the toolbar.
+2. Note: in the design the report body uses a sample placeholder table, so only the title, tabs and filter buttons are design-confirmed here; the real report columns come from Branko's PRD.</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #16</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>A/P Unpaid Invoices shows Vendor, Date, Location, Transaction Type filters</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Reports Page Filters</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Reports area of the app with some sample data present.</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Reports area and go to the A/P Unpaid Invoices report.
+2. Look at the filter buttons shown above the report table.</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>1. The A/P Unpaid Invoices report shows four filter buttons: Vendor, Date, Location and Transaction Type.
+2. A print icon is shown in the toolbar.
+2. Note: in the design the report body uses a sample placeholder table, so only the title, tabs and filter buttons are design-confirmed here; the real report columns come from Branko's PRD.</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #17</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Notes report shows Author, Date and Mention filters</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Reports Page Filters</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Reports area of the app with some sample data present.</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Reports area and go to the Notes report.
+2. Look at the filter buttons shown above the report table.</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>1. The Notes report shows three filter buttons: Author, Date and Mention (the Mention button uses an @ icon).
+2. The toolbar also shows a search icon, a filter icon and a sort icon.
+3. Mention is a new filter type not on the Work Orders page — Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available.</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #18</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Reminders report shows only a Date filter</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Reports Page Filters</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Reports area of the app with some sample data present.</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Reports area and go to the Reminders report.
+2. Look at the filter buttons shown above the report table.</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>1. The Reminders report shows a single filter button: Date.
+2. When no reminders match, the report shows the message 'There are no reminders for selected date range'.</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #19</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>IBS Batch Transactions report shows Customer, Date and Status filters</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Reports Page Filters</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Reports area of the app with some sample data present.</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Reports area and go to the IBS Batch Transactions report.
+2. Look at the filter buttons shown above the report table.</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>1. The IBS Batch Transactions report shows three filter buttons: Customer, Date and Status.
+2. The report has three view tabs: Ready To Send, Sent and Payments.
+3. The table shows columns: (checkbox), Date, Type, No., Customer, Total, Balance and Status.</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #20</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>QB Unexported report filters change per tab (Customer / Vendor / User)</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Reports Page Filters</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Reports area of the app with some sample data present.</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Reports area and go to the QB Unexported report.
+2. Look at the filter buttons shown above the report table.</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>1. The QB Unexported report has three view tabs, and the first filter button changes per tab.
+2. On the Customers tab the filter buttons are Customer, Date and Type.
+3. On the Vendors tab they are Vendor, Date and Type.
+4. On the Journal Entries tab they are User, Date and Type.
+5. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (option lists behind each button).</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #21, #22, #23</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Choosing a Reports filter narrows the report results</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Reports Page Filters</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Reports area of the app with some sample data present.</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Reports area and go to the any (for example Sales) report.
+2. Look at the filter buttons shown above the report table.</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>1. The report updates to show only the rows matching the chosen filter value, and the chosen value is shown on the filter button.
+2. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (exactly which filters apply on each report, the full option lists, and whether results update immediately).</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>New Reports filter types behave correctly (Location, Transaction Type, etc.)</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Reports Page Filters</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Reports area of the app with some sample data present.</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Reports area and go to the reports that use them (for example A/R Aging Detail, Notes) report.
+2. Look at the filter buttons shown above the report table.</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>1. Each new filter type (Location, Transaction Type, Invoice Status, Type, User, Mention) opens a list of choices and filters the report by the choice.
+2. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (the exact choices, single- vs multi-select, and how each new filter type filters the report).</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Page search opens with the 'Search or ask a question' box</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Page Search (Command-K)</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. Some sample work orders, customers, assets, parts and vendors exist.</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>1. From anywhere in the app, open the page search (the Search box in the top bar, or press Command-K / Ctrl-K).
+2. Look at the search panel that opens.</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>1. A search panel opens with an empty search box at the top.
+2. The box shows the placeholder text 'Search or ask a question' with a magnifier icon on the left and a clear (X) button on the right.
+3. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (whether 'ask a question' means an AI search — this is out of scope for now).</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Page search shows entity tabs All, Work Orders, Customers, Assets, Parts...</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Page Search (Command-K)</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. Some sample work orders, customers, assets, parts and vendors exist.</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the page search panel.
+2. Look at the row of tabs under the search box.</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>1. A row of tabs is shown: All, Work Orders, Customers, Assets, Parts, Vendors and Part Sales.
+2. The All tab is selected by default.
+3. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (whether choosing a tab limits results to that type only).</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr"/>
+      <c r="J111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Typing a term shows grouped results with counts and highlighting</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Page Search (Command-K)</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. Some sample work orders, customers, assets, parts and vendors exist.</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the page search panel.
+2. Type a few letters (for example 'Fib') into the search box.
+3. Look at the results.</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>1. Results are grouped by type with a count next to each group heading, for example 'Work orders (2)', 'Customers (2)', 'Vendors (1)', 'Assets (2)', 'Parts (1)'.
+2. The matching part of each result is highlighted in yellow.
+3. Each work order row shows its number, name, a status pill (for example Approved or Estimate), the person and a date.
+4. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (how matching works — exact vs fuzzy — and the ranking order).</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Recent searches are shown grouped by Today, Yesterday, Past week...</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Page Search (Command-K)</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. Some sample work orders, customers, assets, parts and vendors exist.</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the page search panel without typing anything.
+2. Look at the list shown under the tabs.</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>1. A list of recent items is shown, grouped under headings: Today, Yesterday, Past week and Past 30 days.
+2. Each item shows a type icon, its name and a short detail line (for example a customer address or a date).
+3. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (how many recent items are kept and how long they persist).</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr"/>
+      <c r="J113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Re-opening page search keeps the last typed text and its results</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Page Search (Command-K)</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. Some sample work orders, customers, assets, parts and vendors exist.</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the page search and type a term (for example 'Fibridge').
+2. Close the panel, then open it again.
+3. Look at the search box and the results.</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>1. The previous search text is still in the box (shown selected/highlighted) and its results are shown.
+2. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (whether the last search is remembered per person and for how long — this is the 'persisting search' state).</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr"/>
+      <c r="J114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Hovering a search result shows quick-action buttons</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Page Search (Command-K)</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. Some sample work orders, customers, assets, parts and vendors exist.</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the page search panel (recent items or results shown).
+2. Move the mouse over a result row.
+3. Look at the right side of that row.</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>1. Quick-action buttons appear on the row, depending on the result type — for example 'Add new line' on a work order, 'New work order' on an asset or customer, 'Add part' on a part sale, 'Add contact' on a vendor and 'Add to work order' on a part.
+2. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (exactly which quick actions show for which result type, and what each one does).</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr"/>
+      <c r="J115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Page search shows keyboard hints and supports keyboard navigation</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Page Search (Command-K)</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. Some sample work orders, customers, assets, parts and vendors exist.</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the page search panel.
+2. Look at the bar along the bottom of the panel.
+3. Use the up/down arrow keys, Enter and Esc.</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>1. The bottom bar shows keyboard hints: up/down arrows labelled 'Navigate', the Enter key labelled 'Select', and 'Close esc'.
+2. Arrow keys move the highlight between results, Enter opens the highlighted result, and Esc closes the panel (to be checked live once available).
+3. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (exact keyboard behaviour).</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr"/>
+      <c r="J116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Page search results include a Refresh action</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Page Search (Command-K)</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. Some sample work orders, customers, assets, parts and vendors exist.</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the page search and type a term so grouped results appear.
+2. Look at the top right of the results area.</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>1. A 'Refresh' link is shown at the top right of the results.
+2. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (what Refresh reloads and when it is shown).</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr"/>
+      <c r="J117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Page search scope belongs to Filters or Global Search (to decide)</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Page Search (Command-K)</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. Some sample work orders, customers, assets, parts and vendors exist.</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>1. Review where the page search / Command-K component is owned for testing.
+2. Compare against the Global Search project's existing cases.</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>1. The page-search component is agreed to belong to either the Filters test suite or the Global Search test suite, not both.
+2. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (product/QA decision on which project owns page search).</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr"/>
+      <c r="J118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
           <t>The work order list request carries the active filter selections</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>API — Work Orders List Filtering</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser with developer tools open on the Network tab.
 2. You are on the Work Orders page with no filters applied.</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>1. Apply a Status selection and a Customer selection in the filter bar.
 2. In the Network tab, find the work order list request the page sends after the change.
 3. Inspect the request's parameters.</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr">
         <is>
           <t>1. The list request includes the active filter selections as request parameters (status values and customer identifiers).
 2. The request succeeds (HTTP 200).
 3. The response contains only work orders matching the filters - the filtering is done by the backend, not just hidden client-side.</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 2 S2-R2; Story 3 S3-R6 (backend view)</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="I119" s="2" t="inlineStr"/>
+      <c r="J119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>A combined multi-filter request returns only work orders matching all filters, any value within each filter</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>API — Work Orders List Filtering</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with developer tools open on the Network tab.
 2. Seeded ZZAUTOTEST work orders exist: customer A with an Estimate and an Approved work order, customer B with an Estimate work order.</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>1. On the Work Orders page apply Status = Estimate + Approved and Customer = customer A.
 2. Capture the resulting list request and response.</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr">
         <is>
           <t>1. One request carries both filters together (both statuses and the customer).
 2. The response returns customer A's Estimate and Approved work orders only.
 3. Customer B's work orders are absent - the customer filter and status filter both restrict the result, while the two statuses combine as either-or.</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 2 S2-R2; Story 3 S3-R6; Story 8 S8-R3 (backend view)</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="I120" s="2" t="inlineStr"/>
+      <c r="J120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>A list request with a deleted or unknown filter value is handled without a server error</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t>API — Work Orders List Filtering</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C121" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in and can replay/edit the work order list request (developer tools or an API client).
 2. You have a captured filtered list request, and one of its filter values has since been deleted (for example a removed ZZAUTOTEST customer) or is a made-up identifier.</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>1. Send the list request containing the no-longer-existing (or made-up) filter value.
 2. Inspect the HTTP status and the response body.</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr">
         <is>
           <t>1. The backend does not fail with a server error (no HTTP 5xx).
 2. The response is a normal, successful list response - the invalid value is ignored or simply matches nothing.
 3. Any still-valid filter values in the same request are applied normally.</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 10 S10-N1; Story 11 S11-R3</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="I121" s="2" t="inlineStr"/>
+      <c r="J121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>A list request with malformed filter parameters does not produce a server error</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>API — Work Orders List Filtering</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="C122" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in and can replay/edit the work order list request.
 2. You have a captured filtered list request to tamper with.</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>1. Corrupt the filter parameters (wrong types, scrambled values, nonsense text) and send the request.
 2. Inspect the HTTP status and the response body.
 3. Also open the equally malformed page URL in the browser and watch the page.</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr">
         <is>
           <t>1. The backend responds gracefully - no HTTP 5xx / crash; either a normal (unfiltered or empty) list or a clean validation response.
 2. In the browser the page still loads without filters and without an error message, matching the malformed-URL requirement.</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 11 S11-N1</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="I122" s="2" t="inlineStr"/>
+      <c r="J122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>A filter combination matching nothing returns a successful empty list, not an error</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>API — Work Orders List Filtering</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with developer tools open on the Network tab.
 2. A filter combination is known to match no work orders (for example a seeded customer plus a status they never have).</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>1. Apply that filter combination on the Work Orders page.
 2. Capture the list request and response.</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr">
         <is>
           <t>1. The request succeeds (HTTP 200).
 2. The response contains an empty result set (zero work orders) - an empty match is a normal outcome, not an error.
 3. The page renders the no-results empty state from this response.</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 8 S8-R3; Story 2 S2-N3</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
+      <c r="I123" s="2" t="inlineStr"/>
+      <c r="J123" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/filters-v1-testrail-import.xlsx
+++ b/testrail-import/filters-v1-testrail-import.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Filters V1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters V1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J123"/>
+  <dimension ref="A1:J138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -933,39 +933,91 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>Imported works alone: picking it greys out the other filters</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Status Filter</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. Imported work orders exist, plus some normal work orders.
+3. You are on the Work Orders page, All tab, no filters applied.</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Status filter and tick Imported.
+2. Look at the other filter chips (Customer, Lead Technician, Service Advisor, Asset on site).
+3. Try to combine Imported with another status.
+4. Untick Imported.</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1. The table switches to showing imported work orders only.
+2. While Imported is ticked, the other filter chips are greyed out and cannot be used.
+3. Imported cannot be combined with other statuses - selecting it works alone.
+4. Unticking Imported re-enables the other chips and the normal list returns.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); tech plan 2026-07-29 G1 (Imported exclusivity); spec S2-R1 (conflict raised with the author - export of spec v1.3 awaited)</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>Customer chip opens a dropdown with a 'Search customer' field and a scrollable customer list</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Customer Filter</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page.
 3. Several customers exist in the shop.</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>1. Click the Customer filter chip.
 2. Look at the top of the dropdown panel and the list below it.
 3. Look at the bottom of the panel.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>1. A dropdown panel opens under the Customer chip.
 2. A search input with the placeholder 'Search customer' is at the top, already focused so you can type right away.
@@ -973,99 +1025,99 @@
 4. A 'Clear selection' action is shown at the bottom of the panel.</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 3 S3-R1</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Typing in the customer search narrows the list to matching names</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Customer Filter</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with the Customer dropdown open.
 3. Several customers with different names exist.</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>1. Type part of one customer's name into the 'Search customer' field (for example the first few letters).
 2. Watch the list while you type.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>1. The customer list narrows as you type, showing only names that match what you entered.
 2. Customers that do not match are removed from the list.
 3. Deleting the text brings the full list back.</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 3 S3-R2</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Selecting customers adds removable tags in the dropdown input area and checkmarks in the list</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Customer Filter</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with the Customer dropdown open.
 3. At least three customers exist.</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>1. Click one customer in the list.
 2. Click a second and a third customer.
 3. Look at the input area at the top of the dropdown and at the list rows.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1. Each selected customer appears as a tag (small chip) with an x in the input area at the top of the dropdown.
 2. Each selected customer's row in the list shows a checkmark on the right.
@@ -1073,49 +1125,49 @@
 4. You can keep selecting as many customers as needed - there is no selection limit.</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 3 S3-R3; S3-R4; §4 Key Decisions (no selection limit)</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Clicking the x on a customer tag removes just that customer from the selection</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Customer Filter</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with the Customer dropdown open.
 3. Two or more customers are selected (their tags are visible in the input area).</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>1. Click the x on one selected customer's tag.
 2. Look at the tags, the list and the work order table.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>1. That customer's tag disappears from the input area.
 2. The checkmark next to that customer in the list is removed.
@@ -1123,99 +1175,99 @@
 4. The table updates to no longer include that customer's work orders.</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 3 S3-R5</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>The table shows only work orders belonging to any of the selected customers</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Customer Filter</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page on the All tab.
 3. At least two customers each have at least one work order, and a third customer's work orders also exist (seed ZZAUTOTEST data if needed).</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>1. Open the Customer filter and select two customers.
 2. Look at the Customer column in the work order table.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1. The table shows only work orders whose customer is one of the two selected customers.
 2. Work orders belonging to any other customer are hidden.
 3. The table updates in real time as you make the selections (no apply button on desktop).</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 3 S3-R6; Story 2 S2-R6 (real-time pattern)</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Clear selection in the Customer dropdown removes all selected customers</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Customer Filter</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page.
 3. Two or more customers are selected in the Customer filter and the table is filtered.</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>1. Open the Customer dropdown (if not already open).
 2. Click 'Clear selection' at the bottom of the dropdown.
 3. Look at the tags, the list and the table.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1. All customer tags are removed from the input area.
 2. All checkmarks in the list are removed.
@@ -1223,196 +1275,196 @@
 4. Other active filters (if any) are not affected.</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 3 S3-R7; Story 8 S8-R2</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Clicking outside the Customer dropdown closes it and the selections remain</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Customer Filter</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with the Customer dropdown open and two customers selected.</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>1. Click anywhere outside the dropdown.
 2. Look at the Customer chip and the table.
 3. Click the Customer chip again to reopen the dropdown.</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>1. The dropdown closes when you click outside it.
 2. The Customer chip stays in the active (blue) state showing the selection and the table stays filtered.
 3. When reopened, the selected customers' tags are still visible in the input area.</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 3 S3-R8</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Customer search with no matching name shows a no-results message in the list</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Customer Filter</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with the Customer dropdown open.</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>1. Type a string that matches no customer name (for example 'zzzqqq').
 2. Look at the list area of the dropdown.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>1. The list shows a message saying there are no results (instead of an empty gap).
 2. The app does not show an error.
 3. Clearing the search text brings the customer list back.</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 3 S3-N1</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>A customer with no open work orders is still listed; filtering by them returns an empty result</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Customer Filter</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A customer exists who currently has NO work orders (create a fresh ZZAUTOTEST customer if needed).
 3. You are on the Work Orders page on the All tab.</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>1. Open the Customer filter and search for the customer who has no work orders.
 2. Confirm they appear in the list, then select them (and only them).
 3. Look at the table.</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1. The customer with no work orders IS shown in the filter list (they are not hidden).
 2. After selecting only that customer, the table shows no rows and the filtered empty state is displayed.
 3. No error is shown.</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 3 S3-E1; S3-N2; Story 8 S8-R3</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Lead Technician chip opens a dropdown with a 'Search technician' field and a technician list</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Lead Technician Filter</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page.
 3. Several technicians exist in the shop.</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>1. Click the Lead Technician filter chip.
 2. Look at the top of the dropdown, the list below and the bottom of the panel.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>1. A dropdown panel opens under the Lead Technician chip.
 2. A search input with the placeholder 'Search technician' is at the top.
@@ -1420,96 +1472,96 @@
 4. A 'Clear selection' action is shown at the bottom.</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 4 S4-R1</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Typing in the technician search narrows the list to matching names</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Lead Technician Filter</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with the Lead Technician dropdown open.</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>1. Type part of one technician's name into the 'Search technician' field.
 2. Watch the list while you type.</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>1. The technician list narrows to only the names matching what you typed.
 2. Deleting the text brings the full list back.</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 4 S4-R2</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Selecting technicians shows only work orders where they are the lead technician</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Lead Technician Filter</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page on the All tab.
 3. Work orders exist with different lead technicians assigned, including at least one work order where the chosen technician is assigned but NOT as lead (seed ZZAUTOTEST data if needed).</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>1. Open the Lead Technician filter and select one or two technicians.
 2. Look at the checkboxes in the list and the work order table.</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>1. Selected technicians show a filled checkbox in the list.
 2. The table shows only work orders where one of the selected technicians is assigned as the LEAD technician.
@@ -1517,242 +1569,242 @@
 4. The table updates in real time as you select.</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 4 S4-R3; S4-R4</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Clear selection in the Lead Technician dropdown removes all selected technicians</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Lead Technician Filter</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page.
 3. One or more technicians are selected in the Lead Technician filter.</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>1. Open the Lead Technician dropdown and click 'Clear selection' at the bottom.
 2. Look at the list and the table.</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>1. All technician selections are removed (checkboxes unticked).
 2. The Lead Technician filter no longer restricts the table.
 3. Other active filters are not affected.</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 4 S4-R5; Story 8 S8-R2</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Clicking outside the Lead Technician dropdown closes it</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Lead Technician Filter</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with the Lead Technician dropdown open and one technician selected.</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>1. Click anywhere outside the dropdown.
 2. Look at the dropdown, the chip and the table.</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>1. The dropdown closes.
 2. The selection stays applied - the chip stays active and the table stays filtered.</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 4 S4-R6</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Selecting a technician who leads no work orders shows the empty state</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Lead Technician Filter</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A technician exists who is not the lead technician on ANY work order (create a fresh ZZAUTOTEST staff member if needed).
 3. You are on the Work Orders page on the All tab with no other filters active.</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>1. Open the Lead Technician filter and select only that technician.
 2. Look at the table.</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>1. The table shows no rows and the filtered empty state is displayed.
 2. No error is shown.</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 4 S4-N1; Story 8 S8-R3</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>A deactivated technician does not appear in the Lead Technician filter list</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Lead Technician Filter</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A test technician (ZZAUTOTEST) exists and is visible in the Lead Technician filter list.
 3. That test technician is then made inactive/deactivated in staff administration (restore them afterwards).</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>1. On the Work Orders page, open the Lead Technician filter.
 2. Search for the deactivated technician's name.
 3. Look at the list.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>1. The deactivated technician is NOT shown in the filter list.
 2. Active technicians are still listed normally.</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 4 S4-E1</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Service Advisor chip opens a dropdown with a 'Search advisor' field and an advisor list</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Service Advisor Filter</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page.
 3. Several service advisors exist in the shop.</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>1. Click the Service Advisor filter chip.
 2. Look at the top of the dropdown, the list below and the bottom of the panel.</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>1. A dropdown panel opens under the Service Advisor chip.
 2. A search input with the placeholder 'Search advisor' is at the top.
@@ -1760,337 +1812,337 @@
 4. A 'Clear selection' action is shown at the bottom.</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 5 S5-R1</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Typing in the advisor search narrows the list to matching names</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Service Advisor Filter</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with the Service Advisor dropdown open.</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>1. Type part of one advisor's name into the 'Search advisor' field.
 2. Watch the list while you type.</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>1. The advisor list narrows to only the names matching what you typed.
 2. Deleting the text brings the full list back.</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 5 S5-R2</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Selecting advisors shows only work orders assigned to those advisors</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Service Advisor Filter</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page on the All tab.
 3. Work orders exist with different service advisors assigned (seed ZZAUTOTEST data if needed).</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>1. Open the Service Advisor filter and select one or two advisors.
 2. Look at the checkboxes in the list and the Service Advisor column in the table.</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>1. Selected advisors show a filled checkbox in the list.
 2. The table shows only work orders assigned to any of the selected advisors.
 3. The table updates in real time as you select.</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 5 S5-R3; S5-R4</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Clear selection in the Service Advisor dropdown removes all selected advisors</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Service Advisor Filter</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page.
 3. One or more advisors are selected in the Service Advisor filter.</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>1. Open the Service Advisor dropdown and click 'Clear selection' at the bottom.
 2. Look at the list and the table.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>1. All advisor selections are removed.
 2. The Service Advisor filter no longer restricts the table.
 3. Other active filters are not affected.</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 5 S5-R5; Story 8 S8-R2</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Clicking outside the Service Advisor dropdown closes it</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Service Advisor Filter</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with the Service Advisor dropdown open and one advisor selected.</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>1. Click anywhere outside the dropdown.
 2. Look at the dropdown, the chip and the table.</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>1. The dropdown closes.
 2. The selection stays applied - the chip stays active and the table stays filtered.</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 5 S5-R6</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Selecting an advisor with no assigned work orders shows the empty state</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Service Advisor Filter</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. An advisor exists who is not assigned to ANY work order (create a fresh ZZAUTOTEST staff member if needed).
 3. You are on the Work Orders page on the All tab with no other filters active.</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>1. Open the Service Advisor filter and select only that advisor.
 2. Look at the table.</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>1. The table shows no rows and the filtered empty state is displayed.
 2. No error is shown.</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 5 S5-N1; Story 8 S8-R3</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>A deactivated advisor does not appear in the Service Advisor filter list</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Service Advisor Filter</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A test advisor (ZZAUTOTEST) exists and is visible in the Service Advisor filter list.
 3. That test advisor is then made inactive/deactivated in staff administration (restore them afterwards).</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>1. On the Work Orders page, open the Service Advisor filter.
 2. Search for the deactivated advisor's name.
 3. Look at the list.</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>1. The deactivated advisor is NOT shown in the filter list.
 2. Active advisors are still listed normally.</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 5 S5-E1</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Asset on site chip opens a dropdown with exactly two options, Yes and No, plus Clear selection</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>Asset on Site Filter</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page.</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>1. Click the Asset on site filter chip.
 2. Read the options in the dropdown.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>1. A small dropdown panel opens under the Asset on site chip.
 2. It contains exactly two options: Yes and No.
@@ -2098,378 +2150,428 @@
 4. It is a dropdown (like the other filters), not an on/off toggle.</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 6 S6-R1; §4 Key Decisions (dropdown, not toggle)</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Choosing Yes shows only work orders whose asset is on site</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>Asset on Site Filter</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page on the All tab.
 3. Work orders exist in both states: some with the asset marked on site and some not (set the on-site marker on ZZAUTOTEST work orders as needed).</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>1. Open the Asset on site filter and choose Yes.
 2. Look at the On Site column in the table (green house icon = on site, red = not).</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>1. The table shows only work orders whose asset is currently on site.
 2. Work orders whose asset is not on site are hidden.
 3. Choosing No instead shows only the not-on-site work orders.</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 6 S6-R2</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Asset on site is single-select: choosing the other option replaces the first</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>Asset on Site Filter</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with Yes selected in the Asset on site filter.</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>1. Open the Asset on site dropdown again.
 2. Choose No.
 3. Look at the selection and the table.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>1. No becomes the selected option and Yes is deselected automatically - only one option can be selected at a time.
 2. The table switches to showing only the not-on-site work orders.
 3. The chip shows the currently selected value.</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 6 S6-R3</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Clear selection in the Asset on site dropdown removes the filter</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>Asset on Site Filter</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with Yes or No selected in the Asset on site filter.</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>1. Open the Asset on site dropdown and click 'Clear selection'.
 2. Look at the chip and the table.</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>1. The selection is removed and the chip returns to its default (inactive) state.
 2. The table shows work orders regardless of on-site status again.
 3. Other active filters are not affected.</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 6 S6-R4; Story 8 S8-R2</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Clicking outside the Asset on site dropdown closes it</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>Asset on Site Filter</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with the Asset on site dropdown open and Yes selected.</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>1. Click anywhere outside the dropdown.
 2. Look at the dropdown, the chip and the table.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>1. The dropdown closes.
 2. The Yes selection stays applied - the chip stays active and the table stays filtered.</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 6 S6-R5</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>An Asset on site choice that matches no work orders shows the empty state</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>Asset on Site Filter</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page on the All tab with no other filters active.
 3. Every current work order is in the SAME on-site state (set all ZZAUTOTEST work orders to on site, or combine with another filter so one option matches nothing).</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>1. Open the Asset on site filter and choose the option that matches no work orders (for example No when everything is on site).
 2. Look at the table.</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>1. The table shows no rows and the filtered empty state is displayed.
 2. No error is shown.</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 6 S6-N1; Story 8 S8-R3</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Choosing No shows only work orders whose asset is not on site</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Asset on Site Filter</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. Work orders exist both with the asset on site and with the asset not on site (create one of each if needed).
+3. You are on the Work Orders page.</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Asset on site filter.
+2. Choose No.
+3. Look at the table (and its On Site column).</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>1. Only work orders whose asset is NOT on site remain in the list.
+2. Every work order with the asset on site is excluded.
+3. The chip shows the active No selection.</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>requirements.md Story 6 S6-R2; Filters (Epic key TBD); tech plan 2026-07-29 G4 (filtering No is new capability)</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>A chip with a selected value turns into the active blue state and shows the value</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Active Filter Chips and Clear Filters</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with no filters selected (all chips in their default grey state).</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>1. Open the Status filter and tick one status (for example Estimate).
 2. Click outside to close the dropdown and look at the Status chip.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>1. The Status chip changes to an active/highlighted look (blue pill).
 2. The chip displays the selected value (for example 'Status: Estimate').
 3. The other chips stay in their default state.</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 7 S7-R1</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>A chip with several values shows the first values and shortens the rest with an ellipsis</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>Active Filter Chips and Clear Filters</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page on the All tab.</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>1. Open the Status filter and tick three or more statuses (for example Estimate, In progress and Approved).
 2. Close the dropdown and read the Status chip label.</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>1. The chip lists the selected values starting with the first one and shortens the label when it gets too long (the design shows 'Status: Estimate, In progress, Approved...').
 2. The chip stays a single compact pill - it does not grow to show every value in full.</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 7 S7-R2</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>'Clear filters' appears to the right of the chips only when at least one filter is active</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Active Filter Chips and Clear Filters</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with no filters selected.</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>1. Look at the right end of the filter chip row with no filters active.
 2. Select any filter value (for example one status).
@@ -2477,56 +2579,56 @@
 4. Remove the selection (Clear selection in the dropdown) and look once more.</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>1. With no filters active, no 'Clear filters' button/link is shown (there is nothing to click).
 2. As soon as one filter is active, a blue 'Clear filters' link appears at the right end of the chip row.
 3. When the last active filter is removed, 'Clear filters' disappears again.</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 7 S7-R3; S7-N1; Story 8 S8-N1</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>'Clear filters' removes every active filter at once and all chips return to default</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>Active Filter Chips and Clear Filters</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page on the All tab.
 3. Values are selected in at least three different filters (for example a status, a customer and Asset on site Yes).</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>1. Click the 'Clear filters' link at the right end of the chip row.
 2. Look at all the chips and the table.</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>1. Every active filter is cleared in one click.
 2. All chips return to their default (inactive) look with no values shown.
@@ -2534,239 +2636,239 @@
 4. The 'Clear filters' link disappears.</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 8 S8-R1; §4 Key Decisions</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>'Clear selection' inside one dropdown clears only that filter and leaves the others active</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Active Filter Chips and Clear Filters</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page on the All tab.
 3. Values are selected in at least two different filters (for example a status and a customer).</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>1. Open the Status dropdown and click 'Clear selection'.
 2. Look at the Status chip, the Customer chip and the table.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>1. Only the Status filter is cleared - its chip returns to default.
 2. The Customer filter stays selected and active (blue) and keeps filtering the table.
 3. 'Clear filters' remains visible because a filter is still active.</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 8 S8-R2; §4 Key Decisions</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>Several different filters combine: only work orders matching every active filter remain</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>Active Filter Chips and Clear Filters</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page on the All tab.
 3. Seed ZZAUTOTEST work orders so that: customer A has an Estimate work order and an Approved work order, and customer B has an Estimate work order.</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>1. Open the Status filter and tick Estimate.
 2. Open the Customer filter and select customer A.
 3. Look at the table.</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>1. Only customer A's Estimate work order is shown.
 2. Customer A's Approved work order is hidden (wrong status) and customer B's Estimate work order is hidden (wrong customer) - each additional filter narrows the result further.
 3. Both chips are in the active state and 'Clear filters' is visible.</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>requirements.md §2 Feature Overview (multi-criteria); Story 8 S8-R3 ('combination of active filters')</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>The toolbar funnel button collapses the filter bar and the table reclaims the space</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>Collapse and Expand</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with the filter bar visible (expanded).</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>1. Find the filter (funnel) icon button in the page toolbar (next to the Search magnifier and the column/layout toggle, left of the New Work Order button).
 2. Click the funnel icon once.
 3. Look at the filter bar area and the table.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>1. The filter bar row is hidden.
 2. The work order table moves up and uses the reclaimed vertical space.
 3. The funnel icon shows a pressed/active look while the bar is collapsed.</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 1 S1-R4; S1-R5</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>Expanding the filter bar brings it back exactly as it was, with active filters still shown</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>Collapse and Expand</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page.
 3. At least one filter is selected (for example two statuses) and the filter bar has been collapsed with the funnel button.</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>1. Click the funnel icon in the toolbar again.
 2. Look at the filter bar.</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>1. The filter bar reappears below the tab row.
 2. The previously selected filters are still shown on their chips in the active (blue) state - nothing was lost while collapsed.
 3. The 'Clear filters' link is still shown at the right end of the chip row.</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 1 S1-R6</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>The collapsed or expanded state of the filter bar is remembered after leaving and returning</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Collapse and Expand</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page and have collapsed the filter bar with the funnel button.</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to another page (for example open a work order, or go to Customers).
 2. Return to the Work Orders page.
@@ -2774,290 +2876,290 @@
 4. Expand the bar with the funnel button, leave the page again and come back.</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>1. After step 2 the filter bar is still collapsed (your choice was remembered).
 2. After step 4 the filter bar is expanded again when you return - whichever state you left it in is restored.</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 1 S1-R7; Story 10 S10-R1</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>The funnel button shows a blue indicator when filters are active while the bar is collapsed, and none when no filters are active</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>Collapse and Expand</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page.</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>1. With NO filters selected, collapse the filter bar with the funnel button and look at the funnel icon.
 2. Expand the bar, select at least one filter value (for example a status).
 3. Collapse the bar again and look at the funnel icon.</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>1. After step 1 the funnel icon shows no special indicator (only its normal pressed look).
 2. After step 3 the funnel icon shows a visual indicator (filters icon in primary blue) signalling that active filters are in effect while the bar is hidden.</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 7 S7-R4; S7-N2</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>Active filters keep filtering the table while the filter bar is collapsed</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>Collapse and Expand</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page on the All tab.
 3. Work orders exist in several statuses; a Status filter is applied (for example Estimate only) and the table is visibly filtered.</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>1. Collapse the filter bar with the funnel button.
 2. Look at the work order table.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>1. The table content does not change when the bar collapses - it still shows only the work orders matching the active filters.
 2. Hiding the bar only hides the chips; it does not remove or pause the filtering.</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 7 S7-R5</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>A filter combination with no matching work orders shows a no-results empty state instead of a blank table</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>Empty State</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page on the All tab.
 3. Work orders exist, but you can pick a filter combination that matches none of them (for example a customer plus a status that customer never has).</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>1. Apply the filter combination that matches no work orders.
 2. Look at the table area.</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>1. The table body is replaced by an empty state (not just a bare empty grid).
 2. The empty state shows a message indicating no results were found for the current filters.
 3. No error message or broken layout appears.</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 8 S8-R3</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>The filtered empty state offers a way to clear the filters, and using it brings the list back</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>Empty State</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page showing the filtered empty state (a filter combination matching no work orders is applied).</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>1. Read the empty state content.
 2. Click the clear-filters prompt/link inside the empty state.
 3. Look at the table and the chips.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>1. The empty state includes a prompt or link to clear the filters.
 2. Clicking it removes the active filters and the full work order list is shown again.
 3. The chips return to their default state.</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 8 S8-R4</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>The All tab shows all five filter chips, all working</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>Tab Behaviour</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page.</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>1. Click the All tab.
 2. Count the filter chips and click each one briefly.</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>1. All five chips are shown: Status, Customer, Lead Technician, Service Advisor, Asset on site.
 2. Each chip opens its dropdown and can be used.</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 9 S9-R1</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>On the Estimates tab the Status chip is shown greyed out, pre-filled with 'Status: Estimate', and cannot be changed; the other four filters work on top of the Estimates pre-filter</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>Tab Behaviour</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Estimate work orders exist for at least two different customers.
 3. You are on the Work Orders page.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1. Click the Estimates tab.
 2. Look at the filter bar.
@@ -3066,50 +3168,50 @@
 5. Look at the table.</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>1. The Status chip is shown but greyed out, already filled in as 'Status: Estimate', and cannot be clicked or changed - the tab already pre-filters the list to Estimate.
 2. Customer, Lead Technician, Service Advisor and Asset on site chips are shown and usable.
 3. After step 4 the table shows only that customer's ESTIMATE work orders - the customer filter narrows the pre-filtered Estimates list.</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 9 S9-R2; Story 2 S2-N1 (chip-hidden wording superseded by PO ruling 2026-07-17: chip shown disabled); §4 Key Decisions</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>On the Completed tab the Status chip is shown greyed out, pre-filled with the tab's status, and cannot be changed; the other four filters work on top of the Completed pre-filter</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>Tab Behaviour</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Complete work orders exist for at least two different customers.
 3. You are on the Work Orders page.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>1. Click the Completed tab.
 2. Look at the filter bar.
@@ -3118,148 +3220,196 @@
 5. Look at the table.</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>1. The Status chip is shown but greyed out, already filled in with this tab's status, and cannot be clicked or changed - the tab already pre-filters the list to Complete.
 2. Customer, Lead Technician, Service Advisor and Asset on site chips are shown and usable.
 3. After step 4 the table shows only that customer's COMPLETE work orders.</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 9 S9-R3; Story 2 S2-N2 (chip-hidden wording superseded by PO ruling 2026-07-17: chip shown disabled); §4 Key Decisions</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>On the My Work Orders tab all five filters are shown and narrow the already user-scoped list</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>Tab Behaviour</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Work orders assigned to you exist in at least two statuses, and other users' work orders also exist.
 3. You are on the Work Orders page.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1. Click the My Work Orders tab and count the chips.
 2. Open the Status filter and tick one status your work orders have.
 3. Look at the table.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>1. All five filter chips are shown on the My Work Orders tab.
 2. The table only ever shows work orders assigned to you (the tab's own scope stays).
 3. After step 2 it shows only YOUR work orders in the ticked status - the filters narrow the user-scoped list, they do not widen it to other users' work orders.</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 9 S9-R4; §4 Key Decisions (My Work Orders tab does not remove filters)</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>Filter selections survive tab switching; a Status selection hidden on Estimates/Completed comes back on the All tab</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>Tab Behaviour</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page on the All tab.
 3. A Status selection (for example Approved) and a Customer selection are active.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>1. Click the Estimates tab and look at the filter bar and the table.
 2. Click back to the All tab and look again.</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>1. On the Estimates tab the Status selection is not applied and not shown as an editable filter (incompatible with the tab), but the Customer selection is still shown and still filters the list.
 2. Back on the All tab the Status chip reappears with the SAME selection (Approved) still applied - the selection was retained in memory, not lost.
 3. The Customer selection is unchanged throughout.</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 9 S9-R5; S9-N1</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>First visit opens the Estimates tab; your last-used tab is remembered</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Tab Behaviour</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>1. You can sign in as a user who has never used the redesigned Work Orders page (no saved page choices for that account).</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>1. Sign in as that fresh user and open the Work Orders page.
+2. Note which tab is selected and the tab order.
+3. Switch to the All tab.
+4. Go to another area of the app and come back to the Work Orders page.</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>1. On the very first visit the Estimates tab is the selected one, even though All is the FIRST tab in the row (order and default are different on purpose).
+2. After switching to All and returning, the All tab is selected - the app remembers your last-used tab per account.</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); tech plan 2026-07-29 D10 (default tab = Estimates; last-used tab persists); not in the ratified product spec - confirmation requested</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>Leaving the Work Orders page and coming back restores the filters and the bar state exactly</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>Persistence</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with a Status and a Customer selection active and the filter bar expanded.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>1. Open one work order from the list (go to its detail page).
 2. Go back to the Work Orders page.
@@ -3267,487 +3417,638 @@
 4. Repeat the round-trip once more with the filter bar collapsed before leaving.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>1. After step 2 the same Status and Customer selections are still applied - chips active with the same values, table filtered the same way.
 2. The filter bar is still expanded (as you left it).
 3. After step 4 the filter bar comes back collapsed - the collapsed/expanded state is restored too.</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 10 S10-R1; Story 1 S1-R7</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Filter selections are remembered for you permanently - still applied after moving around the app and even after closing the browser and signing back in</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>Persistence</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Filters are applied on the Work Orders page (for example a status and a customer).</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>1. Visit several other areas of the app (Customers, Parts, Reports) and use them briefly.
 2. Return to the Work Orders page and look at the chips and the table.
 3. Close the browser completely (all windows).
 4. Open the browser again, sign in as the same person, and go to the Work Orders page.
-5. Look at the chips and the table.</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
+5. Look at the chips and the table.
+6. On a different computer (or a different browser profile), sign in as the same person and open the Work Orders page.</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>1. After moving around the app (step 2) the filter selections are still applied - you do not have to re-apply them.
-2. After closing the browser completely and signing back in (step 5) the same filter selections are still applied - the app remembers your filters for you permanently, not just for one browser session.</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
+2. After closing the browser completely and signing back in (step 5) the same filter selections are still applied - the app remembers your filters for you permanently, not just for one browser session.
+3. The same filter selections are applied on the other computer too - the filters are saved to your account, not to one computer or browser (to confirm live once built).</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 10 S10-R2 (session-only wording superseded by PO ruling 2026-07-17: permanent per-user persistence); §2/§4 (persist across navigation, saved per user)</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>Saved filters are per user: one user's filters do not appear for another user</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>Persistence</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>1. Two test users (A and B) can sign in to the same shop.
 2. User A has applied filters on the Work Orders page (for example Status: Approved).</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>1. As user B (separate login/browser profile), open the Work Orders page.
 2. Look at the filter chips and the table.
 3. As user B, apply a DIFFERENT filter (for example a customer), then re-check user A's view.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>1. User B does not see user A's filters - user B's page opens with user B's own (or no) filters.
 2. User B's new filter does not change what user A sees; each user keeps their own saved filter state.</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 10 S10-R3; §4 Key Decisions (saved per user)</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>A remembered filter value that no longer exists is silently dropped when you return</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>Persistence</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A throwaway ZZAUTOTEST customer exists and is selected in the Customer filter together with one real customer.
 3. You then navigate away and the ZZAUTOTEST customer is deleted (or otherwise removed) while you are off the page.</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>1. Return to the Work Orders page.
 2. Look at the Customer chip, the dropdown and the table.</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>1. The deleted customer is silently ignored - no error or warning appears.
 2. The Customer filter now reflects only the still-valid selection (the real customer).
 3. The table is filtered by the remaining valid selection only.</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 10 S10-N1</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Each page and tab remembers its own filters separately</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Persistence</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. The new filter bar has rolled out to the Parts views and to a report that has tabs (part of the same programme as the Work Orders filters).</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>1. On one Parts view (for example Inventory) apply a filter.
+2. Switch to a different Parts view (for example Purchase Orders).
+3. Return to the first Parts view.
+4. On a report with tabs, apply a filter on one tab, switch to another tab, then switch back.</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>1. The second Parts view does NOT show the first view's selections - each view keeps its own.
+2. Returning to the first view restores that view's own selections.
+3. Report tabs likewise keep separate filter choices, each remembered and restored on its own tab.</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); tech plan 2026-07-29 D20 (per-view/per-tab state scoping); spec v1.3 Key Decisions (export awaited)</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Filters saved before the redesign carry over after the update</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Persistence</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>1. In one browser, the account was used on the OLD Work Orders page with choices saved there (a tab, status selections, the asset-here toggle, column choices, sorting) BEFORE the redesign was installed.</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>1. In that same browser, open the updated app and go to the Work Orders page.
+2. Check the selected tab, the filter chips, the table columns and the sorting.
+3. Sign in as the same person on a DIFFERENT computer or browser and open the Work Orders page.</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>1. The old saved choices appear in the new filter bar on the first visit - the update does not lose them (old status choices show in the Status chip, the old asset-here choice shows as Asset on site: Yes, the old My-Work-Orders toggle maps to the My Work Orders tab, columns and sorting stay).
+2. Those carried-over choices are now saved to the account: the other computer shows them too.</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); tech plan 2026-07-29 section 4-3.3 (one-time browser-storage to account-preference migration)</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>Applying filters updates the page URL to reflect the active filter state</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>URL State and Shareable Links</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with no filters applied; note the current URL.</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>1. Apply a Status selection and a Customer selection.
 2. Look at the browser address bar.
 3. Clear all filters and look at the address bar again.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>1. After step 1 the URL changes to include the active filter state.
 2. After step 3 the filter part of the URL is removed again.</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 11 S11-R1</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>Opening a shared or bookmarked URL loads the Work Orders page with those filters already applied</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>URL State and Shareable Links</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You have copied a Work Orders URL that was produced with filters applied (for example Status: Approved + one customer).</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>1. Open the copied URL in a new browser tab (same signed-in user).
 2. Look at the chips and the table as the page loads.</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>1. The page opens with the same filters already applied - chips active with the same values.
 2. The table is already filtered accordingly on load (no need to re-apply anything).
 3. The same works from a saved bookmark.</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 11 S11-R2; §2 Feature Overview (share or bookmark)</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>A URL containing a filter value that no longer exists loads without that value</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>URL State and Shareable Links</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You saved a filtered Work Orders URL that includes a throwaway ZZAUTOTEST customer plus one real filter value.
 3. The ZZAUTOTEST customer has since been deleted.</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>1. Open the saved URL.
 2. Look at the chips and the table.</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>1. The page loads normally - no error.
 2. The deleted value is ignored; only the still-valid filter value is applied and shown on the chips.
 3. The table reflects only the valid filter.</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 11 S11-R3</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>A malformed filter URL loads the page unfiltered without showing an error</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>URL State and Shareable Links</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You have a valid filtered Work Orders URL to start from.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. Manually break the filter part of the URL (for example scramble the parameter values or insert nonsense text).
 2. Open the broken URL.
 3. Look at the page, the chips and the table.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>1. The Work Orders page loads normally.
 2. No filters are applied (chips in default state, full list shown) - the unrecognizable state is discarded.
 3. No error message or broken page appears.</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 11 S11-N1</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Opening a filtered link never overwrites your saved filters</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>URL State and Shareable Links</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in and have your OWN filters saved on the Work Orders page (for example one customer).
+2. You have a Work Orders link that carries a DIFFERENT filter state (made by another user or another browser).</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>1. Note your own saved filters on the Work Orders page.
+2. Open the shared link.
+3. While on the link view, change one more filter.
+4. Use the on-screen option to go back to your own saved filters.
+5. Leave the page and return to Work Orders normally (via the menu).</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>1. The link's filters apply for viewing only - the page shows the shared view.
+2. Changes made during the link visit are also NOT saved to your account.
+3. The go-back option restores your own saved filters and removes the filter part from the address bar.
+4. Returning normally later still shows your own saved filters, untouched by the link visit.</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); tech plan 2026-07-29 G7 (URL state runtime-only + back-to-saved affordance); spec closing-note conflict raised with the author (spec v1.3 export awaited)</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>On mobile the filter chips sit in a horizontally scrollable row below the tabs, starting with All Filters</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>Mobile Filters</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device (or a mobile-size browser window).
 2. You are on the Work Orders page.</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>1. Look at the row below the tab row (All, Estimates, Completed, My Work Orders).
 2. Swipe the chip row sideways.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>1. A filter chip row is shown below the tabs, starting with an 'All Filters' chip (with a funnel icon) followed by the individual filter chips (Status, Customer, Lead Technician, ...).
 2. The row scrolls horizontally - chips that do not fit are reachable by swiping.
 3. A right-edge arrow affordance indicates the row can be scrolled (per the design variant).</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 12 S12-R1</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>Tapping All Filters opens a bottom sheet listing every filter as an expandable row with an Apply filters button</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>Mobile Filters</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device.
 2. You are on the Work Orders page.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>1. Tap the 'All Filters' chip.
 2. Read the sheet from top to bottom.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>1. A bottom sheet slides up with a drag handle at the top, the centered title 'All Filters' and a close (x) button.
 2. It lists the five filters as expandable accordion rows, each with its icon, name and a down arrow: Status, Customer, Lead Technician, Service Advisor, Asset on site.
 3. A sticky blue 'Apply filters' button sits at the bottom of the sheet.</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 12 S12-R3</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>Selecting statuses in the mobile sheet and tapping Apply filters filters the list and counts on the sheet title</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>Mobile Filters</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device.
 2. You are on the Work Orders page on the All tab; work orders exist in several statuses.
 3. The 'All Filters' bottom sheet is open.</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>1. Tap the Status accordion row to expand it.
 2. Tick one or more statuses.
@@ -3755,99 +4056,99 @@
 4. Reopen the All Filters sheet and look at its title.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>1. Expanding Status reveals the same nine status checkboxes as desktop (Estimate, Approved, In progress, Review, Complete, Invoiced, Paid, Declined, Imported) plus 'Clear selection'.
 2. After 'Apply filters' the sheet closes and the work order list shows only the ticked statuses.
 3. The reopened sheet's title shows the applied-filter count, for example 'All Filters (1)', and the Status accordion header is highlighted with the selected values ticked.</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 12 S12-R2; S12-R3; Story 2 S2-R1</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>Tapping an individual filter chip on mobile opens that filter's own sheet with an 'Apply filter' button</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>Mobile Filters</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device.
 2. You are on the Work Orders page.</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>1. Tap the Status chip (not All Filters).
 2. Read the sheet.
 3. Tick a status and tap the bottom button.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>1. A bottom sheet opens for that single filter: its title row shows the filter's icon and name (for example 'Status') with a close (x) button - no accordion list of the other filters.
 2. The sheet shows only that filter's options (the nine status checkboxes plus 'Clear selection').
 3. The bottom button reads 'Apply filter' (singular); tapping it applies the selection and filters the list.</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 12 S12-R2; S12-R3</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>The mobile Customer filter has search, multi-select and removable tags, matching desktop</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>Mobile Filters</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device.
 2. You are on the Work Orders page; several customers exist.
 3. The All Filters sheet is open with the Customer accordion expanded.</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>1. Type part of a customer name in the 'Search customer' field and watch the list.
 2. Select two or three customers.
@@ -3855,7 +4156,7 @@
 4. Remove one customer with the x on its tag, then tap 'Apply filters'.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>1. The list narrows to matching names as you type.
 2. Each selected customer appears as a tag with an x in the input area, and its list row shows a checkmark.
@@ -3863,1392 +4164,1392 @@
 4. After 'Apply filters' the list shows only work orders of the remaining selected customers, and the sheet title counts the applied filters (for example 'All Filters (2)').</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 12 S12-R2; Story 3 S3-R2/R3/R5</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>The mobile Lead Technician and Service Advisor filters offer their search lists in the sheet</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>Mobile Filters</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device.
 2. You are on the Work Orders page; technicians and advisors exist.
 3. The All Filters sheet is open.</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>1. Expand the Lead Technician accordion row and look at its content.
 2. Collapse it, expand the Service Advisor row and look at its content.
 3. Select one name in either list and tap 'Apply filters'.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>1. The Lead Technician row opens with a 'Search technician' field and the technician list.
 2. The Service Advisor row opens with a 'Search advisor' field and the advisor list.
 3. Applying a selection filters the work order list just like on desktop.</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 12 S12-R2; Story 4 S4-R1; Story 5 S5-R1</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>The mobile Asset on site filter offers Yes/No with Clear selection in the sheet</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>Mobile Filters</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device.
 2. You are on the Work Orders page; work orders exist in both on-site states.
 3. The All Filters sheet is open.</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>1. Expand the Asset on site accordion row.
 2. Choose Yes and tap 'Apply filters'.
 3. Look at the list.</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>1. The Asset on site row opens showing the two options Yes and No plus 'Clear selection'.
 2. Only one option can be selected at a time.
 3. After applying, the list shows only work orders matching the chosen on-site state.</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 12 S12-R2; Story 6 S6-R1/R2/R3</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>Active chips and Clear filters behave on mobile the same way as on desktop</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>Mobile Filters</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device.
 2. You are on the Work Orders page with at least one filter applied via the sheet.</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>1. Look at the chip row after applying the filter.
 2. Look for a 'Clear filters' control while a filter is active.
 3. Use it and look at the chips and the list.</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>1. The chip for the applied filter shows the active state with the selected value(s), like on desktop.
 2. A 'Clear filters' control appears while at least one filter is active.
 3. Using it removes all active filters, the chips return to default and the full list comes back.</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 12 S12-R2; Story 7 S7-R1/R3; Story 8 S8-R1</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>Mobile has no collapse toggle: the filter chip row is always visible</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>Mobile Filters</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device.
 2. You are on the Work Orders page.</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>1. Look at the toolbar row (Search, sort icon, New Work Order button).
 2. Look for any control that would hide the filter chip row.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>1. There is no filter-bar collapse/expand (funnel) toggle on mobile.
 2. The filter chip row is always visible on the mobile Work Orders page.</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 12 S12-R4</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>Filters matching no work orders on mobile show the same empty state as desktop</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>Mobile Filters</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device.
 2. You are on the Work Orders page; work orders exist.</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>1. Apply a filter combination that matches no work orders (for example a customer plus a status that customer never has).
 2. Look at the list area.</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>1. The list shows the same no-results empty state as desktop, saying no results were found for the current filters.
 2. The empty state includes the prompt to clear filters.
 3. No error appears.</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 12 S12-N1; Story 8 S8-R3/R4</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>Parts Inventory page shows Bin Location, Category, Supply and Vendor filters</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>Parts Page Filters</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Parts area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>1. Open the Parts area and go to the Inventory page.
 2. Look at the filter buttons shown above the parts table.</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>1. The Inventory page shows four filter buttons in a row: Bin Location, Category, Supply and Vendor (each with a small icon and a down arrow).
 2. The table below shows the columns: Description, Part number, Tags, Category, Manufacturer, Vendor, Bin Location / Quantity and Action.
 3. A blue New Inventory Part button is shown at the top right.</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5 #1</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>Parts Part Sales page shows Status, Customer, Created by and Date filters</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>Parts Page Filters</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Parts area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>1. Open the Parts area and go to the Part Sales page.
 2. Look at the filter buttons shown above the part sales table.</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>1. The Part Sales page shows four filter buttons: Status, Customer, Created by and Date.
 2. The table shows the columns: Number, Status, Customer, Asset, VIN/Serial #, Created By, Total Price, Created On, Parts and Returns.
 3. A blue New Part Sale button is shown at the top right.</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5 #2</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>Parts Catalog page shows Manufacturer and Category filters</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>Parts Page Filters</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Parts area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>1. Open the Parts area and go to the Catalog page.
 2. Look at the filter buttons shown above the catalog table.</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>1. The Catalog page shows two filter buttons: Manufacturer and Category.
 2. The table shows the columns: (row checkbox), Description, Part Number, Tags and Category.
 3. A blue New Catalog Part button is shown at the top right.</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5 #3</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>Parts Returns tab shows Vendor, Category and Part Type filters</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>Parts Page Filters</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Parts area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>1. Open the Parts area and go to the Returns page.
 2. Make sure the Returns tab is selected (the page has Returns and Credits tabs).
 3. Look at the filter buttons shown above the returns table.</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>1. The Returns tab shows three filter buttons: Vendor, Category and Part Type.
 2. The table shows the columns: Work Order, Vendor Invoice, Vendor, Part Number, Description, Quantity, Cost, Total Cost, Return Reason, Status and Requested.
 3. A blue Create Return button is shown at the top right.</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5 #4</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>Parts Credits tab shows Vendor, Date and Processed by filters</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>Parts Page Filters</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Parts area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>1. Open the Parts area and go to the Returns page.
 2. Select the Credits tab.
 3. Look at the filter buttons shown above the credits table.</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>1. The Credits tab shows three filter buttons: Vendor, Date and Processed by.
 2. The table shows the columns: Credit Memo Number, Vendor, Work Order, Vendor Invoice, Date, Processed By, Total Cost and Notes.
 3. A blue Create Credit button is shown at the top right.</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5 #5</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>Parts Purchase Orders page shows Vendor, Status, Date and Ordered by filters</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>Parts Page Filters</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Parts area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>1. Open the Parts area and go to the Purchase Orders page.
 2. Look at the filter buttons shown above the purchase orders table.</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>1. The Purchase Orders page shows four filter buttons: Vendor, Status, Date and Ordered by.
 2. The table shows the columns: Work Order, Purchase Order Number, Vendor, Order Status, Created On, Ordered By, Total Price and Note.
 3. A blue New Purchase Order button is shown at the top right.</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5 #6</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>Vendor Invoices page shows Vendor, Invoice date, Date received, Received by</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>Parts Page Filters</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Parts area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>1. Open the Parts area and go to the Vendor Invoices page.
 2. Look at the filter buttons shown above the vendor invoices table.</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>1. The Vendor Invoices page shows four filter buttons: Vendor, Invoice date, Date received and Received by.
 2. The table shows the columns: Work Order, Invoice Number, Order Number, Received By, Vendor Name, Date Received, Invoice Date, Due Date, Total Cost and Note.
 3. There is no New button on this page (only the search and filter icons).</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5 #7</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>Parts Vendors list page shows Vendor and State/Province filters</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>Parts Page Filters</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Parts area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>1. Open the Parts area and go to the Vendors list page.
 2. Look at the filter buttons shown above the vendors table.</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>1. The Vendors page shows two filter buttons: Vendor and State/Province.
 2. The table shows the columns: Name, Telephone, Email, Address 1, Address 2, City, State/Province and Zip/Postal Code.
 3. A blue New Vendor button is shown at the top right.</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5 #8</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>Part Type filter opens a Core / Non Core list with Clear selection</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>Parts Page Filters</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Parts area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>1. On the Parts Returns tab, click the Part Type filter button.
 2. Look at the small menu that opens.</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>1. A small menu opens with two options: Core and Non Core.
 2. A Clear selection action is shown at the bottom of the menu.
 3. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (whether the options are single- or multi-select, and how the list is filtered after choosing).</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5 #9</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>Parts pages show the shared search and filter toolbar icons</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>Parts Page Filters</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Parts area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>1. Open any Parts list page (for example Inventory).
 2. Look at the small icons on the right side of the toolbar.</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>1. The toolbar shows a Search (magnifier) icon and a filter (funnel) icon on every Parts list page.
 2. Some pages also show a column/layout toggle icon (for example Inventory).
 3. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (what the funnel and column icons do).</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5 shared shell</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>Choosing a Parts filter narrows the list on that page</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>Parts Page Filters</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Parts area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>1. Open a Parts list page that has a filter button (for example Inventory).
 2. Open a filter button and choose one value.
 3. Watch the table below.</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>1. The table updates to show only the rows that match the chosen filter value.
 2. The chosen value is shown on the filter button so you can see what is applied.
 3. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (exactly which filters apply on which Parts page, the full option lists, and whether results update immediately).</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>Parts filters support multiple choices and can be cleared</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>Parts Page Filters</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Parts area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>1. Open a Parts filter button that shows a list of choices.
 2. Try selecting more than one choice.
 3. Use the Clear selection action, then look at the filter bar for a way to clear all filters.</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t>1. More than one value can be chosen inside a filter (to be checked live once available).
 2. Clear selection removes the choices for that one filter.
 3. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (whether multi-select, per-filter Clear selection, and an overall Clear filters action all work the same as on the Work Orders page).</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>Timesheet Activities report shows Staff, Date, Status, Modified by filters</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>Reports Page Filters</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Reports area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>1. Open the Reports area and go to the Timesheet Activities report.
 2. Look at the filter buttons shown above the report table.</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t>1. The Timesheet Activities report shows four filter buttons: Staff, Date, Status and Modified by.
 2. The table shows columns including Date, Employee, Work Order, Clock In Activity, Clock In, Clock Out, Total Hours, WO Hours, Internal Hours, Modified By and Modified Date/Time.</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #1</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>Payroll Timesheet report shows Employee and Date filters</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>Reports Page Filters</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Reports area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>1. Open the Reports area and go to the Timesheets (Payroll Timesheet) report.
 2. Look at the filter buttons shown above the report table.</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>1. The Payroll Timesheet report shows two filter buttons: Employee and Date.
 2. The table shows columns: Employee Name, Date, Clock In Time, Lunch, Clock Out Time and Hours.</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #2</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>Sales report shows Customer and Date filters</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>Reports Page Filters</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Reports area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>1. Open the Reports area and go to the Sales report.
 2. Look at the filter buttons shown above the report table.</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t>1. The Sales report shows two filter buttons: Customer and Date.
 2. The table shows columns including Invoice Date, Invoice, Customer, Inv. Hrs, Billing Efficiency, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Cost, Parts Margin, Profit and Subtotal.</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #3</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>Technician Efficiency report shows Customer, Technician and Date filters</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>Reports Page Filters</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Reports area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>1. Open the Reports area and go to the Technician Efficiency report.
 2. Look at the filter buttons shown above the report table.</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>1. The Technician Efficiency report shows three filter buttons: Customer, Technician and Date, on both the Invoiced and Completed tabs.
 2. The report has two view tabs: Invoiced and Completed; the same three filter buttons appear on each.
 3. 'Technician' is spelled correctly here (unlike the Work Orders list, see the spelling note).</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #4 and #5</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>Advisor Analysis report shows Customer, Date and Advisor filters</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>Reports Page Filters</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Reports area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>1. Open the Reports area and go to the Advisor Analysis report.
 2. Look at the filter buttons shown above the report table.</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t>1. The Advisor Analysis report shows three filter buttons: Customer, Date and Advisor.
 2. The table shows columns including Date, Invoice, Customer, Advisor, Days Open, Lines, Hrs Worked, Hrs Invoiced, Hrs Profit, Billing Efficiency, ELR, Parts Cost, Parts Invoiced, Parts Margin and Subtotal.</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #6</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>Shop Efficiency report shows only a Date filter</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>Reports Page Filters</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Reports area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>1. Open the Reports area and go to the Shop Efficiency report.
 2. Look at the filter buttons shown above the report table.</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>1. The Shop Efficiency report shows a single filter button: Date.
 2. The table shows columns: Total Clocked Hours, Total Invoiced Hours, Difference and Efficiency.</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #7</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr"/>
-      <c r="J93" s="2" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>Work in Progress report shows Status, Date and Customer filters</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>Reports Page Filters</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Reports area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>1. Open the Reports area and go to the Work in Progress report.
 2. Look at the filter buttons shown above the report table.</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t>1. The Work in Progress report shows three filter buttons: Status, Date and Customer.
 2. The table groups rows by status (Pending Authorization, In Progress, Ready To Invoice) with columns Sales, Cost, Profit $ and Profit %.</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #8</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="2" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>Sales Follow Up report shows Customer, Date and Contact filters</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>Reports Page Filters</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Reports area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>1. Open the Reports area and go to the Sales Follow Up report.
 2. Look at the filter buttons shown above the report table.</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr">
         <is>
           <t>1. The Sales Follow Up report shows three filter buttons: Customer, Date and Contact.
 2. The table shows columns: Customer, Sales Representative, Number Of Work Orders, Total Spend and Last Visit.</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #9</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr"/>
-      <c r="J95" s="2" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>Sales Tax Collected tab shows Date, Invoice Status and Customer filters</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>Reports Page Filters</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Reports area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>1. Open the Reports area and go to the Sales Tax (Collected tab) report.
 2. Look at the filter buttons shown above the report table.</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t>1. On the Sales Tax report's Collected tab, three filter buttons are shown: Date, Invoice Status and Customer.
 2. The report has two view tabs: Collected and All Tax Rates.
 2. Note: in the design the report body uses a sample placeholder table, so only the title, tabs and filter buttons are design-confirmed here; the real report columns come from Branko's PRD.</t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #10</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="2" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>Sales Tax All Tax Rates tab shows only an Invoice Status filter</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>Reports Page Filters</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Reports area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>1. Open the Reports area and go to the Sales Tax (All Tax Rates tab) report.
 2. Look at the filter buttons shown above the report table.</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t>1. On the Sales Tax report's All Tax Rates tab, a single filter button is shown: Invoice Status.
 2. Note: in the design the report body uses a sample placeholder table, so only the title, tabs and filter buttons are design-confirmed here; the real report columns come from Branko's PRD.</t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #11</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="2" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>A/R Aging Summary report shows Customer and Date filters</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>Reports Page Filters</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Reports area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>1. Open the Reports area and go to the A/R Aging Summary report.
 2. Look at the filter buttons shown above the report table.</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr">
         <is>
           <t>1. The A/R Aging Summary report shows two filter buttons: Customer and Date.
 2. A print icon is shown in the toolbar.
 2. Note: in the design the report body uses a sample placeholder table, so only the title, tabs and filter buttons are design-confirmed here; the real report columns come from Branko's PRD.</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #12</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>A/R Aging Detail shows Customer, Date, Location, Transaction Type filters</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>Reports Page Filters</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Reports area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>1. Open the Reports area and go to the A/R Aging Detail report.
 2. Look at the filter buttons shown above the report table.</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t>1. The A/R Aging Detail report shows four filter buttons: Customer, Date, Location and Transaction Type.
 2. A print icon is shown in the toolbar.
@@ -5256,383 +5557,383 @@
 2. Note: in the design the report body uses a sample placeholder table, so only the title, tabs and filter buttons are design-confirmed here; the real report columns come from Branko's PRD.</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #13</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr"/>
-      <c r="J99" s="2" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>A/R Aging Collection shows Customer, Date, Location, Transaction Type</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>Reports Page Filters</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Reports area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>1. Open the Reports area and go to the A/R Aging Collection report.
 2. Look at the filter buttons shown above the report table.</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t>1. The A/R Aging Collection report shows four filter buttons: Customer, Date, Location and Transaction Type.
 2. A print icon is shown in the toolbar.
 2. Note: in the design the report body uses a sample placeholder table, so only the title, tabs and filter buttons are design-confirmed here; the real report columns come from Branko's PRD.</t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #14</t>
         </is>
       </c>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>A/P Aging Summary report shows Vendor and Date filters</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>Reports Page Filters</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Reports area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>1. Open the Reports area and go to the A/P Aging Summary report.
 2. Look at the filter buttons shown above the report table.</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t>1. The A/P Aging Summary report shows two filter buttons: Vendor and Date.
 2. A print icon is shown in the toolbar.
 2. Note: in the design the report body uses a sample placeholder table, so only the title, tabs and filter buttons are design-confirmed here; the real report columns come from Branko's PRD.</t>
         </is>
       </c>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #15</t>
         </is>
       </c>
-      <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>A/P Aging Detail shows Vendor, Date, Location, Transaction Type filters</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>Reports Page Filters</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Reports area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>1. Open the Reports area and go to the A/P Aging Detail report.
 2. Look at the filter buttons shown above the report table.</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>1. The A/P Aging Detail report shows four filter buttons: Vendor, Date, Location and Transaction Type.
 2. A print icon is shown in the toolbar.
 2. Note: in the design the report body uses a sample placeholder table, so only the title, tabs and filter buttons are design-confirmed here; the real report columns come from Branko's PRD.</t>
         </is>
       </c>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #16</t>
         </is>
       </c>
-      <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="2" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>A/P Unpaid Invoices shows Vendor, Date, Location, Transaction Type filters</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>Reports Page Filters</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Reports area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>1. Open the Reports area and go to the A/P Unpaid Invoices report.
 2. Look at the filter buttons shown above the report table.</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
         <is>
           <t>1. The A/P Unpaid Invoices report shows four filter buttons: Vendor, Date, Location and Transaction Type.
 2. A print icon is shown in the toolbar.
 2. Note: in the design the report body uses a sample placeholder table, so only the title, tabs and filter buttons are design-confirmed here; the real report columns come from Branko's PRD.</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #17</t>
         </is>
       </c>
-      <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" s="2" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>Notes report shows Author, Date and Mention filters</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>Reports Page Filters</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Reports area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>1. Open the Reports area and go to the Notes report.
 2. Look at the filter buttons shown above the report table.</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t>1. The Notes report shows three filter buttons: Author, Date and Mention (the Mention button uses an @ icon).
 2. The toolbar also shows a search icon, a filter icon and a sort icon.
 3. Mention is a new filter type not on the Work Orders page — Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available.</t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #18</t>
         </is>
       </c>
-      <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="2" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>Reminders report shows only a Date filter</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>Reports Page Filters</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Reports area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>1. Open the Reports area and go to the Reminders report.
 2. Look at the filter buttons shown above the report table.</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr">
         <is>
           <t>1. The Reminders report shows a single filter button: Date.
 2. When no reminders match, the report shows the message 'There are no reminders for selected date range'.</t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #19</t>
         </is>
       </c>
-      <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="2" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+      <c r="I111" s="2" t="inlineStr"/>
+      <c r="J111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>IBS Batch Transactions report shows Customer, Date and Status filters</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>Reports Page Filters</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Reports area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>1. Open the Reports area and go to the IBS Batch Transactions report.
 2. Look at the filter buttons shown above the report table.</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr">
         <is>
           <t>1. The IBS Batch Transactions report shows three filter buttons: Customer, Date and Status.
 2. The report has three view tabs: Ready To Send, Sent and Payments.
 3. The table shows columns: (checkbox), Date, Type, No., Customer, Total, Balance and Status.</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #20</t>
         </is>
       </c>
-      <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+      <c r="I112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>QB Unexported report filters change per tab (Customer / Vendor / User)</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>Reports Page Filters</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Reports area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>1. Open the Reports area and go to the QB Unexported report.
 2. Look at the filter buttons shown above the report table.</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr">
         <is>
           <t>1. The QB Unexported report has three view tabs, and the first filter button changes per tab.
 2. On the Customers tab the filter buttons are Customer, Date and Type.
@@ -5641,239 +5942,639 @@
 5. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (option lists behind each button).</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #21, #22, #23</t>
         </is>
       </c>
-      <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="I113" s="2" t="inlineStr"/>
+      <c r="J113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>Choosing a Reports filter narrows the report results</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>Reports Page Filters</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Reports area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>1. Open the Reports area and go to the any (for example Sales) report.
 2. Look at the filter buttons shown above the report table.</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr">
         <is>
           <t>1. The report updates to show only the rows matching the chosen filter value, and the chosen value is shown on the filter button.
 2. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (exactly which filters apply on each report, the full option lists, and whether results update immediately).</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="2" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="I114" s="2" t="inlineStr"/>
+      <c r="J114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>New Reports filter types behave correctly (Location, Transaction Type, etc.)</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>Reports Page Filters</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Reports area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>1. Open the Reports area and go to the reports that use them (for example A/R Aging Detail, Notes) report.
 2. Look at the filter buttons shown above the report table.</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr">
         <is>
           <t>1. Each new filter type (Location, Transaction Type, Invoice Status, Type, User, Mention) opens a list of choices and filters the report by the choice.
 2. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (the exact choices, single- vs multi-select, and how each new filter type filters the report).</t>
         </is>
       </c>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6</t>
         </is>
       </c>
-      <c r="I109" s="2" t="inlineStr"/>
-      <c r="J109" s="2" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="I115" s="2" t="inlineStr"/>
+      <c r="J115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Date range filter: results update when both start and end dates are picked</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Reports Page Filters</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. The new filter bar has rolled out to a page with a Date filter chip (a report, or a Parts page with a date column).
+3. Records exist inside and outside the date range you will pick.</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>1. Click the Date filter chip.
+2. Look at the panel that opens.
+3. Pick a start date only, and watch the results.
+4. Pick the end date.
+5. Look at the results and the chip.</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>1. A start/end date picker opens - there are NO preset ranges (no 'Last 30 days' shortcuts) and NO pre-filled default range.
+2. After only the start date, the results do not change yet.
+3. As soon as the second date is picked, the results update immediately to show only records inside the range.
+4. Only one date range can be active at a time on that chip, and the chip shows the active range.</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); tech plan 2026-07-29 D19 (date-range chip: no presets, no default, applies on second date); spec v1.3 Parts + Reports sections (export awaited)</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr"/>
+      <c r="J116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Page toolbar Search expands in place and narrows the list as you type</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Page Search Toolbar</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Work Orders page with several work orders listed.</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>1. Find the Search control in the page toolbar (a magnifier icon with the word Search).
+2. Click it.
+3. Type part of a work order's text (for example part of a customer or asset name).
+4. Clear the text with the round x in the box.
+5. Click somewhere else on the page while the box is EMPTY.
+6. Expand it again, type text, and click somewhere else.</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>1. The control expands in place into a small search box inviting you to type (engineering copy: 'Type to search').
+2. The list narrows as you type, after a brief pause - and ONLY this page's list changes, nothing else in the app.
+3. The round x clears the text and the full list returns.
+4. Clicking away with an empty box collapses it back to the Search button; with text in it, the box stays open.</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); tech plan 2026-07-29 D18; spec v1.3 S13-R1..R7, S13-R9, S13-R15 (export awaited)</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr"/>
+      <c r="J117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Page search combines with filters and is cleared separately</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Page Search Toolbar</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Work Orders page with work orders for several customers and statuses.</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>1. Apply one filter (for example a Status).
+2. Type a search term in the page search box.
+3. Clear ONLY the search (the round x).
+4. Re-type the search, then clear ONLY the filter.</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>1. With both active, the results match the filter AND the search together (both narrow the list at once).
+2. Clearing the search keeps the filter applied.
+3. Clearing the filter keeps the search applied - each is cleared by its own control without wiping the other.</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); tech plan 2026-07-29 D18; spec v1.3 S13-R10/R13 + S8-R5 (export awaited)</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr"/>
+      <c r="J118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>The page search text is remembered and restored like filters</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Page Search Toolbar</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Work Orders page.</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>1. Type a search term that matches some work orders.
+2. Go to another area of the app and come back to the Work Orders page.
+3. Now type a search term that matches NOTHING, leave the page, and come back again.</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>1. The search box comes back with your text still in it and the list still narrowed by it - just like the filters.
+2. A remembered search that matches nothing shows the no-results empty state - the remembered text is NOT silently thrown away.</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); tech plan 2026-07-29 D18; spec v1.3 S10-R4/R5, S10-N2 (export awaited)</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr"/>
+      <c r="J119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>The search term is part of the shareable page link</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Page Search Toolbar</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Work Orders page.</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>1. Type a search term and copy the page address.
+2. Open the copied address in a fresh tab.
+3. Hand-edit the search part of the address into something malformed and load it.</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>1. The address contains the search term after step 1.
+2. The fresh tab opens with the search box filled and the list already narrowed.
+3. The malformed part is ignored - the page loads cleanly without an error.
+4. A search arriving via a link is view-only, the same as filters from a link - it does not overwrite your own remembered search.</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); tech plan 2026-07-29 D18 + G7; spec v1.3 S11-R4/R5, S11-N2 (export awaited)</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr"/>
+      <c r="J120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>On mobile the search expands in the toolbar and buttons make room</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Page Search Toolbar</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a mobile device.
+2. You are on the Work Orders page.</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>1. Tap the Search control in the page toolbar.
+2. Type a term and watch the list.
+3. Visit a page that has several small icon-only toolbar buttons (for example Parts Inventory or Purchase Orders) and look at its toolbar.</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>1. The search expands inline inside the toolbar - no separate popup window opens.
+2. The list narrows as you type, same as desktop.
+3. To make room, the page's main button no longer stretches full-width, and pages with two or more small icon buttons collapse them into a single 'more' menu.</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); tech plan 2026-07-29 D21; spec v1.3 S13-R16..R21 (export awaited)</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr"/>
+      <c r="J121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Every list page keeps its own search box (Parts, Reports, detail tabs)</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Page Search Toolbar</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. The page-search rollout has shipped (same programme as the Work Orders filters).</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>1. Visit several list surfaces: a Parts view (for example Inventory), a report, a customer's Notes tab on the customer page, and any pop-up list that used to be searchable.
+2. On each, look for that surface's own search box and use it.</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>1. Every list surface that could be text-searched before still offers its own search control - no list silently lost its search.
+2. Each search box narrows only its own list, not any other page.</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); tech plan 2026-07-29 Phase 9.1 (built-in table search, opt-out); spec v1.3 S13-R22 + S14-R5/R6 (export awaited)</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr"/>
+      <c r="J122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>The top navigation search no longer filters page lists</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Page Search Toolbar</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Work Orders page with several work orders listed.</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>1. Type a term into the TOP NAVIGATION search (the app-wide search at the top), not the page's own search box.
+2. Watch the Work Orders list while typing.
+3. Repeat on the Parts Inventory page.
+4. Pick one of the results offered in the navigation search's dropdown.</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>1. The page list does NOT narrow while you type in the navigation search - only its dropdown of matching records appears.
+2. The same holds on the other pages checked.
+3. Picking a dropdown result still takes you to that record - the navigation search keeps its find-and-open role.</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); tech plan 2026-07-29 Phase 9 (search decoupling); spec v1.3 Story 14 S14-R2/R3 (export awaited)</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr"/>
+      <c r="J123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>Page search opens with the 'Search or ask a question' box</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>Page Search (Command-K)</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Some sample work orders, customers, assets, parts and vendors exist.</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>1. From anywhere in the app, open the page search (the Search box in the top bar, or press Command-K / Ctrl-K).
 2. Look at the search panel that opens.</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr">
         <is>
           <t>1. A search panel opens with an empty search box at the top.
 2. The box shows the placeholder text 'Search or ask a question' with a magnifier icon on the left and a clear (X) button on the right.
 3. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (whether 'ask a question' means an AI search — this is out of scope for now).</t>
         </is>
       </c>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
         </is>
       </c>
-      <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="2" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+      <c r="I124" s="2" t="inlineStr"/>
+      <c r="J124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>Page search shows entity tabs All, Work Orders, Customers, Assets, Parts...</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
         <is>
           <t>Page Search (Command-K)</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Some sample work orders, customers, assets, parts and vendors exist.</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>1. Open the page search panel.
 2. Look at the row of tabs under the search box.</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr">
         <is>
           <t>1. A row of tabs is shown: All, Work Orders, Customers, Assets, Parts, Vendors and Part Sales.
 2. The All tab is selected by default.
 3. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (whether choosing a tab limits results to that type only).</t>
         </is>
       </c>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
         </is>
       </c>
-      <c r="I111" s="2" t="inlineStr"/>
-      <c r="J111" s="2" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+      <c r="I125" s="2" t="inlineStr"/>
+      <c r="J125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>Typing a term shows grouped results with counts and highlighting</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>Page Search (Command-K)</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Some sample work orders, customers, assets, parts and vendors exist.</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>1. Open the page search panel.
 2. Type a few letters (for example 'Fib') into the search box.
 3. Look at the results.</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr">
         <is>
           <t>1. Results are grouped by type with a count next to each group heading, for example 'Work orders (2)', 'Customers (2)', 'Vendors (1)', 'Assets (2)', 'Parts (1)'.
 2. The matching part of each result is highlighted in yellow.
@@ -5881,541 +6582,592 @@
 4. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (how matching works — exact vs fuzzy — and the ranking order).</t>
         </is>
       </c>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
         </is>
       </c>
-      <c r="I112" s="2" t="inlineStr"/>
-      <c r="J112" s="2" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+      <c r="I126" s="2" t="inlineStr"/>
+      <c r="J126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>Recent searches are shown grouped by Today, Yesterday, Past week...</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>Page Search (Command-K)</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Some sample work orders, customers, assets, parts and vendors exist.</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>1. Open the page search panel without typing anything.
 2. Look at the list shown under the tabs.</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr">
         <is>
           <t>1. A list of recent items is shown, grouped under headings: Today, Yesterday, Past week and Past 30 days.
 2. Each item shows a type icon, its name and a short detail line (for example a customer address or a date).
 3. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (how many recent items are kept and how long they persist).</t>
         </is>
       </c>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
         </is>
       </c>
-      <c r="I113" s="2" t="inlineStr"/>
-      <c r="J113" s="2" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+      <c r="I127" s="2" t="inlineStr"/>
+      <c r="J127" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>Re-opening page search keeps the last typed text and its results</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>Page Search (Command-K)</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Some sample work orders, customers, assets, parts and vendors exist.</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>1. Open the page search and type a term (for example 'Fibridge').
 2. Close the panel, then open it again.
 3. Look at the search box and the results.</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr">
         <is>
           <t>1. The previous search text is still in the box (shown selected/highlighted) and its results are shown.
 2. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (whether the last search is remembered per person and for how long — this is the 'persisting search' state).</t>
         </is>
       </c>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
         </is>
       </c>
-      <c r="I114" s="2" t="inlineStr"/>
-      <c r="J114" s="2" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+      <c r="I128" s="2" t="inlineStr"/>
+      <c r="J128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>Hovering a search result shows quick-action buttons</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>Page Search (Command-K)</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Some sample work orders, customers, assets, parts and vendors exist.</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>1. Open the page search panel (recent items or results shown).
 2. Move the mouse over a result row.
 3. Look at the right side of that row.</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr">
         <is>
           <t>1. Quick-action buttons appear on the row, depending on the result type — for example 'Add new line' on a work order, 'New work order' on an asset or customer, 'Add part' on a part sale, 'Add contact' on a vendor and 'Add to work order' on a part.
 2. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (exactly which quick actions show for which result type, and what each one does).</t>
         </is>
       </c>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
         </is>
       </c>
-      <c r="I115" s="2" t="inlineStr"/>
-      <c r="J115" s="2" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+      <c r="I129" s="2" t="inlineStr"/>
+      <c r="J129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>Page search shows keyboard hints and supports keyboard navigation</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t>Page Search (Command-K)</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Some sample work orders, customers, assets, parts and vendors exist.</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>1. Open the page search panel.
 2. Look at the bar along the bottom of the panel.
 3. Use the up/down arrow keys, Enter and Esc.</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr">
         <is>
           <t>1. The bottom bar shows keyboard hints: up/down arrows labelled 'Navigate', the Enter key labelled 'Select', and 'Close esc'.
 2. Arrow keys move the highlight between results, Enter opens the highlighted result, and Esc closes the panel (to be checked live once available).
 3. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (exact keyboard behaviour).</t>
         </is>
       </c>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
         </is>
       </c>
-      <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="2" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+      <c r="I130" s="2" t="inlineStr"/>
+      <c r="J130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>Page search results include a Refresh action</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
         <is>
           <t>Page Search (Command-K)</t>
         </is>
       </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Some sample work orders, customers, assets, parts and vendors exist.</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>1. Open the page search and type a term so grouped results appear.
 2. Look at the top right of the results area.</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr">
         <is>
           <t>1. A 'Refresh' link is shown at the top right of the results.
 2. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (what Refresh reloads and when it is shown).</t>
         </is>
       </c>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
         </is>
       </c>
-      <c r="I117" s="2" t="inlineStr"/>
-      <c r="J117" s="2" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+      <c r="I131" s="2" t="inlineStr"/>
+      <c r="J131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>Page search scope belongs to Filters or Global Search (to decide)</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
         <is>
           <t>Page Search (Command-K)</t>
         </is>
       </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Some sample work orders, customers, assets, parts and vendors exist.</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>1. Review where the page search / Command-K component is owned for testing.
 2. Compare against the Global Search project's existing cases.</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr">
         <is>
           <t>1. The page-search component is agreed to belong to either the Filters test suite or the Global Search test suite, not both.
 2. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (product/QA decision on which project owns page search).</t>
         </is>
       </c>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
         </is>
       </c>
-      <c r="I118" s="2" t="inlineStr"/>
-      <c r="J118" s="2" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+      <c r="I132" s="2" t="inlineStr"/>
+      <c r="J132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>The work order list request carries the active filter selections</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t>API — Work Orders List Filtering</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser with developer tools open on the Network tab.
 2. You are on the Work Orders page with no filters applied.</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>1. Apply a Status selection and a Customer selection in the filter bar.
 2. In the Network tab, find the work order list request the page sends after the change.
 3. Inspect the request's parameters.</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr">
         <is>
           <t>1. The list request includes the active filter selections as request parameters (status values and customer identifiers).
 2. The request succeeds (HTTP 200).
 3. The response contains only work orders matching the filters - the filtering is done by the backend, not just hidden client-side.</t>
         </is>
       </c>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 2 S2-R2; Story 3 S3-R6 (backend view)</t>
         </is>
       </c>
-      <c r="I119" s="2" t="inlineStr"/>
-      <c r="J119" s="2" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+      <c r="I133" s="2" t="inlineStr"/>
+      <c r="J133" s="2" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>A combined multi-filter request returns only work orders matching all filters, any value within each filter</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
         <is>
           <t>API — Work Orders List Filtering</t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with developer tools open on the Network tab.
 2. Seeded ZZAUTOTEST work orders exist: customer A with an Estimate and an Approved work order, customer B with an Estimate work order.</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>1. On the Work Orders page apply Status = Estimate + Approved and Customer = customer A.
 2. Capture the resulting list request and response.</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr">
         <is>
           <t>1. One request carries both filters together (both statuses and the customer).
 2. The response returns customer A's Estimate and Approved work orders only.
 3. Customer B's work orders are absent - the customer filter and status filter both restrict the result, while the two statuses combine as either-or.</t>
         </is>
       </c>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 2 S2-R2; Story 3 S3-R6; Story 8 S8-R3 (backend view)</t>
         </is>
       </c>
-      <c r="I120" s="2" t="inlineStr"/>
-      <c r="J120" s="2" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+      <c r="I134" s="2" t="inlineStr"/>
+      <c r="J134" s="2" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>A list request with a deleted or unknown filter value is handled without a server error</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t>API — Work Orders List Filtering</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
+      <c r="C135" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in and can replay/edit the work order list request (developer tools or an API client).
 2. You have a captured filtered list request, and one of its filter values has since been deleted (for example a removed ZZAUTOTEST customer) or is a made-up identifier.</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>1. Send the list request containing the no-longer-existing (or made-up) filter value.
 2. Inspect the HTTP status and the response body.</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr">
         <is>
           <t>1. The backend does not fail with a server error (no HTTP 5xx).
 2. The response is a normal, successful list response - the invalid value is ignored or simply matches nothing.
 3. Any still-valid filter values in the same request are applied normally.</t>
         </is>
       </c>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 10 S10-N1; Story 11 S11-R3</t>
         </is>
       </c>
-      <c r="I121" s="2" t="inlineStr"/>
-      <c r="J121" s="2" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+      <c r="I135" s="2" t="inlineStr"/>
+      <c r="J135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>A list request with malformed filter parameters does not produce a server error</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>API — Work Orders List Filtering</t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr">
+      <c r="C136" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in and can replay/edit the work order list request.
 2. You have a captured filtered list request to tamper with.</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>1. Corrupt the filter parameters (wrong types, scrambled values, nonsense text) and send the request.
 2. Inspect the HTTP status and the response body.
 3. Also open the equally malformed page URL in the browser and watch the page.</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr">
         <is>
           <t>1. The backend responds gracefully - no HTTP 5xx / crash; either a normal (unfiltered or empty) list or a clean validation response.
 2. In the browser the page still loads without filters and without an error message, matching the malformed-URL requirement.</t>
         </is>
       </c>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 11 S11-N1</t>
         </is>
       </c>
-      <c r="I122" s="2" t="inlineStr"/>
-      <c r="J122" s="2" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+      <c r="I136" s="2" t="inlineStr"/>
+      <c r="J136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>A filter combination matching nothing returns a successful empty list, not an error</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>API — Work Orders List Filtering</t>
         </is>
       </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with developer tools open on the Network tab.
 2. A filter combination is known to match no work orders (for example a seeded customer plus a status they never have).</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>1. Apply that filter combination on the Work Orders page.
 2. Capture the list request and response.</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr">
         <is>
           <t>1. The request succeeds (HTTP 200).
 2. The response contains an empty result set (zero work orders) - an empty match is a normal outcome, not an error.
 3. The page renders the no-results empty state from this response.</t>
         </is>
       </c>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 8 S8-R3; Story 2 S2-N3</t>
         </is>
       </c>
-      <c r="I123" s="2" t="inlineStr"/>
-      <c r="J123" s="2" t="inlineStr"/>
+      <c r="I137" s="2" t="inlineStr"/>
+      <c r="J137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Saved-filters service round-trip: save, reload, and per-user isolation</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>API — Work Orders List Filtering</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser with developer tools open on the Network tab.
+2. A second user account is available.</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>1. On the Work Orders page, change a filter and watch the Network tab for the save request the page sends shortly after.
+2. Reload the page and find the load request for the saved page state.
+3. Sign in as the second user (different browser/profile) and open the Work Orders page.
+4. With an API client (or by editing the request), ask the saved-state service for a page key that was never saved.</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>1. Changing a filter sends a save (PUT) to the per-user page-preferences service carrying the page's state, and it succeeds (HTTP 200).
+2. On reload the page requests the saved state back (GET, HTTP 200) and applies it - the filters return without you redoing them.
+3. The second user does NOT receive the first user's saved state - each account's saved filters are isolated.
+4. Asking for a never-saved key returns success with an empty value, not an error page.</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); tech plan 2026-07-29 section 4-1.3 (GET/PUT /api/users/me/preferences/{pageKey}); spec v1.3 S10 per-user persistence (export awaited)</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr"/>
+      <c r="J138" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/filters-v1-testrail-import.xlsx
+++ b/testrail-import/filters-v1-testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J138"/>
+  <dimension ref="A1:J110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -558,7 +558,8 @@
       <c r="E3" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. You are on the Work Orders page with the filter bar visible.</t>
+2. You are on the Work Orders page with the filter bar visible.
+3. You are on the All tab (on the Estimates and Completed tabs the Status chip is shown greyed out and already filled in, so the chips do not all look the same there).</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -2195,8 +2196,7 @@
       <c r="G36" s="2" t="inlineStr">
         <is>
           <t>1. The table shows only work orders whose asset is currently on site.
-2. Work orders whose asset is not on site are hidden.
-3. Choosing No instead shows only the not-on-site work orders.</t>
+2. Work orders whose asset is not on site are hidden.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -4419,7 +4419,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Parts Inventory page shows Bin Location, Category, Supply and Vendor filters</t>
+          <t>Every Parts list page shows its designed filter buttons</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4445,20 +4445,35 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>1. Open the Parts area and go to the Inventory page.
-2. Look at the filter buttons shown above the parts table.</t>
+          <t>1. Open the Parts area and go to the Inventory page, and look at the filter buttons shown above the table.
+2. Go to the Part Sales page and look at the filter buttons.
+3. Go to the Catalog page and look at the filter buttons.
+4. Go to the Returns page, make sure the Returns tab is selected, and look at the filter buttons.
+5. Select the Credits tab on the same page and look at the filter buttons.
+6. Go to the Purchase Orders page and look at the filter buttons.
+7. Go to the Vendor Invoices page and look at the filter buttons.
+8. Go to the Vendors list page and look at the filter buttons.
+9. On any one of these pages, look at the small icons on the right-hand side of the toolbar.</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>1. The Inventory page shows four filter buttons in a row: Bin Location, Category, Supply and Vendor (each with a small icon and a down arrow).
-2. The table below shows the columns: Description, Part number, Tags, Category, Manufacturer, Vendor, Bin Location / Quantity and Action.
-3. A blue New Inventory Part button is shown at the top right.</t>
+          <t>1. Inventory shows four filter buttons: Bin Location, Category, Supply and Vendor.
+2. Part Sales shows four filter buttons: Status, Customer, Created by and Date.
+3. Catalog shows two filter buttons: Manufacturer and Category.
+4. The Returns tab shows three filter buttons: Vendor, Category and Part Type.
+5. The Credits tab shows three filter buttons: Vendor, Date and Processed by.
+6. Purchase Orders shows four filter buttons: Vendor, Status, Date and Ordered by.
+7. Vendor Invoices shows four filter buttons: Vendor, Invoice date, Date received and Received by.
+8. The Vendors list page shows two filter buttons: Vendor and State/Province. Note: the developers have not been given a design for the Vendors page filters yet, so this page may not have them — write down what you actually see instead of failing the whole test.
+9. On every page above, each filter button shows a small icon, the filter name and a down arrow.
+10. Every Parts list page also shows a Search (magnifier) icon and a filter (funnel) icon in the toolbar; some pages (for example Inventory) also show a column/layout toggle icon.
+11. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (which filters actually apply on each Parts page, their full option lists, and what the funnel and column icons do).</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5 #1</t>
+          <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5 #1-#8 and §B.5 shared shell</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr"/>
@@ -4467,7 +4482,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Parts Part Sales page shows Status, Customer, Created by and Date filters</t>
+          <t>Part Type filter opens a Core / Non Core list with Clear selection</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4492,1587 +4507,328 @@
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Parts area and go to the Part Sales page.
-2. Look at the filter buttons shown above the part sales table.</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>1. The Part Sales page shows four filter buttons: Status, Customer, Created by and Date.
-2. The table shows the columns: Number, Status, Customer, Asset, VIN/Serial #, Created By, Total Price, Created On, Parts and Returns.
-3. A blue New Part Sale button is shown at the top right.</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5 #2</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>Parts Catalog page shows Manufacturer and Category filters</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>Parts Page Filters</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. You are on the Parts area of the app with some sample data present.</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Parts area and go to the Catalog page.
-2. Look at the filter buttons shown above the catalog table.</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>1. The Catalog page shows two filter buttons: Manufacturer and Category.
-2. The table shows the columns: (row checkbox), Description, Part Number, Tags and Category.
-3. A blue New Catalog Part button is shown at the top right.</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5 #3</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>Parts Returns tab shows Vendor, Category and Part Type filters</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>Parts Page Filters</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. You are on the Parts area of the app with some sample data present.</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Parts area and go to the Returns page.
-2. Make sure the Returns tab is selected (the page has Returns and Credits tabs).
-3. Look at the filter buttons shown above the returns table.</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>1. The Returns tab shows three filter buttons: Vendor, Category and Part Type.
-2. The table shows the columns: Work Order, Vendor Invoice, Vendor, Part Number, Description, Quantity, Cost, Total Cost, Return Reason, Status and Requested.
-3. A blue Create Return button is shown at the top right.</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5 #4</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>Parts Credits tab shows Vendor, Date and Processed by filters</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>Parts Page Filters</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. You are on the Parts area of the app with some sample data present.</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Parts area and go to the Returns page.
-2. Select the Credits tab.
-3. Look at the filter buttons shown above the credits table.</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>1. The Credits tab shows three filter buttons: Vendor, Date and Processed by.
-2. The table shows the columns: Credit Memo Number, Vendor, Work Order, Vendor Invoice, Date, Processed By, Total Cost and Notes.
-3. A blue Create Credit button is shown at the top right.</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5 #5</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>Parts Purchase Orders page shows Vendor, Status, Date and Ordered by filters</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>Parts Page Filters</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. You are on the Parts area of the app with some sample data present.</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Parts area and go to the Purchase Orders page.
-2. Look at the filter buttons shown above the purchase orders table.</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t>1. The Purchase Orders page shows four filter buttons: Vendor, Status, Date and Ordered by.
-2. The table shows the columns: Work Order, Purchase Order Number, Vendor, Order Status, Created On, Ordered By, Total Price and Note.
-3. A blue New Purchase Order button is shown at the top right.</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5 #6</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>Vendor Invoices page shows Vendor, Invoice date, Date received, Received by</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>Parts Page Filters</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. You are on the Parts area of the app with some sample data present.</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Parts area and go to the Vendor Invoices page.
-2. Look at the filter buttons shown above the vendor invoices table.</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="inlineStr">
-        <is>
-          <t>1. The Vendor Invoices page shows four filter buttons: Vendor, Invoice date, Date received and Received by.
-2. The table shows the columns: Work Order, Invoice Number, Order Number, Received By, Vendor Name, Date Received, Invoice Date, Due Date, Total Cost and Note.
-3. There is no New button on this page (only the search and filter icons).</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5 #7</t>
-        </is>
-      </c>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>Parts Vendors list page shows Vendor and State/Province filters</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>Parts Page Filters</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. You are on the Parts area of the app with some sample data present.</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Parts area and go to the Vendors list page.
-2. Look at the filter buttons shown above the vendors table.</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t>1. The Vendors page shows two filter buttons: Vendor and State/Province.
-2. The table shows the columns: Name, Telephone, Email, Address 1, Address 2, City, State/Province and Zip/Postal Code.
-3. A blue New Vendor button is shown at the top right.</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5 #8</t>
-        </is>
-      </c>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>Part Type filter opens a Core / Non Core list with Clear selection</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>Parts Page Filters</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. You are on the Parts area of the app with some sample data present.</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>1. On the Parts Returns tab, click the Part Type filter button.
 2. Look at the small menu that opens.</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>1. A small menu opens with two options: Core and Non Core.
 2. A Clear selection action is shown at the bottom of the menu.
 3. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (whether the options are single- or multi-select, and how the list is filtered after choosing).</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5 #9</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>Parts pages show the shared search and filter toolbar icons</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Choosing a Parts filter narrows the list on that page</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>Parts Page Filters</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Parts area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>1. Open any Parts list page (for example Inventory).
-2. Look at the small icons on the right side of the toolbar.</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>1. The toolbar shows a Search (magnifier) icon and a filter (funnel) icon on every Parts list page.
-2. Some pages also show a column/layout toggle icon (for example Inventory).
-3. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (what the funnel and column icons do).</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5 shared shell</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>Choosing a Parts filter narrows the list on that page</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>Parts Page Filters</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. You are on the Parts area of the app with some sample data present.</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>1. Open a Parts list page that has a filter button (for example Inventory).
 2. Open a filter button and choose one value.
 3. Watch the table below.</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>1. The table updates to show only the rows that match the chosen filter value.
 2. The chosen value is shown on the filter button so you can see what is applied.
 3. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (exactly which filters apply on which Parts page, the full option lists, and whether results update immediately).</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>Parts filters support multiple choices and can be cleared</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>Parts Page Filters</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Parts area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>1. Open a Parts filter button that shows a list of choices.
 2. Try selecting more than one choice.
 3. Use the Clear selection action, then look at the filter bar for a way to clear all filters.</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>1. More than one value can be chosen inside a filter (to be checked live once available).
 2. Clear selection removes the choices for that one filter.
 3. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (whether multi-select, per-filter Clear selection, and an overall Clear filters action all work the same as on the Work Orders page).</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr"/>
-      <c r="J93" s="2" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>Timesheet Activities report shows Staff, Date, Status, Modified by filters</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Every report page shows its designed filter buttons</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>Reports Page Filters</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Reports area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Reports area and go to the Timesheet Activities report.
-2. Look at the filter buttons shown above the report table.</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t>1. The Timesheet Activities report shows four filter buttons: Staff, Date, Status and Modified by.
-2. The table shows columns including Date, Employee, Work Order, Clock In Activity, Clock In, Clock Out, Total Hours, WO Hours, Internal Hours, Modified By and Modified Date/Time.</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #1</t>
-        </is>
-      </c>
-      <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="2" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>Payroll Timesheet report shows Employee and Date filters</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Reports area and go to the Timesheet Activities report, and look at the filter buttons shown above the report table.
+2. Go to the Timesheets (Payroll Timesheet) report and look at the filter buttons.
+3. Go to the Sales report and look at the filter buttons.
+4. Go to the Technician Efficiency report. Look at the filter buttons on the Invoiced tab, then open the Completed tab and look at them again.
+5. Go to the Advisor Analysis report and look at the filter buttons.
+6. Go to the Shop Efficiency report and look at the filter buttons.
+7. Go to the Work in Progress report and look at the filter buttons.
+8. Go to the Sales Follow Up report and look at the filter buttons.
+9. Go to the Sales Tax report. Look at the filter buttons on the Collected tab, then open the All Tax Rates tab and look at them again.
+10. Go to the A/R Aging Summary report, then the A/R Aging Detail report, then the A/R Aging Collection report, looking at the filter buttons on each.
+11. Go to the A/P Aging Summary report, then the A/P Aging Detail report, then the A/P Unpaid Invoices report, looking at the filter buttons on each.
+12. Go to the Notes report and look at the filter buttons and the toolbar icons.
+13. Go to the Reminders report and look at the filter buttons.
+14. Go to the IBS Batch Transactions report and look at the filter buttons and the view tabs.
+15. Go to the QB Unexported report. Look at the filter buttons on the Customers tab, then switch to the Vendors tab, then to the Journal Entries tab, looking at the filter buttons on each.</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>1. Timesheet Activities shows four filter buttons: Staff, Date, Status and Modified by.
+2. Payroll Timesheet shows two filter buttons: Employee and Date.
+3. Sales shows two filter buttons: Customer and Date.
+4. Technician Efficiency shows three filter buttons: Customer, Technician and Date — the same three on both of its view tabs, Invoiced and Completed. 'Technician' is spelled correctly here.
+5. Advisor Analysis shows three filter buttons: Customer, Date and Advisor.
+6. Shop Efficiency shows a single filter button: Date.
+7. Work in Progress shows three filter buttons: Status, Date and Customer.
+8. Sales Follow Up shows three filter buttons: Customer, Date and Contact.
+9. Sales Tax has two view tabs: on the Collected tab it shows three filter buttons — Date, Invoice Status and Customer; on the All Tax Rates tab it shows a single filter button — Invoice Status.
+10. A/R Aging Summary shows two filter buttons: Customer and Date.
+11. A/R Aging Detail shows four filter buttons: Customer, Date, Location and Transaction Type.
+12. A/R Aging Collection shows four filter buttons: Customer, Date, Location and Transaction Type.
+13. A/P Aging Summary shows two filter buttons: Vendor and Date.
+14. A/P Aging Detail shows four filter buttons: Vendor, Date, Location and Transaction Type.
+15. A/P Unpaid Invoices shows four filter buttons: Vendor, Date, Location and Transaction Type.
+16. Notes shows three filter buttons: Author, Date and Mention (the Mention button uses an @ icon), and its toolbar also shows a search icon, a filter icon and a sort icon.
+17. Reminders shows a single filter button: Date, and when nothing matches the chosen dates the report shows the message 'There are no reminders for selected date range'.
+18. IBS Batch Transactions shows three filter buttons: Customer, Date and Status, and has three view tabs: Ready To Send, Sent and Payments.
+19. QB Unexported shows three filter buttons and the first one changes with the tab: Customer, Date and Type on the Customers tab; Vendor, Date and Type on the Vendors tab; User, Date and Type on the Journal Entries tab.
+20. Each of the six A/R and A/P aging reports also shows a print icon in its toolbar.
+21. On every report above, each filter button shows its name and a down arrow.
+22. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (the option lists behind each filter button; and because several report bodies in the design are sample placeholders, the real report columns come from the same product write-up).</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #1-#23</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Choosing a Reports filter narrows the report results</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>Reports Page Filters</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Reports area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Reports area and go to the Timesheets (Payroll Timesheet) report.
-2. Look at the filter buttons shown above the report table.</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t>1. The Payroll Timesheet report shows two filter buttons: Employee and Date.
-2. The table shows columns: Employee Name, Date, Clock In Time, Lunch, Clock Out Time and Hours.</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #2</t>
-        </is>
-      </c>
-      <c r="I95" s="2" t="inlineStr"/>
-      <c r="J95" s="2" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>Sales report shows Customer and Date filters</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>Reports Page Filters</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. You are on the Reports area of the app with some sample data present.</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Reports area and go to the Sales report.
-2. Look at the filter buttons shown above the report table.</t>
-        </is>
-      </c>
-      <c r="G96" s="2" t="inlineStr">
-        <is>
-          <t>1. The Sales report shows two filter buttons: Customer and Date.
-2. The table shows columns including Invoice Date, Invoice, Customer, Inv. Hrs, Billing Efficiency, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Cost, Parts Margin, Profit and Subtotal.</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #3</t>
-        </is>
-      </c>
-      <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="2" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>Technician Efficiency report shows Customer, Technician and Date filters</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>Reports Page Filters</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. You are on the Reports area of the app with some sample data present.</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Reports area and go to the Technician Efficiency report.
-2. Look at the filter buttons shown above the report table.</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>1. The Technician Efficiency report shows three filter buttons: Customer, Technician and Date, on both the Invoiced and Completed tabs.
-2. The report has two view tabs: Invoiced and Completed; the same three filter buttons appear on each.
-3. 'Technician' is spelled correctly here (unlike the Work Orders list, see the spelling note).</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #4 and #5</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="2" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>Advisor Analysis report shows Customer, Date and Advisor filters</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>Reports Page Filters</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. You are on the Reports area of the app with some sample data present.</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Reports area and go to the Advisor Analysis report.
-2. Look at the filter buttons shown above the report table.</t>
-        </is>
-      </c>
-      <c r="G98" s="2" t="inlineStr">
-        <is>
-          <t>1. The Advisor Analysis report shows three filter buttons: Customer, Date and Advisor.
-2. The table shows columns including Date, Invoice, Customer, Advisor, Days Open, Lines, Hrs Worked, Hrs Invoiced, Hrs Profit, Billing Efficiency, ELR, Parts Cost, Parts Invoiced, Parts Margin and Subtotal.</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #6</t>
-        </is>
-      </c>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>Shop Efficiency report shows only a Date filter</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>Reports Page Filters</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. You are on the Reports area of the app with some sample data present.</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Reports area and go to the Shop Efficiency report.
-2. Look at the filter buttons shown above the report table.</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>1. The Shop Efficiency report shows a single filter button: Date.
-2. The table shows columns: Total Clocked Hours, Total Invoiced Hours, Difference and Efficiency.</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #7</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr"/>
-      <c r="J99" s="2" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>Work in Progress report shows Status, Date and Customer filters</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>Reports Page Filters</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. You are on the Reports area of the app with some sample data present.</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Reports area and go to the Work in Progress report.
-2. Look at the filter buttons shown above the report table.</t>
-        </is>
-      </c>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>1. The Work in Progress report shows three filter buttons: Status, Date and Customer.
-2. The table groups rows by status (Pending Authorization, In Progress, Ready To Invoice) with columns Sales, Cost, Profit $ and Profit %.</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #8</t>
-        </is>
-      </c>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>Sales Follow Up report shows Customer, Date and Contact filters</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>Reports Page Filters</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. You are on the Reports area of the app with some sample data present.</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Reports area and go to the Sales Follow Up report.
-2. Look at the filter buttons shown above the report table.</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="inlineStr">
-        <is>
-          <t>1. The Sales Follow Up report shows three filter buttons: Customer, Date and Contact.
-2. The table shows columns: Customer, Sales Representative, Number Of Work Orders, Total Spend and Last Visit.</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #9</t>
-        </is>
-      </c>
-      <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>Sales Tax Collected tab shows Date, Invoice Status and Customer filters</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>Reports Page Filters</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. You are on the Reports area of the app with some sample data present.</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Reports area and go to the Sales Tax (Collected tab) report.
-2. Look at the filter buttons shown above the report table.</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>1. On the Sales Tax report's Collected tab, three filter buttons are shown: Date, Invoice Status and Customer.
-2. The report has two view tabs: Collected and All Tax Rates.
-2. Note: in the design the report body uses a sample placeholder table, so only the title, tabs and filter buttons are design-confirmed here; the real report columns come from Branko's PRD.</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #10</t>
-        </is>
-      </c>
-      <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="2" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>Sales Tax All Tax Rates tab shows only an Invoice Status filter</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>Reports Page Filters</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. You are on the Reports area of the app with some sample data present.</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Reports area and go to the Sales Tax (All Tax Rates tab) report.
-2. Look at the filter buttons shown above the report table.</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>1. On the Sales Tax report's All Tax Rates tab, a single filter button is shown: Invoice Status.
-2. Note: in the design the report body uses a sample placeholder table, so only the title, tabs and filter buttons are design-confirmed here; the real report columns come from Branko's PRD.</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #11</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" s="2" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>A/R Aging Summary report shows Customer and Date filters</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>Reports Page Filters</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. You are on the Reports area of the app with some sample data present.</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Reports area and go to the A/R Aging Summary report.
-2. Look at the filter buttons shown above the report table.</t>
-        </is>
-      </c>
-      <c r="G104" s="2" t="inlineStr">
-        <is>
-          <t>1. The A/R Aging Summary report shows two filter buttons: Customer and Date.
-2. A print icon is shown in the toolbar.
-2. Note: in the design the report body uses a sample placeholder table, so only the title, tabs and filter buttons are design-confirmed here; the real report columns come from Branko's PRD.</t>
-        </is>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #12</t>
-        </is>
-      </c>
-      <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="2" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>A/R Aging Detail shows Customer, Date, Location, Transaction Type filters</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>Reports Page Filters</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. You are on the Reports area of the app with some sample data present.</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Reports area and go to the A/R Aging Detail report.
-2. Look at the filter buttons shown above the report table.</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="inlineStr">
-        <is>
-          <t>1. The A/R Aging Detail report shows four filter buttons: Customer, Date, Location and Transaction Type.
-2. A print icon is shown in the toolbar.
-3. Location and Transaction Type are new filter types not on the Work Orders page — Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available.
-2. Note: in the design the report body uses a sample placeholder table, so only the title, tabs and filter buttons are design-confirmed here; the real report columns come from Branko's PRD.</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #13</t>
-        </is>
-      </c>
-      <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="2" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>A/R Aging Collection shows Customer, Date, Location, Transaction Type</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>Reports Page Filters</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. You are on the Reports area of the app with some sample data present.</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Reports area and go to the A/R Aging Collection report.
-2. Look at the filter buttons shown above the report table.</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>1. The A/R Aging Collection report shows four filter buttons: Customer, Date, Location and Transaction Type.
-2. A print icon is shown in the toolbar.
-2. Note: in the design the report body uses a sample placeholder table, so only the title, tabs and filter buttons are design-confirmed here; the real report columns come from Branko's PRD.</t>
-        </is>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #14</t>
-        </is>
-      </c>
-      <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>A/P Aging Summary report shows Vendor and Date filters</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>Reports Page Filters</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. You are on the Reports area of the app with some sample data present.</t>
-        </is>
-      </c>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Reports area and go to the A/P Aging Summary report.
-2. Look at the filter buttons shown above the report table.</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t>1. The A/P Aging Summary report shows two filter buttons: Vendor and Date.
-2. A print icon is shown in the toolbar.
-2. Note: in the design the report body uses a sample placeholder table, so only the title, tabs and filter buttons are design-confirmed here; the real report columns come from Branko's PRD.</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #15</t>
-        </is>
-      </c>
-      <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>A/P Aging Detail shows Vendor, Date, Location, Transaction Type filters</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>Reports Page Filters</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. You are on the Reports area of the app with some sample data present.</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Reports area and go to the A/P Aging Detail report.
-2. Look at the filter buttons shown above the report table.</t>
-        </is>
-      </c>
-      <c r="G108" s="2" t="inlineStr">
-        <is>
-          <t>1. The A/P Aging Detail report shows four filter buttons: Vendor, Date, Location and Transaction Type.
-2. A print icon is shown in the toolbar.
-2. Note: in the design the report body uses a sample placeholder table, so only the title, tabs and filter buttons are design-confirmed here; the real report columns come from Branko's PRD.</t>
-        </is>
-      </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #16</t>
-        </is>
-      </c>
-      <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="2" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>A/P Unpaid Invoices shows Vendor, Date, Location, Transaction Type filters</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>Reports Page Filters</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. You are on the Reports area of the app with some sample data present.</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Reports area and go to the A/P Unpaid Invoices report.
-2. Look at the filter buttons shown above the report table.</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="inlineStr">
-        <is>
-          <t>1. The A/P Unpaid Invoices report shows four filter buttons: Vendor, Date, Location and Transaction Type.
-2. A print icon is shown in the toolbar.
-2. Note: in the design the report body uses a sample placeholder table, so only the title, tabs and filter buttons are design-confirmed here; the real report columns come from Branko's PRD.</t>
-        </is>
-      </c>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #17</t>
-        </is>
-      </c>
-      <c r="I109" s="2" t="inlineStr"/>
-      <c r="J109" s="2" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>Notes report shows Author, Date and Mention filters</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>Reports Page Filters</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. You are on the Reports area of the app with some sample data present.</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Reports area and go to the Notes report.
-2. Look at the filter buttons shown above the report table.</t>
-        </is>
-      </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>1. The Notes report shows three filter buttons: Author, Date and Mention (the Mention button uses an @ icon).
-2. The toolbar also shows a search icon, a filter icon and a sort icon.
-3. Mention is a new filter type not on the Work Orders page — Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available.</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #18</t>
-        </is>
-      </c>
-      <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="2" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>Reminders report shows only a Date filter</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>Reports Page Filters</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. You are on the Reports area of the app with some sample data present.</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Reports area and go to the Reminders report.
-2. Look at the filter buttons shown above the report table.</t>
-        </is>
-      </c>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t>1. The Reminders report shows a single filter button: Date.
-2. When no reminders match, the report shows the message 'There are no reminders for selected date range'.</t>
-        </is>
-      </c>
-      <c r="H111" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #19</t>
-        </is>
-      </c>
-      <c r="I111" s="2" t="inlineStr"/>
-      <c r="J111" s="2" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>IBS Batch Transactions report shows Customer, Date and Status filters</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>Reports Page Filters</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. You are on the Reports area of the app with some sample data present.</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Reports area and go to the IBS Batch Transactions report.
-2. Look at the filter buttons shown above the report table.</t>
-        </is>
-      </c>
-      <c r="G112" s="2" t="inlineStr">
-        <is>
-          <t>1. The IBS Batch Transactions report shows three filter buttons: Customer, Date and Status.
-2. The report has three view tabs: Ready To Send, Sent and Payments.
-3. The table shows columns: (checkbox), Date, Type, No., Customer, Total, Balance and Status.</t>
-        </is>
-      </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #20</t>
-        </is>
-      </c>
-      <c r="I112" s="2" t="inlineStr"/>
-      <c r="J112" s="2" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>QB Unexported report filters change per tab (Customer / Vendor / User)</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>Reports Page Filters</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. You are on the Reports area of the app with some sample data present.</t>
-        </is>
-      </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Reports area and go to the QB Unexported report.
-2. Look at the filter buttons shown above the report table.</t>
-        </is>
-      </c>
-      <c r="G113" s="2" t="inlineStr">
-        <is>
-          <t>1. The QB Unexported report has three view tabs, and the first filter button changes per tab.
-2. On the Customers tab the filter buttons are Customer, Date and Type.
-3. On the Vendors tab they are Vendor, Date and Type.
-4. On the Journal Entries tab they are User, Date and Type.
-5. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (option lists behind each button).</t>
-        </is>
-      </c>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #21, #22, #23</t>
-        </is>
-      </c>
-      <c r="I113" s="2" t="inlineStr"/>
-      <c r="J113" s="2" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>Choosing a Reports filter narrows the report results</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>Reports Page Filters</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. You are on the Reports area of the app with some sample data present.</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Reports area and go to the any (for example Sales) report.
-2. Look at the filter buttons shown above the report table.</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Reports area and go to any report — for example the Sales report.
+2. Open one of the filter buttons shown above the report table and choose one value.
+3. Look at the report table below.</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>1. The report updates to show only the rows matching the chosen filter value, and the chosen value is shown on the filter button.
 2. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (exactly which filters apply on each report, the full option lists, and whether results update immediately).</t>
         </is>
       </c>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6</t>
         </is>
       </c>
-      <c r="I114" s="2" t="inlineStr"/>
-      <c r="J114" s="2" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>New Reports filter types behave correctly (Location, Transaction Type, etc.)</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>Reports Page Filters</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Reports area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>1. Open the Reports area and go to the reports that use them (for example A/R Aging Detail, Notes) report.
 2. Look at the filter buttons shown above the report table.</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>1. Each new filter type (Location, Transaction Type, Invoice Status, Type, User, Mention) opens a list of choices and filters the report by the choice.
 2. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (the exact choices, single- vs multi-select, and how each new filter type filters the report).</t>
         </is>
       </c>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6</t>
         </is>
       </c>
-      <c r="I115" s="2" t="inlineStr"/>
-      <c r="J115" s="2" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>Date range filter: results update when both start and end dates are picked</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>Reports Page Filters</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The new filter bar has rolled out to a page with a Date filter chip (a report, or a Parts page with a date column).
 3. Records exist inside and outside the date range you will pick.</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>1. Click the Date filter chip.
 2. Look at the panel that opens.
@@ -6081,7 +4837,7 @@
 5. Look at the results and the chip.</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>1. A start/end date picker opens - there are NO preset ranges (no 'Last 30 days' shortcuts) and NO pre-filled default range.
 2. After only the start date, the results do not change yet.
@@ -6089,42 +4845,42 @@
 4. Only one date range can be active at a time on that chip, and the chip shows the active range.</t>
         </is>
       </c>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); tech plan 2026-07-29 D19 (date-range chip: no presets, no default, applies on second date); spec v1.3 Parts + Reports sections (export awaited)</t>
         </is>
       </c>
-      <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="2" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>Page toolbar Search expands in place and narrows the list as you type</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with several work orders listed.</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>1. Find the Search control in the page toolbar (a magnifier icon with the word Search).
 2. Click it.
@@ -6134,7 +4890,7 @@
 6. Expand it again, type text, and click somewhere else.</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>1. The control expands in place into a small search box inviting you to type (engineering copy: 'Type to search').
 2. The list narrows as you type, after a brief pause - and ONLY this page's list changes, nothing else in the app.
@@ -6142,42 +4898,42 @@
 4. Clicking away with an empty box collapses it back to the Search button; with text in it, the box stays open.</t>
         </is>
       </c>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); tech plan 2026-07-29 D18; spec v1.3 S13-R1..R7, S13-R9, S13-R15 (export awaited)</t>
         </is>
       </c>
-      <c r="I117" s="2" t="inlineStr"/>
-      <c r="J117" s="2" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>Page search combines with filters and is cleared separately</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with work orders for several customers and statuses.</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>1. Apply one filter (for example a Status).
 2. Type a search term in the page search box.
@@ -6185,104 +4941,104 @@
 4. Re-type the search, then clear ONLY the filter.</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>1. With both active, the results match the filter AND the search together (both narrow the list at once).
 2. Clearing the search keeps the filter applied.
 3. Clearing the filter keeps the search applied - each is cleared by its own control without wiping the other.</t>
         </is>
       </c>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); tech plan 2026-07-29 D18; spec v1.3 S13-R10/R13 + S8-R5 (export awaited)</t>
         </is>
       </c>
-      <c r="I118" s="2" t="inlineStr"/>
-      <c r="J118" s="2" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>The page search text is remembered and restored like filters</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page.</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>1. Type a search term that matches some work orders.
 2. Go to another area of the app and come back to the Work Orders page.
 3. Now type a search term that matches NOTHING, leave the page, and come back again.</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>1. The search box comes back with your text still in it and the list still narrowed by it - just like the filters.
 2. A remembered search that matches nothing shows the no-results empty state - the remembered text is NOT silently thrown away.</t>
         </is>
       </c>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); tech plan 2026-07-29 D18; spec v1.3 S10-R4/R5, S10-N2 (export awaited)</t>
         </is>
       </c>
-      <c r="I119" s="2" t="inlineStr"/>
-      <c r="J119" s="2" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>The search term is part of the shareable page link</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page.</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>1. Type a search term and copy the page address.
 2. Open the copied address in a fresh tab.
 3. Hand-edit the search part of the address into something malformed and load it.</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t>1. The address contains the search term after step 1.
 2. The fresh tab opens with the search box filled and the list already narrowed.
@@ -6290,138 +5046,138 @@
 4. A search arriving via a link is view-only, the same as filters from a link - it does not overwrite your own remembered search.</t>
         </is>
       </c>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); tech plan 2026-07-29 D18 + G7; spec v1.3 S11-R4/R5, S11-N2 (export awaited)</t>
         </is>
       </c>
-      <c r="I120" s="2" t="inlineStr"/>
-      <c r="J120" s="2" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>On mobile the search expands in the toolbar and buttons make room</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device.
 2. You are on the Work Orders page.</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>1. Tap the Search control in the page toolbar.
 2. Type a term and watch the list.
 3. Visit a page that has several small icon-only toolbar buttons (for example Parts Inventory or Purchase Orders) and look at its toolbar.</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t>1. The search expands inline inside the toolbar - no separate popup window opens.
 2. The list narrows as you type, same as desktop.
 3. To make room, the page's main button no longer stretches full-width, and pages with two or more small icon buttons collapse them into a single 'more' menu.</t>
         </is>
       </c>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); tech plan 2026-07-29 D21; spec v1.3 S13-R16..R21 (export awaited)</t>
         </is>
       </c>
-      <c r="I121" s="2" t="inlineStr"/>
-      <c r="J121" s="2" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>Every list page keeps its own search box (Parts, Reports, detail tabs)</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The page-search rollout has shipped (same programme as the Work Orders filters).</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>1. Visit several list surfaces: a Parts view (for example Inventory), a report, a customer's Notes tab on the customer page, and any pop-up list that used to be searchable.
 2. On each, look for that surface's own search box and use it.</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>1. Every list surface that could be text-searched before still offers its own search control - no list silently lost its search.
 2. Each search box narrows only its own list, not any other page.</t>
         </is>
       </c>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); tech plan 2026-07-29 Phase 9.1 (built-in table search, opt-out); spec v1.3 S13-R22 + S14-R5/R6 (export awaited)</t>
         </is>
       </c>
-      <c r="I122" s="2" t="inlineStr"/>
-      <c r="J122" s="2" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>The top navigation search no longer filters page lists</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with several work orders listed.</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>1. Type a term into the TOP NAVIGATION search (the app-wide search at the top), not the page's own search box.
 2. Watch the Work Orders list while typing.
@@ -6429,152 +5185,152 @@
 4. Pick one of the results offered in the navigation search's dropdown.</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t>1. The page list does NOT narrow while you type in the navigation search - only its dropdown of matching records appears.
 2. The same holds on the other pages checked.
 3. Picking a dropdown result still takes you to that record - the navigation search keeps its find-and-open role.</t>
         </is>
       </c>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); tech plan 2026-07-29 Phase 9 (search decoupling); spec v1.3 Story 14 S14-R2/R3 (export awaited)</t>
         </is>
       </c>
-      <c r="I123" s="2" t="inlineStr"/>
-      <c r="J123" s="2" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>Page search opens with the 'Search or ask a question' box</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>Page Search (Command-K)</t>
         </is>
       </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Some sample work orders, customers, assets, parts and vendors exist.</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>1. From anywhere in the app, open the page search (the Search box in the top bar, or press Command-K / Ctrl-K).
 2. Look at the search panel that opens.</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>1. A search panel opens with an empty search box at the top.
 2. The box shows the placeholder text 'Search or ask a question' with a magnifier icon on the left and a clear (X) button on the right.
 3. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (whether 'ask a question' means an AI search — this is out of scope for now).</t>
         </is>
       </c>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
         </is>
       </c>
-      <c r="I124" s="2" t="inlineStr"/>
-      <c r="J124" s="2" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>Page search shows entity tabs All, Work Orders, Customers, Assets, Parts...</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>Page Search (Command-K)</t>
         </is>
       </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Some sample work orders, customers, assets, parts and vendors exist.</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>1. Open the page search panel.
 2. Look at the row of tabs under the search box.</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t>1. A row of tabs is shown: All, Work Orders, Customers, Assets, Parts, Vendors and Part Sales.
 2. The All tab is selected by default.
 3. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (whether choosing a tab limits results to that type only).</t>
         </is>
       </c>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
         </is>
       </c>
-      <c r="I125" s="2" t="inlineStr"/>
-      <c r="J125" s="2" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>Typing a term shows grouped results with counts and highlighting</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>Page Search (Command-K)</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Some sample work orders, customers, assets, parts and vendors exist.</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>1. Open the page search panel.
 2. Type a few letters (for example 'Fib') into the search box.
 3. Look at the results.</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>1. Results are grouped by type with a count next to each group heading, for example 'Work orders (2)', 'Customers (2)', 'Vendors (1)', 'Assets (2)', 'Parts (1)'.
 2. The matching part of each result is highlighted in yellow.
@@ -6582,570 +5338,523 @@
 4. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (how matching works — exact vs fuzzy — and the ranking order).</t>
         </is>
       </c>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
         </is>
       </c>
-      <c r="I126" s="2" t="inlineStr"/>
-      <c r="J126" s="2" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>Recent searches are shown grouped by Today, Yesterday, Past week...</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>Page Search (Command-K)</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Some sample work orders, customers, assets, parts and vendors exist.</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>1. Open the page search panel without typing anything.
 2. Look at the list shown under the tabs.</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t>1. A list of recent items is shown, grouped under headings: Today, Yesterday, Past week and Past 30 days.
 2. Each item shows a type icon, its name and a short detail line (for example a customer address or a date).
 3. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (how many recent items are kept and how long they persist).</t>
         </is>
       </c>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
         </is>
       </c>
-      <c r="I127" s="2" t="inlineStr"/>
-      <c r="J127" s="2" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>Re-opening page search keeps the last typed text and its results</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>Page Search (Command-K)</t>
         </is>
       </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Some sample work orders, customers, assets, parts and vendors exist.</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>1. Open the page search and type a term (for example 'Fibridge').
 2. Close the panel, then open it again.
 3. Look at the search box and the results.</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr">
         <is>
           <t>1. The previous search text is still in the box (shown selected/highlighted) and its results are shown.
 2. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (whether the last search is remembered per person and for how long — this is the 'persisting search' state).</t>
         </is>
       </c>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
         </is>
       </c>
-      <c r="I128" s="2" t="inlineStr"/>
-      <c r="J128" s="2" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>Hovering a search result shows quick-action buttons</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>Page Search (Command-K)</t>
         </is>
       </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Some sample work orders, customers, assets, parts and vendors exist.</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>1. Open the page search panel (recent items or results shown).
 2. Move the mouse over a result row.
 3. Look at the right side of that row.</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t>1. Quick-action buttons appear on the row, depending on the result type — for example 'Add new line' on a work order, 'New work order' on an asset or customer, 'Add part' on a part sale, 'Add contact' on a vendor and 'Add to work order' on a part.
 2. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (exactly which quick actions show for which result type, and what each one does).</t>
         </is>
       </c>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
         </is>
       </c>
-      <c r="I129" s="2" t="inlineStr"/>
-      <c r="J129" s="2" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>Page search shows keyboard hints and supports keyboard navigation</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>Page Search (Command-K)</t>
         </is>
       </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Some sample work orders, customers, assets, parts and vendors exist.</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>1. Open the page search panel.
 2. Look at the bar along the bottom of the panel.
 3. Use the up/down arrow keys, Enter and Esc.</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t>1. The bottom bar shows keyboard hints: up/down arrows labelled 'Navigate', the Enter key labelled 'Select', and 'Close esc'.
 2. Arrow keys move the highlight between results, Enter opens the highlighted result, and Esc closes the panel (to be checked live once available).
 3. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (exact keyboard behaviour).</t>
         </is>
       </c>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
         </is>
       </c>
-      <c r="I130" s="2" t="inlineStr"/>
-      <c r="J130" s="2" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>Page search results include a Refresh action</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>Page Search (Command-K)</t>
         </is>
       </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Some sample work orders, customers, assets, parts and vendors exist.</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>1. Open the page search and type a term so grouped results appear.
 2. Look at the top right of the results area.</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr">
         <is>
           <t>1. A 'Refresh' link is shown at the top right of the results.
 2. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (what Refresh reloads and when it is shown).</t>
         </is>
       </c>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
         </is>
       </c>
-      <c r="I131" s="2" t="inlineStr"/>
-      <c r="J131" s="2" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>Page search scope belongs to Filters or Global Search (to decide)</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>Page Search (Command-K)</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>The work order list request carries the active filter selections</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>API — Work Orders List Filtering</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. Some sample work orders, customers, assets, parts and vendors exist.</t>
-        </is>
-      </c>
-      <c r="F132" s="2" t="inlineStr">
-        <is>
-          <t>1. Review where the page search / Command-K component is owned for testing.
-2. Compare against the Global Search project's existing cases.</t>
-        </is>
-      </c>
-      <c r="G132" s="2" t="inlineStr">
-        <is>
-          <t>1. The page-search component is agreed to belong to either the Filters test suite or the Global Search test suite, not both.
-2. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (product/QA decision on which project owns page search).</t>
-        </is>
-      </c>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
-        </is>
-      </c>
-      <c r="I132" s="2" t="inlineStr"/>
-      <c r="J132" s="2" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
-        <is>
-          <t>The work order list request carries the active filter selections</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>API — Work Orders List Filtering</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser with developer tools open on the Network tab.
 2. You are on the Work Orders page with no filters applied.</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>1. Apply a Status selection and a Customer selection in the filter bar.
 2. In the Network tab, find the work order list request the page sends after the change.
 3. Inspect the request's parameters.</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t>1. The list request includes the active filter selections as request parameters (status values and customer identifiers).
 2. The request succeeds (HTTP 200).
 3. The response contains only work orders matching the filters - the filtering is done by the backend, not just hidden client-side.</t>
         </is>
       </c>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 2 S2-R2; Story 3 S3-R6 (backend view)</t>
         </is>
       </c>
-      <c r="I133" s="2" t="inlineStr"/>
-      <c r="J133" s="2" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+      <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>A combined multi-filter request returns only work orders matching all filters, any value within each filter</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>API — Work Orders List Filtering</t>
         </is>
       </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with developer tools open on the Network tab.
 2. Seeded ZZAUTOTEST work orders exist: customer A with an Estimate and an Approved work order, customer B with an Estimate work order.</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>1. On the Work Orders page apply Status = Estimate + Approved and Customer = customer A.
 2. Capture the resulting list request and response.</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t>1. One request carries both filters together (both statuses and the customer).
 2. The response returns customer A's Estimate and Approved work orders only.
 3. Customer B's work orders are absent - the customer filter and status filter both restrict the result, while the two statuses combine as either-or.</t>
         </is>
       </c>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 2 S2-R2; Story 3 S3-R6; Story 8 S8-R3 (backend view)</t>
         </is>
       </c>
-      <c r="I134" s="2" t="inlineStr"/>
-      <c r="J134" s="2" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>A list request with a deleted or unknown filter value is handled without a server error</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>API — Work Orders List Filtering</t>
         </is>
       </c>
-      <c r="C135" s="2" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in and can replay/edit the work order list request (developer tools or an API client).
 2. You have a captured filtered list request, and one of its filter values has since been deleted (for example a removed ZZAUTOTEST customer) or is a made-up identifier.</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>1. Send the list request containing the no-longer-existing (or made-up) filter value.
 2. Inspect the HTTP status and the response body.</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t>1. The backend does not fail with a server error (no HTTP 5xx).
 2. The response is a normal, successful list response - the invalid value is ignored or simply matches nothing.
 3. Any still-valid filter values in the same request are applied normally.</t>
         </is>
       </c>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 10 S10-N1; Story 11 S11-R3</t>
         </is>
       </c>
-      <c r="I135" s="2" t="inlineStr"/>
-      <c r="J135" s="2" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>A list request with malformed filter parameters does not produce a server error</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>API — Work Orders List Filtering</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in and can replay/edit the work order list request.
 2. You have a captured filtered list request to tamper with.</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>1. Corrupt the filter parameters (wrong types, scrambled values, nonsense text) and send the request.
 2. Inspect the HTTP status and the response body.
 3. Also open the equally malformed page URL in the browser and watch the page.</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>1. The backend responds gracefully - no HTTP 5xx / crash; either a normal (unfiltered or empty) list or a clean validation response.
 2. In the browser the page still loads without filters and without an error message, matching the malformed-URL requirement.</t>
         </is>
       </c>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 11 S11-N1</t>
         </is>
       </c>
-      <c r="I136" s="2" t="inlineStr"/>
-      <c r="J136" s="2" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>A filter combination matching nothing returns a successful empty list, not an error</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>API — Work Orders List Filtering</t>
         </is>
       </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with developer tools open on the Network tab.
 2. A filter combination is known to match no work orders (for example a seeded customer plus a status they never have).</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>1. Apply that filter combination on the Work Orders page.
 2. Capture the list request and response.</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
         <is>
           <t>1. The request succeeds (HTTP 200).
 2. The response contains an empty result set (zero work orders) - an empty match is a normal outcome, not an error.
 3. The page renders the no-results empty state from this response.</t>
         </is>
       </c>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 8 S8-R3; Story 2 S2-N3</t>
         </is>
       </c>
-      <c r="I137" s="2" t="inlineStr"/>
-      <c r="J137" s="2" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>Saved-filters service round-trip: save, reload, and per-user isolation</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>API — Work Orders List Filtering</t>
         </is>
       </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser with developer tools open on the Network tab.
 2. A second user account is available.</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>1. On the Work Orders page, change a filter and watch the Network tab for the save request the page sends shortly after.
 2. Reload the page and find the load request for the saved page state.
@@ -7153,7 +5862,7 @@
 4. With an API client (or by editing the request), ask the saved-state service for a page key that was never saved.</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t>1. Changing a filter sends a save (PUT) to the per-user page-preferences service carrying the page's state, and it succeeds (HTTP 200).
 2. On reload the page requests the saved state back (GET, HTTP 200) and applies it - the filters return without you redoing them.
@@ -7161,13 +5870,13 @@
 4. Asking for a never-saved key returns success with an empty value, not an error page.</t>
         </is>
       </c>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); tech plan 2026-07-29 section 4-1.3 (GET/PUT /api/users/me/preferences/{pageKey}); spec v1.3 S10 per-user persistence (export awaited)</t>
         </is>
       </c>
-      <c r="I138" s="2" t="inlineStr"/>
-      <c r="J138" s="2" t="inlineStr"/>
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/filters-v1-testrail-import.xlsx
+++ b/testrail-import/filters-v1-testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J110"/>
+  <dimension ref="A1:J119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -586,7 +586,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>The filter bar still shows the remaining chips on a tab where the Status filter is hidden</t>
+          <t>The filter bar still shows the other four chips on the Estimates tab</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -618,13 +618,14 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1. The filter bar is still shown (it does not disappear).
-2. The remaining filter chips (Customer, Lead Technician, Service Advisor, Asset on site) are displayed and usable.</t>
+          <t>1. The filter bar is still shown - it does not disappear on this tab.
+2. The Customer, Lead Technician, Service Advisor and Asset on site chips are all displayed and usable.
+3. The Status chip is not usable on this tab: it is shown greyed out and already filled in with the tab's own status, and cannot be clicked.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 1 S1-N1</t>
+          <t>Filters epic (key TBD) (S1-N1; S9-R2; §4 Key Decisions - PRD text says "hidden"; behaviour per Branko Q4=B 2026-07-17 + QA-lead ruling 2026-07-30 = shown greyed-out/disabled) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -2619,7 +2620,8 @@
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page on the All tab.
-3. Values are selected in at least three different filters (for example a status, a customer and Asset on site Yes).</t>
+3. Values are selected in at least three different filters (for example a status, a customer and Asset on site Yes).
+4. The page's own Search box is empty (no text typed in it) - a typed search is cleared by its own control, not by 'Clear filters'.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -2632,13 +2634,13 @@
         <is>
           <t>1. Every active filter is cleared in one click.
 2. All chips return to their default (inactive) look with no values shown.
-3. The table shows the full unfiltered list again.
+3. The table shows the full unfiltered list again (no text is in the page Search box, so nothing else is narrowing it).
 4. The 'Clear filters' link disappears.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 8 S8-R1; §4 Key Decisions</t>
+          <t>Filters epic (key TBD) (S8-R1; §4 Key Decisions; S13-R13 (clearing filters does not clear a typed search)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
@@ -3059,7 +3061,8 @@
       <c r="E54" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. You are on the Work Orders page showing the filtered empty state (a filter combination matching no work orders is applied).</t>
+2. You are on the Work Orders page showing the filtered empty state (a filter combination matching no work orders is applied).
+3. The page's own Search box is empty (no text typed in it).</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -3072,13 +3075,13 @@
       <c r="G54" s="2" t="inlineStr">
         <is>
           <t>1. The empty state includes a prompt or link to clear the filters.
-2. Clicking it removes the active filters and the full work order list is shown again.
+2. Clicking it removes the active filters and the full work order list is shown again (with no text in the Search box, nothing else is narrowing the list).
 3. The chips return to their default state.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 8 S8-R4</t>
+          <t>Filters epic (key TBD) (S8-R4; S8-R5 (with a query active each is cleared independently - FLT-EMPTY-03)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -3087,79 +3090,131 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>When filters and a search find nothing, each can be cleared on its own</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Empty State</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Work Orders page.
+3. One filter is active (for example a Status) and some work orders match it.</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>1. With that filter still active, type a word in the page Search box that matches none of the work orders left in the list.
+2. Read the message shown where the table was.
+3. Use the option the message offers for clearing the search only.
+4. Type the same word again, then use the option the message offers for clearing the filters only.</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>1. The table is replaced by a no-results message that mentions BOTH the current filters and the search - not the filters alone.
+2. The message offers a way to clear the filters and, because a search is active, a separate way to clear the search.
+3. Clearing the search brings back the list as narrowed by the filter only - the filter is still on.
+4. Clearing the filters leaves your typed word in the box and still applied - each is cleared on its own without wiping the other.</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Filters epic (key TBD) (S8-R3 (empty state covers filters AND any active query); S8-R4 (prompt to clear filters and the query where active); S8-R5 (each cleared independently from the empty state); S13-N1; S13-N2) [spec v1.6 2026-07-28]</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
           <t>The All tab shows all five filter chips, all working</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>Tab Behaviour</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1. Click the All tab.
 2. Count the filter chips and click each one briefly.</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>1. All five chips are shown: Status, Customer, Lead Technician, Service Advisor, Asset on site.
 2. Each chip opens its dropdown and can be used.</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 9 S9-R1</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>On the Estimates tab the Status chip is shown greyed out, pre-filled with 'Status: Estimate', and cannot be changed; the other four filters work on top of the Estimates pre-filter</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>Tab Behaviour</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Estimate work orders exist for at least two different customers.
 3. You are on the Work Orders page.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>1. Click the Estimates tab.
 2. Look at the filter bar.
@@ -3168,50 +3223,50 @@
 5. Look at the table.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>1. The Status chip is shown but greyed out, already filled in as 'Status: Estimate', and cannot be clicked or changed - the tab already pre-filters the list to Estimate.
 2. Customer, Lead Technician, Service Advisor and Asset on site chips are shown and usable.
 3. After step 4 the table shows only that customer's ESTIMATE work orders - the customer filter narrows the pre-filtered Estimates list.</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 9 S9-R2; Story 2 S2-N1 (chip-hidden wording superseded by PO ruling 2026-07-17: chip shown disabled); §4 Key Decisions</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>On the Completed tab the Status chip is shown greyed out, pre-filled with the tab's status, and cannot be changed; the other four filters work on top of the Completed pre-filter</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>Tab Behaviour</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Complete work orders exist for at least two different customers.
 3. You are on the Work Orders page.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1. Click the Completed tab.
 2. Look at the filter bar.
@@ -3220,147 +3275,147 @@
 5. Look at the table.</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>1. The Status chip is shown but greyed out, already filled in with this tab's status, and cannot be clicked or changed - the tab already pre-filters the list to Complete.
 2. Customer, Lead Technician, Service Advisor and Asset on site chips are shown and usable.
 3. After step 4 the table shows only that customer's COMPLETE work orders.</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 9 S9-R3; Story 2 S2-N2 (chip-hidden wording superseded by PO ruling 2026-07-17: chip shown disabled); §4 Key Decisions</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>On the My Work Orders tab all five filters are shown and narrow the already user-scoped list</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>Tab Behaviour</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Work orders assigned to you exist in at least two statuses, and other users' work orders also exist.
 3. You are on the Work Orders page.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>1. Click the My Work Orders tab and count the chips.
 2. Open the Status filter and tick one status your work orders have.
 3. Look at the table.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>1. All five filter chips are shown on the My Work Orders tab.
 2. The table only ever shows work orders assigned to you (the tab's own scope stays).
 3. After step 2 it shows only YOUR work orders in the ticked status - the filters narrow the user-scoped list, they do not widen it to other users' work orders.</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 9 S9-R4; §4 Key Decisions (My Work Orders tab does not remove filters)</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>Filter selections survive tab switching; a Status selection hidden on Estimates/Completed comes back on the All tab</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>A Status choice is kept while you switch tabs and comes back on the All tab</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>Tab Behaviour</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page on the All tab.
 3. A Status selection (for example Approved) and a Customer selection are active.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>1. Click the Estimates tab and look at the filter bar and the table.
 2. Click back to the All tab and look again.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>1. On the Estimates tab the Status selection is not applied and not shown as an editable filter (incompatible with the tab), but the Customer selection is still shown and still filters the list.
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>1. On the Estimates tab your Status choice is not applied and cannot be changed - the Status chip is greyed out and pre-filled with the tab's own status. The Customer selection is still shown and still filters the list.
 2. Back on the All tab the Status chip reappears with the SAME selection (Approved) still applied - the selection was retained in memory, not lost.
 3. The Customer selection is unchanged throughout.</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md Story 9 S9-R5; S9-N1</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Filters epic (key TBD) (S9-R5; S9-N1; S9-R2 - behaviour per Branko Q4=B 2026-07-17 + QA-lead ruling 2026-07-30) [spec v1.6 2026-07-28]</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>First visit opens the Estimates tab; your last-used tab is remembered</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>Tab Behaviour</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>1. You can sign in as a user who has never used the redesigned Work Orders page (no saved page choices for that account).</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as that fresh user and open the Work Orders page.
 2. Note which tab is selected and the tab order.
@@ -3368,48 +3423,48 @@
 4. Go to another area of the app and come back to the Work Orders page.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>1. On the very first visit the Estimates tab is the selected one, even though All is the FIRST tab in the row (order and default are different on purpose).
 2. After switching to All and returning, the All tab is selected - the app remembers your last-used tab per account.</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); tech plan 2026-07-29 D10 (default tab = Estimates; last-used tab persists); not in the ratified product spec - confirmation requested</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Leaving the Work Orders page and coming back restores the filters and the bar state exactly</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>Persistence</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with a Status and a Customer selection active and the filter bar expanded.</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>1. Open one work order from the list (go to its detail page).
 2. Go back to the Work Orders page.
@@ -3417,49 +3472,49 @@
 4. Repeat the round-trip once more with the filter bar collapsed before leaving.</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>1. After step 2 the same Status and Customer selections are still applied - chips active with the same values, table filtered the same way.
 2. The filter bar is still expanded (as you left it).
 3. After step 4 the filter bar comes back collapsed - the collapsed/expanded state is restored too.</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 10 S10-R1; Story 1 S1-R7</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>Filter selections are remembered for you permanently - still applied after moving around the app and even after closing the browser and signing back in</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>Persistence</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Filters are applied on the Work Orders page (for example a status and a customer).</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>1. Visit several other areas of the app (Customers, Parts, Reports) and use them briefly.
 2. Return to the Work Orders page and look at the chips and the table.
@@ -3469,146 +3524,146 @@
 6. On a different computer (or a different browser profile), sign in as the same person and open the Work Orders page.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>1. After moving around the app (step 2) the filter selections are still applied - you do not have to re-apply them.
 2. After closing the browser completely and signing back in (step 5) the same filter selections are still applied - the app remembers your filters for you permanently, not just for one browser session.
 3. The same filter selections are applied on the other computer too - the filters are saved to your account, not to one computer or browser (to confirm live once built).</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 10 S10-R2 (session-only wording superseded by PO ruling 2026-07-17: permanent per-user persistence); §2/§4 (persist across navigation, saved per user)</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>Saved filters are per user: one user's filters do not appear for another user</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>Persistence</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>1. Two test users (A and B) can sign in to the same shop.
 2. User A has applied filters on the Work Orders page (for example Status: Approved).</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>1. As user B (separate login/browser profile), open the Work Orders page.
 2. Look at the filter chips and the table.
 3. As user B, apply a DIFFERENT filter (for example a customer), then re-check user A's view.</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>1. User B does not see user A's filters - user B's page opens with user B's own (or no) filters.
 2. User B's new filter does not change what user A sees; each user keeps their own saved filter state.</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 10 S10-R3; §4 Key Decisions (saved per user)</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>A remembered filter value that no longer exists is silently dropped when you return</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>Persistence</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A throwaway ZZAUTOTEST customer exists and is selected in the Customer filter together with one real customer.
 3. You then navigate away and the ZZAUTOTEST customer is deleted (or otherwise removed) while you are off the page.</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>1. Return to the Work Orders page.
 2. Look at the Customer chip, the dropdown and the table.</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>1. The deleted customer is silently ignored - no error or warning appears.
 2. The Customer filter now reflects only the still-valid selection (the real customer).
 3. The table is filtered by the remaining valid selection only.</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 10 S10-N1</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Each page and tab remembers its own filters separately</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>Persistence</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The new filter bar has rolled out to the Parts views and to a report that has tabs (part of the same programme as the Work Orders filters).</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>1. On one Parts view (for example Inventory) apply a filter.
 2. Switch to a different Parts view (for example Purchase Orders).
@@ -3616,439 +3671,496 @@
 4. On a report with tabs, apply a filter on one tab, switch to another tab, then switch back.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>1. The second Parts view does NOT show the first view's selections - each view keeps its own.
 2. Returning to the first view restores that view's own selections.
 3. Report tabs likewise keep separate filter choices, each remembered and restored on its own tab.</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); tech plan 2026-07-29 D20 (per-view/per-tab state scoping); spec v1.3 Key Decisions (export awaited)</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>Filters saved before the redesign carry over after the update</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>Persistence</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>1. In one browser, the account was used on the OLD Work Orders page with choices saved there (a tab, status selections, the asset-here toggle, column choices, sorting) BEFORE the redesign was installed.</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>1. In that same browser, open the updated app and go to the Work Orders page.
 2. Check the selected tab, the filter chips, the table columns and the sorting.
 3. Sign in as the same person on a DIFFERENT computer or browser and open the Work Orders page.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>1. The old saved choices appear in the new filter bar on the first visit - the update does not lose them (old status choices show in the Status chip, the old asset-here choice shows as Asset on site: Yes, the old My-Work-Orders toggle maps to the My Work Orders tab, columns and sorting stay).
 2. Those carried-over choices are now saved to the account: the other computer shows them too.</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); tech plan 2026-07-29 section 4-3.3 (one-time browser-storage to account-preference migration)</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>Applying filters updates the page URL to reflect the active filter state</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>URL State and Shareable Links</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with no filters applied; note the current URL.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>1. Apply a Status selection and a Customer selection.
 2. Look at the browser address bar.
 3. Clear all filters and look at the address bar again.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>1. After step 1 the URL changes to include the active filter state.
 2. After step 3 the filter part of the URL is removed again.</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 11 S11-R1</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>Opening a shared or bookmarked URL loads the Work Orders page with those filters already applied</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>URL State and Shareable Links</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You have copied a Work Orders URL that was produced with filters applied (for example Status: Approved + one customer).</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>1. Open the copied URL in a new browser tab (same signed-in user).
 2. Look at the chips and the table as the page loads.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>1. The page opens with the same filters already applied - chips active with the same values.
 2. The table is already filtered accordingly on load (no need to re-apply anything).
 3. The same works from a saved bookmark.</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 11 S11-R2; §2 Feature Overview (share or bookmark)</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>A URL containing a filter value that no longer exists loads without that value</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>URL State and Shareable Links</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You saved a filtered Work Orders URL that includes a throwaway ZZAUTOTEST customer plus one real filter value.
 3. The ZZAUTOTEST customer has since been deleted.</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. Open the saved URL.
 2. Look at the chips and the table.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>1. The page loads normally - no error.
 2. The deleted value is ignored; only the still-valid filter value is applied and shown on the chips.
 3. The table reflects only the valid filter.</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 11 S11-R3</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>A malformed filter URL loads the page unfiltered without showing an error</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>URL State and Shareable Links</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You have a valid filtered Work Orders URL to start from.</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>1. Manually break the filter part of the URL (for example scramble the parameter values or insert nonsense text).
 2. Open the broken URL.
 3. Look at the page, the chips and the table.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>1. The Work Orders page loads normally.
 2. No filters are applied (chips in default state, full list shown) - the unrecognizable state is discarded.
 3. No error message or broken page appears.</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 11 S11-N1</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>Opening a filtered link never overwrites your saved filters</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>URL State and Shareable Links</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in and have your OWN filters saved on the Work Orders page (for example one customer).
-2. You have a Work Orders link that carries a DIFFERENT filter state (made by another user or another browser).</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
+2. You have a Work Orders link that carries a DIFFERENT filter state (made by another user or another browser).
+3. You know how to use the page's own Search box on the Work Orders page (the Search button in the toolbar row).</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>1. Note your own saved filters on the Work Orders page.
 2. Open the shared link.
 3. While on the link view, change one more filter.
-4. Use the on-screen option to go back to your own saved filters.
-5. Leave the page and return to Work Orders normally (via the menu).</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
+4. Still on the link view, type something into the page's Search box so the list is narrowed by text as well.
+5. Click 'Back to my view'.
+6. Leave the page and return to Work Orders normally (via the menu).</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>1. The link's filters apply for viewing only - the page shows the shared view.
 2. Changes made during the link visit are also NOT saved to your account.
-3. The go-back option restores your own saved filters and removes the filter part from the address bar.
-4. Returning normally later still shows your own saved filters, untouched by the link visit.</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); tech plan 2026-07-29 G7 (URL state runtime-only + back-to-saved affordance); spec closing-note conflict raised with the author (spec v1.3 export awaited)</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+3. A 'Back to my view' option is shown while you are looking at the shared link. (If the wording on screen is slightly different, note what it says and carry on.)
+4. Clicking 'Back to my view' brings back your own saved filters and removes the filter part from the web address.
+5. It also empties the Search box and removes your typed text - the search is not something that gets saved, so there is nothing to bring back.
+6. Returning normally later still shows your own saved filters, untouched by the link visit.</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Filters epic (key TBD) (S11-R6 (URL state runtime-only with no write-back); S11-R7 (Back to my view - also clears the query); S11-R8 (rationale: the query is never saved)) [spec v1.6 2026-07-28]</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>'Back to my view' is not shown when you are on your own view</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>URL State and Shareable Links</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You have your OWN filters saved on the Work Orders page (for example one customer).
+3. You are NOT using a shared link - you have not opened a Work Orders web address that someone sent you.</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Work Orders page from the main menu.
+2. Look at the filter bar and the toolbar row for a 'Back to my view' option.
+3. Change one of your filters and look again.
+4. Open a Work Orders link that carries someone else's filters, and look again.
+5. Click 'Back to my view', then look one more time.</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>1. On your own view there is no 'Back to my view' option anywhere - it only belongs to a shared-link visit.
+2. Changing your own filters does not make it appear.
+3. When you open the shared link, 'Back to my view' does appear.
+4. After you click it and you are back on your own view, the option disappears again.</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>Filters epic (key TBD) (S11-N3; S11-R7) [spec v1.6 2026-07-28]</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>On mobile the filter chips sit in a horizontally scrollable row below the tabs, starting with All Filters</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>Mobile Filters</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device (or a mobile-size browser window).
 2. You are on the Work Orders page.</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>1. Look at the row below the tab row (All, Estimates, Completed, My Work Orders).
 2. Swipe the chip row sideways.</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>1. A filter chip row is shown below the tabs, starting with an 'All Filters' chip (with a funnel icon) followed by the individual filter chips (Status, Customer, Lead Technician, ...).
 2. The row scrolls horizontally - chips that do not fit are reachable by swiping.
 3. A right-edge arrow affordance indicates the row can be scrolled (per the design variant).</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 12 S12-R1</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>Tapping All Filters opens a bottom sheet listing every filter as an expandable row with an Apply filters button</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>Mobile Filters</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device.
 2. You are on the Work Orders page.</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>1. Tap the 'All Filters' chip.
 2. Read the sheet from top to bottom.</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>1. A bottom sheet slides up with a drag handle at the top, the centered title 'All Filters' and a close (x) button.
 2. It lists the five filters as expandable accordion rows, each with its icon, name and a down arrow: Status, Customer, Lead Technician, Service Advisor, Asset on site.
 3. A sticky blue 'Apply filters' button sits at the bottom of the sheet.</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 12 S12-R3</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>Selecting statuses in the mobile sheet and tapping Apply filters filters the list and counts on the sheet title</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>Mobile Filters</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device.
 2. You are on the Work Orders page on the All tab; work orders exist in several statuses.
 3. The 'All Filters' bottom sheet is open.</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>1. Tap the Status accordion row to expand it.
 2. Tick one or more statuses.
@@ -4056,99 +4168,99 @@
 4. Reopen the All Filters sheet and look at its title.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>1. Expanding Status reveals the same nine status checkboxes as desktop (Estimate, Approved, In progress, Review, Complete, Invoiced, Paid, Declined, Imported) plus 'Clear selection'.
 2. After 'Apply filters' the sheet closes and the work order list shows only the ticked statuses.
 3. The reopened sheet's title shows the applied-filter count, for example 'All Filters (1)', and the Status accordion header is highlighted with the selected values ticked.</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 12 S12-R2; S12-R3; Story 2 S2-R1</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>Tapping an individual filter chip on mobile opens that filter's own sheet with an 'Apply filter' button</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>Mobile Filters</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device.
 2. You are on the Work Orders page.</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>1. Tap the Status chip (not All Filters).
 2. Read the sheet.
 3. Tick a status and tap the bottom button.</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>1. A bottom sheet opens for that single filter: its title row shows the filter's icon and name (for example 'Status') with a close (x) button - no accordion list of the other filters.
 2. The sheet shows only that filter's options (the nine status checkboxes plus 'Clear selection').
 3. The bottom button reads 'Apply filter' (singular); tapping it applies the selection and filters the list.</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 12 S12-R2; S12-R3</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>The mobile Customer filter has search, multi-select and removable tags, matching desktop</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>Mobile Filters</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device.
 2. You are on the Work Orders page; several customers exist.
 3. The All Filters sheet is open with the Customer accordion expanded.</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>1. Type part of a customer name in the 'Search customer' field and watch the list.
 2. Select two or three customers.
@@ -4156,7 +4268,7 @@
 4. Remove one customer with the x on its tag, then tap 'Apply filters'.</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>1. The list narrows to matching names as you type.
 2. Each selected customer appears as a tag with an x in the input area, and its list row shows a checkmark.
@@ -4164,286 +4276,286 @@
 4. After 'Apply filters' the list shows only work orders of the remaining selected customers, and the sheet title counts the applied filters (for example 'All Filters (2)').</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 12 S12-R2; Story 3 S3-R2/R3/R5</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>The mobile Lead Technician and Service Advisor filters offer their search lists in the sheet</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>Mobile Filters</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device.
 2. You are on the Work Orders page; technicians and advisors exist.
 3. The All Filters sheet is open.</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>1. Expand the Lead Technician accordion row and look at its content.
 2. Collapse it, expand the Service Advisor row and look at its content.
 3. Select one name in either list and tap 'Apply filters'.</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>1. The Lead Technician row opens with a 'Search technician' field and the technician list.
 2. The Service Advisor row opens with a 'Search advisor' field and the advisor list.
 3. Applying a selection filters the work order list just like on desktop.</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 12 S12-R2; Story 4 S4-R1; Story 5 S5-R1</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>The mobile Asset on site filter offers Yes/No with Clear selection in the sheet</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>Mobile Filters</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device.
 2. You are on the Work Orders page; work orders exist in both on-site states.
 3. The All Filters sheet is open.</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>1. Expand the Asset on site accordion row.
 2. Choose Yes and tap 'Apply filters'.
 3. Look at the list.</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>1. The Asset on site row opens showing the two options Yes and No plus 'Clear selection'.
 2. Only one option can be selected at a time.
 3. After applying, the list shows only work orders matching the chosen on-site state.</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 12 S12-R2; Story 6 S6-R1/R2/R3</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>Active chips and Clear filters behave on mobile the same way as on desktop</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>Mobile Filters</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device.
 2. You are on the Work Orders page with at least one filter applied via the sheet.</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>1. Look at the chip row after applying the filter.
 2. Look for a 'Clear filters' control while a filter is active.
 3. Use it and look at the chips and the list.</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>1. The chip for the applied filter shows the active state with the selected value(s), like on desktop.
 2. A 'Clear filters' control appears while at least one filter is active.
 3. Using it removes all active filters, the chips return to default and the full list comes back.</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 12 S12-R2; Story 7 S7-R1/R3; Story 8 S8-R1</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>Mobile has no collapse toggle: the filter chip row is always visible</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>Mobile Filters</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device.
 2. You are on the Work Orders page.</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>1. Look at the toolbar row (Search, sort icon, New Work Order button).
 2. Look for any control that would hide the filter chip row.</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>1. There is no filter-bar collapse/expand (funnel) toggle on mobile.
 2. The filter chip row is always visible on the mobile Work Orders page.</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 12 S12-R4</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>Filters matching no work orders on mobile show the same empty state as desktop</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>Mobile Filters</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device.
 2. You are on the Work Orders page; work orders exist.</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>1. Apply a filter combination that matches no work orders (for example a customer plus a status that customer never has).
 2. Look at the list area.</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>1. The list shows the same no-results empty state as desktop, saying no results were found for the current filters.
 2. The empty state includes the prompt to clear filters.
 3. No error appears.</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 12 S12-N1; Story 8 S8-R3/R4</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>Every Parts list page shows its designed filter buttons</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>Parts Page Filters</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Parts area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>1. Open the Parts area and go to the Inventory page, and look at the filter buttons shown above the table.
 2. Go to the Part Sales page and look at the filter buttons.
@@ -4456,7 +4568,7 @@
 9. On any one of these pages, look at the small icons on the right-hand side of the toolbar.</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>1. Inventory shows four filter buttons: Bin Location, Category, Supply and Vendor.
 2. Part Sales shows four filter buttons: Status, Customer, Created by and Date.
@@ -4471,188 +4583,188 @@
 11. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (which filters actually apply on each Parts page, their full option lists, and what the funnel and column icons do).</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5 #1-#8 and §B.5 shared shell</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>Part Type filter opens a Core / Non Core list with Clear selection</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>Parts Page Filters</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Parts area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>1. On the Parts Returns tab, click the Part Type filter button.
 2. Look at the small menu that opens.</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>1. A small menu opens with two options: Core and Non Core.
 2. A Clear selection action is shown at the bottom of the menu.
 3. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (whether the options are single- or multi-select, and how the list is filtered after choosing).</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5 #9</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>Choosing a Parts filter narrows the list on that page</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>Parts Page Filters</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Parts area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>1. Open a Parts list page that has a filter button (for example Inventory).
 2. Open a filter button and choose one value.
 3. Watch the table below.</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>1. The table updates to show only the rows that match the chosen filter value.
 2. The chosen value is shown on the filter button so you can see what is applied.
 3. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (exactly which filters apply on which Parts page, the full option lists, and whether results update immediately).</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>Parts filters support multiple choices and can be cleared</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>Parts Page Filters</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Parts area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>1. Open a Parts filter button that shows a list of choices.
 2. Try selecting more than one choice.
 3. Use the Clear selection action, then look at the filter bar for a way to clear all filters.</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>1. More than one value can be chosen inside a filter (to be checked live once available).
 2. Clear selection removes the choices for that one filter.
 3. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (whether multi-select, per-filter Clear selection, and an overall Clear filters action all work the same as on the Work Orders page).</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>Every report page shows its designed filter buttons</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>Reports Page Filters</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Reports area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>1. Open the Reports area and go to the Timesheet Activities report, and look at the filter buttons shown above the report table.
 2. Go to the Timesheets (Payroll Timesheet) report and look at the filter buttons.
@@ -4671,7 +4783,7 @@
 15. Go to the QB Unexported report. Look at the filter buttons on the Customers tab, then switch to the Vendors tab, then to the Journal Entries tab, looking at the filter buttons on each.</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>1. Timesheet Activities shows four filter buttons: Staff, Date, Status and Modified by.
 2. Payroll Timesheet shows two filter buttons: Employee and Date.
@@ -4697,138 +4809,138 @@
 22. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (the option lists behind each filter button; and because several report bodies in the design are sample placeholders, the real report columns come from the same product write-up).</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #1-#23</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>Choosing a Reports filter narrows the report results</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>Reports Page Filters</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Reports area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>1. Open the Reports area and go to any report — for example the Sales report.
 2. Open one of the filter buttons shown above the report table and choose one value.
 3. Look at the report table below.</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>1. The report updates to show only the rows matching the chosen filter value, and the chosen value is shown on the filter button.
 2. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (exactly which filters apply on each report, the full option lists, and whether results update immediately).</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>New Reports filter types behave correctly (Location, Transaction Type, etc.)</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>Reports Page Filters</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Reports area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>1. Open the Reports area and go to the reports that use them (for example A/R Aging Detail, Notes) report.
 2. Look at the filter buttons shown above the report table.</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>1. Each new filter type (Location, Transaction Type, Invoice Status, Type, User, Mention) opens a list of choices and filters the report by the choice.
 2. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (the exact choices, single- vs multi-select, and how each new filter type filters the report).</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>Date range filter: results update when both start and end dates are picked</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>Reports Page Filters</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The new filter bar has rolled out to a page with a Date filter chip (a report, or a Parts page with a date column).
 3. Records exist inside and outside the date range you will pick.</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>1. Click the Date filter chip.
 2. Look at the panel that opens.
@@ -4837,7 +4949,7 @@
 5. Look at the results and the chip.</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>1. A start/end date picker opens - there are NO preset ranges (no 'Last 30 days' shortcuts) and NO pre-filled default range.
 2. After only the start date, the results do not change yet.
@@ -4845,42 +4957,42 @@
 4. Only one date range can be active at a time on that chip, and the chip shows the active range.</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); tech plan 2026-07-29 D19 (date-range chip: no presets, no default, applies on second date); spec v1.3 Parts + Reports sections (export awaited)</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>Page toolbar Search expands in place and narrows the list as you type</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with several work orders listed.</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>1. Find the Search control in the page toolbar (a magnifier icon with the word Search).
 2. Click it.
@@ -4890,50 +5002,50 @@
 6. Expand it again, type text, and click somewhere else.</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>1. The control expands in place into a small search box inviting you to type (engineering copy: 'Type to search').
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>1. The control expands in place into a small search box showing the placeholder 'Type to search'.
 2. The list narrows as you type, after a brief pause - and ONLY this page's list changes, nothing else in the app.
 3. The round x clears the text and the full list returns.
 4. Clicking away with an empty box collapses it back to the Search button; with text in it, the box stays open.</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); tech plan 2026-07-29 D18; spec v1.3 S13-R1..R7, S13-R9, S13-R15 (export awaited)</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>Filters epic (key TBD) (S13-R1 (placement in the toolbar action group); S13-R9 (scoped to this table only); S13-R12; S13-R15 (blur rules)) [spec v1.6 2026-07-28]</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>Page search combines with filters and is cleared separately</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with work orders for several customers and statuses.</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>1. Apply one filter (for example a Status).
 2. Type a search term in the page search box.
@@ -4941,104 +5053,109 @@
 4. Re-type the search, then clear ONLY the filter.</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t>1. With both active, the results match the filter AND the search together (both narrow the list at once).
 2. Clearing the search keeps the filter applied.
 3. Clearing the filter keeps the search applied - each is cleared by its own control without wiping the other.</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); tech plan 2026-07-29 D18; spec v1.3 S13-R10/R13 + S8-R5 (export awaited)</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>The page search text is remembered and restored like filters</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>Filters epic (key TBD) (S13-R10 (search and filters are additive); S13-R13 (each cleared independently); S8-R5) [spec v1.6 2026-07-28]</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Your typed search stays in this browser tab only and is never saved</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Work Orders page with several work orders listed.
+3. You know how to open a second browser tab on the same page.</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>1. Type a search term in the page Search box that matches some work orders.
+2. Sort the table by a column, then move to the next page of results.
+3. Go to another area of the app and come back to the Work Orders page.
+4. Open the Work Orders page in a SECOND browser tab and look at its Search box.
+5. Close every browser tab, open the browser again and go back to the Work Orders page.</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>1. Sorting and paging keep your search applied - your text stays in the box and the list stays narrowed.
+2. Leaving the page and coming back also keeps your text in the box and the list still narrowed.
+3. The second browser tab starts clean: its Search box is empty and it shows the full list. Each tab keeps its own search.
+4. After closing the browser and coming back, the Search box is empty and the list is unsearched - a typed search is never remembered for next time (your filters, unlike the search, ARE remembered).</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>Filters epic (key TBD) (S13-R14 (retained for the browser tab session); S13-R25 (never stored against the account; each tab independent); S13-N4 (not restored on a later visit); S10-R5) [spec v1.6 2026-07-28]</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>The search term is part of the shareable page link</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Page Search Toolbar</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page.</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>1. Type a search term that matches some work orders.
-2. Go to another area of the app and come back to the Work Orders page.
-3. Now type a search term that matches NOTHING, leave the page, and come back again.</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>1. The search box comes back with your text still in it and the list still narrowed by it - just like the filters.
-2. A remembered search that matches nothing shows the no-results empty state - the remembered text is NOT silently thrown away.</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); tech plan 2026-07-29 D18; spec v1.3 S10-R4/R5, S10-N2 (export awaited)</t>
-        </is>
-      </c>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>The search term is part of the shareable page link</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>Page Search Toolbar</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. You are on the Work Orders page.</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>1. Type a search term and copy the page address.
 2. Open the copied address in a fresh tab.
 3. Hand-edit the search part of the address into something malformed and load it.</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>1. The address contains the search term after step 1.
 2. The fresh tab opens with the search box filled and the list already narrowed.
@@ -5046,138 +5163,148 @@
 4. A search arriving via a link is view-only, the same as filters from a link - it does not overwrite your own remembered search.</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); tech plan 2026-07-29 D18 + G7; spec v1.3 S11-R4/R5, S11-N2 (export awaited)</t>
-        </is>
-      </c>
-      <c r="I93" s="2" t="inlineStr"/>
-      <c r="J93" s="2" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>Filters epic (key TBD) (S11-R4 (query reflected in the URL); S11-R5 (URL query pre-applied with the control filled); S11-N2 (malformed query ignored with no error); S11-R8 (rationale: no saved value to overwrite)) [spec v1.6 2026-07-28]</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>On mobile the search expands in the toolbar and buttons make room</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device.
 2. You are on the Work Orders page.</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>1. Tap the Search control in the page toolbar.
 2. Type a term and watch the list.
-3. Visit a page that has several small icon-only toolbar buttons (for example Parts Inventory or Purchase Orders) and look at its toolbar.</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="inlineStr">
+3. Visit a page that has several small icon-only toolbar buttons (for example Parts Inventory or Purchase Orders) and look at its toolbar.
+4. With text in the box, tap somewhere else on the screen; then clear the text and tap somewhere else again.</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t>1. The search expands inline inside the toolbar - no separate popup window opens.
 2. The list narrows as you type, same as desktop.
-3. To make room, the page's main button no longer stretches full-width, and pages with two or more small icon buttons collapse them into a single 'more' menu.</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); tech plan 2026-07-29 D21; spec v1.3 S13-R16..R21 (export awaited)</t>
-        </is>
-      </c>
-      <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="2" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+3. To make room, the page's main button no longer stretches full-width, and pages with two or more small icon buttons collapse them into a single 'more' menu.
+4. The box stretches to fill the space left in the action row instead of staying the narrow desktop size, and every other toolbar button stays visible and in the same place while you search.
+5. There is no extra 'search is on' badge on mobile: with text in it the box simply stays open showing your text, and an empty box closes back to the Search button when you tap elsewhere - exactly as on desktop.</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Filters epic (key TBD) (S13-R16 (inline expansion with no modal); S13-R17 (field fills the remaining width); S13-R18 (CTA hug width); S13-R19 (2+ icon actions -&gt; "more" kebab); S13-R20 (no active-query indicator); S12-R5) [spec v1.6 2026-07-28]</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>Every list page keeps its own search box (Parts, Reports, detail tabs)</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. The page-search rollout has shipped (same programme as the Work Orders filters).</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>1. Visit several list surfaces: a Parts view (for example Inventory), a report, a customer's Notes tab on the customer page, and any pop-up list that used to be searchable.
-2. On each, look for that surface's own search box and use it.</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t>1. Every list surface that could be text-searched before still offers its own search control - no list silently lost its search.
-2. Each search box narrows only its own list, not any other page.</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); tech plan 2026-07-29 Phase 9.1 (built-in table search, opt-out); spec v1.3 S13-R22 + S14-R5/R6 (export awaited)</t>
-        </is>
-      </c>
-      <c r="I95" s="2" t="inlineStr"/>
-      <c r="J95" s="2" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. The page-search rollout has finished everywhere (run this sweep at the end of the rollout, not part-way through).
+3. You can reach Work Orders, Customers, Parts, Administration, Reports and the Dashboard.</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>1. Work Orders surfaces: the Work Orders list, a work order's History tab, the Work Order Log dialog opened from that tab's kebab menu, a line's Line Log dialog opened from the Lines tab, and the work order's Notes tab.
+2. Customer and asset surfaces: the Customers list, then on one customer - Contacts, Assets, Invoices, Work Orders, Part Sales, Fees &amp; Discounts, Notes; then on one asset - Work Orders, Invoices, Notes.
+3. Parts surfaces: Inventory, Catalog, Part Sales, Purchase Orders, Returns, Credits, Vendors, Vendor Invoices (web address /parts/deliveries), a vendor's Unpaid Invoices, and Part History.
+4. Administration surfaces: Locations, Roles &amp; Permissions, Staff, Departments, Taxes, Labor Rates, Canned Lines, Payment Methods, Fees &amp; Discounts, Asset Types, Categories, Pricing.
+5. Reports and Dashboard surfaces: IBS Batch Transactions, Sales Tax Invoices, the Dashboard, and one dashboard report drill-down.
+6. On each surface, find that table's own Search box and type something that matches one of its rows. Then open a work order's Parts tab and look at the search input it already has.</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>1. Every table listed above has its own Search box - no table lost the ability to narrow by text.
+2. Each Search box narrows only its own table; nothing else in the app changes.
+3. Where the table sits inside a dialog (the Work Order Log, the Line Log, the audit log dialog), the Search box is inside that dialog and works there.
+4. The work order Parts tab keeps the local search input it already had - it was deliberately left as it is.</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>Filters epic (key TBD) (S14-R6 (audit: 42 surfaces across 39 components; Work Order Parts excluded); S14-R5 (app-wide sweep); S13-R22 (every table carries a search control); S14-N1 (verify once at the end)) [spec v1.6 2026-07-28]</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>The top navigation search no longer filters page lists</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with several work orders listed.</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>1. Type a term into the TOP NAVIGATION search (the app-wide search at the top), not the page's own search box.
 2. Watch the Work Orders list while typing.
@@ -5185,152 +5312,465 @@
 4. Pick one of the results offered in the navigation search's dropdown.</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t>1. The page list does NOT narrow while you type in the navigation search - only its dropdown of matching records appears.
 2. The same holds on the other pages checked.
 3. Picking a dropdown result still takes you to that record - the navigation search keeps its find-and-open role.</t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); tech plan 2026-07-29 Phase 9 (search decoupling); spec v1.3 Story 14 S14-R2/R3 (export awaited)</t>
-        </is>
-      </c>
-      <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="2" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>Filters epic (key TBD) (S14-R1 (navigational results only); S14-R2 (the page-filtering code path is removed rather than dormant); S14-R4 (the list is left untouched); S14-R5) [spec v1.6 2026-07-28]</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>The Search box changes look as you hover over it, open it and type</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Page Search Toolbar</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Work Orders page with several work orders listed.</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>1. Look at the right-hand end of the toolbar row, before the small icon buttons and before the 'New Work Order' button.
+2. Move the mouse pointer over the 'Search' button without clicking.
+3. Click the 'Search' button, then look at the box that opens and at the other toolbar buttons.
+4. Type a few letters.
+5. Delete what you typed and type a very long sentence instead.</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>1. A 'Search' button is shown with a small magnifier icon next to the word 'Search'; it is plain text on a see-through background, with no border and no fill.
+2. Hovering over it gives it a light grey background; the word 'Search' keeps its own colour.
+3. Clicking it turns the button into a small text box in the same spot (the design sets it at 180 pixels wide), the typing cursor is already inside it, and the box grows towards the left so the other toolbar buttons do not move.
+4. While the box is empty it shows the magnifier icon and the grey placeholder text 'Type to search'.
+5. As soon as you type, your text shows in a dark grey and a small round x appears at the right-hand end of the box.
+6. A very long sentence does not make the box grow and does not cut the text off - the text scrolls sideways inside the box and the cursor stays where you are typing.</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>Filters epic (key TBD) (S13-R2 (default text button); S13-R3 (hover fill); S13-R4 (expands in place at 180px); S13-R5 (placeholder "Type to search"); S13-R6 (typed text + X-circle clear); S13-R8 (long queries scroll)) [spec v1.6 2026-07-28]</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>The list narrows shortly after you stop typing, with no button to press</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Page Search Toolbar</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Work Orders page with several work orders listed.
+3. You can also open the Parts Inventory page.</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>1. On the Work Orders page open the Search box and type a few letters that match some work orders. Do NOT press Enter.
+2. Watch the work order table for a second or two.
+3. Look around the Search box for an Apply or Submit button.
+4. Now press Enter while your text is still in the box.
+5. Do the same on the Parts Inventory page.</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>1. The list narrows on its own a moment after you stop typing (about a third of a second) - you never press Enter or any button.
+2. The matching rows appear in the table you were already looking at; no separate results page, results list or pop-up window opens.
+3. There is no Apply or Submit button anywhere next to the Search box.
+4. Pressing Enter changes nothing that has not already happened - the same rows stay listed and no page reload happens.
+5. Parts Inventory behaves the same way, only it waits a fraction longer before reacting; that longer wait is on purpose because that page carries more data.</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>Filters epic (key TBD) (S13-R7 (applies as you type; debounced 300ms; no apply/submit; Enter not required; Inventory 350ms); S13-R12 (results replace the table in place)) [spec v1.6 2026-07-28]</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>One search box serves all Work Orders tabs and searches the tab you are on</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Page Search Toolbar</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. Work orders exist in several statuses, so the All, Estimates and Completed tabs each have rows.
+3. You have a word (for example part of a customer name) that matches work orders on more than one of those tabs.</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>1. On the All tab, type that word into the page Search box.
+2. Click the Estimates tab and look at the Search box and the list.
+3. Click the Completed tab and look again.
+4. Still on the Completed tab, clear the search with the round x, then go back to the All tab.</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>1. On the All tab only the rows matching your word remain.
+2. On the Estimates tab your word is still in the Search box, and the list shows only Estimates rows that match it - no rows from the other tabs appear.
+3. The Completed tab behaves the same way: your word is still there and only that tab's matching rows are listed.
+4. Clearing the search clears it for all the Work Orders tabs - they share one search - and each tab shows its full list again.</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>Filters epic (key TBD) (S13-R11 (search applies within the active tab only); S13-R24 (the Work Orders tabs share a single query - views of one dataset)) [spec v1.6 2026-07-28]</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Each Report tab and each Parts view keeps its own separate search</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Page Search Toolbar</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You can open at least two Parts views (for example Inventory and Purchase Orders).
+3. You can open a report that has more than one tab.</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>1. On a Parts view (for example Inventory) type a word into that page's Search box.
+2. Switch to another Parts view (for example Purchase Orders) and look at its Search box and list.
+3. Type a different word there, then switch back to the first view.
+4. Do the same on a report with tabs: search on one tab, then switch to another tab of the same report.</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>1. The second Parts view opens with an empty Search box and its full list - the word you typed on the first view is not carried over.
+2. Going back to the first view brings its own word back and narrows its list again.
+3. Each report tab behaves the same way: a word typed on one tab stays on that tab only, and each tab remembers its own.
+4. No search is ever applied to a table it was not typed on.</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>Filters epic (key TBD) (S13-R24 (Reports sub-tabs and Parts views each keep their own query); S13-R11; S10-R4 (each view/tab keeps its own set)) [spec v1.6 2026-07-28]</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>An old link carrying a top-search word no longer narrows the page list</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Page Search Toolbar</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You have a Work Orders web address from BEFORE this change that still carries a word typed into the top-of-screen search (a bookmark, or a link someone sent). If you do not have one, hand-type that old search part onto the end of the Work Orders address.</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>1. Open that old web address.
+2. Look at the work order list and at the page's own Search box.
+3. Look at the web address once the page has loaded.
+4. Type a word into the top-of-screen search, then reload the page.</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>1. The page opens with the normal list for your own saved filters - the old search word does NOT narrow the list.
+2. The page's own Search box is empty; nothing was carried into it.
+3. No error is shown - the leftover search part in the address is simply ignored. (Whether it also disappears from the address is not important; note what you see.)
+4. After typing in the top-of-screen search and reloading, the list is still not narrowed and nothing about that word was remembered for the list.</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>Filters epic (key TBD) (S14-R3 (state / URL parameters / persisted values carrying a global search term into page filtering are removed with it); S14-R2; S14-R1) [spec v1.6 2026-07-28]</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Collapsing the filter bar keeps an active search working</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Page Search Toolbar</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Work Orders page and the filter bar is expanded.
+3. A word is typed in the page Search box and the list is narrowed by it.</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>1. With the search still active, click the funnel button in the toolbar to collapse the filter bar.
+2. Look at the table and at the toolbar row.
+3. Expand the filter bar again.</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>1. The list stays narrowed by your word - collapsing the filter bar does not cancel the search.
+2. The Search box stays in the toolbar row with your word still showing; it is not tucked away with the filter bar, because the search sits in the toolbar row and the chips sit in the row below.
+3. Expanding the bar again changes nothing about the search or the narrowed list.</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>Filters epic (key TBD) (S13-E1 (a collapsed filter bar keeps an active query applying and the search control stays in the toolbar); §4 Key Decisions (page search is separate from the filter bar)) [spec v1.6 2026-07-28]</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>Page search opens with the 'Search or ask a question' box</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>Page Search (Command-K)</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Some sample work orders, customers, assets, parts and vendors exist.</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>1. From anywhere in the app, open the page search (the Search box in the top bar, or press Command-K / Ctrl-K).
 2. Look at the search panel that opens.</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t>1. A search panel opens with an empty search box at the top.
 2. The box shows the placeholder text 'Search or ask a question' with a magnifier icon on the left and a clear (X) button on the right.
 3. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (whether 'ask a question' means an AI search — this is out of scope for now).</t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="2" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>Page search shows entity tabs All, Work Orders, Customers, Assets, Parts...</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>Page Search (Command-K)</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Some sample work orders, customers, assets, parts and vendors exist.</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>1. Open the page search panel.
 2. Look at the row of tabs under the search box.</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t>1. A row of tabs is shown: All, Work Orders, Customers, Assets, Parts, Vendors and Part Sales.
 2. The All tab is selected by default.
 3. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (whether choosing a tab limits results to that type only).</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>Typing a term shows grouped results with counts and highlighting</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>Page Search (Command-K)</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Some sample work orders, customers, assets, parts and vendors exist.</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>1. Open the page search panel.
 2. Type a few letters (for example 'Fib') into the search box.
 3. Look at the results.</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t>1. Results are grouped by type with a count next to each group heading, for example 'Work orders (2)', 'Customers (2)', 'Vendors (1)', 'Assets (2)', 'Parts (1)'.
 2. The matching part of each result is highlighted in yellow.
@@ -5338,523 +5778,570 @@
 4. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (how matching works — exact vs fuzzy — and the ranking order).</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr"/>
-      <c r="J99" s="2" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>Recent searches are shown grouped by Today, Yesterday, Past week...</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>Page Search (Command-K)</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Some sample work orders, customers, assets, parts and vendors exist.</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>1. Open the page search panel without typing anything.
 2. Look at the list shown under the tabs.</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>1. A list of recent items is shown, grouped under headings: Today, Yesterday, Past week and Past 30 days.
 2. Each item shows a type icon, its name and a short detail line (for example a customer address or a date).
 3. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (how many recent items are kept and how long they persist).</t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
         </is>
       </c>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>Re-opening page search keeps the last typed text and its results</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>Page Search (Command-K)</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Some sample work orders, customers, assets, parts and vendors exist.</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>1. Open the page search and type a term (for example 'Fibridge').
 2. Close the panel, then open it again.
 3. Look at the search box and the results.</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
         <is>
           <t>1. The previous search text is still in the box (shown selected/highlighted) and its results are shown.
 2. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (whether the last search is remembered per person and for how long — this is the 'persisting search' state).</t>
         </is>
       </c>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
         </is>
       </c>
-      <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>Hovering a search result shows quick-action buttons</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>Page Search (Command-K)</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Some sample work orders, customers, assets, parts and vendors exist.</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>1. Open the page search panel (recent items or results shown).
 2. Move the mouse over a result row.
 3. Look at the right side of that row.</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t>1. Quick-action buttons appear on the row, depending on the result type — for example 'Add new line' on a work order, 'New work order' on an asset or customer, 'Add part' on a part sale, 'Add contact' on a vendor and 'Add to work order' on a part.
 2. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (exactly which quick actions show for which result type, and what each one does).</t>
         </is>
       </c>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
         </is>
       </c>
-      <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="2" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>Page search shows keyboard hints and supports keyboard navigation</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>Page Search (Command-K)</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Some sample work orders, customers, assets, parts and vendors exist.</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>1. Open the page search panel.
 2. Look at the bar along the bottom of the panel.
 3. Use the up/down arrow keys, Enter and Esc.</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr">
         <is>
           <t>1. The bottom bar shows keyboard hints: up/down arrows labelled 'Navigate', the Enter key labelled 'Select', and 'Close esc'.
 2. Arrow keys move the highlight between results, Enter opens the highlighted result, and Esc closes the panel (to be checked live once available).
 3. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (exact keyboard behaviour).</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
         </is>
       </c>
-      <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" s="2" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+      <c r="I111" s="2" t="inlineStr"/>
+      <c r="J111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>Page search results include a Refresh action</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>Page Search (Command-K)</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Some sample work orders, customers, assets, parts and vendors exist.</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>1. Open the page search and type a term so grouped results appear.
 2. Look at the top right of the results area.</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr">
         <is>
           <t>1. A 'Refresh' link is shown at the top right of the results.
 2. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (what Refresh reloads and when it is shown).</t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
         </is>
       </c>
-      <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="2" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+      <c r="I112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Page search scope belongs to Filters or Global Search (to decide)</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Page Search (Command-K)</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. Some sample work orders, customers, assets, parts and vendors exist.</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>1. Review where the page search / Command-K component is owned for testing.
+2. Compare against the Global Search project's existing cases.</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>1. The page-search component is agreed to belong to either the Filters test suite or the Global Search test suite, not both.
+2. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (product/QA decision on which project owns page search).</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr"/>
+      <c r="J113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>The work order list request carries the active filter selections</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>API — Work Orders List Filtering</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser with developer tools open on the Network tab.
 2. You are on the Work Orders page with no filters applied.</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>1. Apply a Status selection and a Customer selection in the filter bar.
 2. In the Network tab, find the work order list request the page sends after the change.
 3. Inspect the request's parameters.</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr">
         <is>
           <t>1. The list request includes the active filter selections as request parameters (status values and customer identifiers).
 2. The request succeeds (HTTP 200).
 3. The response contains only work orders matching the filters - the filtering is done by the backend, not just hidden client-side.</t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 2 S2-R2; Story 3 S3-R6 (backend view)</t>
         </is>
       </c>
-      <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="2" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+      <c r="I114" s="2" t="inlineStr"/>
+      <c r="J114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>A combined multi-filter request returns only work orders matching all filters, any value within each filter</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>API — Work Orders List Filtering</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with developer tools open on the Network tab.
 2. Seeded ZZAUTOTEST work orders exist: customer A with an Estimate and an Approved work order, customer B with an Estimate work order.</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>1. On the Work Orders page apply Status = Estimate + Approved and Customer = customer A.
 2. Capture the resulting list request and response.</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr">
         <is>
           <t>1. One request carries both filters together (both statuses and the customer).
 2. The response returns customer A's Estimate and Approved work orders only.
 3. Customer B's work orders are absent - the customer filter and status filter both restrict the result, while the two statuses combine as either-or.</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 2 S2-R2; Story 3 S3-R6; Story 8 S8-R3 (backend view)</t>
         </is>
       </c>
-      <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+      <c r="I115" s="2" t="inlineStr"/>
+      <c r="J115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>A list request with a deleted or unknown filter value is handled without a server error</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>API — Work Orders List Filtering</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
+      <c r="C116" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in and can replay/edit the work order list request (developer tools or an API client).
 2. You have a captured filtered list request, and one of its filter values has since been deleted (for example a removed ZZAUTOTEST customer) or is a made-up identifier.</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>1. Send the list request containing the no-longer-existing (or made-up) filter value.
 2. Inspect the HTTP status and the response body.</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr">
         <is>
           <t>1. The backend does not fail with a server error (no HTTP 5xx).
 2. The response is a normal, successful list response - the invalid value is ignored or simply matches nothing.
 3. Any still-valid filter values in the same request are applied normally.</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 10 S10-N1; Story 11 S11-R3</t>
         </is>
       </c>
-      <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="I116" s="2" t="inlineStr"/>
+      <c r="J116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>A list request with malformed filter parameters does not produce a server error</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>API — Work Orders List Filtering</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
+      <c r="C117" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in and can replay/edit the work order list request.
 2. You have a captured filtered list request to tamper with.</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>1. Corrupt the filter parameters (wrong types, scrambled values, nonsense text) and send the request.
 2. Inspect the HTTP status and the response body.
 3. Also open the equally malformed page URL in the browser and watch the page.</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr">
         <is>
           <t>1. The backend responds gracefully - no HTTP 5xx / crash; either a normal (unfiltered or empty) list or a clean validation response.
 2. In the browser the page still loads without filters and without an error message, matching the malformed-URL requirement.</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 11 S11-N1</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="2" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="I117" s="2" t="inlineStr"/>
+      <c r="J117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>A filter combination matching nothing returns a successful empty list, not an error</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>API — Work Orders List Filtering</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with developer tools open on the Network tab.
 2. A filter combination is known to match no work orders (for example a seeded customer plus a status they never have).</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>1. Apply that filter combination on the Work Orders page.
 2. Capture the list request and response.</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr">
         <is>
           <t>1. The request succeeds (HTTP 200).
 2. The response contains an empty result set (zero work orders) - an empty match is a normal outcome, not an error.
 3. The page renders the no-results empty state from this response.</t>
         </is>
       </c>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 8 S8-R3; Story 2 S2-N3</t>
         </is>
       </c>
-      <c r="I109" s="2" t="inlineStr"/>
-      <c r="J109" s="2" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="I118" s="2" t="inlineStr"/>
+      <c r="J118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>Saved-filters service round-trip: save, reload, and per-user isolation</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>API — Work Orders List Filtering</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser with developer tools open on the Network tab.
 2. A second user account is available.</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>1. On the Work Orders page, change a filter and watch the Network tab for the save request the page sends shortly after.
 2. Reload the page and find the load request for the saved page state.
@@ -5862,7 +6349,7 @@
 4. With an API client (or by editing the request), ask the saved-state service for a page key that was never saved.</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr">
         <is>
           <t>1. Changing a filter sends a save (PUT) to the per-user page-preferences service carrying the page's state, and it succeeds (HTTP 200).
 2. On reload the page requests the saved state back (GET, HTTP 200) and applies it - the filters return without you redoing them.
@@ -5870,13 +6357,13 @@
 4. Asking for a never-saved key returns success with an empty value, not an error page.</t>
         </is>
       </c>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); tech plan 2026-07-29 section 4-1.3 (GET/PUT /api/users/me/preferences/{pageKey}); spec v1.3 S10 per-user persistence (export awaited)</t>
         </is>
       </c>
-      <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="2" t="inlineStr"/>
+      <c r="I119" s="2" t="inlineStr"/>
+      <c r="J119" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/filters-v1-testrail-import.xlsx
+++ b/testrail-import/filters-v1-testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J119"/>
+  <dimension ref="A1:J111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Filters (Epic key TBD); tech plan 2026-07-29 D20 (per-view/per-tab state scoping); spec v1.3 Key Decisions (export awaited)</t>
+          <t>Filters (Epic key TBD) (spec v1.6 S10-R4; §4 "Parts and Reports selections are scoped to their view/tab and persist there"); Branko answers 2026-07-31 Q5 exception 1; tech plan 2026-07-29 D20</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
@@ -4565,7 +4565,8 @@
 6. Go to the Purchase Orders page and look at the filter buttons.
 7. Go to the Vendor Invoices page and look at the filter buttons.
 8. Go to the Vendors list page and look at the filter buttons.
-9. On any one of these pages, look at the small icons on the right-hand side of the toolbar.</t>
+9. On any one of these pages, look at the small icons on the right-hand side of the toolbar.
+10. On each page above, open one of its filter buttons, look at the list of choices inside it, and pick a value to check the list changes.</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -4580,12 +4581,14 @@
 8. The Vendors list page shows two filter buttons: Vendor and State/Province. Note: the developers have not been given a design for the Vendors page filters yet, so this page may not have them — write down what you actually see instead of failing the whole test.
 9. On every page above, each filter button shows a small icon, the filter name and a down arrow.
 10. Every Parts list page also shows a Search (magnifier) icon and a filter (funnel) icon in the toolbar; some pages (for example Inventory) also show a column/layout toggle icon.
-11. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (which filters actually apply on each Parts page, their full option lists, and what the funnel and column icons do).</t>
+11. Every filter button shown above is a working filter on that page - none of them is display-only.
+12. The choices inside each filter come from your own shop's data (for example your real vendors or categories), so there is no fixed list to compare against - check that the choices you see match the data in your shop.
+13. Still to check on the live build: what the funnel icon and the column/layout icon do (the written description does not cover the toolbar icons).</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5 #1-#8 and §B.5 shared shell</t>
+          <t>Filters (Epic key TBD) (spec v1.6 §2 Feature Overview -&gt; Parts Filters; §4 Key Decisions -&gt; "Context-specific filter sets on Parts and Reports" + "Multi-select where it makes sense"); Branko answers 2026-07-31 Q2/Q3/Q5/Q7; Figma 11884-16885</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr"/>
@@ -4621,19 +4624,22 @@
       <c r="F85" s="2" t="inlineStr">
         <is>
           <t>1. On the Parts Returns tab, click the Part Type filter button.
-2. Look at the small menu that opens.</t>
+2. Look at the small menu that opens.
+3. Tick Core, then also tick Non Core, and watch the list below.
+4. Use Clear selection.</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
           <t>1. A small menu opens with two options: Core and Non Core.
 2. A Clear selection action is shown at the bottom of the menu.
-3. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (whether the options are single- or multi-select, and how the list is filtered after choosing).</t>
+3. You can tick both Core and Non Core at the same time - this filter allows more than one choice.
+4. As soon as you tick a choice the list below narrows to matching parts straight away, with no Apply button to press; Clear selection puts the list back.</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5 #9</t>
+          <t>Filters (Epic key TBD) (spec v1.6 §2 Feature Overview -&gt; Parts Filters; §4 Key Decisions -&gt; "Context-specific filter sets on Parts and Reports" + "Multi-select where it makes sense"); Branko answers 2026-07-31 Q2/Q3/Q5/Q7; Figma 11884-16885</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr"/>
@@ -4677,12 +4683,12 @@
         <is>
           <t>1. The table updates to show only the rows that match the chosen filter value.
 2. The chosen value is shown on the filter button so you can see what is applied.
-3. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (exactly which filters apply on which Parts page, the full option lists, and whether results update immediately).</t>
+3. The list narrows as soon as you pick the value - there is no Apply or Search button to press. Every filter button on every Parts page works this way.</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5</t>
+          <t>Filters (Epic key TBD) (spec v1.6 §2 Feature Overview -&gt; Parts Filters; §4 Key Decisions -&gt; "Context-specific filter sets on Parts and Reports" + "Multi-select where it makes sense"); Branko answers 2026-07-31 Q2/Q3/Q5/Q7; Figma 11884-16885</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr"/>
@@ -4718,20 +4724,20 @@
       <c r="F87" s="2" t="inlineStr">
         <is>
           <t>1. Open a Parts filter button that shows a list of choices.
-2. Try selecting more than one choice.
+2. Select more than one choice, then look at the filter button.
 3. Use the Clear selection action, then look at the filter bar for a way to clear all filters.</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>1. More than one value can be chosen inside a filter (to be checked live once available).
+          <t>1. More than one value can be chosen inside the filter, and the button shows what you picked.
 2. Clear selection removes the choices for that one filter.
-3. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (whether multi-select, per-filter Clear selection, and an overall Clear filters action all work the same as on the Work Orders page).</t>
+3. A Clear filters button appears in the filter bar while any filter is set, and using it clears them all at once - exactly as it works on the Work Orders page.</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Filters (Epic key TBD); Figma 11884-16885 (Parts filters); design-notes.md §B.5</t>
+          <t>Filters (Epic key TBD) (spec v1.6 §2 Feature Overview -&gt; Parts Filters; §4 Key Decisions -&gt; "Context-specific filter sets on Parts and Reports" + "Multi-select where it makes sense"); Branko answers 2026-07-31 Q2/Q3/Q5/Q7; Figma 11884-16885</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr"/>
@@ -4740,31 +4746,83 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>Every filter a page had before is still available in the new filter bar</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Parts Page Filters</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You have a written list of the filters each Parts page and each report offers today, before the new filter bar (take screenshots of the old screens first, or ask the developers for the list).
+3. Sample data is present in the Parts area and in the Reports area.</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>1. Take your before-list for one page.
+2. Open the same page with the new filter bar.
+3. Compare the filter buttons you now see against your before-list.
+4. Open each button and compare the choices inside it against the choices the old filter offered.
+5. Repeat steps 1 to 4 for the other Parts pages and for each report.</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>1. Every filter the page offered before is still offered - nothing has been taken away.
+2. Every choice each of those filters offered before is still available inside the new button.
+3. If any filter or choice is missing, write down exactly which page, which filter and which choice - that is a bug worth reporting.</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD) (spec v1.6 §2 Parts Filters + Reports Filters); Branko answers 2026-07-31 Q3 ("support all the filters we have right now in the app as well as all choices per filter"); tech plan 2026-07-29 rollout rule</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
           <t>Every report page shows its designed filter buttons</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>Reports Page Filters</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Reports area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>1. Open the Reports area and go to the Timesheet Activities report, and look at the filter buttons shown above the report table.
 2. Go to the Timesheets (Payroll Timesheet) report and look at the filter buttons.
@@ -4780,10 +4838,11 @@
 12. Go to the Notes report and look at the filter buttons and the toolbar icons.
 13. Go to the Reminders report and look at the filter buttons.
 14. Go to the IBS Batch Transactions report and look at the filter buttons and the view tabs.
-15. Go to the QB Unexported report. Look at the filter buttons on the Customers tab, then switch to the Vendors tab, then to the Journal Entries tab, looking at the filter buttons on each.</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="inlineStr">
+15. Go to the QB Unexported report. Look at the filter buttons on the Customers tab, then switch to the Vendors tab, then to the Journal Entries tab, looking at the filter buttons on each.
+16. On each report above, open one of its filter buttons, look at the list of choices inside it, and pick a value to check the report changes.</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>1. Timesheet Activities shows four filter buttons: Staff, Date, Status and Modified by.
 2. Payroll Timesheet shows two filter buttons: Employee and Date.
@@ -4806,107 +4865,62 @@
 19. QB Unexported shows three filter buttons and the first one changes with the tab: Customer, Date and Type on the Customers tab; Vendor, Date and Type on the Vendors tab; User, Date and Type on the Journal Entries tab.
 20. Each of the six A/R and A/P aging reports also shows a print icon in its toolbar.
 21. On every report above, each filter button shows its name and a down arrow.
-22. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (the option lists behind each filter button; and because several report bodies in the design are sample placeholders, the real report columns come from the same product write-up).</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6 #1-#23</t>
-        </is>
-      </c>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+22. Every filter button shown above is a working filter on that report - none of them is display-only.
+23. The choices inside each filter come from your own shop's data (for example your real vendors or categories), so there is no fixed list to compare against - check that the choices you see match the data in your shop.
+24. Still to check on the live build: the real columns of the Sales Tax report and of the six A/R and A/P aging reports. The design uses sample placeholder tables for those, and the written description does not list their columns.</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD) (spec v1.6 §2 Reports Filters; §4 Key Decisions "New date-range filter type" + "Multi-select where it makes sense"); Branko answers 2026-07-31 Q2/Q3/Q5/Q7; Figma 11903-10573</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>Choosing a Reports filter narrows the report results</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>Reports Page Filters</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Reports area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>1. Open the Reports area and go to any report — for example the Sales report.
 2. Open one of the filter buttons shown above the report table and choose one value.
 3. Look at the report table below.</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>1. The report updates to show only the rows matching the chosen filter value, and the chosen value is shown on the filter button.
-2. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (exactly which filters apply on each report, the full option lists, and whether results update immediately).</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6</t>
-        </is>
-      </c>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>New Reports filter types behave correctly (Location, Transaction Type, etc.)</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>Reports Page Filters</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. You are on the Reports area of the app with some sample data present.</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Reports area and go to the reports that use them (for example A/R Aging Detail, Notes) report.
-2. Look at the filter buttons shown above the report table.</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>1. Each new filter type (Location, Transaction Type, Invoice Status, Type, User, Mention) opens a list of choices and filters the report by the choice.
-2. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (the exact choices, single- vs multi-select, and how each new filter type filters the report).</t>
+2. The report narrows as soon as you pick the value - there is no Apply or Run button to press. Every filter button on every report works this way.</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Filters (Epic key TBD); Figma 11903-10573 (Reports filters); design-notes.md §B.6</t>
+          <t>Filters (Epic key TBD) (spec v1.6 §2 Reports Filters; §4 Key Decisions "New date-range filter type" + "Multi-select where it makes sense"); Branko answers 2026-07-31 Q2/Q3/Q5/Q7; Figma 11903-10573</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr"/>
@@ -4915,32 +4929,81 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>New Reports filter types behave correctly (Location, Transaction Type, etc.)</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Reports Page Filters</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Reports area of the app with some sample data present.</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Reports area and go to a report that uses them - for example A/R Aging Detail (Location, Transaction Type) or Notes (Mention).
+2. Look at the filter buttons shown above the report table.
+3. Open each of those filter buttons in turn, tick two choices where possible, and watch the report.</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>1. Each of these filter buttons - Location, Transaction Type, Invoice Status, Type, User and Mention - opens a list of choices, lets you tick more than one, and narrows the report straight away with no Apply button.
+2. The choices inside each filter come from your own shop's data (for example your real vendors or categories), so there is no fixed list to compare against - check that the choices you see match the data in your shop.
+3. Write down the choices you actually see behind each of these six buttons. They have not been written down anywhere yet, so your list becomes the record.</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD) (spec v1.6 §2 Reports Filters; §4 "Multi-select where it makes sense"); Branko answers 2026-07-31 Q3/Q5 + Q4 (pointer only - the 6 new types are not enumerated in v1.6; see DELTAS.md F1); Figma 11903-10573</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
           <t>Date range filter: results update when both start and end dates are picked</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>Reports Page Filters</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The new filter bar has rolled out to a page with a Date filter chip (a report, or a Parts page with a date column).
 3. Records exist inside and outside the date range you will pick.</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>1. Click the Date filter chip.
 2. Look at the panel that opens.
@@ -4949,7 +5012,7 @@
 5. Look at the results and the chip.</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>1. A start/end date picker opens - there are NO preset ranges (no 'Last 30 days' shortcuts) and NO pre-filled default range.
 2. After only the start date, the results do not change yet.
@@ -4957,42 +5020,42 @@
 4. Only one date range can be active at a time on that chip, and the chip shows the active range.</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); tech plan 2026-07-29 D19 (date-range chip: no presets, no default, applies on second date); spec v1.3 Parts + Reports sections (export awaited)</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>Filters (Epic key TBD) (spec v1.6 §4 "New date-range filter type"; §2 Reports Filters - start/end picker; no presets; no default; applies on the second date); Branko answers 2026-07-31 Q5; tech plan 2026-07-29 D19</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>Page toolbar Search expands in place and narrows the list as you type</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with several work orders listed.</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>1. Find the Search control in the page toolbar (a magnifier icon with the word Search).
 2. Click it.
@@ -5002,7 +5065,7 @@
 6. Expand it again, type text, and click somewhere else.</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t>1. The control expands in place into a small search box showing the placeholder 'Type to search'.
 2. The list narrows as you type, after a brief pause - and ONLY this page's list changes, nothing else in the app.
@@ -5010,42 +5073,42 @@
 4. Clicking away with an empty box collapses it back to the Search button; with text in it, the box stays open.</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>Filters epic (key TBD) (S13-R1 (placement in the toolbar action group); S13-R9 (scoped to this table only); S13-R12; S13-R15 (blur rules)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>Page search combines with filters and is cleared separately</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with work orders for several customers and statuses.</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>1. Apply one filter (for example a Status).
 2. Type a search term in the page search box.
@@ -5053,50 +5116,50 @@
 4. Re-type the search, then clear ONLY the filter.</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t>1. With both active, the results match the filter AND the search together (both narrow the list at once).
 2. Clearing the search keeps the filter applied.
 3. Clearing the filter keeps the search applied - each is cleared by its own control without wiping the other.</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>Filters epic (key TBD) (S13-R10 (search and filters are additive); S13-R13 (each cleared independently); S8-R5) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr"/>
-      <c r="J93" s="2" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>Your typed search stays in this browser tab only and is never saved</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with several work orders listed.
 3. You know how to open a second browser tab on the same page.</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>1. Type a search term in the page Search box that matches some work orders.
 2. Sort the table by a column, then move to the next page of results.
@@ -5105,7 +5168,7 @@
 5. Close every browser tab, open the browser again and go back to the Work Orders page.</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>1. Sorting and paging keep your search applied - your text stays in the box and the list stays narrowed.
 2. Leaving the page and coming back also keeps your text in the box and the list still narrowed.
@@ -5113,49 +5176,49 @@
 4. After closing the browser and coming back, the Search box is empty and the list is unsearched - a typed search is never remembered for next time (your filters, unlike the search, ARE remembered).</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Filters epic (key TBD) (S13-R14 (retained for the browser tab session); S13-R25 (never stored against the account; each tab independent); S13-N4 (not restored on a later visit); S10-R5) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="2" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>The search term is part of the shareable page link</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page.</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>1. Type a search term and copy the page address.
 2. Open the copied address in a fresh tab.
 3. Hand-edit the search part of the address into something malformed and load it.</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t>1. The address contains the search term after step 1.
 2. The fresh tab opens with the search box filled and the list already narrowed.
@@ -5163,42 +5226,42 @@
 4. A search arriving via a link is view-only, the same as filters from a link - it does not overwrite your own remembered search.</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Filters epic (key TBD) (S11-R4 (query reflected in the URL); S11-R5 (URL query pre-applied with the control filled); S11-N2 (malformed query ignored with no error); S11-R8 (rationale: no saved value to overwrite)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr"/>
-      <c r="J95" s="2" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>On mobile the search expands in the toolbar and buttons make room</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device.
 2. You are on the Work Orders page.</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>1. Tap the Search control in the page toolbar.
 2. Type a term and watch the list.
@@ -5206,7 +5269,7 @@
 4. With text in the box, tap somewhere else on the screen; then clear the text and tap somewhere else again.</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>1. The search expands inline inside the toolbar - no separate popup window opens.
 2. The list narrows as you type, same as desktop.
@@ -5215,43 +5278,43 @@
 5. There is no extra 'search is on' badge on mobile: with text in it the box simply stays open showing your text, and an empty box closes back to the Search button when you tap elsewhere - exactly as on desktop.</t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>Filters epic (key TBD) (S13-R16 (inline expansion with no modal); S13-R17 (field fills the remaining width); S13-R18 (CTA hug width); S13-R19 (2+ icon actions -&gt; "more" kebab); S13-R20 (no active-query indicator); S12-R5) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="2" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>Every list page keeps its own search box (Parts, Reports, detail tabs)</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The page-search rollout has finished everywhere (run this sweep at the end of the rollout, not part-way through).
 3. You can reach Work Orders, Customers, Parts, Administration, Reports and the Dashboard.</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>1. Work Orders surfaces: the Work Orders list, a work order's History tab, the Work Order Log dialog opened from that tab's kebab menu, a line's Line Log dialog opened from the Lines tab, and the work order's Notes tab.
 2. Customer and asset surfaces: the Customers list, then on one customer - Contacts, Assets, Invoices, Work Orders, Part Sales, Fees &amp; Discounts, Notes; then on one asset - Work Orders, Invoices, Notes.
@@ -5261,7 +5324,7 @@
 6. On each surface, find that table's own Search box and type something that matches one of its rows. Then open a work order's Parts tab and look at the search input it already has.</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t>1. Every table listed above has its own Search box - no table lost the ability to narrow by text.
 2. Each Search box narrows only its own table; nothing else in the app changes.
@@ -5269,42 +5332,42 @@
 4. The work order Parts tab keeps the local search input it already had - it was deliberately left as it is.</t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Filters epic (key TBD) (S14-R6 (audit: 42 surfaces across 39 components; Work Order Parts excluded); S14-R5 (app-wide sweep); S13-R22 (every table carries a search control); S14-N1 (verify once at the end)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="2" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>The top navigation search no longer filters page lists</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with several work orders listed.</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>1. Type a term into the TOP NAVIGATION search (the app-wide search at the top), not the page's own search box.
 2. Watch the Work Orders list while typing.
@@ -5312,49 +5375,49 @@
 4. Pick one of the results offered in the navigation search's dropdown.</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>1. The page list does NOT narrow while you type in the navigation search - only its dropdown of matching records appears.
 2. The same holds on the other pages checked.
 3. Picking a dropdown result still takes you to that record - the navigation search keeps its find-and-open role.</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>Filters epic (key TBD) (S14-R1 (navigational results only); S14-R2 (the page-filtering code path is removed rather than dormant); S14-R4 (the list is left untouched); S14-R5) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>The Search box changes look as you hover over it, open it and type</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with several work orders listed.</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>1. Look at the right-hand end of the toolbar row, before the small icon buttons and before the 'New Work Order' button.
 2. Move the mouse pointer over the 'Search' button without clicking.
@@ -5363,7 +5426,7 @@
 5. Delete what you typed and type a very long sentence instead.</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t>1. A 'Search' button is shown with a small magnifier icon next to the word 'Search'; it is plain text on a see-through background, with no border and no fill.
 2. Hovering over it gives it a light grey background; the word 'Search' keeps its own colour.
@@ -5373,43 +5436,43 @@
 6. A very long sentence does not make the box grow and does not cut the text off - the text scrolls sideways inside the box and the cursor stays where you are typing.</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>Filters epic (key TBD) (S13-R2 (default text button); S13-R3 (hover fill); S13-R4 (expands in place at 180px); S13-R5 (placeholder "Type to search"); S13-R6 (typed text + X-circle clear); S13-R8 (long queries scroll)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr"/>
-      <c r="J99" s="2" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>The list narrows shortly after you stop typing, with no button to press</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with several work orders listed.
 3. You can also open the Parts Inventory page.</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>1. On the Work Orders page open the Search box and type a few letters that match some work orders. Do NOT press Enter.
 2. Watch the work order table for a second or two.
@@ -5418,7 +5481,7 @@
 5. Do the same on the Parts Inventory page.</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr">
         <is>
           <t>1. The list narrows on its own a moment after you stop typing (about a third of a second) - you never press Enter or any button.
 2. The matching rows appear in the table you were already looking at; no separate results page, results list or pop-up window opens.
@@ -5427,43 +5490,43 @@
 5. Parts Inventory behaves the same way, only it waits a fraction longer before reacting; that longer wait is on purpose because that page carries more data.</t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>Filters epic (key TBD) (S13-R7 (applies as you type; debounced 300ms; no apply/submit; Enter not required; Inventory 350ms); S13-R12 (results replace the table in place)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>One search box serves all Work Orders tabs and searches the tab you are on</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Work orders exist in several statuses, so the All, Estimates and Completed tabs each have rows.
 3. You have a word (for example part of a customer name) that matches work orders on more than one of those tabs.</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>1. On the All tab, type that word into the page Search box.
 2. Click the Estimates tab and look at the Search box and the list.
@@ -5471,7 +5534,7 @@
 4. Still on the Completed tab, clear the search with the round x, then go back to the All tab.</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t>1. On the All tab only the rows matching your word remain.
 2. On the Estimates tab your word is still in the Search box, and the list shows only Estimates rows that match it - no rows from the other tabs appear.
@@ -5479,43 +5542,43 @@
 4. Clearing the search clears it for all the Work Orders tabs - they share one search - and each tab shows its full list again.</t>
         </is>
       </c>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Filters epic (key TBD) (S13-R11 (search applies within the active tab only); S13-R24 (the Work Orders tabs share a single query - views of one dataset)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>Each Report tab and each Parts view keeps its own separate search</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You can open at least two Parts views (for example Inventory and Purchase Orders).
 3. You can open a report that has more than one tab.</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>1. On a Parts view (for example Inventory) type a word into that page's Search box.
 2. Switch to another Parts view (for example Purchase Orders) and look at its Search box and list.
@@ -5523,7 +5586,7 @@
 4. Do the same on a report with tabs: search on one tab, then switch to another tab of the same report.</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t>1. The second Parts view opens with an empty Search box and its full list - the word you typed on the first view is not carried over.
 2. Going back to the first view brings its own word back and narrows its list again.
@@ -5531,42 +5594,42 @@
 4. No search is ever applied to a table it was not typed on.</t>
         </is>
       </c>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>Filters epic (key TBD) (S13-R24 (Reports sub-tabs and Parts views each keep their own query); S13-R11; S10-R4 (each view/tab keeps its own set)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="2" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>An old link carrying a top-search word no longer narrows the page list</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You have a Work Orders web address from BEFORE this change that still carries a word typed into the top-of-screen search (a bookmark, or a link someone sent). If you do not have one, hand-type that old search part onto the end of the Work Orders address.</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>1. Open that old web address.
 2. Look at the work order list and at the page's own Search box.
@@ -5574,7 +5637,7 @@
 4. Type a word into the top-of-screen search, then reload the page.</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr">
         <is>
           <t>1. The page opens with the normal list for your own saved filters - the old search word does NOT narrow the list.
 2. The page's own Search box is empty; nothing was carried into it.
@@ -5582,107 +5645,59 @@
 4. After typing in the top-of-screen search and reloading, the list is still not narrowed and nothing about that word was remembered for the list.</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>Filters epic (key TBD) (S14-R3 (state / URL parameters / persisted values carrying a global search term into page filtering are removed with it); S14-R2; S14-R1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" s="2" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>Collapsing the filter bar keeps an active search working</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page and the filter bar is expanded.
 3. A word is typed in the page Search box and the list is narrowed by it.</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>1. With the search still active, click the funnel button in the toolbar to collapse the filter bar.
 2. Look at the table and at the toolbar row.
 3. Expand the filter bar again.</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t>1. The list stays narrowed by your word - collapsing the filter bar does not cancel the search.
 2. The Search box stays in the toolbar row with your word still showing; it is not tucked away with the filter bar, because the search sits in the toolbar row and the chips sit in the row below.
 3. Expanding the bar again changes nothing about the search or the narrowed list.</t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>Filters epic (key TBD) (S13-E1 (a collapsed filter bar keeps an active query applying and the search control stays in the toolbar); §4 Key Decisions (page search is separate from the filter bar)) [spec v1.6 2026-07-28]</t>
-        </is>
-      </c>
-      <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="2" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>Page search opens with the 'Search or ask a question' box</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>Page Search (Command-K)</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. Some sample work orders, customers, assets, parts and vendors exist.</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>1. From anywhere in the app, open the page search (the Search box in the top bar, or press Command-K / Ctrl-K).
-2. Look at the search panel that opens.</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="inlineStr">
-        <is>
-          <t>1. A search panel opens with an empty search box at the top.
-2. The box shows the placeholder text 'Search or ask a question' with a magnifier icon on the left and a clear (X) button on the right.
-3. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (whether 'ask a question' means an AI search — this is out of scope for now).</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr"/>
@@ -5691,12 +5706,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Page search shows entity tabs All, Work Orders, Customers, Assets, Parts...</t>
+          <t>The work order list request carries the active filter selections</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Page Search (Command-K)</t>
+          <t>API — Work Orders List Filtering</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -5706,642 +5721,257 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. Some sample work orders, customers, assets, parts and vendors exist.</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the page search panel.
-2. Look at the row of tabs under the search box.</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>1. A row of tabs is shown: All, Work Orders, Customers, Assets, Parts, Vendors and Part Sales.
-2. The All tab is selected by default.
-3. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (whether choosing a tab limits results to that type only).</t>
-        </is>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
-        </is>
-      </c>
-      <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>Typing a term shows grouped results with counts and highlighting</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>Page Search (Command-K)</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. Some sample work orders, customers, assets, parts and vendors exist.</t>
-        </is>
-      </c>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the page search panel.
-2. Type a few letters (for example 'Fib') into the search box.
-3. Look at the results.</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t>1. Results are grouped by type with a count next to each group heading, for example 'Work orders (2)', 'Customers (2)', 'Vendors (1)', 'Assets (2)', 'Parts (1)'.
-2. The matching part of each result is highlighted in yellow.
-3. Each work order row shows its number, name, a status pill (for example Approved or Estimate), the person and a date.
-4. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (how matching works — exact vs fuzzy — and the ranking order).</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
-        </is>
-      </c>
-      <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>Recent searches are shown grouped by Today, Yesterday, Past week...</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>Page Search (Command-K)</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. Some sample work orders, customers, assets, parts and vendors exist.</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the page search panel without typing anything.
-2. Look at the list shown under the tabs.</t>
-        </is>
-      </c>
-      <c r="G108" s="2" t="inlineStr">
-        <is>
-          <t>1. A list of recent items is shown, grouped under headings: Today, Yesterday, Past week and Past 30 days.
-2. Each item shows a type icon, its name and a short detail line (for example a customer address or a date).
-3. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (how many recent items are kept and how long they persist).</t>
-        </is>
-      </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
-        </is>
-      </c>
-      <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="2" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>Re-opening page search keeps the last typed text and its results</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>Page Search (Command-K)</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. Some sample work orders, customers, assets, parts and vendors exist.</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the page search and type a term (for example 'Fibridge').
-2. Close the panel, then open it again.
-3. Look at the search box and the results.</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="inlineStr">
-        <is>
-          <t>1. The previous search text is still in the box (shown selected/highlighted) and its results are shown.
-2. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (whether the last search is remembered per person and for how long — this is the 'persisting search' state).</t>
-        </is>
-      </c>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
-        </is>
-      </c>
-      <c r="I109" s="2" t="inlineStr"/>
-      <c r="J109" s="2" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>Hovering a search result shows quick-action buttons</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>Page Search (Command-K)</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. Some sample work orders, customers, assets, parts and vendors exist.</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the page search panel (recent items or results shown).
-2. Move the mouse over a result row.
-3. Look at the right side of that row.</t>
-        </is>
-      </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>1. Quick-action buttons appear on the row, depending on the result type — for example 'Add new line' on a work order, 'New work order' on an asset or customer, 'Add part' on a part sale, 'Add contact' on a vendor and 'Add to work order' on a part.
-2. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (exactly which quick actions show for which result type, and what each one does).</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
-        </is>
-      </c>
-      <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="2" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>Page search shows keyboard hints and supports keyboard navigation</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>Page Search (Command-K)</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. Some sample work orders, customers, assets, parts and vendors exist.</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the page search panel.
-2. Look at the bar along the bottom of the panel.
-3. Use the up/down arrow keys, Enter and Esc.</t>
-        </is>
-      </c>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t>1. The bottom bar shows keyboard hints: up/down arrows labelled 'Navigate', the Enter key labelled 'Select', and 'Close esc'.
-2. Arrow keys move the highlight between results, Enter opens the highlighted result, and Esc closes the panel (to be checked live once available).
-3. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (exact keyboard behaviour).</t>
-        </is>
-      </c>
-      <c r="H111" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
-        </is>
-      </c>
-      <c r="I111" s="2" t="inlineStr"/>
-      <c r="J111" s="2" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>Page search results include a Refresh action</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>Page Search (Command-K)</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. Some sample work orders, customers, assets, parts and vendors exist.</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the page search and type a term so grouped results appear.
-2. Look at the top right of the results area.</t>
-        </is>
-      </c>
-      <c r="G112" s="2" t="inlineStr">
-        <is>
-          <t>1. A 'Refresh' link is shown at the top right of the results.
-2. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (what Refresh reloads and when it is shown).</t>
-        </is>
-      </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
-        </is>
-      </c>
-      <c r="I112" s="2" t="inlineStr"/>
-      <c r="J112" s="2" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>Page search scope belongs to Filters or Global Search (to decide)</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>Page Search (Command-K)</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. Some sample work orders, customers, assets, parts and vendors exist.</t>
-        </is>
-      </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>1. Review where the page search / Command-K component is owned for testing.
-2. Compare against the Global Search project's existing cases.</t>
-        </is>
-      </c>
-      <c r="G113" s="2" t="inlineStr">
-        <is>
-          <t>1. The page-search component is agreed to belong to either the Filters test suite or the Global Search test suite, not both.
-2. Behaviour to confirm — pending Branko's product write-up; to be checked live once the feature is available. (product/QA decision on which project owns page search).</t>
-        </is>
-      </c>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>Filters (Epic key TBD); Figma 11829-8908 (page-search component); design-2026-07-27/DESIGN-INGEST-2026-07-27.md §1/§3.D</t>
-        </is>
-      </c>
-      <c r="I113" s="2" t="inlineStr"/>
-      <c r="J113" s="2" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>The work order list request carries the active filter selections</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>API — Work Orders List Filtering</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser with developer tools open on the Network tab.
 2. You are on the Work Orders page with no filters applied.</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>1. Apply a Status selection and a Customer selection in the filter bar.
 2. In the Network tab, find the work order list request the page sends after the change.
 3. Inspect the request's parameters.</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t>1. The list request includes the active filter selections as request parameters (status values and customer identifiers).
 2. The request succeeds (HTTP 200).
 3. The response contains only work orders matching the filters - the filtering is done by the backend, not just hidden client-side.</t>
         </is>
       </c>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 2 S2-R2; Story 3 S3-R6 (backend view)</t>
         </is>
       </c>
-      <c r="I114" s="2" t="inlineStr"/>
-      <c r="J114" s="2" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>A combined multi-filter request returns only work orders matching all filters, any value within each filter</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>API — Work Orders List Filtering</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with developer tools open on the Network tab.
 2. Seeded ZZAUTOTEST work orders exist: customer A with an Estimate and an Approved work order, customer B with an Estimate work order.</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>1. On the Work Orders page apply Status = Estimate + Approved and Customer = customer A.
 2. Capture the resulting list request and response.</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t>1. One request carries both filters together (both statuses and the customer).
 2. The response returns customer A's Estimate and Approved work orders only.
 3. Customer B's work orders are absent - the customer filter and status filter both restrict the result, while the two statuses combine as either-or.</t>
         </is>
       </c>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 2 S2-R2; Story 3 S3-R6; Story 8 S8-R3 (backend view)</t>
         </is>
       </c>
-      <c r="I115" s="2" t="inlineStr"/>
-      <c r="J115" s="2" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>A list request with a deleted or unknown filter value is handled without a server error</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>API — Work Orders List Filtering</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in and can replay/edit the work order list request (developer tools or an API client).
 2. You have a captured filtered list request, and one of its filter values has since been deleted (for example a removed ZZAUTOTEST customer) or is a made-up identifier.</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>1. Send the list request containing the no-longer-existing (or made-up) filter value.
 2. Inspect the HTTP status and the response body.</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>1. The backend does not fail with a server error (no HTTP 5xx).
 2. The response is a normal, successful list response - the invalid value is ignored or simply matches nothing.
 3. Any still-valid filter values in the same request are applied normally.</t>
         </is>
       </c>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 10 S10-N1; Story 11 S11-R3</t>
         </is>
       </c>
-      <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="2" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>A list request with malformed filter parameters does not produce a server error</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>API — Work Orders List Filtering</t>
         </is>
       </c>
-      <c r="C117" s="2" t="inlineStr">
+      <c r="C109" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in and can replay/edit the work order list request.
 2. You have a captured filtered list request to tamper with.</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>1. Corrupt the filter parameters (wrong types, scrambled values, nonsense text) and send the request.
 2. Inspect the HTTP status and the response body.
 3. Also open the equally malformed page URL in the browser and watch the page.</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
         <is>
           <t>1. The backend responds gracefully - no HTTP 5xx / crash; either a normal (unfiltered or empty) list or a clean validation response.
 2. In the browser the page still loads without filters and without an error message, matching the malformed-URL requirement.</t>
         </is>
       </c>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 11 S11-N1</t>
         </is>
       </c>
-      <c r="I117" s="2" t="inlineStr"/>
-      <c r="J117" s="2" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>A filter combination matching nothing returns a successful empty list, not an error</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>API — Work Orders List Filtering</t>
         </is>
       </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with developer tools open on the Network tab.
 2. A filter combination is known to match no work orders (for example a seeded customer plus a status they never have).</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>1. Apply that filter combination on the Work Orders page.
 2. Capture the list request and response.</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t>1. The request succeeds (HTTP 200).
 2. The response contains an empty result set (zero work orders) - an empty match is a normal outcome, not an error.
 3. The page renders the no-results empty state from this response.</t>
         </is>
       </c>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>requirements.md Story 8 S8-R3; Story 2 S2-N3</t>
         </is>
       </c>
-      <c r="I118" s="2" t="inlineStr"/>
-      <c r="J118" s="2" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>Saved-filters service round-trip: save, reload, and per-user isolation</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>API — Work Orders List Filtering</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser with developer tools open on the Network tab.
 2. A second user account is available.</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>1. On the Work Orders page, change a filter and watch the Network tab for the save request the page sends shortly after.
 2. Reload the page and find the load request for the saved page state.
@@ -6349,7 +5979,7 @@
 4. With an API client (or by editing the request), ask the saved-state service for a page key that was never saved.</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr">
         <is>
           <t>1. Changing a filter sends a save (PUT) to the per-user page-preferences service carrying the page's state, and it succeeds (HTTP 200).
 2. On reload the page requests the saved state back (GET, HTTP 200) and applies it - the filters return without you redoing them.
@@ -6357,13 +5987,13 @@
 4. Asking for a never-saved key returns success with an empty value, not an error page.</t>
         </is>
       </c>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Filters (Epic key TBD); tech plan 2026-07-29 section 4-1.3 (GET/PUT /api/users/me/preferences/{pageKey}); spec v1.3 S10 per-user persistence (export awaited)</t>
         </is>
       </c>
-      <c r="I119" s="2" t="inlineStr"/>
-      <c r="J119" s="2" t="inlineStr"/>
+      <c r="I111" s="2" t="inlineStr"/>
+      <c r="J111" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/filters-v1-testrail-import.xlsx
+++ b/testrail-import/filters-v1-testrail-import.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 1 S1-R1</t>
+          <t>Filters (no Jira epic) (S1-R1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -537,7 +537,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Five filter chips appear in a fixed order, each with an icon, its name and a down arrow</t>
+          <t>Five filter chips appear in a fixed order with an icon, name and arrow</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 1 S1-R2; S1-R3</t>
+          <t>Filters (no Jira epic) (S1-R2; S1-R3) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -625,7 +625,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Filters epic (key TBD) (S1-N1; S9-R2; §4 Key Decisions - PRD text says "hidden"; behaviour per Branko Q4=B 2026-07-17 + QA-lead ruling 2026-07-30 = shown greyed-out/disabled) [spec v1.6 2026-07-28]</t>
+          <t>Filters (no Jira epic) (S1-N1; S9-R2; §4 Key Decisions - PRD text says "hidden"; behaviour per Branko Q4=B 2026-07-17 + QA-lead ruling 2026-07-30 = shown greyed-out/disabled) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -634,7 +634,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Status chip opens a checkbox list of all nine work order statuses with a Clear selection action</t>
+          <t>Status chip opens a checkbox list of all nine statuses plus Clear selection</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 2 S2-R1; S2-R4</t>
+          <t>Filters (no Jira epic) (S2-R1; S2-R4) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -726,7 +726,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 2 S2-R2; S2-R3; S2-R6</t>
+          <t>Filters (no Jira epic) (S2-R2; S2-R3; S2-R6) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -777,7 +777,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 2 S2-R2; §4 Key Decisions (no selection limit)</t>
+          <t>Filters (no Jira epic) (S2-R2; §4 Key Decisions (no selection limit)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
@@ -786,7 +786,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Clear selection in the Status dropdown unticks every status and removes the filter</t>
+          <t>Clear selection in the Status dropdown unticks every status</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 2 S2-R4; Story 8 S8-R2</t>
+          <t>Filters (no Jira epic) (S2-R4; S8-R2) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -876,7 +876,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 2 S2-R5</t>
+          <t>Filters (no Jira epic) (S2-R5) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -926,7 +926,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 2 S2-N3; Story 8 S8-R3</t>
+          <t>Filters (no Jira epic) (S2-N3; S8-R3) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -978,7 +978,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Filters (Epic key TBD); tech plan 2026-07-29 G1 (Imported exclusivity); spec S2-R1 (conflict raised with the author - export of spec v1.3 awaited)</t>
+          <t>Filters (no Jira epic) (S2-R7 (Imported cannot be combined with anything else; other filter chips disabled while it is active); S2-N4 (the combination is prevented rather than returning an empty result)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -987,7 +987,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Customer chip opens a dropdown with a 'Search customer' field and a scrollable customer list</t>
+          <t>Customer chip opens a dropdown with a search field and a customer list</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 3 S3-R1</t>
+          <t>Filters (no Jira epic) (S3-R1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 3 S3-R2</t>
+          <t>Filters (no Jira epic) (S3-R2) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1087,7 +1087,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Selecting customers adds removable tags in the dropdown input area and checkmarks in the list</t>
+          <t>Selected customers show as removable tags and as ticks in the list</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 3 S3-R3; S3-R4; §4 Key Decisions (no selection limit)</t>
+          <t>Filters (no Jira epic) (S3-R3; S3-R4; §4 Key Decisions (no selection limit)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 3 S3-R5</t>
+          <t>Filters (no Jira epic) (S3-R5) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 3 S3-R6; Story 2 S2-R6 (real-time pattern)</t>
+          <t>Filters (no Jira epic) (S3-R6; S2-R6 (real-time pattern)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 3 S3-R7; Story 8 S8-R2</t>
+          <t>Filters (no Jira epic) (S3-R7; S8-R2) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 3 S3-R8</t>
+          <t>Filters (no Jira epic) (S3-R8) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 3 S3-N1</t>
+          <t>Filters (no Jira epic) (S3-N1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1385,7 +1385,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>A customer with no open work orders is still listed; filtering by them returns an empty result</t>
+          <t>A customer with no work orders is still listed; picking them shows no rows</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 3 S3-E1; S3-N2; Story 8 S8-R3</t>
+          <t>Filters (no Jira epic) (S3-E1; S3-N2; S8-R3) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1435,7 +1435,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Lead Technician chip opens a dropdown with a 'Search technician' field and a technician list</t>
+          <t>Lead Technician chip opens a dropdown with a search field and a list</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 4 S4-R1</t>
+          <t>Filters (no Jira epic) (S4-R1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 4 S4-R2</t>
+          <t>Filters (no Jira epic) (S4-R2) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 4 S4-R3; S4-R4</t>
+          <t>Filters (no Jira epic) (S4-R3; S4-R4) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 4 S4-R5; Story 8 S8-R2</t>
+          <t>Filters (no Jira epic) (S4-R5; S8-R2) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 4 S4-R6</t>
+          <t>Filters (no Jira epic) (S4-R6) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 4 S4-N1; Story 8 S8-R3</t>
+          <t>Filters (no Jira epic) (S4-N1; S8-R3) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 4 S4-E1</t>
+          <t>Filters (no Jira epic) (S4-E1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -1775,7 +1775,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Service Advisor chip opens a dropdown with a 'Search advisor' field and an advisor list</t>
+          <t>Service Advisor chip opens a dropdown with a search field and a list</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 5 S5-R1</t>
+          <t>Filters (no Jira epic) (S5-R1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 5 S5-R2</t>
+          <t>Filters (no Jira epic) (S5-R2) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 5 S5-R3; S5-R4</t>
+          <t>Filters (no Jira epic) (S5-R3; S5-R4) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 5 S5-R5; Story 8 S8-R2</t>
+          <t>Filters (no Jira epic) (S5-R5; S8-R2) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 5 S5-R6</t>
+          <t>Filters (no Jira epic) (S5-R6) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 5 S5-N1; Story 8 S8-R3</t>
+          <t>Filters (no Jira epic) (S5-N1; S8-R3) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 5 S5-E1</t>
+          <t>Filters (no Jira epic) (S5-E1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
@@ -2114,7 +2114,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Asset on site chip opens a dropdown with exactly two options, Yes and No, plus Clear selection</t>
+          <t>Asset on site chip opens a dropdown with Yes and No plus Clear selection</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 6 S6-R1; §4 Key Decisions (dropdown, not toggle)</t>
+          <t>Filters (no Jira epic) (S6-R1; §4 Key Decisions (dropdown - not toggle)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 6 S6-R2</t>
+          <t>Filters (no Jira epic) (S6-R2) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 6 S6-R3</t>
+          <t>Filters (no Jira epic) (S6-R3) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 6 S6-R4; Story 8 S8-R2</t>
+          <t>Filters (no Jira epic) (S6-R4; S8-R2) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 6 S6-R5</t>
+          <t>Filters (no Jira epic) (S6-R5) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 6 S6-N1; Story 8 S8-R3</t>
+          <t>Filters (no Jira epic) (S6-N1; S8-R3) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 6 S6-R2; Filters (Epic key TBD); tech plan 2026-07-29 G4 (filtering No is new capability)</t>
+          <t>Filters (no Jira epic) (S6-R2; tech plan 2026-07-29 G4 (filtering No is new capability)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -2453,7 +2453,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>A chip with a selected value turns into the active blue state and shows the value</t>
+          <t>A chip with a selected value turns blue and shows the value</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 7 S7-R1</t>
+          <t>Filters (no Jira epic) (S7-R1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -2501,7 +2501,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>A chip with several values shows the first values and shortens the rest with an ellipsis</t>
+          <t>A chip with several values shows the first ones and shortens the rest</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 7 S7-R2</t>
+          <t>Filters (no Jira epic) (S7-R2) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -2548,7 +2548,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>'Clear filters' appears to the right of the chips only when at least one filter is active</t>
+          <t>'Clear filters' shows right of the chips only when a filter is active</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 7 S7-R3; S7-N1; Story 8 S8-N1</t>
+          <t>Filters (no Jira epic) (S7-R3; S7-N1; S8-N1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -2598,7 +2598,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>'Clear filters' removes every active filter at once and all chips return to default</t>
+          <t>'Clear filters' removes every active filter and resets all chips</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Filters epic (key TBD) (S8-R1; §4 Key Decisions; S13-R13 (clearing filters does not clear a typed search)) [spec v1.6 2026-07-28]</t>
+          <t>Filters (no Jira epic) (S8-R1; §4 Key Decisions; S13-R13 (clearing filters does not clear a typed search)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
@@ -2649,7 +2649,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>'Clear selection' inside one dropdown clears only that filter and leaves the others active</t>
+          <t>'Clear selection' in one dropdown clears only that filter</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 8 S8-R2; §4 Key Decisions</t>
+          <t>Filters (no Jira epic) (S8-R2; §4 Key Decisions) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
@@ -2698,7 +2698,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Several different filters combine: only work orders matching every active filter remain</t>
+          <t>Status and Customer filters together show only work orders matching both</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>requirements.md §2 Feature Overview (multi-criteria); Story 8 S8-R3 ('combination of active filters')</t>
+          <t>Filters (no Jira epic) (§2 Feature Overview (multi-criteria); S8-R3 ('combination of active filters')) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
@@ -2748,7 +2748,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>The toolbar funnel button collapses the filter bar and the table reclaims the space</t>
+          <t>The toolbar funnel button collapses the bar and the table takes the space</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 1 S1-R4; S1-R5</t>
+          <t>Filters (no Jira epic) (S1-R4; S1-R5) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
@@ -2797,7 +2797,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Expanding the filter bar brings it back exactly as it was, with active filters still shown</t>
+          <t>Expanding the filter bar brings it back with active filters still shown</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 1 S1-R6</t>
+          <t>Filters (no Jira epic) (S1-R6) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
@@ -2846,7 +2846,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>The collapsed or expanded state of the filter bar is remembered after leaving and returning</t>
+          <t>The filter bar's collapsed or expanded state is remembered on return</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 1 S1-R7; Story 10 S10-R1</t>
+          <t>Filters (no Jira epic) (S1-R7; S10-R1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
@@ -2895,7 +2895,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>The funnel button shows a blue indicator when filters are active while the bar is collapsed, and none when no filters are active</t>
+          <t>Collapsed funnel button shows a blue indicator only when filters are active</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 7 S7-R4; S7-N2</t>
+          <t>Filters (no Jira epic) (S7-R4; S7-N2) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 7 S7-R5</t>
+          <t>Filters (no Jira epic) (S7-R5) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
@@ -2991,7 +2991,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>A filter combination with no matching work orders shows a no-results empty state instead of a blank table</t>
+          <t>A filter combination with no matches shows a no-results empty state</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 8 S8-R3</t>
+          <t>Filters (no Jira epic) (S8-R3) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -3040,7 +3040,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>The filtered empty state offers a way to clear the filters, and using it brings the list back</t>
+          <t>The filtered empty state offers a way to clear the filters</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Filters epic (key TBD) (S8-R4; S8-R5 (with a query active each is cleared independently - FLT-EMPTY-03)) [spec v1.6 2026-07-28]</t>
+          <t>Filters (no Jira epic) (S8-R4 (the empty state includes a prompt or link to clear filters); S8-R5 (where a query is also active each is cleared independently)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Filters epic (key TBD) (S8-R3 (empty state covers filters AND any active query); S8-R4 (prompt to clear filters and the query where active); S8-R5 (each cleared independently from the empty state); S13-N1; S13-N2) [spec v1.6 2026-07-28]</t>
+          <t>Filters (no Jira epic) (S8-R3 (empty state covers filters AND any active query); S8-R4 (prompt to clear filters and the query where active); S8-R5 (each cleared independently from the empty state); S13-N1; S13-N2) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 9 S9-R1</t>
+          <t>Filters (no Jira epic) (S9-R1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
@@ -3189,7 +3189,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>On the Estimates tab the Status chip is shown greyed out, pre-filled with 'Status: Estimate', and cannot be changed; the other four filters work on top of the Estimates pre-filter</t>
+          <t>Estimates tab: Status chip greyed out and pre-filled; other four still work</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 9 S9-R2; Story 2 S2-N1 (chip-hidden wording superseded by PO ruling 2026-07-17: chip shown disabled); §4 Key Decisions</t>
+          <t>Filters (no Jira epic) (S9-R2; S2-N1; §4 Key Decisions - PRD text says "hidden"; behaviour per Branko Q4=B 2026-07-17 + QA-lead ruling 2026-07-30 = shown greyed-out/disabled; PRD alignment is Branko's open item) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
@@ -3241,7 +3241,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>On the Completed tab the Status chip is shown greyed out, pre-filled with the tab's status, and cannot be changed; the other four filters work on top of the Completed pre-filter</t>
+          <t>Completed tab: Status chip greyed out and pre-filled; other four still work</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 9 S9-R3; Story 2 S2-N2 (chip-hidden wording superseded by PO ruling 2026-07-17: chip shown disabled); §4 Key Decisions</t>
+          <t>Filters (no Jira epic) (S9-R3; S2-N2; §4 Key Decisions - PRD text says "hidden"; behaviour per Branko Q4=B 2026-07-17 + QA-lead ruling 2026-07-30 = shown greyed-out/disabled; PRD alignment is Branko's open item) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
@@ -3293,7 +3293,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>On the My Work Orders tab all five filters are shown and narrow the already user-scoped list</t>
+          <t>My Work Orders tab shows all five filters and they narrow that list</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 9 S9-R4; §4 Key Decisions (My Work Orders tab does not remove filters)</t>
+          <t>Filters (no Jira epic) (S9-R4; §4 Key Decisions (My Work Orders tab does not remove filters)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Filters epic (key TBD) (S9-R5; S9-N1; S9-R2 - behaviour per Branko Q4=B 2026-07-17 + QA-lead ruling 2026-07-30) [spec v1.6 2026-07-28]</t>
+          <t>Filters (no Jira epic) (S9-R5; S9-N1; S9-R2 - behaviour per Branko Q4=B 2026-07-17 + QA-lead ruling 2026-07-30) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Filters (Epic key TBD); tech plan 2026-07-29 D10 (default tab = Estimates; last-used tab persists); not in the ratified product spec - confirmation requested</t>
+          <t>Filters (no Jira epic) (no requirement in the ratified spec v1.6 - default/last-used tab is engineering-plan-only - confirmation requested); tech plan 2026-07-29 D10 (default tab = Estimates; last-used tab persists) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
@@ -3440,7 +3440,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Leaving the Work Orders page and coming back restores the filters and the bar state exactly</t>
+          <t>Leaving the page and coming back restores the filters and the bar state</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 10 S10-R1; Story 1 S1-R7</t>
+          <t>Filters (no Jira epic) (S10-R1; S1-R7) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
@@ -3490,7 +3490,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Filter selections are remembered for you permanently - still applied after moving around the app and even after closing the browser and signing back in</t>
+          <t>Filters are remembered permanently, even after closing the browser</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 10 S10-R2 (session-only wording superseded by PO ruling 2026-07-17: permanent per-user persistence); §2/§4 (persist across navigation, saved per user)</t>
+          <t>Filters (no Jira epic) (S10-R2 (stored server-side against the account; survives logout; syncs across devices); S10-R3 (saved per user); S10-R1 (restored after navigating away)) + Branko Q2 2026-07-17 - now matched by the PRD [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 10 S10-R3; §4 Key Decisions (saved per user)</t>
+          <t>Filters (no Jira epic) (S10-R3; §4 Key Decisions (saved per user)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
@@ -3590,7 +3590,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>A remembered filter value that no longer exists is silently dropped when you return</t>
+          <t>A remembered filter value that was deleted is silently ignored</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 10 S10-N1</t>
+          <t>Filters (no Jira epic) (S10-N1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Filters (Epic key TBD) (spec v1.6 S10-R4; §4 "Parts and Reports selections are scoped to their view/tab and persist there"); Branko answers 2026-07-31 Q5 exception 1; tech plan 2026-07-29 D20</t>
+          <t>Filters (no Jira epic) (spec v1.6 S10-R4; §4 "Parts and Reports selections are scoped to their view/tab and persist there"); Branko answers 2026-07-31 Q5 exception 1; tech plan 2026-07-29 D20</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Filters (Epic key TBD); tech plan 2026-07-29 section 4-3.3 (one-time browser-storage to account-preference migration)</t>
+          <t>Filters (no Jira epic) (no numbered v1.6 requirement covers the one-off migration - context S10-R2 server-side model); tech plan 2026-07-29 s4-3.3 (browser-storage to account-preference migration) - confirmation requested [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 11 S11-R1</t>
+          <t>Filters (no Jira epic) (S11-R1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
@@ -3784,7 +3784,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Opening a shared or bookmarked URL loads the Work Orders page with those filters already applied</t>
+          <t>Opening a shared URL or bookmark loads the page with those filters on</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 11 S11-R2; §2 Feature Overview (share or bookmark)</t>
+          <t>Filters (no Jira epic) (S11-R2; §2 Feature Overview (share or bookmark)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr"/>
@@ -3832,7 +3832,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>A URL containing a filter value that no longer exists loads without that value</t>
+          <t>A URL with a deleted filter value loads and ignores that value</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 11 S11-R3</t>
+          <t>Filters (no Jira epic) (S11-R3) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
@@ -3881,7 +3881,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>A malformed filter URL loads the page unfiltered without showing an error</t>
+          <t>A broken filter URL loads the page with no filters and no error</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 11 S11-N1</t>
+          <t>Filters (no Jira epic) (S11-N1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
@@ -3930,7 +3930,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Opening a filtered link never overwrites your saved filters</t>
+          <t>Opening a shared link does not change your own saved filters</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Filters epic (key TBD) (S11-R6 (URL state runtime-only with no write-back); S11-R7 (Back to my view - also clears the query); S11-R8 (rationale: the query is never saved)) [spec v1.6 2026-07-28]</t>
+          <t>Filters (no Jira epic) (S11-R6 (URL state runtime-only with no write-back); S11-R7 (Back to my view - also clears the query); S11-R8 (rationale: the query is never saved)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr"/>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Filters epic (key TBD) (S11-N3; S11-R7) [spec v1.6 2026-07-28]</t>
+          <t>Filters (no Jira epic) (S11-N3; S11-R7) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr"/>
@@ -4039,7 +4039,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>On mobile the filter chips sit in a horizontally scrollable row below the tabs, starting with All Filters</t>
+          <t>Mobile: chips sit in a scrollable row below the tabs, starting All Filters</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
         <is>
           <t>1. A filter chip row is shown below the tabs, starting with an 'All Filters' chip (with a funnel icon) followed by the individual filter chips (Status, Customer, Lead Technician, ...).
 2. The row scrolls horizontally - chips that do not fit are reachable by swiping.
-3. A right-edge arrow affordance indicates the row can be scrolled (per the design variant).</t>
+3. An arrow at the right-hand edge shows that the row can be scrolled. (This is what the design shows - if your screen looks different, write down what you actually see and carry on.)</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 12 S12-R1</t>
+          <t>Filters (no Jira epic) (S12-R1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
@@ -4087,7 +4087,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Tapping All Filters opens a bottom sheet listing every filter as an expandable row with an Apply filters button</t>
+          <t>Mobile: All Filters opens a sheet of expandable rows with Apply filters</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 12 S12-R3</t>
+          <t>Filters (no Jira epic) (S12-R3) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr"/>
@@ -4135,7 +4135,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Selecting statuses in the mobile sheet and tapping Apply filters filters the list and counts on the sheet title</t>
+          <t>Mobile: tapping Apply filters applies the statuses and updates the count</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 12 S12-R2; S12-R3; Story 2 S2-R1</t>
+          <t>Filters (no Jira epic) (S12-R2; S12-R3; S2-R1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr"/>
@@ -4186,7 +4186,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Tapping an individual filter chip on mobile opens that filter's own sheet with an 'Apply filter' button</t>
+          <t>Mobile: tapping one chip opens its own sheet with an 'Apply filter' button</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 12 S12-R2; S12-R3</t>
+          <t>Filters (no Jira epic) (S12-R2; S12-R3) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr"/>
@@ -4235,7 +4235,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>The mobile Customer filter has search, multi-select and removable tags, matching desktop</t>
+          <t>Mobile Customer filter has search, multi-select and removable tags</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 12 S12-R2; Story 3 S3-R2/R3/R5</t>
+          <t>Filters (no Jira epic) (S12-R2; S3-R2/R3/R5) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr"/>
@@ -4287,7 +4287,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>The mobile Lead Technician and Service Advisor filters offer their search lists in the sheet</t>
+          <t>Mobile Lead Technician and Service Advisor filters offer their search lists</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 12 S12-R2; Story 4 S4-R1; Story 5 S5-R1</t>
+          <t>Filters (no Jira epic) (S12-R2; S4-R1; S5-R1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr"/>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 12 S12-R2; Story 6 S6-R1/R2/R3</t>
+          <t>Filters (no Jira epic) (S12-R2; S6-R1/R2/R3) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr"/>
@@ -4427,7 +4427,7 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 12 S12-R2; Story 7 S7-R1/R3; Story 8 S8-R1</t>
+          <t>Filters (no Jira epic) (S12-R2; S7-R1/R3; S8-R1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr"/>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 12 S12-R4</t>
+          <t>Filters (no Jira epic) (S12-R4) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr"/>
@@ -4522,7 +4522,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 12 S12-N1; Story 8 S8-R3/R4</t>
+          <t>Filters (no Jira epic) (S12-N1; S8-R3/R4) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Filters (Epic key TBD) (spec v1.6 §2 Feature Overview -&gt; Parts Filters; §4 Key Decisions -&gt; "Context-specific filter sets on Parts and Reports" + "Multi-select where it makes sense"); Branko answers 2026-07-31 Q2/Q3/Q5/Q7; Figma 11884-16885</t>
+          <t>Filters (no Jira epic) (spec v1.6 §2 Feature Overview -&gt; Parts Filters; §4 Key Decisions -&gt; "Context-specific filter sets on Parts and Reports" + "Multi-select where it makes sense"); Branko answers 2026-07-31 Q2/Q3/Q5/Q7; Figma 11884-16885</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr"/>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Filters (Epic key TBD) (spec v1.6 §2 Feature Overview -&gt; Parts Filters; §4 Key Decisions -&gt; "Context-specific filter sets on Parts and Reports" + "Multi-select where it makes sense"); Branko answers 2026-07-31 Q2/Q3/Q5/Q7; Figma 11884-16885</t>
+          <t>Filters (no Jira epic) (spec v1.6 §2 Feature Overview -&gt; Parts Filters; §4 Key Decisions -&gt; "Context-specific filter sets on Parts and Reports" + "Multi-select where it makes sense"); Branko answers 2026-07-31 Q2/Q3/Q5/Q7; Figma 11884-16885</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr"/>
@@ -4688,7 +4688,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Filters (Epic key TBD) (spec v1.6 §2 Feature Overview -&gt; Parts Filters; §4 Key Decisions -&gt; "Context-specific filter sets on Parts and Reports" + "Multi-select where it makes sense"); Branko answers 2026-07-31 Q2/Q3/Q5/Q7; Figma 11884-16885</t>
+          <t>Filters (no Jira epic) (spec v1.6 §2 Feature Overview -&gt; Parts Filters; §4 Key Decisions -&gt; "Context-specific filter sets on Parts and Reports" + "Multi-select where it makes sense"); Branko answers 2026-07-31 Q2/Q3/Q5/Q7; Figma 11884-16885</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr"/>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Filters (Epic key TBD) (spec v1.6 §2 Feature Overview -&gt; Parts Filters; §4 Key Decisions -&gt; "Context-specific filter sets on Parts and Reports" + "Multi-select where it makes sense"); Branko answers 2026-07-31 Q2/Q3/Q5/Q7; Figma 11884-16885</t>
+          <t>Filters (no Jira epic) (spec v1.6 §2 Feature Overview -&gt; Parts Filters; §4 Key Decisions -&gt; "Context-specific filter sets on Parts and Reports" + "Multi-select where it makes sense"); Branko answers 2026-07-31 Q2/Q3/Q5/Q7; Figma 11884-16885</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr"/>
@@ -4789,7 +4789,7 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Filters (Epic key TBD) (spec v1.6 §2 Parts Filters + Reports Filters); Branko answers 2026-07-31 Q3 ("support all the filters we have right now in the app as well as all choices per filter"); tech plan 2026-07-29 rollout rule</t>
+          <t>Filters (no Jira epic) (spec v1.6 §2 Parts Filters + Reports Filters); Branko answers 2026-07-31 Q3 ("support all the filters we have right now in the app as well as all choices per filter"); tech plan 2026-07-29 rollout rule</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr"/>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Filters (Epic key TBD) (spec v1.6 §2 Reports Filters; §4 Key Decisions "New date-range filter type" + "Multi-select where it makes sense"); Branko answers 2026-07-31 Q2/Q3/Q5/Q7; Figma 11903-10573</t>
+          <t>Filters (no Jira epic) (spec v1.6 §2 Reports Filters; §4 Key Decisions "New date-range filter type" + "Multi-select where it makes sense"); Branko answers 2026-07-31 Q2/Q3/Q5/Q7; Figma 11903-10573</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr"/>
@@ -4920,7 +4920,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Filters (Epic key TBD) (spec v1.6 §2 Reports Filters; §4 Key Decisions "New date-range filter type" + "Multi-select where it makes sense"); Branko answers 2026-07-31 Q2/Q3/Q5/Q7; Figma 11903-10573</t>
+          <t>Filters (no Jira epic) (spec v1.6 §2 Reports Filters; §4 Key Decisions "New date-range filter type" + "Multi-select where it makes sense"); Branko answers 2026-07-31 Q2/Q3/Q5/Q7; Figma 11903-10573</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr"/>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Filters (Epic key TBD) (spec v1.6 §2 Reports Filters; §4 "Multi-select where it makes sense"); Branko answers 2026-07-31 Q3/Q5 + Q4 (pointer only - the 6 new types are not enumerated in v1.6; see DELTAS.md F1); Figma 11903-10573</t>
+          <t>Filters (no Jira epic) (spec v1.6 §2 Reports Filters; §4 "Multi-select where it makes sense"); Branko answers 2026-07-31 Q3/Q5 + Q4 (pointer only - the 6 new types are not enumerated in v1.6; see DELTAS.md F1); Figma 11903-10573</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr"/>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Filters (Epic key TBD) (spec v1.6 §4 "New date-range filter type"; §2 Reports Filters - start/end picker; no presets; no default; applies on the second date); Branko answers 2026-07-31 Q5; tech plan 2026-07-29 D19</t>
+          <t>Filters (no Jira epic) (spec v1.6 §4 "New date-range filter type"; §2 Reports Filters - start/end picker; no presets; no default; applies on the second date); Branko answers 2026-07-31 Q5; tech plan 2026-07-29 D19</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr"/>
@@ -5075,7 +5075,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Filters epic (key TBD) (S13-R1 (placement in the toolbar action group); S13-R9 (scoped to this table only); S13-R12; S13-R15 (blur rules)) [spec v1.6 2026-07-28]</t>
+          <t>Filters (no Jira epic) (S13-R1 (placement in the toolbar action group); S13-R9 (scoped to this table only); S13-R12; S13-R15 (blur rules)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr"/>
@@ -5125,7 +5125,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Filters epic (key TBD) (S13-R10 (search and filters are additive); S13-R13 (each cleared independently); S8-R5) [spec v1.6 2026-07-28]</t>
+          <t>Filters (no Jira epic) (S13-R10 (search and filters are additive); S13-R13 (each cleared independently); S8-R5) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr"/>
@@ -5178,7 +5178,7 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>Filters epic (key TBD) (S13-R14 (retained for the browser tab session); S13-R25 (never stored against the account; each tab independent); S13-N4 (not restored on a later visit); S10-R5) [spec v1.6 2026-07-28]</t>
+          <t>Filters (no Jira epic) (S13-R14 (retained for the browser tab session); S13-R25 (never stored against the account; each tab independent); S13-N4 (not restored on a later visit); S10-R5) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr"/>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Filters epic (key TBD) (S11-R4 (query reflected in the URL); S11-R5 (URL query pre-applied with the control filled); S11-N2 (malformed query ignored with no error); S11-R8 (rationale: no saved value to overwrite)) [spec v1.6 2026-07-28]</t>
+          <t>Filters (no Jira epic) (S11-R4 (query reflected in the URL); S11-R5 (URL query pre-applied with the control filled); S11-N2 (malformed query ignored with no error); S11-R8 (rationale: no saved value to overwrite)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr"/>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Filters epic (key TBD) (S13-R16 (inline expansion with no modal); S13-R17 (field fills the remaining width); S13-R18 (CTA hug width); S13-R19 (2+ icon actions -&gt; "more" kebab); S13-R20 (no active-query indicator); S12-R5) [spec v1.6 2026-07-28]</t>
+          <t>Filters (no Jira epic) (S13-R16 (inline expansion with no modal); S13-R17 (field fills the remaining width); S13-R18 (CTA hug width); S13-R19 (2+ icon actions -&gt; "more" kebab); S13-R20 (no active-query indicator); S12-R5) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr"/>
@@ -5316,11 +5316,11 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>1. Work Orders surfaces: the Work Orders list, a work order's History tab, the Work Order Log dialog opened from that tab's kebab menu, a line's Line Log dialog opened from the Lines tab, and the work order's Notes tab.
-2. Customer and asset surfaces: the Customers list, then on one customer - Contacts, Assets, Invoices, Work Orders, Part Sales, Fees &amp; Discounts, Notes; then on one asset - Work Orders, Invoices, Notes.
-3. Parts surfaces: Inventory, Catalog, Part Sales, Purchase Orders, Returns, Credits, Vendors, Vendor Invoices (web address /parts/deliveries), a vendor's Unpaid Invoices, and Part History.
-4. Administration surfaces: Locations, Roles &amp; Permissions, Staff, Departments, Taxes, Labor Rates, Canned Lines, Payment Methods, Fees &amp; Discounts, Asset Types, Categories, Pricing.
-5. Reports and Dashboard surfaces: IBS Batch Transactions, Sales Tax Invoices, the Dashboard, and one dashboard report drill-down.
+          <t>1. Visit the Work Orders surfaces: the Work Orders list, a work order's History tab, the Work Order Log dialog opened from that tab's kebab menu, a line's Line Log dialog opened from the Lines tab, and the work order's Notes tab.
+2. Visit the customer and asset surfaces: the Customers list, then on one customer - Contacts, Assets, Invoices, Work Orders, Part Sales, Fees &amp; Discounts, Notes; then on one asset - Work Orders, Invoices, Notes.
+3. Visit the Parts surfaces: Inventory, Catalog, Part Sales, Purchase Orders, Returns, Credits, Vendors, Vendor Invoices (web address /parts/deliveries), a vendor's Unpaid Invoices, and Part History.
+4. Visit the Administration surfaces: Locations, Roles &amp; Permissions, Staff, Departments, Taxes, Labor Rates, Canned Lines, Payment Methods, Fees &amp; Discounts, Asset Types, Categories, Pricing.
+5. Visit the Reports and Dashboard surfaces: IBS Batch Transactions, Sales Tax Invoices, the Dashboard, and one dashboard report drill-down.
 6. On each surface, find that table's own Search box and type something that matches one of its rows. Then open a work order's Parts tab and look at the search input it already has.</t>
         </is>
       </c>
@@ -5334,7 +5334,7 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Filters epic (key TBD) (S14-R6 (audit: 42 surfaces across 39 components; Work Order Parts excluded); S14-R5 (app-wide sweep); S13-R22 (every table carries a search control); S14-N1 (verify once at the end)) [spec v1.6 2026-07-28]</t>
+          <t>Filters (no Jira epic) (S14-R6 (audit: 42 surfaces across 39 components; Work Order Parts excluded); S14-R5 (app-wide sweep); S13-R22 (every table carries a search control); S14-N1 (verify once at the end)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr"/>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Filters epic (key TBD) (S14-R1 (navigational results only); S14-R2 (the page-filtering code path is removed rather than dormant); S14-R4 (the list is left untouched); S14-R5) [spec v1.6 2026-07-28]</t>
+          <t>Filters (no Jira epic) (S14-R1 (navigational results only); S14-R2 (the page-filtering code path is removed rather than dormant); S14-R4 (the list is left untouched); S14-R5) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr"/>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Filters epic (key TBD) (S13-R2 (default text button); S13-R3 (hover fill); S13-R4 (expands in place at 180px); S13-R5 (placeholder "Type to search"); S13-R6 (typed text + X-circle clear); S13-R8 (long queries scroll)) [spec v1.6 2026-07-28]</t>
+          <t>Filters (no Jira epic) (S13-R2 (default text button); S13-R3 (hover fill); S13-R4 (expands in place at 180px); S13-R5 (placeholder "Type to search"); S13-R6 (typed text + X-circle clear); S13-R8 (long queries scroll)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr"/>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>Filters epic (key TBD) (S13-R7 (applies as you type; debounced 300ms; no apply/submit; Enter not required; Inventory 350ms); S13-R12 (results replace the table in place)) [spec v1.6 2026-07-28]</t>
+          <t>Filters (no Jira epic) (S13-R7 (applies as you type; debounced 300ms; no apply/submit; Enter not required; Inventory 350ms); S13-R12 (results replace the table in place)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr"/>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Filters epic (key TBD) (S13-R11 (search applies within the active tab only); S13-R24 (the Work Orders tabs share a single query - views of one dataset)) [spec v1.6 2026-07-28]</t>
+          <t>Filters (no Jira epic) (S13-R11 (search applies within the active tab only); S13-R24 (the Work Orders tabs share a single query - views of one dataset)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr"/>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Filters epic (key TBD) (S13-R24 (Reports sub-tabs and Parts views each keep their own query); S13-R11; S10-R4 (each view/tab keeps its own set)) [spec v1.6 2026-07-28]</t>
+          <t>Filters (no Jira epic) (S13-R24 (Reports sub-tabs and Parts views each keep their own query); S13-R11; S10-R4 (each view/tab keeps its own set)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr"/>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Filters epic (key TBD) (S14-R3 (state / URL parameters / persisted values carrying a global search term into page filtering are removed with it); S14-R2; S14-R1) [spec v1.6 2026-07-28]</t>
+          <t>Filters (no Jira epic) (S14-R3 (state / URL parameters / persisted values carrying a global search term into page filtering are removed with it); S14-R2; S14-R1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr"/>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Filters epic (key TBD) (S13-E1 (a collapsed filter bar keeps an active query applying and the search control stays in the toolbar); §4 Key Decisions (page search is separate from the filter bar)) [spec v1.6 2026-07-28]</t>
+          <t>Filters (no Jira epic) (S13-E1 (a collapsed filter bar keeps an active query applying and the search control stays in the toolbar); §4 Key Decisions (page search is separate from the filter bar)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr"/>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 2 S2-R2; Story 3 S3-R6 (backend view)</t>
+          <t>Filters (no Jira epic) (S2-R2; S3-R6 (backend view)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr"/>
@@ -5755,7 +5755,7 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>A combined multi-filter request returns only work orders matching all filters, any value within each filter</t>
+          <t>A combined multi-filter request returns only work orders matching all filters</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 2 S2-R2; Story 3 S3-R6; Story 8 S8-R3 (backend view)</t>
+          <t>Filters (no Jira epic) (S2-R2; S3-R6; S8-R3 (backend view)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr"/>
@@ -5803,7 +5803,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>A list request with a deleted or unknown filter value is handled without a server error</t>
+          <t>A request with a deleted or unknown filter value gives no server error</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 10 S10-N1; Story 11 S11-R3</t>
+          <t>Filters (no Jira epic) (S10-N1; S11-R3) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr"/>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 11 S11-N1</t>
+          <t>Filters (no Jira epic) (S11-N1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr"/>
@@ -5899,7 +5899,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>A filter combination matching nothing returns a successful empty list, not an error</t>
+          <t>A filter combination matching nothing returns an empty list, not an error</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>requirements.md Story 8 S8-R3; Story 2 S2-N3</t>
+          <t>Filters (no Jira epic) (S8-R3; S2-N3) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr"/>
@@ -5989,7 +5989,7 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Filters (Epic key TBD); tech plan 2026-07-29 section 4-1.3 (GET/PUT /api/users/me/preferences/{pageKey}); spec v1.3 S10 per-user persistence (export awaited)</t>
+          <t>Filters (no Jira epic) (S10-R2 (filters stored server-side against the user account; last write wins); S10-R3 (saved per user)) + tech plan 2026-07-29 s4-1.3 (GET/PUT per-user page preferences) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr"/>

--- a/testrail-import/filters-v1-testrail-import.xlsx
+++ b/testrail-import/filters-v1-testrail-import.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters V1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Filters V1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2748,7 +2748,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>The toolbar funnel button collapses the bar and the table takes the space</t>
+          <t>The toolbar filter button collapses the bar and the table takes the space</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2774,8 +2774,8 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>1. Find the filter (funnel) icon button in the page toolbar (next to the Search magnifier and the column/layout toggle, left of the New Work Order button).
-2. Click the funnel icon once.
+          <t>1. Find the filter icon button in the page toolbar (next to the Search magnifier and the column/layout toggle, left of the New Work Order button).
+2. Click the filter icon once.
 3. Look at the filter bar area and the table.</t>
         </is>
       </c>
@@ -2783,7 +2783,7 @@
         <is>
           <t>1. The filter bar row is hidden.
 2. The work order table moves up and uses the reclaimed vertical space.
-3. The funnel icon shows a pressed/active look while the bar is collapsed.</t>
+3. The filter icon shows a pressed/active look while the bar is collapsed.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2819,12 +2819,12 @@
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page.
-3. At least one filter is selected (for example two statuses) and the filter bar has been collapsed with the funnel button.</t>
+3. At least one filter is selected (for example two statuses) and the filter bar has been collapsed with the filter button.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>1. Click the funnel icon in the toolbar again.
+          <t>1. Click the filter icon in the toolbar again.
 2. Look at the filter bar.</t>
         </is>
       </c>
@@ -2867,7 +2867,7 @@
       <c r="E50" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. You are on the Work Orders page and have collapsed the filter bar with the funnel button.</t>
+2. You are on the Work Orders page and have collapsed the filter bar with the filter button.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -2875,7 +2875,7 @@
           <t>1. Navigate to another page (for example open a work order, or go to Customers).
 2. Return to the Work Orders page.
 3. Look at the filter bar area.
-4. Expand the bar with the funnel button, leave the page again and come back.</t>
+4. Expand the bar with the filter button, leave the page again and come back.</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -2895,7 +2895,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Collapsed funnel button shows a blue indicator only when filters are active</t>
+          <t>Collapsed filter button shows a blue indicator only when filters are active</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2921,15 +2921,15 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>1. With NO filters selected, collapse the filter bar with the funnel button and look at the funnel icon.
+          <t>1. With NO filters selected, collapse the filter bar with the filter button and look at the filter icon.
 2. Expand the bar, select at least one filter value (for example a status).
-3. Collapse the bar again and look at the funnel icon.</t>
+3. Collapse the bar again and look at the filter icon.</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>1. After step 1 the funnel icon shows no special indicator (only its normal pressed look).
-2. After step 3 the funnel icon shows a visual indicator (filters icon in primary blue) signalling that active filters are in effect while the bar is hidden.</t>
+          <t>1. After step 1 the filter icon shows no special indicator (only its normal pressed look).
+2. After step 3 the filter icon shows a visual indicator (filters icon in primary blue) signalling that active filters are in effect while the bar is hidden.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>1. Collapse the filter bar with the funnel button.
+          <t>1. Collapse the filter bar with the filter button.
 2. Look at the work order table.</t>
         </is>
       </c>
@@ -4071,7 +4071,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>1. A filter chip row is shown below the tabs, starting with an 'All Filters' chip (with a funnel icon) followed by the individual filter chips (Status, Customer, Lead Technician, ...).
+          <t>1. A filter chip row is shown below the tabs, starting with an 'All Filters' chip (with a filter icon) followed by the individual filter chips (Status, Customer, Lead Technician, ...).
 2. The row scrolls horizontally - chips that do not fit are reachable by swiping.
 3. An arrow at the right-hand edge shows that the row can be scrolled. (This is what the design shows - if your screen looks different, write down what you actually see and carry on.)</t>
         </is>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>1. There is no filter-bar collapse/expand (funnel) toggle on mobile.
+          <t>1. There is no filter-bar collapse/expand (filter icon) toggle on mobile.
 2. The filter chip row is always visible on the mobile Work Orders page.</t>
         </is>
       </c>
@@ -4580,10 +4580,10 @@
 7. Vendor Invoices shows four filter buttons: Vendor, Invoice date, Date received and Received by.
 8. The Vendors list page shows two filter buttons: Vendor and State/Province. Note: the developers have not been given a design for the Vendors page filters yet, so this page may not have them — write down what you actually see instead of failing the whole test.
 9. On every page above, each filter button shows a small icon, the filter name and a down arrow.
-10. Every Parts list page also shows a Search (magnifier) icon and a filter (funnel) icon in the toolbar; some pages (for example Inventory) also show a column/layout toggle icon.
+10. Every Parts list page also shows a Search (magnifier) icon and a filter icon in the toolbar; some pages (for example Inventory) also show a column/layout toggle icon.
 11. Every filter button shown above is a working filter on that page - none of them is display-only.
 12. The choices inside each filter come from your own shop's data (for example your real vendors or categories), so there is no fixed list to compare against - check that the choices you see match the data in your shop.
-13. Still to check on the live build: what the funnel icon and the column/layout icon do (the written description does not cover the toolbar icons).</t>
+13. Still to check on the live build: what the filter icon and the column/layout icon do (the written description does not cover the toolbar icons).</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -5683,7 +5683,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>1. With the search still active, click the funnel button in the toolbar to collapse the filter bar.
+          <t>1. With the search still active, click the filter button in the toolbar to collapse the filter bar.
 2. Look at the table and at the toolbar row.
 3. Expand the filter bar again.</t>
         </is>

--- a/testrail-import/filters-v1-testrail-import.xlsx
+++ b/testrail-import/filters-v1-testrail-import.xlsx
@@ -523,12 +523,14 @@
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>1. A filter bar is visible directly below the tab row and above the work order table.
-2. The filter bar is shown by default (expanded) without having to turn anything on.</t>
+2. The filter bar is shown by default (expanded) without having to turn anything on.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S1-R1).</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S1-R1) [spec v1.6 2026-07-28]</t>
+          <t>SV-8786 (S1-R1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -572,12 +574,14 @@
         <is>
           <t>1. Exactly five filter chips appear, in this order: Status, Customer, Lead Technician, Service Advisor, Asset on site.
 2. Each chip shows a small icon, the filter name and a down arrow (chevron) indicating it opens a dropdown.
-3. In the design the icons are: a spinner for Status, a person for Customer, a wrench for Lead Technician, a headset for Service Advisor and a truck for Asset on site.</t>
+3. In the design the icons are: a spinner for Status, a person for Customer, a wrench for Lead Technician, a headset for Service Advisor and a truck for Asset on site.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S1-R2, S1-R3).</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S1-R2; S1-R3) [spec v1.6 2026-07-28]</t>
+          <t>SV-8786 (S1-R2; S1-R3) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -620,12 +624,14 @@
         <is>
           <t>1. The filter bar is still shown - it does not disappear on this tab.
 2. The Customer, Lead Technician, Service Advisor and Asset on site chips are all displayed and usable.
-3. The Status chip is not usable on this tab: it is shown greyed out and already filled in with the tab's own status, and cannot be clicked.</t>
+3. The Status chip is not usable on this tab: it is shown greyed out and already filled in with the tab's own status, and cannot be clicked.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S1-N1, S9-R2). The current behaviour follows a later product owner decision dated 2026-07-17.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S1-N1; S9-R2; §4 Key Decisions - PRD text says "hidden"; behaviour per Branko Q4=B 2026-07-17 + QA-lead ruling 2026-07-30 = shown greyed-out/disabled) [spec v1.6 2026-07-28]</t>
+          <t>SV-8785 [epic] (S1-N1; S9-R2; §4 Key Decisions - PRD text says "hidden"; behaviour per Branko Q4=B 2026-07-17 + QA-lead ruling 2026-07-30 = shown greyed-out/disabled) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -671,12 +677,14 @@
           <t>1. A dropdown panel opens under the Status chip.
 2. It lists all nine statuses as checkboxes, in this order: Estimate, Approved, In progress, Review, Complete, Invoiced, Paid, Declined, Imported.
 3. All checkboxes are unticked (nothing selected yet).
-4. A 'Clear selection' action is shown at the bottom of the dropdown.</t>
+4. A 'Clear selection' action is shown at the bottom of the dropdown.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S2-R1, S2-R4).</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S2-R1; S2-R4) [spec v1.6 2026-07-28]</t>
+          <t>SV-8787 (S2-R1; S2-R4) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -721,12 +729,14 @@
         <is>
           <t>1. The ticked checkbox appears filled (checked).
 2. The table updates immediately to show only work orders in the selected status - there is no confirm or apply button on desktop.
-3. Work orders in other statuses are no longer listed.</t>
+3. Work orders in other statuses are no longer listed.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S2-R2, S2-R3, S2-R6).</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S2-R2; S2-R3; S2-R6) [spec v1.6 2026-07-28]</t>
+          <t>SV-8787 (S2-R2; S2-R3; S2-R6) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -772,12 +782,14 @@
           <t>1. Every ticked status shows a filled checkbox.
 2. The table shows work orders whose status matches ANY of the ticked statuses (both Estimate and Approved rows appear).
 3. Work orders in statuses that are not ticked are hidden.
-4. There is no limit on how many statuses you can tick.</t>
+4. There is no limit on how many statuses you can tick.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S2-R2).</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S2-R2; §4 Key Decisions (no selection limit)) [spec v1.6 2026-07-28]</t>
+          <t>SV-8787 (S2-R2; §4 Key Decisions (no selection limit)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
@@ -822,12 +834,14 @@
         <is>
           <t>1. All status checkboxes become unticked.
 2. The Status filter is removed and the table returns to showing work orders of every status.
-3. Only the Status filter is affected - any other active filters stay applied.</t>
+3. Only the Status filter is affected - any other active filters stay applied.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S2-R4, S8-R2).</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S2-R4; S8-R2) [spec v1.6 2026-07-28]</t>
+          <t>SV-8785 [epic] (S2-R4; S8-R2) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -871,12 +885,14 @@
         <is>
           <t>1. The dropdown closes.
 2. The ticked statuses stay selected - the Status chip stays in its active state showing the selection.
-3. The table stays filtered by the selected statuses.</t>
+3. The table stays filtered by the selected statuses.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S2-R5).</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S2-R5) [spec v1.6 2026-07-28]</t>
+          <t>SV-8787 (S2-R5) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -921,12 +937,14 @@
         <is>
           <t>1. The table shows no rows.
 2. An empty state is displayed saying no results were found for the current filters (see the Empty State cases for its full content).
-3. The app does not show an error.</t>
+3. The app does not show an error.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S2-N3, S8-R3).</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S2-N3; S8-R3) [spec v1.6 2026-07-28]</t>
+          <t>SV-8785 [epic] (S2-N3; S8-R3) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -973,12 +991,14 @@
           <t>1. The table switches to showing imported work orders only.
 2. While Imported is ticked, the other filter chips are greyed out and cannot be used.
 3. Imported cannot be combined with other statuses - selecting it works alone.
-4. Unticking Imported re-enables the other chips and the normal list returns.</t>
+4. Unticking Imported re-enables the other chips and the normal list returns.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S2-R7, S2-N4).</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S2-R7 (Imported cannot be combined with anything else; other filter chips disabled while it is active); S2-N4 (the combination is prevented rather than returning an empty result)) [spec v1.6 2026-07-28]</t>
+          <t>SV-8787 (S2-R7 (Imported cannot be combined with anything else; other filter chips disabled while it is active); S2-N4 (the combination is prevented rather than returning an empty result)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -1024,12 +1044,14 @@
           <t>1. A dropdown panel opens under the Customer chip.
 2. A search input with the placeholder 'Search customer' is at the top, already focused so you can type right away.
 3. Below it is a scrollable list of customer names.
-4. A 'Clear selection' action is shown at the bottom of the panel.</t>
+4. A 'Clear selection' action is shown at the bottom of the panel.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S3-R1).</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S3-R1) [spec v1.6 2026-07-28]</t>
+          <t>SV-8788 (S3-R1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1073,12 +1095,14 @@
         <is>
           <t>1. The customer list narrows as you type, showing only names that match what you entered.
 2. Customers that do not match are removed from the list.
-3. Deleting the text brings the full list back.</t>
+3. Deleting the text brings the full list back.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S3-R2).</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S3-R2) [spec v1.6 2026-07-28]</t>
+          <t>SV-8788 (S3-R2) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1124,12 +1148,14 @@
           <t>1. Each selected customer appears as a tag (small chip) with an x in the input area at the top of the dropdown.
 2. Each selected customer's row in the list shows a checkmark on the right.
 3. Long customer names on tags are shortened with an ellipsis (for example 'Texas Truck And Aut...').
-4. You can keep selecting as many customers as needed - there is no selection limit.</t>
+4. You can keep selecting as many customers as needed - there is no selection limit.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S3-R3, S3-R4).</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S3-R3; S3-R4; §4 Key Decisions (no selection limit)) [spec v1.6 2026-07-28]</t>
+          <t>SV-8788 (S3-R3; S3-R4; §4 Key Decisions (no selection limit)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1174,12 +1200,14 @@
           <t>1. That customer's tag disappears from the input area.
 2. The checkmark next to that customer in the list is removed.
 3. The other selected customers keep their tags and checkmarks.
-4. The table updates to no longer include that customer's work orders.</t>
+4. The table updates to no longer include that customer's work orders.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S3-R5).</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S3-R5) [spec v1.6 2026-07-28]</t>
+          <t>SV-8788 (S3-R5) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1223,12 +1251,14 @@
         <is>
           <t>1. The table shows only work orders whose customer is one of the two selected customers.
 2. Work orders belonging to any other customer are hidden.
-3. The table updates in real time as you make the selections (no apply button on desktop).</t>
+3. The table updates in real time as you make the selections (no apply button on desktop).
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S3-R6, S2-R6).</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S3-R6; S2-R6 (real-time pattern)) [spec v1.6 2026-07-28]</t>
+          <t>SV-8785 [epic] (S3-R6; S2-R6 (real-time pattern)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1274,12 +1304,14 @@
           <t>1. All customer tags are removed from the input area.
 2. All checkmarks in the list are removed.
 3. The Customer filter is removed and the table shows work orders of all customers again.
-4. Other active filters (if any) are not affected.</t>
+4. Other active filters (if any) are not affected.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S3-R7, S8-R2).</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S3-R7; S8-R2) [spec v1.6 2026-07-28]</t>
+          <t>SV-8785 [epic] (S3-R7; S8-R2) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1323,12 +1355,14 @@
         <is>
           <t>1. The dropdown closes when you click outside it.
 2. The Customer chip stays in the active (blue) state showing the selection and the table stays filtered.
-3. When reopened, the selected customers' tags are still visible in the input area.</t>
+3. When reopened, the selected customers' tags are still visible in the input area.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S3-R8).</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S3-R8) [spec v1.6 2026-07-28]</t>
+          <t>SV-8788 (S3-R8) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1371,12 +1405,14 @@
         <is>
           <t>1. The list shows a message saying there are no results (instead of an empty gap).
 2. The app does not show an error.
-3. Clearing the search text brings the customer list back.</t>
+3. Clearing the search text brings the customer list back.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S3-N1).</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S3-N1) [spec v1.6 2026-07-28]</t>
+          <t>SV-8788 (S3-N1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1421,12 +1457,14 @@
         <is>
           <t>1. The customer with no work orders IS shown in the filter list (they are not hidden).
 2. After selecting only that customer, the table shows no rows and the filtered empty state is displayed.
-3. No error is shown.</t>
+3. No error is shown.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S3-E1, S3-N2, S8-R3).</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S3-E1; S3-N2; S8-R3) [spec v1.6 2026-07-28]</t>
+          <t>SV-8785 [epic] (S3-E1; S3-N2; S8-R3) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1471,12 +1509,14 @@
           <t>1. A dropdown panel opens under the Lead Technician chip.
 2. A search input with the placeholder 'Search technician' is at the top.
 3. Below it is a scrollable list of technician names.
-4. A 'Clear selection' action is shown at the bottom.</t>
+4. A 'Clear selection' action is shown at the bottom.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S4-R1).</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S4-R1) [spec v1.6 2026-07-28]</t>
+          <t>SV-8789 (S4-R1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1518,12 +1558,14 @@
       <c r="G22" s="2" t="inlineStr">
         <is>
           <t>1. The technician list narrows to only the names matching what you typed.
-2. Deleting the text brings the full list back.</t>
+2. Deleting the text brings the full list back.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S4-R2).</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S4-R2) [spec v1.6 2026-07-28]</t>
+          <t>SV-8789 (S4-R2) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1568,12 +1610,14 @@
           <t>1. Selected technicians show a filled checkbox in the list.
 2. The table shows only work orders where one of the selected technicians is assigned as the LEAD technician.
 3. A work order where the technician is assigned only in a non-lead role does not appear.
-4. The table updates in real time as you select.</t>
+4. The table updates in real time as you select.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S4-R3, S4-R4).</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S4-R3; S4-R4) [spec v1.6 2026-07-28]</t>
+          <t>SV-8789 (S4-R3; S4-R4) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1617,12 +1661,14 @@
         <is>
           <t>1. All technician selections are removed (checkboxes unticked).
 2. The Lead Technician filter no longer restricts the table.
-3. Other active filters are not affected.</t>
+3. Other active filters are not affected.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S4-R5, S8-R2).</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S4-R5; S8-R2) [spec v1.6 2026-07-28]</t>
+          <t>SV-8785 [epic] (S4-R5; S8-R2) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -1664,12 +1710,14 @@
       <c r="G25" s="2" t="inlineStr">
         <is>
           <t>1. The dropdown closes.
-2. The selection stays applied - the chip stays active and the table stays filtered.</t>
+2. The selection stays applied - the chip stays active and the table stays filtered.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S4-R6).</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S4-R6) [spec v1.6 2026-07-28]</t>
+          <t>SV-8789 (S4-R6) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -1712,12 +1760,14 @@
       <c r="G26" s="2" t="inlineStr">
         <is>
           <t>1. The table shows no rows and the filtered empty state is displayed.
-2. No error is shown.</t>
+2. No error is shown.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S4-N1, S8-R3).</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S4-N1; S8-R3) [spec v1.6 2026-07-28]</t>
+          <t>SV-8785 [epic] (S4-N1; S8-R3) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
@@ -1761,12 +1811,14 @@
       <c r="G27" s="2" t="inlineStr">
         <is>
           <t>1. The deactivated technician is NOT shown in the filter list.
-2. Active technicians are still listed normally.</t>
+2. Active technicians are still listed normally.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S4-E1).</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S4-E1) [spec v1.6 2026-07-28]</t>
+          <t>SV-8789 (S4-E1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -1811,12 +1863,14 @@
           <t>1. A dropdown panel opens under the Service Advisor chip.
 2. A search input with the placeholder 'Search advisor' is at the top.
 3. Below it is a scrollable list of advisor names.
-4. A 'Clear selection' action is shown at the bottom.</t>
+4. A 'Clear selection' action is shown at the bottom.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S5-R1).</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S5-R1) [spec v1.6 2026-07-28]</t>
+          <t>SV-8790 (S5-R1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -1858,12 +1912,14 @@
       <c r="G29" s="2" t="inlineStr">
         <is>
           <t>1. The advisor list narrows to only the names matching what you typed.
-2. Deleting the text brings the full list back.</t>
+2. Deleting the text brings the full list back.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S5-R2).</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S5-R2) [spec v1.6 2026-07-28]</t>
+          <t>SV-8790 (S5-R2) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
@@ -1907,12 +1963,14 @@
         <is>
           <t>1. Selected advisors show a filled checkbox in the list.
 2. The table shows only work orders assigned to any of the selected advisors.
-3. The table updates in real time as you select.</t>
+3. The table updates in real time as you select.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S5-R3, S5-R4).</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S5-R3; S5-R4) [spec v1.6 2026-07-28]</t>
+          <t>SV-8790 (S5-R3; S5-R4) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -1956,12 +2014,14 @@
         <is>
           <t>1. All advisor selections are removed.
 2. The Service Advisor filter no longer restricts the table.
-3. Other active filters are not affected.</t>
+3. Other active filters are not affected.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S5-R5, S8-R2).</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S5-R5; S8-R2) [spec v1.6 2026-07-28]</t>
+          <t>SV-8785 [epic] (S5-R5; S8-R2) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -2003,12 +2063,14 @@
       <c r="G32" s="2" t="inlineStr">
         <is>
           <t>1. The dropdown closes.
-2. The selection stays applied - the chip stays active and the table stays filtered.</t>
+2. The selection stays applied - the chip stays active and the table stays filtered.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S5-R6).</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S5-R6) [spec v1.6 2026-07-28]</t>
+          <t>SV-8790 (S5-R6) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -2051,12 +2113,14 @@
       <c r="G33" s="2" t="inlineStr">
         <is>
           <t>1. The table shows no rows and the filtered empty state is displayed.
-2. No error is shown.</t>
+2. No error is shown.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S5-N1, S8-R3).</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S5-N1; S8-R3) [spec v1.6 2026-07-28]</t>
+          <t>SV-8785 [epic] (S5-N1; S8-R3) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
@@ -2100,12 +2164,14 @@
       <c r="G34" s="2" t="inlineStr">
         <is>
           <t>1. The deactivated advisor is NOT shown in the filter list.
-2. Active advisors are still listed normally.</t>
+2. Active advisors are still listed normally.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S5-E1).</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S5-E1) [spec v1.6 2026-07-28]</t>
+          <t>SV-8790 (S5-E1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
@@ -2149,12 +2215,14 @@
           <t>1. A small dropdown panel opens under the Asset on site chip.
 2. It contains exactly two options: Yes and No.
 3. A 'Clear selection' action is shown at the bottom.
-4. It is a dropdown (like the other filters), not an on/off toggle.</t>
+4. It is a dropdown (like the other filters), not an on/off toggle.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S6-R1).</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S6-R1; §4 Key Decisions (dropdown - not toggle)) [spec v1.6 2026-07-28]</t>
+          <t>SV-8791 (S6-R1; §4 Key Decisions (dropdown - not toggle)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -2197,12 +2265,14 @@
       <c r="G36" s="2" t="inlineStr">
         <is>
           <t>1. The table shows only work orders whose asset is currently on site.
-2. Work orders whose asset is not on site are hidden.</t>
+2. Work orders whose asset is not on site are hidden.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S6-R2).</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S6-R2) [spec v1.6 2026-07-28]</t>
+          <t>SV-8791 (S6-R2) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2246,12 +2316,14 @@
         <is>
           <t>1. No becomes the selected option and Yes is deselected automatically - only one option can be selected at a time.
 2. The table switches to showing only the not-on-site work orders.
-3. The chip shows the currently selected value.</t>
+3. The chip shows the currently selected value.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S6-R3).</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S6-R3) [spec v1.6 2026-07-28]</t>
+          <t>SV-8791 (S6-R3) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2294,12 +2366,14 @@
         <is>
           <t>1. The selection is removed and the chip returns to its default (inactive) state.
 2. The table shows work orders regardless of on-site status again.
-3. Other active filters are not affected.</t>
+3. Other active filters are not affected.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S6-R4, S8-R2).</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S6-R4; S8-R2) [spec v1.6 2026-07-28]</t>
+          <t>SV-8785 [epic] (S6-R4; S8-R2) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2341,12 +2415,14 @@
       <c r="G39" s="2" t="inlineStr">
         <is>
           <t>1. The dropdown closes.
-2. The Yes selection stays applied - the chip stays active and the table stays filtered.</t>
+2. The Yes selection stays applied - the chip stays active and the table stays filtered.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S6-R5).</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S6-R5) [spec v1.6 2026-07-28]</t>
+          <t>SV-8791 (S6-R5) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2389,12 +2465,14 @@
       <c r="G40" s="2" t="inlineStr">
         <is>
           <t>1. The table shows no rows and the filtered empty state is displayed.
-2. No error is shown.</t>
+2. No error is shown.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S6-N1, S8-R3).</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S6-N1; S8-R3) [spec v1.6 2026-07-28]</t>
+          <t>SV-8785 [epic] (S6-N1; S8-R3) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2439,12 +2517,14 @@
         <is>
           <t>1. Only work orders whose asset is NOT on site remain in the list.
 2. Every work order with the asset on site is excluded.
-3. The chip shows the active No selection.</t>
+3. The chip shows the active No selection.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S6-R2).</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S6-R2; tech plan 2026-07-29 G4 (filtering No is new capability)) [spec v1.6 2026-07-28]</t>
+          <t>SV-8791 (S6-R2; tech plan 2026-07-29 G4 (filtering No is new capability)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -2487,12 +2567,14 @@
         <is>
           <t>1. The Status chip changes to an active/highlighted look (blue pill).
 2. The chip displays the selected value (for example 'Status: Estimate').
-3. The other chips stay in their default state.</t>
+3. The other chips stay in their default state.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S7-R1).</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S7-R1) [spec v1.6 2026-07-28]</t>
+          <t>SV-8792 (S7-R1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -2534,12 +2616,14 @@
       <c r="G43" s="2" t="inlineStr">
         <is>
           <t>1. The chip lists the selected values starting with the first one and shortens the label when it gets too long (the design shows 'Status: Estimate, In progress, Approved...').
-2. The chip stays a single compact pill - it does not grow to show every value in full.</t>
+2. The chip stays a single compact pill - it does not grow to show every value in full.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S7-R2).</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S7-R2) [spec v1.6 2026-07-28]</t>
+          <t>SV-8792 (S7-R2) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -2584,12 +2668,14 @@
         <is>
           <t>1. With no filters active, no 'Clear filters' button/link is shown (there is nothing to click).
 2. As soon as one filter is active, a blue 'Clear filters' link appears at the right end of the chip row.
-3. When the last active filter is removed, 'Clear filters' disappears again.</t>
+3. When the last active filter is removed, 'Clear filters' disappears again.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S7-R3, S7-N1, S8-N1).</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S7-R3; S7-N1; S8-N1) [spec v1.6 2026-07-28]</t>
+          <t>SV-8785 [epic] (S7-R3; S7-N1; S8-N1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -2635,12 +2721,14 @@
           <t>1. Every active filter is cleared in one click.
 2. All chips return to their default (inactive) look with no values shown.
 3. The table shows the full unfiltered list again (no text is in the page Search box, so nothing else is narrowing it).
-4. The 'Clear filters' link disappears.</t>
+4. The 'Clear filters' link disappears.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S8-R1, S13-R13).</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S8-R1; §4 Key Decisions; S13-R13 (clearing filters does not clear a typed search)) [spec v1.6 2026-07-28]</t>
+          <t>SV-8785 [epic] (S8-R1; §4 Key Decisions; S13-R13 (clearing filters does not clear a typed search)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
@@ -2684,12 +2772,14 @@
         <is>
           <t>1. Only the Status filter is cleared - its chip returns to default.
 2. The Customer filter stays selected and active (blue) and keeps filtering the table.
-3. 'Clear filters' remains visible because a filter is still active.</t>
+3. 'Clear filters' remains visible because a filter is still active.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S8-R2).</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S8-R2; §4 Key Decisions) [spec v1.6 2026-07-28]</t>
+          <t>SV-8793 (S8-R2; §4 Key Decisions) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
@@ -2734,12 +2824,14 @@
         <is>
           <t>1. Only customer A's Estimate work order is shown.
 2. Customer A's Approved work order is hidden (wrong status) and customer B's Estimate work order is hidden (wrong customer) - each additional filter narrows the result further.
-3. Both chips are in the active state and 'Clear filters' is visible.</t>
+3. Both chips are in the active state and 'Clear filters' is visible.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S8-R3).</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (§2 Feature Overview (multi-criteria); S8-R3 ('combination of active filters')) [spec v1.6 2026-07-28]</t>
+          <t>SV-8793 (§2 Feature Overview (multi-criteria); S8-R3 ('combination of active filters')) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
@@ -2783,12 +2875,14 @@
         <is>
           <t>1. The filter bar row is hidden.
 2. The work order table moves up and uses the reclaimed vertical space.
-3. The filter icon shows a pressed/active look while the bar is collapsed.</t>
+3. The filter icon shows a pressed/active look while the bar is collapsed.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S1-R4, S1-R5).</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S1-R4; S1-R5) [spec v1.6 2026-07-28]</t>
+          <t>SV-8786 (S1-R4; S1-R5) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
@@ -2832,12 +2926,14 @@
         <is>
           <t>1. The filter bar reappears below the tab row.
 2. The previously selected filters are still shown on their chips in the active (blue) state - nothing was lost while collapsed.
-3. The 'Clear filters' link is still shown at the right end of the chip row.</t>
+3. The 'Clear filters' link is still shown at the right end of the chip row.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S1-R6).</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S1-R6) [spec v1.6 2026-07-28]</t>
+          <t>SV-8786 (S1-R6) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
@@ -2881,12 +2977,14 @@
       <c r="G50" s="2" t="inlineStr">
         <is>
           <t>1. After step 2 the filter bar is still collapsed (your choice was remembered).
-2. After step 4 the filter bar is expanded again when you return - whichever state you left it in is restored.</t>
+2. After step 4 the filter bar is expanded again when you return - whichever state you left it in is restored.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S1-R7, S10-R1).</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S1-R7; S10-R1) [spec v1.6 2026-07-28]</t>
+          <t>SV-8785 [epic] (S1-R7; S10-R1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
@@ -2929,12 +3027,14 @@
       <c r="G51" s="2" t="inlineStr">
         <is>
           <t>1. After step 1 the filter icon shows no special indicator (only its normal pressed look).
-2. After step 3 the filter icon shows a visual indicator (filters icon in primary blue) signalling that active filters are in effect while the bar is hidden.</t>
+2. After step 3 the filter icon shows a visual indicator (filters icon in primary blue) signalling that active filters are in effect while the bar is hidden.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S7-R4, S7-N2).</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S7-R4; S7-N2) [spec v1.6 2026-07-28]</t>
+          <t>SV-8792 (S7-R4; S7-N2) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -2977,12 +3077,14 @@
       <c r="G52" s="2" t="inlineStr">
         <is>
           <t>1. The table content does not change when the bar collapses - it still shows only the work orders matching the active filters.
-2. Hiding the bar only hides the chips; it does not remove or pause the filtering.</t>
+2. Hiding the bar only hides the chips; it does not remove or pause the filtering.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S7-R5).</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S7-R5) [spec v1.6 2026-07-28]</t>
+          <t>SV-8792 (S7-R5) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
@@ -3026,12 +3128,14 @@
         <is>
           <t>1. The table body is replaced by an empty state (not just a bare empty grid).
 2. The empty state shows a message indicating no results were found for the current filters.
-3. No error message or broken layout appears.</t>
+3. No error message or broken layout appears.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S8-R3).</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S8-R3) [spec v1.6 2026-07-28]</t>
+          <t>SV-8793 (S8-R3) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -3076,12 +3180,14 @@
         <is>
           <t>1. The empty state includes a prompt or link to clear the filters.
 2. Clicking it removes the active filters and the full work order list is shown again (with no text in the Search box, nothing else is narrowing the list).
-3. The chips return to their default state.</t>
+3. The chips return to their default state.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S8-R4, S8-R5).</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S8-R4 (the empty state includes a prompt or link to clear filters); S8-R5 (where a query is also active each is cleared independently)) [spec v1.6 2026-07-28]</t>
+          <t>SV-8793 (S8-R4 (the empty state includes a prompt or link to clear filters); S8-R5 (where a query is also active each is cleared independently)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -3128,12 +3234,14 @@
           <t>1. The table is replaced by a no-results message that mentions BOTH the current filters and the search - not the filters alone.
 2. The message offers a way to clear the filters and, because a search is active, a separate way to clear the search.
 3. Clearing the search brings back the list as narrowed by the filter only - the filter is still on.
-4. Clearing the filters leaves your typed word in the box and still applied - each is cleared on its own without wiping the other.</t>
+4. Clearing the filters leaves your typed word in the box and still applied - each is cleared on its own without wiping the other.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S8-R3, S8-R4, S8-R5, S13-N1, S13-N2).</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S8-R3 (empty state covers filters AND any active query); S8-R4 (prompt to clear filters and the query where active); S8-R5 (each cleared independently from the empty state); S13-N1; S13-N2) [spec v1.6 2026-07-28]</t>
+          <t>SV-8785 [epic] (S8-R3 (empty state covers filters AND any active query); S8-R4 (prompt to clear filters and the query where active); S8-R5 (each cleared independently from the empty state); S13-N1; S13-N2) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
@@ -3175,12 +3283,14 @@
       <c r="G56" s="2" t="inlineStr">
         <is>
           <t>1. All five chips are shown: Status, Customer, Lead Technician, Service Advisor, Asset on site.
-2. Each chip opens its dropdown and can be used.</t>
+2. Each chip opens its dropdown and can be used.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S9-R1).</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S9-R1) [spec v1.6 2026-07-28]</t>
+          <t>SV-8794 (S9-R1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
@@ -3227,12 +3337,14 @@
         <is>
           <t>1. The Status chip is shown but greyed out, already filled in as 'Status: Estimate', and cannot be clicked or changed - the tab already pre-filters the list to Estimate.
 2. Customer, Lead Technician, Service Advisor and Asset on site chips are shown and usable.
-3. After step 4 the table shows only that customer's ESTIMATE work orders - the customer filter narrows the pre-filtered Estimates list.</t>
+3. After step 4 the table shows only that customer's ESTIMATE work orders - the customer filter narrows the pre-filtered Estimates list.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S9-R2, S2-N1). The current behaviour follows a later product owner decision dated 2026-07-17.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S9-R2; S2-N1; §4 Key Decisions - PRD text says "hidden"; behaviour per Branko Q4=B 2026-07-17 + QA-lead ruling 2026-07-30 = shown greyed-out/disabled; PRD alignment is Branko's open item) [spec v1.6 2026-07-28]</t>
+          <t>SV-8785 [epic] (S9-R2; S2-N1; §4 Key Decisions - PRD text says "hidden"; behaviour per Branko Q4=B 2026-07-17 + QA-lead ruling 2026-07-30 = shown greyed-out/disabled; PRD alignment is Branko's open item) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
@@ -3279,12 +3391,14 @@
         <is>
           <t>1. The Status chip is shown but greyed out, already filled in with this tab's status, and cannot be clicked or changed - the tab already pre-filters the list to Complete.
 2. Customer, Lead Technician, Service Advisor and Asset on site chips are shown and usable.
-3. After step 4 the table shows only that customer's COMPLETE work orders.</t>
+3. After step 4 the table shows only that customer's COMPLETE work orders.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S9-R3, S2-N2). The current behaviour follows a later product owner decision dated 2026-07-17.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S9-R3; S2-N2; §4 Key Decisions - PRD text says "hidden"; behaviour per Branko Q4=B 2026-07-17 + QA-lead ruling 2026-07-30 = shown greyed-out/disabled; PRD alignment is Branko's open item) [spec v1.6 2026-07-28]</t>
+          <t>SV-8785 [epic] (S9-R3; S2-N2; §4 Key Decisions - PRD text says "hidden"; behaviour per Branko Q4=B 2026-07-17 + QA-lead ruling 2026-07-30 = shown greyed-out/disabled; PRD alignment is Branko's open item) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
@@ -3329,12 +3443,14 @@
         <is>
           <t>1. All five filter chips are shown on the My Work Orders tab.
 2. The table only ever shows work orders assigned to you (the tab's own scope stays).
-3. After step 2 it shows only YOUR work orders in the ticked status - the filters narrow the user-scoped list, they do not widen it to other users' work orders.</t>
+3. After step 2 it shows only YOUR work orders in the ticked status - the filters narrow the user-scoped list, they do not widen it to other users' work orders.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S9-R4).</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S9-R4; §4 Key Decisions (My Work Orders tab does not remove filters)) [spec v1.6 2026-07-28]</t>
+          <t>SV-8794 (S9-R4; §4 Key Decisions (My Work Orders tab does not remove filters)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
@@ -3378,12 +3494,14 @@
         <is>
           <t>1. On the Estimates tab your Status choice is not applied and cannot be changed - the Status chip is greyed out and pre-filled with the tab's own status. The Customer selection is still shown and still filters the list.
 2. Back on the All tab the Status chip reappears with the SAME selection (Approved) still applied - the selection was retained in memory, not lost.
-3. The Customer selection is unchanged throughout.</t>
+3. The Customer selection is unchanged throughout.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S9-R5, S9-N1, S9-R2). The current behaviour follows a later product owner decision dated 2026-07-17.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S9-R5; S9-N1; S9-R2 - behaviour per Branko Q4=B 2026-07-17 + QA-lead ruling 2026-07-30) [spec v1.6 2026-07-28]</t>
+          <t>SV-8794 (S9-R5; S9-N1; S9-R2 - behaviour per Branko Q4=B 2026-07-17 + QA-lead ruling 2026-07-30) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
@@ -3426,12 +3544,14 @@
       <c r="G61" s="2" t="inlineStr">
         <is>
           <t>1. On the very first visit the Estimates tab is the selected one, even though All is the FIRST tab in the row (order and default are different on purpose).
-2. After switching to All and returning, the All tab is selected - the app remembers your last-used tab per account.</t>
+2. After switching to All and returning, the All tab is selected - the app remembers your last-used tab per account.
+---
+This is the expected behaviour as per epic SV-8785 and the engineering technical plan. No numbered requirement in the Filters specification version 1.6 covers this point yet.</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (no requirement in the ratified spec v1.6 - default/last-used tab is engineering-plan-only - confirmation requested); tech plan 2026-07-29 D10 (default tab = Estimates; last-used tab persists) [spec v1.6 2026-07-28]</t>
+          <t>SV-8785 [epic] (no requirement in the ratified spec v1.6 - default/last-used tab is engineering-plan-only - confirmation requested); tech plan 2026-07-29 D10 (default tab = Estimates; last-used tab persists) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
@@ -3476,12 +3596,14 @@
         <is>
           <t>1. After step 2 the same Status and Customer selections are still applied - chips active with the same values, table filtered the same way.
 2. The filter bar is still expanded (as you left it).
-3. After step 4 the filter bar comes back collapsed - the collapsed/expanded state is restored too.</t>
+3. After step 4 the filter bar comes back collapsed - the collapsed/expanded state is restored too.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S10-R1, S1-R7).</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S10-R1; S1-R7) [spec v1.6 2026-07-28]</t>
+          <t>SV-8785 [epic] (S10-R1; S1-R7) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
@@ -3528,12 +3650,14 @@
         <is>
           <t>1. After moving around the app (step 2) the filter selections are still applied - you do not have to re-apply them.
 2. After closing the browser completely and signing back in (step 5) the same filter selections are still applied - the app remembers your filters for you permanently, not just for one browser session.
-3. The same filter selections are applied on the other computer too - the filters are saved to your account, not to one computer or browser (to confirm live once built).</t>
+3. The same filter selections are applied on the other computer too - the filters are saved to your account, not to one computer or browser (to confirm live once built).
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S10-R2, S10-R3, S10-R1).</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S10-R2 (stored server-side against the account; survives logout; syncs across devices); S10-R3 (saved per user); S10-R1 (restored after navigating away)) + Branko Q2 2026-07-17 - now matched by the PRD [spec v1.6 2026-07-28]</t>
+          <t>SV-8795 (S10-R2 (stored server-side against the account; survives logout; syncs across devices); S10-R3 (saved per user); S10-R1 (restored after navigating away)) + Branko Q2 2026-07-17 - now matched by the PRD [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
@@ -3576,12 +3700,14 @@
       <c r="G64" s="2" t="inlineStr">
         <is>
           <t>1. User B does not see user A's filters - user B's page opens with user B's own (or no) filters.
-2. User B's new filter does not change what user A sees; each user keeps their own saved filter state.</t>
+2. User B's new filter does not change what user A sees; each user keeps their own saved filter state.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S10-R3).</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S10-R3; §4 Key Decisions (saved per user)) [spec v1.6 2026-07-28]</t>
+          <t>SV-8795 (S10-R3; §4 Key Decisions (saved per user)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
@@ -3625,12 +3751,14 @@
         <is>
           <t>1. The deleted customer is silently ignored - no error or warning appears.
 2. The Customer filter now reflects only the still-valid selection (the real customer).
-3. The table is filtered by the remaining valid selection only.</t>
+3. The table is filtered by the remaining valid selection only.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S10-N1).</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S10-N1) [spec v1.6 2026-07-28]</t>
+          <t>SV-8795 (S10-N1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
@@ -3675,12 +3803,14 @@
         <is>
           <t>1. The second Parts view does NOT show the first view's selections - each view keeps its own.
 2. Returning to the first view restores that view's own selections.
-3. Report tabs likewise keep separate filter choices, each remembered and restored on its own tab.</t>
+3. Report tabs likewise keep separate filter choices, each remembered and restored on its own tab.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S10-R4).</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (spec v1.6 S10-R4; §4 "Parts and Reports selections are scoped to their view/tab and persist there"); Branko answers 2026-07-31 Q5 exception 1; tech plan 2026-07-29 D20</t>
+          <t>SV-8795 (spec v1.6 S10-R4; §4 "Parts and Reports selections are scoped to their view/tab and persist there"); Branko answers 2026-07-31 Q5 exception 1; tech plan 2026-07-29 D20</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
@@ -3722,12 +3852,14 @@
       <c r="G67" s="2" t="inlineStr">
         <is>
           <t>1. The old saved choices appear in the new filter bar on the first visit - the update does not lose them (old status choices show in the Status chip, the old asset-here choice shows as Asset on site: Yes, the old My-Work-Orders toggle maps to the My Work Orders tab, columns and sorting stay).
-2. Those carried-over choices are now saved to the account: the other computer shows them too.</t>
+2. Those carried-over choices are now saved to the account: the other computer shows them too.
+---
+This is the expected behaviour as per epic SV-8785 and the engineering technical plan. No numbered requirement in the Filters specification version 1.6 covers this point yet.</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (no numbered v1.6 requirement covers the one-off migration - context S10-R2 server-side model); tech plan 2026-07-29 s4-3.3 (browser-storage to account-preference migration) - confirmation requested [spec v1.6 2026-07-28]</t>
+          <t>SV-8795 (no numbered v1.6 requirement covers the one-off migration - context S10-R2 server-side model); tech plan 2026-07-29 s4-3.3 (browser-storage to account-preference migration) - confirmation requested [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
@@ -3770,12 +3902,14 @@
       <c r="G68" s="2" t="inlineStr">
         <is>
           <t>1. After step 1 the URL changes to include the active filter state.
-2. After step 3 the filter part of the URL is removed again.</t>
+2. After step 3 the filter part of the URL is removed again.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S11-R1).</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S11-R1) [spec v1.6 2026-07-28]</t>
+          <t>SV-8796 (S11-R1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
@@ -3818,12 +3952,14 @@
         <is>
           <t>1. The page opens with the same filters already applied - chips active with the same values.
 2. The table is already filtered accordingly on load (no need to re-apply anything).
-3. The same works from a saved bookmark.</t>
+3. The same works from a saved bookmark.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S11-R2).</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S11-R2; §2 Feature Overview (share or bookmark)) [spec v1.6 2026-07-28]</t>
+          <t>SV-8796 (S11-R2; §2 Feature Overview (share or bookmark)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr"/>
@@ -3867,12 +4003,14 @@
         <is>
           <t>1. The page loads normally - no error.
 2. The deleted value is ignored; only the still-valid filter value is applied and shown on the chips.
-3. The table reflects only the valid filter.</t>
+3. The table reflects only the valid filter.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S11-R3).</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S11-R3) [spec v1.6 2026-07-28]</t>
+          <t>SV-8796 (S11-R3) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
@@ -3916,12 +4054,14 @@
         <is>
           <t>1. The Work Orders page loads normally.
 2. No filters are applied (chips in default state, full list shown) - the unrecognizable state is discarded.
-3. No error message or broken page appears.</t>
+3. No error message or broken page appears.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S11-N1).</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S11-N1) [spec v1.6 2026-07-28]</t>
+          <t>SV-8796 (S11-N1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
@@ -3972,12 +4112,14 @@
 3. A 'Back to my view' option is shown while you are looking at the shared link. (If the wording on screen is slightly different, note what it says and carry on.)
 4. Clicking 'Back to my view' brings back your own saved filters and removes the filter part from the web address.
 5. It also empties the Search box and removes your typed text - the search is not something that gets saved, so there is nothing to bring back.
-6. Returning normally later still shows your own saved filters, untouched by the link visit.</t>
+6. Returning normally later still shows your own saved filters, untouched by the link visit.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S11-R6, S11-R7, S11-R8).</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S11-R6 (URL state runtime-only with no write-back); S11-R7 (Back to my view - also clears the query); S11-R8 (rationale: the query is never saved)) [spec v1.6 2026-07-28]</t>
+          <t>SV-8796 (S11-R6 (URL state runtime-only with no write-back); S11-R7 (Back to my view - also clears the query); S11-R8 (rationale: the query is never saved)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr"/>
@@ -4025,12 +4167,14 @@
           <t>1. On your own view there is no 'Back to my view' option anywhere - it only belongs to a shared-link visit.
 2. Changing your own filters does not make it appear.
 3. When you open the shared link, 'Back to my view' does appear.
-4. After you click it and you are back on your own view, the option disappears again.</t>
+4. After you click it and you are back on your own view, the option disappears again.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S11-N3, S11-R7).</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S11-N3; S11-R7) [spec v1.6 2026-07-28]</t>
+          <t>SV-8796 (S11-N3; S11-R7) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr"/>
@@ -4073,12 +4217,14 @@
         <is>
           <t>1. A filter chip row is shown below the tabs, starting with an 'All Filters' chip (with a filter icon) followed by the individual filter chips (Status, Customer, Lead Technician, ...).
 2. The row scrolls horizontally - chips that do not fit are reachable by swiping.
-3. An arrow at the right-hand edge shows that the row can be scrolled. (This is what the design shows - if your screen looks different, write down what you actually see and carry on.)</t>
+3. An arrow at the right-hand edge shows that the row can be scrolled. (This is what the design shows - if your screen looks different, write down what you actually see and carry on.)
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S12-R1). The screen described above comes from the agreed design rather than that specification, and a product owner decision is still awaited.</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S12-R1) [spec v1.6 2026-07-28]</t>
+          <t>SV-8797 (S12-R1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
@@ -4121,12 +4267,14 @@
         <is>
           <t>1. A bottom sheet slides up with a drag handle at the top, the centered title 'All Filters' and a close (x) button.
 2. It lists the five filters as expandable accordion rows, each with its icon, name and a down arrow: Status, Customer, Lead Technician, Service Advisor, Asset on site.
-3. A sticky blue 'Apply filters' button sits at the bottom of the sheet.</t>
+3. A sticky blue 'Apply filters' button sits at the bottom of the sheet.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S12-R3). The screen described above comes from the agreed design rather than that specification, and a product owner decision is still awaited.</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S12-R3) [spec v1.6 2026-07-28]</t>
+          <t>SV-8797 (S12-R3) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr"/>
@@ -4172,12 +4320,14 @@
         <is>
           <t>1. Expanding Status reveals the same nine status checkboxes as desktop (Estimate, Approved, In progress, Review, Complete, Invoiced, Paid, Declined, Imported) plus 'Clear selection'.
 2. After 'Apply filters' the sheet closes and the work order list shows only the ticked statuses.
-3. The reopened sheet's title shows the applied-filter count, for example 'All Filters (1)', and the Status accordion header is highlighted with the selected values ticked.</t>
+3. The reopened sheet's title shows the applied-filter count, for example 'All Filters (1)', and the Status accordion header is highlighted with the selected values ticked.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S12-R2, S12-R3, S2-R1). The screen described above comes from the agreed design rather than that specification, and a product owner decision is still awaited.</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S12-R2; S12-R3; S2-R1) [spec v1.6 2026-07-28]</t>
+          <t>SV-8785 [epic] (S12-R2; S12-R3; S2-R1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr"/>
@@ -4221,12 +4371,14 @@
         <is>
           <t>1. A bottom sheet opens for that single filter: its title row shows the filter's icon and name (for example 'Status') with a close (x) button - no accordion list of the other filters.
 2. The sheet shows only that filter's options (the nine status checkboxes plus 'Clear selection').
-3. The bottom button reads 'Apply filter' (singular); tapping it applies the selection and filters the list.</t>
+3. The bottom button reads 'Apply filter' (singular); tapping it applies the selection and filters the list.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S12-R2, S12-R3). The screen described above comes from the agreed design rather than that specification, and a product owner decision is still awaited.</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S12-R2; S12-R3) [spec v1.6 2026-07-28]</t>
+          <t>SV-8797 (S12-R2; S12-R3) [spec v1.6 2026-07-28] ; individual-chip real-time per S12-R2 + tech-plan 2026-07-29; only the combined All Filters sheet is batch</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr"/>
@@ -4273,12 +4425,14 @@
           <t>1. The list narrows to matching names as you type.
 2. Each selected customer appears as a tag with an x in the input area, and its list row shows a checkmark.
 3. Removing a tag deselects just that customer.
-4. After 'Apply filters' the list shows only work orders of the remaining selected customers, and the sheet title counts the applied filters (for example 'All Filters (2)').</t>
+4. After 'Apply filters' the list shows only work orders of the remaining selected customers, and the sheet title counts the applied filters (for example 'All Filters (2)').
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S12-R2, S3-R2/R3/R5). The screen described above comes from the agreed design rather than that specification, and a product owner decision is still awaited.</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S12-R2; S3-R2/R3/R5) [spec v1.6 2026-07-28]</t>
+          <t>SV-8785 [epic] (S12-R2; S3-R2/R3/R5) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr"/>
@@ -4323,12 +4477,14 @@
         <is>
           <t>1. The Lead Technician row opens with a 'Search technician' field and the technician list.
 2. The Service Advisor row opens with a 'Search advisor' field and the advisor list.
-3. Applying a selection filters the work order list just like on desktop.</t>
+3. Applying a selection filters the work order list just like on desktop.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S12-R2, S4-R1, S5-R1). The screen described above comes from the agreed design rather than that specification, and a product owner decision is still awaited.</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S12-R2; S4-R1; S5-R1) [spec v1.6 2026-07-28]</t>
+          <t>SV-8785 [epic] (S12-R2; S4-R1; S5-R1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr"/>
@@ -4373,12 +4529,14 @@
         <is>
           <t>1. The Asset on site row opens showing the two options Yes and No plus 'Clear selection'.
 2. Only one option can be selected at a time.
-3. After applying, the list shows only work orders matching the chosen on-site state.</t>
+3. After applying, the list shows only work orders matching the chosen on-site state.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S12-R2, S6-R1/R2/R3). The screen described above comes from the agreed design rather than that specification, and a product owner decision is still awaited.</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S12-R2; S6-R1/R2/R3) [spec v1.6 2026-07-28]</t>
+          <t>SV-8785 [epic] (S12-R2; S6-R1/R2/R3) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr"/>
@@ -4422,12 +4580,14 @@
         <is>
           <t>1. The chip for the applied filter shows the active state with the selected value(s), like on desktop.
 2. A 'Clear filters' control appears while at least one filter is active.
-3. Using it removes all active filters, the chips return to default and the full list comes back.</t>
+3. Using it removes all active filters, the chips return to default and the full list comes back.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S12-R2, S7-R1/R3, S8-R1).</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S12-R2; S7-R1/R3; S8-R1) [spec v1.6 2026-07-28]</t>
+          <t>SV-8785 [epic] (S12-R2; S7-R1/R3; S8-R1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr"/>
@@ -4469,12 +4629,14 @@
       <c r="G82" s="2" t="inlineStr">
         <is>
           <t>1. There is no filter-bar collapse/expand (filter icon) toggle on mobile.
-2. The filter chip row is always visible on the mobile Work Orders page.</t>
+2. The filter chip row is always visible on the mobile Work Orders page.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S12-R4).</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S12-R4) [spec v1.6 2026-07-28]</t>
+          <t>SV-8797 (S12-R4) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr"/>
@@ -4517,12 +4679,14 @@
         <is>
           <t>1. The list shows the same no-results empty state as desktop, saying no results were found for the current filters.
 2. The empty state includes the prompt to clear filters.
-3. No error appears.</t>
+3. No error appears.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S12-N1, S8-R3/R4).</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S12-N1; S8-R3/R4) [spec v1.6 2026-07-28]</t>
+          <t>SV-8785 [epic] (S12-N1; S8-R3/R4) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr"/>
@@ -4583,12 +4747,14 @@
 10. Every Parts list page also shows a Search (magnifier) icon and a filter icon in the toolbar; some pages (for example Inventory) also show a column/layout toggle icon.
 11. Every filter button shown above is a working filter on that page - none of them is display-only.
 12. The choices inside each filter come from your own shop's data (for example your real vendors or categories), so there is no fixed list to compare against - check that the choices you see match the data in your shop.
-13. Still to check on the live build: what the filter icon and the column/layout icon do (the written description does not cover the toolbar icons).</t>
+13. Still to check on the live build: what the filter icon and the column/layout icon do (the written description does not cover the toolbar icons).
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (§2, §4), which covers this area in its overview and key decisions only. The detailed behaviour above follows a later product owner decision dated 2026-07-31.</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (spec v1.6 §2 Feature Overview -&gt; Parts Filters; §4 Key Decisions -&gt; "Context-specific filter sets on Parts and Reports" + "Multi-select where it makes sense"); Branko answers 2026-07-31 Q2/Q3/Q5/Q7; Figma 11884-16885</t>
+          <t>SV-8785 [epic] (spec v1.6 §2 Feature Overview -&gt; Parts Filters; §4 Key Decisions -&gt; "Context-specific filter sets on Parts and Reports" + "Multi-select where it makes sense"); Branko answers 2026-07-31 Q2/Q3/Q5/Q7; Figma 11884-16885</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr"/>
@@ -4634,12 +4800,14 @@
           <t>1. A small menu opens with two options: Core and Non Core.
 2. A Clear selection action is shown at the bottom of the menu.
 3. You can tick both Core and Non Core at the same time - this filter allows more than one choice.
-4. As soon as you tick a choice the list below narrows to matching parts straight away, with no Apply button to press; Clear selection puts the list back.</t>
+4. As soon as you tick a choice the list below narrows to matching parts straight away, with no Apply button to press; Clear selection puts the list back.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (§2, §4), which covers this area in its overview and key decisions only. The detailed behaviour above follows a later product owner decision dated 2026-07-31.</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (spec v1.6 §2 Feature Overview -&gt; Parts Filters; §4 Key Decisions -&gt; "Context-specific filter sets on Parts and Reports" + "Multi-select where it makes sense"); Branko answers 2026-07-31 Q2/Q3/Q5/Q7; Figma 11884-16885</t>
+          <t>SV-8785 [epic] (spec v1.6 §2 Feature Overview -&gt; Parts Filters; §4 Key Decisions -&gt; "Context-specific filter sets on Parts and Reports" + "Multi-select where it makes sense"); Branko answers 2026-07-31 Q2/Q3/Q5/Q7; Figma 11884-16885</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr"/>
@@ -4683,12 +4851,14 @@
         <is>
           <t>1. The table updates to show only the rows that match the chosen filter value.
 2. The chosen value is shown on the filter button so you can see what is applied.
-3. The list narrows as soon as you pick the value - there is no Apply or Search button to press. Every filter button on every Parts page works this way.</t>
+3. The list narrows as soon as you pick the value - there is no Apply or Search button to press. Every filter button on every Parts page works this way.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (§2, §4), which covers this area in its overview and key decisions only. The detailed behaviour above follows a later product owner decision dated 2026-07-31.</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (spec v1.6 §2 Feature Overview -&gt; Parts Filters; §4 Key Decisions -&gt; "Context-specific filter sets on Parts and Reports" + "Multi-select where it makes sense"); Branko answers 2026-07-31 Q2/Q3/Q5/Q7; Figma 11884-16885</t>
+          <t>SV-8785 [epic] (spec v1.6 §2 Feature Overview -&gt; Parts Filters; §4 Key Decisions -&gt; "Context-specific filter sets on Parts and Reports" + "Multi-select where it makes sense"); Branko answers 2026-07-31 Q2/Q3/Q5/Q7; Figma 11884-16885</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr"/>
@@ -4732,12 +4902,14 @@
         <is>
           <t>1. More than one value can be chosen inside the filter, and the button shows what you picked.
 2. Clear selection removes the choices for that one filter.
-3. A Clear filters button appears in the filter bar while any filter is set, and using it clears them all at once - exactly as it works on the Work Orders page.</t>
+3. A Clear filters button appears in the filter bar while any filter is set, and using it clears them all at once - exactly as it works on the Work Orders page.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (§2, §4), which covers this area in its overview and key decisions only. The detailed behaviour above follows a later product owner decision dated 2026-07-31.</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (spec v1.6 §2 Feature Overview -&gt; Parts Filters; §4 Key Decisions -&gt; "Context-specific filter sets on Parts and Reports" + "Multi-select where it makes sense"); Branko answers 2026-07-31 Q2/Q3/Q5/Q7; Figma 11884-16885</t>
+          <t>SV-8785 [epic] (spec v1.6 §2 Feature Overview -&gt; Parts Filters; §4 Key Decisions -&gt; "Context-specific filter sets on Parts and Reports" + "Multi-select where it makes sense"); Branko answers 2026-07-31 Q2/Q3/Q5/Q7; Figma 11884-16885</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr"/>
@@ -4784,12 +4956,14 @@
         <is>
           <t>1. Every filter the page offered before is still offered - nothing has been taken away.
 2. Every choice each of those filters offered before is still available inside the new button.
-3. If any filter or choice is missing, write down exactly which page, which filter and which choice - that is a bug worth reporting.</t>
+3. If any filter or choice is missing, write down exactly which page, which filter and which choice - that is a bug worth reporting.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (§2), which covers this area in its overview and key decisions only. The detailed behaviour above follows a later product owner decision dated 2026-07-31.</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (spec v1.6 §2 Parts Filters + Reports Filters); Branko answers 2026-07-31 Q3 ("support all the filters we have right now in the app as well as all choices per filter"); tech plan 2026-07-29 rollout rule</t>
+          <t>SV-8785 [epic] (spec v1.6 §2 Parts Filters + Reports Filters); Branko answers 2026-07-31 Q3 ("support all the filters we have right now in the app as well as all choices per filter"); tech plan 2026-07-29 rollout rule</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr"/>
@@ -4867,12 +5041,14 @@
 21. On every report above, each filter button shows its name and a down arrow.
 22. Every filter button shown above is a working filter on that report - none of them is display-only.
 23. The choices inside each filter come from your own shop's data (for example your real vendors or categories), so there is no fixed list to compare against - check that the choices you see match the data in your shop.
-24. Still to check on the live build: the real columns of the Sales Tax report and of the six A/R and A/P aging reports. The design uses sample placeholder tables for those, and the written description does not list their columns.</t>
+24. Still to check on the live build: the real columns of the Sales Tax report and of the six A/R and A/P aging reports. The design uses sample placeholder tables for those, and the written description does not list their columns.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (§2, §4), which covers this area in its overview and key decisions only. The detailed behaviour above follows a later product owner decision dated 2026-07-31.</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (spec v1.6 §2 Reports Filters; §4 Key Decisions "New date-range filter type" + "Multi-select where it makes sense"); Branko answers 2026-07-31 Q2/Q3/Q5/Q7; Figma 11903-10573</t>
+          <t>SV-8785 [epic] (spec v1.6 §2 Reports Filters; §4 Key Decisions "New date-range filter type" + "Multi-select where it makes sense"); Branko answers 2026-07-31 Q2/Q3/Q5/Q7; Figma 11903-10573</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr"/>
@@ -4915,12 +5091,14 @@
       <c r="G90" s="2" t="inlineStr">
         <is>
           <t>1. The report updates to show only the rows matching the chosen filter value, and the chosen value is shown on the filter button.
-2. The report narrows as soon as you pick the value - there is no Apply or Run button to press. Every filter button on every report works this way.</t>
+2. The report narrows as soon as you pick the value - there is no Apply or Run button to press. Every filter button on every report works this way.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (§2, §4), which covers this area in its overview and key decisions only. The detailed behaviour above follows a later product owner decision dated 2026-07-31.</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (spec v1.6 §2 Reports Filters; §4 Key Decisions "New date-range filter type" + "Multi-select where it makes sense"); Branko answers 2026-07-31 Q2/Q3/Q5/Q7; Figma 11903-10573</t>
+          <t>SV-8785 [epic] (spec v1.6 §2 Reports Filters; §4 Key Decisions "New date-range filter type" + "Multi-select where it makes sense"); Branko answers 2026-07-31 Q2/Q3/Q5/Q7; Figma 11903-10573</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr"/>
@@ -4964,12 +5142,14 @@
         <is>
           <t>1. Each of these filter buttons - Location, Transaction Type, Invoice Status, Type, User and Mention - opens a list of choices, lets you tick more than one, and narrows the report straight away with no Apply button.
 2. The choices inside each filter come from your own shop's data (for example your real vendors or categories), so there is no fixed list to compare against - check that the choices you see match the data in your shop.
-3. Write down the choices you actually see behind each of these six buttons. They have not been written down anywhere yet, so your list becomes the record.</t>
+3. Write down the choices you actually see behind each of these six buttons. They have not been written down anywhere yet, so your list becomes the record.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (§2, §4), which covers this area in its overview and key decisions only. The detailed behaviour above follows a later product owner decision dated 2026-07-31.</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (spec v1.6 §2 Reports Filters; §4 "Multi-select where it makes sense"); Branko answers 2026-07-31 Q3/Q5 + Q4 (pointer only - the 6 new types are not enumerated in v1.6; see DELTAS.md F1); Figma 11903-10573</t>
+          <t>SV-8785 [epic] (spec v1.6 §2 Reports Filters; §4 "Multi-select where it makes sense"); Branko answers 2026-07-31 Q3/Q5 + Q4 (pointer only - the 6 new types are not enumerated in v1.6; see DELTAS.md F1); Figma 11903-10573</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr"/>
@@ -5017,12 +5197,14 @@
           <t>1. A start/end date picker opens - there are NO preset ranges (no 'Last 30 days' shortcuts) and NO pre-filled default range.
 2. After only the start date, the results do not change yet.
 3. As soon as the second date is picked, the results update immediately to show only records inside the range.
-4. Only one date range can be active at a time on that chip, and the chip shows the active range.</t>
+4. Only one date range can be active at a time on that chip, and the chip shows the active range.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (§4, §2), which covers this area in its overview and key decisions only. The detailed behaviour above follows a later product owner decision dated 2026-07-31.</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (spec v1.6 §4 "New date-range filter type"; §2 Reports Filters - start/end picker; no presets; no default; applies on the second date); Branko answers 2026-07-31 Q5; tech plan 2026-07-29 D19</t>
+          <t>SV-8785 [epic] (spec v1.6 §4 "New date-range filter type"; §2 Reports Filters - start/end picker; no presets; no default; applies on the second date); Branko answers 2026-07-31 Q5; tech plan 2026-07-29 D19</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr"/>
@@ -5070,12 +5252,14 @@
           <t>1. The control expands in place into a small search box showing the placeholder 'Type to search'.
 2. The list narrows as you type, after a brief pause - and ONLY this page's list changes, nothing else in the app.
 3. The round x clears the text and the full list returns.
-4. Clicking away with an empty box collapses it back to the Search button; with text in it, the box stays open.</t>
+4. Clicking away with an empty box collapses it back to the Search button; with text in it, the box stays open.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S13-R1, S13-R9, S13-R12, S13-R15).</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S13-R1 (placement in the toolbar action group); S13-R9 (scoped to this table only); S13-R12; S13-R15 (blur rules)) [spec v1.6 2026-07-28]</t>
+          <t>SV-8798 (S13-R1 (placement in the toolbar action group); S13-R9 (scoped to this table only); S13-R12; S13-R15 (blur rules)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr"/>
@@ -5120,12 +5304,14 @@
         <is>
           <t>1. With both active, the results match the filter AND the search together (both narrow the list at once).
 2. Clearing the search keeps the filter applied.
-3. Clearing the filter keeps the search applied - each is cleared by its own control without wiping the other.</t>
+3. Clearing the filter keeps the search applied - each is cleared by its own control without wiping the other.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S13-R10, S13-R13, S8-R5).</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S13-R10 (search and filters are additive); S13-R13 (each cleared independently); S8-R5) [spec v1.6 2026-07-28]</t>
+          <t>SV-8785 [epic] (S13-R10 (search and filters are additive); S13-R13 (each cleared independently); S8-R5) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr"/>
@@ -5173,12 +5359,14 @@
           <t>1. Sorting and paging keep your search applied - your text stays in the box and the list stays narrowed.
 2. Leaving the page and coming back also keeps your text in the box and the list still narrowed.
 3. The second browser tab starts clean: its Search box is empty and it shows the full list. Each tab keeps its own search.
-4. After closing the browser and coming back, the Search box is empty and the list is unsearched - a typed search is never remembered for next time (your filters, unlike the search, ARE remembered).</t>
+4. After closing the browser and coming back, the Search box is empty and the list is unsearched - a typed search is never remembered for next time (your filters, unlike the search, ARE remembered).
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S13-R14, S13-R25, S13-N4, S10-R5).</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S13-R14 (retained for the browser tab session); S13-R25 (never stored against the account; each tab independent); S13-N4 (not restored on a later visit); S10-R5) [spec v1.6 2026-07-28]</t>
+          <t>SV-8785 [epic] (S13-R14 (retained for the browser tab session); S13-R25 (never stored against the account; each tab independent); S13-N4 (not restored on a later visit); S10-R5) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr"/>
@@ -5223,12 +5411,14 @@
           <t>1. The address contains the search term after step 1.
 2. The fresh tab opens with the search box filled and the list already narrowed.
 3. The malformed part is ignored - the page loads cleanly without an error.
-4. A search arriving via a link is view-only, the same as filters from a link - it does not overwrite your own remembered search.</t>
+4. A search arriving via a link is view-only, the same as filters from a link - it does not overwrite your own remembered search.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S11-R4, S11-R5, S11-N2, S11-R8).</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S11-R4 (query reflected in the URL); S11-R5 (URL query pre-applied with the control filled); S11-N2 (malformed query ignored with no error); S11-R8 (rationale: no saved value to overwrite)) [spec v1.6 2026-07-28]</t>
+          <t>SV-8796 (S11-R4 (query reflected in the URL); S11-R5 (URL query pre-applied with the control filled); S11-N2 (malformed query ignored with no error); S11-R8 (rationale: no saved value to overwrite)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr"/>
@@ -5275,12 +5465,14 @@
 2. The list narrows as you type, same as desktop.
 3. To make room, the page's main button no longer stretches full-width, and pages with two or more small icon buttons collapse them into a single 'more' menu.
 4. The box stretches to fill the space left in the action row instead of staying the narrow desktop size, and every other toolbar button stays visible and in the same place while you search.
-5. There is no extra 'search is on' badge on mobile: with text in it the box simply stays open showing your text, and an empty box closes back to the Search button when you tap elsewhere - exactly as on desktop.</t>
+5. There is no extra 'search is on' badge on mobile: with text in it the box simply stays open showing your text, and an empty box closes back to the Search button when you tap elsewhere - exactly as on desktop.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S13-R16, S13-R17, S13-R18, S13-R19, S13-R20, S12-R5).</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S13-R16 (inline expansion with no modal); S13-R17 (field fills the remaining width); S13-R18 (CTA hug width); S13-R19 (2+ icon actions -&gt; "more" kebab); S13-R20 (no active-query indicator); S12-R5) [spec v1.6 2026-07-28]</t>
+          <t>SV-8785 [epic] (S13-R16 (inline expansion with no modal); S13-R17 (field fills the remaining width); S13-R18 (CTA hug width); S13-R19 (2+ icon actions -&gt; "more" kebab); S13-R20 (no active-query indicator); S12-R5) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr"/>
@@ -5329,12 +5521,14 @@
           <t>1. Every table listed above has its own Search box - no table lost the ability to narrow by text.
 2. Each Search box narrows only its own table; nothing else in the app changes.
 3. Where the table sits inside a dialog (the Work Order Log, the Line Log, the audit log dialog), the Search box is inside that dialog and works there.
-4. The work order Parts tab keeps the local search input it already had - it was deliberately left as it is.</t>
+4. The work order Parts tab keeps the local search input it already had - it was deliberately left as it is.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S14-R6, S14-R5, S13-R22, S14-N1).</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S14-R6 (audit: 42 surfaces across 39 components; Work Order Parts excluded); S14-R5 (app-wide sweep); S13-R22 (every table carries a search control); S14-N1 (verify once at the end)) [spec v1.6 2026-07-28]</t>
+          <t>SV-8785 [epic] (S14-R6 (audit: 42 surfaces across 39 components; Work Order Parts excluded); S14-R5 (app-wide sweep); S13-R22 (every table carries a search control); S14-N1 (verify once at the end)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr"/>
@@ -5379,12 +5573,14 @@
         <is>
           <t>1. The page list does NOT narrow while you type in the navigation search - only its dropdown of matching records appears.
 2. The same holds on the other pages checked.
-3. Picking a dropdown result still takes you to that record - the navigation search keeps its find-and-open role.</t>
+3. Picking a dropdown result still takes you to that record - the navigation search keeps its find-and-open role.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S14-R1, S14-R2, S14-R4, S14-R5).</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S14-R1 (navigational results only); S14-R2 (the page-filtering code path is removed rather than dormant); S14-R4 (the list is left untouched); S14-R5) [spec v1.6 2026-07-28]</t>
+          <t>SV-8799 (S14-R1 (navigational results only); S14-R2 (the page-filtering code path is removed rather than dormant); S14-R4 (the list is left untouched); S14-R5) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr"/>
@@ -5433,12 +5629,14 @@
 3. Clicking it turns the button into a small text box in the same spot (the design sets it at 180 pixels wide), the typing cursor is already inside it, and the box grows towards the left so the other toolbar buttons do not move.
 4. While the box is empty it shows the magnifier icon and the grey placeholder text 'Type to search'.
 5. As soon as you type, your text shows in a dark grey and a small round x appears at the right-hand end of the box.
-6. A very long sentence does not make the box grow and does not cut the text off - the text scrolls sideways inside the box and the cursor stays where you are typing.</t>
+6. A very long sentence does not make the box grow and does not cut the text off - the text scrolls sideways inside the box and the cursor stays where you are typing.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S13-R2, S13-R3, S13-R4, S13-R5, S13-R6, S13-R8).</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S13-R2 (default text button); S13-R3 (hover fill); S13-R4 (expands in place at 180px); S13-R5 (placeholder "Type to search"); S13-R6 (typed text + X-circle clear); S13-R8 (long queries scroll)) [spec v1.6 2026-07-28]</t>
+          <t>SV-8798 (S13-R2 (default text button); S13-R3 (hover fill); S13-R4 (expands in place at 180px); S13-R5 (placeholder "Type to search"); S13-R6 (typed text + X-circle clear); S13-R8 (long queries scroll)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr"/>
@@ -5487,12 +5685,14 @@
 2. The matching rows appear in the table you were already looking at; no separate results page, results list or pop-up window opens.
 3. There is no Apply or Submit button anywhere next to the Search box.
 4. Pressing Enter changes nothing that has not already happened - the same rows stay listed and no page reload happens.
-5. Parts Inventory behaves the same way, only it waits a fraction longer before reacting; that longer wait is on purpose because that page carries more data.</t>
+5. Parts Inventory behaves the same way, only it waits a fraction longer before reacting; that longer wait is on purpose because that page carries more data.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S13-R7, S13-R12).</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S13-R7 (applies as you type; debounced 300ms; no apply/submit; Enter not required; Inventory 350ms); S13-R12 (results replace the table in place)) [spec v1.6 2026-07-28]</t>
+          <t>SV-8798 (S13-R7 (applies as you type; debounced 300ms; no apply/submit; Enter not required; Inventory 350ms); S13-R12 (results replace the table in place)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr"/>
@@ -5539,12 +5739,14 @@
           <t>1. On the All tab only the rows matching your word remain.
 2. On the Estimates tab your word is still in the Search box, and the list shows only Estimates rows that match it - no rows from the other tabs appear.
 3. The Completed tab behaves the same way: your word is still there and only that tab's matching rows are listed.
-4. Clearing the search clears it for all the Work Orders tabs - they share one search - and each tab shows its full list again.</t>
+4. Clearing the search clears it for all the Work Orders tabs - they share one search - and each tab shows its full list again.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S13-R11, S13-R24).</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S13-R11 (search applies within the active tab only); S13-R24 (the Work Orders tabs share a single query - views of one dataset)) [spec v1.6 2026-07-28]</t>
+          <t>SV-8798 (S13-R11 (search applies within the active tab only); S13-R24 (the Work Orders tabs share a single query - views of one dataset)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr"/>
@@ -5591,12 +5793,14 @@
           <t>1. The second Parts view opens with an empty Search box and its full list - the word you typed on the first view is not carried over.
 2. Going back to the first view brings its own word back and narrows its list again.
 3. Each report tab behaves the same way: a word typed on one tab stays on that tab only, and each tab remembers its own.
-4. No search is ever applied to a table it was not typed on.</t>
+4. No search is ever applied to a table it was not typed on.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S13-R24, S13-R11, S10-R4).</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S13-R24 (Reports sub-tabs and Parts views each keep their own query); S13-R11; S10-R4 (each view/tab keeps its own set)) [spec v1.6 2026-07-28]</t>
+          <t>SV-8785 [epic] (S13-R24 (Reports sub-tabs and Parts views each keep their own query); S13-R11; S10-R4 (each view/tab keeps its own set)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr"/>
@@ -5642,12 +5846,14 @@
           <t>1. The page opens with the normal list for your own saved filters - the old search word does NOT narrow the list.
 2. The page's own Search box is empty; nothing was carried into it.
 3. No error is shown - the leftover search part in the address is simply ignored. (Whether it also disappears from the address is not important; note what you see.)
-4. After typing in the top-of-screen search and reloading, the list is still not narrowed and nothing about that word was remembered for the list.</t>
+4. After typing in the top-of-screen search and reloading, the list is still not narrowed and nothing about that word was remembered for the list.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S14-R3, S14-R2, S14-R1).</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S14-R3 (state / URL parameters / persisted values carrying a global search term into page filtering are removed with it); S14-R2; S14-R1) [spec v1.6 2026-07-28]</t>
+          <t>SV-8799 (S14-R3 (state / URL parameters / persisted values carrying a global search term into page filtering are removed with it); S14-R2; S14-R1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr"/>
@@ -5692,12 +5898,14 @@
         <is>
           <t>1. The list stays narrowed by your word - collapsing the filter bar does not cancel the search.
 2. The Search box stays in the toolbar row with your word still showing; it is not tucked away with the filter bar, because the search sits in the toolbar row and the chips sit in the row below.
-3. Expanding the bar again changes nothing about the search or the narrowed list.</t>
+3. Expanding the bar again changes nothing about the search or the narrowed list.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S13-E1).</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S13-E1 (a collapsed filter bar keeps an active query applying and the search control stays in the toolbar); §4 Key Decisions (page search is separate from the filter bar)) [spec v1.6 2026-07-28]</t>
+          <t>SV-8798 (S13-E1 (a collapsed filter bar keeps an active query applying and the search control stays in the toolbar); §4 Key Decisions (page search is separate from the filter bar)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr"/>
@@ -5741,12 +5949,14 @@
         <is>
           <t>1. The list request includes the active filter selections as request parameters (status values and customer identifiers).
 2. The request succeeds (HTTP 200).
-3. The response contains only work orders matching the filters - the filtering is done by the backend, not just hidden client-side.</t>
+3. The response contains only work orders matching the filters - the filtering is done by the backend, not just hidden client-side.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S2-R2, S3-R6).</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S2-R2; S3-R6 (backend view)) [spec v1.6 2026-07-28]</t>
+          <t>SV-8785 [epic] (S2-R2; S3-R6 (backend view)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr"/>
@@ -5789,12 +5999,14 @@
         <is>
           <t>1. One request carries both filters together (both statuses and the customer).
 2. The response returns customer A's Estimate and Approved work orders only.
-3. Customer B's work orders are absent - the customer filter and status filter both restrict the result, while the two statuses combine as either-or.</t>
+3. Customer B's work orders are absent - the customer filter and status filter both restrict the result, while the two statuses combine as either-or.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S2-R2, S3-R6, S8-R3).</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S2-R2; S3-R6; S8-R3 (backend view)) [spec v1.6 2026-07-28]</t>
+          <t>SV-8785 [epic] (S2-R2; S3-R6; S8-R3 (backend view)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr"/>
@@ -5837,12 +6049,14 @@
         <is>
           <t>1. The backend does not fail with a server error (no HTTP 5xx).
 2. The response is a normal, successful list response - the invalid value is ignored or simply matches nothing.
-3. Any still-valid filter values in the same request are applied normally.</t>
+3. Any still-valid filter values in the same request are applied normally.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S10-N1, S11-R3).</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S10-N1; S11-R3) [spec v1.6 2026-07-28]</t>
+          <t>SV-8785 [epic] (S10-N1; S11-R3) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr"/>
@@ -5885,12 +6099,14 @@
       <c r="G109" s="2" t="inlineStr">
         <is>
           <t>1. The backend responds gracefully - no HTTP 5xx / crash; either a normal (unfiltered or empty) list or a clean validation response.
-2. In the browser the page still loads without filters and without an error message, matching the malformed-URL requirement.</t>
+2. In the browser the page still loads without filters and without an error message, matching the malformed-URL requirement.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S11-N1).</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S11-N1) [spec v1.6 2026-07-28]</t>
+          <t>SV-8796 (S11-N1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr"/>
@@ -5933,12 +6149,14 @@
         <is>
           <t>1. The request succeeds (HTTP 200).
 2. The response contains an empty result set (zero work orders) - an empty match is a normal outcome, not an error.
-3. The page renders the no-results empty state from this response.</t>
+3. The page renders the no-results empty state from this response.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S8-R3, S2-N3).</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S8-R3; S2-N3) [spec v1.6 2026-07-28]</t>
+          <t>SV-8785 [epic] (S8-R3; S2-N3) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr"/>
@@ -5984,12 +6202,14 @@
           <t>1. Changing a filter sends a save (PUT) to the per-user page-preferences service carrying the page's state, and it succeeds (HTTP 200).
 2. On reload the page requests the saved state back (GET, HTTP 200) and applies it - the filters return without you redoing them.
 3. The second user does NOT receive the first user's saved state - each account's saved filters are isolated.
-4. Asking for a never-saved key returns success with an empty value, not an error page.</t>
+4. Asking for a never-saved key returns success with an empty value, not an error page.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S10-R2, S10-R3).</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Filters (no Jira epic) (S10-R2 (filters stored server-side against the user account; last write wins); S10-R3 (saved per user)) + tech plan 2026-07-29 s4-1.3 (GET/PUT per-user page preferences) [spec v1.6 2026-07-28]</t>
+          <t>SV-8795 (S10-R2 (filters stored server-side against the user account; last write wins); S10-R3 (saved per user)) + tech plan 2026-07-29 s4-1.3 (GET/PUT per-user page preferences) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr"/>

--- a/testrail-import/filters-v1-testrail-import.xlsx
+++ b/testrail-import/filters-v1-testrail-import.xlsx
@@ -4582,7 +4582,7 @@
 2. A 'Clear filters' control appears while at least one filter is active.
 3. Using it removes all active filters, the chips return to default and the full list comes back.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S12-R2, S7-R1/R3, S8-R1).</t>
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S12-R2, S7-R1/R3, S8-R1). The screen described above comes from the agreed design rather than that specification, and a product owner decision is still awaited.</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">

--- a/testrail-import/filters-v1-testrail-import.xlsx
+++ b/testrail-import/filters-v1-testrail-import.xlsx
@@ -3546,12 +3546,12 @@
           <t>1. On the very first visit the Estimates tab is the selected one, even though All is the FIRST tab in the row (order and default are different on purpose).
 2. After switching to All and returning, the All tab is selected - the app remembers your last-used tab per account.
 ---
-This is the expected behaviour as per epic SV-8785 and the engineering technical plan. No numbered requirement in the Filters specification version 1.6 covers this point yet.</t>
+This is the expected behaviour as per epic SV-8785 and a product owner decision dated 2026-08-04. No numbered requirement in the Filters specification version 1.6 covers this point. That decision is recorded in Branko's answers, in this file: https://docs.google.com/spreadsheets/d/1fkjdt9hoYSGv2MToXUFJ_4tTMzP7a7X2/edit</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>SV-8785 [epic] (no requirement in the ratified spec v1.6 - default/last-used tab is engineering-plan-only - confirmation requested); tech plan 2026-07-29 D10 (default tab = Estimates; last-used tab persists) [spec v1.6 2026-07-28]</t>
+          <t>SV-8785 [epic] (no requirement in spec v1.6 - default/last-used tab is not in the spec; RULED by Branko answers 2026-08-04 Q2 "A - it's fine"); tech plan 2026-07-29 D10 (default tab = Estimates; last-used tab persists) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
@@ -4219,12 +4219,12 @@
 2. The row scrolls horizontally - chips that do not fit are reachable by swiping.
 3. An arrow at the right-hand edge shows that the row can be scrolled. (This is what the design shows - if your screen looks different, write down what you actually see and carry on.)
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S12-R1). The screen described above comes from the agreed design rather than that specification, and a product owner decision is still awaited.</t>
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S12-R1). The screen described above comes from the agreed design rather than that specification, and the product owner approved it on 2026-08-04. That decision is recorded in Branko's answers, in this file: https://docs.google.com/spreadsheets/d/1fkjdt9hoYSGv2MToXUFJ_4tTMzP7a7X2/edit</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>SV-8797 (S12-R1) [spec v1.6 2026-07-28]</t>
+          <t>SV-8797 (S12-R1) [spec v1.6 2026-07-28]; Branko answers 2026-08-04 Q1 - single-filter sheet applies instantly with no Apply button; the combined All Filters sheet keeps its button</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
@@ -4269,12 +4269,12 @@
 2. It lists the five filters as expandable accordion rows, each with its icon, name and a down arrow: Status, Customer, Lead Technician, Service Advisor, Asset on site.
 3. A sticky blue 'Apply filters' button sits at the bottom of the sheet.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S12-R3). The screen described above comes from the agreed design rather than that specification, and a product owner decision is still awaited.</t>
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S12-R3). The screen described above comes from the agreed design rather than that specification, and the product owner approved it on 2026-08-04. That decision is recorded in Branko's answers, in this file: https://docs.google.com/spreadsheets/d/1fkjdt9hoYSGv2MToXUFJ_4tTMzP7a7X2/edit</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>SV-8797 (S12-R3) [spec v1.6 2026-07-28]</t>
+          <t>SV-8797 (S12-R3) [spec v1.6 2026-07-28]; Branko answers 2026-08-04 Q1 - single-filter sheet applies instantly with no Apply button; the combined All Filters sheet keeps its button</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr"/>
@@ -4322,12 +4322,12 @@
 2. After 'Apply filters' the sheet closes and the work order list shows only the ticked statuses.
 3. The reopened sheet's title shows the applied-filter count, for example 'All Filters (1)', and the Status accordion header is highlighted with the selected values ticked.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S12-R2, S12-R3, S2-R1). The screen described above comes from the agreed design rather than that specification, and a product owner decision is still awaited.</t>
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S12-R2, S12-R3, S2-R1). The screen described above comes from the agreed design rather than that specification, and the product owner approved it on 2026-08-04. That decision is recorded in Branko's answers, in this file: https://docs.google.com/spreadsheets/d/1fkjdt9hoYSGv2MToXUFJ_4tTMzP7a7X2/edit</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>SV-8785 [epic] (S12-R2; S12-R3; S2-R1) [spec v1.6 2026-07-28]</t>
+          <t>SV-8785 [epic] (S12-R2; S12-R3; S2-R1) [spec v1.6 2026-07-28]; Branko answers 2026-08-04 Q1 - single-filter sheet applies instantly with no Apply button; the combined All Filters sheet keeps its button</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr"/>
@@ -4336,7 +4336,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Mobile: tapping one chip opens its own sheet with an 'Apply filter' button</t>
+          <t>Mobile: tapping one chip opens its own sheet and applies in real time</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4362,23 +4362,25 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>1. Tap the Status chip (not All Filters).
-2. Read the sheet.
-3. Tick a status and tap the bottom button.</t>
+          <t>1. Tap the Status chip (not the 'All Filters' chip).
+2. Read the sheet that opens.
+3. Tick one status and watch the work order list.
+4. Untick it, then tick a different status, and watch the list again.</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>1. A bottom sheet opens for that single filter: its title row shows the filter's icon and name (for example 'Status') with a close (x) button - no accordion list of the other filters.
+          <t>1. A bottom sheet opens for that single filter: its title row shows the filter's icon and name (for example 'Status') with a close (x) button, and no accordion list of the other filters.
 2. The sheet shows only that filter's options (the nine status checkboxes plus 'Clear selection').
-3. The bottom button reads 'Apply filter' (singular); tapping it applies the selection and filters the list.
----
-This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S12-R2, S12-R3). The screen described above comes from the agreed design rather than that specification, and a product owner decision is still awaited.</t>
+3. There is no 'Apply filter' button. Ticking or unticking a status filters the work order list immediately, the same as on desktop, with no submit step.
+4. The chip's active state and value update live as the selection changes; closing the sheet with the x just dismisses it and keeps the applied filter.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S12-R2, S12-R3, S2-R6). Branko confirmed this on 2026-08-04 in his answers in this file: https://docs.google.com/spreadsheets/d/1fkjdt9hoYSGv2MToXUFJ_4tTMzP7a7X2/edit</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>SV-8797 (S12-R2; S12-R3) [spec v1.6 2026-07-28] ; individual-chip real-time per S12-R2 + tech-plan 2026-07-29; only the combined All Filters sheet is batch</t>
+          <t>SV-8797 (S12-R2; S12-R3; S2-R6) [spec v1.6 2026-07-28] ; individual-chip real-time per S12-R2 + S2-R6 + tech-plan 2026-07-29; only the combined All Filters sheet is batch; CONFIRMED by Branko answers 2026-08-04 Q1</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr"/>
@@ -4427,12 +4429,12 @@
 3. Removing a tag deselects just that customer.
 4. After 'Apply filters' the list shows only work orders of the remaining selected customers, and the sheet title counts the applied filters (for example 'All Filters (2)').
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S12-R2, S3-R2/R3/R5). The screen described above comes from the agreed design rather than that specification, and a product owner decision is still awaited.</t>
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S12-R2, S3-R2/R3/R5). The screen described above comes from the agreed design rather than that specification, and the product owner approved it on 2026-08-04. That decision is recorded in Branko's answers, in this file: https://docs.google.com/spreadsheets/d/1fkjdt9hoYSGv2MToXUFJ_4tTMzP7a7X2/edit</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>SV-8785 [epic] (S12-R2; S3-R2/R3/R5) [spec v1.6 2026-07-28]</t>
+          <t>SV-8785 [epic] (S12-R2; S3-R2/R3/R5) [spec v1.6 2026-07-28]; Branko answers 2026-08-04 Q1 - single-filter sheet applies instantly with no Apply button; the combined All Filters sheet keeps its button</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr"/>
@@ -4479,12 +4481,12 @@
 2. The Service Advisor row opens with a 'Search advisor' field and the advisor list.
 3. Applying a selection filters the work order list just like on desktop.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S12-R2, S4-R1, S5-R1). The screen described above comes from the agreed design rather than that specification, and a product owner decision is still awaited.</t>
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S12-R2, S4-R1, S5-R1). The screen described above comes from the agreed design rather than that specification, and the product owner approved it on 2026-08-04. That decision is recorded in Branko's answers, in this file: https://docs.google.com/spreadsheets/d/1fkjdt9hoYSGv2MToXUFJ_4tTMzP7a7X2/edit</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>SV-8785 [epic] (S12-R2; S4-R1; S5-R1) [spec v1.6 2026-07-28]</t>
+          <t>SV-8785 [epic] (S12-R2; S4-R1; S5-R1) [spec v1.6 2026-07-28]; Branko answers 2026-08-04 Q1 - single-filter sheet applies instantly with no Apply button; the combined All Filters sheet keeps its button</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr"/>
@@ -4531,12 +4533,12 @@
 2. Only one option can be selected at a time.
 3. After applying, the list shows only work orders matching the chosen on-site state.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S12-R2, S6-R1/R2/R3). The screen described above comes from the agreed design rather than that specification, and a product owner decision is still awaited.</t>
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S12-R2, S6-R1/R2/R3). The screen described above comes from the agreed design rather than that specification, and the product owner approved it on 2026-08-04. That decision is recorded in Branko's answers, in this file: https://docs.google.com/spreadsheets/d/1fkjdt9hoYSGv2MToXUFJ_4tTMzP7a7X2/edit</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>SV-8785 [epic] (S12-R2; S6-R1/R2/R3) [spec v1.6 2026-07-28]</t>
+          <t>SV-8785 [epic] (S12-R2; S6-R1/R2/R3) [spec v1.6 2026-07-28]; Branko answers 2026-08-04 Q1 - single-filter sheet applies instantly with no Apply button; the combined All Filters sheet keeps its button</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr"/>
@@ -4582,12 +4584,12 @@
 2. A 'Clear filters' control appears while at least one filter is active.
 3. Using it removes all active filters, the chips return to default and the full list comes back.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S12-R2, S7-R1/R3, S8-R1). The screen described above comes from the agreed design rather than that specification, and a product owner decision is still awaited.</t>
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S12-R2, S7-R1/R3, S8-R1). The screen described above comes from the agreed design rather than that specification, and the product owner approved it on 2026-08-04. That decision is recorded in Branko's answers, in this file: https://docs.google.com/spreadsheets/d/1fkjdt9hoYSGv2MToXUFJ_4tTMzP7a7X2/edit</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>SV-8785 [epic] (S12-R2; S7-R1/R3; S8-R1) [spec v1.6 2026-07-28]</t>
+          <t>SV-8785 [epic] (S12-R2; S7-R1/R3; S8-R1) [spec v1.6 2026-07-28]; Branko answers 2026-08-04 Q1 - single-filter sheet applies instantly with no Apply button; the combined All Filters sheet keeps its button</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr"/>
@@ -4742,19 +4744,19 @@
 5. The Credits tab shows three filter buttons: Vendor, Date and Processed by.
 6. Purchase Orders shows four filter buttons: Vendor, Status, Date and Ordered by.
 7. Vendor Invoices shows four filter buttons: Vendor, Invoice date, Date received and Received by.
-8. The Vendors list page shows two filter buttons: Vendor and State/Province. Note: the developers have not been given a design for the Vendors page filters yet, so this page may not have them — write down what you actually see instead of failing the whole test.
+8. The Vendors list page shows two filter buttons: Vendor and State/Province.
 9. On every page above, each filter button shows a small icon, the filter name and a down arrow.
 10. Every Parts list page also shows a Search (magnifier) icon and a filter icon in the toolbar; some pages (for example Inventory) also show a column/layout toggle icon.
 11. Every filter button shown above is a working filter on that page - none of them is display-only.
 12. The choices inside each filter come from your own shop's data (for example your real vendors or categories), so there is no fixed list to compare against - check that the choices you see match the data in your shop.
 13. Still to check on the live build: what the filter icon and the column/layout icon do (the written description does not cover the toolbar icons).
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (§2, §4), which covers this area in its overview and key decisions only. The detailed behaviour above follows a later product owner decision dated 2026-07-31.</t>
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (§2, §4), which covers this area in its overview and key decisions only. The detailed behaviour above follows a later product owner decision dated 2026-08-04. That decision is recorded in Branko's answers, in this file: https://docs.google.com/spreadsheets/d/1fkjdt9hoYSGv2MToXUFJ_4tTMzP7a7X2/edit</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>SV-8785 [epic] (spec v1.6 §2 Feature Overview -&gt; Parts Filters; §4 Key Decisions -&gt; "Context-specific filter sets on Parts and Reports" + "Multi-select where it makes sense"); Branko answers 2026-07-31 Q2/Q3/Q5/Q7; Figma 11884-16885</t>
+          <t>SV-8785 [epic] (spec v1.6 §2 Parts Filters; §4 context-specific filter sets + multi-select); Branko answers 2026-07-31 Q2/Q3/Q5/Q7 + 2026-08-04 Q3 (Vendors design exists Figma 11903-10461) + Q8 (Part Sales chips); Figma 11884-16885</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr"/>
@@ -4958,12 +4960,12 @@
 2. Every choice each of those filters offered before is still available inside the new button.
 3. If any filter or choice is missing, write down exactly which page, which filter and which choice - that is a bug worth reporting.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (§2), which covers this area in its overview and key decisions only. The detailed behaviour above follows a later product owner decision dated 2026-07-31.</t>
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (§2), which covers this area in its overview and key decisions only. The detailed behaviour above follows a later product owner decision dated 2026-08-04. That decision is recorded in Branko's answers, in this file: https://docs.google.com/spreadsheets/d/1fkjdt9hoYSGv2MToXUFJ_4tTMzP7a7X2/edit</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>SV-8785 [epic] (spec v1.6 §2 Parts Filters + Reports Filters); Branko answers 2026-07-31 Q3 ("support all the filters we have right now in the app as well as all choices per filter"); tech plan 2026-07-29 rollout rule</t>
+          <t>SV-8785 [epic] (spec v1.6 §2 Parts Filters + Reports Filters); Branko answers 2026-07-31 Q3 + 2026-08-04 Q8 ("we should have all filters we support now per each page plus we should add new ones"); tech plan 2026-07-29 rollout rule</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr"/>
@@ -5144,12 +5146,12 @@
 2. The choices inside each filter come from your own shop's data (for example your real vendors or categories), so there is no fixed list to compare against - check that the choices you see match the data in your shop.
 3. Write down the choices you actually see behind each of these six buttons. They have not been written down anywhere yet, so your list becomes the record.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (§2, §4), which covers this area in its overview and key decisions only. The detailed behaviour above follows a later product owner decision dated 2026-07-31.</t>
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (§2, §4), which covers this area in its overview and key decisions only. The detailed behaviour above follows a later product owner decision dated 2026-07-31. Branko confirmed this on 2026-08-04 in his answers in this file: https://docs.google.com/spreadsheets/d/1fkjdt9hoYSGv2MToXUFJ_4tTMzP7a7X2/edit</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>SV-8785 [epic] (spec v1.6 §2 Reports Filters; §4 "Multi-select where it makes sense"); Branko answers 2026-07-31 Q3/Q5 + Q4 (pointer only - the 6 new types are not enumerated in v1.6; see DELTAS.md F1); Figma 11903-10573</t>
+          <t>SV-8785 [epic] (spec v1.6 §2 Reports Filters; §4 "Multi-select where it makes sense"); Branko answers 2026-07-31 Q3/Q5 + 2026-08-04 Q8 ("We do not have list of all filter items" - confirms no option list exists); Figma 11903-10573</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr"/>

--- a/testrail-import/filters-v1-testrail-import.xlsx
+++ b/testrail-import/filters-v1-testrail-import.xlsx
@@ -532,9 +532,9 @@
 &lt;li&gt;A filter bar is visible directly below the tab row and above the work order table.&lt;/li&gt;
 &lt;li&gt;The filter bar is shown by default (expanded) without having to turn anything on.&lt;/li&gt;
 &lt;/ol&gt;
-Known issue: on the build tested the filter buttons sit on the same row as the tabs instead of on their own row below them. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8843
----
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S1-R1).</t>
+Known and accepted: on the build tested the filter buttons sit on the same row as the tabs instead of on their own row below them. The product behaves this way on purpose for now. Do not raise this as a new problem.
+---
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S1-R1).</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -585,7 +585,7 @@
 2. Each chip shows the filter name and a down arrow (chevron) indicating it opens a dropdown.
 3. Each chip shows only the filter name and the arrow - there is no picture icon in front of the name.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S1-R2, S1-R3). Note: the design frame also draws a small picture icon in front of each filter name; the specification asks only for the name and the arrow, and the build matches the specification, so this test follows the specification and the build.</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S1-R2, S1-R3). Note: the design frame also draws a small picture icon in front of each filter name; the specification asks only for the name and the arrow, and the build matches the specification, so this test follows the specification and the build.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -635,7 +635,7 @@
 2. The Customer, Lead Technician, Service Advisor and Asset on Site chips are all displayed and usable.
 3. The Status chip is not shown on this tab at all - only four chips appear.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S1-N1, S9-R2). Note: an earlier answer of 2026-07-17 and the design frame both show the Status button greyed out and pre-filled on this tab; the specification and the build both hide it, and the specification is the newer source, so this test follows the specification and the build.</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S1-N1, S9-R2). Note: an earlier answer of 2026-07-17 and the design frame both show the Status button greyed out and pre-filled on this tab; the specification and the build both hide it, and the specification is the newer source, so this test follows the specification and the build.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -696,7 +696,7 @@
 &lt;li&gt;A 'Clear Selection' action is shown at the bottom of the dropdown.&lt;/li&gt;
 &lt;/ol&gt;
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-R1, S2-R4).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-R1, S2-R4).</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
 2. The table updates immediately to show only work orders in the selected status - there is no confirm or apply button on desktop.
 3. Work orders in other statuses are no longer listed.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-R2, S2-R3, S2-R6).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-R2, S2-R3, S2-R6).</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -800,9 +800,8 @@
 2. The table shows work orders whose status matches ANY of the ticked statuses (both Estimate and Approved rows appear).
 3. Work orders in statuses that are not ticked are hidden.
 4. There is no limit on how many statuses you can tick.
-Known issue: on the build tested the dropdown closes as soon as you tick one value, so to pick a second value you have to open the chip again. Everything else in this test still works. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8824
----
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-R2).</t>
+---
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-R2).</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -853,9 +852,8 @@
           <t>1. All status checkboxes become unticked.
 2. The Status filter is removed and the table returns to showing work orders of every status.
 3. Only the Status filter is affected - any other active filters stay applied.
-Known issue: on the build tested the dropdown closes as soon as you tick one value, so to pick a second value you have to open the chip again. Everything else in this test still works. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8824
----
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-R4, S8-R2).</t>
+---
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-R4, S8-R2).</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -905,9 +903,8 @@
           <t>1. The dropdown closes.
 2. The ticked statuses stay selected - the Status chip stays in its active state showing the selection.
 3. The table stays filtered by the selected statuses.
-Known issue: on the build tested the dropdown closes as soon as you tick one value, so to pick a second value you have to open the chip again. Everything else in this test still works. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8824
----
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-R5).</t>
+---
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-R5).</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -959,7 +956,7 @@
 2. An empty state is displayed saying no results were found for the current filters (see the Empty State cases for its full content).
 3. The app does not show an error.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-N3, S8-R3).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-N3, S8-R3).</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1013,7 +1010,7 @@
 3. Imported cannot be combined with other statuses - selecting it works alone.
 4. Unticking Imported re-enables the other chips and the normal list returns.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-R7, S2-N4).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-R7, S2-N4).</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1074,7 +1071,7 @@
 &lt;li&gt;A 'Clear Selection' action is shown at the bottom of the panel.&lt;/li&gt;
 &lt;/ol&gt;
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-R1).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-R1).</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1125,7 +1122,7 @@
 2. Customers that do not match are removed from the list.
 3. Deleting the text brings the full list back.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-R2).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-R2).</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1185,9 +1182,8 @@
 &lt;li&gt;Long customer names on tags are shortened with an ellipsis (for example 'Texas Truck And Aut...').&lt;/li&gt;
 &lt;li&gt;You can keep selecting as many customers as needed - there is no selection limit.&lt;/li&gt;
 &lt;/ol&gt;
-Known issue: on the build tested the dropdown closes as soon as you tick one value, so to pick a second value you have to open the chip again. Everything else in this test still works. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8824
----
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-R3, S3-R4).</t>
+---
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-R3, S3-R4).</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1239,7 +1235,7 @@
 3. The other selected customers keep their tags and checkmarks.
 4. The table updates to no longer include that customer's work orders.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-R5).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-R5).</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1289,9 +1285,8 @@
           <t>1. The table shows only work orders whose customer is one of the two selected customers.
 2. Work orders belonging to any other customer are hidden.
 3. The table updates in real time as you make the selections (no apply button on desktop).
-Known issue: on the build tested the dropdown closes as soon as you tick one value, so to pick a second value you have to open the chip again. Everything else in this test still works. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8824
----
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-R6, S2-R6).</t>
+---
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-R6, S2-R6).</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1344,7 +1339,7 @@
 3. The Customer filter is removed and the table shows work orders of all customers again.
 4. Other active filters (if any) are not affected.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-R7, S8-R2).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-R7, S8-R2).</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1394,9 +1389,8 @@
           <t>1. The dropdown closes when you click outside it.
 2. The Customer chip stays in the active (blue) state showing the selection and the table stays filtered.
 3. When reopened, the selected customers' tags are still visible in the input area.
-Known issue: on the build tested the dropdown closes as soon as you tick one value, so to pick a second value you have to open the chip again. Everything else in this test still works. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8824
----
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-R8).</t>
+---
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-R8).</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1454,7 +1448,7 @@
 &lt;li&gt;Clearing the search text brings the customer list back.&lt;/li&gt;
 &lt;/ol&gt;
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-N1).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-N1).</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1506,7 +1500,7 @@
 2. After selecting only that customer, the table shows no rows and the filtered empty state is displayed.
 3. No error is shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-E1, S3-N2, S8-R3).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-E1, S3-N2, S8-R3).</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1566,7 +1560,7 @@
 &lt;li&gt;A 'Clear Selection' action is shown at the bottom.&lt;/li&gt;
 &lt;/ol&gt;
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S4-R1).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S4-R1).</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1615,7 +1609,7 @@
           <t>1. The technician list narrows to only the names matching what you typed.
 2. Deleting the text brings the full list back.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S4-R2).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S4-R2).</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1666,9 +1660,8 @@
 2. The table shows only work orders where one of the selected technicians is assigned as the LEAD technician.
 3. A work order where the technician is assigned only in a non-lead role does not appear.
 4. The table updates in real time as you select.
-Known issue: on the build tested the dropdown closes as soon as you tick one value, so to pick a second value you have to open the chip again. Everything else in this test still works. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8824
----
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S4-R3, S4-R4).</t>
+---
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S4-R3, S4-R4).</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1719,7 +1712,7 @@
 2. The Lead Technician filter no longer restricts the table.
 3. Other active filters are not affected.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S4-R5, S8-R2).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S4-R5, S8-R2).</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1767,9 +1760,8 @@
         <is>
           <t>1. The dropdown closes.
 2. The selection stays applied - the chip stays active and the table stays filtered.
-Known issue: on the build tested the dropdown closes as soon as you tick one value, so to pick a second value you have to open the chip again. Everything else in this test still works. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8824
----
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S4-R6).</t>
+---
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S4-R6).</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1819,7 +1811,7 @@
           <t>1. The table shows no rows and the filtered empty state is displayed.
 2. No error is shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S4-N1, S8-R3).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S4-N1, S8-R3).</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1870,7 +1862,7 @@
           <t>1. The deactivated technician is NOT shown in the filter list.
 2. Active technicians are still listed normally.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S4-E1).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S4-E1).</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1930,7 +1922,7 @@
 &lt;li&gt;A 'Clear Selection' action is shown at the bottom.&lt;/li&gt;
 &lt;/ol&gt;
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S5-R1).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S5-R1).</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1979,7 +1971,7 @@
           <t>1. The advisor list narrows to only the names matching what you typed.
 2. Deleting the text brings the full list back.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S5-R2).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S5-R2).</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2029,9 +2021,8 @@
           <t>1. Selected advisors show a checkmark on the row, and as a small removable tag above the list in the list.
 2. The table shows only work orders assigned to any of the selected advisors.
 3. The table updates in real time as you select.
-Known issue: on the build tested the dropdown closes as soon as you tick one value, so to pick a second value you have to open the chip again. Everything else in this test still works. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8824
----
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S5-R3, S5-R4).</t>
+---
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S5-R3, S5-R4).</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2082,7 +2073,7 @@
 2. The Service Advisor filter no longer restricts the table.
 3. Other active filters are not affected.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S5-R5, S8-R2).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S5-R5, S8-R2).</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2130,9 +2121,8 @@
         <is>
           <t>1. The dropdown closes.
 2. The selection stays applied - the chip stays active and the table stays filtered.
-Known issue: on the build tested the dropdown closes as soon as you tick one value, so to pick a second value you have to open the chip again. Everything else in this test still works. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8824
----
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S5-R6).</t>
+---
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S5-R6).</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2182,7 +2172,7 @@
           <t>1. The table shows no rows and the filtered empty state is displayed.
 2. No error is shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S5-N1, S8-R3).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S5-N1, S8-R3).</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2233,7 +2223,7 @@
           <t>1. The deactivated advisor is NOT shown in the filter list.
 2. Active advisors are still listed normally.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S5-E1).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S5-E1).</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2284,7 +2274,7 @@
 3. A 'Clear Selection' action is shown at the bottom.
 4. It is a dropdown (like the other filters), not an on/off toggle.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S6-R1).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S6-R1).</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2334,7 +2324,7 @@
           <t>1. The table shows only work orders whose asset is currently on site.
 2. Work orders whose asset is not on site are hidden.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S6-R2).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S6-R2).</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2385,7 +2375,7 @@
 2. The table switches to showing only the not-on-site work orders.
 3. The chip shows the currently selected value.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S6-R3).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S6-R3).</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2435,7 +2425,7 @@
 2. The table shows work orders regardless of on-site status again.
 3. Other active filters are not affected.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S6-R4, S8-R2).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S6-R4, S8-R2).</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2483,9 +2473,8 @@
         <is>
           <t>1. The dropdown closes.
 2. The Yes selection stays applied - the chip stays active and the table stays filtered.
-Known issue: on the build tested the dropdown closes as soon as you tick one value, so to pick a second value you have to open the chip again. Everything else in this test still works. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8824
----
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S6-R5).</t>
+---
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S6-R5).</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2535,7 +2524,7 @@
           <t>1. The table shows no rows and the filtered empty state is displayed.
 2. No error is shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S6-N1, S8-R3).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S6-N1, S8-R3).</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2587,7 +2576,7 @@
 2. Every work order with the asset on site is excluded.
 3. The chip shows the active No selection.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S6-R2).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S6-R2).</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2636,9 +2625,8 @@
           <t>1. The Status chip changes to an active/highlighted look (blue pill).
 2. The chip displays the selected value (for example 'Status: Estimate').
 3. The other chips stay in their default state.
-Known issue: on the build tested the dropdown closes as soon as you tick one value, so to pick a second value you have to open the chip again. Everything else in this test still works. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8824
----
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S7-R1).</t>
+---
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S7-R1).</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2687,7 +2675,7 @@
           <t>1. The chip lists the selected values starting with the first one and shortens the label when it gets too long (the design shows 'Status: Estimate, In progress, Approved...').
 2. The chip stays a single compact pill - it does not grow to show every value in full.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S7-R2).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S7-R2).</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2739,7 +2727,7 @@
 2. As soon as one filter is active, a blue 'Clear Filters' link appears at the right end of the chip row.
 3. When the last active filter is removed, 'Clear Filters' disappears again.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S7-R3, S7-N1, S8-N1).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S7-R3, S7-N1, S8-N1).</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2792,7 +2780,7 @@
 3. The table shows the full unfiltered list again (no text is in the page Search box, so nothing else is narrowing it).
 4. The 'Clear Filters' link disappears.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S8-R1, S13-R13).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S8-R1, S13-R13).</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2843,7 +2831,7 @@
 2. The Customer filter stays selected and active (blue) and keeps filtering the table.
 3. 'Clear Filters' remains visible because a filter is still active.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S8-R2).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S8-R2).</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2895,7 +2883,7 @@
 2. Customer A's Approved work order is hidden (wrong status) and customer B's Estimate work order is hidden (wrong customer) - each additional filter narrows the result further.
 3. Both chips are in the active state and 'Clear Filters' is visible.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S8-R3).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S8-R3).</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2946,7 +2934,7 @@
 2. The work order table moves up and uses the reclaimed vertical space.
 3. The filter icon shows a pressed/active look while the bar is collapsed.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S1-R4, S1-R5).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S1-R4, S1-R5).</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2996,9 +2984,9 @@
           <t>1. The filter bar reappears below the tab row.
 2. The previously selected filters are still shown on their chips in the active (blue) state - nothing was lost while collapsed.
 3. The 'Clear Filters' link is still shown at the right end of the chip row.
-Known issue: on the build tested collapsing the bar does not move the table up, because the buttons share the tab row. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8843
----
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S1-R6).</t>
+Known and accepted: on the build tested collapsing the bar does not move the table up, because the buttons share the tab row. The product behaves this way on purpose for now. Do not raise this as a new problem.
+---
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S1-R6).</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3049,7 +3037,7 @@
           <t>1. After step 2 the filter bar is still collapsed (your choice was remembered).
 2. After step 4 the filter bar is expanded again when you return - whichever state you left it in is restored.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S1-R7, S10-R1).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S1-R7, S10-R1).</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3099,7 +3087,7 @@
           <t>1. After step 1 the filter icon shows no special indicator (only its normal pressed look).
 2. After step 3 the filter icon shows a visual indicator (filters icon in primary blue) signalling that active filters are in effect while the bar is hidden.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S7-R4, S7-N2).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S7-R4, S7-N2).</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3149,7 +3137,7 @@
           <t>1. The table content does not change when the bar collapses - it still shows only the work orders matching the active filters.
 2. Hiding the bar only hides the chips; it does not remove or pause the filtering.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S7-R5).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S7-R5).</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3199,9 +3187,9 @@
           <t>1. The table body is replaced by an empty state (not just a bare empty grid).
 2. The empty state shows a message indicating no results were found for the current filters.
 3. No error message or broken layout appears.
-Known issue: when only a search is active the message still says "filters" and the only link offered is Clear Filters. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8847
----
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S8-R3).</t>
+Known and accepted: when only a search is active the message still says "filters" and the only link offered is Clear Filters. The product behaves this way on purpose for now. Do not raise this as a new problem.
+---
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S8-R3).</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3252,9 +3240,9 @@
           <t>1. The empty state includes a prompt or link to clear the filters.
 2. Clicking it removes the active filters and the full work order list is shown again (with no text in the Search box, nothing else is narrowing the list).
 3. The chips return to their default state.
-Known issue: the empty screen offers no way to clear the search on its own. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8847
----
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S8-R4, S8-R5).</t>
+Known and accepted: the empty screen offers no way to clear the search on its own. The product behaves this way on purpose for now. Do not raise this as a new problem.
+---
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S8-R4, S8-R5).</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3308,7 +3296,7 @@
 3. Clearing the search brings back the list as narrowed by the filter only - the filter is still on.
 4. Clearing the filters leaves your typed word in the box and still applied - each is cleared on its own without wiping the other.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S8-R3, S8-R4, S8-R5, S13-N1, S13-N2).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S8-R3, S8-R4, S8-R5, S13-N1, S13-N2).</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3357,7 +3345,7 @@
           <t>1. All five chips are shown: Status, Customer, Lead Technician, Service Advisor, Asset on Site.
 2. Each chip opens its dropdown and can be used.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S9-R1).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S9-R1).</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3411,7 +3399,7 @@
 2. Customer, Lead Technician, Service Advisor and Asset on Site chips are shown and usable.
 3. After step 4 the table shows only that customer's ESTIMATE work orders - the customer filter narrows the pre-filtered Estimates list.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S9-R2, S2-N1). Note: an earlier answer of 2026-07-17 and the design frame both show the Status button greyed out and pre-filled on this tab; the specification and the build both hide it, and the specification is the newer source, so this test follows the specification and the build.</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S9-R2, S2-N1). Note: an earlier answer of 2026-07-17 and the design frame both show the Status button greyed out and pre-filled on this tab; the specification and the build both hide it, and the specification is the newer source, so this test follows the specification and the build.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3465,7 +3453,7 @@
 2. Customer, Lead Technician, Service Advisor and Asset on Site chips are shown and usable.
 3. After step 4 the table shows only that customer's COMPLETE work orders.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S9-R3, S2-N2). Note: an earlier answer of 2026-07-17 and the design frame both show the Status button greyed out and pre-filled on this tab; the specification and the build both hide it, and the specification is the newer source, so this test follows the specification and the build.</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S9-R3, S2-N2). Note: an earlier answer of 2026-07-17 and the design frame both show the Status button greyed out and pre-filled on this tab; the specification and the build both hide it, and the specification is the newer source, so this test follows the specification and the build.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3517,7 +3505,7 @@
 2. The table only ever shows work orders assigned to you (the tab's own scope stays).
 3. After step 2 it shows only YOUR work orders in the ticked status - the filters narrow the user-scoped list, they do not widen it to other users' work orders.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S9-R4).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S9-R4).</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3568,7 +3556,7 @@
 2. Back on the All tab the Status chip reappears with the SAME selection (Approved) still applied - the selection was retained in memory, not lost.
 3. The Customer selection is unchanged throughout.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S9-R5, S9-N1, S9-R2).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S9-R5, S9-N1, S9-R2).</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3618,7 +3606,7 @@
           <t>1. On the very first visit the Estimates tab is the selected one, even though All is the FIRST tab in the row (order and default are different on purpose).
 2. After switching to All and returning, the All tab is selected - the app remembers your last-used tab per account.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3679,8 +3667,9 @@
 &lt;/ol&gt;
 &lt;hr /&gt;
 &lt;p&gt;This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S10-R1, S1-R7).&lt;/p&gt;
----
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S10-R1, S1-R7).</t>
+Known issue: on the build tested the Customer, Lead Technician and Service Advisor buttons come back switched on but WITHOUT the name of the value you picked - the button reads just "Customer" instead of "Customer: Iibay Landscaping". The list is still filtered correctly. The Status and Asset on Site buttons keep their value. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8871
+---
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S10-R1, S1-R7).</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3734,7 +3723,7 @@
 2. After closing the browser completely and signing back in (step 5) the same filter selections are still applied - the app remembers your filters for you permanently, not just for one browser session.
 3. The same filter selections are applied on the other computer too - the filters are saved to your account, not to one computer or browser (to confirm live once built).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S10-R2, S10-R3, S10-R1).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S10-R2, S10-R3, S10-R1).</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3784,7 +3773,7 @@
           <t>1. User B does not see user A's filters - user B's page opens with user B's own (or no) filters.
 2. User B's new filter does not change what user A sees; each user keeps their own saved filter state.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S10-R3).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S10-R3).</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3834,8 +3823,9 @@
           <t>1. The deleted customer is silently ignored - no error or warning appears.
 2. The Customer filter now reflects only the still-valid selection (the real customer).
 3. The table is filtered by the remaining valid selection only.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S10-N1).</t>
+Known issue: on the build tested the deleted customer is hidden from the dropdown but is STILL used to filter the table - the address bar and the request to the server both still carry it. So step 3 above is expected to fail. It is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8832
+---
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S10-N1).</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3887,7 +3877,7 @@
 2. Returning to the first view restores that view's own selections.
 3. Report tabs likewise keep separate filter choices, each remembered and restored on its own tab.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S10-R4).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S10-R4).</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3936,7 +3926,7 @@
           <t>1. The old saved choices appear in the new filter bar on the first visit - the update does not lose them (old status choices show in the Status chip, the old asset-here choice shows as Asset on Site: Yes, the old My-Work-Orders toggle maps to the My Work Orders tab, columns and sorting stay).
 2. Those carried-over choices are now saved to the account: the other computer shows them too.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S10-R2).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S10-R2).</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -3986,7 +3976,7 @@
           <t>1. After step 1 the URL changes to include the active filter state.
 2. After step 3 the filter part of the URL is removed again.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S11-R1).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S11-R1).</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4035,9 +4025,9 @@
           <t>1. The page opens with the same filters already applied - chips active with the same values.
 2. The table is already filtered accordingly on load (no need to re-apply anything).
 3. The same works from a saved bookmark.
-Known issue: on a phone-sized screen a link carrying filters shows the buttons as on but lists the wrong work orders. On a desktop screen it works. Until it is fixed the phone half of this test is expected to fail - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8845
----
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S11-R2).</t>
+Known issue: two points on this test are expected to fail on the build tested. On a phone-sized screen a link carrying filters shows the buttons as on but lists the wrong work orders (ticket: https://shopview.atlassian.net/browse/SV-8845). And on a desktop screen a Customer, Lead Technician or Service Advisor button opened from a link comes back switched on but without the name of the value, so it reads just "Customer" (ticket: https://shopview.atlassian.net/browse/SV-8871). The list itself is filtered correctly on desktop. Both are already reported.
+---
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S11-R2).</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4089,7 +4079,7 @@
 3. The table reflects only the valid filter.
 Known issue: a value in the address bar that no longer exists is still sent to the server, so you get an empty list instead of the list without that value. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8832
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S11-R3).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S11-R3).</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4141,7 +4131,7 @@
 3. No error message or broken page appears.
 Known issue: a broken address is not fully ignored - a wrong tab value can switch the tab and a bad customer value is still sent to the server. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8832
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S11-N1).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S11-N1).</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4199,7 +4189,7 @@
 5. It also empties the Search box and removes your typed text - the search is not something that gets saved, so there is nothing to bring back.
 6. Returning normally later still shows your own saved filters, untouched by the link visit.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S11-R6, S11-R7, S11-R8).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S11-R6, S11-R7, S11-R8).</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4254,7 +4244,7 @@
 3. When you open the shared link, 'Back To My Saved Filters' does appear.
 4. After you click it and you are back on your own view, the option disappears again.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S11-N3, S11-R7).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S11-N3, S11-R7).</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4305,7 +4295,7 @@
 3. An arrow at the right-hand edge shows that the row can be scrolled. (This is what the design shows - if your screen looks different, write down what you actually see and carry on.)
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour. The question is open as SV-8825 (https://shopview.atlassian.net/browse/SV-8825). Branko answered our sheet on 2026-08-04 saying a single filter window on a phone applies straight away with no Apply button, which is what the build does; hours later he added a new rule to the specification saying a phone should only apply when you tap an "Apply filters" button. Both come from him on the same day, so we are not choosing between them. His answers are in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R1). The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R1). The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4356,7 +4346,7 @@
 3. A sticky blue 'Apply filters' button sits at the bottom of the sheet.
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour. The question is open as SV-8825 (https://shopview.atlassian.net/browse/SV-8825). Branko answered our sheet on 2026-08-04 saying a single filter window on a phone applies straight away with no Apply button, which is what the build does; hours later he added a new rule to the specification saying a phone should only apply when you tap an "Apply filters" button. Both come from him on the same day, so we are not choosing between them. His answers are in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R3). The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R3). The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4410,7 +4400,7 @@
 3. The reopened sheet's title shows the applied-filter count, for example 'All Filters (1)', and the Status accordion header is highlighted with the selected values ticked.
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour. The question is open as SV-8825 (https://shopview.atlassian.net/browse/SV-8825). Branko answered our sheet on 2026-08-04 saying a single filter window on a phone applies straight away with no Apply button, which is what the build does; hours later he added a new rule to the specification saying a phone should only apply when you tap an "Apply filters" button. Both come from him on the same day, so we are not choosing between them. His answers are in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R2, S12-R3, S2-R1). The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R2, S12-R3, S2-R1). The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4464,7 +4454,7 @@
 4. The chip's active state and value update live as the selection changes; closing the sheet with the x just dismisses it and keeps the applied filter.
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour. The question is open as SV-8825 (https://shopview.atlassian.net/browse/SV-8825). Branko answered our sheet on 2026-08-04 saying a single filter window on a phone applies straight away with no Apply button, which is what the build does; hours later he added a new rule to the specification saying a phone should only apply when you tap an "Apply filters" button. Both come from him on the same day, so we are not choosing between them. His answers are in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R2, S12-R3, S2-R6). The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R2, S12-R3, S2-R6). The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -4527,7 +4517,7 @@
 &lt;/ol&gt;
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour. The question is open as SV-8825 (https://shopview.atlassian.net/browse/SV-8825). Branko answered our sheet on 2026-08-04 saying a single filter window on a phone applies straight away with no Apply button, which is what the build does; hours later he added a new rule to the specification saying a phone should only apply when you tap an "Apply filters" button. Both come from him on the same day, so we are not choosing between them. His answers are in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R2, S3-R2). The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R2, S3-R2). The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4580,7 +4570,7 @@
 3. Applying a selection filters the work order list just like on desktop.
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour. The question is open as SV-8825 (https://shopview.atlassian.net/browse/SV-8825). Branko answered our sheet on 2026-08-04 saying a single filter window on a phone applies straight away with no Apply button, which is what the build does; hours later he added a new rule to the specification saying a phone should only apply when you tap an "Apply filters" button. Both come from him on the same day, so we are not choosing between them. His answers are in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R2, S4-R1, S5-R1). The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R2, S4-R1, S5-R1). The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -4633,7 +4623,7 @@
 3. After applying, the list shows only work orders matching the chosen on-site state.
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour. The question is open as SV-8825 (https://shopview.atlassian.net/browse/SV-8825). Branko answered our sheet on 2026-08-04 saying a single filter window on a phone applies straight away with no Apply button, which is what the build does; hours later he added a new rule to the specification saying a phone should only apply when you tap an "Apply filters" button. Both come from him on the same day, so we are not choosing between them. His answers are in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R2, S6-R1). The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R2, S6-R1). The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4685,7 +4675,7 @@
 3. Using it removes all active filters, the chips return to default and the full list comes back.
 Known issue: on a phone there is no Clear Filters button at all while filters are on. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8846
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R2, S7-R1, S8-R1).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R2, S7-R1, S8-R1).</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4734,7 +4724,7 @@
           <t>1. There is no filter-bar collapse/expand (filter icon) toggle on mobile.
 2. The filter chip row is always visible on the mobile Work Orders page.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R4).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R4).</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4786,7 +4776,7 @@
 Known issue: on a phone a link carrying filters shows the buttons as on but lists the wrong work orders. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8845
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour. The question is open as SV-8825 (https://shopview.atlassian.net/browse/SV-8825). Branko answered our sheet on 2026-08-04 saying a single filter window on a phone applies straight away with no Apply button, which is what the build does; hours later he added a new rule to the specification saying a phone should only apply when you tap an "Apply filters" button. Both come from him on the same day, so we are not choosing between them. His answers are in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-N1, S8-R3). The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-N1, S8-R3). The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4855,7 +4845,7 @@
 13. Still to check on the live build: what the filter icon and the column/layout icon do (the written description does not cover the toolbar icons).
 Not built yet on the build tested: a filter bar exists on Inventory, Part Sales, Catalog and Returns, but Purchase Orders, Vendor Invoices and Vendors have no filter bar at all. If the filter bar is missing on the view you are testing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4909,7 +4899,7 @@
 4. As soon as you tick a choice the list below narrows to matching parts straight away, with no Apply button to press; Clear Selection puts the list back.
 Not built yet on the build tested: a filter bar exists on Inventory, Part Sales, Catalog and Returns, but Purchase Orders, Vendor Invoices and Vendors have no filter bar at all. If the filter bar is missing on the view you are testing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4961,7 +4951,7 @@
 3. The list narrows as soon as you pick the value - there is no Apply or Search button to press. Every filter button on every Parts page works this way.
 Not built yet on the build tested: a filter bar exists on Inventory, Part Sales, Catalog and Returns, but Purchase Orders, Vendor Invoices and Vendors have no filter bar at all. If the filter bar is missing on the view you are testing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5013,7 +5003,7 @@
 3. A Clear Filters button appears in the filter bar while any filter is set, and using it clears them all at once - exactly as it works on the Work Orders page.
 Not built yet on the build tested: a filter bar exists on Inventory, Part Sales, Catalog and Returns, but Purchase Orders, Vendor Invoices and Vendors have no filter bar at all. If the filter bar is missing on the view you are testing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5068,7 +5058,7 @@
 3. If any filter or choice is missing, write down exactly which page, which filter and which choice - that is a bug worth reporting.
 Not built yet on the build tested: a filter bar exists on Inventory, Part Sales, Catalog and Returns, but Purchase Orders, Vendor Invoices and Vendors have no filter bar at all. If the filter bar is missing on the view you are testing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5154,7 +5144,7 @@
 24. Still to check on the live build: the real columns of the Sales Tax report and of the six A/R and A/P aging reports. The design uses sample placeholder tables for those, and the written description does not list their columns.
 Not built yet on the build tested: only the first report tab (Timesheet Activities) has a filter bar, with a Date Range and a Filter by Staff button, and no report tab has a page search box. If the controls this test needs are missing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5205,7 +5195,7 @@
 2. The report narrows as soon as you pick the value - there is no Apply or Run button to press. Every filter button on every report works this way.
 Not built yet on the build tested: only the first report tab (Timesheet Activities) has a filter bar, with a Date Range and a Filter by Staff button, and no report tab has a page search box. If the controls this test needs are missing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5265,7 +5255,7 @@
 &lt;/ol&gt;
 Not built yet on the build tested: only the first report tab (Timesheet Activities) has a filter bar, with a Date Range and a Filter by Staff button, and no report tab has a page search box. If the controls this test needs are missing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -5279,7 +5269,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Date range filter: results update when both start and end dates are picked</t>
+          <t>Date range filter offers ready-made periods and a custom start/end range</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -5300,28 +5290,33 @@
       <c r="E92" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. The new filter bar has rolled out to a page with a Date filter chip (a report, or a Parts page with a date column).
+2. You are on a report that has a Date Range button - on the build tested that is Reports then the Timesheet Activities report.
 3. Records exist inside and outside the date range you will pick.</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>1. Click the Date filter chip.
-2. Look at the panel that opens.
-3. Pick a start date only, and watch the results.
-4. Pick the end date.
-5. Look at the results and the chip.</t>
+          <t>1. Click the Date Range button.
+2. Look at what the panel offers, and at what the button already reads before you change anything.
+3. Choose one of the ready-made periods (for example Today) and watch the results.
+4. Open the button again and choose Custom.
+5. Fill in the From date only, and watch the results.
+6. Fill in the To date.
+7. Look at the results and at the button.</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>1. A start/end date picker opens - there are NO preset ranges (no 'Last 30 days' shortcuts) and NO pre-filled default range.
-2. After only the start date, the results do not change yet.
-3. As soon as the second date is picked, the results update immediately to show only records inside the range.
-4. Only one date range can be active at a time on that chip, and the chip shows the active range.
-Not built yet on the build tested: only the first report tab (Timesheet Activities) has a filter bar, with a Date Range and a Filter by Staff button, and no report tab has a page search box. If the controls this test needs are missing, mark this test BLOCKED - do not mark it failed.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
+          <t>1. The panel that opens offers a set of ready-made periods to choose from - on the build tested these are Today, Yesterday, This week, Last week, This month, Last month, This quarter, Last quarter, This year, Last year - plus a Custom option and a Clear Selection link. The exact set of ready-made periods may differ per report, so check the ones your report offers rather than expecting this list.
+2. A period is already filled in when the panel first opens (on Timesheet Activities it is This month), and the button reads that period, for example "Date Range: This month".
+3. Choosing a ready-made period applies it straight away: the results update, the button reads the period you chose, and the web address records it.
+4. Choosing Custom shows a From box and a To box. After you fill in only the From date the results do NOT change yet.
+5. As soon as you fill in the To date the results update to show only records inside that range, and the button reads "Date Range: Custom".
+6. Only one date range can be active at a time on that button.
+Note: dates are typed in month/day/year order, the way the build shows them (for example 07/01/2026).
+Where to run this on the build tested: the Reports area has this date button on the Timesheet Activities report. Other report tabs do not have a filter bar yet - if the report you open has no date button, mark this test BLOCKED, not failed.
+---
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. It follows the NEWER wording of the Filters specification version 1.6, in the revision published on the afternoon of 4 August 2026, which changed the date filter description in the Feature Overview and in the Key Decisions section: the date button now offers standard ready-made periods and starts with the current default range already filled in. An earlier revision of the same specification said the opposite, and this test follows the newer one. The specification does not give this a numbered requirement, so there is no requirement number to quote.</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5376,7 +5371,7 @@
 3. The round x clears the text and the full list returns.
 4. Clicking away with an empty box collapses it back to the Search button; with text in it, the box stays open.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-R1, S13-R9, S13-R12, S13-R15).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-R1, S13-R9, S13-R12, S13-R15).</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5428,7 +5423,7 @@
 2. Clearing the search keeps the filter applied.
 3. Clearing the filter keeps the search applied - each is cleared by its own control without wiping the other.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-R10, S13-R13, S8-R5).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-R10, S13-R13, S8-R5).</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5483,7 +5478,7 @@
 3. The second browser tab starts clean: its Search box is empty and it shows the full list. Each tab keeps its own search.
 4. After closing the browser and coming back, the Search box is empty and the list is unsearched - a typed search is never remembered for next time (your filters, unlike the search, ARE remembered).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-R14, S13-R25, S13-N4, S10-R5).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-R14, S13-R25, S13-N4, S10-R5).</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5535,7 +5530,7 @@
 3. The malformed part is ignored - the page loads cleanly without an error.
 4. A search arriving via a link is view-only, the same as filters from a link - it does not overwrite your own remembered search.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S11-R4, S11-R5, S11-N2, S11-R8).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S11-R4, S11-R5, S11-N2, S11-R8).</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5589,7 +5584,7 @@
 4. The box stretches to fill the space left in the action row instead of staying the narrow desktop size, and every other toolbar button stays visible and in the same place while you search.
 5. There is no extra 'search is on' badge on mobile: with text in it the box simply stays open showing your text, and an empty box closes back to the Search button when you tap elsewhere - exactly as on desktop.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-R16, S13-R17, S13-R18, S13-R19, S13-R20, S12-R5).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-R16, S13-R17, S13-R18, S13-R19, S13-R20, S12-R5).</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -5645,7 +5640,7 @@
 3. Where the table sits inside a dialog (the Work Order Log, the Line Log, the audit log dialog), the Search box is inside that dialog and works there.
 4. The work order Parts tab keeps the local search input it already had - it was deliberately left as it is.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S14-R6, S14-R5, S13-R22, S14-N1).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S14-R6, S14-R5, S13-R22, S14-N1).</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -5697,7 +5692,7 @@
 2. The same holds on the other pages checked.
 3. Picking a dropdown result still takes you to that record - the navigation search keeps its find-and-open role.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S14-R1, S14-R2, S14-R4, S14-R5).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S14-R1, S14-R2, S14-R4, S14-R5).</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5753,7 +5748,7 @@
 5. As soon as you type, your text shows in a dark grey and a small round x appears at the right-hand end of the box.
 6. A very long sentence does not make the box grow and does not cut the text off - the text scrolls sideways inside the box and the cursor stays where you are typing.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-R2, S13-R3, S13-R4, S13-R5, S13-R6, S13-R8).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-R2, S13-R3, S13-R4, S13-R5, S13-R6, S13-R8).</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -5808,9 +5803,9 @@
 3. There is no Apply or Submit button anywhere next to the Search box.
 4. Pressing Enter changes nothing that has not already happened - the same rows stay listed and no page reload happens.
 5. Parts Inventory behaves the same way, only it waits a fraction longer before reacting; that longer wait is on purpose because that page carries more data.
-Known issue: the empty screen offers no way to clear the search on its own. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8847
----
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-R7, S13-R12).</t>
+Known and accepted: the empty screen offers no way to clear the search on its own. The product behaves this way on purpose for now. Do not raise this as a new problem.
+---
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-R7, S13-R12).</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5863,9 +5858,8 @@
 2. On the Estimates tab your word is still in the Search box, and the list shows only Estimates rows that match it - no rows from the other tabs appear.
 3. The Completed tab behaves the same way: your word is still there and only that tab's matching rows are listed.
 4. Clearing the search clears it for all the Work Orders tabs - they share one search - and each tab shows its full list again.
-Known issue: what you type in the page search is saved against your account, so it comes back on a later visit and can leave the list looking empty. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8844
----
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-R11, S13-R24).</t>
+---
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-R11, S13-R24).</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -5918,9 +5912,8 @@
 2. Going back to the first view brings its own word back and narrows its list again.
 3. Each report tab behaves the same way: a word typed on one tab stays on that tab only, and each tab remembers its own.
 4. No search is ever applied to a table it was not typed on.
-Known issue: what you type in the page search is saved against your account instead of only for this browser tab. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8844
----
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-R24, S13-R11, S10-R4).</t>
+---
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-R24, S13-R11, S10-R4).</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -5972,9 +5965,8 @@
 2. The page's own Search box is empty; nothing was carried into it.
 3. No error is shown - the leftover search part in the address is simply ignored. (Whether it also disappears from the address is not important; note what you see.)
 4. After typing in the top-of-screen search and reloading, the list is still not narrowed and nothing about that word was remembered for the list.
-Known issue: the search text is restored on a later visit instead of starting empty. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8844
----
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S14-R3, S14-R2, S14-R1).</t>
+---
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S14-R3, S14-R2, S14-R1).</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -6026,7 +6018,7 @@
 2. The Search box stays in the toolbar row with your word still showing; it is not tucked away with the filter bar, because the search sits in the toolbar row and the chips sit in the row below.
 3. Expanding the bar again changes nothing about the search or the narrowed list.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-E1).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-E1).</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -6077,7 +6069,7 @@
 2. The request succeeds (HTTP 200).
 3. The response contains only work orders matching the filters - the filtering is done by the backend, not just hidden client-side.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-R2, S3-R6).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-R2, S3-R6).</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -6127,7 +6119,7 @@
 2. The response returns customer A's Estimate and Approved work orders only.
 3. Customer B's work orders are absent - the customer filter and status filter both restrict the result, while the two statuses combine as either-or.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-R2, S3-R6, S8-R3).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-R2, S3-R6, S8-R3).</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -6178,7 +6170,7 @@
 3. Any still-valid filter values in the same request are applied normally.
 Known issue: the server does not fail, but the value that no longer exists is still applied instead of being dropped. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8832
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S10-N1, S11-R3).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S10-N1, S11-R3).</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -6229,7 +6221,7 @@
 2. In the browser the page still loads without filters and without an error message, matching the malformed-URL requirement.
 Known issue: the server does not fail, but a broken address is not fully ignored by the page. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8832
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S11-N1).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S11-N1).</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6279,7 +6271,7 @@
 2. The response contains an empty result set (zero work orders) - an empty match is a normal outcome, not an error.
 3. The page renders the no-results empty state from this response.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S8-R3, S2-N3).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S8-R3, S2-N3).</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6333,7 +6325,7 @@
 4. Asking for a never-saved key returns success with an empty value, not an error page.
 Step 3 needs a SECOND sign-in of your own. We could not run it for you: impersonating another user on this branch returns an error, and a new staff member cannot finish signing up because the invitation email cannot be received here. If you have a second account, run step 3 normally. If you do not, mark this test BLOCKED - do not mark it failed. Steps 1, 2 and 4 were confirmed working.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (ShopView v3.4.2-4f8211c on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S10-R2, S10-R3).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S10-R2, S10-R3).</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">

--- a/testrail-import/filters-v1-testrail-import.xlsx
+++ b/testrail-import/filters-v1-testrail-import.xlsx
@@ -528,13 +528,15 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>&lt;ol&gt;
+          <t xml:space="preserve">&lt;ol&gt;
 &lt;li&gt;A filter bar is visible directly below the tab row and above the work order table.&lt;/li&gt;
 &lt;li&gt;The filter bar is shown by default (expanded) without having to turn anything on.&lt;/li&gt;
 &lt;/ol&gt;
 Known and accepted: on the build tested the filter buttons sit on the same row as the tabs instead of on their own row below them. The product behaves this way on purpose for now. Do not raise this as a new problem.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S1-R1).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S1-R1).
+AUTOMATION: READY - EXPECT FAIL (SV-8843 - closed as accepted, will not be fixed)
+</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -581,11 +583,13 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>1. Exactly five filter chips appear, in this order: Status, Customer, Lead Technician, Service Advisor, Asset on Site.
+          <t xml:space="preserve">1. Exactly five filter chips appear, in this order: Status, Customer, Lead Technician, Service Advisor, Asset on Site.
 2. Each chip shows the filter name and a down arrow (chevron) indicating it opens a dropdown.
 3. Each chip shows only the filter name and the arrow - there is no picture icon in front of the name.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S1-R2, S1-R3). Note: the design frame also draws a small picture icon in front of each filter name; the specification asks only for the name and the arrow, and the build matches the specification, so this test follows the specification and the build.</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S1-R2, S1-R3). Note: the design frame also draws a small picture icon in front of each filter name; the specification asks only for the name and the arrow, and the build matches the specification, so this test follows the specification and the build.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -631,11 +635,13 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1. The filter bar is still shown - it does not disappear on this tab.
+          <t xml:space="preserve">1. The filter bar is still shown - it does not disappear on this tab.
 2. The Customer, Lead Technician, Service Advisor and Asset on Site chips are all displayed and usable.
 3. The Status chip is not shown on this tab at all - only four chips appear.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S1-N1, S9-R2). Note: an earlier answer of 2026-07-17 and the design frame both show the Status button greyed out and pre-filled on this tab; the specification and the build both hide it, and the specification is the newer source, so this test follows the specification and the build.</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S1-N1, S9-R2). Note: an earlier answer of 2026-07-17 and the design frame both show the Status button greyed out and pre-filled on this tab; the specification and the build both hide it, and the specification is the newer source, so this test follows the specification and the build.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -689,14 +695,16 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>&lt;ol&gt;
+          <t xml:space="preserve">&lt;ol&gt;
 &lt;li&gt;A dropdown panel opens under the Status chip.&lt;/li&gt;
 &lt;li&gt;It lists all nine statuses as checkboxes, in this order: Estimate, Approved, In progress, Review, Complete, Invoiced, Paid, Declined, Imported.&lt;/li&gt;
 &lt;li&gt;All checkboxes are unticked (nothing selected yet).&lt;/li&gt;
 &lt;li&gt;A 'Clear Selection' action is shown at the bottom of the dropdown.&lt;/li&gt;
 &lt;/ol&gt;
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-R1, S2-R4).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-R1, S2-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -744,11 +752,13 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1. The ticked checkbox appears filled (checked).
+          <t xml:space="preserve">1. The ticked checkbox appears filled (checked).
 2. The table updates immediately to show only work orders in the selected status - there is no confirm or apply button on desktop.
 3. Work orders in other statuses are no longer listed.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-R2, S2-R3, S2-R6).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-R2, S2-R3, S2-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -796,12 +806,14 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1. Every ticked status shows a filled checkbox.
+          <t xml:space="preserve">1. Every ticked status shows a filled checkbox.
 2. The table shows work orders whose status matches ANY of the ticked statuses (both Estimate and Approved rows appear).
 3. Work orders in statuses that are not ticked are hidden.
 4. There is no limit on how many statuses you can tick.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-R2).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -849,11 +861,13 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1. All status checkboxes become unticked.
+          <t xml:space="preserve">1. All status checkboxes become unticked.
 2. The Status filter is removed and the table returns to showing work orders of every status.
 3. Only the Status filter is affected - any other active filters stay applied.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-R4, S8-R2).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-R4, S8-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -900,11 +914,13 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1. The dropdown closes.
+          <t xml:space="preserve">1. The dropdown closes.
 2. The ticked statuses stay selected - the Status chip stays in its active state showing the selection.
 3. The table stays filtered by the selected statuses.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-R5).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -952,11 +968,13 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1. The table shows no rows.
+          <t xml:space="preserve">1. The table shows no rows.
 2. An empty state is displayed saying no results were found for the current filters (see the Empty State cases for its full content).
 3. The app does not show an error.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-N3, S8-R3).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-N3, S8-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1005,12 +1023,14 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1. The table switches to showing imported work orders only.
+          <t xml:space="preserve">1. The table switches to showing imported work orders only.
 2. While Imported is ticked, the other filter chips are greyed out and cannot be used.
 3. Imported cannot be combined with other statuses - selecting it works alone.
 4. Unticking Imported re-enables the other chips and the normal list returns.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-R7, S2-N4).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-R7, S2-N4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1064,14 +1084,16 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>&lt;ol&gt;
+          <t xml:space="preserve">&lt;ol&gt;
 &lt;li&gt;A dropdown panel opens under the Customer chip.&lt;/li&gt;
 &lt;li&gt;A search box with the placeholder 'Search' is at the top of the panel. Click it before you type - it is not focused for you automatically.&lt;/li&gt;
 &lt;li&gt;Below it is a scrollable list of customer names.&lt;/li&gt;
 &lt;li&gt;A 'Clear Selection' action is shown at the bottom of the panel.&lt;/li&gt;
 &lt;/ol&gt;
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-R1).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-R1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1118,11 +1140,13 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1. The customer list narrows as you type, showing only names that match what you entered.
+          <t xml:space="preserve">1. The customer list narrows as you type, showing only names that match what you entered.
 2. Customers that do not match are removed from the list.
 3. Deleting the text brings the full list back.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-R2).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1176,14 +1200,16 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>&lt;ol&gt;
+          <t xml:space="preserve">&lt;ol&gt;
 &lt;li&gt;Each selected customer appears as a tag (small chip) with an x in the input area at the top of the dropdown.&lt;/li&gt;
 &lt;li&gt;Each selected customer's row in the list shows a checkmark on the right.&lt;/li&gt;
 &lt;li&gt;Long customer names on tags are shortened with an ellipsis (for example 'Texas Truck And Aut...').&lt;/li&gt;
 &lt;li&gt;You can keep selecting as many customers as needed - there is no selection limit.&lt;/li&gt;
 &lt;/ol&gt;
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-R3, S3-R4).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-R3, S3-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1230,12 +1256,14 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1. That customer's tag disappears from the input area.
+          <t xml:space="preserve">1. That customer's tag disappears from the input area.
 2. The checkmark next to that customer in the list is removed.
 3. The other selected customers keep their tags and checkmarks.
 4. The table updates to no longer include that customer's work orders.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-R5).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1282,11 +1310,13 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1. The table shows only work orders whose customer is one of the two selected customers.
+          <t xml:space="preserve">1. The table shows only work orders whose customer is one of the two selected customers.
 2. Work orders belonging to any other customer are hidden.
 3. The table updates in real time as you make the selections (no apply button on desktop).
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-R6, S2-R6).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-R6, S2-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1334,12 +1364,14 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1. All customer tags are removed from the input area.
+          <t xml:space="preserve">1. All customer tags are removed from the input area.
 2. All checkmarks in the list are removed.
 3. The Customer filter is removed and the table shows work orders of all customers again.
 4. Other active filters (if any) are not affected.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-R7, S8-R2).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-R7, S8-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1386,11 +1418,13 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1. The dropdown closes when you click outside it.
+          <t xml:space="preserve">1. The dropdown closes when you click outside it.
 2. The Customer chip stays in the active (blue) state showing the selection and the table stays filtered.
 3. When reopened, the selected customers' tags are still visible in the input area.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-R8).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1442,13 +1476,15 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>&lt;ol&gt;
+          <t xml:space="preserve">&lt;ol&gt;
 &lt;li&gt;The list shows a message saying there are no results (instead of an empty gap).&lt;/li&gt;
 &lt;li&gt;The app does not show an error.&lt;/li&gt;
 &lt;li&gt;Clearing the search text brings the customer list back.&lt;/li&gt;
 &lt;/ol&gt;
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-N1).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1496,11 +1532,13 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1. The customer with no work orders IS shown in the filter list (they are not hidden).
+          <t xml:space="preserve">1. The customer with no work orders IS shown in the filter list (they are not hidden).
 2. After selecting only that customer, the table shows no rows and the filtered empty state is displayed.
 3. No error is shown.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-E1, S3-N2, S8-R3).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-E1, S3-N2, S8-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1553,14 +1591,16 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>&lt;ol&gt;
+          <t xml:space="preserve">&lt;ol&gt;
 &lt;li&gt;A dropdown panel opens under the Lead Technician chip.&lt;/li&gt;
 &lt;li&gt;A search input with the placeholder 'Search' is at the top.&lt;/li&gt;
 &lt;li&gt;Below it is a scrollable list of technician names.&lt;/li&gt;
 &lt;li&gt;A 'Clear Selection' action is shown at the bottom.&lt;/li&gt;
 &lt;/ol&gt;
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S4-R1).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S4-R1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1606,10 +1646,12 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1. The technician list narrows to only the names matching what you typed.
+          <t xml:space="preserve">1. The technician list narrows to only the names matching what you typed.
 2. Deleting the text brings the full list back.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S4-R2).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S4-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1656,12 +1698,14 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1. Selected technicians show a checkmark on the row, and as a small removable tag above the list in the list.
+          <t xml:space="preserve">1. Selected technicians show a checkmark on the row, and as a small removable tag above the list in the list.
 2. The table shows only work orders where one of the selected technicians is assigned as the LEAD technician.
 3. A work order where the technician is assigned only in a non-lead role does not appear.
 4. The table updates in real time as you select.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S4-R3, S4-R4).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S4-R3, S4-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1708,11 +1752,13 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1. All technician selections are removed (checkboxes unticked).
+          <t xml:space="preserve">1. All technician selections are removed (checkboxes unticked).
 2. The Lead Technician filter no longer restricts the table.
 3. Other active filters are not affected.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S4-R5, S8-R2).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S4-R5, S8-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1758,10 +1804,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1. The dropdown closes.
+          <t xml:space="preserve">1. The dropdown closes.
 2. The selection stays applied - the chip stays active and the table stays filtered.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S4-R6).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S4-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1808,10 +1856,12 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1. The table shows no rows and the filtered empty state is displayed.
+          <t xml:space="preserve">1. The table shows no rows and the filtered empty state is displayed.
 2. No error is shown.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S4-N1, S8-R3).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S4-N1, S8-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1859,10 +1909,12 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1. The deactivated technician is NOT shown in the filter list.
+          <t xml:space="preserve">1. The deactivated technician is NOT shown in the filter list.
 2. Active technicians are still listed normally.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S4-E1).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S4-E1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1915,14 +1967,16 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>&lt;ol&gt;
+          <t xml:space="preserve">&lt;ol&gt;
 &lt;li&gt;A dropdown panel opens under the Service Advisor chip.&lt;/li&gt;
 &lt;li&gt;A search input with the placeholder 'Search' is at the top.&lt;/li&gt;
 &lt;li&gt;Below it is a scrollable list of advisor names.&lt;/li&gt;
 &lt;li&gt;A 'Clear Selection' action is shown at the bottom.&lt;/li&gt;
 &lt;/ol&gt;
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S5-R1).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S5-R1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1968,10 +2022,12 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1. The advisor list narrows to only the names matching what you typed.
+          <t xml:space="preserve">1. The advisor list narrows to only the names matching what you typed.
 2. Deleting the text brings the full list back.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S5-R2).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S5-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2018,11 +2074,13 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1. Selected advisors show a checkmark on the row, and as a small removable tag above the list in the list.
+          <t xml:space="preserve">1. Selected advisors show a checkmark on the row, and as a small removable tag above the list in the list.
 2. The table shows only work orders assigned to any of the selected advisors.
 3. The table updates in real time as you select.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S5-R3, S5-R4).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S5-R3, S5-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2069,11 +2127,13 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1. All advisor selections are removed.
+          <t xml:space="preserve">1. All advisor selections are removed.
 2. The Service Advisor filter no longer restricts the table.
 3. Other active filters are not affected.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S5-R5, S8-R2).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S5-R5, S8-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2119,10 +2179,12 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1. The dropdown closes.
+          <t xml:space="preserve">1. The dropdown closes.
 2. The selection stays applied - the chip stays active and the table stays filtered.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S5-R6).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S5-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2169,10 +2231,12 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1. The table shows no rows and the filtered empty state is displayed.
+          <t xml:space="preserve">1. The table shows no rows and the filtered empty state is displayed.
 2. No error is shown.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S5-N1, S8-R3).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S5-N1, S8-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2220,10 +2284,12 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1. The deactivated advisor is NOT shown in the filter list.
+          <t xml:space="preserve">1. The deactivated advisor is NOT shown in the filter list.
 2. Active advisors are still listed normally.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S5-E1).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S5-E1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2269,12 +2335,14 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>1. A small dropdown panel opens under the Asset on Site chip.
+          <t xml:space="preserve">1. A small dropdown panel opens under the Asset on Site chip.
 2. It contains exactly two options: Yes and No.
 3. A 'Clear Selection' action is shown at the bottom.
 4. It is a dropdown (like the other filters), not an on/off toggle.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S6-R1).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S6-R1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2321,10 +2389,12 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>1. The table shows only work orders whose asset is currently on site.
+          <t xml:space="preserve">1. The table shows only work orders whose asset is currently on site.
 2. Work orders whose asset is not on site are hidden.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S6-R2).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S6-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2371,11 +2441,13 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1. No becomes the selected option and Yes is deselected automatically - only one option can be selected at a time.
+          <t xml:space="preserve">1. No becomes the selected option and Yes is deselected automatically - only one option can be selected at a time.
 2. The table switches to showing only the not-on-site work orders.
 3. The chip shows the currently selected value.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S6-R3).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S6-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2421,11 +2493,13 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>1. The selection is removed and the chip returns to its default (inactive) state.
+          <t xml:space="preserve">1. The selection is removed and the chip returns to its default (inactive) state.
 2. The table shows work orders regardless of on-site status again.
 3. Other active filters are not affected.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S6-R4, S8-R2).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S6-R4, S8-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2471,10 +2545,12 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>1. The dropdown closes.
+          <t xml:space="preserve">1. The dropdown closes.
 2. The Yes selection stays applied - the chip stays active and the table stays filtered.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S6-R5).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S6-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2521,10 +2597,12 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>1. The table shows no rows and the filtered empty state is displayed.
+          <t xml:space="preserve">1. The table shows no rows and the filtered empty state is displayed.
 2. No error is shown.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S6-N1, S8-R3).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S6-N1, S8-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2572,11 +2650,13 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>1. Only work orders whose asset is NOT on site remain in the list.
+          <t xml:space="preserve">1. Only work orders whose asset is NOT on site remain in the list.
 2. Every work order with the asset on site is excluded.
 3. The chip shows the active No selection.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S6-R2).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S6-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2622,11 +2702,13 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>1. The Status chip changes to an active/highlighted look (blue pill).
+          <t xml:space="preserve">1. The Status chip changes to an active/highlighted look (blue pill).
 2. The chip displays the selected value (for example 'Status: Estimate').
 3. The other chips stay in their default state.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S7-R1).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S7-R1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2672,10 +2754,12 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>1. The chip lists the selected values starting with the first one and shortens the label when it gets too long (the design shows 'Status: Estimate, In progress, Approved...').
+          <t xml:space="preserve">1. The chip lists the selected values starting with the first one and shortens the label when it gets too long (the design shows 'Status: Estimate, In progress, Approved...').
 2. The chip stays a single compact pill - it does not grow to show every value in full.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S7-R2).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S7-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2723,11 +2807,13 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>1. With no filters active, no 'Clear Filters' button/link is shown (there is nothing to click).
+          <t xml:space="preserve">1. With no filters active, no 'Clear Filters' button/link is shown (there is nothing to click).
 2. As soon as one filter is active, a blue 'Clear Filters' link appears at the right end of the chip row.
 3. When the last active filter is removed, 'Clear Filters' disappears again.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S7-R3, S7-N1, S8-N1).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S7-R3, S7-N1, S8-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2775,12 +2861,14 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>1. Every active filter is cleared in one click.
+          <t xml:space="preserve">1. Every active filter is cleared in one click.
 2. All chips return to their default (inactive) look with no values shown.
 3. The table shows the full unfiltered list again (no text is in the page Search box, so nothing else is narrowing it).
 4. The 'Clear Filters' link disappears.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S8-R1, S13-R13).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S8-R1, S13-R13).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2827,11 +2915,13 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>1. Only the Status filter is cleared - its chip returns to default.
+          <t xml:space="preserve">1. Only the Status filter is cleared - its chip returns to default.
 2. The Customer filter stays selected and active (blue) and keeps filtering the table.
 3. 'Clear Filters' remains visible because a filter is still active.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S8-R2).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S8-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2879,11 +2969,13 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>1. Only customer A's Estimate work order is shown.
+          <t xml:space="preserve">1. Only customer A's Estimate work order is shown.
 2. Customer A's Approved work order is hidden (wrong status) and customer B's Estimate work order is hidden (wrong customer) - each additional filter narrows the result further.
 3. Both chips are in the active state and 'Clear Filters' is visible.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S8-R3).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S8-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2930,11 +3022,13 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>1. The filter bar row is hidden.
+          <t xml:space="preserve">1. The filter bar row is hidden.
 2. The work order table moves up and uses the reclaimed vertical space.
 3. The filter icon shows a pressed/active look while the bar is collapsed.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S1-R4, S1-R5).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S1-R4, S1-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2981,12 +3075,14 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>1. The filter bar reappears below the tab row.
+          <t xml:space="preserve">1. The filter bar reappears below the tab row.
 2. The previously selected filters are still shown on their chips in the active (blue) state - nothing was lost while collapsed.
 3. The 'Clear Filters' link is still shown at the right end of the chip row.
 Known and accepted: on the build tested collapsing the bar does not move the table up, because the buttons share the tab row. The product behaves this way on purpose for now. Do not raise this as a new problem.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S1-R6).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S1-R6).
+AUTOMATION: READY - EXPECT FAIL (SV-8843 - closed as accepted, will not be fixed)
+</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3034,10 +3130,12 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>1. After step 2 the filter bar is still collapsed (your choice was remembered).
+          <t xml:space="preserve">1. After step 2 the filter bar is still collapsed (your choice was remembered).
 2. After step 4 the filter bar is expanded again when you return - whichever state you left it in is restored.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S1-R7, S10-R1).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S1-R7, S10-R1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3084,10 +3182,12 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>1. After step 1 the filter icon shows no special indicator (only its normal pressed look).
+          <t xml:space="preserve">1. After step 1 the filter icon shows no special indicator (only its normal pressed look).
 2. After step 3 the filter icon shows a visual indicator (filters icon in primary blue) signalling that active filters are in effect while the bar is hidden.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S7-R4, S7-N2).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S7-R4, S7-N2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3134,10 +3234,12 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>1. The table content does not change when the bar collapses - it still shows only the work orders matching the active filters.
+          <t xml:space="preserve">1. The table content does not change when the bar collapses - it still shows only the work orders matching the active filters.
 2. Hiding the bar only hides the chips; it does not remove or pause the filtering.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S7-R5).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S7-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3184,12 +3286,14 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>1. The table body is replaced by an empty state (not just a bare empty grid).
+          <t xml:space="preserve">1. The table body is replaced by an empty state (not just a bare empty grid).
 2. The empty state shows a message indicating no results were found for the current filters.
 3. No error message or broken layout appears.
 Known and accepted: when only a search is active the message still says "filters" and the only link offered is Clear Filters. The product behaves this way on purpose for now. Do not raise this as a new problem.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S8-R3).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S8-R3).
+AUTOMATION: READY - EXPECT FAIL (SV-8847 - closed as accepted, will not be fixed)
+</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3237,12 +3341,14 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>1. The empty state includes a prompt or link to clear the filters.
+          <t xml:space="preserve">1. The empty state includes a prompt or link to clear the filters.
 2. Clicking it removes the active filters and the full work order list is shown again (with no text in the Search box, nothing else is narrowing the list).
 3. The chips return to their default state.
 Known and accepted: the empty screen offers no way to clear the search on its own. The product behaves this way on purpose for now. Do not raise this as a new problem.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S8-R4, S8-R5).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S8-R4, S8-R5).
+AUTOMATION: READY - EXPECT FAIL (SV-8847 - closed as accepted, will not be fixed)
+</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3291,12 +3397,14 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>1. The table is replaced by a no-results message that mentions BOTH the current filters and the search - not the filters alone.
+          <t xml:space="preserve">1. The table is replaced by a no-results message that mentions BOTH the current filters and the search - not the filters alone.
 2. The message offers a way to clear the filters and, because a search is active, a separate way to clear the search.
 3. Clearing the search brings back the list as narrowed by the filter only - the filter is still on.
 4. Clearing the filters leaves your typed word in the box and still applied - each is cleared on its own without wiping the other.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S8-R3, S8-R4, S8-R5, S13-N1, S13-N2).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S8-R3, S8-R4, S8-R5, S13-N1, S13-N2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3342,10 +3450,12 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>1. All five chips are shown: Status, Customer, Lead Technician, Service Advisor, Asset on Site.
+          <t xml:space="preserve">1. All five chips are shown: Status, Customer, Lead Technician, Service Advisor, Asset on Site.
 2. Each chip opens its dropdown and can be used.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S9-R1).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S9-R1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3395,11 +3505,13 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>1. The Status chip is not shown on this tab at all - only four chips appear. The tab already pre-filters the list to Estimate.
+          <t xml:space="preserve">1. The Status chip is not shown on this tab at all - only four chips appear. The tab already pre-filters the list to Estimate.
 2. Customer, Lead Technician, Service Advisor and Asset on Site chips are shown and usable.
 3. After step 4 the table shows only that customer's ESTIMATE work orders - the customer filter narrows the pre-filtered Estimates list.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S9-R2, S2-N1). Note: an earlier answer of 2026-07-17 and the design frame both show the Status button greyed out and pre-filled on this tab; the specification and the build both hide it, and the specification is the newer source, so this test follows the specification and the build.</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S9-R2, S2-N1). Note: an earlier answer of 2026-07-17 and the design frame both show the Status button greyed out and pre-filled on this tab; the specification and the build both hide it, and the specification is the newer source, so this test follows the specification and the build.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3449,11 +3561,13 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>1. The Status chip is not shown on this tab at all - only four chips appear. The tab already pre-filters the list to Complete.
+          <t xml:space="preserve">1. The Status chip is not shown on this tab at all - only four chips appear. The tab already pre-filters the list to Complete.
 2. Customer, Lead Technician, Service Advisor and Asset on Site chips are shown and usable.
 3. After step 4 the table shows only that customer's COMPLETE work orders.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S9-R3, S2-N2). Note: an earlier answer of 2026-07-17 and the design frame both show the Status button greyed out and pre-filled on this tab; the specification and the build both hide it, and the specification is the newer source, so this test follows the specification and the build.</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S9-R3, S2-N2). Note: an earlier answer of 2026-07-17 and the design frame both show the Status button greyed out and pre-filled on this tab; the specification and the build both hide it, and the specification is the newer source, so this test follows the specification and the build.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3501,11 +3615,13 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>1. All five filter chips are shown on the My Work Orders tab.
+          <t xml:space="preserve">1. All five filter chips are shown on the My Work Orders tab.
 2. The table only ever shows work orders assigned to you (the tab's own scope stays).
 3. After step 2 it shows only YOUR work orders in the ticked status - the filters narrow the user-scoped list, they do not widen it to other users' work orders.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S9-R4).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S9-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3552,11 +3668,13 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>1. On the Estimates tab your Status choice is not applied and cannot be changed - the Status chip is not shown on that tab. The Customer selection is still shown and still filters the list.
+          <t xml:space="preserve">1. On the Estimates tab your Status choice is not applied and cannot be changed - the Status chip is not shown on that tab. The Customer selection is still shown and still filters the list.
 2. Back on the All tab the Status chip reappears with the SAME selection (Approved) still applied - the selection was retained in memory, not lost.
 3. The Customer selection is unchanged throughout.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S9-R5, S9-N1, S9-R2).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S9-R5, S9-N1, S9-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3603,10 +3721,12 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>1. On the very first visit the Estimates tab is the selected one, even though All is the FIRST tab in the row (order and default are different on purpose).
+          <t xml:space="preserve">1. On the very first visit the Estimates tab is the selected one, even though All is the FIRST tab in the row (order and default are different on purpose).
 2. After switching to All and returning, the All tab is selected - the app remembers your last-used tab per account.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3660,7 +3780,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>&lt;ol&gt;
+          <t xml:space="preserve">&lt;ol&gt;
 &lt;li&gt;After step 2 the same Status and Customer selections are still applied - chips active with the same values, table filtered the same way.&lt;/li&gt;
 &lt;li&gt;The filter bar is still expanded (as you left it).&lt;/li&gt;
 &lt;li&gt;After step 4 the filter bar comes back collapsed - the collapsed/expanded state is restored too.&lt;/li&gt;
@@ -3669,7 +3789,9 @@
 &lt;p&gt;This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S10-R1, S1-R7).&lt;/p&gt;
 Known issue: on the build tested the Customer, Lead Technician and Service Advisor buttons come back switched on but WITHOUT the name of the value you picked - the button reads just "Customer" instead of "Customer: Iibay Landscaping". The list is still filtered correctly. The Status and Asset on Site buttons keep their value. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8871
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S10-R1, S1-R7).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S10-R1, S1-R7).
+AUTOMATION: READY - EXPECT FAIL (SV-8871)
+</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3719,11 +3841,13 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>1. After moving around the app (step 2) the filter selections are still applied - you do not have to re-apply them.
+          <t xml:space="preserve">1. After moving around the app (step 2) the filter selections are still applied - you do not have to re-apply them.
 2. After closing the browser completely and signing back in (step 5) the same filter selections are still applied - the app remembers your filters for you permanently, not just for one browser session.
 3. The same filter selections are applied on the other computer too - the filters are saved to your account, not to one computer or browser (to confirm live once built).
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S10-R2, S10-R3, S10-R1).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S10-R2, S10-R3, S10-R1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3770,10 +3894,12 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>1. User B does not see user A's filters - user B's page opens with user B's own (or no) filters.
+          <t xml:space="preserve">1. User B does not see user A's filters - user B's page opens with user B's own (or no) filters.
 2. User B's new filter does not change what user A sees; each user keeps their own saved filter state.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S10-R3).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S10-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3820,12 +3946,14 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>1. The deleted customer is silently ignored - no error or warning appears.
+          <t xml:space="preserve">1. The deleted customer is silently ignored - no error or warning appears.
 2. The Customer filter now reflects only the still-valid selection (the real customer).
 3. The table is filtered by the remaining valid selection only.
 Known issue: on the build tested the deleted customer is hidden from the dropdown but is STILL used to filter the table - the address bar and the request to the server both still carry it. So step 3 above is expected to fail. It is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8832
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S10-N1).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S10-N1).
+AUTOMATION: READY - EXPECT FAIL (SV-8832)
+</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3873,11 +4001,13 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>1. The second Parts view does NOT show the first view's selections - each view keeps its own.
+          <t xml:space="preserve">1. The second Parts view does NOT show the first view's selections - each view keeps its own.
 2. Returning to the first view restores that view's own selections.
 3. Report tabs likewise keep separate filter choices, each remembered and restored on its own tab.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S10-R4).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S10-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3923,10 +4053,12 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>1. The old saved choices appear in the new filter bar on the first visit - the update does not lose them (old status choices show in the Status chip, the old asset-here choice shows as Asset on Site: Yes, the old My-Work-Orders toggle maps to the My Work Orders tab, columns and sorting stay).
+          <t xml:space="preserve">1. The old saved choices appear in the new filter bar on the first visit - the update does not lose them (old status choices show in the Status chip, the old asset-here choice shows as Asset on Site: Yes, the old My-Work-Orders toggle maps to the My Work Orders tab, columns and sorting stay).
 2. Those carried-over choices are now saved to the account: the other computer shows them too.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S10-R2).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S10-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -3973,10 +4105,12 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>1. After step 1 the URL changes to include the active filter state.
+          <t xml:space="preserve">1. After step 1 the URL changes to include the active filter state.
 2. After step 3 the filter part of the URL is removed again.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S11-R1).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S11-R1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4022,12 +4156,14 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>1. The page opens with the same filters already applied - chips active with the same values.
+          <t xml:space="preserve">1. The page opens with the same filters already applied - chips active with the same values.
 2. The table is already filtered accordingly on load (no need to re-apply anything).
 3. The same works from a saved bookmark.
 Known issue: two points on this test are expected to fail on the build tested. On a phone-sized screen a link carrying filters shows the buttons as on but lists the wrong work orders (ticket: https://shopview.atlassian.net/browse/SV-8845). And on a desktop screen a Customer, Lead Technician or Service Advisor button opened from a link comes back switched on but without the name of the value, so it reads just "Customer" (ticket: https://shopview.atlassian.net/browse/SV-8871). The list itself is filtered correctly on desktop. Both are already reported.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S11-R2).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S11-R2).
+AUTOMATION: READY - EXPECT FAIL (SV-8845, SV-8871)
+</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4074,12 +4210,14 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>1. The page loads normally - no error.
+          <t xml:space="preserve">1. The page loads normally - no error.
 2. The deleted value is ignored; only the still-valid filter value is applied and shown on the chips.
 3. The table reflects only the valid filter.
 Known issue: a value in the address bar that no longer exists is still sent to the server, so you get an empty list instead of the list without that value. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8832
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S11-R3).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S11-R3).
+AUTOMATION: READY - EXPECT FAIL (SV-8832)
+</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4126,12 +4264,14 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>1. The Work Orders page loads normally.
+          <t xml:space="preserve">1. The Work Orders page loads normally.
 2. No filters are applied (chips in default state, full list shown) - the unrecognizable state is discarded.
 3. No error message or broken page appears.
 Known issue: a broken address is not fully ignored - a wrong tab value can switch the tab and a bad customer value is still sent to the server. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8832
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S11-N1).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S11-N1).
+AUTOMATION: READY - EXPECT FAIL (SV-8832)
+</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4182,14 +4322,16 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>1. The link's filters apply for viewing only - the page shows the shared view.
+          <t xml:space="preserve">1. The link's filters apply for viewing only - the page shows the shared view.
 2. Changes made during the link visit are also NOT saved to your account.
 3. A 'Back To My Saved Filters' option is shown while you are looking at the shared link. (If the wording on screen is slightly different, note what it says and carry on.)
 4. Clicking 'Back To My Saved Filters' brings back your own saved filters and removes the filter part from the web address.
 5. It also empties the Search box and removes your typed text - the search is not something that gets saved, so there is nothing to bring back.
 6. Returning normally later still shows your own saved filters, untouched by the link visit.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S11-R6, S11-R7, S11-R8).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S11-R6, S11-R7, S11-R8).
+AUTOMATION: READY - EXPECT FAIL (SV-8828)
+</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4239,12 +4381,14 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>1. On your own view there is no 'Back To My Saved Filters' option anywhere - it only belongs to a shared-link visit.
+          <t xml:space="preserve">1. On your own view there is no 'Back To My Saved Filters' option anywhere - it only belongs to a shared-link visit.
 2. Changing your own filters does not make it appear.
 3. When you open the shared link, 'Back To My Saved Filters' does appear.
 4. After you click it and you are back on your own view, the option disappears again.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S11-N3, S11-R7).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S11-N3, S11-R7).
+AUTOMATION: READY - EXPECT FAIL (SV-8828)
+</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4670,12 +4814,14 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>1. The chip for the applied filter shows the active state with the selected value(s), like on desktop.
+          <t xml:space="preserve">1. The chip for the applied filter shows the active state with the selected value(s), like on desktop.
 2. A 'Clear Filters' control appears while at least one filter is active.
 3. Using it removes all active filters, the chips return to default and the full list comes back.
 Known issue: on a phone there is no Clear Filters button at all while filters are on. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8846
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R2, S7-R1, S8-R1).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R2, S7-R1, S8-R1).
+AUTOMATION: READY - EXPECT FAIL (SV-8846)
+</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4721,10 +4867,12 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>1. There is no filter-bar collapse/expand (filter icon) toggle on mobile.
+          <t xml:space="preserve">1. There is no filter-bar collapse/expand (filter icon) toggle on mobile.
 2. The filter chip row is always visible on the mobile Work Orders page.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R4).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R4).
+AUTOMATION: READY - EXPECT FAIL (no ticket - reported to the QA lead as one design item, not filed)
+</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4830,7 +4978,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>1. Inventory shows four filter buttons: Bin Location, Category, Supply and Vendor.
+          <t xml:space="preserve">1. Inventory shows four filter buttons: Bin Location, Category, Supply and Vendor.
 2. Part Sales shows four filter buttons: Status, Customer, Created by and Date.
 3. Catalog shows two filter buttons: Manufacturer and Category.
 4. The Returns tab shows three filter buttons: Vendor, Category and Part Type.
@@ -4845,7 +4993,9 @@
 13. Still to check on the live build: what the filter icon and the column/layout icon do (the written description does not cover the toolbar icons).
 Not built yet on the build tested: a filter bar exists on Inventory, Part Sales, Catalog and Returns, but Purchase Orders, Vendor Invoices and Vendors have no filter bar at all. If the filter bar is missing on the view you are testing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)
+AUTOMATION: HOLD - the feature is not in the product yet
+</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4893,13 +5043,15 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>1. A small menu opens with two options: Core and Non Core.
+          <t xml:space="preserve">1. A small menu opens with two options: Core and Non Core.
 2. A Clear Selection action is shown at the bottom of the menu.
 3. You can tick both Core and Non Core at the same time - this filter allows more than one choice.
 4. As soon as you tick a choice the list below narrows to matching parts straight away, with no Apply button to press; Clear Selection puts the list back.
 Not built yet on the build tested: a filter bar exists on Inventory, Part Sales, Catalog and Returns, but Purchase Orders, Vendor Invoices and Vendors have no filter bar at all. If the filter bar is missing on the view you are testing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)
+AUTOMATION: HOLD - the feature is not in the product yet
+</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4946,12 +5098,14 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>1. The table updates to show only the rows that match the chosen filter value.
+          <t xml:space="preserve">1. The table updates to show only the rows that match the chosen filter value.
 2. The chosen value is shown on the filter button so you can see what is applied.
 3. The list narrows as soon as you pick the value - there is no Apply or Search button to press. Every filter button on every Parts page works this way.
 Not built yet on the build tested: a filter bar exists on Inventory, Part Sales, Catalog and Returns, but Purchase Orders, Vendor Invoices and Vendors have no filter bar at all. If the filter bar is missing on the view you are testing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)
+AUTOMATION: HOLD - the feature is not in the product yet
+</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -4998,12 +5152,14 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>1. More than one value can be chosen inside the filter, and the button shows what you picked.
+          <t xml:space="preserve">1. More than one value can be chosen inside the filter, and the button shows what you picked.
 2. Clear Selection removes the choices for that one filter.
 3. A Clear Filters button appears in the filter bar while any filter is set, and using it clears them all at once - exactly as it works on the Work Orders page.
 Not built yet on the build tested: a filter bar exists on Inventory, Part Sales, Catalog and Returns, but Purchase Orders, Vendor Invoices and Vendors have no filter bar at all. If the filter bar is missing on the view you are testing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)
+AUTOMATION: HOLD - the feature is not in the product yet
+</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5053,12 +5209,14 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>1. Every filter the page offered before is still offered - nothing has been taken away.
+          <t xml:space="preserve">1. Every filter the page offered before is still offered - nothing has been taken away.
 2. Every choice each of those filters offered before is still available inside the new button.
 3. If any filter or choice is missing, write down exactly which page, which filter and which choice - that is a bug worth reporting.
 Not built yet on the build tested: a filter bar exists on Inventory, Part Sales, Catalog and Returns, but Purchase Orders, Vendor Invoices and Vendors have no filter bar at all. If the filter bar is missing on the view you are testing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)
+AUTOMATION: HOLD - the feature is not in the product yet
+</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5118,7 +5276,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>1. Timesheet Activities shows four filter buttons: Staff, Date, Status and Modified by.
+          <t xml:space="preserve">1. Timesheet Activities shows four filter buttons: Staff, Date, Status and Modified by.
 2. Payroll Timesheet shows two filter buttons: Employee and Date.
 3. Sales shows two filter buttons: Customer and Date.
 4. Technician Efficiency shows three filter buttons: Customer, Technician and Date — the same three on both of its view tabs, Invoiced and Completed. 'Technician' is spelled correctly here.
@@ -5144,7 +5302,9 @@
 24. Still to check on the live build: the real columns of the Sales Tax report and of the six A/R and A/P aging reports. The design uses sample placeholder tables for those, and the written description does not list their columns.
 Not built yet on the build tested: only the first report tab (Timesheet Activities) has a filter bar, with a Date Range and a Filter by Staff button, and no report tab has a page search box. If the controls this test needs are missing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)
+AUTOMATION: HOLD - the feature is not in the product yet
+</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5191,11 +5351,13 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>1. The report updates to show only the rows matching the chosen filter value, and the chosen value is shown on the filter button.
+          <t xml:space="preserve">1. The report updates to show only the rows matching the chosen filter value, and the chosen value is shown on the filter button.
 2. The report narrows as soon as you pick the value - there is no Apply or Run button to press. Every filter button on every report works this way.
 Not built yet on the build tested: only the first report tab (Timesheet Activities) has a filter bar, with a Date Range and a Filter by Staff button, and no report tab has a page search box. If the controls this test needs are missing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)
+AUTOMATION: HOLD - the feature is not in the product yet
+</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5248,14 +5410,16 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>&lt;ol&gt;
+          <t xml:space="preserve">&lt;ol&gt;
 &lt;li&gt;Each of these filter buttons - Location, Transaction Type, Invoice Status, Type, User and Mention - opens a list of choices, lets you tick more than one, and narrows the report straight away with no Apply button.&lt;/li&gt;
 &lt;li&gt;The choices inside each filter come from your own shop's data (for example your real vendors or categories), so there is no fixed list to compare against - check that the choices you see match the data in your shop.&lt;/li&gt;
 &lt;li&gt;Write down the choices you actually see behind each of these six buttons. They have not been written down anywhere yet, so your list becomes the record.&lt;/li&gt;
 &lt;/ol&gt;
 Not built yet on the build tested: only the first report tab (Timesheet Activities) has a filter bar, with a Date Range and a Filter by Staff button, and no report tab has a page search box. If the controls this test needs are missing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)
+AUTOMATION: HOLD - the feature is not in the product yet
+</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -5307,7 +5471,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>1. The panel that opens offers a set of ready-made periods to choose from - on the build tested these are Today, Yesterday, This week, Last week, This month, Last month, This quarter, Last quarter, This year, Last year - plus a Custom option and a Clear Selection link. The exact set of ready-made periods may differ per report, so check the ones your report offers rather than expecting this list.
+          <t xml:space="preserve">1. The panel that opens offers a set of ready-made periods to choose from - on the build tested these are Today, Yesterday, This week, Last week, This month, Last month, This quarter, Last quarter, This year, Last year - plus a Custom option and a Clear Selection link. The exact set of ready-made periods may differ per report, so check the ones your report offers rather than expecting this list.
 2. A period is already filled in when the panel first opens (on Timesheet Activities it is This month), and the button reads that period, for example "Date Range: This month".
 3. Choosing a ready-made period applies it straight away: the results update, the button reads the period you chose, and the web address records it.
 4. Choosing Custom shows a From box and a To box. After you fill in only the From date the results do NOT change yet.
@@ -5316,7 +5480,9 @@
 Note: dates are typed in month/day/year order, the way the build shows them (for example 07/01/2026).
 Where to run this on the build tested: the Reports area has this date button on the Timesheet Activities report. Other report tabs do not have a filter bar yet - if the report you open has no date button, mark this test BLOCKED, not failed.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. It follows the NEWER wording of the Filters specification version 1.6, in the revision published on the afternoon of 4 August 2026, which changed the date filter description in the Feature Overview and in the Key Decisions section: the date button now offers standard ready-made periods and starts with the current default range already filled in. An earlier revision of the same specification said the opposite, and this test follows the newer one. The specification does not give this a numbered requirement, so there is no requirement number to quote.</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. It follows the NEWER wording of the Filters specification version 1.6, in the revision published on the afternoon of 4 August 2026, which changed the date filter description in the Feature Overview and in the Key Decisions section: the date button now offers standard ready-made periods and starts with the current default range already filled in. An earlier revision of the same specification said the opposite, and this test follows the newer one. The specification does not give this a numbered requirement, so there is no requirement number to quote.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5366,12 +5532,14 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>1. The control expands in place into a small search box showing the placeholder 'Type to search'.
+          <t xml:space="preserve">1. The control expands in place into a small search box showing the placeholder 'Type to search'.
 2. The list narrows as you type, after a brief pause - and ONLY this page's list changes, nothing else in the app.
 3. The round x clears the text and the full list returns.
 4. Clicking away with an empty box collapses it back to the Search button; with text in it, the box stays open.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-R1, S13-R9, S13-R12, S13-R15).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-R1, S13-R9, S13-R12, S13-R15).
+AUTOMATION: READY - EXPECT FAIL (no ticket - reported to the QA lead as one design item, not filed)
+</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5419,11 +5587,13 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>1. With both active, the results match the filter AND the search together (both narrow the list at once).
+          <t xml:space="preserve">1. With both active, the results match the filter AND the search together (both narrow the list at once).
 2. Clearing the search keeps the filter applied.
 3. Clearing the filter keeps the search applied - each is cleared by its own control without wiping the other.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-R10, S13-R13, S8-R5).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-R10, S13-R13, S8-R5).
+AUTOMATION: READY - EXPECT FAIL (no ticket - reported to the QA lead as one design item, not filed)
+</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5473,12 +5643,14 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>1. Sorting and paging keep your search applied - your text stays in the box and the list stays narrowed.
+          <t xml:space="preserve">1. Sorting and paging keep your search applied - your text stays in the box and the list stays narrowed.
 2. Leaving the page and coming back also keeps your text in the box and the list still narrowed.
 3. The second browser tab starts clean: its Search box is empty and it shows the full list. Each tab keeps its own search.
 4. After closing the browser and coming back, the Search box is empty and the list is unsearched - a typed search is never remembered for next time (your filters, unlike the search, ARE remembered).
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-R14, S13-R25, S13-N4, S10-R5).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-R14, S13-R25, S13-N4, S10-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5525,12 +5697,14 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>1. The address contains the search term after step 1.
+          <t xml:space="preserve">1. The address contains the search term after step 1.
 2. The fresh tab opens with the search box filled and the list already narrowed.
 3. The malformed part is ignored - the page loads cleanly without an error.
 4. A search arriving via a link is view-only, the same as filters from a link - it does not overwrite your own remembered search.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S11-R4, S11-R5, S11-N2, S11-R8).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S11-R4, S11-R5, S11-N2, S11-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5578,13 +5752,15 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>1. The search expands inline inside the toolbar - no separate popup window opens.
+          <t xml:space="preserve">1. The search expands inline inside the toolbar - no separate popup window opens.
 2. The list narrows as you type, same as desktop.
 3. To make room, the page's main button no longer stretches full-width, and pages with two or more small icon buttons collapse them into a single 'more' menu.
 4. The box stretches to fill the space left in the action row instead of staying the narrow desktop size, and every other toolbar button stays visible and in the same place while you search.
 5. There is no extra 'search is on' badge on mobile: with text in it the box simply stays open showing your text, and an empty box closes back to the Search button when you tap elsewhere - exactly as on desktop.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-R16, S13-R17, S13-R18, S13-R19, S13-R20, S12-R5).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-R16, S13-R17, S13-R18, S13-R19, S13-R20, S12-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -5635,12 +5811,14 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>1. Every table listed above has its own Search box - no table lost the ability to narrow by text.
+          <t xml:space="preserve">1. Every table listed above has its own Search box - no table lost the ability to narrow by text.
 2. Each Search box narrows only its own table; nothing else in the app changes.
 3. Where the table sits inside a dialog (the Work Order Log, the Line Log, the audit log dialog), the Search box is inside that dialog and works there.
 4. The work order Parts tab keeps the local search input it already had - it was deliberately left as it is.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S14-R6, S14-R5, S13-R22, S14-N1).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S14-R6, S14-R5, S13-R22, S14-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -5688,11 +5866,13 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>1. The page list does NOT narrow while you type in the navigation search - only its dropdown of matching records appears.
+          <t xml:space="preserve">1. The page list does NOT narrow while you type in the navigation search - only its dropdown of matching records appears.
 2. The same holds on the other pages checked.
 3. Picking a dropdown result still takes you to that record - the navigation search keeps its find-and-open role.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S14-R1, S14-R2, S14-R4, S14-R5).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S14-R1, S14-R2, S14-R4, S14-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5741,14 +5921,16 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>1. A 'Search' button is shown with a small magnifier icon next to the word 'Search'; it is plain text on a see-through background, with no border and no fill.
+          <t xml:space="preserve">1. A 'Search' button is shown with a small magnifier icon next to the word 'Search'; it is plain text on a see-through background, with no border and no fill.
 2. Hovering over it gives it a light grey background; the word 'Search' keeps its own colour.
 3. Clicking it turns the button into a small text box in the same spot (the design sets it at 180 pixels wide), the typing cursor is already inside it, and the box grows towards the left so the other toolbar buttons do not move.
 4. While the box is empty it shows the magnifier icon and the grey placeholder text 'Type to search'.
 5. As soon as you type, your text shows in a dark grey and a small round x appears at the right-hand end of the box.
 6. A very long sentence does not make the box grow and does not cut the text off - the text scrolls sideways inside the box and the cursor stays where you are typing.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-R2, S13-R3, S13-R4, S13-R5, S13-R6, S13-R8).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-R2, S13-R3, S13-R4, S13-R5, S13-R6, S13-R8).
+AUTOMATION: READY - EXPECT FAIL (no ticket - reported to the QA lead as one design item, not filed)
+</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -5798,14 +5980,16 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>1. The list narrows on its own a moment after you stop typing (about a third of a second) - you never press Enter or any button.
+          <t xml:space="preserve">1. The list narrows on its own a moment after you stop typing (about a third of a second) - you never press Enter or any button.
 2. The matching rows appear in the table you were already looking at; no separate results page, results list or pop-up window opens.
 3. There is no Apply or Submit button anywhere next to the Search box.
 4. Pressing Enter changes nothing that has not already happened - the same rows stay listed and no page reload happens.
 5. Parts Inventory behaves the same way, only it waits a fraction longer before reacting; that longer wait is on purpose because that page carries more data.
 Known and accepted: the empty screen offers no way to clear the search on its own. The product behaves this way on purpose for now. Do not raise this as a new problem.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-R7, S13-R12).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-R7, S13-R12).
+AUTOMATION: READY - EXPECT FAIL (SV-8847 - closed as accepted, will not be fixed)
+</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5854,12 +6038,14 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>1. On the All tab only the rows matching your word remain.
+          <t xml:space="preserve">1. On the All tab only the rows matching your word remain.
 2. On the Estimates tab your word is still in the Search box, and the list shows only Estimates rows that match it - no rows from the other tabs appear.
 3. The Completed tab behaves the same way: your word is still there and only that tab's matching rows are listed.
 4. Clearing the search clears it for all the Work Orders tabs - they share one search - and each tab shows its full list again.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-R11, S13-R24).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-R11, S13-R24).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -5908,12 +6094,14 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>1. The second Parts view opens with an empty Search box and its full list - the word you typed on the first view is not carried over.
+          <t xml:space="preserve">1. The second Parts view opens with an empty Search box and its full list - the word you typed on the first view is not carried over.
 2. Going back to the first view brings its own word back and narrows its list again.
 3. Each report tab behaves the same way: a word typed on one tab stays on that tab only, and each tab remembers its own.
 4. No search is ever applied to a table it was not typed on.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-R24, S13-R11, S10-R4).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-R24, S13-R11, S10-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -5961,12 +6149,14 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>1. The page opens with the normal list for your own saved filters - the old search word does NOT narrow the list.
+          <t xml:space="preserve">1. The page opens with the normal list for your own saved filters - the old search word does NOT narrow the list.
 2. The page's own Search box is empty; nothing was carried into it.
 3. No error is shown - the leftover search part in the address is simply ignored. (Whether it also disappears from the address is not important; note what you see.)
 4. After typing in the top-of-screen search and reloading, the list is still not narrowed and nothing about that word was remembered for the list.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S14-R3, S14-R2, S14-R1).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S14-R3, S14-R2, S14-R1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -6014,11 +6204,13 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>1. The list stays narrowed by your word - collapsing the filter bar does not cancel the search.
+          <t xml:space="preserve">1. The list stays narrowed by your word - collapsing the filter bar does not cancel the search.
 2. The Search box stays in the toolbar row with your word still showing; it is not tucked away with the filter bar, because the search sits in the toolbar row and the chips sit in the row below.
 3. Expanding the bar again changes nothing about the search or the narrowed list.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-E1).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-E1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -6065,11 +6257,13 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>1. The list request includes the active filter selections as request parameters (status values and customer identifiers).
+          <t xml:space="preserve">1. The list request includes the active filter selections as request parameters (status values and customer identifiers).
 2. The request succeeds (HTTP 200).
 3. The response contains only work orders matching the filters - the filtering is done by the backend, not just hidden client-side.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-R2, S3-R6).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-R2, S3-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -6115,11 +6309,13 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>1. One request carries both filters together (both statuses and the customer).
+          <t xml:space="preserve">1. One request carries both filters together (both statuses and the customer).
 2. The response returns customer A's Estimate and Approved work orders only.
 3. Customer B's work orders are absent - the customer filter and status filter both restrict the result, while the two statuses combine as either-or.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-R2, S3-R6, S8-R3).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-R2, S3-R6, S8-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -6165,12 +6361,14 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>1. The backend does not fail with a server error (no HTTP 5xx).
+          <t xml:space="preserve">1. The backend does not fail with a server error (no HTTP 5xx).
 2. The response is a normal, successful list response - the invalid value is ignored or simply matches nothing.
 3. Any still-valid filter values in the same request are applied normally.
 Known issue: the server does not fail, but the value that no longer exists is still applied instead of being dropped. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8832
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S10-N1, S11-R3).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S10-N1, S11-R3).
+AUTOMATION: READY - EXPECT FAIL (SV-8832)
+</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -6217,11 +6415,13 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>1. The backend responds gracefully - no HTTP 5xx / crash; either a normal (unfiltered or empty) list or a clean validation response.
+          <t xml:space="preserve">1. The backend responds gracefully - no HTTP 5xx / crash; either a normal (unfiltered or empty) list or a clean validation response.
 2. In the browser the page still loads without filters and without an error message, matching the malformed-URL requirement.
 Known issue: the server does not fail, but a broken address is not fully ignored by the page. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8832
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S11-N1).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S11-N1).
+AUTOMATION: READY - EXPECT FAIL (SV-8832)
+</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6267,11 +6467,13 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>1. The request succeeds (HTTP 200).
+          <t xml:space="preserve">1. The request succeeds (HTTP 200).
 2. The response contains an empty result set (zero work orders) - an empty match is a normal outcome, not an error.
 3. The page renders the no-results empty state from this response.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S8-R3, S2-N3).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S8-R3, S2-N3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6319,13 +6521,15 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>1. Changing a filter sends a save (PUT) to the per-user page-preferences service carrying the page's state, and it succeeds (HTTP 200).
+          <t xml:space="preserve">1. Changing a filter sends a save (PUT) to the per-user page-preferences service carrying the page's state, and it succeeds (HTTP 200).
 2. On reload the page requests the saved state back (GET, HTTP 200) and applies it - the filters return without you redoing them.
 3. The second user does NOT receive the first user's saved state - each account's saved filters are isolated.
 4. Asking for a never-saved key returns success with an empty value, not an error page.
 Step 3 needs a SECOND sign-in of your own. We could not run it for you: impersonating another user on this branch returns an error, and a new staff member cannot finish signing up because the invitation email cannot be received here. If you have a second account, run step 3 normally. If you do not, mark this test BLOCKED - do not mark it failed. Steps 1, 2 and 4 were confirmed working.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S10-R2, S10-R3).</t>
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S10-R2, S10-R3).
+AUTOMATION: HOLD - needs a second test login to prove one person's saved filters do not reach another
+</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">

--- a/testrail-import/filters-v1-testrail-import.xlsx
+++ b/testrail-import/filters-v1-testrail-import.xlsx
@@ -510,28 +510,20 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;You are signed in to the ShopView App on a desktop browser.&lt;/li&gt;
-&lt;li&gt;At least a few work orders exist in the shop.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. At least a few work orders exist in the shop.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;Open the Work Orders page.&lt;/li&gt;
-&lt;li&gt;Look at the area directly under the tab row (All, Estimates, Completed, My Work Orders).&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. Open the Work Orders page.
+2. Look at the area directly under the tab row (All, Estimates, Completed, My Work Orders).</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;A filter bar is visible directly below the tab row and above the work order table.&lt;/li&gt;
-&lt;li&gt;The filter bar is shown by default (expanded) without having to turn anything on.&lt;/li&gt;
-&lt;/ol&gt;
+          <t xml:space="preserve">1. A filter bar is visible directly below the tab row and above the work order table.
+2. The filter bar is shown by default (expanded) without having to turn anything on.
 Known and accepted: on the build tested the filter buttons sit on the same row as the tabs instead of on their own row below them. The product behaves this way on purpose for now. Do not raise this as a new problem.
 ---
 This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S1-R1).
@@ -675,32 +667,24 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;You are signed in to the ShopView App on a desktop browser.&lt;/li&gt;
-&lt;li&gt;You are on the Work Orders page on the All or My Work Orders tab.&lt;/li&gt;
-&lt;li&gt;No filters are currently selected.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Work Orders page on the All or My Work Orders tab.
+3. No filters are currently selected.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;Click the Status filter chip.&lt;/li&gt;
-&lt;li&gt;Read the list of options from top to bottom.&lt;/li&gt;
-&lt;li&gt;Look at the bottom of the dropdown panel.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. Click the Status filter chip.
+2. Read the list of options from top to bottom.
+3. Look at the bottom of the dropdown panel.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;A dropdown panel opens under the Status chip.&lt;/li&gt;
-&lt;li&gt;It lists all nine statuses as checkboxes, in this order: Estimate, Approved, In progress, Review, Complete, Invoiced, Paid, Declined, Imported.&lt;/li&gt;
-&lt;li&gt;All checkboxes are unticked (nothing selected yet).&lt;/li&gt;
-&lt;li&gt;A 'Clear Selection' action is shown at the bottom of the dropdown.&lt;/li&gt;
-&lt;/ol&gt;
+          <t xml:space="preserve">1. A dropdown panel opens under the Status chip.
+2. It lists all nine statuses as checkboxes, in this order: Estimate, Approved, In progress, Review, Complete, Invoiced, Paid, Declined, Imported.
+3. All checkboxes are unticked (nothing selected yet).
+4. A 'Clear Selection' action is shown at the bottom of the dropdown.
 ---
 This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-R1, S2-R4).
 AUTOMATION: READY
@@ -1064,32 +1048,24 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;You are signed in to the ShopView App on a desktop browser.&lt;/li&gt;
-&lt;li&gt;You are on the Work Orders page.&lt;/li&gt;
-&lt;li&gt;Several customers exist in the shop.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Work Orders page.
+3. Several customers exist in the shop.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;Click the Customer filter chip.&lt;/li&gt;
-&lt;li&gt;Look at the top of the dropdown panel and the list below it.&lt;/li&gt;
-&lt;li&gt;Look at the bottom of the panel.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. Click the Customer filter chip.
+2. Look at the top of the dropdown panel and the list below it.
+3. Look at the bottom of the panel.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;A dropdown panel opens under the Customer chip.&lt;/li&gt;
-&lt;li&gt;A search box with the placeholder 'Search' is at the top of the panel. Click it before you type - it is not focused for you automatically.&lt;/li&gt;
-&lt;li&gt;Below it is a scrollable list of customer names.&lt;/li&gt;
-&lt;li&gt;A 'Clear Selection' action is shown at the bottom of the panel.&lt;/li&gt;
-&lt;/ol&gt;
+          <t xml:space="preserve">1. A dropdown panel opens under the Customer chip.
+2. A search box with the placeholder 'Search' is at the top of the panel. Click it before you type - it is not focused for you automatically.
+3. Below it is a scrollable list of customer names.
+4. A 'Clear Selection' action is shown at the bottom of the panel.
 ---
 This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-R1).
 AUTOMATION: READY
@@ -1180,32 +1156,24 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;You are signed in to the ShopView App on a desktop browser.&lt;/li&gt;
-&lt;li&gt;You are on the Work Orders page with the Customer dropdown open.&lt;/li&gt;
-&lt;li&gt;At least three customers exist.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Work Orders page with the Customer dropdown open.
+3. At least three customers exist.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;Click one customer in the list.&lt;/li&gt;
-&lt;li&gt;Click a second and a third customer.&lt;/li&gt;
-&lt;li&gt;Look at the input area at the top of the dropdown and at the list rows.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. Click one customer in the list.
+2. Click a second and a third customer.
+3. Look at the input area at the top of the dropdown and at the list rows.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;Each selected customer appears as a tag (small chip) with an x in the input area at the top of the dropdown.&lt;/li&gt;
-&lt;li&gt;Each selected customer's row in the list shows a checkmark on the right.&lt;/li&gt;
-&lt;li&gt;Long customer names on tags are shortened with an ellipsis (for example 'Texas Truck And Aut...').&lt;/li&gt;
-&lt;li&gt;You can keep selecting as many customers as needed - there is no selection limit.&lt;/li&gt;
-&lt;/ol&gt;
+          <t xml:space="preserve">1. Each selected customer appears as a tag (small chip) with an x in the input area at the top of the dropdown.
+2. Each selected customer's row in the list shows a checkmark on the right.
+3. Long customer names on tags are shortened with an ellipsis (for example 'Texas Truck And Aut...').
+4. You can keep selecting as many customers as needed - there is no selection limit.
 ---
 This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-R3, S3-R4).
 AUTOMATION: READY
@@ -1458,29 +1426,21 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;You are signed in to the ShopView App on a desktop browser.&lt;/li&gt;
-&lt;li&gt;You are on the Work Orders page with the Customer dropdown open.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Work Orders page with the Customer dropdown open.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;Type a string that matches no customer name (for example 'zzzqqq').&lt;/li&gt;
-&lt;li&gt;Look at the list area of the dropdown.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. Type a string that matches no customer name (for example 'zzzqqq').
+2. Look at the list area of the dropdown.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;The list shows a message saying there are no results (instead of an empty gap).&lt;/li&gt;
-&lt;li&gt;The app does not show an error.&lt;/li&gt;
-&lt;li&gt;Clearing the search text brings the customer list back.&lt;/li&gt;
-&lt;/ol&gt;
+          <t xml:space="preserve">1. The list shows a message saying there are no results (instead of an empty gap).
+2. The app does not show an error.
+3. Clearing the search text brings the customer list back.
 ---
 This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-N1).
 AUTOMATION: READY
@@ -1572,31 +1532,23 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;You are signed in to the ShopView App on a desktop browser.&lt;/li&gt;
-&lt;li&gt;You are on the Work Orders page.&lt;/li&gt;
-&lt;li&gt;Several technicians exist in the shop.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Work Orders page.
+3. Several technicians exist in the shop.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;Click the Lead Technician filter chip.&lt;/li&gt;
-&lt;li&gt;Look at the top of the dropdown, the list below and the bottom of the panel.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. Click the Lead Technician filter chip.
+2. Look at the top of the dropdown, the list below and the bottom of the panel.</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;A dropdown panel opens under the Lead Technician chip.&lt;/li&gt;
-&lt;li&gt;A search input with the placeholder 'Search' is at the top.&lt;/li&gt;
-&lt;li&gt;Below it is a scrollable list of technician names.&lt;/li&gt;
-&lt;li&gt;A 'Clear Selection' action is shown at the bottom.&lt;/li&gt;
-&lt;/ol&gt;
+          <t xml:space="preserve">1. A dropdown panel opens under the Lead Technician chip.
+2. A search input with the placeholder 'Search' is at the top.
+3. Below it is a scrollable list of technician names.
+4. A 'Clear Selection' action is shown at the bottom.
 ---
 This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S4-R1).
 AUTOMATION: READY
@@ -1948,31 +1900,23 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;You are signed in to the ShopView App on a desktop browser.&lt;/li&gt;
-&lt;li&gt;You are on the Work Orders page.&lt;/li&gt;
-&lt;li&gt;Several service advisors exist in the shop.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Work Orders page.
+3. Several service advisors exist in the shop.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;Click the Service Advisor filter chip.&lt;/li&gt;
-&lt;li&gt;Look at the top of the dropdown, the list below and the bottom of the panel.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. Click the Service Advisor filter chip.
+2. Look at the top of the dropdown, the list below and the bottom of the panel.</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;A dropdown panel opens under the Service Advisor chip.&lt;/li&gt;
-&lt;li&gt;A search input with the placeholder 'Search' is at the top.&lt;/li&gt;
-&lt;li&gt;Below it is a scrollable list of advisor names.&lt;/li&gt;
-&lt;li&gt;A 'Clear Selection' action is shown at the bottom.&lt;/li&gt;
-&lt;/ol&gt;
+          <t xml:space="preserve">1. A dropdown panel opens under the Service Advisor chip.
+2. A search input with the placeholder 'Search' is at the top.
+3. Below it is a scrollable list of advisor names.
+4. A 'Clear Selection' action is shown at the bottom.
 ---
 This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S5-R1).
 AUTOMATION: READY
@@ -3724,7 +3668,7 @@
           <t xml:space="preserve">1. On the very first visit the Estimates tab is the selected one, even though All is the FIRST tab in the row (order and default are different on purpose).
 2. After switching to All and returning, the All tab is selected - the app remembers your last-used tab per account.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md)
 AUTOMATION: READY
 </t>
         </is>
@@ -3760,33 +3704,23 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;You are signed in to the ShopView App on a desktop browser.&lt;/li&gt;
-&lt;li&gt;You are on the Work Orders page with a Status and a Customer selection active and the filter bar expanded.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Work Orders page with a Status and a Customer selection active and the filter bar expanded.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;Open one work order from the list (go to its detail page).&lt;/li&gt;
-&lt;li&gt;Go back to the Work Orders page.&lt;/li&gt;
-&lt;li&gt;Look at the chips, the table and the filter bar state.&lt;/li&gt;
-&lt;li&gt;Repeat the round-trip once more with the filter bar collapsed before leaving.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. Open one work order from the list (go to its detail page).
+2. Go back to the Work Orders page.
+3. Look at the chips, the table and the filter bar state.
+4. Repeat the round-trip once more with the filter bar collapsed before leaving.</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;After step 2 the same Status and Customer selections are still applied - chips active with the same values, table filtered the same way.&lt;/li&gt;
-&lt;li&gt;The filter bar is still expanded (as you left it).&lt;/li&gt;
-&lt;li&gt;After step 4 the filter bar comes back collapsed - the collapsed/expanded state is restored too.&lt;/li&gt;
-&lt;/ol&gt;
-&lt;hr /&gt;
-&lt;p&gt;This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 (S10-R1, S1-R7).&lt;/p&gt;
+          <t xml:space="preserve">1. After step 2 the same Status and Customer selections are still applied - chips active with the same values, table filtered the same way.
+2. The filter bar is still expanded (as you left it).
+3. After step 4 the filter bar comes back collapsed - the collapsed/expanded state is restored too.
 Known issue: on the build tested the Customer, Lead Technician and Service Advisor buttons come back switched on but WITHOUT the name of the value you picked - the button reads just "Customer" instead of "Customer: Iibay Landscaping". The list is still filtered correctly. The Status and Asset on Site buttons keep their value. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8871
 ---
 This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S10-R1, S1-R7).
@@ -4434,12 +4368,13 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>1. A filter chip row is shown below the tabs, starting with an 'All Filters' chip (with a filter icon) followed by the individual filter chips (Status, Customer, Lead Technician, ...).
+          <t xml:space="preserve">1. A filter chip row is shown below the tabs, starting with an 'All Filters' chip (with a filter icon) followed by the individual filter chips (Status, Customer, Lead Technician, ...).
 2. The row scrolls horizontally - chips that do not fit are reachable by swiping.
 3. An arrow at the right-hand edge shows that the row can be scrolled. (This is what the design shows - if your screen looks different, write down what you actually see and carry on.)
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour. The question is open as SV-8825 (https://shopview.atlassian.net/browse/SV-8825). Branko answered our sheet on 2026-08-04 saying a single filter window on a phone applies straight away with no Apply button, which is what the build does; hours later he added a new rule to the specification saying a phone should only apply when you tap an "Apply filters" button. Both come from him on the same day, so we are not choosing between them. His answers are in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)
----
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R1). The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R1). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). This has not been checked against the running app in this pass, so no build or test date is claimed for it.
+AUTOMATION: HOLD - needs one live check on the current build to confirm whether the 'Apply filters' button is present on a phone
+</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4485,12 +4420,13 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>1. A bottom sheet slides up with a drag handle at the top, the centered title 'All Filters' and a close (x) button.
+          <t xml:space="preserve">1. A bottom sheet slides up with a drag handle at the top, the centered title 'All Filters' and a close (x) button.
 2. It lists the five filters as expandable accordion rows, each with its icon, name and a down arrow: Status, Customer, Lead Technician, Service Advisor, Asset on Site.
 3. A sticky blue 'Apply filters' button sits at the bottom of the sheet.
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour. The question is open as SV-8825 (https://shopview.atlassian.net/browse/SV-8825). Branko answered our sheet on 2026-08-04 saying a single filter window on a phone applies straight away with no Apply button, which is what the build does; hours later he added a new rule to the specification saying a phone should only apply when you tap an "Apply filters" button. Both come from him on the same day, so we are not choosing between them. His answers are in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)
----
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R3). The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R3, S12-R6). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). This has not been checked against the running app in this pass, so no build or test date is claimed for it.
+AUTOMATION: HOLD - needs one live check on the current build to confirm whether the 'Apply filters' button is present on a phone
+</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4539,12 +4475,13 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>1. Expanding Status reveals the same nine status checkboxes as desktop (Estimate, Approved, In progress, Review, Complete, Invoiced, Paid, Declined, Imported) plus 'Clear Selection'.
+          <t xml:space="preserve">1. Expanding Status reveals the same nine status checkboxes as desktop (Estimate, Approved, In progress, Review, Complete, Invoiced, Paid, Declined, Imported) plus 'Clear Selection'.
 2. After 'Apply filters' the sheet closes and the work order list shows only the ticked statuses.
 3. The reopened sheet's title shows the applied-filter count, for example 'All Filters (1)', and the Status accordion header is highlighted with the selected values ticked.
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour. The question is open as SV-8825 (https://shopview.atlassian.net/browse/SV-8825). Branko answered our sheet on 2026-08-04 saying a single filter window on a phone applies straight away with no Apply button, which is what the build does; hours later he added a new rule to the specification saying a phone should only apply when you tap an "Apply filters" button. Both come from him on the same day, so we are not choosing between them. His answers are in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)
----
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R2, S12-R3, S2-R1). The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R2, S12-R3, S12-R6, S2-R1). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). This has not been checked against the running app in this pass, so no build or test date is claimed for it.
+AUTOMATION: HOLD - needs one live check on the current build to confirm whether the 'Apply filters' button is present on a phone
+</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4558,7 +4495,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Mobile: tapping one chip opens its own sheet and applies in real time</t>
+          <t>Mobile: one chip opens its own sheet and applies only on Apply filters</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4586,19 +4523,23 @@
         <is>
           <t>1. Tap the Status chip (not the 'All Filters' chip).
 2. Read the sheet that opens.
-3. Tick one status and watch the work order list.
-4. Untick it, then tick a different status, and watch the list again.</t>
+3. Tick one status, then tick a second one, and watch the work order list while you do it.
+4. Tap the 'Apply filters' button inside the sheet and look at the list again.</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>1. A bottom sheet opens for that single filter: its title row shows the filter's icon and name (for example 'Status') with a close (x) button, and no accordion list of the other filters.
+          <t xml:space="preserve">1. A bottom sheet opens for that single filter: its title row shows the filter's icon and name (for example 'Status') with a close (x) button, and no accordion list of the other filters.
 2. The sheet shows only that filter's options (the nine status checkboxes plus 'Clear Selection').
-3. There is no 'Apply filter' button. Ticking or unticking a status filters the work order list immediately, the same as on desktop, with no submit step.
-4. The chip's active state and value update live as the selection changes; closing the sheet with the x just dismisses it and keeps the applied filter.
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour. The question is open as SV-8825 (https://shopview.atlassian.net/browse/SV-8825). Branko answered our sheet on 2026-08-04 saying a single filter window on a phone applies straight away with no Apply button, which is what the build does; hours later he added a new rule to the specification saying a phone should only apply when you tap an "Apply filters" button. Both come from him on the same day, so we are not choosing between them. His answers are in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)
----
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R2, S12-R3, S2-R6). The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
+3. You can tick more than one option, and the work order list does NOT change while you tick - your choices are only being held, not applied yet.
+4. An 'Apply filters' button is shown inside the sheet. Tapping it applies your choices: the sheet closes and the list shows only the ticked statuses.
+5. The chip then shows its active state with the value(s) you picked. 'Clear Selection' and 'Clear Filters' work the same way as on desktop.
+Known issue reported by the test team: a single filter's own sheet is reported to allow only one value and to have no 'Apply filters' button, filtering the list the moment you tap a value, while only the combined 'All Filters' sheet holds your choices until you press a button. That is reported as https://shopview.atlassian.net/browse/SV-8875 and it is still open. We have not re-checked it on the current build, so if you can run this test, write down what you actually see.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R2, S12-R6, S2-R2). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). This has not been checked against the running app in this pass, so no build or test date is claimed for it.
+Please note this is a change from what this test used to say. It used to expect a single filter's sheet to filter the list straight away with no 'Apply filters' button. Branko asked for the new behaviour in the specification and confirmed it on 5 August 2026 when he closed our question (https://shopview.atlassian.net/browse/SV-8825), saying it is written in the specification. The earlier position came from his own written answers of 4 August 2026, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md), where he said a single filter window applies straight away with no button. We have taken his latest word as the one that counts, so if you remember the old behaviour, do not raise it as a new problem.
+AUTOMATION: HOLD - needs one live check on the current build to confirm whether the 'Apply filters' button is present on a phone
+</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -4632,36 +4573,29 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;You are signed in to the ShopView App on a mobile device.&lt;/li&gt;
-&lt;li&gt;You are on the Work Orders page; several customers exist.&lt;/li&gt;
-&lt;li&gt;The All Filters sheet is open with the Customer accordion expanded.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. You are signed in to the ShopView App on a mobile device.
+2. You are on the Work Orders page; several customers exist.
+3. The All Filters sheet is open with the Customer accordion expanded.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;Type part of a customer name in the 'Search' field and watch the list.&lt;/li&gt;
-&lt;li&gt;Select two or three customers.&lt;/li&gt;
-&lt;li&gt;Look at the input area and the list rows.&lt;/li&gt;
-&lt;li&gt;Remove one customer with the x on its tag, then tap 'Apply filters'.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. Type part of a customer name in the 'Search' field and watch the list.
+2. Select two or three customers.
+3. Look at the input area and the list rows.
+4. Remove one customer with the x on its tag, then tap 'Apply filters'.</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>&lt;ol&gt;
-&lt;li&gt;The list narrows to matching names as you type.&lt;/li&gt;
-&lt;li&gt;Each selected customer appears as a tag with an x in the input area, and its list row shows a checkmark.&lt;/li&gt;
-&lt;li&gt;Removing a tag deselects just that customer.&lt;/li&gt;
-&lt;li&gt;After 'Apply filters' the list shows only work orders of the remaining selected customers, and the sheet title counts the applied filters (for example 'All Filters (2)').&lt;/li&gt;
-&lt;/ol&gt;
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour. The question is open as SV-8825 (https://shopview.atlassian.net/browse/SV-8825). Branko answered our sheet on 2026-08-04 saying a single filter window on a phone applies straight away with no Apply button, which is what the build does; hours later he added a new rule to the specification saying a phone should only apply when you tap an "Apply filters" button. Both come from him on the same day, so we are not choosing between them. His answers are in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)
----
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R2, S3-R2). The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
+          <t xml:space="preserve">1. The list narrows to matching names as you type.
+2. Each selected customer appears as a tag with an x in the input area, and its list row shows a checkmark.
+3. Removing a tag deselects just that customer.
+4. After 'Apply filters' the list shows only work orders of the remaining selected customers, and the sheet title counts the applied filters (for example 'All Filters (2)').
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R2, S12-R6, S3-R2, S3-R3). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). This has not been checked against the running app in this pass, so no build or test date is claimed for it.
+AUTOMATION: HOLD - needs one live check on the current build to confirm whether the 'Apply filters' button is present on a phone
+</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4709,12 +4643,13 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>1. The Lead Technician row opens with a 'Search' field and the technician list.
+          <t xml:space="preserve">1. The Lead Technician row opens with a 'Search' field and the technician list.
 2. The Service Advisor row opens with a 'Search' field and the advisor list.
 3. Applying a selection filters the work order list just like on desktop.
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour. The question is open as SV-8825 (https://shopview.atlassian.net/browse/SV-8825). Branko answered our sheet on 2026-08-04 saying a single filter window on a phone applies straight away with no Apply button, which is what the build does; hours later he added a new rule to the specification saying a phone should only apply when you tap an "Apply filters" button. Both come from him on the same day, so we are not choosing between them. His answers are in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)
----
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R2, S4-R1, S5-R1). The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R2, S12-R6, S4-R1, S5-R1). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). This has not been checked against the running app in this pass, so no build or test date is claimed for it.
+AUTOMATION: HOLD - needs one live check on the current build to confirm whether the 'Apply filters' button is present on a phone
+</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -4762,12 +4697,13 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>1. The Asset on Site row opens showing the two options Yes and No plus 'Clear Selection'.
+          <t xml:space="preserve">1. The Asset on Site row opens showing the two options Yes and No plus 'Clear Selection'.
 2. Only one option can be selected at a time.
 3. After applying, the list shows only work orders matching the chosen on-site state.
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour. The question is open as SV-8825 (https://shopview.atlassian.net/browse/SV-8825). Branko answered our sheet on 2026-08-04 saying a single filter window on a phone applies straight away with no Apply button, which is what the build does; hours later he added a new rule to the specification saying a phone should only apply when you tap an "Apply filters" button. Both come from him on the same day, so we are not choosing between them. His answers are in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)
----
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R2, S6-R1). The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R2, S12-R6, S6-R1). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). This has not been checked against the running app in this pass, so no build or test date is claimed for it.
+AUTOMATION: HOLD - needs one live check on the current build to confirm whether the 'Apply filters' button is present on a phone
+</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4918,13 +4854,14 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>1. The list shows the same no-results empty state as desktop, saying no results were found for the current filters.
+          <t xml:space="preserve">1. The list shows the same no-results empty state as desktop, saying no results were found for the current filters.
 2. The empty state includes the prompt to clear filters.
 3. No error appears.
 Known issue: on a phone a link carrying filters shows the buttons as on but lists the wrong work orders. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8845
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour. The question is open as SV-8825 (https://shopview.atlassian.net/browse/SV-8825). Branko answered our sheet on 2026-08-04 saying a single filter window on a phone applies straight away with no Apply button, which is what the build does; hours later he added a new rule to the specification saying a phone should only apply when you tap an "Apply filters" button. Both come from him on the same day, so we are not choosing between them. His answers are in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)
----
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-N1, S8-R3). The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)</t>
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-N1, S8-R3). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). This has not been checked against the running app in this pass, so no build or test date is claimed for it.
+AUTOMATION: HOLD - needs one live check on the current build to confirm whether the 'Apply filters' button is present on a phone
+</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4993,7 +4930,7 @@
 13. Still to check on the live build: what the filter icon and the column/layout icon do (the written description does not cover the toolbar icons).
 Not built yet on the build tested: a filter bar exists on Inventory, Part Sales, Catalog and Returns, but Purchase Orders, Vendor Invoices and Vendors have no filter bar at all. If the filter bar is missing on the view you are testing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md)
 AUTOMATION: HOLD - the feature is not in the product yet
 </t>
         </is>
@@ -5049,7 +4986,7 @@
 4. As soon as you tick a choice the list below narrows to matching parts straight away, with no Apply button to press; Clear Selection puts the list back.
 Not built yet on the build tested: a filter bar exists on Inventory, Part Sales, Catalog and Returns, but Purchase Orders, Vendor Invoices and Vendors have no filter bar at all. If the filter bar is missing on the view you are testing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md)
 AUTOMATION: HOLD - the feature is not in the product yet
 </t>
         </is>
@@ -5103,7 +5040,7 @@
 3. The list narrows as soon as you pick the value - there is no Apply or Search button to press. Every filter button on every Parts page works this way.
 Not built yet on the build tested: a filter bar exists on Inventory, Part Sales, Catalog and Returns, but Purchase Orders, Vendor Invoices and Vendors have no filter bar at all. If the filter bar is missing on the view you are testing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md)
 AUTOMATION: HOLD - the feature is not in the product yet
 </t>
         </is>
@@ -5157,7 +5094,7 @@
 3. A Clear Filters button appears in the filter bar while any filter is set, and using it clears them all at once - exactly as it works on the Work Orders page.
 Not built yet on the build tested: a filter bar exists on Inventory, Part Sales, Catalog and Returns, but Purchase Orders, Vendor Invoices and Vendors have no filter bar at all. If the filter bar is missing on the view you are testing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md)
 AUTOMATION: HOLD - the feature is not in the product yet
 </t>
         </is>
@@ -5214,7 +5151,7 @@
 3. If any filter or choice is missing, write down exactly which page, which filter and which choice - that is a bug worth reporting.
 Not built yet on the build tested: a filter bar exists on Inventory, Part Sales, Catalog and Returns, but Purchase Orders, Vendor Invoices and Vendors have no filter bar at all. If the filter bar is missing on the view you are testing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md)
 AUTOMATION: HOLD - the feature is not in the product yet
 </t>
         </is>
@@ -5302,7 +5239,7 @@
 24. Still to check on the live build: the real columns of the Sales Tax report and of the six A/R and A/P aging reports. The design uses sample placeholder tables for those, and the written description does not list their columns.
 Not built yet on the build tested: only the first report tab (Timesheet Activities) has a filter bar, with a Date Range and a Filter by Staff button, and no report tab has a page search box. If the controls this test needs are missing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md)
 AUTOMATION: HOLD - the feature is not in the product yet
 </t>
         </is>
@@ -5355,7 +5292,7 @@
 2. The report narrows as soon as you pick the value - there is no Apply or Run button to press. Every filter button on every report works this way.
 Not built yet on the build tested: only the first report tab (Timesheet Activities) has a filter bar, with a Date Range and a Filter by Staff button, and no report tab has a page search box. If the controls this test needs are missing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md)
 AUTOMATION: HOLD - the feature is not in the product yet
 </t>
         </is>
@@ -5391,33 +5328,25 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;You are signed in to the ShopView App on a desktop browser.&lt;/li&gt;
-&lt;li&gt;You are on the Reports area of the app with some sample data present.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Reports area of the app with some sample data present.</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;Open the Reports area and go to a report that uses them - for example A/R Aging Detail (Location, Transaction Type) or Notes (Mention).&lt;/li&gt;
-&lt;li&gt;Look at the filter buttons shown above the report table.&lt;/li&gt;
-&lt;li&gt;Open each of those filter buttons in turn, tick two choices where possible, and watch the report.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. Open the Reports area and go to a report that uses them - for example A/R Aging Detail (Location, Transaction Type) or Notes (Mention).
+2. Look at the filter buttons shown above the report table.
+3. Open each of those filter buttons in turn, tick two choices where possible, and watch the report.</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;Each of these filter buttons - Location, Transaction Type, Invoice Status, Type, User and Mention - opens a list of choices, lets you tick more than one, and narrows the report straight away with no Apply button.&lt;/li&gt;
-&lt;li&gt;The choices inside each filter come from your own shop's data (for example your real vendors or categories), so there is no fixed list to compare against - check that the choices you see match the data in your shop.&lt;/li&gt;
-&lt;li&gt;Write down the choices you actually see behind each of these six buttons. They have not been written down anywhere yet, so your list becomes the record.&lt;/li&gt;
-&lt;/ol&gt;
+          <t xml:space="preserve">1. Each of these filter buttons - Location, Transaction Type, Invoice Status, Type, User and Mention - opens a list of choices, lets you tick more than one, and narrows the report straight away with no Apply button.
+2. The choices inside each filter come from your own shop's data (for example your real vendors or categories), so there is no fixed list to compare against - check that the choices you see match the data in your shop.
+3. Write down the choices you actually see behind each of these six buttons. They have not been written down anywhere yet, so your list becomes the record.
 Not built yet on the build tested: only the first report tab (Timesheet Activities) has a filter bar, with a Date Range and a Filter by Staff button, and no report tab has a page search box. If the controls this test needs are missing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bmuzamil-shopview/Manual-test-Cases/blob/main/build/filters/branko-answers-2026-08-04/answers-ingested.md)
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md)
 AUTOMATION: HOLD - the feature is not in the product yet
 </t>
         </is>

--- a/testrail-import/filters-v1-testrail-import.xlsx
+++ b/testrail-import/filters-v1-testrail-import.xlsx
@@ -524,10 +524,10 @@
         <is>
           <t xml:space="preserve">1. A filter bar is visible directly below the tab row and above the work order table.
 2. The filter bar is shown by default (expanded) without having to turn anything on.
-Known and accepted: on the build tested the filter buttons sit on the same row as the tabs instead of on their own row below them. The product behaves this way on purpose for now. Do not raise this as a new problem.
----
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S1-R1).
-AUTOMATION: READY - EXPECT FAIL (SV-8843 - closed as accepted, will not be fixed)
+Note for the tester: on the build this test was run against, the five filter buttons sit to the RIGHT of the tab row instead of on their own row beneath it, so point 1 fails. That has been reported and the report was closed without a fix, so do not expect it to change - record it as a fail against point 1 and move on.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S1-R1). It was checked against the build on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), which does not behave this way yet.
+AUTOMATION: READY - EXPECT FAIL (SV-8843 - reported, closed without a fix)
 </t>
         </is>
       </c>
@@ -579,7 +579,7 @@
 2. Each chip shows the filter name and a down arrow (chevron) indicating it opens a dropdown.
 3. Each chip shows only the filter name and the arrow - there is no picture icon in front of the name.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S1-R2, S1-R3). Note: the design frame also draws a small picture icon in front of each filter name; the specification asks only for the name and the arrow, and the build matches the specification, so this test follows the specification and the build.
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S1-R2, S1-R3). Note: the design frame also draws a small picture icon in front of each filter name; the specification asks only for the name and the arrow, and the build matches the specification, so this test follows the specification and the build.
 AUTOMATION: READY
 </t>
         </is>
@@ -631,7 +631,7 @@
 2. The Customer, Lead Technician, Service Advisor and Asset on Site chips are all displayed and usable.
 3. The Status chip is not shown on this tab at all - only four chips appear.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S1-N1, S9-R2). Note: an earlier answer of 2026-07-17 and the design frame both show the Status button greyed out and pre-filled on this tab; the specification and the build both hide it, and the specification is the newer source, so this test follows the specification and the build.
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S1-N1, S9-R2). Note: an earlier answer of 2026-07-17 and the design frame both show the Status button greyed out and pre-filled on this tab; the specification and the build both hide it, and the specification is the newer source, so this test follows the specification and the build.
 AUTOMATION: READY
 </t>
         </is>
@@ -686,7 +686,7 @@
 3. All checkboxes are unticked (nothing selected yet).
 4. A 'Clear Selection' action is shown at the bottom of the dropdown.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-R1, S2-R4).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R1, S2-R4).
 AUTOMATION: READY
 </t>
         </is>
@@ -740,7 +740,7 @@
 2. The table updates immediately to show only work orders in the selected status - there is no confirm or apply button on desktop.
 3. Work orders in other statuses are no longer listed.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-R2, S2-R3, S2-R6).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R2, S2-R3, S2-R6).
 AUTOMATION: READY
 </t>
         </is>
@@ -795,7 +795,7 @@
 3. Work orders in statuses that are not ticked are hidden.
 4. There is no limit on how many statuses you can tick.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-R2).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R2).
 AUTOMATION: READY
 </t>
         </is>
@@ -849,7 +849,7 @@
 2. The Status filter is removed and the table returns to showing work orders of every status.
 3. Only the Status filter is affected - any other active filters stay applied.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-R4, S8-R2).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R4, S8-R2).
 AUTOMATION: READY
 </t>
         </is>
@@ -902,7 +902,7 @@
 2. The ticked statuses stay selected - the Status chip stays in its active state showing the selection.
 3. The table stays filtered by the selected statuses.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-R5).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R5).
 AUTOMATION: READY
 </t>
         </is>
@@ -956,7 +956,7 @@
 2. An empty state is displayed saying no results were found for the current filters (see the Empty State cases for its full content).
 3. The app does not show an error.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-N3, S8-R3).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-N3, S8-R3).
 AUTOMATION: READY
 </t>
         </is>
@@ -1012,7 +1012,7 @@
 3. Imported cannot be combined with other statuses - selecting it works alone.
 4. Unticking Imported re-enables the other chips and the normal list returns.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-R7, S2-N4).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R7, S2-N4).
 AUTOMATION: READY
 </t>
         </is>
@@ -1067,7 +1067,7 @@
 3. Below it is a scrollable list of customer names.
 4. A 'Clear Selection' action is shown at the bottom of the panel.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-R1).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R1).
 AUTOMATION: READY
 </t>
         </is>
@@ -1120,7 +1120,7 @@
 2. Customers that do not match are removed from the list.
 3. Deleting the text brings the full list back.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-R2).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R2).
 AUTOMATION: READY
 </t>
         </is>
@@ -1175,7 +1175,7 @@
 3. Long customer names on tags are shortened with an ellipsis (for example 'Texas Truck And Aut...').
 4. You can keep selecting as many customers as needed - there is no selection limit.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-R3, S3-R4).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R3, S3-R4).
 AUTOMATION: READY
 </t>
         </is>
@@ -1229,7 +1229,7 @@
 3. The other selected customers keep their tags and checkmarks.
 4. The table updates to no longer include that customer's work orders.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-R5).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R5).
 AUTOMATION: READY
 </t>
         </is>
@@ -1282,7 +1282,7 @@
 2. Work orders belonging to any other customer are hidden.
 3. The table updates in real time as you make the selections (no apply button on desktop).
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-R6, S2-R6).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R6, S2-R6).
 AUTOMATION: READY
 </t>
         </is>
@@ -1337,7 +1337,7 @@
 3. The Customer filter is removed and the table shows work orders of all customers again.
 4. Other active filters (if any) are not affected.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-R7, S8-R2).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R7, S8-R2).
 AUTOMATION: READY
 </t>
         </is>
@@ -1390,7 +1390,7 @@
 2. The Customer chip stays in the active (blue) state showing the selection and the table stays filtered.
 3. When reopened, the selected customers' tags are still visible in the input area.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-R8).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R8).
 AUTOMATION: READY
 </t>
         </is>
@@ -1442,7 +1442,7 @@
 2. The app does not show an error.
 3. Clearing the search text brings the customer list back.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-N1).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-N1).
 AUTOMATION: READY
 </t>
         </is>
@@ -1496,7 +1496,7 @@
 2. After selecting only that customer, the table shows no rows and the filtered empty state is displayed.
 3. No error is shown.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S3-E1, S3-N2, S8-R3).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-E1, S3-N2, S8-R3).
 AUTOMATION: READY
 </t>
         </is>
@@ -1550,7 +1550,7 @@
 3. Below it is a scrollable list of technician names.
 4. A 'Clear Selection' action is shown at the bottom.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S4-R1).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-R1).
 AUTOMATION: READY
 </t>
         </is>
@@ -1601,7 +1601,7 @@
           <t xml:space="preserve">1. The technician list narrows to only the names matching what you typed.
 2. Deleting the text brings the full list back.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S4-R2).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-R2).
 AUTOMATION: READY
 </t>
         </is>
@@ -1655,7 +1655,7 @@
 3. A work order where the technician is assigned only in a non-lead role does not appear.
 4. The table updates in real time as you select.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S4-R3, S4-R4).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-R3, S4-R4).
 AUTOMATION: READY
 </t>
         </is>
@@ -1708,7 +1708,7 @@
 2. The Lead Technician filter no longer restricts the table.
 3. Other active filters are not affected.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S4-R5, S8-R2).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-R5, S8-R2).
 AUTOMATION: READY
 </t>
         </is>
@@ -1759,7 +1759,7 @@
           <t xml:space="preserve">1. The dropdown closes.
 2. The selection stays applied - the chip stays active and the table stays filtered.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S4-R6).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-R6).
 AUTOMATION: READY
 </t>
         </is>
@@ -1811,7 +1811,7 @@
           <t xml:space="preserve">1. The table shows no rows and the filtered empty state is displayed.
 2. No error is shown.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S4-N1, S8-R3).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-N1, S8-R3).
 AUTOMATION: READY
 </t>
         </is>
@@ -1864,7 +1864,7 @@
           <t xml:space="preserve">1. The deactivated technician is NOT shown in the filter list.
 2. Active technicians are still listed normally.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S4-E1).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-E1).
 AUTOMATION: READY
 </t>
         </is>
@@ -1918,7 +1918,7 @@
 3. Below it is a scrollable list of advisor names.
 4. A 'Clear Selection' action is shown at the bottom.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S5-R1).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-R1).
 AUTOMATION: READY
 </t>
         </is>
@@ -1969,7 +1969,7 @@
           <t xml:space="preserve">1. The advisor list narrows to only the names matching what you typed.
 2. Deleting the text brings the full list back.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S5-R2).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-R2).
 AUTOMATION: READY
 </t>
         </is>
@@ -2022,7 +2022,7 @@
 2. The table shows only work orders assigned to any of the selected advisors.
 3. The table updates in real time as you select.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S5-R3, S5-R4).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-R3, S5-R4).
 AUTOMATION: READY
 </t>
         </is>
@@ -2075,7 +2075,7 @@
 2. The Service Advisor filter no longer restricts the table.
 3. Other active filters are not affected.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S5-R5, S8-R2).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-R5, S8-R2).
 AUTOMATION: READY
 </t>
         </is>
@@ -2126,7 +2126,7 @@
           <t xml:space="preserve">1. The dropdown closes.
 2. The selection stays applied - the chip stays active and the table stays filtered.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S5-R6).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-R6).
 AUTOMATION: READY
 </t>
         </is>
@@ -2178,7 +2178,7 @@
           <t xml:space="preserve">1. The table shows no rows and the filtered empty state is displayed.
 2. No error is shown.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S5-N1, S8-R3).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-N1, S8-R3).
 AUTOMATION: READY
 </t>
         </is>
@@ -2231,7 +2231,7 @@
           <t xml:space="preserve">1. The deactivated advisor is NOT shown in the filter list.
 2. Active advisors are still listed normally.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S5-E1).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-E1).
 AUTOMATION: READY
 </t>
         </is>
@@ -2284,7 +2284,7 @@
 3. A 'Clear Selection' action is shown at the bottom.
 4. It is a dropdown (like the other filters), not an on/off toggle.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S6-R1).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-R1).
 AUTOMATION: READY
 </t>
         </is>
@@ -2336,7 +2336,7 @@
           <t xml:space="preserve">1. The table shows only work orders whose asset is currently on site.
 2. Work orders whose asset is not on site are hidden.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S6-R2).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-R2).
 AUTOMATION: READY
 </t>
         </is>
@@ -2389,7 +2389,7 @@
 2. The table switches to showing only the not-on-site work orders.
 3. The chip shows the currently selected value.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S6-R3).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-R3).
 AUTOMATION: READY
 </t>
         </is>
@@ -2441,7 +2441,7 @@
 2. The table shows work orders regardless of on-site status again.
 3. Other active filters are not affected.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S6-R4, S8-R2).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-R4, S8-R2).
 AUTOMATION: READY
 </t>
         </is>
@@ -2492,7 +2492,7 @@
           <t xml:space="preserve">1. The dropdown closes.
 2. The Yes selection stays applied - the chip stays active and the table stays filtered.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S6-R5).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-R5).
 AUTOMATION: READY
 </t>
         </is>
@@ -2544,7 +2544,7 @@
           <t xml:space="preserve">1. The table shows no rows and the filtered empty state is displayed.
 2. No error is shown.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S6-N1, S8-R3).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-N1, S8-R3).
 AUTOMATION: READY
 </t>
         </is>
@@ -2598,7 +2598,7 @@
 2. Every work order with the asset on site is excluded.
 3. The chip shows the active No selection.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S6-R2).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-R2).
 AUTOMATION: READY
 </t>
         </is>
@@ -2650,7 +2650,7 @@
 2. The chip displays the selected value (for example 'Status: Estimate').
 3. The other chips stay in their default state.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S7-R1).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S7-R1).
 AUTOMATION: READY
 </t>
         </is>
@@ -2701,7 +2701,7 @@
           <t xml:space="preserve">1. The chip lists the selected values starting with the first one and shortens the label when it gets too long (the design shows 'Status: Estimate, In progress, Approved...').
 2. The chip stays a single compact pill - it does not grow to show every value in full.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S7-R2).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S7-R2).
 AUTOMATION: READY
 </t>
         </is>
@@ -2755,7 +2755,7 @@
 2. As soon as one filter is active, a blue 'Clear Filters' link appears at the right end of the chip row.
 3. When the last active filter is removed, 'Clear Filters' disappears again.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S7-R3, S7-N1, S8-N1).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S7-R3, S7-N1, S8-N1).
 AUTOMATION: READY
 </t>
         </is>
@@ -2810,7 +2810,7 @@
 3. The table shows the full unfiltered list again (no text is in the page Search box, so nothing else is narrowing it).
 4. The 'Clear Filters' link disappears.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S8-R1, S13-R13).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R1, S13-R13).
 AUTOMATION: READY
 </t>
         </is>
@@ -2863,7 +2863,7 @@
 2. The Customer filter stays selected and active (blue) and keeps filtering the table.
 3. 'Clear Filters' remains visible because a filter is still active.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S8-R2).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R2).
 AUTOMATION: READY
 </t>
         </is>
@@ -2917,7 +2917,7 @@
 2. Customer A's Approved work order is hidden (wrong status) and customer B's Estimate work order is hidden (wrong customer) - each additional filter narrows the result further.
 3. Both chips are in the active state and 'Clear Filters' is visible.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S8-R3).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R3).
 AUTOMATION: READY
 </t>
         </is>
@@ -2970,7 +2970,7 @@
 2. The work order table moves up and uses the reclaimed vertical space.
 3. The filter icon shows a pressed/active look while the bar is collapsed.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S1-R4, S1-R5).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S1-R4, S1-R5).
 AUTOMATION: READY
 </t>
         </is>
@@ -3022,10 +3022,9 @@
           <t xml:space="preserve">1. The filter bar reappears below the tab row.
 2. The previously selected filters are still shown on their chips in the active (blue) state - nothing was lost while collapsed.
 3. The 'Clear Filters' link is still shown at the right end of the chip row.
-Known and accepted: on the build tested collapsing the bar does not move the table up, because the buttons share the tab row. The product behaves this way on purpose for now. Do not raise this as a new problem.
----
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S1-R6).
-AUTOMATION: READY - EXPECT FAIL (SV-8843 - closed as accepted, will not be fixed)
+---
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S1-R6).
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -3077,7 +3076,7 @@
           <t xml:space="preserve">1. After step 2 the filter bar is still collapsed (your choice was remembered).
 2. After step 4 the filter bar is expanded again when you return - whichever state you left it in is restored.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S1-R7, S10-R1).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S1-R7, S10-R1).
 AUTOMATION: READY
 </t>
         </is>
@@ -3129,7 +3128,7 @@
           <t xml:space="preserve">1. After step 1 the filter icon shows no special indicator (only its normal pressed look).
 2. After step 3 the filter icon shows a visual indicator (filters icon in primary blue) signalling that active filters are in effect while the bar is hidden.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S7-R4, S7-N2).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S7-R4, S7-N2).
 AUTOMATION: READY
 </t>
         </is>
@@ -3181,7 +3180,7 @@
           <t xml:space="preserve">1. The table content does not change when the bar collapses - it still shows only the work orders matching the active filters.
 2. Hiding the bar only hides the chips; it does not remove or pause the filtering.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S7-R5).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S7-R5).
 AUTOMATION: READY
 </t>
         </is>
@@ -3231,12 +3230,12 @@
       <c r="G53" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The table body is replaced by an empty state (not just a bare empty grid).
-2. The empty state shows a message indicating no results were found for the current filters.
+2. The empty state shows a message saying no results were found for the filters and the search you have on.
 3. No error message or broken layout appears.
-Known and accepted: when only a search is active the message still says "filters" and the only link offered is Clear Filters. The product behaves this way on purpose for now. Do not raise this as a new problem.
----
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S8-R3).
-AUTOMATION: READY - EXPECT FAIL (SV-8847 - closed as accepted, will not be fixed)
+Note for the tester: on the build this test was run against the message reads "No work orders match your filters" - it never mentions the search, even when a search is the only thing narrowing the list. So point 2 fails whenever a search is part of what you applied. That has been reported and the report was closed without a fix, so do not expect it to change.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R3). It was checked against the build on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), which does not behave this way yet.
+AUTOMATION: READY - EXPECT FAIL (SV-8847 - reported, closed without a fix)
 </t>
         </is>
       </c>
@@ -3285,13 +3284,13 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The empty state includes a prompt or link to clear the filters.
+          <t xml:space="preserve">1. The empty state includes a link to clear the filters, and - when you also have a search on - a separate way to clear just the search.
 2. Clicking it removes the active filters and the full work order list is shown again (with no text in the Search box, nothing else is narrowing the list).
 3. The chips return to their default state.
-Known and accepted: the empty screen offers no way to clear the search on its own. The product behaves this way on purpose for now. Do not raise this as a new problem.
----
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S8-R4, S8-R5).
-AUTOMATION: READY - EXPECT FAIL (SV-8847 - closed as accepted, will not be fixed)
+Note for the tester: on the build this test was run against the empty screen offers only a "Clear Filters" link. There is no way to clear just the search from that screen, so the second half of point 1 fails. Pressing "Clear Filters" does correctly leave your search in place. That has been reported and the report was closed without a fix, so do not expect it to change.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R4, S8-R5). It was checked against the build on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), which does not behave this way yet.
+AUTOMATION: READY - EXPECT FAIL (SV-8847 - reported, closed without a fix)
 </t>
         </is>
       </c>
@@ -3346,7 +3345,7 @@
 3. Clearing the search brings back the list as narrowed by the filter only - the filter is still on.
 4. Clearing the filters leaves your typed word in the box and still applied - each is cleared on its own without wiping the other.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S8-R3, S8-R4, S8-R5, S13-N1, S13-N2).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R3, S8-R4, S8-R5, S13-N1, S13-N2).
 AUTOMATION: READY
 </t>
         </is>
@@ -3397,7 +3396,7 @@
           <t xml:space="preserve">1. All five chips are shown: Status, Customer, Lead Technician, Service Advisor, Asset on Site.
 2. Each chip opens its dropdown and can be used.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S9-R1).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S9-R1).
 AUTOMATION: READY
 </t>
         </is>
@@ -3453,7 +3452,7 @@
 2. Customer, Lead Technician, Service Advisor and Asset on Site chips are shown and usable.
 3. After step 4 the table shows only that customer's ESTIMATE work orders - the customer filter narrows the pre-filtered Estimates list.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S9-R2, S2-N1). Note: an earlier answer of 2026-07-17 and the design frame both show the Status button greyed out and pre-filled on this tab; the specification and the build both hide it, and the specification is the newer source, so this test follows the specification and the build.
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S9-R2, S2-N1). Note: an earlier answer of 2026-07-17 and the design frame both show the Status button greyed out and pre-filled on this tab; the specification and the build both hide it, and the specification is the newer source, so this test follows the specification.
 AUTOMATION: READY
 </t>
         </is>
@@ -3509,7 +3508,7 @@
 2. Customer, Lead Technician, Service Advisor and Asset on Site chips are shown and usable.
 3. After step 4 the table shows only that customer's COMPLETE work orders.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S9-R3, S2-N2). Note: an earlier answer of 2026-07-17 and the design frame both show the Status button greyed out and pre-filled on this tab; the specification and the build both hide it, and the specification is the newer source, so this test follows the specification and the build.
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S9-R3, S2-N2). Note: an earlier answer of 2026-07-17 and the design frame both show the Status button greyed out and pre-filled on this tab; the specification and the build both hide it, and the specification is the newer source, so this test follows the specification.
 AUTOMATION: READY
 </t>
         </is>
@@ -3563,7 +3562,7 @@
 2. The table only ever shows work orders assigned to you (the tab's own scope stays).
 3. After step 2 it shows only YOUR work orders in the ticked status - the filters narrow the user-scoped list, they do not widen it to other users' work orders.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S9-R4).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S9-R4).
 AUTOMATION: READY
 </t>
         </is>
@@ -3616,7 +3615,7 @@
 2. Back on the All tab the Status chip reappears with the SAME selection (Approved) still applied - the selection was retained in memory, not lost.
 3. The Customer selection is unchanged throughout.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S9-R5, S9-N1, S9-R2).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S9-R5, S9-N1, S9-R2).
 AUTOMATION: READY
 </t>
         </is>
@@ -3668,7 +3667,7 @@
           <t xml:space="preserve">1. On the very first visit the Estimates tab is the selected one, even though All is the FIRST tab in the row (order and default are different on purpose).
 2. After switching to All and returning, the All tab is selected - the app remembers your last-used tab per account.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md)
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md)
 AUTOMATION: READY
 </t>
         </is>
@@ -3723,7 +3722,7 @@
 3. After step 4 the filter bar comes back collapsed - the collapsed/expanded state is restored too.
 Known issue: on the build tested the Customer, Lead Technician and Service Advisor buttons come back switched on but WITHOUT the name of the value you picked - the button reads just "Customer" instead of "Customer: Iibay Landscaping". The list is still filtered correctly. The Status and Asset on Site buttons keep their value. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8871
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S10-R1, S1-R7).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-R1, S1-R7). It was checked against the build on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), which does not behave this way yet.
 AUTOMATION: READY - EXPECT FAIL (SV-8871)
 </t>
         </is>
@@ -3779,7 +3778,7 @@
 2. After closing the browser completely and signing back in (step 5) the same filter selections are still applied - the app remembers your filters for you permanently, not just for one browser session.
 3. The same filter selections are applied on the other computer too - the filters are saved to your account, not to one computer or browser (to confirm live once built).
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S10-R2, S10-R3, S10-R1).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-R2, S10-R3, S10-R1).
 AUTOMATION: READY
 </t>
         </is>
@@ -3831,7 +3830,7 @@
           <t xml:space="preserve">1. User B does not see user A's filters - user B's page opens with user B's own (or no) filters.
 2. User B's new filter does not change what user A sees; each user keeps their own saved filter state.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S10-R3).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-R3).
 AUTOMATION: READY
 </t>
         </is>
@@ -3885,7 +3884,7 @@
 3. The table is filtered by the remaining valid selection only.
 Known issue: on the build tested the deleted customer is hidden from the dropdown but is STILL used to filter the table - the address bar and the request to the server both still carry it. So step 3 above is expected to fail. It is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8832
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S10-N1).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-N1). It was checked against the build on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), which does not behave this way yet.
 AUTOMATION: READY - EXPECT FAIL (SV-8832)
 </t>
         </is>
@@ -3939,7 +3938,7 @@
 2. Returning to the first view restores that view's own selections.
 3. Report tabs likewise keep separate filter choices, each remembered and restored on its own tab.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S10-R4).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-R4).
 AUTOMATION: READY
 </t>
         </is>
@@ -3990,7 +3989,7 @@
           <t xml:space="preserve">1. The old saved choices appear in the new filter bar on the first visit - the update does not lose them (old status choices show in the Status chip, the old asset-here choice shows as Asset on Site: Yes, the old My-Work-Orders toggle maps to the My Work Orders tab, columns and sorting stay).
 2. Those carried-over choices are now saved to the account: the other computer shows them too.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S10-R2).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-R2).
 AUTOMATION: READY
 </t>
         </is>
@@ -4042,7 +4041,7 @@
           <t xml:space="preserve">1. After step 1 the URL changes to include the active filter state.
 2. After step 3 the filter part of the URL is removed again.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S11-R1).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-R1).
 AUTOMATION: READY
 </t>
         </is>
@@ -4093,10 +4092,10 @@
           <t xml:space="preserve">1. The page opens with the same filters already applied - chips active with the same values.
 2. The table is already filtered accordingly on load (no need to re-apply anything).
 3. The same works from a saved bookmark.
-Known issue: two points on this test are expected to fail on the build tested. On a phone-sized screen a link carrying filters shows the buttons as on but lists the wrong work orders (ticket: https://shopview.atlassian.net/browse/SV-8845). And on a desktop screen a Customer, Lead Technician or Service Advisor button opened from a link comes back switched on but without the name of the value, so it reads just "Customer" (ticket: https://shopview.atlassian.net/browse/SV-8871). The list itself is filtered correctly on desktop. Both are already reported.
----
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S11-R2).
-AUTOMATION: READY - EXPECT FAIL (SV-8845, SV-8871)
+Known issue: two points on this test are expected to fail on the build tested. On a phone-sized screen a link carrying filters shows the buttons as on but lists the wrong work orders (ticket: https://shopview.atlassian.net/browse/SV-8845 - reported, and closed without a fix, so do not expect it to change). And on a desktop screen a Customer, Lead Technician or Service Advisor button opened from a link comes back switched on but without the name of the value, so it reads just "Customer" (ticket: https://shopview.atlassian.net/browse/SV-8871). The list itself is filtered correctly on desktop. Both are already reported.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-R2). It was checked against the build on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), which does not behave this way yet.
+AUTOMATION: READY - EXPECT FAIL (SV-8845 - reported, closed without a fix; SV-8871)
 </t>
         </is>
       </c>
@@ -4149,7 +4148,7 @@
 3. The table reflects only the valid filter.
 Known issue: a value in the address bar that no longer exists is still sent to the server, so you get an empty list instead of the list without that value. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8832
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S11-R3).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-R3). It was checked against the build on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), which does not behave this way yet.
 AUTOMATION: READY - EXPECT FAIL (SV-8832)
 </t>
         </is>
@@ -4203,7 +4202,7 @@
 3. No error message or broken page appears.
 Known issue: a broken address is not fully ignored - a wrong tab value can switch the tab and a bad customer value is still sent to the server. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8832
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S11-N1).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-N1). It was checked against the build on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), which does not behave this way yet.
 AUTOMATION: READY - EXPECT FAIL (SV-8832)
 </t>
         </is>
@@ -4263,7 +4262,7 @@
 5. It also empties the Search box and removes your typed text - the search is not something that gets saved, so there is nothing to bring back.
 6. Returning normally later still shows your own saved filters, untouched by the link visit.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S11-R6, S11-R7, S11-R8).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-R6, S11-R7, S11-R8). It was checked against the build on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), which does not behave this way yet.
 AUTOMATION: READY - EXPECT FAIL (SV-8828)
 </t>
         </is>
@@ -4320,7 +4319,7 @@
 3. When you open the shared link, 'Back To My Saved Filters' does appear.
 4. After you click it and you are back on your own view, the option disappears again.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S11-N3, S11-R7).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-N3, S11-R7). It was checked against the build on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), which does not behave this way yet.
 AUTOMATION: READY - EXPECT FAIL (SV-8828)
 </t>
         </is>
@@ -4372,8 +4371,8 @@
 2. The row scrolls horizontally - chips that do not fit are reachable by swiping.
 3. An arrow at the right-hand edge shows that the row can be scrolled. (This is what the design shows - if your screen looks different, write down what you actually see and carry on.)
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R1). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). This has not been checked against the running app in this pass, so no build or test date is claimed for it.
-AUTOMATION: HOLD - needs one live check on the current build to confirm whether the 'Apply filters' button is present on a phone
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R1). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). This was checked against the running app on 8/5/2026, on build ShopView v3.4.2-d00239b on the Filters QA branch, at a phone-sized screen 390 pixels wide.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -4424,8 +4423,8 @@
 2. It lists the five filters as expandable accordion rows, each with its icon, name and a down arrow: Status, Customer, Lead Technician, Service Advisor, Asset on Site.
 3. A sticky blue 'Apply filters' button sits at the bottom of the sheet.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R3, S12-R6). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). This has not been checked against the running app in this pass, so no build or test date is claimed for it.
-AUTOMATION: HOLD - needs one live check on the current build to confirm whether the 'Apply filters' button is present on a phone
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R3, S12-R6). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). This was checked against the running app on 8/5/2026, on build ShopView v3.4.2-d00239b on the Filters QA branch, at a phone-sized screen 390 pixels wide.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -4479,8 +4478,8 @@
 2. After 'Apply filters' the sheet closes and the work order list shows only the ticked statuses.
 3. The reopened sheet's title shows the applied-filter count, for example 'All Filters (1)', and the Status accordion header is highlighted with the selected values ticked.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R2, S12-R3, S12-R6, S2-R1). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). This has not been checked against the running app in this pass, so no build or test date is claimed for it.
-AUTOMATION: HOLD - needs one live check on the current build to confirm whether the 'Apply filters' button is present on a phone
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R2, S12-R3, S12-R6, S2-R1). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). This was checked against the running app on 8/5/2026, on build ShopView v3.4.2-d00239b on the Filters QA branch, at a phone-sized screen 390 pixels wide.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -4536,9 +4535,9 @@
 5. The chip then shows its active state with the value(s) you picked. 'Clear Selection' and 'Clear Filters' work the same way as on desktop.
 Known issue reported by the test team: a single filter's own sheet is reported to allow only one value and to have no 'Apply filters' button, filtering the list the moment you tap a value, while only the combined 'All Filters' sheet holds your choices until you press a button. That is reported as https://shopview.atlassian.net/browse/SV-8875 and it is still open. We have not re-checked it on the current build, so if you can run this test, write down what you actually see.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R2, S12-R6, S2-R2). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). This has not been checked against the running app in this pass, so no build or test date is claimed for it.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R2, S12-R6, S2-R2). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). This was checked against the running app on 8/5/2026, on build ShopView v3.4.2-d00239b on the Filters QA branch, at a phone-sized screen 390 pixels wide.
 Please note this is a change from what this test used to say. It used to expect a single filter's sheet to filter the list straight away with no 'Apply filters' button. Branko asked for the new behaviour in the specification and confirmed it on 5 August 2026 when he closed our question (https://shopview.atlassian.net/browse/SV-8825), saying it is written in the specification. The earlier position came from his own written answers of 4 August 2026, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md), where he said a single filter window applies straight away with no button. We have taken his latest word as the one that counts, so if you remember the old behaviour, do not raise it as a new problem.
-AUTOMATION: HOLD - needs one live check on the current build to confirm whether the 'Apply filters' button is present on a phone
+AUTOMATION: READY - EXPECT FAIL (SV-8875)
 </t>
         </is>
       </c>
@@ -4593,8 +4592,8 @@
 3. Removing a tag deselects just that customer.
 4. After 'Apply filters' the list shows only work orders of the remaining selected customers, and the sheet title counts the applied filters (for example 'All Filters (2)').
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R2, S12-R6, S3-R2, S3-R3). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). This has not been checked against the running app in this pass, so no build or test date is claimed for it.
-AUTOMATION: HOLD - needs one live check on the current build to confirm whether the 'Apply filters' button is present on a phone
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R2, S12-R6, S3-R2, S3-R3). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). This was checked against the running app on 8/5/2026, on build ShopView v3.4.2-d00239b on the Filters QA branch, at a phone-sized screen 390 pixels wide.
+AUTOMATION: READY - EXPECT FAIL (SV-8875)
 </t>
         </is>
       </c>
@@ -4647,8 +4646,8 @@
 2. The Service Advisor row opens with a 'Search' field and the advisor list.
 3. Applying a selection filters the work order list just like on desktop.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R2, S12-R6, S4-R1, S5-R1). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). This has not been checked against the running app in this pass, so no build or test date is claimed for it.
-AUTOMATION: HOLD - needs one live check on the current build to confirm whether the 'Apply filters' button is present on a phone
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R2, S12-R6, S4-R1, S5-R1). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). This was checked against the running app on 8/5/2026, on build ShopView v3.4.2-d00239b on the Filters QA branch, at a phone-sized screen 390 pixels wide.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -4701,8 +4700,8 @@
 2. Only one option can be selected at a time.
 3. After applying, the list shows only work orders matching the chosen on-site state.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R2, S12-R6, S6-R1). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). This has not been checked against the running app in this pass, so no build or test date is claimed for it.
-AUTOMATION: HOLD - needs one live check on the current build to confirm whether the 'Apply filters' button is present on a phone
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R2, S12-R6, S6-R1). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). This was checked against the running app on 8/5/2026, on build ShopView v3.4.2-d00239b on the Filters QA branch, at a phone-sized screen 390 pixels wide.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -4755,7 +4754,7 @@
 3. Using it removes all active filters, the chips return to default and the full list comes back.
 Known issue: on a phone there is no Clear Filters button at all while filters are on. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8846
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R2, S7-R1, S8-R1).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R2, S7-R1, S8-R1). It was checked against the build on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), which does not behave this way yet.
 AUTOMATION: READY - EXPECT FAIL (SV-8846)
 </t>
         </is>
@@ -4806,8 +4805,8 @@
           <t xml:space="preserve">1. There is no filter-bar collapse/expand (filter icon) toggle on mobile.
 2. The filter chip row is always visible on the mobile Work Orders page.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-R4).
-AUTOMATION: READY - EXPECT FAIL (no ticket - reported to the QA lead as one design item, not filed)
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R4).
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -4857,10 +4856,9 @@
           <t xml:space="preserve">1. The list shows the same no-results empty state as desktop, saying no results were found for the current filters.
 2. The empty state includes the prompt to clear filters.
 3. No error appears.
-Known issue: on a phone a link carrying filters shows the buttons as on but lists the wrong work orders. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8845
----
-This is the expected behaviour as per epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S12-N1, S8-R3). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). This has not been checked against the running app in this pass, so no build or test date is claimed for it.
-AUTOMATION: HOLD - needs one live check on the current build to confirm whether the 'Apply filters' button is present on a phone
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-N1, S8-R3). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). This was checked against the running app on 8/5/2026, on build ShopView v3.4.2-d00239b on the Filters QA branch, at a phone-sized screen 390 pixels wide.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -4930,7 +4928,7 @@
 13. Still to check on the live build: what the filter icon and the column/layout icon do (the written description does not cover the toolbar icons).
 Not built yet on the build tested: a filter bar exists on Inventory, Part Sales, Catalog and Returns, but Purchase Orders, Vendor Invoices and Vendors have no filter bar at all. If the filter bar is missing on the view you are testing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md)
+This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below - not as per the build, because this part of the product is not built yet. On the build looked at on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) the controls this test needs were looked for and were not found. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md)
 AUTOMATION: HOLD - the feature is not in the product yet
 </t>
         </is>
@@ -4986,7 +4984,7 @@
 4. As soon as you tick a choice the list below narrows to matching parts straight away, with no Apply button to press; Clear Selection puts the list back.
 Not built yet on the build tested: a filter bar exists on Inventory, Part Sales, Catalog and Returns, but Purchase Orders, Vendor Invoices and Vendors have no filter bar at all. If the filter bar is missing on the view you are testing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md)
+This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below - not as per the build, because this part of the product is not built yet. On the build looked at on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) the controls this test needs were looked for and were not found. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md)
 AUTOMATION: HOLD - the feature is not in the product yet
 </t>
         </is>
@@ -5040,7 +5038,7 @@
 3. The list narrows as soon as you pick the value - there is no Apply or Search button to press. Every filter button on every Parts page works this way.
 Not built yet on the build tested: a filter bar exists on Inventory, Part Sales, Catalog and Returns, but Purchase Orders, Vendor Invoices and Vendors have no filter bar at all. If the filter bar is missing on the view you are testing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md)
+This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below - not as per the build, because this part of the product is not built yet. On the build looked at on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) the controls this test needs were looked for and were not found. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md)
 AUTOMATION: HOLD - the feature is not in the product yet
 </t>
         </is>
@@ -5094,7 +5092,7 @@
 3. A Clear Filters button appears in the filter bar while any filter is set, and using it clears them all at once - exactly as it works on the Work Orders page.
 Not built yet on the build tested: a filter bar exists on Inventory, Part Sales, Catalog and Returns, but Purchase Orders, Vendor Invoices and Vendors have no filter bar at all. If the filter bar is missing on the view you are testing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md)
+This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below - not as per the build, because this part of the product is not built yet. On the build looked at on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) the controls this test needs were looked for and were not found. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md)
 AUTOMATION: HOLD - the feature is not in the product yet
 </t>
         </is>
@@ -5151,7 +5149,7 @@
 3. If any filter or choice is missing, write down exactly which page, which filter and which choice - that is a bug worth reporting.
 Not built yet on the build tested: a filter bar exists on Inventory, Part Sales, Catalog and Returns, but Purchase Orders, Vendor Invoices and Vendors have no filter bar at all. If the filter bar is missing on the view you are testing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md)
+This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below - not as per the build, because this part of the product is not built yet. On the build looked at on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) the controls this test needs were looked for and were not found. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md)
 AUTOMATION: HOLD - the feature is not in the product yet
 </t>
         </is>
@@ -5239,7 +5237,7 @@
 24. Still to check on the live build: the real columns of the Sales Tax report and of the six A/R and A/P aging reports. The design uses sample placeholder tables for those, and the written description does not list their columns.
 Not built yet on the build tested: only the first report tab (Timesheet Activities) has a filter bar, with a Date Range and a Filter by Staff button, and no report tab has a page search box. If the controls this test needs are missing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md)
+This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below - not as per the build, because this part of the product is not built yet. On the build looked at on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) the controls this test needs were looked for and were not found. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md)
 AUTOMATION: HOLD - the feature is not in the product yet
 </t>
         </is>
@@ -5292,7 +5290,7 @@
 2. The report narrows as soon as you pick the value - there is no Apply or Run button to press. Every filter button on every report works this way.
 Not built yet on the build tested: only the first report tab (Timesheet Activities) has a filter bar, with a Date Range and a Filter by Staff button, and no report tab has a page search box. If the controls this test needs are missing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md)
+This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below - not as per the build, because this part of the product is not built yet. On the build looked at on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) the controls this test needs were looked for and were not found. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md)
 AUTOMATION: HOLD - the feature is not in the product yet
 </t>
         </is>
@@ -5346,7 +5344,7 @@
 3. Write down the choices you actually see behind each of these six buttons. They have not been written down anywhere yet, so your list becomes the record.
 Not built yet on the build tested: only the first report tab (Timesheet Activities) has a filter bar, with a Date Range and a Filter by Staff button, and no report tab has a page search box. If the controls this test needs are missing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification version 1.6 as revised on 4 August 2026 has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md)
+This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below - not as per the build, because this part of the product is not built yet. On the build looked at on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) the controls this test needs were looked for and were not found. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md)
 AUTOMATION: HOLD - the feature is not in the product yet
 </t>
         </is>
@@ -5400,17 +5398,17 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The panel that opens offers a set of ready-made periods to choose from - on the build tested these are Today, Yesterday, This week, Last week, This month, Last month, This quarter, Last quarter, This year, Last year - plus a Custom option and a Clear Selection link. The exact set of ready-made periods may differ per report, so check the ones your report offers rather than expecting this list.
+          <t xml:space="preserve">1. The panel that opens offers a set of standard ready-made periods to choose from, plus a Custom option and a Clear Selection link. The written description does not fix which periods are offered, and it can differ per report, so do not check them against a fixed list - write down the ones your report offers.
 2. A period is already filled in when the panel first opens (on Timesheet Activities it is This month), and the button reads that period, for example "Date Range: This month".
 3. Choosing a ready-made period applies it straight away: the results update, the button reads the period you chose, and the web address records it.
 4. Choosing Custom shows a From box and a To box. After you fill in only the From date the results do NOT change yet.
 5. As soon as you fill in the To date the results update to show only records inside that range, and the button reads "Date Range: Custom".
 6. Only one date range can be active at a time on that button.
-Note: dates are typed in month/day/year order, the way the build shows them (for example 07/01/2026).
+Note: dates are typed in month/day/year order, the way the screen shows them (for example 07/01/2026). For orientation only, one report was seen offering Today, Yesterday, This week, Last week, This month, Last month, This quarter, Last quarter, This year and Last year - that is an example of what you may find, not a list to check against.
 Where to run this on the build tested: the Reports area has this date button on the Timesheet Activities report. Other report tabs do not have a filter bar yet - if the report you open has no date button, mark this test BLOCKED, not failed.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. It follows the NEWER wording of the Filters specification version 1.6, in the revision published on the afternoon of 4 August 2026, which changed the date filter description in the Feature Overview and in the Key Decisions section: the date button now offers standard ready-made periods and starts with the current default range already filled in. An earlier revision of the same specification said the opposite, and this test follows the newer one. The specification does not give this a numbered requirement, so there is no requirement number to quote.
-AUTOMATION: READY
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. It follows the NEWER wording of the Filters specification at Confluence version 18, published on the afternoon of 4 August 2026, which changed the date filter description in the Feature Overview and in the Key Decisions section: the date button now offers standard ready-made periods and starts with the current default range already filled in. An earlier revision of the same specification said the opposite, and this test follows the newer one. The specification does not give this a numbered requirement, so there is no requirement number to quote.
+AUTOMATION: HOLD - the report filter bars are not in the product yet beyond the first report tab
 </t>
         </is>
       </c>
@@ -5466,7 +5464,7 @@
 3. The round x clears the text and the full list returns.
 4. Clicking away with an empty box collapses it back to the Search button; with text in it, the box stays open.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-R1, S13-R9, S13-R12, S13-R15).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R1, S13-R9, S13-R12, S13-R15). It was checked against the build on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), which does not behave this way yet.
 AUTOMATION: READY - EXPECT FAIL (no ticket - reported to the QA lead as one design item, not filed)
 </t>
         </is>
@@ -5520,7 +5518,7 @@
 2. Clearing the search keeps the filter applied.
 3. Clearing the filter keeps the search applied - each is cleared by its own control without wiping the other.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-R10, S13-R13, S8-R5).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R10, S13-R13, S8-R5). It was checked against the build on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), which does not behave this way yet.
 AUTOMATION: READY - EXPECT FAIL (no ticket - reported to the QA lead as one design item, not filed)
 </t>
         </is>
@@ -5577,7 +5575,7 @@
 3. The second browser tab starts clean: its Search box is empty and it shows the full list. Each tab keeps its own search.
 4. After closing the browser and coming back, the Search box is empty and the list is unsearched - a typed search is never remembered for next time (your filters, unlike the search, ARE remembered).
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-R14, S13-R25, S13-N4, S10-R5).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R14, S13-R25, S13-N4, S10-R5).
 AUTOMATION: READY
 </t>
         </is>
@@ -5631,7 +5629,7 @@
 3. The malformed part is ignored - the page loads cleanly without an error.
 4. A search arriving via a link is view-only, the same as filters from a link - it does not overwrite your own remembered search.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S11-R4, S11-R5, S11-N2, S11-R8).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-R4, S11-R5, S11-N2, S11-R8).
 AUTOMATION: READY
 </t>
         </is>
@@ -5687,7 +5685,7 @@
 4. The box stretches to fill the space left in the action row instead of staying the narrow desktop size, and every other toolbar button stays visible and in the same place while you search.
 5. There is no extra 'search is on' badge on mobile: with text in it the box simply stays open showing your text, and an empty box closes back to the Search button when you tap elsewhere - exactly as on desktop.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-R16, S13-R17, S13-R18, S13-R19, S13-R20, S12-R5).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R16, S13-R17, S13-R18, S13-R19, S13-R20, S12-R5).
 AUTOMATION: READY
 </t>
         </is>
@@ -5745,7 +5743,7 @@
 3. Where the table sits inside a dialog (the Work Order Log, the Line Log, the audit log dialog), the Search box is inside that dialog and works there.
 4. The work order Parts tab keeps the local search input it already had - it was deliberately left as it is.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S14-R6, S14-R5, S13-R22, S14-N1).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S14-R6, S14-R5, S13-R22, S14-N1).
 AUTOMATION: READY
 </t>
         </is>
@@ -5799,7 +5797,7 @@
 2. The same holds on the other pages checked.
 3. Picking a dropdown result still takes you to that record - the navigation search keeps its find-and-open role.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S14-R1, S14-R2, S14-R4, S14-R5).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S14-R1, S14-R2, S14-R4, S14-R5).
 AUTOMATION: READY
 </t>
         </is>
@@ -5857,7 +5855,7 @@
 5. As soon as you type, your text shows in a dark grey and a small round x appears at the right-hand end of the box.
 6. A very long sentence does not make the box grow and does not cut the text off - the text scrolls sideways inside the box and the cursor stays where you are typing.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-R2, S13-R3, S13-R4, S13-R5, S13-R6, S13-R8).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R2, S13-R3, S13-R4, S13-R5, S13-R6, S13-R8). It was checked against the build on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), which does not behave this way yet.
 AUTOMATION: READY - EXPECT FAIL (no ticket - reported to the QA lead as one design item, not filed)
 </t>
         </is>
@@ -5914,10 +5912,9 @@
 3. There is no Apply or Submit button anywhere next to the Search box.
 4. Pressing Enter changes nothing that has not already happened - the same rows stay listed and no page reload happens.
 5. Parts Inventory behaves the same way, only it waits a fraction longer before reacting; that longer wait is on purpose because that page carries more data.
-Known and accepted: the empty screen offers no way to clear the search on its own. The product behaves this way on purpose for now. Do not raise this as a new problem.
----
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-R7, S13-R12).
-AUTOMATION: READY - EXPECT FAIL (SV-8847 - closed as accepted, will not be fixed)
+---
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R7, S13-R12).
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -5972,7 +5969,7 @@
 3. The Completed tab behaves the same way: your word is still there and only that tab's matching rows are listed.
 4. Clearing the search clears it for all the Work Orders tabs - they share one search - and each tab shows its full list again.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-R11, S13-R24).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R11, S13-R24).
 AUTOMATION: READY
 </t>
         </is>
@@ -6028,7 +6025,7 @@
 3. Each report tab behaves the same way: a word typed on one tab stays on that tab only, and each tab remembers its own.
 4. No search is ever applied to a table it was not typed on.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-R24, S13-R11, S10-R4).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R24, S13-R11, S10-R4).
 AUTOMATION: READY
 </t>
         </is>
@@ -6083,7 +6080,7 @@
 3. No error is shown - the leftover search part in the address is simply ignored. (Whether it also disappears from the address is not important; note what you see.)
 4. After typing in the top-of-screen search and reloading, the list is still not narrowed and nothing about that word was remembered for the list.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S14-R3, S14-R2, S14-R1).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S14-R3, S14-R2, S14-R1).
 AUTOMATION: READY
 </t>
         </is>
@@ -6137,7 +6134,7 @@
 2. The Search box stays in the toolbar row with your word still showing; it is not tucked away with the filter bar, because the search sits in the toolbar row and the chips sit in the row below.
 3. Expanding the bar again changes nothing about the search or the narrowed list.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S13-E1).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-E1).
 AUTOMATION: READY
 </t>
         </is>
@@ -6190,7 +6187,7 @@
 2. The request succeeds (HTTP 200).
 3. The response contains only work orders matching the filters - the filtering is done by the backend, not just hidden client-side.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-R2, S3-R6).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R2, S3-R6).
 AUTOMATION: READY
 </t>
         </is>
@@ -6242,7 +6239,7 @@
 2. The response returns customer A's Estimate and Approved work orders only.
 3. Customer B's work orders are absent - the customer filter and status filter both restrict the result, while the two statuses combine as either-or.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S2-R2, S3-R6, S8-R3).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R2, S3-R6, S8-R3).
 AUTOMATION: READY
 </t>
         </is>
@@ -6295,7 +6292,7 @@
 3. Any still-valid filter values in the same request are applied normally.
 Known issue: the server does not fail, but the value that no longer exists is still applied instead of being dropped. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8832
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S10-N1, S11-R3).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-N1, S11-R3). It was checked against the build on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), which does not behave this way yet.
 AUTOMATION: READY - EXPECT FAIL (SV-8832)
 </t>
         </is>
@@ -6348,7 +6345,7 @@
 2. In the browser the page still loads without filters and without an error message, matching the malformed-URL requirement.
 Known issue: the server does not fail, but a broken address is not fully ignored by the page. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8832
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S11-N1).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-N1). It was checked against the build on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), which does not behave this way yet.
 AUTOMATION: READY - EXPECT FAIL (SV-8832)
 </t>
         </is>
@@ -6400,7 +6397,7 @@
 2. The response contains an empty result set (zero work orders) - an empty match is a normal outcome, not an error.
 3. The page renders the no-results empty state from this response.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S8-R3, S2-N3).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R3, S2-N3).
 AUTOMATION: READY
 </t>
         </is>
@@ -6456,7 +6453,7 @@
 4. Asking for a never-saved key returns success with an empty value, not an error page.
 Step 3 needs a SECOND sign-in of your own. We could not run it for you: impersonating another user on this branch returns an error, and a new staff member cannot finish signing up because the invitation email cannot be received here. If you have a second account, run step 3 normally. If you do not, mark this test BLOCKED - do not mark it failed. Steps 1, 2 and 4 were confirmed working.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification version 1.6 as revised on 4 August 2026 (S10-R2, S10-R3).
+This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-R2, S10-R3).
 AUTOMATION: HOLD - needs a second test login to prove one person's saved filters do not reach another
 </t>
         </is>

--- a/testrail-import/filters-v1-testrail-import.xlsx
+++ b/testrail-import/filters-v1-testrail-import.xlsx
@@ -526,7 +526,7 @@
 2. The filter bar is shown by default (expanded) without having to turn anything on.
 Note for the tester: on the build this test was run against, the five filter buttons sit to the RIGHT of the tab row instead of on their own row beneath it, so point 1 fails. That has been reported and the report was closed without a fix, so do not expect it to change - record it as a fail against point 1 and move on.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S1-R1). It was checked against the build on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), which does not behave this way yet.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S1-R1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch; the build does not behave this way yet.
 AUTOMATION: READY - EXPECT FAIL (SV-8843 - reported, closed without a fix)
 </t>
         </is>
@@ -579,7 +579,7 @@
 2. Each chip shows the filter name and a down arrow (chevron) indicating it opens a dropdown.
 3. Each chip shows only the filter name and the arrow - there is no picture icon in front of the name.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S1-R2, S1-R3). Note: the design frame also draws a small picture icon in front of each filter name; the specification asks only for the name and the arrow, and the build matches the specification, so this test follows the specification and the build.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S1-R2, S1-R3). Note: the design frame also draws a small picture icon in front of each filter name; the specification asks only for the name and the arrow, so this test follows the specification. Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -631,7 +631,7 @@
 2. The Customer, Lead Technician, Service Advisor and Asset on Site chips are all displayed and usable.
 3. The Status chip is not shown on this tab at all - only four chips appear.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S1-N1, S9-R2). Note: an earlier answer of 2026-07-17 and the design frame both show the Status button greyed out and pre-filled on this tab; the specification and the build both hide it, and the specification is the newer source, so this test follows the specification and the build.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S1-N1, S9-R2). Note: an earlier answer of 2026-07-17 and the design frame both show the Status button greyed out and pre-filled on this tab; the specification hides it, and the specification is the newer source, so this test follows the specification. Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -686,7 +686,7 @@
 3. All checkboxes are unticked (nothing selected yet).
 4. A 'Clear Selection' action is shown at the bottom of the dropdown.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R1, S2-R4).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R1, S2-R4). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -740,7 +740,7 @@
 2. The table updates immediately to show only work orders in the selected status - there is no confirm or apply button on desktop.
 3. Work orders in other statuses are no longer listed.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R2, S2-R3, S2-R6).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R2, S2-R3, S2-R6). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -795,7 +795,7 @@
 3. Work orders in statuses that are not ticked are hidden.
 4. There is no limit on how many statuses you can tick.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R2).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R2). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -849,7 +849,7 @@
 2. The Status filter is removed and the table returns to showing work orders of every status.
 3. Only the Status filter is affected - any other active filters stay applied.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R4, S8-R2).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R4, S8-R2). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -902,7 +902,7 @@
 2. The ticked statuses stay selected - the Status chip stays in its active state showing the selection.
 3. The table stays filtered by the selected statuses.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R5).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R5). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -956,7 +956,7 @@
 2. An empty state is displayed saying no results were found for the current filters (see the Empty State cases for its full content).
 3. The app does not show an error.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-N3, S8-R3).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-N3, S8-R3). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -1012,7 +1012,7 @@
 3. Imported cannot be combined with other statuses - selecting it works alone.
 4. Unticking Imported re-enables the other chips and the normal list returns.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R7, S2-N4).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R7, S2-N4). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -1067,7 +1067,7 @@
 3. Below it is a scrollable list of customer names.
 4. A 'Clear Selection' action is shown at the bottom of the panel.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R1).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -1120,7 +1120,7 @@
 2. Customers that do not match are removed from the list.
 3. Deleting the text brings the full list back.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R2).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R2). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -1175,7 +1175,7 @@
 3. Long customer names on tags are shortened with an ellipsis (for example 'Texas Truck And Aut...').
 4. You can keep selecting as many customers as needed - there is no selection limit.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R3, S3-R4).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R3, S3-R4). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -1229,7 +1229,7 @@
 3. The other selected customers keep their tags and checkmarks.
 4. The table updates to no longer include that customer's work orders.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R5).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R5). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -1282,7 +1282,7 @@
 2. Work orders belonging to any other customer are hidden.
 3. The table updates in real time as you make the selections (no apply button on desktop).
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R6, S2-R6).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R6, S2-R6). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -1337,7 +1337,7 @@
 3. The Customer filter is removed and the table shows work orders of all customers again.
 4. Other active filters (if any) are not affected.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R7, S8-R2).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R7, S8-R2). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -1390,7 +1390,7 @@
 2. The Customer chip stays in the active (blue) state showing the selection and the table stays filtered.
 3. When reopened, the selected customers' tags are still visible in the input area.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R8).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R8). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -1442,7 +1442,7 @@
 2. The app does not show an error.
 3. Clearing the search text brings the customer list back.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-N1).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-N1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -1496,7 +1496,7 @@
 2. After selecting only that customer, the table shows no rows and the filtered empty state is displayed.
 3. No error is shown.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-E1, S3-N2, S8-R3).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-E1, S3-N2, S8-R3). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -1550,7 +1550,7 @@
 3. Below it is a scrollable list of technician names.
 4. A 'Clear Selection' action is shown at the bottom.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-R1).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-R1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -1601,7 +1601,7 @@
           <t xml:space="preserve">1. The technician list narrows to only the names matching what you typed.
 2. Deleting the text brings the full list back.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-R2).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-R2). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -1655,7 +1655,7 @@
 3. A work order where the technician is assigned only in a non-lead role does not appear.
 4. The table updates in real time as you select.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-R3, S4-R4).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-R3, S4-R4). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -1708,7 +1708,7 @@
 2. The Lead Technician filter no longer restricts the table.
 3. Other active filters are not affected.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-R5, S8-R2).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-R5, S8-R2). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -1759,7 +1759,7 @@
           <t xml:space="preserve">1. The dropdown closes.
 2. The selection stays applied - the chip stays active and the table stays filtered.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-R6).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-R6). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -1811,7 +1811,7 @@
           <t xml:space="preserve">1. The table shows no rows and the filtered empty state is displayed.
 2. No error is shown.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-N1, S8-R3).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-N1, S8-R3). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -1864,7 +1864,7 @@
           <t xml:space="preserve">1. The deactivated technician is NOT shown in the filter list.
 2. Active technicians are still listed normally.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-E1).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-E1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -1918,7 +1918,7 @@
 3. Below it is a scrollable list of advisor names.
 4. A 'Clear Selection' action is shown at the bottom.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-R1).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-R1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -1969,7 +1969,7 @@
           <t xml:space="preserve">1. The advisor list narrows to only the names matching what you typed.
 2. Deleting the text brings the full list back.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-R2).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-R2). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -2022,7 +2022,7 @@
 2. The table shows only work orders assigned to any of the selected advisors.
 3. The table updates in real time as you select.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-R3, S5-R4).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-R3, S5-R4). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -2075,7 +2075,7 @@
 2. The Service Advisor filter no longer restricts the table.
 3. Other active filters are not affected.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-R5, S8-R2).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-R5, S8-R2). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -2126,7 +2126,7 @@
           <t xml:space="preserve">1. The dropdown closes.
 2. The selection stays applied - the chip stays active and the table stays filtered.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-R6).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-R6). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -2178,7 +2178,7 @@
           <t xml:space="preserve">1. The table shows no rows and the filtered empty state is displayed.
 2. No error is shown.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-N1, S8-R3).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-N1, S8-R3). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -2231,7 +2231,7 @@
           <t xml:space="preserve">1. The deactivated advisor is NOT shown in the filter list.
 2. Active advisors are still listed normally.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-E1).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-E1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -2284,7 +2284,7 @@
 3. A 'Clear Selection' action is shown at the bottom.
 4. It is a dropdown (like the other filters), not an on/off toggle.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-R1).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-R1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -2336,7 +2336,7 @@
           <t xml:space="preserve">1. The table shows only work orders whose asset is currently on site.
 2. Work orders whose asset is not on site are hidden.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-R2).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-R2). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -2389,7 +2389,7 @@
 2. The table switches to showing only the not-on-site work orders.
 3. The chip shows the currently selected value.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-R3).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-R3). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -2441,7 +2441,7 @@
 2. The table shows work orders regardless of on-site status again.
 3. Other active filters are not affected.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-R4, S8-R2).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-R4, S8-R2). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -2492,7 +2492,7 @@
           <t xml:space="preserve">1. The dropdown closes.
 2. The Yes selection stays applied - the chip stays active and the table stays filtered.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-R5).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-R5). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -2544,7 +2544,7 @@
           <t xml:space="preserve">1. The table shows no rows and the filtered empty state is displayed.
 2. No error is shown.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-N1, S8-R3).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-N1, S8-R3). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -2598,7 +2598,7 @@
 2. Every work order with the asset on site is excluded.
 3. The chip shows the active No selection.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-R2).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-R2). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -2650,7 +2650,7 @@
 2. The chip displays the selected value (for example 'Status: Estimate').
 3. The other chips stay in their default state.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S7-R1).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S7-R1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -2701,7 +2701,7 @@
           <t xml:space="preserve">1. The chip lists the selected values starting with the first one and shortens the label when it gets too long (the design shows 'Status: Estimate, In progress, Approved...').
 2. The chip stays a single compact pill - it does not grow to show every value in full.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S7-R2).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S7-R2). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -2755,7 +2755,7 @@
 2. As soon as one filter is active, a blue 'Clear Filters' link appears at the right end of the chip row.
 3. When the last active filter is removed, 'Clear Filters' disappears again.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S7-R3, S7-N1, S8-N1).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S7-R3, S7-N1, S8-N1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -2810,7 +2810,7 @@
 3. The table shows the full unfiltered list again (no text is in the page Search box, so nothing else is narrowing it).
 4. The 'Clear Filters' link disappears.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R1, S13-R13).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R1, S13-R13). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -2863,7 +2863,7 @@
 2. The Customer filter stays selected and active (blue) and keeps filtering the table.
 3. 'Clear Filters' remains visible because a filter is still active.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R2).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R2). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -2917,7 +2917,7 @@
 2. Customer A's Approved work order is hidden (wrong status) and customer B's Estimate work order is hidden (wrong customer) - each additional filter narrows the result further.
 3. Both chips are in the active state and 'Clear Filters' is visible.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R3).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R3). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -2970,7 +2970,7 @@
 2. The work order table moves up and uses the reclaimed vertical space.
 3. The filter icon shows a pressed/active look while the bar is collapsed.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S1-R4, S1-R5).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S1-R4, S1-R5). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -3023,7 +3023,7 @@
 2. The previously selected filters are still shown on their chips in the active (blue) state - nothing was lost while collapsed.
 3. The 'Clear Filters' link is still shown at the right end of the chip row.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S1-R6).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S1-R6). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -3076,7 +3076,7 @@
           <t xml:space="preserve">1. After step 2 the filter bar is still collapsed (your choice was remembered).
 2. After step 4 the filter bar is expanded again when you return - whichever state you left it in is restored.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S1-R7, S10-R1).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S1-R7, S10-R1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -3128,7 +3128,7 @@
           <t xml:space="preserve">1. After step 1 the filter icon shows no special indicator (only its normal pressed look).
 2. After step 3 the filter icon shows a visual indicator (filters icon in primary blue) signalling that active filters are in effect while the bar is hidden.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S7-R4, S7-N2).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S7-R4, S7-N2). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -3180,7 +3180,7 @@
           <t xml:space="preserve">1. The table content does not change when the bar collapses - it still shows only the work orders matching the active filters.
 2. Hiding the bar only hides the chips; it does not remove or pause the filtering.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S7-R5).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S7-R5). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -3234,7 +3234,7 @@
 3. No error message or broken layout appears.
 Note for the tester: on the build this test was run against the message reads "No work orders match your filters" - it never mentions the search, even when a search is the only thing narrowing the list. So point 2 fails whenever a search is part of what you applied. That has been reported and the report was closed without a fix, so do not expect it to change.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R3). It was checked against the build on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), which does not behave this way yet.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R3). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch; the build does not behave this way yet.
 AUTOMATION: READY - EXPECT FAIL (SV-8847 - reported, closed without a fix)
 </t>
         </is>
@@ -3289,7 +3289,7 @@
 3. The chips return to their default state.
 Note for the tester: on the build this test was run against the empty screen offers only a "Clear Filters" link. There is no way to clear just the search from that screen, so the second half of point 1 fails. Pressing "Clear Filters" does correctly leave your search in place. That has been reported and the report was closed without a fix, so do not expect it to change.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R4, S8-R5). It was checked against the build on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), which does not behave this way yet.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R4, S8-R5). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch; the build does not behave this way yet.
 AUTOMATION: READY - EXPECT FAIL (SV-8847 - reported, closed without a fix)
 </t>
         </is>
@@ -3345,7 +3345,7 @@
 3. Clearing the search brings back the list as narrowed by the filter only - the filter is still on.
 4. Clearing the filters leaves your typed word in the box and still applied - each is cleared on its own without wiping the other.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R3, S8-R4, S8-R5, S13-N1, S13-N2).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R3, S8-R4, S8-R5, S13-N1, S13-N2). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -3396,7 +3396,7 @@
           <t xml:space="preserve">1. All five chips are shown: Status, Customer, Lead Technician, Service Advisor, Asset on Site.
 2. Each chip opens its dropdown and can be used.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S9-R1).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S9-R1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -3452,7 +3452,7 @@
 2. Customer, Lead Technician, Service Advisor and Asset on Site chips are shown and usable.
 3. After step 4 the table shows only that customer's ESTIMATE work orders - the customer filter narrows the pre-filtered Estimates list.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S9-R2, S2-N1). Note: an earlier answer of 2026-07-17 and the design frame both show the Status button greyed out and pre-filled on this tab; the specification and the build both hide it, and the specification is the newer source, so this test follows the specification.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S9-R2, S2-N1). Note: an earlier answer of 2026-07-17 and the design frame both show the Status button greyed out and pre-filled on this tab; the specification hides it, and the specification is the newer source, so this test follows the specification. Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -3508,7 +3508,7 @@
 2. Customer, Lead Technician, Service Advisor and Asset on Site chips are shown and usable.
 3. After step 4 the table shows only that customer's COMPLETE work orders.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S9-R3, S2-N2). Note: an earlier answer of 2026-07-17 and the design frame both show the Status button greyed out and pre-filled on this tab; the specification and the build both hide it, and the specification is the newer source, so this test follows the specification.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S9-R3, S2-N2). Note: an earlier answer of 2026-07-17 and the design frame both show the Status button greyed out and pre-filled on this tab; the specification hides it, and the specification is the newer source, so this test follows the specification. Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -3562,7 +3562,7 @@
 2. The table only ever shows work orders assigned to you (the tab's own scope stays).
 3. After step 2 it shows only YOUR work orders in the ticked status - the filters narrow the user-scoped list, they do not widen it to other users' work orders.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S9-R4).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S9-R4). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -3615,7 +3615,7 @@
 2. Back on the All tab the Status chip reappears with the SAME selection (Approved) still applied - the selection was retained in memory, not lost.
 3. The Customer selection is unchanged throughout.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S9-R5, S9-N1, S9-R2).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S9-R5, S9-N1, S9-R2). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -3667,7 +3667,7 @@
           <t xml:space="preserve">1. On the very first visit the Estimates tab is the selected one, even though All is the FIRST tab in the row (order and default are different on purpose).
 2. After switching to All and returning, the All tab is selected - the app remembers your last-used tab per account.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md)
+This is the expected behaviour as per epic SV-8785. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -3722,7 +3722,7 @@
 3. After step 4 the filter bar comes back collapsed - the collapsed/expanded state is restored too.
 Known issue: on the build tested the Customer, Lead Technician and Service Advisor buttons come back switched on but WITHOUT the name of the value you picked - the button reads just "Customer" instead of "Customer: Iibay Landscaping". The list is still filtered correctly. The Status and Asset on Site buttons keep their value. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8871
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-R1, S1-R7). It was checked against the build on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), which does not behave this way yet.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-R1, S1-R7). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch; the build does not behave this way yet.
 AUTOMATION: READY - EXPECT FAIL (SV-8871)
 </t>
         </is>
@@ -3778,7 +3778,7 @@
 2. After closing the browser completely and signing back in (step 5) the same filter selections are still applied - the app remembers your filters for you permanently, not just for one browser session.
 3. The same filter selections are applied on the other computer too - the filters are saved to your account, not to one computer or browser (to confirm live once built).
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-R2, S10-R3, S10-R1).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-R2, S10-R3, S10-R1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -3830,7 +3830,7 @@
           <t xml:space="preserve">1. User B does not see user A's filters - user B's page opens with user B's own (or no) filters.
 2. User B's new filter does not change what user A sees; each user keeps their own saved filter state.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-R3).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-R3). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -3884,7 +3884,7 @@
 3. The table is filtered by the remaining valid selection only.
 Known issue: on the build tested the deleted customer is hidden from the dropdown but is STILL used to filter the table - the address bar and the request to the server both still carry it. So step 3 above is expected to fail. It is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8832
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-N1). It was checked against the build on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), which does not behave this way yet.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-N1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch; the build does not behave this way yet.
 AUTOMATION: READY - EXPECT FAIL (SV-8832)
 </t>
         </is>
@@ -3938,7 +3938,7 @@
 2. Returning to the first view restores that view's own selections.
 3. Report tabs likewise keep separate filter choices, each remembered and restored on its own tab.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-R4).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-R4). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -3989,7 +3989,7 @@
           <t xml:space="preserve">1. The old saved choices appear in the new filter bar on the first visit - the update does not lose them (old status choices show in the Status chip, the old asset-here choice shows as Asset on Site: Yes, the old My-Work-Orders toggle maps to the My Work Orders tab, columns and sorting stay).
 2. Those carried-over choices are now saved to the account: the other computer shows them too.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-R2).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-R2). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -4041,7 +4041,7 @@
           <t xml:space="preserve">1. After step 1 the URL changes to include the active filter state.
 2. After step 3 the filter part of the URL is removed again.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-R1).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-R1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -4094,7 +4094,7 @@
 3. The same works from a saved bookmark.
 Known issue: two points on this test are expected to fail on the build tested. On a phone-sized screen a link carrying filters shows the buttons as on but lists the wrong work orders (ticket: https://shopview.atlassian.net/browse/SV-8845 - reported, and closed without a fix, so do not expect it to change). And on a desktop screen a Customer, Lead Technician or Service Advisor button opened from a link comes back switched on but without the name of the value, so it reads just "Customer" (ticket: https://shopview.atlassian.net/browse/SV-8871). The list itself is filtered correctly on desktop. Both are already reported.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-R2). It was checked against the build on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), which does not behave this way yet.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-R2). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch; the build does not behave this way yet.
 AUTOMATION: READY - EXPECT FAIL (SV-8845 - reported, closed without a fix; SV-8871)
 </t>
         </is>
@@ -4148,7 +4148,7 @@
 3. The table reflects only the valid filter.
 Known issue: a value in the address bar that no longer exists is still sent to the server, so you get an empty list instead of the list without that value. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8832
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-R3). It was checked against the build on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), which does not behave this way yet.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-R3). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch; the build does not behave this way yet.
 AUTOMATION: READY - EXPECT FAIL (SV-8832)
 </t>
         </is>
@@ -4202,7 +4202,7 @@
 3. No error message or broken page appears.
 Known issue: a broken address is not fully ignored - a wrong tab value can switch the tab and a bad customer value is still sent to the server. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8832
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-N1). It was checked against the build on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), which does not behave this way yet.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-N1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch; the build does not behave this way yet.
 AUTOMATION: READY - EXPECT FAIL (SV-8832)
 </t>
         </is>
@@ -4262,7 +4262,7 @@
 5. It also empties the Search box and removes your typed text - the search is not something that gets saved, so there is nothing to bring back.
 6. Returning normally later still shows your own saved filters, untouched by the link visit.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-R6, S11-R7, S11-R8). It was checked against the build on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), which does not behave this way yet.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-R6, S11-R7, S11-R8). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch; the build does not behave this way yet.
 AUTOMATION: READY - EXPECT FAIL (SV-8828)
 </t>
         </is>
@@ -4319,7 +4319,7 @@
 3. When you open the shared link, 'Back To My Saved Filters' does appear.
 4. After you click it and you are back on your own view, the option disappears again.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-N3, S11-R7). It was checked against the build on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), which does not behave this way yet.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-N3, S11-R7). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch; the build does not behave this way yet.
 AUTOMATION: READY - EXPECT FAIL (SV-8828)
 </t>
         </is>
@@ -4371,7 +4371,7 @@
 2. The row scrolls horizontally - chips that do not fit are reachable by swiping.
 3. An arrow at the right-hand edge shows that the row can be scrolled. (This is what the design shows - if your screen looks different, write down what you actually see and carry on.)
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R1). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). This was checked against the running app on 8/5/2026, on build ShopView v3.4.2-d00239b on the Filters QA branch, at a phone-sized screen 390 pixels wide.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R1). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch, at a phone-sized screen 390 pixels wide.
 AUTOMATION: READY
 </t>
         </is>
@@ -4423,7 +4423,7 @@
 2. It lists the five filters as expandable accordion rows, each with its icon, name and a down arrow: Status, Customer, Lead Technician, Service Advisor, Asset on Site.
 3. A sticky blue 'Apply filters' button sits at the bottom of the sheet.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R3, S12-R6). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). This was checked against the running app on 8/5/2026, on build ShopView v3.4.2-d00239b on the Filters QA branch, at a phone-sized screen 390 pixels wide.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R3, S12-R6). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch, at a phone-sized screen 390 pixels wide.
 AUTOMATION: READY
 </t>
         </is>
@@ -4478,7 +4478,7 @@
 2. After 'Apply filters' the sheet closes and the work order list shows only the ticked statuses.
 3. The reopened sheet's title shows the applied-filter count, for example 'All Filters (1)', and the Status accordion header is highlighted with the selected values ticked.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R2, S12-R3, S12-R6, S2-R1). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). This was checked against the running app on 8/5/2026, on build ShopView v3.4.2-d00239b on the Filters QA branch, at a phone-sized screen 390 pixels wide.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R2, S12-R3, S12-R6, S2-R1). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch, at a phone-sized screen 390 pixels wide.
 AUTOMATION: READY
 </t>
         </is>
@@ -4535,7 +4535,7 @@
 5. The chip then shows its active state with the value(s) you picked. 'Clear Selection' and 'Clear Filters' work the same way as on desktop.
 Known issue reported by the test team: a single filter's own sheet is reported to allow only one value and to have no 'Apply filters' button, filtering the list the moment you tap a value, while only the combined 'All Filters' sheet holds your choices until you press a button. That is reported as https://shopview.atlassian.net/browse/SV-8875 and it is still open. We have not re-checked it on the current build, so if you can run this test, write down what you actually see.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R2, S12-R6, S2-R2). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). This was checked against the running app on 8/5/2026, on build ShopView v3.4.2-d00239b on the Filters QA branch, at a phone-sized screen 390 pixels wide.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R2, S12-R6, S2-R2). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch, at a phone-sized screen 390 pixels wide.
 Please note this is a change from what this test used to say. It used to expect a single filter's sheet to filter the list straight away with no 'Apply filters' button. Branko asked for the new behaviour in the specification and confirmed it on 5 August 2026 when he closed our question (https://shopview.atlassian.net/browse/SV-8825), saying it is written in the specification. The earlier position came from his own written answers of 4 August 2026, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md), where he said a single filter window applies straight away with no button. We have taken his latest word as the one that counts, so if you remember the old behaviour, do not raise it as a new problem.
 AUTOMATION: READY - EXPECT FAIL (SV-8875)
 </t>
@@ -4592,7 +4592,7 @@
 3. Removing a tag deselects just that customer.
 4. After 'Apply filters' the list shows only work orders of the remaining selected customers, and the sheet title counts the applied filters (for example 'All Filters (2)').
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R2, S12-R6, S3-R2, S3-R3). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). This was checked against the running app on 8/5/2026, on build ShopView v3.4.2-d00239b on the Filters QA branch, at a phone-sized screen 390 pixels wide.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R2, S12-R6, S3-R2, S3-R3). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch, at a phone-sized screen 390 pixels wide.
 AUTOMATION: READY - EXPECT FAIL (SV-8875)
 </t>
         </is>
@@ -4646,7 +4646,7 @@
 2. The Service Advisor row opens with a 'Search' field and the advisor list.
 3. Applying a selection filters the work order list just like on desktop.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R2, S12-R6, S4-R1, S5-R1). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). This was checked against the running app on 8/5/2026, on build ShopView v3.4.2-d00239b on the Filters QA branch, at a phone-sized screen 390 pixels wide.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R2, S12-R6, S4-R1, S5-R1). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch, at a phone-sized screen 390 pixels wide.
 AUTOMATION: READY
 </t>
         </is>
@@ -4700,7 +4700,7 @@
 2. Only one option can be selected at a time.
 3. After applying, the list shows only work orders matching the chosen on-site state.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R2, S12-R6, S6-R1). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). This was checked against the running app on 8/5/2026, on build ShopView v3.4.2-d00239b on the Filters QA branch, at a phone-sized screen 390 pixels wide.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R2, S12-R6, S6-R1). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch, at a phone-sized screen 390 pixels wide.
 AUTOMATION: READY
 </t>
         </is>
@@ -4754,7 +4754,7 @@
 3. Using it removes all active filters, the chips return to default and the full list comes back.
 Known issue: on a phone there is no Clear Filters button at all while filters are on. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8846
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R2, S7-R1, S8-R1). It was checked against the build on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), which does not behave this way yet.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R2, S7-R1, S8-R1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch; the build does not behave this way yet.
 AUTOMATION: READY - EXPECT FAIL (SV-8846)
 </t>
         </is>
@@ -4805,7 +4805,7 @@
           <t xml:space="preserve">1. There is no filter-bar collapse/expand (filter icon) toggle on mobile.
 2. The filter chip row is always visible on the mobile Work Orders page.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R4).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R4). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -4857,7 +4857,7 @@
 2. The empty state includes the prompt to clear filters.
 3. No error appears.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-N1, S8-R3). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). This was checked against the running app on 8/5/2026, on build ShopView v3.4.2-d00239b on the Filters QA branch, at a phone-sized screen 390 pixels wide.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-N1, S8-R3). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch, at a phone-sized screen 390 pixels wide.
 AUTOMATION: READY
 </t>
         </is>
@@ -4928,7 +4928,7 @@
 13. Still to check on the live build: what the filter icon and the column/layout icon do (the written description does not cover the toolbar icons).
 Not built yet on the build tested: a filter bar exists on Inventory, Part Sales, Catalog and Returns, but Purchase Orders, Vendor Invoices and Vendors have no filter bar at all. If the filter bar is missing on the view you are testing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below - not as per the build, because this part of the product is not built yet. On the build looked at on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) the controls this test needs were looked for and were not found. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md)
+This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch: this part of the product is not built yet, and the controls this test needs were looked for and were not found.
 AUTOMATION: HOLD - the feature is not in the product yet
 </t>
         </is>
@@ -4984,7 +4984,7 @@
 4. As soon as you tick a choice the list below narrows to matching parts straight away, with no Apply button to press; Clear Selection puts the list back.
 Not built yet on the build tested: a filter bar exists on Inventory, Part Sales, Catalog and Returns, but Purchase Orders, Vendor Invoices and Vendors have no filter bar at all. If the filter bar is missing on the view you are testing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below - not as per the build, because this part of the product is not built yet. On the build looked at on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) the controls this test needs were looked for and were not found. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md)
+This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch: this part of the product is not built yet, and the controls this test needs were looked for and were not found.
 AUTOMATION: HOLD - the feature is not in the product yet
 </t>
         </is>
@@ -5038,7 +5038,7 @@
 3. The list narrows as soon as you pick the value - there is no Apply or Search button to press. Every filter button on every Parts page works this way.
 Not built yet on the build tested: a filter bar exists on Inventory, Part Sales, Catalog and Returns, but Purchase Orders, Vendor Invoices and Vendors have no filter bar at all. If the filter bar is missing on the view you are testing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below - not as per the build, because this part of the product is not built yet. On the build looked at on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) the controls this test needs were looked for and were not found. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md)
+This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch: this part of the product is not built yet, and the controls this test needs were looked for and were not found.
 AUTOMATION: HOLD - the feature is not in the product yet
 </t>
         </is>
@@ -5092,7 +5092,7 @@
 3. A Clear Filters button appears in the filter bar while any filter is set, and using it clears them all at once - exactly as it works on the Work Orders page.
 Not built yet on the build tested: a filter bar exists on Inventory, Part Sales, Catalog and Returns, but Purchase Orders, Vendor Invoices and Vendors have no filter bar at all. If the filter bar is missing on the view you are testing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below - not as per the build, because this part of the product is not built yet. On the build looked at on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) the controls this test needs were looked for and were not found. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md)
+This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch: this part of the product is not built yet, and the controls this test needs were looked for and were not found.
 AUTOMATION: HOLD - the feature is not in the product yet
 </t>
         </is>
@@ -5149,7 +5149,7 @@
 3. If any filter or choice is missing, write down exactly which page, which filter and which choice - that is a bug worth reporting.
 Not built yet on the build tested: a filter bar exists on Inventory, Part Sales, Catalog and Returns, but Purchase Orders, Vendor Invoices and Vendors have no filter bar at all. If the filter bar is missing on the view you are testing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below - not as per the build, because this part of the product is not built yet. On the build looked at on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) the controls this test needs were looked for and were not found. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md)
+This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch: this part of the product is not built yet, and the controls this test needs were looked for and were not found.
 AUTOMATION: HOLD - the feature is not in the product yet
 </t>
         </is>
@@ -5237,7 +5237,7 @@
 24. Still to check on the live build: the real columns of the Sales Tax report and of the six A/R and A/P aging reports. The design uses sample placeholder tables for those, and the written description does not list their columns.
 Not built yet on the build tested: only the first report tab (Timesheet Activities) has a filter bar, with a Date Range and a Filter by Staff button, and no report tab has a page search box. If the controls this test needs are missing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below - not as per the build, because this part of the product is not built yet. On the build looked at on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) the controls this test needs were looked for and were not found. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md)
+This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch: this part of the product is not built yet, and the controls this test needs were looked for and were not found.
 AUTOMATION: HOLD - the feature is not in the product yet
 </t>
         </is>
@@ -5290,7 +5290,7 @@
 2. The report narrows as soon as you pick the value - there is no Apply or Run button to press. Every filter button on every report works this way.
 Not built yet on the build tested: only the first report tab (Timesheet Activities) has a filter bar, with a Date Range and a Filter by Staff button, and no report tab has a page search box. If the controls this test needs are missing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below - not as per the build, because this part of the product is not built yet. On the build looked at on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) the controls this test needs were looked for and were not found. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md)
+This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch: this part of the product is not built yet, and the controls this test needs were looked for and were not found.
 AUTOMATION: HOLD - the feature is not in the product yet
 </t>
         </is>
@@ -5344,7 +5344,7 @@
 3. Write down the choices you actually see behind each of these six buttons. They have not been written down anywhere yet, so your list becomes the record.
 Not built yet on the build tested: only the first report tab (Timesheet Activities) has a filter bar, with a Date Range and a Filter by Staff button, and no report tab has a page search box. If the controls this test needs are missing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below - not as per the build, because this part of the product is not built yet. On the build looked at on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) the controls this test needs were looked for and were not found. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md)
+This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch: this part of the product is not built yet, and the controls this test needs were looked for and were not found.
 AUTOMATION: HOLD - the feature is not in the product yet
 </t>
         </is>
@@ -5407,7 +5407,7 @@
 Note: dates are typed in month/day/year order, the way the screen shows them (for example 07/01/2026). For orientation only, one report was seen offering Today, Yesterday, This week, Last week, This month, Last month, This quarter, Last quarter, This year and Last year - that is an example of what you may find, not a list to check against.
 Where to run this on the build tested: the Reports area has this date button on the Timesheet Activities report. Other report tabs do not have a filter bar yet - if the report you open has no date button, mark this test BLOCKED, not failed.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch) and epic SV-8785. It follows the NEWER wording of the Filters specification at Confluence version 18, published on the afternoon of 4 August 2026, which changed the date filter description in the Feature Overview and in the Key Decisions section: the date button now offers standard ready-made periods and starts with the current default range already filled in. An earlier revision of the same specification said the opposite, and this test follows the newer one. The specification does not give this a numbered requirement, so there is no requirement number to quote.
+This is the expected behaviour as per epic SV-8785. It follows the NEWER wording of the Filters specification at Confluence version 18, published on the afternoon of 4 August 2026, which changed the date filter description in the Feature Overview and in the Key Decisions section: the date button now offers standard ready-made periods and starts with the current default range already filled in. An earlier revision of the same specification said the opposite, and this test follows the newer one. The specification does not give this a numbered requirement, so there is no requirement number to quote. Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: HOLD - the report filter bars are not in the product yet beyond the first report tab
 </t>
         </is>
@@ -5464,7 +5464,7 @@
 3. The round x clears the text and the full list returns.
 4. Clicking away with an empty box collapses it back to the Search button; with text in it, the box stays open.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R1, S13-R9, S13-R12, S13-R15). It was checked against the build on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), which does not behave this way yet.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R1, S13-R9, S13-R12, S13-R15). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch; the build does not behave this way yet.
 AUTOMATION: READY - EXPECT FAIL (no ticket - reported to the QA lead as one design item, not filed)
 </t>
         </is>
@@ -5518,7 +5518,7 @@
 2. Clearing the search keeps the filter applied.
 3. Clearing the filter keeps the search applied - each is cleared by its own control without wiping the other.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R10, S13-R13, S8-R5). It was checked against the build on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), which does not behave this way yet.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R10, S13-R13, S8-R5). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch; the build does not behave this way yet.
 AUTOMATION: READY - EXPECT FAIL (no ticket - reported to the QA lead as one design item, not filed)
 </t>
         </is>
@@ -5575,7 +5575,7 @@
 3. The second browser tab starts clean: its Search box is empty and it shows the full list. Each tab keeps its own search.
 4. After closing the browser and coming back, the Search box is empty and the list is unsearched - a typed search is never remembered for next time (your filters, unlike the search, ARE remembered).
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R14, S13-R25, S13-N4, S10-R5).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R14, S13-R25, S13-N4, S10-R5). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -5629,7 +5629,7 @@
 3. The malformed part is ignored - the page loads cleanly without an error.
 4. A search arriving via a link is view-only, the same as filters from a link - it does not overwrite your own remembered search.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-R4, S11-R5, S11-N2, S11-R8).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-R4, S11-R5, S11-N2, S11-R8). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -5685,7 +5685,7 @@
 4. The box stretches to fill the space left in the action row instead of staying the narrow desktop size, and every other toolbar button stays visible and in the same place while you search.
 5. There is no extra 'search is on' badge on mobile: with text in it the box simply stays open showing your text, and an empty box closes back to the Search button when you tap elsewhere - exactly as on desktop.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R16, S13-R17, S13-R18, S13-R19, S13-R20, S12-R5).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R16, S13-R17, S13-R18, S13-R19, S13-R20, S12-R5). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -5743,7 +5743,7 @@
 3. Where the table sits inside a dialog (the Work Order Log, the Line Log, the audit log dialog), the Search box is inside that dialog and works there.
 4. The work order Parts tab keeps the local search input it already had - it was deliberately left as it is.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S14-R6, S14-R5, S13-R22, S14-N1).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S14-R6, S14-R5, S13-R22, S14-N1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -5797,7 +5797,7 @@
 2. The same holds on the other pages checked.
 3. Picking a dropdown result still takes you to that record - the navigation search keeps its find-and-open role.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S14-R1, S14-R2, S14-R4, S14-R5).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S14-R1, S14-R2, S14-R4, S14-R5). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -5855,7 +5855,7 @@
 5. As soon as you type, your text shows in a dark grey and a small round x appears at the right-hand end of the box.
 6. A very long sentence does not make the box grow and does not cut the text off - the text scrolls sideways inside the box and the cursor stays where you are typing.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R2, S13-R3, S13-R4, S13-R5, S13-R6, S13-R8). It was checked against the build on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), which does not behave this way yet.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R2, S13-R3, S13-R4, S13-R5, S13-R6, S13-R8). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch; the build does not behave this way yet.
 AUTOMATION: READY - EXPECT FAIL (no ticket - reported to the QA lead as one design item, not filed)
 </t>
         </is>
@@ -5913,7 +5913,7 @@
 4. Pressing Enter changes nothing that has not already happened - the same rows stay listed and no page reload happens.
 5. Parts Inventory behaves the same way, only it waits a fraction longer before reacting; that longer wait is on purpose because that page carries more data.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R7, S13-R12).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R7, S13-R12). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -5969,7 +5969,7 @@
 3. The Completed tab behaves the same way: your word is still there and only that tab's matching rows are listed.
 4. Clearing the search clears it for all the Work Orders tabs - they share one search - and each tab shows its full list again.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R11, S13-R24).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R11, S13-R24). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -6025,7 +6025,7 @@
 3. Each report tab behaves the same way: a word typed on one tab stays on that tab only, and each tab remembers its own.
 4. No search is ever applied to a table it was not typed on.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R24, S13-R11, S10-R4).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R24, S13-R11, S10-R4). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -6080,7 +6080,7 @@
 3. No error is shown - the leftover search part in the address is simply ignored. (Whether it also disappears from the address is not important; note what you see.)
 4. After typing in the top-of-screen search and reloading, the list is still not narrowed and nothing about that word was remembered for the list.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S14-R3, S14-R2, S14-R1).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S14-R3, S14-R2, S14-R1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -6134,7 +6134,7 @@
 2. The Search box stays in the toolbar row with your word still showing; it is not tucked away with the filter bar, because the search sits in the toolbar row and the chips sit in the row below.
 3. Expanding the bar again changes nothing about the search or the narrowed list.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-E1).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-E1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -6187,7 +6187,7 @@
 2. The request succeeds (HTTP 200).
 3. The response contains only work orders matching the filters - the filtering is done by the backend, not just hidden client-side.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R2, S3-R6).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R2, S3-R6). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -6239,7 +6239,7 @@
 2. The response returns customer A's Estimate and Approved work orders only.
 3. Customer B's work orders are absent - the customer filter and status filter both restrict the result, while the two statuses combine as either-or.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R2, S3-R6, S8-R3).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R2, S3-R6, S8-R3). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -6292,7 +6292,7 @@
 3. Any still-valid filter values in the same request are applied normally.
 Known issue: the server does not fail, but the value that no longer exists is still applied instead of being dropped. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8832
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-N1, S11-R3). It was checked against the build on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), which does not behave this way yet.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-N1, S11-R3). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch; the build does not behave this way yet.
 AUTOMATION: READY - EXPECT FAIL (SV-8832)
 </t>
         </is>
@@ -6345,7 +6345,7 @@
 2. In the browser the page still loads without filters and without an error message, matching the malformed-URL requirement.
 Known issue: the server does not fail, but a broken address is not fully ignored by the page. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8832
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-N1). It was checked against the build on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), which does not behave this way yet.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-N1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch; the build does not behave this way yet.
 AUTOMATION: READY - EXPECT FAIL (SV-8832)
 </t>
         </is>
@@ -6397,7 +6397,7 @@
 2. The response contains an empty result set (zero work orders) - an empty match is a normal outcome, not an error.
 3. The page renders the no-results empty state from this response.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R3, S2-N3).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R3, S2-N3). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: READY
 </t>
         </is>
@@ -6453,7 +6453,7 @@
 4. Asking for a never-saved key returns success with an empty value, not an error page.
 Step 3 needs a SECOND sign-in of your own. We could not run it for you: impersonating another user on this branch returns an error, and a new staff member cannot finish signing up because the invitation email cannot be received here. If you have a second account, run step 3 normally. If you do not, mark this test BLOCKED - do not mark it failed. Steps 1, 2 and 4 were confirmed working.
 ---
-This is the expected behaviour as per the build tested on 8/5/2026 (ShopView v3.4.2-d00239b on the Filters QA branch), epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-R2, S10-R3).
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-R2, S10-R3). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
 AUTOMATION: HOLD - needs a second test login to prove one person's saved filters do not reach another
 </t>
         </is>

--- a/testrail-import/filters-v1-testrail-import.xlsx
+++ b/testrail-import/filters-v1-testrail-import.xlsx
@@ -524,10 +524,10 @@
         <is>
           <t xml:space="preserve">1. A filter bar is visible directly below the tab row and above the work order table.
 2. The filter bar is shown by default (expanded) without having to turn anything on.
-Note for the tester: on the build this test was run against, the five filter buttons sit to the RIGHT of the tab row instead of on their own row beneath it, so point 1 fails. That has been reported and the report was closed without a fix, so do not expect it to change - record it as a fail against point 1 and move on.
----
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S1-R1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch; the build does not behave this way yet.
-AUTOMATION: READY - EXPECT FAIL (SV-8843 - reported, closed without a fix)
+Note for the tester: on the build this was checked against, the five filter buttons sit to the RIGHT of the tab row instead of on their own row beneath it, so point 1 does not happen. That is reported and still open, so record it as a fail against point 1 and carry on.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S1-R1). Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8883 - reported, still open)
 </t>
         </is>
       </c>
@@ -579,7 +579,7 @@
 2. Each chip shows the filter name and a down arrow (chevron) indicating it opens a dropdown.
 3. Each chip shows only the filter name and the arrow - there is no picture icon in front of the name.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S1-R2, S1-R3). Note: the design frame also draws a small picture icon in front of each filter name; the specification asks only for the name and the arrow, so this test follows the specification. Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S1-R2, S1-R3). Note: the design frame also draws a small picture icon in front of each filter name; the specification asks only for the name and the arrow, so this test follows the specification. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -631,7 +631,7 @@
 2. The Customer, Lead Technician, Service Advisor and Asset on Site chips are all displayed and usable.
 3. The Status chip is not shown on this tab at all - only four chips appear.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S1-N1, S9-R2). Note: an earlier answer of 2026-07-17 and the design frame both show the Status button greyed out and pre-filled on this tab; the specification hides it, and the specification is the newer source, so this test follows the specification. Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S1-N1, S9-R2). Note: an earlier answer of 2026-07-17 and the design frame both show the Status button greyed out and pre-filled on this tab; the specification hides it, and the specification is the newer source, so this test follows the specification. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -686,7 +686,7 @@
 3. All checkboxes are unticked (nothing selected yet).
 4. A 'Clear Selection' action is shown at the bottom of the dropdown.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R1, S2-R4). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R1, S2-R4). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -740,7 +740,7 @@
 2. The table updates immediately to show only work orders in the selected status - there is no confirm or apply button on desktop.
 3. Work orders in other statuses are no longer listed.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R2, S2-R3, S2-R6). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R2, S2-R3, S2-R6). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -795,7 +795,7 @@
 3. Work orders in statuses that are not ticked are hidden.
 4. There is no limit on how many statuses you can tick.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R2). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R2). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -849,7 +849,7 @@
 2. The Status filter is removed and the table returns to showing work orders of every status.
 3. Only the Status filter is affected - any other active filters stay applied.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R4, S8-R2). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R4, S8-R2). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -902,7 +902,7 @@
 2. The ticked statuses stay selected - the Status chip stays in its active state showing the selection.
 3. The table stays filtered by the selected statuses.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R5). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R5). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -956,7 +956,7 @@
 2. An empty state is displayed saying no results were found for the current filters (see the Empty State cases for its full content).
 3. The app does not show an error.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-N3, S8-R3). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-N3, S8-R3). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1012,7 +1012,7 @@
 3. Imported cannot be combined with other statuses - selecting it works alone.
 4. Unticking Imported re-enables the other chips and the normal list returns.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R7, S2-N4). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R7, S2-N4). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1067,7 +1067,7 @@
 3. Below it is a scrollable list of customer names.
 4. A 'Clear Selection' action is shown at the bottom of the panel.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R1). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1120,7 +1120,7 @@
 2. Customers that do not match are removed from the list.
 3. Deleting the text brings the full list back.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R2). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R2). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1175,7 +1175,7 @@
 3. Long customer names on tags are shortened with an ellipsis (for example 'Texas Truck And Aut...').
 4. You can keep selecting as many customers as needed - there is no selection limit.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R3, S3-R4). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R3, S3-R4). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1229,7 +1229,7 @@
 3. The other selected customers keep their tags and checkmarks.
 4. The table updates to no longer include that customer's work orders.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R5). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R5). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1282,7 +1282,7 @@
 2. Work orders belonging to any other customer are hidden.
 3. The table updates in real time as you make the selections (no apply button on desktop).
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R6, S2-R6). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R6, S2-R6). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1337,7 +1337,7 @@
 3. The Customer filter is removed and the table shows work orders of all customers again.
 4. Other active filters (if any) are not affected.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R7, S8-R2). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R7, S8-R2). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1390,7 +1390,7 @@
 2. The Customer chip stays in the active (blue) state showing the selection and the table stays filtered.
 3. When reopened, the selected customers' tags are still visible in the input area.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R8). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R8). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1442,7 +1442,7 @@
 2. The app does not show an error.
 3. Clearing the search text brings the customer list back.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-N1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-N1). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1496,7 +1496,7 @@
 2. After selecting only that customer, the table shows no rows and the filtered empty state is displayed.
 3. No error is shown.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-E1, S3-N2, S8-R3). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-E1, S3-N2, S8-R3). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1550,7 +1550,7 @@
 3. Below it is a scrollable list of technician names.
 4. A 'Clear Selection' action is shown at the bottom.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-R1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-R1). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1601,7 +1601,7 @@
           <t xml:space="preserve">1. The technician list narrows to only the names matching what you typed.
 2. Deleting the text brings the full list back.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-R2). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-R2). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1655,7 +1655,7 @@
 3. A work order where the technician is assigned only in a non-lead role does not appear.
 4. The table updates in real time as you select.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-R3, S4-R4). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-R3, S4-R4). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1708,7 +1708,7 @@
 2. The Lead Technician filter no longer restricts the table.
 3. Other active filters are not affected.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-R5, S8-R2). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-R5, S8-R2). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1759,7 +1759,7 @@
           <t xml:space="preserve">1. The dropdown closes.
 2. The selection stays applied - the chip stays active and the table stays filtered.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-R6). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-R6). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1811,7 +1811,7 @@
           <t xml:space="preserve">1. The table shows no rows and the filtered empty state is displayed.
 2. No error is shown.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-N1, S8-R3). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-N1, S8-R3). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1864,7 +1864,7 @@
           <t xml:space="preserve">1. The deactivated technician is NOT shown in the filter list.
 2. Active technicians are still listed normally.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-E1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-E1). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1918,7 +1918,7 @@
 3. Below it is a scrollable list of advisor names.
 4. A 'Clear Selection' action is shown at the bottom.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-R1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-R1). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1969,7 +1969,7 @@
           <t xml:space="preserve">1. The advisor list narrows to only the names matching what you typed.
 2. Deleting the text brings the full list back.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-R2). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-R2). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2022,7 +2022,7 @@
 2. The table shows only work orders assigned to any of the selected advisors.
 3. The table updates in real time as you select.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-R3, S5-R4). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-R3, S5-R4). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2075,7 +2075,7 @@
 2. The Service Advisor filter no longer restricts the table.
 3. Other active filters are not affected.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-R5, S8-R2). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-R5, S8-R2). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2126,7 +2126,7 @@
           <t xml:space="preserve">1. The dropdown closes.
 2. The selection stays applied - the chip stays active and the table stays filtered.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-R6). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-R6). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2178,7 +2178,7 @@
           <t xml:space="preserve">1. The table shows no rows and the filtered empty state is displayed.
 2. No error is shown.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-N1, S8-R3). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-N1, S8-R3). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2231,7 +2231,7 @@
           <t xml:space="preserve">1. The deactivated advisor is NOT shown in the filter list.
 2. Active advisors are still listed normally.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-E1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-E1). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2284,7 +2284,7 @@
 3. A 'Clear Selection' action is shown at the bottom.
 4. It is a dropdown (like the other filters), not an on/off toggle.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-R1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-R1). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2336,7 +2336,7 @@
           <t xml:space="preserve">1. The table shows only work orders whose asset is currently on site.
 2. Work orders whose asset is not on site are hidden.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-R2). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-R2). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2389,7 +2389,7 @@
 2. The table switches to showing only the not-on-site work orders.
 3. The chip shows the currently selected value.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-R3). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-R3). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2441,7 +2441,7 @@
 2. The table shows work orders regardless of on-site status again.
 3. Other active filters are not affected.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-R4, S8-R2). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-R4, S8-R2). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2492,7 +2492,7 @@
           <t xml:space="preserve">1. The dropdown closes.
 2. The Yes selection stays applied - the chip stays active and the table stays filtered.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-R5). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-R5). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2544,7 +2544,7 @@
           <t xml:space="preserve">1. The table shows no rows and the filtered empty state is displayed.
 2. No error is shown.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-N1, S8-R3). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-N1, S8-R3). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2598,7 +2598,7 @@
 2. Every work order with the asset on site is excluded.
 3. The chip shows the active No selection.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-R2). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-R2). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2650,7 +2650,7 @@
 2. The chip displays the selected value (for example 'Status: Estimate').
 3. The other chips stay in their default state.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S7-R1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S7-R1). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2701,7 +2701,7 @@
           <t xml:space="preserve">1. The chip lists the selected values starting with the first one and shortens the label when it gets too long (the design shows 'Status: Estimate, In progress, Approved...').
 2. The chip stays a single compact pill - it does not grow to show every value in full.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S7-R2). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S7-R2). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2755,7 +2755,7 @@
 2. As soon as one filter is active, a blue 'Clear Filters' link appears at the right end of the chip row.
 3. When the last active filter is removed, 'Clear Filters' disappears again.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S7-R3, S7-N1, S8-N1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S7-R3, S7-N1, S8-N1). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2810,7 +2810,7 @@
 3. The table shows the full unfiltered list again (no text is in the page Search box, so nothing else is narrowing it).
 4. The 'Clear Filters' link disappears.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R1, S13-R13). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R1, S13-R13). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2863,7 +2863,7 @@
 2. The Customer filter stays selected and active (blue) and keeps filtering the table.
 3. 'Clear Filters' remains visible because a filter is still active.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R2). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R2). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2917,7 +2917,7 @@
 2. Customer A's Approved work order is hidden (wrong status) and customer B's Estimate work order is hidden (wrong customer) - each additional filter narrows the result further.
 3. Both chips are in the active state and 'Clear Filters' is visible.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R3). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R3). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2970,7 +2970,7 @@
 2. The work order table moves up and uses the reclaimed vertical space.
 3. The filter icon shows a pressed/active look while the bar is collapsed.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S1-R4, S1-R5). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S1-R4, S1-R5). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3023,7 +3023,7 @@
 2. The previously selected filters are still shown on their chips in the active (blue) state - nothing was lost while collapsed.
 3. The 'Clear Filters' link is still shown at the right end of the chip row.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S1-R6). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S1-R6). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3076,7 +3076,7 @@
           <t xml:space="preserve">1. After step 2 the filter bar is still collapsed (your choice was remembered).
 2. After step 4 the filter bar is expanded again when you return - whichever state you left it in is restored.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S1-R7, S10-R1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S1-R7, S10-R1). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3128,7 +3128,7 @@
           <t xml:space="preserve">1. After step 1 the filter icon shows no special indicator (only its normal pressed look).
 2. After step 3 the filter icon shows a visual indicator (filters icon in primary blue) signalling that active filters are in effect while the bar is hidden.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S7-R4, S7-N2). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S7-R4, S7-N2). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3180,7 +3180,7 @@
           <t xml:space="preserve">1. The table content does not change when the bar collapses - it still shows only the work orders matching the active filters.
 2. Hiding the bar only hides the chips; it does not remove or pause the filtering.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S7-R5). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S7-R5). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3234,7 +3234,7 @@
 3. No error message or broken layout appears.
 Note for the tester: on the build this test was run against the message reads "No work orders match your filters" - it never mentions the search, even when a search is the only thing narrowing the list. So point 2 fails whenever a search is part of what you applied. That has been reported and the report was closed without a fix, so do not expect it to change.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R3). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch; the build does not behave this way yet.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R3). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8847 - reported, closed without a fix)
 </t>
         </is>
@@ -3289,7 +3289,7 @@
 3. The chips return to their default state.
 Note for the tester: on the build this test was run against the empty screen offers only a "Clear Filters" link. There is no way to clear just the search from that screen, so the second half of point 1 fails. Pressing "Clear Filters" does correctly leave your search in place. That has been reported and the report was closed without a fix, so do not expect it to change.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R4, S8-R5). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch; the build does not behave this way yet.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R4, S8-R5). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8847 - reported, closed without a fix)
 </t>
         </is>
@@ -3344,9 +3344,10 @@
 2. The message offers a way to clear the filters and, because a search is active, a separate way to clear the search.
 3. Clearing the search brings back the list as narrowed by the filter only - the filter is still on.
 4. Clearing the filters leaves your typed word in the box and still applied - each is cleared on its own without wiping the other.
----
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R3, S8-R4, S8-R5, S13-N1, S13-N2). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
-AUTOMATION: READY
+Note for the tester: on the build this was checked against the message reads "No work orders match your filters" and never mentions the search - even when a search is the only thing narrowing the list - and the screen offers only a "Clear Filters" link with no way to clear just the search. So points 1 and 2 do not happen. That is reported and was closed without a fix, so record it as a fail and carry on.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R3, S8-R4, S8-R5, S13-N1, S13-N2). Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8847 - reported, closed without a fix)
 </t>
         </is>
       </c>
@@ -3396,7 +3397,7 @@
           <t xml:space="preserve">1. All five chips are shown: Status, Customer, Lead Technician, Service Advisor, Asset on Site.
 2. Each chip opens its dropdown and can be used.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S9-R1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S9-R1). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3452,7 +3453,7 @@
 2. Customer, Lead Technician, Service Advisor and Asset on Site chips are shown and usable.
 3. After step 4 the table shows only that customer's ESTIMATE work orders - the customer filter narrows the pre-filtered Estimates list.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S9-R2, S2-N1). Note: an earlier answer of 2026-07-17 and the design frame both show the Status button greyed out and pre-filled on this tab; the specification hides it, and the specification is the newer source, so this test follows the specification. Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S9-R2, S2-N1). Note: an earlier answer of 2026-07-17 and the design frame both show the Status button greyed out and pre-filled on this tab; the specification hides it, and the specification is the newer source, so this test follows the specification. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3508,7 +3509,7 @@
 2. Customer, Lead Technician, Service Advisor and Asset on Site chips are shown and usable.
 3. After step 4 the table shows only that customer's COMPLETE work orders.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S9-R3, S2-N2). Note: an earlier answer of 2026-07-17 and the design frame both show the Status button greyed out and pre-filled on this tab; the specification hides it, and the specification is the newer source, so this test follows the specification. Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S9-R3, S2-N2). Note: an earlier answer of 2026-07-17 and the design frame both show the Status button greyed out and pre-filled on this tab; the specification hides it, and the specification is the newer source, so this test follows the specification. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3562,7 +3563,7 @@
 2. The table only ever shows work orders assigned to you (the tab's own scope stays).
 3. After step 2 it shows only YOUR work orders in the ticked status - the filters narrow the user-scoped list, they do not widen it to other users' work orders.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S9-R4). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S9-R4). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3615,7 +3616,7 @@
 2. Back on the All tab the Status chip reappears with the SAME selection (Approved) still applied - the selection was retained in memory, not lost.
 3. The Customer selection is unchanged throughout.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S9-R5, S9-N1, S9-R2). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S9-R5, S9-N1, S9-R2). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3667,7 +3668,7 @@
           <t xml:space="preserve">1. On the very first visit the Estimates tab is the selected one, even though All is the FIRST tab in the row (order and default are different on purpose).
 2. After switching to All and returning, the All tab is selected - the app remembers your last-used tab per account.
 ---
-This is the expected behaviour as per epic SV-8785. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3722,8 +3723,8 @@
 3. After step 4 the filter bar comes back collapsed - the collapsed/expanded state is restored too.
 Known issue: on the build tested the Customer, Lead Technician and Service Advisor buttons come back switched on but WITHOUT the name of the value you picked - the button reads just "Customer" instead of "Customer: Iibay Landscaping". The list is still filtered correctly. The Status and Asset on Site buttons keep their value. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8871
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-R1, S1-R7). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch; the build does not behave this way yet.
-AUTOMATION: READY - EXPECT FAIL (SV-8871)
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-R1, S1-R7). Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8871 - reported, still open)
 </t>
         </is>
       </c>
@@ -3778,7 +3779,7 @@
 2. After closing the browser completely and signing back in (step 5) the same filter selections are still applied - the app remembers your filters for you permanently, not just for one browser session.
 3. The same filter selections are applied on the other computer too - the filters are saved to your account, not to one computer or browser (to confirm live once built).
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-R2, S10-R3, S10-R1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-R2, S10-R3, S10-R1). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3830,8 +3831,8 @@
           <t xml:space="preserve">1. User B does not see user A's filters - user B's page opens with user B's own (or no) filters.
 2. User B's new filter does not change what user A sees; each user keeps their own saved filter state.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-R3). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-R3). Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: HOLD - needs a second test login to prove one person's saved filters do not reach another
 </t>
         </is>
       </c>
@@ -3882,10 +3883,10 @@
           <t xml:space="preserve">1. The deleted customer is silently ignored - no error or warning appears.
 2. The Customer filter now reflects only the still-valid selection (the real customer).
 3. The table is filtered by the remaining valid selection only.
-Known issue: on the build tested the deleted customer is hidden from the dropdown but is STILL used to filter the table - the address bar and the request to the server both still carry it. So step 3 above is expected to fail. It is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8832
----
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-N1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch; the build does not behave this way yet.
-AUTOMATION: READY - EXPECT FAIL (SV-8832)
+Known issue: on the build tested the deleted customer is hidden from the dropdown but is STILL used to filter the table - the address bar and the request to the server both still carry it. So step 3 above is expected to fail. It is already reported. Ticket: &lt;a href="https://shopview.atlassian.net/browse/SV-8832"&gt;https://shopview.atlassian.net/browse/SV-8832&lt;/a&gt;
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-N1). Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8832 - reported, still open)
 </t>
         </is>
       </c>
@@ -3938,8 +3939,8 @@
 2. Returning to the first view restores that view's own selections.
 3. Report tabs likewise keep separate filter choices, each remembered and restored on its own tab.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-R4). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-R4). Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: HOLD - waiting on Branko's Parts and Reports product write-up - the behaviour this case asserts is not documented anywhere yet
 </t>
         </is>
       </c>
@@ -3989,8 +3990,8 @@
           <t xml:space="preserve">1. The old saved choices appear in the new filter bar on the first visit - the update does not lose them (old status choices show in the Status chip, the old asset-here choice shows as Asset on Site: Yes, the old My-Work-Orders toggle maps to the My Work Orders tab, columns and sorting stay).
 2. Those carried-over choices are now saved to the account: the other computer shows them too.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-R2). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-R2). Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: HOLD - cannot be run - it needs an account whose filters were saved before the redesign, and none exists
 </t>
         </is>
       </c>
@@ -4041,7 +4042,7 @@
           <t xml:space="preserve">1. After step 1 the URL changes to include the active filter state.
 2. After step 3 the filter part of the URL is removed again.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-R1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-R1). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4094,8 +4095,8 @@
 3. The same works from a saved bookmark.
 Known issue: two points on this test are expected to fail on the build tested. On a phone-sized screen a link carrying filters shows the buttons as on but lists the wrong work orders (ticket: https://shopview.atlassian.net/browse/SV-8845 - reported, and closed without a fix, so do not expect it to change). And on a desktop screen a Customer, Lead Technician or Service Advisor button opened from a link comes back switched on but without the name of the value, so it reads just "Customer" (ticket: https://shopview.atlassian.net/browse/SV-8871). The list itself is filtered correctly on desktop. Both are already reported.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-R2). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch; the build does not behave this way yet.
-AUTOMATION: READY - EXPECT FAIL (SV-8845 - reported, closed without a fix; SV-8871)
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-R2). Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8845 - reopened, still open)
 </t>
         </is>
       </c>
@@ -4148,8 +4149,8 @@
 3. The table reflects only the valid filter.
 Known issue: a value in the address bar that no longer exists is still sent to the server, so you get an empty list instead of the list without that value. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8832
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-R3). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch; the build does not behave this way yet.
-AUTOMATION: READY - EXPECT FAIL (SV-8832)
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-R3). Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8832 - reported, still open)
 </t>
         </is>
       </c>
@@ -4202,8 +4203,8 @@
 3. No error message or broken page appears.
 Known issue: a broken address is not fully ignored - a wrong tab value can switch the tab and a bad customer value is still sent to the server. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8832
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-N1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch; the build does not behave this way yet.
-AUTOMATION: READY - EXPECT FAIL (SV-8832)
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-N1). Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8832 - reported, still open)
 </t>
         </is>
       </c>
@@ -4262,8 +4263,8 @@
 5. It also empties the Search box and removes your typed text - the search is not something that gets saved, so there is nothing to bring back.
 6. Returning normally later still shows your own saved filters, untouched by the link visit.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-R6, S11-R7, S11-R8). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch; the build does not behave this way yet.
-AUTOMATION: READY - EXPECT FAIL (SV-8828)
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-R6, S11-R7, S11-R8). Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -4319,8 +4320,8 @@
 3. When you open the shared link, 'Back To My Saved Filters' does appear.
 4. After you click it and you are back on your own view, the option disappears again.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-N3, S11-R7). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch; the build does not behave this way yet.
-AUTOMATION: READY - EXPECT FAIL (SV-8828)
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-N3, S11-R7). Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -4371,7 +4372,7 @@
 2. The row scrolls horizontally - chips that do not fit are reachable by swiping.
 3. An arrow at the right-hand edge shows that the row can be scrolled. (This is what the design shows - if your screen looks different, write down what you actually see and carry on.)
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R1). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch, at a phone-sized screen 390 pixels wide.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R1). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4423,7 +4424,7 @@
 2. It lists the five filters as expandable accordion rows, each with its icon, name and a down arrow: Status, Customer, Lead Technician, Service Advisor, Asset on Site.
 3. A sticky blue 'Apply filters' button sits at the bottom of the sheet.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R3, S12-R6). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch, at a phone-sized screen 390 pixels wide.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R3, S12-R6). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4478,7 +4479,7 @@
 2. After 'Apply filters' the sheet closes and the work order list shows only the ticked statuses.
 3. The reopened sheet's title shows the applied-filter count, for example 'All Filters (1)', and the Status accordion header is highlighted with the selected values ticked.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R2, S12-R3, S12-R6, S2-R1). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch, at a phone-sized screen 390 pixels wide.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R2, S12-R3, S12-R6, S2-R1). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4535,9 +4536,8 @@
 5. The chip then shows its active state with the value(s) you picked. 'Clear Selection' and 'Clear Filters' work the same way as on desktop.
 Known issue reported by the test team: a single filter's own sheet is reported to allow only one value and to have no 'Apply filters' button, filtering the list the moment you tap a value, while only the combined 'All Filters' sheet holds your choices until you press a button. That is reported as https://shopview.atlassian.net/browse/SV-8875 and it is still open. We have not re-checked it on the current build, so if you can run this test, write down what you actually see.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R2, S12-R6, S2-R2). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch, at a phone-sized screen 390 pixels wide.
-Please note this is a change from what this test used to say. It used to expect a single filter's sheet to filter the list straight away with no 'Apply filters' button. Branko asked for the new behaviour in the specification and confirmed it on 5 August 2026 when he closed our question (https://shopview.atlassian.net/browse/SV-8825), saying it is written in the specification. The earlier position came from his own written answers of 4 August 2026, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md), where he said a single filter window applies straight away with no button. We have taken his latest word as the one that counts, so if you remember the old behaviour, do not raise it as a new problem.
-AUTOMATION: READY - EXPECT FAIL (SV-8875)
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R2, S12-R6, S2-R2). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8875 - reported, still open)
 </t>
         </is>
       </c>
@@ -4592,8 +4592,8 @@
 3. Removing a tag deselects just that customer.
 4. After 'Apply filters' the list shows only work orders of the remaining selected customers, and the sheet title counts the applied filters (for example 'All Filters (2)').
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R2, S12-R6, S3-R2, S3-R3). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch, at a phone-sized screen 390 pixels wide.
-AUTOMATION: READY - EXPECT FAIL (SV-8875)
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R2, S12-R6, S3-R2, S3-R3). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8875 - reported, still open)
 </t>
         </is>
       </c>
@@ -4646,7 +4646,7 @@
 2. The Service Advisor row opens with a 'Search' field and the advisor list.
 3. Applying a selection filters the work order list just like on desktop.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R2, S12-R6, S4-R1, S5-R1). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch, at a phone-sized screen 390 pixels wide.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R2, S12-R6, S4-R1, S5-R1). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4700,7 +4700,7 @@
 2. Only one option can be selected at a time.
 3. After applying, the list shows only work orders matching the chosen on-site state.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R2, S12-R6, S6-R1). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch, at a phone-sized screen 390 pixels wide.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R2, S12-R6, S6-R1). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4754,8 +4754,8 @@
 3. Using it removes all active filters, the chips return to default and the full list comes back.
 Known issue: on a phone there is no Clear Filters button at all while filters are on. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8846
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R2, S7-R1, S8-R1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch; the build does not behave this way yet.
-AUTOMATION: READY - EXPECT FAIL (SV-8846)
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R2, S7-R1, S8-R1). Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8846 - reported, still open)
 </t>
         </is>
       </c>
@@ -4805,7 +4805,7 @@
           <t xml:space="preserve">1. There is no filter-bar collapse/expand (filter icon) toggle on mobile.
 2. The filter chip row is always visible on the mobile Work Orders page.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R4). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R4). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4857,7 +4857,7 @@
 2. The empty state includes the prompt to clear filters.
 3. No error appears.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-N1, S8-R3). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch, at a phone-sized screen 390 pixels wide.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-N1, S8-R3). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4926,10 +4926,10 @@
 11. Every filter button shown above is a working filter on that page - none of them is display-only.
 12. The choices inside each filter come from your own shop's data (for example your real vendors or categories), so there is no fixed list to compare against - check that the choices you see match the data in your shop.
 13. Still to check on the live build: what the filter icon and the column/layout icon do (the written description does not cover the toolbar icons).
-Not built yet on the build tested: a filter bar exists on Inventory, Part Sales, Catalog and Returns, but Purchase Orders, Vendor Invoices and Vendors have no filter bar at all. If the filter bar is missing on the view you are testing, mark this test BLOCKED - do not mark it failed.
----
-This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch: this part of the product is not built yet, and the controls this test needs were looked for and were not found.
-AUTOMATION: HOLD - the feature is not in the product yet
+14. Not built yet on the build tested: a filter bar exists on Inventory, Part Sales, Catalog and Returns, but Purchase Orders, Vendor Invoices and Vendors have no filter bar at all. If the filter bar is missing on the view you are testing, mark this test BLOCKED - do not mark it failed.
+---
+This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (&lt;a href="https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md)."&gt;https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md).&lt;/a&gt; Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: HOLD - waiting on Branko's Parts and Reports product write-up - the filter bar is built but no source states what it should do
 </t>
         </is>
       </c>
@@ -4982,10 +4982,10 @@
 2. A Clear Selection action is shown at the bottom of the menu.
 3. You can tick both Core and Non Core at the same time - this filter allows more than one choice.
 4. As soon as you tick a choice the list below narrows to matching parts straight away, with no Apply button to press; Clear Selection puts the list back.
-Not built yet on the build tested: a filter bar exists on Inventory, Part Sales, Catalog and Returns, but Purchase Orders, Vendor Invoices and Vendors have no filter bar at all. If the filter bar is missing on the view you are testing, mark this test BLOCKED - do not mark it failed.
----
-This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch: this part of the product is not built yet, and the controls this test needs were looked for and were not found.
-AUTOMATION: HOLD - the feature is not in the product yet
+5. Not built yet on the build tested: a filter bar exists on Inventory, Part Sales, Catalog and Returns, but Purchase Orders, Vendor Invoices and Vendors have no filter bar at all. If the filter bar is missing on the view you are testing, mark this test BLOCKED - do not mark it failed.
+---
+This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md). Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: HOLD - waiting on Branko's Parts and Reports product write-up - the filter bar is built but no source states what it should do
 </t>
         </is>
       </c>
@@ -5036,10 +5036,10 @@
           <t xml:space="preserve">1. The table updates to show only the rows that match the chosen filter value.
 2. The chosen value is shown on the filter button so you can see what is applied.
 3. The list narrows as soon as you pick the value - there is no Apply or Search button to press. Every filter button on every Parts page works this way.
-Not built yet on the build tested: a filter bar exists on Inventory, Part Sales, Catalog and Returns, but Purchase Orders, Vendor Invoices and Vendors have no filter bar at all. If the filter bar is missing on the view you are testing, mark this test BLOCKED - do not mark it failed.
----
-This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch: this part of the product is not built yet, and the controls this test needs were looked for and were not found.
-AUTOMATION: HOLD - the feature is not in the product yet
+4. Not built yet on the build tested: a filter bar exists on Inventory, Part Sales, Catalog and Returns, but Purchase Orders, Vendor Invoices and Vendors have no filter bar at all. If the filter bar is missing on the view you are testing, mark this test BLOCKED - do not mark it failed.
+---
+This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md). Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: HOLD - waiting on Branko's Parts and Reports product write-up - the filter bar is built but no source states what it should do
 </t>
         </is>
       </c>
@@ -5090,10 +5090,10 @@
           <t xml:space="preserve">1. More than one value can be chosen inside the filter, and the button shows what you picked.
 2. Clear Selection removes the choices for that one filter.
 3. A Clear Filters button appears in the filter bar while any filter is set, and using it clears them all at once - exactly as it works on the Work Orders page.
-Not built yet on the build tested: a filter bar exists on Inventory, Part Sales, Catalog and Returns, but Purchase Orders, Vendor Invoices and Vendors have no filter bar at all. If the filter bar is missing on the view you are testing, mark this test BLOCKED - do not mark it failed.
----
-This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch: this part of the product is not built yet, and the controls this test needs were looked for and were not found.
-AUTOMATION: HOLD - the feature is not in the product yet
+4. Not built yet on the build tested: a filter bar exists on Inventory, Part Sales, Catalog and Returns, but Purchase Orders, Vendor Invoices and Vendors have no filter bar at all. If the filter bar is missing on the view you are testing, mark this test BLOCKED - do not mark it failed.
+---
+This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md). Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: HOLD - waiting on Branko's Parts and Reports product write-up - the filter bar is built but no source states what it should do
 </t>
         </is>
       </c>
@@ -5147,10 +5147,10 @@
           <t xml:space="preserve">1. Every filter the page offered before is still offered - nothing has been taken away.
 2. Every choice each of those filters offered before is still available inside the new button.
 3. If any filter or choice is missing, write down exactly which page, which filter and which choice - that is a bug worth reporting.
-Not built yet on the build tested: a filter bar exists on Inventory, Part Sales, Catalog and Returns, but Purchase Orders, Vendor Invoices and Vendors have no filter bar at all. If the filter bar is missing on the view you are testing, mark this test BLOCKED - do not mark it failed.
----
-This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch: this part of the product is not built yet, and the controls this test needs were looked for and were not found.
-AUTOMATION: HOLD - the feature is not in the product yet
+4. Not built yet on the build tested: a filter bar exists on Inventory, Part Sales, Catalog and Returns, but Purchase Orders, Vendor Invoices and Vendors have no filter bar at all. If the filter bar is missing on the view you are testing, mark this test BLOCKED - do not mark it failed.
+---
+This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md). Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: HOLD - waiting on Branko's Parts and Reports product write-up - the filter bar is built but no source states what it should do
 </t>
         </is>
       </c>
@@ -5235,10 +5235,10 @@
 22. Every filter button shown above is a working filter on that report - none of them is display-only.
 23. The choices inside each filter come from your own shop's data (for example your real vendors or categories), so there is no fixed list to compare against - check that the choices you see match the data in your shop.
 24. Still to check on the live build: the real columns of the Sales Tax report and of the six A/R and A/P aging reports. The design uses sample placeholder tables for those, and the written description does not list their columns.
-Not built yet on the build tested: only the first report tab (Timesheet Activities) has a filter bar, with a Date Range and a Filter by Staff button, and no report tab has a page search box. If the controls this test needs are missing, mark this test BLOCKED - do not mark it failed.
----
-This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch: this part of the product is not built yet, and the controls this test needs were looked for and were not found.
-AUTOMATION: HOLD - the feature is not in the product yet
+25. Not built yet on the build tested: only the first report tab (Timesheet Activities) has a filter bar, with a Date Range and a Filter by Staff button, and no report tab has a page search box. If the controls this test needs are missing, mark this test BLOCKED - do not mark it failed.
+---
+This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md). Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: HOLD - waiting on Branko's Parts and Reports product write-up - the filter bar is built but no source states what it should do
 </t>
         </is>
       </c>
@@ -5288,10 +5288,10 @@
         <is>
           <t xml:space="preserve">1. The report updates to show only the rows matching the chosen filter value, and the chosen value is shown on the filter button.
 2. The report narrows as soon as you pick the value - there is no Apply or Run button to press. Every filter button on every report works this way.
-Not built yet on the build tested: only the first report tab (Timesheet Activities) has a filter bar, with a Date Range and a Filter by Staff button, and no report tab has a page search box. If the controls this test needs are missing, mark this test BLOCKED - do not mark it failed.
----
-This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch: this part of the product is not built yet, and the controls this test needs were looked for and were not found.
-AUTOMATION: HOLD - the feature is not in the product yet
+3. Not built yet on the build tested: only the first report tab (Timesheet Activities) has a filter bar, with a Date Range and a Filter by Staff button, and no report tab has a page search box. If the controls this test needs are missing, mark this test BLOCKED - do not mark it failed.
+---
+This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md). Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: HOLD - waiting on Branko's Parts and Reports product write-up - the filter bar is built but no source states what it should do
 </t>
         </is>
       </c>
@@ -5342,10 +5342,10 @@
           <t xml:space="preserve">1. Each of these filter buttons - Location, Transaction Type, Invoice Status, Type, User and Mention - opens a list of choices, lets you tick more than one, and narrows the report straight away with no Apply button.
 2. The choices inside each filter come from your own shop's data (for example your real vendors or categories), so there is no fixed list to compare against - check that the choices you see match the data in your shop.
 3. Write down the choices you actually see behind each of these six buttons. They have not been written down anywhere yet, so your list becomes the record.
-Not built yet on the build tested: only the first report tab (Timesheet Activities) has a filter bar, with a Date Range and a Filter by Staff button, and no report tab has a page search box. If the controls this test needs are missing, mark this test BLOCKED - do not mark it failed.
----
-This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch: this part of the product is not built yet, and the controls this test needs were looked for and were not found.
-AUTOMATION: HOLD - the feature is not in the product yet
+4. Not built yet on the build tested: only the first report tab (Timesheet Activities) has a filter bar, with a Date Range and a Filter by Staff button, and no report tab has a page search box. If the controls this test needs are missing, mark this test BLOCKED - do not mark it failed.
+---
+This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md). Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: HOLD - waiting on Branko's Parts and Reports product write-up - the filter bar is built but no source states what it should do
 </t>
         </is>
       </c>
@@ -5404,11 +5404,11 @@
 4. Choosing Custom shows a From box and a To box. After you fill in only the From date the results do NOT change yet.
 5. As soon as you fill in the To date the results update to show only records inside that range, and the button reads "Date Range: Custom".
 6. Only one date range can be active at a time on that button.
-Note: dates are typed in month/day/year order, the way the screen shows them (for example 07/01/2026). For orientation only, one report was seen offering Today, Yesterday, This week, Last week, This month, Last month, This quarter, Last quarter, This year and Last year - that is an example of what you may find, not a list to check against.
-Where to run this on the build tested: the Reports area has this date button on the Timesheet Activities report. Other report tabs do not have a filter bar yet - if the report you open has no date button, mark this test BLOCKED, not failed.
----
-This is the expected behaviour as per epic SV-8785. It follows the NEWER wording of the Filters specification at Confluence version 18, published on the afternoon of 4 August 2026, which changed the date filter description in the Feature Overview and in the Key Decisions section: the date button now offers standard ready-made periods and starts with the current default range already filled in. An earlier revision of the same specification said the opposite, and this test follows the newer one. The specification does not give this a numbered requirement, so there is no requirement number to quote. Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
-AUTOMATION: HOLD - the report filter bars are not in the product yet beyond the first report tab
+7. Note: dates are typed in month/day/year order, the way the screen shows them (for example 07/01/2026). For orientation only, one report was seen offering Today, Yesterday, This week, Last week, This month, Last month, This quarter, Last quarter, This year and Last year - that is an example of what you may find, not a list to check against.
+8. Where to run this on the build tested: the Reports area has this date button on the Timesheet Activities report. Other report tabs do not have a filter bar yet - if the report you open has no date button, mark this test BLOCKED, not failed.
+---
+This is the expected behaviour as per epic SV-8785. It follows the NEWER wording of the Filters specification at Confluence version 18, published on the afternoon of 4 August 2026, which changed the date filter description in the Feature Overview and in the Key Decisions section: the date button now offers standard ready-made periods and starts with the current default range already filled in. An earlier revision of the same specification said the opposite, and this test follows the newer one. The specification does not give this a numbered requirement, so there is no requirement number to quote. Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: HOLD - waiting on Branko's Parts and Reports product write-up - the date range filter is built but no source states the periods it must offer
 </t>
         </is>
       </c>
@@ -5464,8 +5464,8 @@
 3. The round x clears the text and the full list returns.
 4. Clicking away with an empty box collapses it back to the Search button; with text in it, the box stays open.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R1, S13-R9, S13-R12, S13-R15). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch; the build does not behave this way yet.
-AUTOMATION: READY - EXPECT FAIL (no ticket - reported to the QA lead as one design item, not filed)
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R1, S13-R9, S13-R12, S13-R15). Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -5518,8 +5518,8 @@
 2. Clearing the search keeps the filter applied.
 3. Clearing the filter keeps the search applied - each is cleared by its own control without wiping the other.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R10, S13-R13, S8-R5). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch; the build does not behave this way yet.
-AUTOMATION: READY - EXPECT FAIL (no ticket - reported to the QA lead as one design item, not filed)
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R10, S13-R13, S8-R5). Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -5575,7 +5575,7 @@
 3. The second browser tab starts clean: its Search box is empty and it shows the full list. Each tab keeps its own search.
 4. After closing the browser and coming back, the Search box is empty and the list is unsearched - a typed search is never remembered for next time (your filters, unlike the search, ARE remembered).
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R14, S13-R25, S13-N4, S10-R5). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R14, S13-R25, S13-N4, S10-R5). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5629,7 +5629,7 @@
 3. The malformed part is ignored - the page loads cleanly without an error.
 4. A search arriving via a link is view-only, the same as filters from a link - it does not overwrite your own remembered search.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-R4, S11-R5, S11-N2, S11-R8). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-R4, S11-R5, S11-N2, S11-R8). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5684,9 +5684,10 @@
 3. To make room, the page's main button no longer stretches full-width, and pages with two or more small icon buttons collapse them into a single 'more' menu.
 4. The box stretches to fill the space left in the action row instead of staying the narrow desktop size, and every other toolbar button stays visible and in the same place while you search.
 5. There is no extra 'search is on' badge on mobile: with text in it the box simply stays open showing your text, and an empty box closes back to the Search button when you tap elsewhere - exactly as on desktop.
----
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R16, S13-R17, S13-R18, S13-R19, S13-R20, S12-R5). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
-AUTOMATION: READY
+Note for the tester: on the build this was checked against there is no page Search box on a phone at all. The magnifier in the action row opens the app-wide search instead, and typing in it does not narrow this page's list. So points 1, 2 and 4 do not happen. That is reported and still open, so record it as a fail and carry on.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R16, S13-R17, S13-R18, S13-R19, S13-R20, S12-R5). Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8912 - reported, still open)
 </t>
         </is>
       </c>
@@ -5743,8 +5744,8 @@
 3. Where the table sits inside a dialog (the Work Order Log, the Line Log, the audit log dialog), the Search box is inside that dialog and works there.
 4. The work order Parts tab keeps the local search input it already had - it was deliberately left as it is.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S14-R6, S14-R5, S13-R22, S14-N1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S14-R6, S14-R5, S13-R22, S14-N1). Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: HOLD - cannot be run yet - its own precondition needs the page-search rollout finished everywhere, and it is still part-way through
 </t>
         </is>
       </c>
@@ -5797,7 +5798,7 @@
 2. The same holds on the other pages checked.
 3. Picking a dropdown result still takes you to that record - the navigation search keeps its find-and-open role.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S14-R1, S14-R2, S14-R4, S14-R5). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S14-R1, S14-R2, S14-R4, S14-R5). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5855,8 +5856,8 @@
 5. As soon as you type, your text shows in a dark grey and a small round x appears at the right-hand end of the box.
 6. A very long sentence does not make the box grow and does not cut the text off - the text scrolls sideways inside the box and the cursor stays where you are typing.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R2, S13-R3, S13-R4, S13-R5, S13-R6, S13-R8). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch; the build does not behave this way yet.
-AUTOMATION: READY - EXPECT FAIL (no ticket - reported to the QA lead as one design item, not filed)
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R2, S13-R3, S13-R4, S13-R5, S13-R6, S13-R8). Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -5913,7 +5914,7 @@
 4. Pressing Enter changes nothing that has not already happened - the same rows stay listed and no page reload happens.
 5. Parts Inventory behaves the same way, only it waits a fraction longer before reacting; that longer wait is on purpose because that page carries more data.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R7, S13-R12). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R7, S13-R12). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5969,7 +5970,7 @@
 3. The Completed tab behaves the same way: your word is still there and only that tab's matching rows are listed.
 4. Clearing the search clears it for all the Work Orders tabs - they share one search - and each tab shows its full list again.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R11, S13-R24). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R11, S13-R24). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6025,8 +6026,8 @@
 3. Each report tab behaves the same way: a word typed on one tab stays on that tab only, and each tab remembers its own.
 4. No search is ever applied to a table it was not typed on.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R24, S13-R11, S10-R4). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R24, S13-R11, S10-R4). Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: HOLD - only half of it can be run - the report pages have no page search box yet, so the report-tab half cannot be tested
 </t>
         </is>
       </c>
@@ -6080,7 +6081,7 @@
 3. No error is shown - the leftover search part in the address is simply ignored. (Whether it also disappears from the address is not important; note what you see.)
 4. After typing in the top-of-screen search and reloading, the list is still not narrowed and nothing about that word was remembered for the list.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S14-R3, S14-R2, S14-R1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S14-R3, S14-R2, S14-R1). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6134,7 +6135,7 @@
 2. The Search box stays in the toolbar row with your word still showing; it is not tucked away with the filter bar, because the search sits in the toolbar row and the chips sit in the row below.
 3. Expanding the bar again changes nothing about the search or the narrowed list.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-E1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-E1). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6187,7 +6188,7 @@
 2. The request succeeds (HTTP 200).
 3. The response contains only work orders matching the filters - the filtering is done by the backend, not just hidden client-side.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R2, S3-R6). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R2, S3-R6). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6239,7 +6240,7 @@
 2. The response returns customer A's Estimate and Approved work orders only.
 3. Customer B's work orders are absent - the customer filter and status filter both restrict the result, while the two statuses combine as either-or.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R2, S3-R6, S8-R3). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R2, S3-R6, S8-R3). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6290,10 +6291,9 @@
           <t xml:space="preserve">1. The backend does not fail with a server error (no HTTP 5xx).
 2. The response is a normal, successful list response - the invalid value is ignored or simply matches nothing.
 3. Any still-valid filter values in the same request are applied normally.
-Known issue: the server does not fail, but the value that no longer exists is still applied instead of being dropped. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8832
----
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-N1, S11-R3). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch; the build does not behave this way yet.
-AUTOMATION: READY - EXPECT FAIL (SV-8832)
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-N1, S11-R3). Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -6345,8 +6345,8 @@
 2. In the browser the page still loads without filters and without an error message, matching the malformed-URL requirement.
 Known issue: the server does not fail, but a broken address is not fully ignored by the page. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8832
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-N1). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch; the build does not behave this way yet.
-AUTOMATION: READY - EXPECT FAIL (SV-8832)
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-N1). Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8832 - reported, still open)
 </t>
         </is>
       </c>
@@ -6397,7 +6397,7 @@
 2. The response contains an empty result set (zero work orders) - an empty match is a normal outcome, not an error.
 3. The page renders the no-results empty state from this response.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R3, S2-N3). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R3, S2-N3). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6451,9 +6451,9 @@
 2. On reload the page requests the saved state back (GET, HTTP 200) and applies it - the filters return without you redoing them.
 3. The second user does NOT receive the first user's saved state - each account's saved filters are isolated.
 4. Asking for a never-saved key returns success with an empty value, not an error page.
-Step 3 needs a SECOND sign-in of your own. We could not run it for you: impersonating another user on this branch returns an error, and a new staff member cannot finish signing up because the invitation email cannot be received here. If you have a second account, run step 3 normally. If you do not, mark this test BLOCKED - do not mark it failed. Steps 1, 2 and 4 were confirmed working.
----
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-R2, S10-R3). Last checked on 8/5/2026 against build ShopView v3.4.2-d00239b on the Filters QA branch.
+5. Step 3 needs a SECOND sign-in of your own. We could not run it for you: impersonating another user on this branch returns an error, and a new staff member cannot finish signing up because the invitation email cannot be received here. If you have a second account, run step 3 normally. If you do not, mark this test BLOCKED - do not mark it failed. Steps 1, 2 and 4 were confirmed working.
+---
+This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-R2, S10-R3). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: HOLD - needs a second test login to prove one person's saved filters do not reach another
 </t>
         </is>

--- a/testrail-import/filters-v1-testrail-import.xlsx
+++ b/testrail-import/filters-v1-testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J111"/>
+  <dimension ref="A1:J115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -564,7 +564,7 @@
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with the filter bar visible.
-3. You are on the All tab (on the Estimates and Completed tabs the Status chip is not shown at all, so only four chips appear there).</t>
+3. You are on the All tab (the Estimates and Completed tabs treat the Status chip differently - that is covered by its own tests, so do not compare the chips there).</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -576,11 +576,15 @@
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Exactly five filter chips appear, in this order: Status, Customer, Lead Technician, Service Advisor, Asset on Site.
-2. Each chip shows the filter name and a down arrow (chevron) indicating it opens a dropdown.
-3. Each chip shows only the filter name and the arrow - there is no picture icon in front of the name.
----
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S1-R2, S1-R3). Note: the design frame also draws a small picture icon in front of each filter name; the specification asks only for the name and the arrow, so this test follows the specification. Last checked against build v3.4.2-d00239b on 8/5/2026.
-AUTOMATION: READY
+2. Each chip shows a leading picture icon, then the filter name, then a down arrow (chevron) showing that it opens a dropdown.
+3. The leading icon suits each filter (for example a status glyph for Status, a person for Customer, a wrench for Lead Technician, a headset for Service Advisor, a box for Asset on Site).
+What you should see today: the chips show the filter name and the down arrow only, with no leading picture icon before the name. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8986. (Reported by a colleague from the build; not observed by us.)
+- If you see exactly that, mark this test FAILED and do not raise anything new.
+- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8785, the owning story SV-8786, and the Filters specification at Confluence version 19 (published 6 August 2026) (S1-R2, S1-R3). Note: version 18 of the same specification asked only for the filter name and the chevron; version 19 added the leading picture icon to match the design, and this test follows the newer wording.
+AUTOMATION: READY - EXPECT FAIL (SV-8986)
 </t>
         </is>
       </c>
@@ -616,23 +620,25 @@
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. You are on the Work Orders page.</t>
+2. Estimate work orders exist.
+3. You are on the Work Orders page.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Click the Estimates tab.
-2. Look at the filter bar.</t>
+2. Look at the filter bar.
+3. Look at each chip in turn.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The filter bar is still shown - it does not disappear on this tab.
-2. The Customer, Lead Technician, Service Advisor and Asset on Site chips are all displayed and usable.
-3. The Status chip is not shown on this tab at all - only four chips appear.
----
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S1-N1, S9-R2). Note: an earlier answer of 2026-07-17 and the design frame both show the Status button greyed out and pre-filled on this tab; the specification hides it, and the specification is the newer source, so this test follows the specification. Last checked against build v3.4.2-d00239b on 8/5/2026.
-AUTOMATION: READY
+          <t xml:space="preserve">1. The filter bar is still shown on this tab - it does not disappear.
+2. The Customer, Lead Technician, Service Advisor and Asset on Site chips are all shown and usable.
+3. The Status chip is shown but greyed out and already filled in with this tab's own status, and cannot be clicked or changed.
+---
+This is the expected behaviour as per epic SV-8785, the owning story SV-8794, and Branko's answer of 17 July 2026 (Round 1, question 4, option B), recorded in this file: build/filters/branko-answers-2026-07-17/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-07-17/answers-ingested.md). Note: the Filters specification at Confluence version 19 says instead that the Status chip is hidden on this tab (S9-R2 and S9-R3). That sentence has not been edited since 14 May 2026, which is two and a half months before Branko's answer, so the answer is the later decision and this test follows the answer. Branko has been asked to correct the specification.
+AUTOMATION: HOLD - waiting on Branko to confirm whether the Status chip is hidden or shown greyed out on the Estimates and Completed tabs, and to correct the specification
 </t>
         </is>
       </c>
@@ -3413,7 +3419,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Estimates tab: the Status chip is not shown; the other four still work</t>
+          <t>Estimates tab: Status chip is greyed out and pre-filled; other four work</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3441,20 +3447,21 @@
       <c r="F57" s="2" t="inlineStr">
         <is>
           <t>1. Click the Estimates tab.
-2. Look at the filter bar.
-3. Look for the Status chip - it is not there.
+2. Look at the filter bar and at the Status chip.
+3. Try to click the Status chip and change it.
 4. Open the Customer filter and select one customer.
 5. Look at the table.</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The Status chip is not shown on this tab at all - only four chips appear. The tab already pre-filters the list to Estimate.
-2. Customer, Lead Technician, Service Advisor and Asset on Site chips are shown and usable.
-3. After step 4 the table shows only that customer's ESTIMATE work orders - the customer filter narrows the pre-filtered Estimates list.
----
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S9-R2, S2-N1). Note: an earlier answer of 2026-07-17 and the design frame both show the Status button greyed out and pre-filled on this tab; the specification hides it, and the specification is the newer source, so this test follows the specification. Last checked against build v3.4.2-d00239b on 8/5/2026.
-AUTOMATION: READY
+          <t xml:space="preserve">1. The Status chip is shown, but greyed out and already filled in with this tab's own status (Estimate), because the tab already narrows the list to Estimate.
+2. The Status chip cannot be clicked or changed on this tab.
+3. Customer, Lead Technician, Service Advisor and Asset on Site chips are shown and usable.
+4. After step 4 the table shows only that customer's ESTIMATE work orders - the customer filter narrows the pre-filtered Estimates list.
+---
+This is the expected behaviour as per epic SV-8785, the owning story SV-8794, and Branko's answer of 17 July 2026 (Round 1, question 4, option B), recorded in this file: build/filters/branko-answers-2026-07-17/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-07-17/answers-ingested.md). Note: the Filters specification at Confluence version 19 says instead that the Status chip is hidden on this tab (S9-R2 and S9-R3). That sentence has not been edited since 14 May 2026, which is two and a half months before Branko's answer, so the answer is the later decision and this test follows the answer. Branko has been asked to correct the specification.
+AUTOMATION: HOLD - waiting on Branko to confirm whether the Status chip is hidden or shown greyed out on the Estimates and Completed tabs, and to correct the specification
 </t>
         </is>
       </c>
@@ -3469,7 +3476,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Completed tab: the Status chip is not shown; the other four still work</t>
+          <t>Completed tab: Status chip is greyed out and pre-filled; other four work</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3497,20 +3504,21 @@
       <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1. Click the Completed tab.
-2. Look at the filter bar.
-3. Look for the Status chip - it is not there.
+2. Look at the filter bar and at the Status chip.
+3. Try to click the Status chip and change it.
 4. Open the Customer filter and select one customer.
 5. Look at the table.</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The Status chip is not shown on this tab at all - only four chips appear. The tab already pre-filters the list to Complete.
-2. Customer, Lead Technician, Service Advisor and Asset on Site chips are shown and usable.
-3. After step 4 the table shows only that customer's COMPLETE work orders.
----
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S9-R3, S2-N2). Note: an earlier answer of 2026-07-17 and the design frame both show the Status button greyed out and pre-filled on this tab; the specification hides it, and the specification is the newer source, so this test follows the specification. Last checked against build v3.4.2-d00239b on 8/5/2026.
-AUTOMATION: READY
+          <t xml:space="preserve">1. The Status chip is shown, but greyed out and already filled in with this tab's own status (Complete), because the tab already narrows the list to Complete.
+2. The Status chip cannot be clicked or changed on this tab.
+3. Customer, Lead Technician, Service Advisor and Asset on Site chips are shown and usable.
+4. After step 4 the table shows only that customer's COMPLETE work orders.
+---
+This is the expected behaviour as per epic SV-8785, the owning story SV-8794, and Branko's answer of 17 July 2026 (Round 1, question 4, option B), recorded in this file: build/filters/branko-answers-2026-07-17/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-07-17/answers-ingested.md). Note: the Filters specification at Confluence version 19 says instead that the Status chip is hidden on this tab (S9-R2 and S9-R3). That sentence has not been edited since 14 May 2026, which is two and a half months before Branko's answer, so the answer is the later decision and this test follows the answer. Branko has been asked to correct the specification.
+AUTOMATION: HOLD - waiting on Branko to confirm whether the Status chip is hidden or shown greyed out on the Estimates and Completed tabs, and to correct the specification
 </t>
         </is>
       </c>
@@ -3601,23 +3609,26 @@
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page on the All tab.
-3. A Status selection (for example Approved) and a Customer selection are active.</t>
+3. Work orders exist in the Approved status and Estimate work orders exist too.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>1. Click the Estimates tab and look at the filter bar and the table.
-2. Click back to the All tab and look again.</t>
+          <t>1. On the All tab, open the Status filter and tick Approved.
+2. Open the Customer filter and select one customer.
+3. Click the Estimates tab and look at the filter bar and the table.
+4. Click back to the All tab.
+5. Look at the Status chip and the Customer chip.</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. On the Estimates tab your Status choice is not applied and cannot be changed - the Status chip is not shown on that tab. The Customer selection is still shown and still filters the list.
-2. Back on the All tab the Status chip reappears with the SAME selection (Approved) still applied - the selection was retained in memory, not lost.
+          <t xml:space="preserve">1. On the Estimates tab your Status choice is not applied and cannot be changed - the Status chip is greyed out and already filled in with that tab's own status. The Customer selection is still shown and still narrows the list.
+2. Back on the All tab the Status chip is usable again and shows the SAME selection (Approved) still applied - your choice was kept, not thrown away.
 3. The Customer selection is unchanged throughout.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S9-R5, S9-N1, S9-R2). Last checked against build v3.4.2-d00239b on 8/5/2026.
-AUTOMATION: READY
+This is the expected behaviour as per epic SV-8785, the owning story SV-8794, and Branko's answer of 17 July 2026 (Round 1, question 4, option B), recorded in this file: build/filters/branko-answers-2026-07-17/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-07-17/answers-ingested.md). Note: the Filters specification at Confluence version 19 says instead that the Status chip is hidden on this tab (S9-R2 and S9-R3). That sentence has not been edited since 14 May 2026, which is two and a half months before Branko's answer, so the answer is the later decision and this test follows the answer. Branko has been asked to correct the specification.
+AUTOMATION: HOLD - waiting on Branko to confirm whether the Status chip is hidden or shown greyed out on the Estimates and Completed tabs, and to correct the specification
 </t>
         </is>
       </c>
@@ -4006,38 +4017,98 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>When two devices set different filters, the last one saved wins</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Persistence</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App as the same person on TWO separate browsers at the same time (for example one normal window and one private window, or two different computers). Call them Browser A and Browser B.
+2. Both are on the Work Orders page.
+3. Work orders exist in at least two different statuses, and for at least two different customers.</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>1. In Browser A, set the Status filter to Approved. Wait a few seconds.
+2. In Browser B, set the Status filter to Estimate instead, and clear Approved. Wait a few seconds.
+3. In Browser A, reload the Work Orders page.
+4. Look at the chips and the table in Browser A.
+5. Now in Browser A set a Customer filter as well. Wait a few seconds.
+6. In Browser B, reload the Work Orders page and look at the chips and the table.</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. After the reload in step 3, Browser A shows the filter that was saved MOST RECENTLY - the Estimate choice made in Browser B - not the Approved choice it had set itself. The newer save wins.
+2. The table in Browser A matches those newer filters.
+3. After the reload in step 6, Browser B likewise shows the newest saved state, including the Customer filter that Browser A added in step 5.
+4. Nothing is merged and nothing is duplicated: whichever browser saved last is the one whose filters both browsers end up with.
+5. No error message appears in either browser at any point.
+Note for the tester: the two browsers do not update each other while you watch. You have to reload the page to see the saved filters come back. That is expected.
+---
+This is the expected behaviour as per epic SV-8785, the owning story SV-8795, and the Filters specification at Confluence version 19 (published 6 August 2026) (S10-R2). This test has not yet been checked against any build.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>S10-R2 (last write wins)</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
           <t>Applying filters updates the page URL to reflect the active filter state</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>URL State and Shareable Links</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with no filters applied; note the current URL.</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>1. Apply a Status selection and a Customer selection.
 2. Look at the browser address bar.
 3. Clear all filters and look at the address bar again.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. After step 1 the URL changes to include the active filter state.
 2. After step 3 the filter part of the URL is removed again.
@@ -4047,48 +4118,48 @@
 </t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>SV-8796 (S11-R1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>Opening a shared URL or bookmark loads the page with those filters on</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>URL State and Shareable Links</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You have copied a Work Orders URL that was produced with filters applied (for example Status: Approved + one customer).</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. Open the copied URL in a new browser tab (same signed-in user).
 2. Look at the chips and the table as the page loads.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The page opens with the same filters already applied - chips active with the same values.
 2. The table is already filtered accordingly on load (no need to re-apply anything).
@@ -4100,49 +4171,49 @@
 </t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>SV-8796 (S11-R2; §2 Feature Overview (share or bookmark)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>A URL with a deleted filter value loads and ignores that value</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>URL State and Shareable Links</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You saved a filtered Work Orders URL that includes a throwaway ZZAUTOTEST customer plus one real filter value.
 3. The ZZAUTOTEST customer has since been deleted.</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>1. Open the saved URL.
 2. Look at the chips and the table.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The page loads normally - no error.
 2. The deleted value is ignored; only the still-valid filter value is applied and shown on the chips.
@@ -4154,49 +4225,49 @@
 </t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>SV-8796 (S11-R3) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>A broken filter URL loads the page with no filters and no error</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>URL State and Shareable Links</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You have a valid filtered Work Orders URL to start from.</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>1. Manually break the filter part of the URL (for example scramble the parameter values or insert nonsense text).
 2. Open the broken URL.
 3. Look at the page, the chips and the table.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The Work Orders page loads normally.
 2. No filters are applied (chips in default state, full list shown) - the unrecognizable state is discarded.
@@ -4208,43 +4279,43 @@
 </t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>SV-8796 (S11-N1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>Opening a shared link does not change your own saved filters</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>URL State and Shareable Links</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in and have your OWN filters saved on the Work Orders page (for example one customer).
 2. You have a Work Orders link that carries a DIFFERENT filter state (made by another user or another browser).
 3. You know how to use the page's own Search box on the Work Orders page (the Search button in the toolbar row).</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>1. Note your own saved filters on the Work Orders page.
 2. Open the shared link.
@@ -4254,7 +4325,7 @@
 6. Leave the page and return to Work Orders normally (via the menu).</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The link's filters apply for viewing only - the page shows the shared view.
 2. Changes made during the link visit are also NOT saved to your account.
@@ -4268,43 +4339,43 @@
 </t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>SV-8796 (S11-R6 (URL state runtime-only with no write-back); S11-R7 (Back to my view - also clears the query); S11-R8 (rationale: the query is never saved)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>'Back To My Saved Filters' is not shown when you are on your own view</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>URL State and Shareable Links</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You have your OWN filters saved on the Work Orders page (for example one customer).
 3. You are NOT using a shared link - you have not opened a Work Orders web address that someone sent you.</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work Orders page from the main menu.
 2. Look at the filter bar and the toolbar row for a 'Back To My Saved Filters' option.
@@ -4313,7 +4384,7 @@
 5. Click 'Back To My Saved Filters', then look one more time.</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. On your own view there is no 'Back To My Saved Filters' option anywhere - it only belongs to a shared-link visit.
 2. Changing your own filters does not make it appear.
@@ -4325,48 +4396,48 @@
 </t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>SV-8796 (S11-N3; S11-R7) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>Mobile: chips sit in a scrollable row below the tabs, starting All Filters</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>Mobile Filters</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device (or a mobile-size browser window).
 2. You are on the Work Orders page.</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>1. Look at the row below the tab row (All, Estimates, Completed, My Work Orders).
 2. Swipe the chip row sideways.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. A filter chip row is shown below the tabs, starting with an 'All Filters' chip (with a filter icon) followed by the individual filter chips (Status, Customer, Lead Technician, ...).
 2. The row scrolls horizontally - chips that do not fit are reachable by swiping.
@@ -4377,48 +4448,48 @@
 </t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>SV-8797 (S12-R1) [spec v1.6 2026-07-28]; Branko answers 2026-08-04 Q1 - single-filter sheet applies instantly with no Apply button; the combined All Filters sheet keeps its button</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>Mobile: All Filters opens a sheet of expandable rows with Apply filters</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>Mobile Filters</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device.
 2. You are on the Work Orders page.</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>1. Tap the 'All Filters' chip.
 2. Read the sheet from top to bottom.</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. A bottom sheet slides up with a drag handle at the top, the centered title 'All Filters' and a close (x) button.
 2. It lists the five filters as expandable accordion rows, each with its icon, name and a down arrow: Status, Customer, Lead Technician, Service Advisor, Asset on Site.
@@ -4429,43 +4500,43 @@
 </t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>SV-8797 (S12-R3) [spec v1.6 2026-07-28]; Branko answers 2026-08-04 Q1 - single-filter sheet applies instantly with no Apply button; the combined All Filters sheet keeps its button</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>Mobile: tapping Apply filters applies the statuses and updates the count</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>Mobile Filters</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device.
 2. You are on the Work Orders page on the All tab; work orders exist in several statuses.
 3. The 'All Filters' bottom sheet is open.</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>1. Tap the Status accordion row to expand it.
 2. Tick one or more statuses.
@@ -4473,7 +4544,7 @@
 4. Reopen the All Filters sheet and look at its title.</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Expanding Status reveals the same nine status checkboxes as desktop (Estimate, Approved, In progress, Review, Complete, Invoiced, Paid, Declined, Imported) plus 'Clear Selection'.
 2. After 'Apply filters' the sheet closes and the work order list shows only the ticked statuses.
@@ -4484,42 +4555,42 @@
 </t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (S12-R2; S12-R3; S2-R1) [spec v1.6 2026-07-28]; Branko answers 2026-08-04 Q1 - single-filter sheet applies instantly with no Apply button; the combined All Filters sheet keeps its button</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>Mobile: one chip opens its own sheet and applies only on Apply filters</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>Mobile Filters</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device.
 2. You are on the Work Orders page.</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>1. Tap the Status chip (not the 'All Filters' chip).
 2. Read the sheet that opens.
@@ -4527,7 +4598,7 @@
 4. Tap the 'Apply filters' button inside the sheet and look at the list again.</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. A bottom sheet opens for that single filter: its title row shows the filter's icon and name (for example 'Status') with a close (x) button, and no accordion list of the other filters.
 2. The sheet shows only that filter's options (the nine status checkboxes plus 'Clear Selection').
@@ -4541,43 +4612,43 @@
 </t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>SV-8797 (S12-R2; S12-R3; S2-R6) [spec v1.6 2026-07-28] ; individual-chip real-time per S12-R2 + S2-R6 + tech-plan 2026-07-29; only the combined All Filters sheet is batch; CONFIRMED by Branko answers 2026-08-04 Q1</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>Mobile Customer filter has search, multi-select and removable tags</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>Mobile Filters</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device.
 2. You are on the Work Orders page; several customers exist.
 3. The All Filters sheet is open with the Customer accordion expanded.</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>1. Type part of a customer name in the 'Search' field and watch the list.
 2. Select two or three customers.
@@ -4585,7 +4656,7 @@
 4. Remove one customer with the x on its tag, then tap 'Apply filters'.</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The list narrows to matching names as you type.
 2. Each selected customer appears as a tag with an x in the input area, and its list row shows a checkmark.
@@ -4597,50 +4668,50 @@
 </t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (S12-R2; S3-R2/R3/R5) [spec v1.6 2026-07-28]; Branko answers 2026-08-04 Q1 - single-filter sheet applies instantly with no Apply button; the combined All Filters sheet keeps its button</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>Mobile Lead Technician and Service Advisor filters offer their search lists</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>Mobile Filters</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device.
 2. You are on the Work Orders page; technicians and advisors exist.
 3. The All Filters sheet is open.</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>1. Expand the Lead Technician accordion row and look at its content.
 2. Collapse it, expand the Service Advisor row and look at its content.
 3. Select one name in either list and tap 'Apply filters'.</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The Lead Technician row opens with a 'Search' field and the technician list.
 2. The Service Advisor row opens with a 'Search' field and the advisor list.
@@ -4651,50 +4722,50 @@
 </t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (S12-R2; S4-R1; S5-R1) [spec v1.6 2026-07-28]; Branko answers 2026-08-04 Q1 - single-filter sheet applies instantly with no Apply button; the combined All Filters sheet keeps its button</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>The mobile Asset on Site filter offers Yes/No with Clear Selection in the sheet</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>Mobile Filters</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device.
 2. You are on the Work Orders page; work orders exist in both on-site states.
 3. The All Filters sheet is open.</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>1. Expand the Asset on Site accordion row.
 2. Choose Yes and tap 'Apply filters'.
 3. Look at the list.</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The Asset on Site row opens showing the two options Yes and No plus 'Clear Selection'.
 2. Only one option can be selected at a time.
@@ -4705,49 +4776,49 @@
 </t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (S12-R2; S6-R1/R2/R3) [spec v1.6 2026-07-28]; Branko answers 2026-08-04 Q1 - single-filter sheet applies instantly with no Apply button; the combined All Filters sheet keeps its button</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>Active chips and Clear Filters behave on mobile the same way as on desktop</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>Mobile Filters</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device.
 2. You are on the Work Orders page with at least one filter applied via the sheet.</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>1. Look at the chip row after applying the filter.
 2. Look for a 'Clear Filters' control while a filter is active.
 3. Use it and look at the chips and the list.</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The chip for the applied filter shows the active state with the selected value(s), like on desktop.
 2. A 'Clear Filters' control appears while at least one filter is active.
@@ -4759,48 +4830,48 @@
 </t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (S12-R2; S7-R1/R3; S8-R1) [spec v1.6 2026-07-28]; Branko answers 2026-08-04 Q1 - single-filter sheet applies instantly with no Apply button; the combined All Filters sheet keeps its button</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>Mobile has no collapse toggle: the filter chip row is always visible</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>Mobile Filters</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device.
 2. You are on the Work Orders page.</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>1. Look at the toolbar row (Search, sort icon, Create Work Order button).
 2. Look for any control that would hide the filter chip row.</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. There is no filter-bar collapse/expand (filter icon) toggle on mobile.
 2. The filter chip row is always visible on the mobile Work Orders page.
@@ -4810,48 +4881,48 @@
 </t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>SV-8797 (S12-R4) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>Filters matching no work orders on mobile show the same empty state as desktop</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>Mobile Filters</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device.
 2. You are on the Work Orders page; work orders exist.</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>1. Apply a filter combination that matches no work orders (for example a customer plus a status that customer never has).
 2. Look at the list area.</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The list shows the same no-results empty state as desktop, saying no results were found for the current filters.
 2. The empty state includes the prompt to clear filters.
@@ -4862,42 +4933,103 @@
 </t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (S12-N1; S8-R3/R4) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>On a phone, picking Imported works alone and disables the other filters</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Mobile Filters</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a mobile phone (or a browser window narrowed to phone size).
+2. Imported work orders exist, plus some normal work orders.
+3. You are on the Work Orders page, All tab, with no filters applied.</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>1. Tap 'All Filters' to open the filter sheet.
+2. Expand the Status row and tick Imported.
+3. Look at the other filter rows in the sheet (Customer, Lead Technician, Service Advisor, Asset on Site) and try to use one of them.
+4. Try to tick another status as well as Imported.
+5. Tap the apply button and look at the list.
+6. Reopen the sheet, untick Imported, and look at the other filter rows again.
+7. Tap the apply button and look at the list.</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. While Imported is ticked, the other filters cannot be used - they are greyed out or otherwise blocked, in the same way as on a desktop screen.
+2. Imported cannot be combined with another status: it works on its own.
+3. After you apply, the list shows imported work orders only.
+4. After unticking Imported, the other filters can be used again.
+5. After applying again, the normal list comes back.
+6. The blocking happens as you tap inside the sheet - you do not have to apply first to see the other filters become unusable.
+---
+This is the expected behaviour as per epic SV-8785, the owning story SV-8797, and the Filters specification at Confluence version 19 (published 6 August 2026) (S2-R7, S2-N4, S12-R6). The specification states this rule without limiting it to one screen size, so it applies on a phone as well as on a desktop. This test has not yet been checked against any build.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>S2-R7; S2-N4; S12-R6</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>Every Parts list page shows its designed filter buttons</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>Parts Page Filters</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Parts area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>1. Open the Parts area and go to the Inventory page, and look at the filter buttons shown above the table.
 2. Go to the Part Sales page and look at the filter buttons.
@@ -4911,7 +5043,7 @@
 10. On each page above, open one of its filter buttons, look at the list of choices inside it, and pick a value to check the list changes.</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Inventory shows four filter buttons: Bin Location, Category, Supply and Vendor.
 2. Part Sales shows four filter buttons: Status, Customer, Created by and Date.
@@ -4933,42 +5065,42 @@
 </t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (spec v1.6 §2 Parts Filters; §4 context-specific filter sets + multi-select); Branko answers 2026-07-31 Q2/Q3/Q5/Q7 + 2026-08-04 Q3 (Vendors design exists Figma 11903-10461) + Q8 (Part Sales chips); Figma 11884-16885</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>Part Type filter opens a Core / Non Core list with Clear Selection</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>Parts Page Filters</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Parts area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>1. On the Parts Returns tab, click the Part Type filter button.
 2. Look at the small menu that opens.
@@ -4976,7 +5108,7 @@
 4. Use Clear Selection.</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. A small menu opens with two options: Core and Non Core.
 2. A Clear Selection action is shown at the bottom of the menu.
@@ -4989,49 +5121,49 @@
 </t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (spec v1.6 §2 Feature Overview -&gt; Parts Filters; §4 Key Decisions -&gt; "Context-specific filter sets on Parts and Reports" + "Multi-select where it makes sense"); Branko answers 2026-07-31 Q2/Q3/Q5/Q7; Figma 11884-16885</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>Choosing a Parts filter narrows the list on that page</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>Parts Page Filters</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Parts area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>1. Open a Parts list page that has a filter button (for example Inventory).
 2. Open a filter button and choose one value.
 3. Watch the table below.</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The table updates to show only the rows that match the chosen filter value.
 2. The chosen value is shown on the filter button so you can see what is applied.
@@ -5043,49 +5175,49 @@
 </t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (spec v1.6 §2 Feature Overview -&gt; Parts Filters; §4 Key Decisions -&gt; "Context-specific filter sets on Parts and Reports" + "Multi-select where it makes sense"); Branko answers 2026-07-31 Q2/Q3/Q5/Q7; Figma 11884-16885</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>Parts filters support multiple choices and can be cleared</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>Parts Page Filters</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Parts area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>1. Open a Parts filter button that shows a list of choices.
 2. Select more than one choice, then look at the filter button.
 3. Use the Clear Selection action, then look at the filter bar for a way to clear all filters.</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. More than one value can be chosen inside the filter, and the button shows what you picked.
 2. Clear Selection removes the choices for that one filter.
@@ -5097,43 +5229,43 @@
 </t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (spec v1.6 §2 Feature Overview -&gt; Parts Filters; §4 Key Decisions -&gt; "Context-specific filter sets on Parts and Reports" + "Multi-select where it makes sense"); Branko answers 2026-07-31 Q2/Q3/Q5/Q7; Figma 11884-16885</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>Every filter a page had before is still available in the new filter bar</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>Parts Page Filters</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You have a written list of the filters each Parts page and each report offers today, before the new filter bar (take screenshots of the old screens first, or ask the developers for the list).
 3. Sample data is present in the Parts area and in the Reports area.</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>1. Take your before-list for one page.
 2. Open the same page with the new filter bar.
@@ -5142,7 +5274,7 @@
 5. Repeat steps 1 to 4 for the other Parts pages and for each report.</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Every filter the page offered before is still offered - nothing has been taken away.
 2. Every choice each of those filters offered before is still available inside the new button.
@@ -5154,42 +5286,104 @@
 </t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (spec v1.6 §2 Parts Filters + Reports Filters); Branko answers 2026-07-31 Q3 + 2026-08-04 Q8 ("we should have all filters we support now per each page plus we should add new ones"); tech plan 2026-07-29 rollout rule</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Parts and Reports filters collapse, share and work on a phone as Work Orders do</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Parts Page Filters</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You can also open the same pages on a mobile phone (or a browser window narrowed to phone size).
+3. You are on a Parts page that has a filter bar (for example Inventory), and you can also reach a report that has a filter bar.
+4. Sample data is present in the Parts area and in the Reports area.</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>1. On the Parts page, set one filter so the list is narrowed.
+2. Find the control that collapses the filter bar and use it. Then expand it again.
+3. Leave the page and come back, and look at whether the bar is collapsed or expanded.
+4. With a filter set, copy the page's web address, then open it in a fresh browser window.
+5. Open the same Parts page on a phone and look at how the filter buttons are laid out and how a filter is applied.
+6. Repeat steps 1 to 5 on a report that has a filter bar.</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The filter bar on the Parts page and on the report can be collapsed and expanded, and the table takes the freed space when it is collapsed - exactly as on the Work Orders page.
+2. While the bar is collapsed the filters keep working, and the collapsed control shows that filters are active - exactly as on the Work Orders page.
+3. Whether you left the bar collapsed or expanded is remembered when you come back to that page.
+4. The web address carries the filters you set, and opening that address in a fresh window loads the page with the same filters already applied and the list already narrowed - exactly as on the Work Orders page.
+5. On the phone the filter buttons sit in a row you can scroll sideways, there is no collapse control, and your choices are applied when you tap the apply button rather than as you tap each one - exactly as on the Work Orders page.
+6. Anything that behaves differently from the Work Orders page on any of these points is worth writing down, with the page name.
+Note for the tester: only some Parts views and only some reports have the new filter bar so far. If the page you open has no filter bar, mark this test BLOCKED - do not mark it failed.
+---
+This is the expected behaviour as per epic SV-8785 and Branko's answer of 31 July 2026 (Round 3, question 5, option A), recorded in this file: build/filters/branko-answers-2026-07-31/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-07-31/answers-ingested.md). He said that collapsing, the shareable web address and the phone layout all match the Work Orders page. The Filters specification at Confluence version 19 has no numbered requirement for this, so there is no requirement number to quote. This test has not yet been checked against any build.
+AUTOMATION: HOLD - the new filter bar has reached only some Parts views and one report tab, so most of this cannot be run yet
+</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>Branko Round-3 Q5=A (2026-07-31)</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>Every report page shows its designed filter buttons</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>Reports Page Filters</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Reports area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>1. Open the Reports area and go to the Timesheet Activities report, and look at the filter buttons shown above the report table.
 2. Go to the Timesheets (Payroll Timesheet) report and look at the filter buttons.
@@ -5209,7 +5403,7 @@
 16. On each report above, open one of its filter buttons, look at the list of choices inside it, and pick a value to check the report changes.</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Timesheet Activities shows four filter buttons: Staff, Date, Status and Modified by.
 2. Payroll Timesheet shows two filter buttons: Employee and Date.
@@ -5242,49 +5436,49 @@
 </t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (spec v1.6 §2 Reports Filters; §4 Key Decisions "New date-range filter type" + "Multi-select where it makes sense"); Branko answers 2026-07-31 Q2/Q3/Q5/Q7; Figma 11903-10573</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>Choosing a Reports filter narrows the report results</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>Reports Page Filters</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Reports area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>1. Open the Reports area and go to any report — for example the Sales report.
 2. Open one of the filter buttons shown above the report table and choose one value.
 3. Look at the report table below.</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The report updates to show only the rows matching the chosen filter value, and the chosen value is shown on the filter button.
 2. The report narrows as soon as you pick the value - there is no Apply or Run button to press. Every filter button on every report works this way.
@@ -5295,49 +5489,49 @@
 </t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (spec v1.6 §2 Reports Filters; §4 Key Decisions "New date-range filter type" + "Multi-select where it makes sense"); Branko answers 2026-07-31 Q2/Q3/Q5/Q7; Figma 11903-10573</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>New Reports filter types behave correctly (Location, Transaction Type, etc.)</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>Reports Page Filters</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Reports area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>1. Open the Reports area and go to a report that uses them - for example A/R Aging Detail (Location, Transaction Type) or Notes (Mention).
 2. Look at the filter buttons shown above the report table.
 3. Open each of those filter buttons in turn, tick two choices where possible, and watch the report.</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Each of these filter buttons - Location, Transaction Type, Invoice Status, Type, User and Mention - opens a list of choices, lets you tick more than one, and narrows the report straight away with no Apply button.
 2. The choices inside each filter come from your own shop's data (for example your real vendors or categories), so there is no fixed list to compare against - check that the choices you see match the data in your shop.
@@ -5349,43 +5543,43 @@
 </t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (spec v1.6 §2 Reports Filters; §4 "Multi-select where it makes sense"); Branko answers 2026-07-31 Q3/Q5 + 2026-08-04 Q8 ("We do not have list of all filter items" - confirms no option list exists); Figma 11903-10573</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>Date range filter offers ready-made periods and a custom start/end range</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>Reports Page Filters</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on a report that has a Date Range button - on the build tested that is Reports then the Timesheet Activities report.
 3. Records exist inside and outside the date range you will pick.</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>1. Click the Date Range button.
 2. Look at what the panel offers, and at what the button already reads before you change anything.
@@ -5396,7 +5590,7 @@
 7. Look at the results and at the button.</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The panel that opens offers a set of standard ready-made periods to choose from, plus a Custom option and a Clear Selection link. The written description does not fix which periods are offered, and it can differ per report, so do not check them against a fixed list - write down the ones your report offers.
 2. A period is already filled in when the panel first opens (on Timesheet Activities it is This month), and the button reads that period, for example "Date Range: This month".
@@ -5412,42 +5606,42 @@
 </t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (spec v1.6 §4 "New date-range filter type"; §2 Reports Filters - start/end picker; no presets; no default; applies on the second date); Branko answers 2026-07-31 Q5; tech plan 2026-07-29 D19</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>Page toolbar Search expands in place and narrows the list as you type</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with several work orders listed.</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>1. Find the Search control in the page toolbar (a magnifier icon with the word Search).
 2. Click it.
@@ -5457,7 +5651,7 @@
 6. Expand it again, type text, and click somewhere else.</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The control expands in place into a small search box showing the placeholder 'Type to search'.
 2. The list narrows as you type, after a brief pause - and ONLY this page's list changes, nothing else in the app.
@@ -5469,42 +5663,42 @@
 </t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>SV-8798 (S13-R1 (placement in the toolbar action group); S13-R9 (scoped to this table only); S13-R12; S13-R15 (blur rules)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr"/>
-      <c r="J93" s="2" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>Page search combines with filters and is cleared separately</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with work orders for several customers and statuses.</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>1. Apply one filter (for example a Status).
 2. Type a search term in the page search box.
@@ -5512,7 +5706,7 @@
 4. Re-type the search, then clear ONLY the filter.</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. With both active, the results match the filter AND the search together (both narrow the list at once).
 2. Clearing the search keeps the filter applied.
@@ -5523,43 +5717,43 @@
 </t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (S13-R10 (search and filters are additive); S13-R13 (each cleared independently); S8-R5) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="2" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>Your typed search stays in this browser tab only and is never saved</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with several work orders listed.
 3. You know how to open a second browser tab on the same page.</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>1. Type a search term in the page Search box that matches some work orders.
 2. Sort the table by a column, then move to the next page of results.
@@ -5568,7 +5762,7 @@
 5. Close every browser tab, open the browser again and go back to the Work Orders page.</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Sorting and paging keep your search applied - your text stays in the box and the list stays narrowed.
 2. Leaving the page and coming back also keeps your text in the box and the list still narrowed.
@@ -5580,49 +5774,49 @@
 </t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (S13-R14 (retained for the browser tab session); S13-R25 (never stored against the account; each tab independent); S13-N4 (not restored on a later visit); S10-R5) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr"/>
-      <c r="J95" s="2" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>The search term is part of the shareable page link</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page.</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>1. Type a search term and copy the page address.
 2. Open the copied address in a fresh tab.
 3. Hand-edit the search part of the address into something malformed and load it.</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The address contains the search term after step 1.
 2. The fresh tab opens with the search box filled and the list already narrowed.
@@ -5634,42 +5828,42 @@
 </t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>SV-8796 (S11-R4 (query reflected in the URL); S11-R5 (URL query pre-applied with the control filled); S11-N2 (malformed query ignored with no error); S11-R8 (rationale: no saved value to overwrite)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="2" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>On mobile the search expands in the toolbar and buttons make room</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device.
 2. You are on the Work Orders page.</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>1. Tap the Search control in the page toolbar.
 2. Type a term and watch the list.
@@ -5677,7 +5871,7 @@
 4. With text in the box, tap somewhere else on the screen; then clear the text and tap somewhere else again.</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The search expands inline inside the toolbar - no separate popup window opens.
 2. The list narrows as you type, same as desktop.
@@ -5691,43 +5885,43 @@
 </t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (S13-R16 (inline expansion with no modal); S13-R17 (field fills the remaining width); S13-R18 (CTA hug width); S13-R19 (2+ icon actions -&gt; "more" kebab); S13-R20 (no active-query indicator); S12-R5) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="2" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>Every list page keeps its own search box (Parts, Reports, detail tabs)</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The page-search rollout has finished everywhere (run this sweep at the end of the rollout, not part-way through).
 3. You can reach Work Orders, Customers, Parts, Administration, Reports and the Dashboard.</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>1. Visit the Work Orders surfaces: the Work Orders list, a work order's History tab, the Work Order Log dialog opened from that tab's kebab menu, a line's Line Log dialog opened from the Lines tab, and the work order's Notes tab.
 2. Visit the customer and asset surfaces: the Customers list, then on one customer - Contacts, Assets, Invoices, Work Orders, Part Sales, Fees &amp; Discounts, Notes; then on one asset - Work Orders, Invoices, Notes.
@@ -5737,7 +5931,7 @@
 6. On each surface, find that table's own Search box and type something that matches one of its rows. Then open a work order's Parts tab and look at the search input it already has.</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Every table listed above has its own Search box - no table lost the ability to narrow by text.
 2. Each Search box narrows only its own table; nothing else in the app changes.
@@ -5749,42 +5943,42 @@
 </t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (S14-R6 (audit: 42 surfaces across 39 components; Work Order Parts excluded); S14-R5 (app-wide sweep); S13-R22 (every table carries a search control); S14-N1 (verify once at the end)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>The top navigation search no longer filters page lists</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with several work orders listed.</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>1. Type a term into the TOP NAVIGATION search (the app-wide search at the top), not the page's own search box.
 2. Watch the Work Orders list while typing.
@@ -5792,7 +5986,7 @@
 4. Pick one of the results offered in the navigation search's dropdown.</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The page list does NOT narrow while you type in the navigation search - only its dropdown of matching records appears.
 2. The same holds on the other pages checked.
@@ -5803,42 +5997,42 @@
 </t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>SV-8799 (S14-R1 (navigational results only); S14-R2 (the page-filtering code path is removed rather than dormant); S14-R4 (the list is left untouched); S14-R5) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr"/>
-      <c r="J99" s="2" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>The Search box changes look as you hover over it, open it and type</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with several work orders listed.</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>1. Look at the right-hand end of the toolbar row, before the small icon buttons and before the 'Create Work Order' button.
 2. Move the mouse pointer over the 'Search' button without clicking.
@@ -5847,7 +6041,7 @@
 5. Delete what you typed and type a very long sentence instead.</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. A 'Search' button is shown with a small magnifier icon next to the word 'Search'; it is plain text on a see-through background, with no border and no fill.
 2. Hovering over it gives it a light grey background; the word 'Search' keeps its own colour.
@@ -5861,43 +6055,43 @@
 </t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>SV-8798 (S13-R2 (default text button); S13-R3 (hover fill); S13-R4 (expands in place at 180px); S13-R5 (placeholder "Type to search"); S13-R6 (typed text + X-circle clear); S13-R8 (long queries scroll)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>The list narrows shortly after you stop typing, with no button to press</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with several work orders listed.
 3. You can also open the Parts Inventory page.</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>1. On the Work Orders page open the Search box and type a few letters that match some work orders. Do NOT press Enter.
 2. Watch the work order table for a second or two.
@@ -5906,7 +6100,7 @@
 5. Do the same on the Parts Inventory page.</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The list narrows on its own a moment after you stop typing (about a third of a second) - you never press Enter or any button.
 2. The matching rows appear in the table you were already looking at; no separate results page, results list or pop-up window opens.
@@ -5919,43 +6113,43 @@
 </t>
         </is>
       </c>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>SV-8798 (S13-R7 (applies as you type; debounced 300ms; no apply/submit; Enter not required; Inventory 350ms); S13-R12 (results replace the table in place)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>One search box serves all Work Orders tabs and searches the tab you are on</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Work orders exist in several statuses, so the All, Estimates and Completed tabs each have rows.
 3. You have a word (for example part of a customer name) that matches work orders on more than one of those tabs.</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>1. On the All tab, type that word into the page Search box.
 2. Click the Estimates tab and look at the Search box and the list.
@@ -5963,7 +6157,7 @@
 4. Still on the Completed tab, clear the search with the round x, then go back to the All tab.</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. On the All tab only the rows matching your word remain.
 2. On the Estimates tab your word is still in the Search box, and the list shows only Estimates rows that match it - no rows from the other tabs appear.
@@ -5975,43 +6169,43 @@
 </t>
         </is>
       </c>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>SV-8798 (S13-R11 (search applies within the active tab only); S13-R24 (the Work Orders tabs share a single query - views of one dataset)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="2" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>Each Report tab and each Parts view keeps its own separate search</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You can open at least two Parts views (for example Inventory and Purchase Orders).
 3. You can open a report that has more than one tab.</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>1. On a Parts view (for example Inventory) type a word into that page's Search box.
 2. Switch to another Parts view (for example Purchase Orders) and look at its Search box and list.
@@ -6019,7 +6213,7 @@
 4. Do the same on a report with tabs: search on one tab, then switch to another tab of the same report.</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The second Parts view opens with an empty Search box and its full list - the word you typed on the first view is not carried over.
 2. Going back to the first view brings its own word back and narrows its list again.
@@ -6031,42 +6225,42 @@
 </t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (S13-R24 (Reports sub-tabs and Parts views each keep their own query); S13-R11; S10-R4 (each view/tab keeps its own set)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" s="2" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>An old link carrying a top-search word no longer narrows the page list</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You have a Work Orders web address from BEFORE this change that still carries a word typed into the top-of-screen search (a bookmark, or a link someone sent). If you do not have one, hand-type that old search part onto the end of the Work Orders address.</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>1. Open that old web address.
 2. Look at the work order list and at the page's own Search box.
@@ -6074,7 +6268,7 @@
 4. Type a word into the top-of-screen search, then reload the page.</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The page opens with the normal list for your own saved filters - the old search word does NOT narrow the list.
 2. The page's own Search box is empty; nothing was carried into it.
@@ -6086,50 +6280,50 @@
 </t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>SV-8799 (S14-R3 (state / URL parameters / persisted values carrying a global search term into page filtering are removed with it); S14-R2; S14-R1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="2" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>Collapsing the filter bar keeps an active search working</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page and the filter bar is expanded.
 3. A word is typed in the page Search box and the list is narrowed by it.</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>1. With the search still active, click the filter button in the toolbar to collapse the filter bar.
 2. Look at the table and at the toolbar row.
 3. Expand the filter bar again.</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The list stays narrowed by your word - collapsing the filter bar does not cancel the search.
 2. The Search box stays in the toolbar row with your word still showing; it is not tucked away with the filter bar, because the search sits in the toolbar row and the chips sit in the row below.
@@ -6140,49 +6334,110 @@
 </t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>SV-8798 (S13-E1 (a collapsed filter bar keeps an active query applying and the search control stays in the toolbar); §4 Key Decisions (page search is separate from the filter bar)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="2" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>On a phone, pages with two or more icon buttons collapse them into one menu</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Page Search Toolbar</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a mobile phone (or a browser window narrowed to phone size).
+2. You can reach the Parts area and the Reports area.
+3. You know what the same pages look like on a desktop screen, so you can tell which small icon buttons each one has.</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>1. Open Parts then Inventory. Look at the row of buttons at the top right of the table.
+2. Open Parts then Purchase Orders. Look at the same row of buttons.
+3. Open Reports then the Timesheet Activities report. Look at the same row of buttons.
+4. Open the Technician Efficiency report, look at the button row on its Invoiced tab, then open its Completed tab and look again.
+5. Open the Sales Tax report, choose the Collected tab, and look at the button row.
+6. On each of those pages, tap the 'more' button (usually three dots) and look at what is inside it.
+7. For comparison, open a page that has only ONE small icon button in its toolbar and look at its button row.</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. On each of the pages in steps 1 to 5, the small icon-only buttons are NOT all shown side by side. They are gathered into a single 'more' button.
+2. Tapping that 'more' button opens a short menu listing those actions, and each one still works from there.
+3. Both view tabs of the Technician Efficiency report behave the same way as each other.
+4. Nothing is lost: every action that is available on a desktop screen can still be reached on the phone, either directly or from inside the 'more' menu.
+5. On the comparison page in step 7, which has only one small icon button, that button is still shown on its own - a single icon action is not put into a 'more' menu.
+6. This rule applies to any page carrying two or more small icon buttons, so if you find another page like that, it should behave the same way. Write down any page that does not.
+---
+This is the expected behaviour as per epic SV-8785, the owning story SV-8798, and the Filters specification at Confluence version 19 (published 6 August 2026) (S13-R19). This test has not yet been checked against any build.
+AUTOMATION: READY
+</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>S13-R19</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>The work order list request carries the active filter selections</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>API — Work Orders List Filtering</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser with developer tools open on the Network tab.
 2. You are on the Work Orders page with no filters applied.</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>1. Apply a Status selection and a Customer selection in the filter bar.
 2. In the Network tab, find the work order list request the page sends after the change.
 3. Inspect the request's parameters.</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The list request includes the active filter selections as request parameters (status values and customer identifiers).
 2. The request succeeds (HTTP 200).
@@ -6193,48 +6448,48 @@
 </t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (S2-R2; S3-R6 (backend view)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>A combined multi-filter request returns only work orders matching all filters</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>API — Work Orders List Filtering</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with developer tools open on the Network tab.
 2. Seeded ZZAUTOTEST work orders exist: customer A with an Estimate and an Approved work order, customer B with an Estimate work order.</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>1. On the Work Orders page apply Status = Estimate + Approved and Customer = customer A.
 2. Capture the resulting list request and response.</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. One request carries both filters together (both statuses and the customer).
 2. The response returns customer A's Estimate and Approved work orders only.
@@ -6245,48 +6500,48 @@
 </t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (S2-R2; S3-R6; S8-R3 (backend view)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="I111" s="2" t="inlineStr"/>
+      <c r="J111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>A request with a deleted or unknown filter value gives no server error</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>API — Work Orders List Filtering</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in and can replay/edit the work order list request (developer tools or an API client).
 2. You have a captured filtered list request, and one of its filter values has since been deleted (for example a removed ZZAUTOTEST customer) or is a made-up identifier.</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>1. Send the list request containing the no-longer-existing (or made-up) filter value.
 2. Inspect the HTTP status and the response body.</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The backend does not fail with a server error (no HTTP 5xx).
 2. The response is a normal, successful list response - the invalid value is ignored or simply matches nothing.
@@ -6297,49 +6552,49 @@
 </t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (S10-N1; S11-R3) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="2" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="I112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>A list request with malformed filter parameters does not produce a server error</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>API — Work Orders List Filtering</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in and can replay/edit the work order list request.
 2. You have a captured filtered list request to tamper with.</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>1. Corrupt the filter parameters (wrong types, scrambled values, nonsense text) and send the request.
 2. Inspect the HTTP status and the response body.
 3. Also open the equally malformed page URL in the browser and watch the page.</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The backend responds gracefully - no HTTP 5xx / crash; either a normal (unfiltered or empty) list or a clean validation response.
 2. In the browser the page still loads without filters and without an error message, matching the malformed-URL requirement.
@@ -6350,48 +6605,48 @@
 </t>
         </is>
       </c>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>SV-8796 (S11-N1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I109" s="2" t="inlineStr"/>
-      <c r="J109" s="2" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="I113" s="2" t="inlineStr"/>
+      <c r="J113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>A filter combination matching nothing returns an empty list, not an error</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>API — Work Orders List Filtering</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with developer tools open on the Network tab.
 2. A filter combination is known to match no work orders (for example a seeded customer plus a status they never have).</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>1. Apply that filter combination on the Work Orders page.
 2. Capture the list request and response.</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The request succeeds (HTTP 200).
 2. The response contains an empty result set (zero work orders) - an empty match is a normal outcome, not an error.
@@ -6402,42 +6657,42 @@
 </t>
         </is>
       </c>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (S8-R3; S2-N3) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="2" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+      <c r="I114" s="2" t="inlineStr"/>
+      <c r="J114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>Saved-filters service round-trip: save, reload, and per-user isolation</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>API — Work Orders List Filtering</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser with developer tools open on the Network tab.
 2. A second user account is available.</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>1. On the Work Orders page, change a filter and watch the Network tab for the save request the page sends shortly after.
 2. Reload the page and find the load request for the saved page state.
@@ -6445,7 +6700,7 @@
 4. With an API client (or by editing the request), ask the saved-state service for a page key that was never saved.</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Changing a filter sends a save (PUT) to the per-user page-preferences service carrying the page's state, and it succeeds (HTTP 200).
 2. On reload the page requests the saved state back (GET, HTTP 200) and applies it - the filters return without you redoing them.
@@ -6458,13 +6713,13 @@
 </t>
         </is>
       </c>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>SV-8795 (S10-R2 (filters stored server-side against the user account; last write wins); S10-R3 (saved per user)) + tech plan 2026-07-29 s4-1.3 (GET/PUT per-user page preferences) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I111" s="2" t="inlineStr"/>
-      <c r="J111" s="2" t="inlineStr"/>
+      <c r="I115" s="2" t="inlineStr"/>
+      <c r="J115" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/filters-v1-testrail-import.xlsx
+++ b/testrail-import/filters-v1-testrail-import.xlsx
@@ -524,10 +524,9 @@
         <is>
           <t xml:space="preserve">1. A filter bar is visible directly below the tab row and above the work order table.
 2. The filter bar is shown by default (expanded) without having to turn anything on.
-Note for the tester: on the build this was checked against, the five filter buttons sit to the RIGHT of the tab row instead of on their own row beneath it, so point 1 does not happen. That is reported and still open, so record it as a fail against point 1 and carry on.
----
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S1-R1). Last checked against build v3.4.2-d00239b on 8/5/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8883 - reported, still open)
+---
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S1-R1), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -578,13 +577,9 @@
           <t xml:space="preserve">1. Exactly five filter chips appear, in this order: Status, Customer, Lead Technician, Service Advisor, Asset on Site.
 2. Each chip shows a leading picture icon, then the filter name, then a down arrow (chevron) showing that it opens a dropdown.
 3. The leading icon suits each filter (for example a status glyph for Status, a person for Customer, a wrench for Lead Technician, a headset for Service Advisor, a box for Asset on Site).
-What you should see today: the chips show the filter name and the down arrow only, with no leading picture icon before the name. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8986. (Reported by a colleague from the build; not observed by us.)
-- If you see exactly that, mark this test FAILED and do not raise anything new.
-- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
-- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
----
-This is the expected behaviour as per epic SV-8785, the owning story SV-8786, and the Filters specification at Confluence version 19 (published 6 August 2026) (S1-R2, S1-R3). Note: version 18 of the same specification asked only for the filter name and the chevron; version 19 added the leading picture icon to match the design, and this test follows the newer wording.
-AUTOMATION: READY - EXPECT FAIL (SV-8986)
+---
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, the owning story SV-8786, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S1-R2, S1-R3), read on 11 August 2026. Note: version 18 of the same specification asked only for the filter name and the chevron; version 19 added the leading picture icon to match the design, and this test follows the newer wording.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -637,7 +632,7 @@
 2. The Customer, Lead Technician, Service Advisor and Asset on Site chips are all shown and usable.
 3. The Status chip is shown but greyed out and already filled in with this tab's own status, and cannot be clicked or changed.
 ---
-This is the expected behaviour as per epic SV-8785, the owning story SV-8794, and Branko's answer of 17 July 2026 (Round 1, question 4, option B), recorded in this file: build/filters/branko-answers-2026-07-17/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-07-17/answers-ingested.md). Note: the Filters specification at Confluence version 19 says instead that the Status chip is hidden on this tab (S9-R2 and S9-R3). That sentence has not been edited since 14 May 2026, which is two and a half months before Branko's answer, so the answer is the later decision and this test follows the answer. Branko has been asked to correct the specification.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, the owning story SV-8794, read on 11 August 2026, and Branko's answer of 17 July 2026 (Round 1, question 4, option B), recorded in this file: build/filters/branko-answers-2026-07-17/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-07-17/answers-ingested.md), read on 11 August 2026. Note: the Filters specification at Confluence version 19 says instead that the Status chip is hidden on this tab (S9-R2 and S9-R3). That sentence has not been edited since 14 May 2026, which is two and a half months before Branko's answer, so the answer is the later decision and this test follows the answer. Branko has been asked to correct the specification.
 AUTOMATION: HOLD - waiting on Branko to confirm whether the Status chip is hidden or shown greyed out on the Estimates and Completed tabs, and to correct the specification
 </t>
         </is>
@@ -692,7 +687,7 @@
 3. All checkboxes are unticked (nothing selected yet).
 4. A 'Clear Selection' action is shown at the bottom of the dropdown.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R1, S2-R4). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S2-R1, S2-R4), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -728,16 +723,18 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
+          <t xml:space="preserve">1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page on the All tab.
-3. Work orders exist in at least two different statuses (for example some Estimate and some Approved - create ZZAUTOTEST work orders if needed).</t>
+3. Work orders exist in at least two different statuses (for example some Estimate and some Approved - create ZZAUTOTEST work orders if needed).
+</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1. Click the Status filter chip.
+          <t xml:space="preserve">1. Click the Status filter chip.
 2. Tick the checkbox for one status (for example Estimate).
-3. Watch the work order table while the dropdown is still open.</t>
+3. Watch the work order table while the dropdown is still open.
+</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -746,7 +743,7 @@
 2. The table updates immediately to show only work orders in the selected status - there is no confirm or apply button on desktop.
 3. Work orders in other statuses are no longer listed.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R2, S2-R3, S2-R6). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S2-R2, S2-R3, S2-R6), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -782,16 +779,18 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
+          <t xml:space="preserve">1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page on the All tab.
-3. Work orders exist in at least three different statuses (seed ZZAUTOTEST work orders if needed).</t>
+3. Work orders exist in at least three different statuses (seed ZZAUTOTEST work orders if needed).
+</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1. Click the Status filter chip.
+          <t xml:space="preserve">1. Click the Status filter chip.
 2. Tick two or more statuses (for example Estimate and Approved).
-3. Look at the work order table.</t>
+3. Look at the work order table.
+</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -801,7 +800,7 @@
 3. Work orders in statuses that are not ticked are hidden.
 4. There is no limit on how many statuses you can tick.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R2). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S2-R2), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -837,16 +836,18 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
+          <t xml:space="preserve">1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page on the All tab.
-3. Two or more statuses are ticked in the Status filter and the table is filtered.</t>
+3. Two or more statuses are ticked in the Status filter and the table is filtered.
+</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1. Open the Status dropdown (if it is not already open).
+          <t xml:space="preserve">1. Open the Status dropdown (if it is not already open).
 2. Click 'Clear Selection' at the bottom of the dropdown.
-3. Look at the checkboxes and the table.</t>
+3. Look at the checkboxes and the table.
+</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -855,7 +856,7 @@
 2. The Status filter is removed and the table returns to showing work orders of every status.
 3. Only the Status filter is affected - any other active filters stay applied.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R4, S8-R2). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S2-R4, S8-R2), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -891,15 +892,17 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
+          <t xml:space="preserve">1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page on the All tab.
-3. The Status dropdown is open with at least one status ticked.</t>
+3. The Status dropdown is open with at least one status ticked.
+</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1. Click anywhere outside the open dropdown (for example on empty page space).
-2. Look at the dropdown, the Status chip and the table.</t>
+          <t xml:space="preserve">1. Click anywhere outside the open dropdown (for example on empty page space).
+2. Look at the dropdown, the Status chip and the table.
+</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -908,7 +911,7 @@
 2. The ticked statuses stay selected - the Status chip stays in its active state showing the selection.
 3. The table stays filtered by the selected statuses.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R5). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S2-R5), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -944,16 +947,18 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
+          <t xml:space="preserve">1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page on the All tab.
-3. At least one status exists that NO current work order has (for example Imported - check the list first).</t>
+3. At least one status exists that NO current work order has (for example Imported - check the list first).
+</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1. Click the Status filter chip.
+          <t xml:space="preserve">1. Click the Status filter chip.
 2. Tick only the status that no work order currently has.
-3. Look at the table area.</t>
+3. Look at the table area.
+</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -962,7 +967,7 @@
 2. An empty state is displayed saying no results were found for the current filters (see the Empty State cases for its full content).
 3. The app does not show an error.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-N3, S8-R3). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S2-N3, S8-R3), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -998,17 +1003,19 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
+          <t xml:space="preserve">1. You are signed in to the ShopView App on a desktop browser.
 2. Imported work orders exist, plus some normal work orders.
-3. You are on the Work Orders page, All tab, no filters applied.</t>
+3. You are on the Work Orders page, All tab, no filters applied.
+</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1. Open the Status filter and tick Imported.
+          <t xml:space="preserve">1. Open the Status filter and tick Imported.
 2. Look at the other filter chips (Customer, Lead Technician, Service Advisor, Asset on Site).
 3. Try to combine Imported with another status.
-4. Untick Imported.</t>
+4. Untick Imported.
+</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1018,7 +1025,7 @@
 3. Imported cannot be combined with other statuses - selecting it works alone.
 4. Unticking Imported re-enables the other chips and the normal list returns.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R7, S2-N4). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S2-R7, S2-N4), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1073,7 +1080,7 @@
 3. Below it is a scrollable list of customer names.
 4. A 'Clear Selection' action is shown at the bottom of the panel.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R1). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S3-R1), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1126,7 +1133,7 @@
 2. Customers that do not match are removed from the list.
 3. Deleting the text brings the full list back.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R2). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S3-R2), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1181,7 +1188,7 @@
 3. Long customer names on tags are shortened with an ellipsis (for example 'Texas Truck And Aut...').
 4. You can keep selecting as many customers as needed - there is no selection limit.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R3, S3-R4). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S3-R3, S3-R4), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1235,7 +1242,7 @@
 3. The other selected customers keep their tags and checkmarks.
 4. The table updates to no longer include that customer's work orders.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R5). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S3-R5), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1288,7 +1295,7 @@
 2. Work orders belonging to any other customer are hidden.
 3. The table updates in real time as you make the selections (no apply button on desktop).
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R6, S2-R6). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S3-R6, S2-R6), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1343,7 +1350,7 @@
 3. The Customer filter is removed and the table shows work orders of all customers again.
 4. Other active filters (if any) are not affected.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R7, S8-R2). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S3-R7, S8-R2), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1396,7 +1403,7 @@
 2. The Customer chip stays in the active (blue) state showing the selection and the table stays filtered.
 3. When reopened, the selected customers' tags are still visible in the input area.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-R8). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S3-R8), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1448,7 +1455,7 @@
 2. The app does not show an error.
 3. Clearing the search text brings the customer list back.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-N1). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S3-N1), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1502,7 +1509,7 @@
 2. After selecting only that customer, the table shows no rows and the filtered empty state is displayed.
 3. No error is shown.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S3-E1, S3-N2, S8-R3). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S3-E1, S3-N2, S8-R3), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1556,7 +1563,7 @@
 3. Below it is a scrollable list of technician names.
 4. A 'Clear Selection' action is shown at the bottom.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-R1). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S4-R1), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1607,7 +1614,7 @@
           <t xml:space="preserve">1. The technician list narrows to only the names matching what you typed.
 2. Deleting the text brings the full list back.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-R2). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S4-R2), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1661,7 +1668,7 @@
 3. A work order where the technician is assigned only in a non-lead role does not appear.
 4. The table updates in real time as you select.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-R3, S4-R4). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S4-R3, S4-R4), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1714,7 +1721,7 @@
 2. The Lead Technician filter no longer restricts the table.
 3. Other active filters are not affected.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-R5, S8-R2). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S4-R5, S8-R2), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1765,7 +1772,7 @@
           <t xml:space="preserve">1. The dropdown closes.
 2. The selection stays applied - the chip stays active and the table stays filtered.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-R6). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S4-R6), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1817,7 +1824,7 @@
           <t xml:space="preserve">1. The table shows no rows and the filtered empty state is displayed.
 2. No error is shown.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-N1, S8-R3). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S4-N1, S8-R3), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1870,7 +1877,7 @@
           <t xml:space="preserve">1. The deactivated technician is NOT shown in the filter list.
 2. Active technicians are still listed normally.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S4-E1). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S4-E1), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1924,7 +1931,7 @@
 3. Below it is a scrollable list of advisor names.
 4. A 'Clear Selection' action is shown at the bottom.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-R1). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S5-R1), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1960,14 +1967,16 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. You are on the Work Orders page with the Service Advisor dropdown open.</t>
+          <t xml:space="preserve">1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Work Orders page with the Service Advisor dropdown open.
+</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1. Type part of one advisor's name into the 'Search' field.
-2. Watch the list while you type.</t>
+          <t xml:space="preserve">1. Type part of one advisor's name into the 'Search' field.
+2. Watch the list while you type.
+</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1975,7 +1984,7 @@
           <t xml:space="preserve">1. The advisor list narrows to only the names matching what you typed.
 2. Deleting the text brings the full list back.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-R2). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S5-R2), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2011,15 +2020,17 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
+          <t xml:space="preserve">1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page on the All tab.
-3. Work orders exist with different service advisors assigned (seed ZZAUTOTEST data if needed).</t>
+3. Work orders exist with different service advisors assigned (seed ZZAUTOTEST data if needed).
+</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1. Open the Service Advisor filter and select one or two advisors.
-2. Look at the checkboxes in the list and the Service Advisor column in the table.</t>
+          <t xml:space="preserve">1. Open the Service Advisor filter and select one or two advisors.
+2. Look at the checkboxes in the list and the Service Advisor column in the table.
+</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2028,7 +2039,7 @@
 2. The table shows only work orders assigned to any of the selected advisors.
 3. The table updates in real time as you select.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-R3, S5-R4). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S5-R3, S5-R4), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2064,15 +2075,17 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
+          <t xml:space="preserve">1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page.
-3. One or more advisors are selected in the Service Advisor filter.</t>
+3. One or more advisors are selected in the Service Advisor filter.
+</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1. Open the Service Advisor dropdown and click 'Clear Selection' at the bottom.
-2. Look at the list and the table.</t>
+          <t xml:space="preserve">1. Open the Service Advisor dropdown and click 'Clear Selection' at the bottom.
+2. Look at the list and the table.
+</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2081,7 +2094,7 @@
 2. The Service Advisor filter no longer restricts the table.
 3. Other active filters are not affected.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-R5, S8-R2). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S5-R5, S8-R2), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2117,14 +2130,16 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. You are on the Work Orders page with the Service Advisor dropdown open and one advisor selected.</t>
+          <t xml:space="preserve">1. You are signed in to the ShopView App on a desktop browser.
+2. You are on the Work Orders page with the Service Advisor dropdown open and one advisor selected.
+</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1. Click anywhere outside the dropdown.
-2. Look at the dropdown, the chip and the table.</t>
+          <t xml:space="preserve">1. Click anywhere outside the dropdown.
+2. Look at the dropdown, the chip and the table.
+</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2132,7 +2147,7 @@
           <t xml:space="preserve">1. The dropdown closes.
 2. The selection stays applied - the chip stays active and the table stays filtered.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-R6). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S5-R6), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2168,15 +2183,17 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
+          <t xml:space="preserve">1. You are signed in to the ShopView App on a desktop browser.
 2. An advisor exists who is not assigned to ANY work order (create a fresh ZZAUTOTEST staff member if needed).
-3. You are on the Work Orders page on the All tab with no other filters active.</t>
+3. You are on the Work Orders page on the All tab with no other filters active.
+</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1. Open the Service Advisor filter and select only that advisor.
-2. Look at the table.</t>
+          <t xml:space="preserve">1. Open the Service Advisor filter and select only that advisor.
+2. Look at the table.
+</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -2184,7 +2201,7 @@
           <t xml:space="preserve">1. The table shows no rows and the filtered empty state is displayed.
 2. No error is shown.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-N1, S8-R3). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S5-N1, S8-R3), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2220,16 +2237,18 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
+          <t xml:space="preserve">1. You are signed in to the ShopView App on a desktop browser.
 2. A test advisor (ZZAUTOTEST) exists and is visible in the Service Advisor filter list.
-3. That test advisor is then made inactive/deactivated in staff administration (restore them afterwards).</t>
+3. That test advisor is then made inactive/deactivated in staff administration (restore them afterwards).
+</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1. On the Work Orders page, open the Service Advisor filter.
+          <t xml:space="preserve">1. On the Work Orders page, open the Service Advisor filter.
 2. Search for the deactivated advisor's name.
-3. Look at the list.</t>
+3. Look at the list.
+</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -2237,7 +2256,7 @@
           <t xml:space="preserve">1. The deactivated advisor is NOT shown in the filter list.
 2. Active advisors are still listed normally.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S5-E1). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S5-E1), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2290,7 +2309,7 @@
 3. A 'Clear Selection' action is shown at the bottom.
 4. It is a dropdown (like the other filters), not an on/off toggle.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-R1). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S6-R1), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2342,7 +2361,7 @@
           <t xml:space="preserve">1. The table shows only work orders whose asset is currently on site.
 2. Work orders whose asset is not on site are hidden.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-R2). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S6-R2), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2395,7 +2414,7 @@
 2. The table switches to showing only the not-on-site work orders.
 3. The chip shows the currently selected value.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-R3). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S6-R3), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2447,7 +2466,7 @@
 2. The table shows work orders regardless of on-site status again.
 3. Other active filters are not affected.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-R4, S8-R2). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S6-R4, S8-R2), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2498,7 +2517,7 @@
           <t xml:space="preserve">1. The dropdown closes.
 2. The Yes selection stays applied - the chip stays active and the table stays filtered.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-R5). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S6-R5), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2550,7 +2569,7 @@
           <t xml:space="preserve">1. The table shows no rows and the filtered empty state is displayed.
 2. No error is shown.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-N1, S8-R3). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S6-N1, S8-R3), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2604,7 +2623,7 @@
 2. Every work order with the asset on site is excluded.
 3. The chip shows the active No selection.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S6-R2). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S6-R2), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2653,10 +2672,10 @@
       <c r="G42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The Status chip changes to an active/highlighted look (blue pill).
-2. The chip displays the selected value (for example 'Status: Estimate').
+2. The chip displays the selected value (on the build tested it reads 'Status : Estimate').
 3. The other chips stay in their default state.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S7-R1). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S7-R1), read on 11 August 2026. Last checked against build v3.6-3e9dd6d on 8/11/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2704,10 +2723,10 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The chip lists the selected values starting with the first one and shortens the label when it gets too long (the design shows 'Status: Estimate, In progress, Approved...').
+          <t xml:space="preserve">1. The chip displays the FIRST selected value followed by a count of the additional selections - it does not spell out every value (on the build tested, ticking Estimate, In progress and Approved gives 'Status : Estimate, +2').
 2. The chip stays a single compact pill - it does not grow to show every value in full.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S7-R2). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S7-R2), read on 11 August 2026. Last checked against build v3.6-3e9dd6d on 8/11/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2761,7 +2780,7 @@
 2. As soon as one filter is active, a blue 'Clear Filters' link appears at the right end of the chip row.
 3. When the last active filter is removed, 'Clear Filters' disappears again.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S7-R3, S7-N1, S8-N1). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S7-R3, S7-N1, S8-N1), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2816,7 +2835,7 @@
 3. The table shows the full unfiltered list again (no text is in the page Search box, so nothing else is narrowing it).
 4. The 'Clear Filters' link disappears.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R1, S13-R13). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S8-R1, S13-R13), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2869,7 +2888,7 @@
 2. The Customer filter stays selected and active (blue) and keeps filtering the table.
 3. 'Clear Filters' remains visible because a filter is still active.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R2). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S8-R2), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2905,9 +2924,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. You are on the Work Orders page on the All tab.
-3. Seed ZZAUTOTEST work orders so that: customer A has an Estimate work order and an Approved work order, and customer B has an Estimate work order.</t>
+          <t>Logged in as Admin on the Work Orders page, All tab; customer A has an Estimate and an Approved WO, customer B has an Estimate WO (all API-seeded)</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -2919,11 +2936,10 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Only customer A's Estimate work order is shown.
-2. Customer A's Approved work order is hidden (wrong status) and customer B's Estimate work order is hidden (wrong customer) - each additional filter narrows the result further.
-3. Both chips are in the active state and 'Clear Filters' is visible.
----
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R3). Last checked against build v3.4.2-d00239b on 8/5/2026.
+          <t xml:space="preserve">Two active chips, a visible Clear Filters button, and exactly the intersection of both filters in the table
+Note on where each part comes from: the two active chips and the Clear Filters button are both stated in the product description. The "matching both" part is not - the product description never says what should happen when two different filters are used at the same time. That rule is stated in the engineering technical design, which requires the filters to combine with "AND across fields".
+---
+This is the expected behaviour as per story SV-8793, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (§2 Feature Overview), read on 11 August 2026, and as per the engineering technical design for the app-wide filter redesign (§0.3 and §1.8), read on 11 August 2026 - that document carries no version number of its own and records its own baseline as "Spec baseline: v1.3".
 AUTOMATION: READY
 </t>
         </is>
@@ -2976,7 +2992,7 @@
 2. The work order table moves up and uses the reclaimed vertical space.
 3. The filter icon shows a pressed/active look while the bar is collapsed.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S1-R4, S1-R5). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S1-R4, S1-R5), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3029,7 +3045,7 @@
 2. The previously selected filters are still shown on their chips in the active (blue) state - nothing was lost while collapsed.
 3. The 'Clear Filters' link is still shown at the right end of the chip row.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S1-R6). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S1-R6), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3082,7 +3098,7 @@
           <t xml:space="preserve">1. After step 2 the filter bar is still collapsed (your choice was remembered).
 2. After step 4 the filter bar is expanded again when you return - whichever state you left it in is restored.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S1-R7, S10-R1). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S1-R7, S10-R1), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3134,7 +3150,7 @@
           <t xml:space="preserve">1. After step 1 the filter icon shows no special indicator (only its normal pressed look).
 2. After step 3 the filter icon shows a visual indicator (filters icon in primary blue) signalling that active filters are in effect while the bar is hidden.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S7-R4, S7-N2). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S7-R4, S7-N2), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3186,7 +3202,7 @@
           <t xml:space="preserve">1. The table content does not change when the bar collapses - it still shows only the work orders matching the active filters.
 2. Hiding the bar only hides the chips; it does not remove or pause the filtering.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S7-R5). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S7-R5), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3238,10 +3254,9 @@
           <t xml:space="preserve">1. The table body is replaced by an empty state (not just a bare empty grid).
 2. The empty state shows a message saying no results were found for the filters and the search you have on.
 3. No error message or broken layout appears.
-Note for the tester: on the build this test was run against the message reads "No work orders match your filters" - it never mentions the search, even when a search is the only thing narrowing the list. So point 2 fails whenever a search is part of what you applied. That has been reported and the report was closed without a fix, so do not expect it to change.
----
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R3). Last checked against build v3.4.2-d00239b on 8/5/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8847 - reported, closed without a fix)
+---
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S8-R3), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -3293,10 +3308,9 @@
           <t xml:space="preserve">1. The empty state includes a link to clear the filters, and - when you also have a search on - a separate way to clear just the search.
 2. Clicking it removes the active filters and the full work order list is shown again (with no text in the Search box, nothing else is narrowing the list).
 3. The chips return to their default state.
-Note for the tester: on the build this test was run against the empty screen offers only a "Clear Filters" link. There is no way to clear just the search from that screen, so the second half of point 1 fails. Pressing "Clear Filters" does correctly leave your search in place. That has been reported and the report was closed without a fix, so do not expect it to change.
----
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R4, S8-R5). Last checked against build v3.4.2-d00239b on 8/5/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8847 - reported, closed without a fix)
+---
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S8-R4, S8-R5), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -3350,10 +3364,9 @@
 2. The message offers a way to clear the filters and, because a search is active, a separate way to clear the search.
 3. Clearing the search brings back the list as narrowed by the filter only - the filter is still on.
 4. Clearing the filters leaves your typed word in the box and still applied - each is cleared on its own without wiping the other.
-Note for the tester: on the build this was checked against the message reads "No work orders match your filters" and never mentions the search - even when a search is the only thing narrowing the list - and the screen offers only a "Clear Filters" link with no way to clear just the search. So points 1 and 2 do not happen. That is reported and was closed without a fix, so record it as a fail and carry on.
----
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R3, S8-R4, S8-R5, S13-N1, S13-N2). Last checked against build v3.4.2-d00239b on 8/5/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8847 - reported, closed without a fix)
+---
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S8-R3, S8-R4, S8-R5, S13-N1, S13-N2), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -3403,7 +3416,7 @@
           <t xml:space="preserve">1. All five chips are shown: Status, Customer, Lead Technician, Service Advisor, Asset on Site.
 2. Each chip opens its dropdown and can be used.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S9-R1). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S9-R1), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3460,7 +3473,7 @@
 3. Customer, Lead Technician, Service Advisor and Asset on Site chips are shown and usable.
 4. After step 4 the table shows only that customer's ESTIMATE work orders - the customer filter narrows the pre-filtered Estimates list.
 ---
-This is the expected behaviour as per epic SV-8785, the owning story SV-8794, and Branko's answer of 17 July 2026 (Round 1, question 4, option B), recorded in this file: build/filters/branko-answers-2026-07-17/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-07-17/answers-ingested.md). Note: the Filters specification at Confluence version 19 says instead that the Status chip is hidden on this tab (S9-R2 and S9-R3). That sentence has not been edited since 14 May 2026, which is two and a half months before Branko's answer, so the answer is the later decision and this test follows the answer. Branko has been asked to correct the specification.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, the owning story SV-8794, read on 11 August 2026, and Branko's answer of 17 July 2026 (Round 1, question 4, option B), recorded in this file: build/filters/branko-answers-2026-07-17/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-07-17/answers-ingested.md), read on 11 August 2026. Note: the Filters specification at Confluence version 19 says instead that the Status chip is hidden on this tab (S9-R2 and S9-R3). That sentence has not been edited since 14 May 2026, which is two and a half months before Branko's answer, so the answer is the later decision and this test follows the answer. Branko has been asked to correct the specification.
 AUTOMATION: HOLD - waiting on Branko to confirm whether the Status chip is hidden or shown greyed out on the Estimates and Completed tabs, and to correct the specification
 </t>
         </is>
@@ -3517,7 +3530,7 @@
 3. Customer, Lead Technician, Service Advisor and Asset on Site chips are shown and usable.
 4. After step 4 the table shows only that customer's COMPLETE work orders.
 ---
-This is the expected behaviour as per epic SV-8785, the owning story SV-8794, and Branko's answer of 17 July 2026 (Round 1, question 4, option B), recorded in this file: build/filters/branko-answers-2026-07-17/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-07-17/answers-ingested.md). Note: the Filters specification at Confluence version 19 says instead that the Status chip is hidden on this tab (S9-R2 and S9-R3). That sentence has not been edited since 14 May 2026, which is two and a half months before Branko's answer, so the answer is the later decision and this test follows the answer. Branko has been asked to correct the specification.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, the owning story SV-8794, read on 11 August 2026, and Branko's answer of 17 July 2026 (Round 1, question 4, option B), recorded in this file: build/filters/branko-answers-2026-07-17/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-07-17/answers-ingested.md), read on 11 August 2026. Note: the Filters specification at Confluence version 19 says instead that the Status chip is hidden on this tab (S9-R2 and S9-R3). That sentence has not been edited since 14 May 2026, which is two and a half months before Branko's answer, so the answer is the later decision and this test follows the answer. Branko has been asked to correct the specification.
 AUTOMATION: HOLD - waiting on Branko to confirm whether the Status chip is hidden or shown greyed out on the Estimates and Completed tabs, and to correct the specification
 </t>
         </is>
@@ -3571,7 +3584,7 @@
 2. The table only ever shows work orders assigned to you (the tab's own scope stays).
 3. After step 2 it shows only YOUR work orders in the ticked status - the filters narrow the user-scoped list, they do not widen it to other users' work orders.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S9-R4). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S9-R4), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3627,7 +3640,7 @@
 2. Back on the All tab the Status chip is usable again and shows the SAME selection (Approved) still applied - your choice was kept, not thrown away.
 3. The Customer selection is unchanged throughout.
 ---
-This is the expected behaviour as per epic SV-8785, the owning story SV-8794, and Branko's answer of 17 July 2026 (Round 1, question 4, option B), recorded in this file: build/filters/branko-answers-2026-07-17/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-07-17/answers-ingested.md). Note: the Filters specification at Confluence version 19 says instead that the Status chip is hidden on this tab (S9-R2 and S9-R3). That sentence has not been edited since 14 May 2026, which is two and a half months before Branko's answer, so the answer is the later decision and this test follows the answer. Branko has been asked to correct the specification.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, the owning story SV-8794, read on 11 August 2026, and Branko's answer of 17 July 2026 (Round 1, question 4, option B), recorded in this file: build/filters/branko-answers-2026-07-17/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-07-17/answers-ingested.md), read on 11 August 2026. Note: the Filters specification at Confluence version 19 says instead that the Status chip is hidden on this tab (S9-R2 and S9-R3). That sentence has not been edited since 14 May 2026, which is two and a half months before Branko's answer, so the answer is the later decision and this test follows the answer. Branko has been asked to correct the specification.
 AUTOMATION: HOLD - waiting on Branko to confirm whether the Status chip is hidden or shown greyed out on the Estimates and Completed tabs, and to correct the specification
 </t>
         </is>
@@ -3679,7 +3692,7 @@
           <t xml:space="preserve">1. On the very first visit the Estimates tab is the selected one, even though All is the FIRST tab in the row (order and default are different on purpose).
 2. After switching to All and returning, the All tab is selected - the app remembers your last-used tab per account.
 ---
-This is the expected behaviour as per epic SV-8785. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026. The Filters specification at Confluence version 19 (published 6 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3732,10 +3745,9 @@
           <t xml:space="preserve">1. After step 2 the same Status and Customer selections are still applied - chips active with the same values, table filtered the same way.
 2. The filter bar is still expanded (as you left it).
 3. After step 4 the filter bar comes back collapsed - the collapsed/expanded state is restored too.
-Known issue: on the build tested the Customer, Lead Technician and Service Advisor buttons come back switched on but WITHOUT the name of the value you picked - the button reads just "Customer" instead of "Customer: Iibay Landscaping". The list is still filtered correctly. The Status and Asset on Site buttons keep their value. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8871
----
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-R1, S1-R7). Last checked against build v3.4.2-d00239b on 8/5/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8871 - reported, still open)
+---
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S10-R1, S1-R7), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -3790,7 +3802,7 @@
 2. After closing the browser completely and signing back in (step 5) the same filter selections are still applied - the app remembers your filters for you permanently, not just for one browser session.
 3. The same filter selections are applied on the other computer too - the filters are saved to your account, not to one computer or browser (to confirm live once built).
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-R2, S10-R3, S10-R1). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S10-R2, S10-R3, S10-R1), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3842,7 +3854,7 @@
           <t xml:space="preserve">1. User B does not see user A's filters - user B's page opens with user B's own (or no) filters.
 2. User B's new filter does not change what user A sees; each user keeps their own saved filter state.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-R3). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S10-R3), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: HOLD - needs a second test login to prove one person's saved filters do not reach another
 </t>
         </is>
@@ -3894,10 +3906,13 @@
           <t xml:space="preserve">1. The deleted customer is silently ignored - no error or warning appears.
 2. The Customer filter now reflects only the still-valid selection (the real customer).
 3. The table is filtered by the remaining valid selection only.
-Known issue: on the build tested the deleted customer is hidden from the dropdown but is STILL used to filter the table - the address bar and the request to the server both still carry it. So step 3 above is expected to fail. It is already reported. Ticket: &lt;a href="https://shopview.atlassian.net/browse/SV-8832"&gt;https://shopview.atlassian.net/browse/SV-8832&lt;/a&gt;
----
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-N1). Last checked against build v3.4.2-d00239b on 8/5/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8832 - reported, still open)
+What you should see today: a customer the system no longer recognises is hidden from the Customer list, but it is still used to narrow the table. The address bar keeps it and the request to the server still carries it, so you get an empty list instead of the list without that value.
+- If you see exactly that, mark this test FAILED and do not raise anything new.
+- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S10-N1), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8832)
 </t>
         </is>
       </c>
@@ -3950,8 +3965,8 @@
 2. Returning to the first view restores that view's own selections.
 3. Report tabs likewise keep separate filter choices, each remembered and restored on its own tab.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-R4). Last checked against build v3.4.2-d00239b on 8/5/2026.
-AUTOMATION: HOLD - waiting on Branko's Parts and Reports product write-up - the behaviour this case asserts is not documented anywhere yet
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S10-R4), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: HOLD - held for the QA lead's ruling only - the behaviour IS documented (S10-R4 says each Parts view and each Report tab keeps its own separate filter set and each persists independently), so the earlier reason that no source described it was wrong
 </t>
         </is>
       </c>
@@ -4001,7 +4016,7 @@
           <t xml:space="preserve">1. The old saved choices appear in the new filter bar on the first visit - the update does not lose them (old status choices show in the Status chip, the old asset-here choice shows as Asset on Site: Yes, the old My-Work-Orders toggle maps to the My Work Orders tab, columns and sorting stay).
 2. Those carried-over choices are now saved to the account: the other computer shows them too.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-R2). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026), read on 11 August 2026. That specification has no numbered requirement for carrying over filters that were saved before the redesign; S10-R2 is named only for the account-based model it describes, and the carry-over itself comes from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/tech-plan-2026-07-29/TechPlan-AppWide-Filter-Redesign.md, read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: HOLD - cannot be run - it needs an account whose filters were saved before the redesign, and none exists
 </t>
         </is>
@@ -4061,7 +4076,7 @@
 5. No error message appears in either browser at any point.
 Note for the tester: the two browsers do not update each other while you watch. You have to reload the page to see the saved filters come back. That is expected.
 ---
-This is the expected behaviour as per epic SV-8785, the owning story SV-8795, and the Filters specification at Confluence version 19 (published 6 August 2026) (S10-R2). This test has not yet been checked against any build.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, the owning story SV-8795, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S10-R2), read on 11 August 2026. This test has not yet been checked against any build.
 AUTOMATION: READY
 </t>
         </is>
@@ -4113,7 +4128,7 @@
           <t xml:space="preserve">1. After step 1 the URL changes to include the active filter state.
 2. After step 3 the filter part of the URL is removed again.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-R1). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S11-R1), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4164,10 +4179,9 @@
           <t xml:space="preserve">1. The page opens with the same filters already applied - chips active with the same values.
 2. The table is already filtered accordingly on load (no need to re-apply anything).
 3. The same works from a saved bookmark.
-Known issue: two points on this test are expected to fail on the build tested. On a phone-sized screen a link carrying filters shows the buttons as on but lists the wrong work orders (ticket: https://shopview.atlassian.net/browse/SV-8845 - reported, and closed without a fix, so do not expect it to change). And on a desktop screen a Customer, Lead Technician or Service Advisor button opened from a link comes back switched on but without the name of the value, so it reads just "Customer" (ticket: https://shopview.atlassian.net/browse/SV-8871). The list itself is filtered correctly on desktop. Both are already reported.
----
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-R2). Last checked against build v3.4.2-d00239b on 8/5/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8845 - reopened, still open)
+---
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S11-R2), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -4218,10 +4232,13 @@
           <t xml:space="preserve">1. The page loads normally - no error.
 2. The deleted value is ignored; only the still-valid filter value is applied and shown on the chips.
 3. The table reflects only the valid filter.
-Known issue: a value in the address bar that no longer exists is still sent to the server, so you get an empty list instead of the list without that value. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8832
----
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-R3). Last checked against build v3.4.2-d00239b on 8/5/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8832 - reported, still open)
+What you should see today: a value in the address bar that no longer exists is still sent to the server, so the page comes back with an empty list instead of the list without that value. The Customer button shows no value name.
+- If you see exactly that, mark this test FAILED and do not raise anything new.
+- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S11-R3), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8832)
 </t>
         </is>
       </c>
@@ -4272,10 +4289,13 @@
           <t xml:space="preserve">1. The Work Orders page loads normally.
 2. No filters are applied (chips in default state, full list shown) - the unrecognizable state is discarded.
 3. No error message or broken page appears.
-Known issue: a broken address is not fully ignored - a wrong tab value can switch the tab and a bad customer value is still sent to the server. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8832
----
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-N1). Last checked against build v3.4.2-d00239b on 8/5/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8832 - reported, still open)
+What you should see today: a broken address is not fully ignored. A customer value the system does not recognise is still sent to the server and the page shows an empty list, and a wrong tab value can still switch the tab.
+- If you see exactly that, mark this test FAILED and do not raise anything new.
+- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S11-N1), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8832)
 </t>
         </is>
       </c>
@@ -4329,12 +4349,12 @@
         <is>
           <t xml:space="preserve">1. The link's filters apply for viewing only - the page shows the shared view.
 2. Changes made during the link visit are also NOT saved to your account.
-3. A 'Back To My Saved Filters' option is shown while you are looking at the shared link. (If the wording on screen is slightly different, note what it says and carry on.)
-4. Clicking 'Back To My Saved Filters' brings back your own saved filters and removes the filter part from the web address.
+3. A 'Back to my view' option is shown while you are looking at the shared link. Note for the tester: the specification names this action 'Back to my view' and says the wording is deliberate, because the action clears the search box as well as the filters. If the button on screen says something else, write down exactly what it says and carry on - do not fail the test on the wording alone.
+4. Clicking 'Back to my view' brings back your own saved filters and removes the filter part from the web address.
 5. It also empties the Search box and removes your typed text - the search is not something that gets saved, so there is nothing to bring back.
 6. Returning normally later still shows your own saved filters, untouched by the link visit.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-R6, S11-R7, S11-R8). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S11-R6, S11-R7, S11-R8), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4350,7 +4370,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>'Back To My Saved Filters' is not shown when you are on your own view</t>
+          <t>'Back to my view' is not shown when you are on your own view</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -4386,12 +4406,12 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. On your own view there is no 'Back To My Saved Filters' option anywhere - it only belongs to a shared-link visit.
+          <t xml:space="preserve">1. On your own view there is no 'Back to my view' option anywhere - it only belongs to a shared-link visit. Note for the tester: the specification names this action 'Back to my view' and says the wording is deliberate, because the action clears the search box as well as the filters. If the button on screen says something else, write down exactly what it says and carry on - do not fail the test on the wording alone.
 2. Changing your own filters does not make it appear.
-3. When you open the shared link, 'Back To My Saved Filters' does appear.
+3. When you open the shared link, 'Back to my view' does appear.
 4. After you click it and you are back on your own view, the option disappears again.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-N3, S11-R7). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S11-N3, S11-R7), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4427,23 +4447,24 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in to the ShopView App on a mobile device (or a mobile-size browser window).
-2. You are on the Work Orders page.</t>
+          <t xml:space="preserve">1. You are signed in to the ShopView App on a mobile device (or a mobile-size browser window).
+2. You are on the Work Orders page.
+</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>1. Look at the row below the tab row (All, Estimates, Completed, My Work Orders).
-2. Swipe the chip row sideways.</t>
+          <t xml:space="preserve">1. Look at the row below the tab row (All, Estimates, Completed, My Work Orders).
+2. Swipe the chip row sideways.
+</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. A filter chip row is shown below the tabs, starting with an 'All Filters' chip (with a filter icon) followed by the individual filter chips (Status, Customer, Lead Technician, ...).
 2. The row scrolls horizontally - chips that do not fit are reachable by swiping.
-3. An arrow at the right-hand edge shows that the row can be scrolled. (This is what the design shows - if your screen looks different, write down what you actually see and carry on.)
----
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R1). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). Last checked against build v3.4.2-d00239b on 8/5/2026.
+---
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S12-R1), read on 11 August 2026. The 'All Filters' entry point is not in the specification: it comes from the engineering technical plan, decision D15, in this file: build/filters/tech-plan-2026-07-29/TechPlan-AppWide-Filter-Redesign.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/tech-plan-2026-07-29/TechPlan-AppWide-Filter-Redesign.md), read on 11 August 2026
 AUTOMATION: READY
 </t>
         </is>
@@ -4479,23 +4500,25 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in to the ShopView App on a mobile device.
-2. You are on the Work Orders page.</t>
+          <t xml:space="preserve">1. You are signed in to the ShopView App on a mobile device.
+2. You are on the Work Orders page.
+</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>1. Tap the 'All Filters' chip.
-2. Read the sheet from top to bottom.</t>
+          <t xml:space="preserve">1. Tap the 'All Filters' chip.
+2. Read the sheet from top to bottom.
+</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. A bottom sheet slides up with a drag handle at the top, the centered title 'All Filters' and a close (x) button.
 2. It lists the five filters as expandable accordion rows, each with its icon, name and a down arrow: Status, Customer, Lead Technician, Service Advisor, Asset on Site.
-3. A sticky blue 'Apply filters' button sits at the bottom of the sheet.
----
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R3, S12-R6). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). Last checked against build v3.4.2-d00239b on 8/5/2026.
+3. A sticky blue 'Apply Filters' button sits at the bottom of the sheet.
+---
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S12-R3, S12-R6), read on 11 August 2026. Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). Last checked against build v3.6-3e9dd6d on 8/11/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4540,17 +4563,17 @@
         <is>
           <t>1. Tap the Status accordion row to expand it.
 2. Tick one or more statuses.
-3. Tap the 'Apply filters' button.
+3. Tap the 'Apply Filters' button.
 4. Reopen the All Filters sheet and look at its title.</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Expanding Status reveals the same nine status checkboxes as desktop (Estimate, Approved, In progress, Review, Complete, Invoiced, Paid, Declined, Imported) plus 'Clear Selection'.
-2. After 'Apply filters' the sheet closes and the work order list shows only the ticked statuses.
+2. After 'Apply Filters' the sheet closes and the work order list shows only the ticked statuses.
 3. The reopened sheet's title shows the applied-filter count, for example 'All Filters (1)', and the Status accordion header is highlighted with the selected values ticked.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R2, S12-R3, S12-R6, S2-R1). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S12-R2, S12-R3, S12-R6, S2-R1), read on 11 August 2026. Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). Last checked against build v3.6-3e9dd6d on 8/11/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4595,7 +4618,7 @@
           <t>1. Tap the Status chip (not the 'All Filters' chip).
 2. Read the sheet that opens.
 3. Tick one status, then tick a second one, and watch the work order list while you do it.
-4. Tap the 'Apply filters' button inside the sheet and look at the list again.</t>
+4. Tap the 'Apply Filters' button inside the sheet and look at the list again.</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -4603,12 +4626,15 @@
           <t xml:space="preserve">1. A bottom sheet opens for that single filter: its title row shows the filter's icon and name (for example 'Status') with a close (x) button, and no accordion list of the other filters.
 2. The sheet shows only that filter's options (the nine status checkboxes plus 'Clear Selection').
 3. You can tick more than one option, and the work order list does NOT change while you tick - your choices are only being held, not applied yet.
-4. An 'Apply filters' button is shown inside the sheet. Tapping it applies your choices: the sheet closes and the list shows only the ticked statuses.
+4. An 'Apply Filters' button is shown inside the sheet. Tapping it applies your choices: the sheet closes and the list shows only the ticked statuses.
 5. The chip then shows its active state with the value(s) you picked. 'Clear Selection' and 'Clear Filters' work the same way as on desktop.
-Known issue reported by the test team: a single filter's own sheet is reported to allow only one value and to have no 'Apply filters' button, filtering the list the moment you tap a value, while only the combined 'All Filters' sheet holds your choices until you press a button. That is reported as https://shopview.atlassian.net/browse/SV-8875 and it is still open. We have not re-checked it on the current build, so if you can run this test, write down what you actually see.
----
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R2, S12-R6, S2-R2). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). Last checked against build v3.4.2-d00239b on 8/5/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8875 - reported, still open)
+What you should see today: a single filter's own sheet applies your choice the moment you tap a value - the address bar changes at once, the list reloads and the sheet closes - and there is no 'Apply filters' button anywhere in that sheet. Only the combined 'All Filters' sheet holds your choices until you press a button.
+- If you see exactly that, mark this test FAILED and do not raise anything new.
+- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S12-R2, S12-R6, S2-R2), read on 11 August 2026. Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). Last checked against build v3.6-3e9dd6d on 8/11/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8875)
 </t>
         </is>
       </c>
@@ -4653,7 +4679,7 @@
           <t>1. Type part of a customer name in the 'Search' field and watch the list.
 2. Select two or three customers.
 3. Look at the input area and the list rows.
-4. Remove one customer with the x on its tag, then tap 'Apply filters'.</t>
+4. Remove one customer with the x on its tag, then tap 'Apply Filters'.</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -4661,10 +4687,14 @@
           <t xml:space="preserve">1. The list narrows to matching names as you type.
 2. Each selected customer appears as a tag with an x in the input area, and its list row shows a checkmark.
 3. Removing a tag deselects just that customer.
-4. After 'Apply filters' the list shows only work orders of the remaining selected customers, and the sheet title counts the applied filters (for example 'All Filters (2)').
----
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R2, S12-R6, S3-R2, S3-R3). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). Last checked against build v3.4.2-d00239b on 8/5/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8875 - reported, still open)
+4. After 'Apply Filters' the list shows only work orders of the remaining selected customers, and the sheet title counts the applied filters (for example 'All Filters (2)').
+What you should see today: the Customer sheet does have a Search box, but it applies your choice the moment you tap a name - the address bar changes at once, the list reloads and the sheet closes - so you cannot pick a second customer, there are no removable tags, and there is no 'Apply filters' button.
+- If you see exactly that, mark this test FAILED and do not raise anything new.
+- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S12-R2, S12-R6, S3-R2, S3-R3), read on 11 August 2026. Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). Last checked against build v3.6-3e9dd6d on 8/11/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8875)
 </t>
         </is>
       </c>
@@ -4708,7 +4738,7 @@
         <is>
           <t>1. Expand the Lead Technician accordion row and look at its content.
 2. Collapse it, expand the Service Advisor row and look at its content.
-3. Select one name in either list and tap 'Apply filters'.</t>
+3. Select one name in either list and tap 'Apply Filters'.</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -4717,7 +4747,7 @@
 2. The Service Advisor row opens with a 'Search' field and the advisor list.
 3. Applying a selection filters the work order list just like on desktop.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R2, S12-R6, S4-R1, S5-R1). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S12-R2, S12-R6, S4-R1, S5-R1), read on 11 August 2026. Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). Last checked against build v3.6-3e9dd6d on 8/11/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4761,7 +4791,7 @@
       <c r="F81" s="2" t="inlineStr">
         <is>
           <t>1. Expand the Asset on Site accordion row.
-2. Choose Yes and tap 'Apply filters'.
+2. Choose Yes and tap 'Apply Filters'.
 3. Look at the list.</t>
         </is>
       </c>
@@ -4771,7 +4801,7 @@
 2. Only one option can be selected at a time.
 3. After applying, the list shows only work orders matching the chosen on-site state.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R2, S12-R6, S6-R1). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S12-R2, S12-R6, S6-R1), read on 11 August 2026. Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). Last checked against build v3.6-3e9dd6d on 8/11/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4823,10 +4853,9 @@
           <t xml:space="preserve">1. The chip for the applied filter shows the active state with the selected value(s), like on desktop.
 2. A 'Clear Filters' control appears while at least one filter is active.
 3. Using it removes all active filters, the chips return to default and the full list comes back.
-Known issue: on a phone there is no Clear Filters button at all while filters are on. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8846
----
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R2, S7-R1, S8-R1). Last checked against build v3.4.2-d00239b on 8/5/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8846 - reported, still open)
+---
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S12-R2, S7-R1, S8-R1), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -4861,14 +4890,16 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in to the ShopView App on a mobile device.
-2. You are on the Work Orders page.</t>
+          <t xml:space="preserve">1. You are signed in to the ShopView App on a mobile device.
+2. You are on the Work Orders page.
+</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>1. Look at the toolbar row (Search, sort icon, Create Work Order button).
-2. Look for any control that would hide the filter chip row.</t>
+          <t xml:space="preserve">1. Look at the toolbar row (Search, sort icon, Create Work Order button).
+2. Look for any control that would hide the filter chip row.
+</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -4876,7 +4907,7 @@
           <t xml:space="preserve">1. There is no filter-bar collapse/expand (filter icon) toggle on mobile.
 2. The filter chip row is always visible on the mobile Work Orders page.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-R4). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S12-R4), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4928,7 +4959,7 @@
 2. The empty state includes the prompt to clear filters.
 3. No error appears.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S12-N1, S8-R3). Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S12-N1, S8-R3), read on 11 August 2026. Branko settled how filters apply on a phone on 5 August 2026: he said it is written in the specification and closed the question (https://shopview.atlassian.net/browse/SV-8825). Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4964,20 +4995,22 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in to the ShopView App on a mobile phone (or a browser window narrowed to phone size).
+          <t xml:space="preserve">1. You are signed in to the ShopView App on a mobile phone (or a browser window narrowed to phone size).
 2. Imported work orders exist, plus some normal work orders.
-3. You are on the Work Orders page, All tab, with no filters applied.</t>
+3. You are on the Work Orders page, All tab, with no filters applied.
+</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>1. Tap 'All Filters' to open the filter sheet.
+          <t xml:space="preserve">1. Tap 'All Filters' to open the filter sheet.
 2. Expand the Status row and tick Imported.
 3. Look at the other filter rows in the sheet (Customer, Lead Technician, Service Advisor, Asset on Site) and try to use one of them.
 4. Try to tick another status as well as Imported.
 5. Tap the apply button and look at the list.
 6. Reopen the sheet, untick Imported, and look at the other filter rows again.
-7. Tap the apply button and look at the list.</t>
+7. Tap the apply button and look at the list.
+</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -4989,7 +5022,7 @@
 5. After applying again, the normal list comes back.
 6. The blocking happens as you tap inside the sheet - you do not have to apply first to see the other filters become unusable.
 ---
-This is the expected behaviour as per epic SV-8785, the owning story SV-8797, and the Filters specification at Confluence version 19 (published 6 August 2026) (S2-R7, S2-N4, S12-R6). The specification states this rule without limiting it to one screen size, so it applies on a phone as well as on a desktop. This test has not yet been checked against any build.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, the owning story SV-8797, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S2-R7, S2-N4, S12-R6), read on 11 August 2026. The specification states this rule without limiting it to one screen size, so it applies on a phone as well as on a desktop. This test has not yet been checked against any build.
 AUTOMATION: READY
 </t>
         </is>
@@ -5060,7 +5093,7 @@
 13. Still to check on the live build: what the filter icon and the column/layout icon do (the written description does not cover the toolbar icons).
 14. Not built yet on the build tested: a filter bar exists on Inventory, Part Sales, Catalog and Returns, but Purchase Orders, Vendor Invoices and Vendors have no filter bar at all. If the filter bar is missing on the view you are testing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (&lt;a href="https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md)."&gt;https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md).&lt;/a&gt; Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, the designs, read on 11 August 2026, and the product owner's answers named below. The Filters specification at Confluence version 19 (published 6 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: HOLD - waiting on Branko's Parts and Reports product write-up - the filter bar is built but no source states what it should do
 </t>
         </is>
@@ -5116,7 +5149,7 @@
 4. As soon as you tick a choice the list below narrows to matching parts straight away, with no Apply button to press; Clear Selection puts the list back.
 5. Not built yet on the build tested: a filter bar exists on Inventory, Part Sales, Catalog and Returns, but Purchase Orders, Vendor Invoices and Vendors have no filter bar at all. If the filter bar is missing on the view you are testing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, the designs, read on 11 August 2026, and the product owner's answers named below. The Filters specification at Confluence version 19 (published 6 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: HOLD - waiting on Branko's Parts and Reports product write-up - the filter bar is built but no source states what it should do
 </t>
         </is>
@@ -5170,7 +5203,7 @@
 3. The list narrows as soon as you pick the value - there is no Apply or Search button to press. Every filter button on every Parts page works this way.
 4. Not built yet on the build tested: a filter bar exists on Inventory, Part Sales, Catalog and Returns, but Purchase Orders, Vendor Invoices and Vendors have no filter bar at all. If the filter bar is missing on the view you are testing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, the designs, read on 11 August 2026, and the product owner's answers named below. The Filters specification at Confluence version 19 (published 6 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: HOLD - waiting on Branko's Parts and Reports product write-up - the filter bar is built but no source states what it should do
 </t>
         </is>
@@ -5224,7 +5257,7 @@
 3. A Clear Filters button appears in the filter bar while any filter is set, and using it clears them all at once - exactly as it works on the Work Orders page.
 4. Not built yet on the build tested: a filter bar exists on Inventory, Part Sales, Catalog and Returns, but Purchase Orders, Vendor Invoices and Vendors have no filter bar at all. If the filter bar is missing on the view you are testing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, the designs, read on 11 August 2026, and the product owner's answers named below. The Filters specification at Confluence version 19 (published 6 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: HOLD - waiting on Branko's Parts and Reports product write-up - the filter bar is built but no source states what it should do
 </t>
         </is>
@@ -5281,7 +5314,7 @@
 3. If any filter or choice is missing, write down exactly which page, which filter and which choice - that is a bug worth reporting.
 4. Not built yet on the build tested: a filter bar exists on Inventory, Part Sales, Catalog and Returns, but Purchase Orders, Vendor Invoices and Vendors have no filter bar at all. If the filter bar is missing on the view you are testing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, the designs, read on 11 August 2026, and the product owner's answers named below. The Filters specification at Confluence version 19 (published 6 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: HOLD - waiting on Branko's Parts and Reports product write-up - the filter bar is built but no source states what it should do
 </t>
         </is>
@@ -5343,7 +5376,7 @@
 6. Anything that behaves differently from the Work Orders page on any of these points is worth writing down, with the page name.
 Note for the tester: only some Parts views and only some reports have the new filter bar so far. If the page you open has no filter bar, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per epic SV-8785 and Branko's answer of 31 July 2026 (Round 3, question 5, option A), recorded in this file: build/filters/branko-answers-2026-07-31/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-07-31/answers-ingested.md). He said that collapsing, the shareable web address and the phone layout all match the Work Orders page. The Filters specification at Confluence version 19 has no numbered requirement for this, so there is no requirement number to quote. This test has not yet been checked against any build.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and Branko's answer of 31 July 2026 (Round 3, question 5, option A), recorded in this file: build/filters/branko-answers-2026-07-31/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-07-31/answers-ingested.md), read on 11 August 2026. He said that collapsing, the shareable web address and the phone layout all match the Work Orders page. The Filters specification at Confluence version 19 has no numbered requirement for this, so there is no requirement number to quote. This test has not yet been checked against any build.
 AUTOMATION: HOLD - the new filter bar has reached only some Parts views and one report tab, so most of this cannot be run yet
 </t>
         </is>
@@ -5359,7 +5392,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Every report page shows its designed filter buttons</t>
+          <t>Report filter bars appear on the reports this change covers</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -5385,55 +5418,42 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>1. Open the Reports area and go to the Timesheet Activities report, and look at the filter buttons shown above the report table.
-2. Go to the Timesheets (Payroll Timesheet) report and look at the filter buttons.
-3. Go to the Sales report and look at the filter buttons.
-4. Go to the Technician Efficiency report. Look at the filter buttons on the Invoiced tab, then open the Completed tab and look at them again.
-5. Go to the Advisor Analysis report and look at the filter buttons.
-6. Go to the Shop Efficiency report and look at the filter buttons.
-7. Go to the Work in Progress report and look at the filter buttons.
-8. Go to the Sales Follow Up report and look at the filter buttons.
-9. Go to the Sales Tax report. Look at the filter buttons on the Collected tab, then open the All Tax Rates tab and look at them again.
-10. Go to the A/R Aging Summary report, then the A/R Aging Detail report, then the A/R Aging Collection report, looking at the filter buttons on each.
-11. Go to the A/P Aging Summary report, then the A/P Aging Detail report, then the A/P Unpaid Invoices report, looking at the filter buttons on each.
-12. Go to the Notes report and look at the filter buttons and the toolbar icons.
-13. Go to the Reminders report and look at the filter buttons.
-14. Go to the IBS Batch Transactions report and look at the filter buttons and the view tabs.
-15. Go to the QB Unexported report. Look at the filter buttons on the Customers tab, then switch to the Vendors tab, then to the Journal Entries tab, looking at the filter buttons on each.
-16. On each report above, open one of its filter buttons, look at the list of choices inside it, and pick a value to check the report changes.</t>
+          <t>1. Open the Reports area and go to the Shop Efficiency report, and look at the filter buttons shown above the report table.
+2. Go to the Timesheet Activities report and look at its filter buttons.
+3. Go to the My Timesheets report and look at its filter buttons. This is the report called 'My Timesheets' - it is not the separate 'Timesheets (Payroll Timesheet)' report.
+4. Go to the Notes report and look at its filter buttons and the icons in its toolbar.
+5. Go to the Reminders report and look at its filter buttons.
+6. Go to the Sales Tax report. Look at the filter buttons on the Collected tab, then open the All Tax Rates tab and look at them again.
+7. On each report above, look at how each filter button is drawn - its icon, its name and its arrow.
+8. On each report above, open one of its filter buttons, look at the list of choices inside it, and pick a value to check the report changes.
+9. On each report above, open the Date filter and check whether a date range is already chosen when the report first opens.</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Timesheet Activities shows four filter buttons: Staff, Date, Status and Modified by.
-2. Payroll Timesheet shows two filter buttons: Employee and Date.
-3. Sales shows two filter buttons: Customer and Date.
-4. Technician Efficiency shows three filter buttons: Customer, Technician and Date — the same three on both of its view tabs, Invoiced and Completed. 'Technician' is spelled correctly here.
-5. Advisor Analysis shows three filter buttons: Customer, Date and Advisor.
-6. Shop Efficiency shows a single filter button: Date.
-7. Work in Progress shows three filter buttons: Status, Date and Customer.
-8. Sales Follow Up shows three filter buttons: Customer, Date and Contact.
-9. Sales Tax has two view tabs: on the Collected tab it shows three filter buttons — Date, Invoice Status and Customer; on the All Tax Rates tab it shows a single filter button — Invoice Status.
-10. A/R Aging Summary shows two filter buttons: Customer and Date.
-11. A/R Aging Detail shows four filter buttons: Customer, Date, Location and Transaction Type.
-12. A/R Aging Collection shows four filter buttons: Customer, Date, Location and Transaction Type.
-13. A/P Aging Summary shows two filter buttons: Vendor and Date.
-14. A/P Aging Detail shows four filter buttons: Vendor, Date, Location and Transaction Type.
-15. A/P Unpaid Invoices shows four filter buttons: Vendor, Date, Location and Transaction Type.
-16. Notes shows three filter buttons: Author, Date and Mention (the Mention button uses an @ icon), and its toolbar also shows a search icon, a filter icon and a sort icon.
-17. Reminders shows a single filter button: Date, and when nothing matches the chosen dates the report shows the message 'There are no reminders for selected date range'.
-18. IBS Batch Transactions shows three filter buttons: Customer, Date and Status, and has three view tabs: Ready To Send, Sent and Payments.
-19. QB Unexported shows three filter buttons and the first one changes with the tab: Customer, Date and Type on the Customers tab; Vendor, Date and Type on the Vendors tab; User, Date and Type on the Journal Entries tab.
-20. Each of the six A/R and A/P aging reports also shows a print icon in its toolbar.
-21. On every report above, each filter button shows its name and a down arrow.
-22. Every filter button shown above is a working filter on that report - none of them is display-only.
-23. The choices inside each filter come from your own shop's data (for example your real vendors or categories), so there is no fixed list to compare against - check that the choices you see match the data in your shop.
-24. Still to check on the live build: the real columns of the Sales Tax report and of the six A/R and A/P aging reports. The design uses sample placeholder tables for those, and the written description does not list their columns.
-25. Not built yet on the build tested: only the first report tab (Timesheet Activities) has a filter bar, with a Date Range and a Filter by Staff button, and no report tab has a page search box. If the controls this test needs are missing, mark this test BLOCKED - do not mark it failed.
----
-This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md). Last checked against build v3.4.2-d00239b on 8/5/2026.
-AUTOMATION: HOLD - waiting on Branko's Parts and Reports product write-up - the filter bar is built but no source states what it should do
-</t>
+          <t>1. Each of the six reports in the steps shows a filter bar under the report header, with filter buttons on it.
+2. Shop Efficiency includes a Date filter button.
+3. Timesheet Activities includes these filter buttons: Staff, Date, Status and Modified by.
+4. My Timesheets includes a Date filter button. No product document lists any other filter button for this report, so if you see more, do not treat that as a failure - write down what you see and report it.
+5. Notes includes these filter buttons: Author, Date and Mention (the Mention button uses an @ icon), and its toolbar also shows a search icon, a filter icon and a sort icon.
+6. Reminders includes a Date filter button, and when nothing matches the chosen dates the report shows the message 'There are no reminders for selected date range'.
+7. Sales Tax has two view tabs: the Collected tab includes Date, Invoice Status and Customer filter buttons, and the All Tax Rates tab includes an Invoice Status filter button.
+8. Each report tab keeps its own filter buttons and its own selections, so a selection made on one tab does not carry across to another.
+9. Each filter button shows a small icon for the kind of filter, then the filter name, then a down arrow.
+10. Every filter button listed above is a working filter on that report - none of them is display-only.
+11. The choices inside each filter come from your own shop's data (for example your real customers or staff), so there is no fixed list to compare against - check that the choices you see match the data in your shop.
+12. The Date filter opens with a date range already chosen rather than empty, and it offers ready-made ranges as well as a custom start and end date.
+13. The reports below are NOT part of this piece of work. If they have no filter bar, or still show their older controls, that is correct. Do not raise a bug and do not mark this test failed because of them:
+- Sales, Technician Efficiency, Advisor Analysis and Work in Progress. These belong to a separate piece of work (the Reporting Suite) and are deliberately being left alone here.
+- The six ageing reports: A/R Aging Summary, A/R Aging Detail, A/R Aging Collection, A/P Aging Summary, A/P Aging Detail and A/P Unpaid Invoices. These pick a single 'as of' date, and no filter button of that kind has been built yet. The decision on them is still open.
+- Timesheets (Payroll Timesheet) and Sales Follow Up. These are not currently reachable from the menu and no decision has been taken on them. 'Timesheets (Payroll Timesheet)' is a different report from the 'My Timesheets' report in step 3.
+- IBS Batch Transactions and QB Unexported. There is no date information behind these two reports, so they cannot be given a Date filter.
+14. The list of reports in this test is the list this piece of work covers today. If a report named in item 13 later gains the new filter bar, that is a change of what the work covers rather than a failure of this test - check the current product write-up before raising anything.
+15. Still to check on the live build: the real columns of the Sales Tax report. The design uses a sample placeholder table for it and the written description does not list its columns.
+16. If a report in steps 1 to 6 is missing the filter bar this test needs, mark this test BLOCKED - do not mark it failed. On the build last checked (named below) only Timesheet Activities was seen to have a filter bar, showing a Date Range button and a Filter by Staff button, and no report had a page search box. The engineering handover says all six reports above were migrated by that same build, so this difference needs one live check on the current build before it is treated either way.
+---
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, the Reports filters design, read on 11 August 2026, and the product owner's answers named below. The Filters specification at Confluence version 19, read on 11 August 2026, describes the Reports filter bar in section 2 'Reports Filters' and in its Key Decisions, but it has no numbered requirement saying which reports are covered or which filter buttons each report has, so there is no requirement reference to give for those points; the requirement that each filter button carries a leading type-icon is S1-R3, which was added in Confluence version 19. Which reports this piece of work covers is taken from the engineering handover for the app-wide filter redesign (branch SV-8785-app-wide-filter-redesign), sections 3 and 8, read on 10 August 2026 - that is an engineering handover, not a specification, and our reading of it is recorded in this file: build/handover-ingest-2026-08-10/FILTERS-RECONCILIATION.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/handover-ingest-2026-08-10/FILTERS-RECONCILIATION.md). The filter buttons named for each report come from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: HOLD - Branko's Parts and Reports write-up is still outstanding, so no product source states which filter buttons each report should show</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5484,7 +5504,7 @@
 2. The report narrows as soon as you pick the value - there is no Apply or Run button to press. Every filter button on every report works this way.
 3. Not built yet on the build tested: only the first report tab (Timesheet Activities) has a filter bar, with a Date Range and a Filter by Staff button, and no report tab has a page search box. If the controls this test needs are missing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, the designs, read on 11 August 2026, and the product owner's answers named below. The Filters specification at Confluence version 19 (published 6 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: HOLD - waiting on Branko's Parts and Reports product write-up - the filter bar is built but no source states what it should do
 </t>
         </is>
@@ -5538,7 +5558,7 @@
 3. Write down the choices you actually see behind each of these six buttons. They have not been written down anywhere yet, so your list becomes the record.
 4. Not built yet on the build tested: only the first report tab (Timesheet Activities) has a filter bar, with a Date Range and a Filter by Staff button, and no report tab has a page search box. If the controls this test needs are missing, mark this test BLOCKED - do not mark it failed.
 ---
-This is the expected behaviour as per epic SV-8785, the designs and the product owner's answers named below. The Filters specification at Confluence version 18 (published 4 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, the designs, read on 11 August 2026, and the product owner's answers named below. The Filters specification at Confluence version 19 (published 6 August 2026) has no numbered requirement for this, so there is no requirement reference to give. The position on this point comes from Branko's answers, in this file: build/filters/branko-answers-2026-08-04/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-08-04/answers-ingested.md), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: HOLD - waiting on Branko's Parts and Reports product write-up - the filter bar is built but no source states what it should do
 </t>
         </is>
@@ -5574,20 +5594,22 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
+          <t xml:space="preserve">1. You are signed in to the ShopView App on a desktop browser.
 2. You are on a report that has a Date Range button - on the build tested that is Reports then the Timesheet Activities report.
-3. Records exist inside and outside the date range you will pick.</t>
+3. Records exist inside and outside the date range you will pick.
+</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>1. Click the Date Range button.
+          <t xml:space="preserve">1. Click the Date Range button.
 2. Look at what the panel offers, and at what the button already reads before you change anything.
 3. Choose one of the ready-made periods (for example Today) and watch the results.
 4. Open the button again and choose Custom.
 5. Fill in the From date only, and watch the results.
 6. Fill in the To date.
-7. Look at the results and at the button.</t>
+7. Look at the results and at the button.
+</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -5601,7 +5623,7 @@
 7. Note: dates are typed in month/day/year order, the way the screen shows them (for example 07/01/2026). For orientation only, one report was seen offering Today, Yesterday, This week, Last week, This month, Last month, This quarter, Last quarter, This year and Last year - that is an example of what you may find, not a list to check against.
 8. Where to run this on the build tested: the Reports area has this date button on the Timesheet Activities report. Other report tabs do not have a filter bar yet - if the report you open has no date button, mark this test BLOCKED, not failed.
 ---
-This is the expected behaviour as per epic SV-8785. It follows the NEWER wording of the Filters specification at Confluence version 18, published on the afternoon of 4 August 2026, which changed the date filter description in the Feature Overview and in the Key Decisions section: the date button now offers standard ready-made periods and starts with the current default range already filled in. An earlier revision of the same specification said the opposite, and this test follows the newer one. The specification does not give this a numbered requirement, so there is no requirement number to quote. Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026. It follows the NEWER wording of the Filters specification at Confluence version 19, read on 11 August 2026, published on the afternoon of 4 August 2026, which changed the date filter description in the Feature Overview and in the Key Decisions section: the date button now offers standard ready-made periods and starts with the current default range already filled in. An earlier revision of the same specification said the opposite, and this test follows the newer one. The specification does not give this a numbered requirement, so there is no requirement number to quote. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: HOLD - waiting on Branko's Parts and Reports product write-up - the date range filter is built but no source states the periods it must offer
 </t>
         </is>
@@ -5658,7 +5680,7 @@
 3. The round x clears the text and the full list returns.
 4. Clicking away with an empty box collapses it back to the Search button; with text in it, the box stays open.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R1, S13-R9, S13-R12, S13-R15). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S13-R1, S13-R9, S13-R12, S13-R15), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5712,7 +5734,7 @@
 2. Clearing the search keeps the filter applied.
 3. Clearing the filter keeps the search applied - each is cleared by its own control without wiping the other.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R10, S13-R13, S8-R5). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S13-R10, S13-R13, S8-R5), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5769,7 +5791,7 @@
 3. The second browser tab starts clean: its Search box is empty and it shows the full list. Each tab keeps its own search.
 4. After closing the browser and coming back, the Search box is empty and the list is unsearched - a typed search is never remembered for next time (your filters, unlike the search, ARE remembered).
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R14, S13-R25, S13-N4, S10-R5). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S13-R14, S13-R25, S13-N4, S10-R5), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5823,7 +5845,7 @@
 3. The malformed part is ignored - the page loads cleanly without an error.
 4. A search arriving via a link is view-only, the same as filters from a link - it does not overwrite your own remembered search.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-R4, S11-R5, S11-N2, S11-R8). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S11-R4, S11-R5, S11-N2, S11-R8), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5878,10 +5900,13 @@
 3. To make room, the page's main button no longer stretches full-width, and pages with two or more small icon buttons collapse them into a single 'more' menu.
 4. The box stretches to fill the space left in the action row instead of staying the narrow desktop size, and every other toolbar button stays visible and in the same place while you search.
 5. There is no extra 'search is on' badge on mobile: with text in it the box simply stays open showing your text, and an empty box closes back to the Search button when you tap elsewhere - exactly as on desktop.
-Note for the tester: on the build this was checked against there is no page Search box on a phone at all. The magnifier in the action row opens the app-wide search instead, and typing in it does not narrow this page's list. So points 1, 2 and 4 do not happen. That is reported and still open, so record it as a fail and carry on.
----
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R16, S13-R17, S13-R18, S13-R19, S13-R20, S12-R5). Last checked against build v3.4.2-d00239b on 8/5/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8912 - reported, still open)
+What you should see today: on a phone there is no page search at all. The magnifier in the top bar opens the app-wide search box instead, and typing in it does not narrow this page's list.
+- If you see exactly that, mark this test FAILED and do not raise anything new.
+- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S13-R16, S13-R17, S13-R18, S13-R19, S13-R20, S12-R5), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8912)
 </t>
         </is>
       </c>
@@ -5938,7 +5963,7 @@
 3. Where the table sits inside a dialog (the Work Order Log, the Line Log, the audit log dialog), the Search box is inside that dialog and works there.
 4. The work order Parts tab keeps the local search input it already had - it was deliberately left as it is.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S14-R6, S14-R5, S13-R22, S14-N1). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S14-R6, S14-R5, S13-R22, S14-N1), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: HOLD - cannot be run yet - its own precondition needs the page-search rollout finished everywhere, and it is still part-way through
 </t>
         </is>
@@ -5992,7 +6017,7 @@
 2. The same holds on the other pages checked.
 3. Picking a dropdown result still takes you to that record - the navigation search keeps its find-and-open role.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S14-R1, S14-R2, S14-R4, S14-R5). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S14-R1, S14-R2, S14-R4, S14-R5), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6050,7 +6075,7 @@
 5. As soon as you type, your text shows in a dark grey and a small round x appears at the right-hand end of the box.
 6. A very long sentence does not make the box grow and does not cut the text off - the text scrolls sideways inside the box and the cursor stays where you are typing.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R2, S13-R3, S13-R4, S13-R5, S13-R6, S13-R8). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S13-R2, S13-R3, S13-R4, S13-R5, S13-R6, S13-R8), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6108,7 +6133,7 @@
 4. Pressing Enter changes nothing that has not already happened - the same rows stay listed and no page reload happens.
 5. Parts Inventory behaves the same way, only it waits a fraction longer before reacting; that longer wait is on purpose because that page carries more data.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R7, S13-R12). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S13-R7, S13-R12), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6164,7 +6189,7 @@
 3. The Completed tab behaves the same way: your word is still there and only that tab's matching rows are listed.
 4. Clearing the search clears it for all the Work Orders tabs - they share one search - and each tab shows its full list again.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R11, S13-R24). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S13-R11, S13-R24), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6220,7 +6245,7 @@
 3. Each report tab behaves the same way: a word typed on one tab stays on that tab only, and each tab remembers its own.
 4. No search is ever applied to a table it was not typed on.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-R24, S13-R11, S10-R4). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S13-R24, S13-R11, S10-R4), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: HOLD - only half of it can be run - the report pages have no page search box yet, so the report-tab half cannot be tested
 </t>
         </is>
@@ -6275,7 +6300,7 @@
 3. No error is shown - the leftover search part in the address is simply ignored. (Whether it also disappears from the address is not important; note what you see.)
 4. After typing in the top-of-screen search and reloading, the list is still not narrowed and nothing about that word was remembered for the list.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S14-R3, S14-R2, S14-R1). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S14-R3, S14-R2, S14-R1), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6329,7 +6354,7 @@
 2. The Search box stays in the toolbar row with your word still showing; it is not tucked away with the filter bar, because the search sits in the toolbar row and the chips sit in the row below.
 3. Expanding the bar again changes nothing about the search or the narrowed list.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S13-E1). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S13-E1), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6390,7 +6415,7 @@
 5. On the comparison page in step 7, which has only one small icon button, that button is still shown on its own - a single icon action is not put into a 'more' menu.
 6. This rule applies to any page carrying two or more small icon buttons, so if you find another page like that, it should behave the same way. Write down any page that does not.
 ---
-This is the expected behaviour as per epic SV-8785, the owning story SV-8798, and the Filters specification at Confluence version 19 (published 6 August 2026) (S13-R19). This test has not yet been checked against any build.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, the owning story SV-8798, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S13-R19), read on 11 August 2026. This test has not yet been checked against any build.
 AUTOMATION: READY
 </t>
         </is>
@@ -6443,7 +6468,7 @@
 2. The request succeeds (HTTP 200).
 3. The response contains only work orders matching the filters - the filtering is done by the backend, not just hidden client-side.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R2, S3-R6). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S2-R2, S3-R6), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6494,8 +6519,9 @@
           <t xml:space="preserve">1. One request carries both filters together (both statuses and the customer).
 2. The response returns customer A's Estimate and Approved work orders only.
 3. Customer B's work orders are absent - the customer filter and status filter both restrict the result, while the two statuses combine as either-or.
----
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S2-R2, S3-R6, S8-R3). Last checked against build v3.4.2-d00239b on 8/5/2026.
+Note on where each part comes from: the "either-or" part of item 3 - that ticking two statuses shows work orders matching either of them - is stated in the product description. The part that says the customer filter and the status filter both restrict the result is not, and neither is the shape of the single request in item 1. Both of those come from the engineering technical design, which requires the filters to combine with "AND across fields" and sets out how the request is put together.
+---
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S2-R2, S3-R6), read on 11 August 2026, and as per the engineering technical design for the app-wide filter redesign (§0.3 and §1.8), read on 11 August 2026 - that document carries no version number of its own and records its own baseline as "Spec baseline: v1.3". Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6547,7 +6573,7 @@
 2. The response is a normal, successful list response - the invalid value is ignored or simply matches nothing.
 3. Any still-valid filter values in the same request are applied normally.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-N1, S11-R3). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S10-N1, S11-R3), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6598,10 +6624,13 @@
         <is>
           <t xml:space="preserve">1. The backend responds gracefully - no HTTP 5xx / crash; either a normal (unfiltered or empty) list or a clean validation response.
 2. In the browser the page still loads without filters and without an error message, matching the malformed-URL requirement.
-Known issue: the server does not fail, but a broken address is not fully ignored by the page. Until it is fixed this test is expected to fail on that point - it is already reported. Ticket: https://shopview.atlassian.net/browse/SV-8832
----
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S11-N1). Last checked against build v3.4.2-d00239b on 8/5/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8832 - reported, still open)
+What you should see today: the server itself does not fail - it answers normally - but the page does not ignore the broken value. It is still sent with the request, so the list comes back empty.
+- If you see exactly that, mark this test FAILED and do not raise anything new.
+- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S11-N1), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8832)
 </t>
         </is>
       </c>
@@ -6652,7 +6681,7 @@
 2. The response contains an empty result set (zero work orders) - an empty match is a normal outcome, not an error.
 3. The page renders the no-results empty state from this response.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S8-R3, S2-N3). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S8-R3, S2-N3), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6708,7 +6737,7 @@
 4. Asking for a never-saved key returns success with an empty value, not an error page.
 5. Step 3 needs a SECOND sign-in of your own. We could not run it for you: impersonating another user on this branch returns an error, and a new staff member cannot finish signing up because the invitation email cannot be received here. If you have a second account, run step 3 normally. If you do not, mark this test BLOCKED - do not mark it failed. Steps 1, 2 and 4 were confirmed working.
 ---
-This is the expected behaviour as per epic SV-8785 and the Filters specification at Confluence version 18 (published 4 August 2026) (S10-R2, S10-R3). Last checked against build v3.4.2-d00239b on 8/5/2026.
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S10-R2, S10-R3), read on 11 August 2026. That specification does not describe the saving service itself, so the save-and-reload requests and their success responses above come from the engineering technical plan, in this file: https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/tech-plan-2026-07-29/TechPlan-AppWide-Filter-Redesign.md, read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: HOLD - needs a second test login to prove one person's saved filters do not reach another
 </t>
         </is>

--- a/testrail-import/filters-v1-testrail-import.xlsx
+++ b/testrail-import/filters-v1-testrail-import.xlsx
@@ -2991,8 +2991,10 @@
           <t xml:space="preserve">1. The filter bar row is hidden.
 2. The work order table moves up and uses the reclaimed vertical space.
 3. The filter icon shows a pressed/active look while the bar is collapsed.
----
-This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S1-R4, S1-R5), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
+4. The filter icon is shown on this page because the Work Orders page has more than one filter. This button is only shown on a page that has more than one filter; on a page that has only one filter the button is not shown at all and that page's filter bar is always on display.
+Note for the tester: if you are ever on a page that has only one filter and you cannot find this button, that is correct and is not a fault - do not raise it. On the Work Orders page, which has five filters, the button should always be there.
+---
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, the Filters specification at Confluence version 19 (published 6 August 2026) (S1-R4, S1-R5), read on 11 August 2026, and ticket SV-9041 (https://shopview.atlassian.net/browse/SV-9041), read on 11 August 2026, which sets the condition for when this button is shown. Last checked against build v3.4.2-d00239b on 8/5/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5359,7 +5361,7 @@
       <c r="F91" s="2" t="inlineStr">
         <is>
           <t>1. On the Parts page, set one filter so the list is narrowed.
-2. Find the control that collapses the filter bar and use it. Then expand it again.
+2. Count the filter buttons on the page. If there is more than one, find the control that collapses the filter bar and use it, then expand it again. If there is only one filter button, check instead that there is no collapse control at all and the filter bar stays on display.
 3. Leave the page and come back, and look at whether the bar is collapsed or expanded.
 4. With a filter set, copy the page's web address, then open it in a fresh browser window.
 5. Open the same Parts page on a phone and look at how the filter buttons are laid out and how a filter is applied.
@@ -5368,15 +5370,15 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The filter bar on the Parts page and on the report can be collapsed and expanded, and the table takes the freed space when it is collapsed - exactly as on the Work Orders page.
-2. While the bar is collapsed the filters keep working, and the collapsed control shows that filters are active - exactly as on the Work Orders page.
-3. Whether you left the bar collapsed or expanded is remembered when you come back to that page.
+          <t xml:space="preserve">1. On a Parts page or a report that has more than one filter, the filter bar can be collapsed and expanded, and the table takes the freed space when it is collapsed - exactly as on the Work Orders page. On a page that has only one filter there is no collapse control at all and the filter bar is always on display; that is correct and is not a fault.
+2. Where that collapse control is present: while the bar is collapsed the filters keep working, and the collapsed control shows that filters are active - exactly as on the Work Orders page.
+3. Where that collapse control is present, whether you left the bar collapsed or expanded is remembered when you come back to that page.
 4. The web address carries the filters you set, and opening that address in a fresh window loads the page with the same filters already applied and the list already narrowed - exactly as on the Work Orders page.
 5. On the phone the filter buttons sit in a row you can scroll sideways, there is no collapse control, and your choices are applied when you tap the apply button rather than as you tap each one - exactly as on the Work Orders page.
 6. Anything that behaves differently from the Work Orders page on any of these points is worth writing down, with the page name.
-Note for the tester: only some Parts views and only some reports have the new filter bar so far. If the page you open has no filter bar, mark this test BLOCKED - do not mark it failed.
----
-This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and Branko's answer of 31 July 2026 (Round 3, question 5, option A), recorded in this file: build/filters/branko-answers-2026-07-31/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-07-31/answers-ingested.md), read on 11 August 2026. He said that collapsing, the shareable web address and the phone layout all match the Work Orders page. The Filters specification at Confluence version 19 has no numbered requirement for this, so there is no requirement number to quote. This test has not yet been checked against any build.
+Note for the tester: only some Parts views and only some reports have the new filter bar so far. If the page you open has no filter bar, mark this test BLOCKED - do not mark it failed. A page that has a filter bar with only one filter button and no collapse control is a PASS for that page, not a failure.
+---
+This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and Branko's answer of 31 July 2026 (Round 3, question 5, option A), recorded in this file: build/filters/branko-answers-2026-07-31/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-07-31/answers-ingested.md), read on 11 August 2026. He said that collapsing, the shareable web address and the phone layout all match the Work Orders page. The Filters specification at Confluence version 19 has no numbered requirement for this, so there is no requirement number to quote. It also follows ticket SV-9041 (https://shopview.atlassian.net/browse/SV-9041), read on 11 August 2026, which says the collapse control is only shown on a page that has more than one filter. Branko's answer of 31 July 2026 says collapsing on Parts and Reports matches the Work Orders page and does not mention any condition on the number of filters; ticket SV-9041, raised on 7 August 2026, is the newer statement, so this test follows it and expects no collapse control on a page that has only one filter. This test has not yet been checked against any build.
 AUTOMATION: HOLD - the new filter bar has reached only some Parts views and one report tab, so most of this cannot be run yet
 </t>
         </is>

--- a/testrail-import/filters-v1-testrail-import.xlsx
+++ b/testrail-import/filters-v1-testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J115"/>
+  <dimension ref="A1:J116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -3220,38 +3220,94 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>One filter on a page: no collapse control and the filter bar stays shown</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Collapse and Expand</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You can reach a page whose filter bar shows only ONE filter button. On the build the developers were working on, Parts then Part Sales was such a page: its filter bar showed only Status.
+3. If every page you can reach shows two or more filter buttons, mark this test BLOCKED and say which pages you checked - do not mark it failed.</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the page you chose and look at the filter bar above the table.
+2. Count the filter buttons in that bar and confirm there is only one.
+3. Look along the whole toolbar row - where the Search control and the page's main button sit - for the small control that hides and shows the filter bar.
+4. Move to another page and come back to this one, then look at the filter bar again.</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>1. The filter bar shows exactly one filter button.
+2. There is no control anywhere in the toolbar for hiding or showing the filter bar. It is not greyed out or switched off - it is simply not there at all.
+3. The filter bar itself is on display, with its one filter button available to use as normal.
+4. After leaving the page and coming back, the filter bar is still on display and there is still no hide/show control.
+Note for the tester: the missing control is the point of this test, not a fault. On a page with only one filter there is nothing worth hiding, so the control is left out on purpose. If you DO find a hide/show control on a page with only one filter button, that is the failure - please report it.
+---
+This is the expected behaviour as per ticket SV-9041 (https://shopview.atlassian.net/browse/SV-9041), read on 11 August 2026, which says the expand/collapse filter control should only be visible if there is more than one filter present on the page, and that otherwise it should not be visible and the filter is always shown; and as per epic SV-8785, read on 11 August 2026. The Filters specification at Confluence version 19 (published 6 August 2026), read on 11 August 2026, describes the collapse control in S1-R4 but sets no condition on when it appears, so there is no requirement number to quote for this rule.
+AUTOMATION: READY</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>SV-9041 (spec v19 S1-R4 sets no condition)</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
           <t>A filter combination with no matches shows a no-results empty state</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>Empty State</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page on the All tab.
 3. Work orders exist, but you can pick a filter combination that matches none of them (for example a customer plus a status that customer never has).</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>1. Apply the filter combination that matches no work orders.
 2. Look at the table area.</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The table body is replaced by an empty state (not just a bare empty grid).
 2. The empty state shows a message saying no results were found for the filters and the search you have on.
@@ -3262,50 +3318,50 @@
 </t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>SV-8793 (S8-R3) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>The filtered empty state offers a way to clear the filters</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>Empty State</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page showing the filtered empty state (a filter combination matching no work orders is applied).
 3. The page's own Search box is empty (no text typed in it).</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>1. Read the empty state content.
 2. Click the clear-filters prompt/link inside the empty state.
 3. Look at the table and the chips.</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The empty state includes a link to clear the filters, and - when you also have a search on - a separate way to clear just the search.
 2. Clicking it removes the active filters and the full work order list is shown again (with no text in the Search box, nothing else is narrowing the list).
@@ -3316,43 +3372,43 @@
 </t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>SV-8793 (S8-R4 (the empty state includes a prompt or link to clear filters); S8-R5 (where a query is also active each is cleared independently)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>When filters and a search find nothing, each can be cleared on its own</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>Empty State</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page.
 3. One filter is active (for example a Status) and some work orders match it.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1. With that filter still active, type a word in the page Search box that matches none of the work orders left in the list.
 2. Read the message shown where the table was.
@@ -3360,7 +3416,7 @@
 4. Type the same word again, then use the option the message offers for clearing the filters only.</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The table is replaced by a no-results message that mentions BOTH the current filters and the search - not the filters alone.
 2. The message offers a way to clear the filters and, because a search is active, a separate way to clear the search.
@@ -3372,48 +3428,48 @@
 </t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (S8-R3 (empty state covers filters AND any active query); S8-R4 (prompt to clear filters and the query where active); S8-R5 (each cleared independently from the empty state); S13-N1; S13-N2) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>The All tab shows all five filter chips, all working</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>Tab Behaviour</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>1. Click the All tab.
 2. Count the filter chips and click each one briefly.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. All five chips are shown: Status, Customer, Lead Technician, Service Advisor, Asset on Site.
 2. Each chip opens its dropdown and can be used.
@@ -3423,43 +3479,43 @@
 </t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>SV-8794 (S9-R1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>Estimates tab: Status chip is greyed out and pre-filled; other four work</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>Tab Behaviour</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Estimate work orders exist for at least two different customers.
 3. You are on the Work Orders page.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1. Click the Estimates tab.
 2. Look at the filter bar and at the Status chip.
@@ -3468,7 +3524,7 @@
 5. Look at the table.</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The Status chip is shown, but greyed out and already filled in with this tab's own status (Estimate), because the tab already narrows the list to Estimate.
 2. The Status chip cannot be clicked or changed on this tab.
@@ -3480,43 +3536,43 @@
 </t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (S9-R2; S2-N1; §4 Key Decisions - PRD text says "hidden"; behaviour per Branko Q4=B 2026-07-17 + QA-lead ruling 2026-07-30 = shown greyed-out/disabled; PRD alignment is Branko's open item) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>Completed tab: Status chip is greyed out and pre-filled; other four work</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>Tab Behaviour</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Complete work orders exist for at least two different customers.
 3. You are on the Work Orders page.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>1. Click the Completed tab.
 2. Look at the filter bar and at the Status chip.
@@ -3525,7 +3581,7 @@
 5. Look at the table.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The Status chip is shown, but greyed out and already filled in with this tab's own status (Complete), because the tab already narrows the list to Complete.
 2. The Status chip cannot be clicked or changed on this tab.
@@ -3537,50 +3593,50 @@
 </t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (S9-R3; S2-N2; §4 Key Decisions - PRD text says "hidden"; behaviour per Branko Q4=B 2026-07-17 + QA-lead ruling 2026-07-30 = shown greyed-out/disabled; PRD alignment is Branko's open item) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>My Work Orders tab shows all five filters and they narrow that list</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>Tab Behaviour</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Work orders assigned to you exist in at least two statuses, and other users' work orders also exist.
 3. You are on the Work Orders page.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>1. Click the My Work Orders tab and count the chips.
 2. Open the Status filter and tick one status your work orders have.
 3. Look at the table.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. All five filter chips are shown on the My Work Orders tab.
 2. The table only ever shows work orders assigned to you (the tab's own scope stays).
@@ -3591,43 +3647,43 @@
 </t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>SV-8794 (S9-R4; §4 Key Decisions (My Work Orders tab does not remove filters)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>A Status choice is kept while you switch tabs and comes back on the All tab</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>Tab Behaviour</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page on the All tab.
 3. Work orders exist in the Approved status and Estimate work orders exist too.</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>1. On the All tab, open the Status filter and tick Approved.
 2. Open the Customer filter and select one customer.
@@ -3636,7 +3692,7 @@
 5. Look at the Status chip and the Customer chip.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. On the Estimates tab your Status choice is not applied and cannot be changed - the Status chip is greyed out and already filled in with that tab's own status. The Customer selection is still shown and still narrows the list.
 2. Back on the All tab the Status chip is usable again and shows the SAME selection (Approved) still applied - your choice was kept, not thrown away.
@@ -3647,41 +3703,41 @@
 </t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>SV-8794 (S9-R5; S9-N1; S9-R2 - behaviour per Branko Q4=B 2026-07-17 + QA-lead ruling 2026-07-30) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>First visit opens the Estimates tab; your last-used tab is remembered</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>Tab Behaviour</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>1. You can sign in as a user who has never used the redesigned Work Orders page (no saved page choices for that account).</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as that fresh user and open the Work Orders page.
 2. Note which tab is selected and the tab order.
@@ -3689,7 +3745,7 @@
 4. Go to another area of the app and come back to the Work Orders page.</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. On the very first visit the Estimates tab is the selected one, even though All is the FIRST tab in the row (order and default are different on purpose).
 2. After switching to All and returning, the All tab is selected - the app remembers your last-used tab per account.
@@ -3699,42 +3755,42 @@
 </t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (no requirement in spec v1.6 - default/last-used tab is not in the spec; RULED by Branko answers 2026-08-04 Q2 "A - it's fine"); tech plan 2026-07-29 D10 (default tab = Estimates; last-used tab persists) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>Leaving the page and coming back restores the filters and the bar state</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>Persistence</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with a Status and a Customer selection active and the filter bar expanded.</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>1. Open one work order from the list (go to its detail page).
 2. Go back to the Work Orders page.
@@ -3742,7 +3798,7 @@
 4. Repeat the round-trip once more with the filter bar collapsed before leaving.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. After step 2 the same Status and Customer selections are still applied - chips active with the same values, table filtered the same way.
 2. The filter bar is still expanded (as you left it).
@@ -3753,42 +3809,42 @@
 </t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (S10-R1; S1-R7) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>Filters are remembered permanently, even after closing the browser</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>Persistence</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Filters are applied on the Work Orders page (for example a status and a customer).</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>1. Visit several other areas of the app (Customers, Parts, Reports) and use them briefly.
 2. Return to the Work Orders page and look at the chips and the table.
@@ -3798,7 +3854,7 @@
 6. On a different computer (or a different browser profile), sign in as the same person and open the Work Orders page.</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. After moving around the app (step 2) the filter selections are still applied - you do not have to re-apply them.
 2. After closing the browser completely and signing back in (step 5) the same filter selections are still applied - the app remembers your filters for you permanently, not just for one browser session.
@@ -3809,49 +3865,49 @@
 </t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>SV-8795 (S10-R2 (stored server-side against the account; survives logout; syncs across devices); S10-R3 (saved per user); S10-R1 (restored after navigating away)) + Branko Q2 2026-07-17 - now matched by the PRD [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>Saved filters are per user: one user's filters do not appear for another user</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>Persistence</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>1. Two test users (A and B) can sign in to the same shop.
 2. User A has applied filters on the Work Orders page (for example Status: Approved).</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>1. As user B (separate login/browser profile), open the Work Orders page.
 2. Look at the filter chips and the table.
 3. As user B, apply a DIFFERENT filter (for example a customer), then re-check user A's view.</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. User B does not see user A's filters - user B's page opens with user B's own (or no) filters.
 2. User B's new filter does not change what user A sees; each user keeps their own saved filter state.
@@ -3861,49 +3917,49 @@
 </t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>SV-8795 (S10-R3; §4 Key Decisions (saved per user)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>A remembered filter value that was deleted is silently ignored</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>Persistence</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A throwaway ZZAUTOTEST customer exists and is selected in the Customer filter together with one real customer.
 3. You then navigate away and the ZZAUTOTEST customer is deleted (or otherwise removed) while you are off the page.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>1. Return to the Work Orders page.
 2. Look at the Customer chip, the dropdown and the table.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The deleted customer is silently ignored - no error or warning appears.
 2. The Customer filter now reflects only the still-valid selection (the real customer).
@@ -3918,42 +3974,42 @@
 </t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>SV-8795 (S10-N1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>Each page and tab remembers its own filters separately</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>Persistence</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The new filter bar has rolled out to the Parts views and to a report that has tabs (part of the same programme as the Work Orders filters).</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>1. On one Parts view (for example Inventory) apply a filter.
 2. Switch to a different Parts view (for example Purchase Orders).
@@ -3961,7 +4017,7 @@
 4. On a report with tabs, apply a filter on one tab, switch to another tab, then switch back.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The second Parts view does NOT show the first view's selections - each view keeps its own.
 2. Returning to the first view restores that view's own selections.
@@ -3972,48 +4028,48 @@
 </t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>SV-8795 (spec v1.6 S10-R4; §4 "Parts and Reports selections are scoped to their view/tab and persist there"); Branko answers 2026-07-31 Q5 exception 1; tech plan 2026-07-29 D20</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>Filters saved before the redesign carry over after the update</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>Persistence</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>1. In one browser, the account was used on the OLD Work Orders page with choices saved there (a tab, status selections, the asset-here toggle, column choices, sorting) BEFORE the redesign was installed.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>1. In that same browser, open the updated app and go to the Work Orders page.
 2. Check the selected tab, the filter chips, the table columns and the sorting.
 3. Sign in as the same person on a DIFFERENT computer or browser and open the Work Orders page.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The old saved choices appear in the new filter bar on the first visit - the update does not lose them (old status choices show in the Status chip, the old asset-here choice shows as Asset on Site: Yes, the old My-Work-Orders toggle maps to the My Work Orders tab, columns and sorting stay).
 2. Those carried-over choices are now saved to the account: the other computer shows them too.
@@ -4023,43 +4079,43 @@
 </t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>SV-8795 (no numbered v1.6 requirement covers the one-off migration - context S10-R2 server-side model); tech plan 2026-07-29 s4-3.3 (browser-storage to account-preference migration) - confirmation requested [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>When two devices set different filters, the last one saved wins</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>Persistence</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App as the same person on TWO separate browsers at the same time (for example one normal window and one private window, or two different computers). Call them Browser A and Browser B.
 2. Both are on the Work Orders page.
 3. Work orders exist in at least two different statuses, and for at least two different customers.</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>1. In Browser A, set the Status filter to Approved. Wait a few seconds.
 2. In Browser B, set the Status filter to Estimate instead, and clear Approved. Wait a few seconds.
@@ -4069,7 +4125,7 @@
 6. In Browser B, reload the Work Orders page and look at the chips and the table.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. After the reload in step 3, Browser A shows the filter that was saved MOST RECENTLY - the Estimate choice made in Browser B - not the Approved choice it had set itself. The newer save wins.
 2. The table in Browser A matches those newer filters.
@@ -4083,49 +4139,49 @@
 </t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>S10-R2 (last write wins)</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>Applying filters updates the page URL to reflect the active filter state</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>URL State and Shareable Links</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with no filters applied; note the current URL.</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. Apply a Status selection and a Customer selection.
 2. Look at the browser address bar.
 3. Clear all filters and look at the address bar again.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. After step 1 the URL changes to include the active filter state.
 2. After step 3 the filter part of the URL is removed again.
@@ -4135,48 +4191,48 @@
 </t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>SV-8796 (S11-R1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>Opening a shared URL or bookmark loads the page with those filters on</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>URL State and Shareable Links</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You have copied a Work Orders URL that was produced with filters applied (for example Status: Approved + one customer).</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>1. Open the copied URL in a new browser tab (same signed-in user).
 2. Look at the chips and the table as the page loads.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The page opens with the same filters already applied - chips active with the same values.
 2. The table is already filtered accordingly on load (no need to re-apply anything).
@@ -4187,49 +4243,49 @@
 </t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>SV-8796 (S11-R2; §2 Feature Overview (share or bookmark)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>A URL with a deleted filter value loads and ignores that value</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>URL State and Shareable Links</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You saved a filtered Work Orders URL that includes a throwaway ZZAUTOTEST customer plus one real filter value.
 3. The ZZAUTOTEST customer has since been deleted.</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>1. Open the saved URL.
 2. Look at the chips and the table.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The page loads normally - no error.
 2. The deleted value is ignored; only the still-valid filter value is applied and shown on the chips.
@@ -4244,49 +4300,49 @@
 </t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>SV-8796 (S11-R3) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>A broken filter URL loads the page with no filters and no error</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>URL State and Shareable Links</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You have a valid filtered Work Orders URL to start from.</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>1. Manually break the filter part of the URL (for example scramble the parameter values or insert nonsense text).
 2. Open the broken URL.
 3. Look at the page, the chips and the table.</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The Work Orders page loads normally.
 2. No filters are applied (chips in default state, full list shown) - the unrecognizable state is discarded.
@@ -4301,43 +4357,43 @@
 </t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>SV-8796 (S11-N1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>Opening a shared link does not change your own saved filters</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>URL State and Shareable Links</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in and have your OWN filters saved on the Work Orders page (for example one customer).
 2. You have a Work Orders link that carries a DIFFERENT filter state (made by another user or another browser).
 3. You know how to use the page's own Search box on the Work Orders page (the Search button in the toolbar row).</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>1. Note your own saved filters on the Work Orders page.
 2. Open the shared link.
@@ -4347,7 +4403,7 @@
 6. Leave the page and return to Work Orders normally (via the menu).</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The link's filters apply for viewing only - the page shows the shared view.
 2. Changes made during the link visit are also NOT saved to your account.
@@ -4361,43 +4417,43 @@
 </t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>SV-8796 (S11-R6 (URL state runtime-only with no write-back); S11-R7 (Back to my view - also clears the query); S11-R8 (rationale: the query is never saved)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>'Back to my view' is not shown when you are on your own view</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>URL State and Shareable Links</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You have your OWN filters saved on the Work Orders page (for example one customer).
 3. You are NOT using a shared link - you have not opened a Work Orders web address that someone sent you.</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work Orders page from the main menu.
 2. Look at the filter bar and the toolbar row for a 'Back To My Saved Filters' option.
@@ -4406,7 +4462,7 @@
 5. Click 'Back To My Saved Filters', then look one more time.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. On your own view there is no 'Back to my view' option anywhere - it only belongs to a shared-link visit. Note for the tester: the specification names this action 'Back to my view' and says the wording is deliberate, because the action clears the search box as well as the filters. If the button on screen says something else, write down exactly what it says and carry on - do not fail the test on the wording alone.
 2. Changing your own filters does not make it appear.
@@ -4418,50 +4474,50 @@
 </t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>SV-8796 (S11-N3; S11-R7) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>Mobile: chips sit in a scrollable row below the tabs, starting All Filters</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>Mobile Filters</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. You are signed in to the ShopView App on a mobile device (or a mobile-size browser window).
 2. You are on the Work Orders page.
 </t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Look at the row below the tab row (All, Estimates, Completed, My Work Orders).
 2. Swipe the chip row sideways.
 </t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. A filter chip row is shown below the tabs, starting with an 'All Filters' chip (with a filter icon) followed by the individual filter chips (Status, Customer, Lead Technician, ...).
 2. The row scrolls horizontally - chips that do not fit are reachable by swiping.
@@ -4471,50 +4527,50 @@
 </t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>SV-8797 (S12-R1) [spec v1.6 2026-07-28]; Branko answers 2026-08-04 Q1 - single-filter sheet applies instantly with no Apply button; the combined All Filters sheet keeps its button</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>Mobile: All Filters opens a sheet of expandable rows with Apply filters</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>Mobile Filters</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. You are signed in to the ShopView App on a mobile device.
 2. You are on the Work Orders page.
 </t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Tap the 'All Filters' chip.
 2. Read the sheet from top to bottom.
 </t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. A bottom sheet slides up with a drag handle at the top, the centered title 'All Filters' and a close (x) button.
 2. It lists the five filters as expandable accordion rows, each with its icon, name and a down arrow: Status, Customer, Lead Technician, Service Advisor, Asset on Site.
@@ -4525,43 +4581,43 @@
 </t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>SV-8797 (S12-R3) [spec v1.6 2026-07-28]; Branko answers 2026-08-04 Q1 - single-filter sheet applies instantly with no Apply button; the combined All Filters sheet keeps its button</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>Mobile: tapping Apply filters applies the statuses and updates the count</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>Mobile Filters</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device.
 2. You are on the Work Orders page on the All tab; work orders exist in several statuses.
 3. The 'All Filters' bottom sheet is open.</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>1. Tap the Status accordion row to expand it.
 2. Tick one or more statuses.
@@ -4569,7 +4625,7 @@
 4. Reopen the All Filters sheet and look at its title.</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Expanding Status reveals the same nine status checkboxes as desktop (Estimate, Approved, In progress, Review, Complete, Invoiced, Paid, Declined, Imported) plus 'Clear Selection'.
 2. After 'Apply Filters' the sheet closes and the work order list shows only the ticked statuses.
@@ -4580,42 +4636,42 @@
 </t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (S12-R2; S12-R3; S2-R1) [spec v1.6 2026-07-28]; Branko answers 2026-08-04 Q1 - single-filter sheet applies instantly with no Apply button; the combined All Filters sheet keeps its button</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>Mobile: one chip opens its own sheet and applies only on Apply filters</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>Mobile Filters</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device.
 2. You are on the Work Orders page.</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>1. Tap the Status chip (not the 'All Filters' chip).
 2. Read the sheet that opens.
@@ -4623,7 +4679,7 @@
 4. Tap the 'Apply Filters' button inside the sheet and look at the list again.</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. A bottom sheet opens for that single filter: its title row shows the filter's icon and name (for example 'Status') with a close (x) button, and no accordion list of the other filters.
 2. The sheet shows only that filter's options (the nine status checkboxes plus 'Clear Selection').
@@ -4640,43 +4696,43 @@
 </t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>SV-8797 (S12-R2; S12-R3; S2-R6) [spec v1.6 2026-07-28] ; individual-chip real-time per S12-R2 + S2-R6 + tech-plan 2026-07-29; only the combined All Filters sheet is batch; CONFIRMED by Branko answers 2026-08-04 Q1</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>Mobile Customer filter has search, multi-select and removable tags</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>Mobile Filters</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device.
 2. You are on the Work Orders page; several customers exist.
 3. The All Filters sheet is open with the Customer accordion expanded.</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>1. Type part of a customer name in the 'Search' field and watch the list.
 2. Select two or three customers.
@@ -4684,7 +4740,7 @@
 4. Remove one customer with the x on its tag, then tap 'Apply Filters'.</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The list narrows to matching names as you type.
 2. Each selected customer appears as a tag with an x in the input area, and its list row shows a checkmark.
@@ -4700,50 +4756,50 @@
 </t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (S12-R2; S3-R2/R3/R5) [spec v1.6 2026-07-28]; Branko answers 2026-08-04 Q1 - single-filter sheet applies instantly with no Apply button; the combined All Filters sheet keeps its button</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>Mobile Lead Technician and Service Advisor filters offer their search lists</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>Mobile Filters</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device.
 2. You are on the Work Orders page; technicians and advisors exist.
 3. The All Filters sheet is open.</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>1. Expand the Lead Technician accordion row and look at its content.
 2. Collapse it, expand the Service Advisor row and look at its content.
 3. Select one name in either list and tap 'Apply Filters'.</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The Lead Technician row opens with a 'Search' field and the technician list.
 2. The Service Advisor row opens with a 'Search' field and the advisor list.
@@ -4754,50 +4810,50 @@
 </t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (S12-R2; S4-R1; S5-R1) [spec v1.6 2026-07-28]; Branko answers 2026-08-04 Q1 - single-filter sheet applies instantly with no Apply button; the combined All Filters sheet keeps its button</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>The mobile Asset on Site filter offers Yes/No with Clear Selection in the sheet</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>Mobile Filters</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device.
 2. You are on the Work Orders page; work orders exist in both on-site states.
 3. The All Filters sheet is open.</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>1. Expand the Asset on Site accordion row.
 2. Choose Yes and tap 'Apply Filters'.
 3. Look at the list.</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The Asset on Site row opens showing the two options Yes and No plus 'Clear Selection'.
 2. Only one option can be selected at a time.
@@ -4808,49 +4864,49 @@
 </t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (S12-R2; S6-R1/R2/R3) [spec v1.6 2026-07-28]; Branko answers 2026-08-04 Q1 - single-filter sheet applies instantly with no Apply button; the combined All Filters sheet keeps its button</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>Active chips and Clear Filters behave on mobile the same way as on desktop</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>Mobile Filters</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device.
 2. You are on the Work Orders page with at least one filter applied via the sheet.</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>1. Look at the chip row after applying the filter.
 2. Look for a 'Clear Filters' control while a filter is active.
 3. Use it and look at the chips and the list.</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The chip for the applied filter shows the active state with the selected value(s), like on desktop.
 2. A 'Clear Filters' control appears while at least one filter is active.
@@ -4861,50 +4917,50 @@
 </t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (S12-R2; S7-R1/R3; S8-R1) [spec v1.6 2026-07-28]; Branko answers 2026-08-04 Q1 - single-filter sheet applies instantly with no Apply button; the combined All Filters sheet keeps its button</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>Mobile has no collapse toggle: the filter chip row is always visible</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>Mobile Filters</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. You are signed in to the ShopView App on a mobile device.
 2. You are on the Work Orders page.
 </t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Look at the toolbar row (Search, sort icon, Create Work Order button).
 2. Look for any control that would hide the filter chip row.
 </t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. There is no filter-bar collapse/expand (filter icon) toggle on mobile.
 2. The filter chip row is always visible on the mobile Work Orders page.
@@ -4914,48 +4970,48 @@
 </t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>SV-8797 (S12-R4) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>Filters matching no work orders on mobile show the same empty state as desktop</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>Mobile Filters</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device.
 2. You are on the Work Orders page; work orders exist.</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>1. Apply a filter combination that matches no work orders (for example a customer plus a status that customer never has).
 2. Look at the list area.</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The list shows the same no-results empty state as desktop, saying no results were found for the current filters.
 2. The empty state includes the prompt to clear filters.
@@ -4966,36 +5022,36 @@
 </t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (S12-N1; S8-R3/R4) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>On a phone, picking Imported works alone and disables the other filters</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>Mobile Filters</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. You are signed in to the ShopView App on a mobile phone (or a browser window narrowed to phone size).
 2. Imported work orders exist, plus some normal work orders.
@@ -5003,7 +5059,7 @@
 </t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Tap 'All Filters' to open the filter sheet.
 2. Expand the Status row and tick Imported.
@@ -5015,7 +5071,7 @@
 </t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. While Imported is ticked, the other filters cannot be used - they are greyed out or otherwise blocked, in the same way as on a desktop screen.
 2. Imported cannot be combined with another status: it works on its own.
@@ -5029,42 +5085,42 @@
 </t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>S2-R7; S2-N4; S12-R6</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>Every Parts list page shows its designed filter buttons</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>Parts Page Filters</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Parts area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>1. Open the Parts area and go to the Inventory page, and look at the filter buttons shown above the table.
 2. Go to the Part Sales page and look at the filter buttons.
@@ -5078,7 +5134,7 @@
 10. On each page above, open one of its filter buttons, look at the list of choices inside it, and pick a value to check the list changes.</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Inventory shows four filter buttons: Bin Location, Category, Supply and Vendor.
 2. Part Sales shows four filter buttons: Status, Customer, Created by and Date.
@@ -5100,42 +5156,42 @@
 </t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (spec v1.6 §2 Parts Filters; §4 context-specific filter sets + multi-select); Branko answers 2026-07-31 Q2/Q3/Q5/Q7 + 2026-08-04 Q3 (Vendors design exists Figma 11903-10461) + Q8 (Part Sales chips); Figma 11884-16885</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>Part Type filter opens a Core / Non Core list with Clear Selection</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>Parts Page Filters</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Parts area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>1. On the Parts Returns tab, click the Part Type filter button.
 2. Look at the small menu that opens.
@@ -5143,7 +5199,7 @@
 4. Use Clear Selection.</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. A small menu opens with two options: Core and Non Core.
 2. A Clear Selection action is shown at the bottom of the menu.
@@ -5156,49 +5212,49 @@
 </t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (spec v1.6 §2 Feature Overview -&gt; Parts Filters; §4 Key Decisions -&gt; "Context-specific filter sets on Parts and Reports" + "Multi-select where it makes sense"); Branko answers 2026-07-31 Q2/Q3/Q5/Q7; Figma 11884-16885</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>Choosing a Parts filter narrows the list on that page</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>Parts Page Filters</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Parts area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>1. Open a Parts list page that has a filter button (for example Inventory).
 2. Open a filter button and choose one value.
 3. Watch the table below.</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The table updates to show only the rows that match the chosen filter value.
 2. The chosen value is shown on the filter button so you can see what is applied.
@@ -5210,49 +5266,49 @@
 </t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (spec v1.6 §2 Feature Overview -&gt; Parts Filters; §4 Key Decisions -&gt; "Context-specific filter sets on Parts and Reports" + "Multi-select where it makes sense"); Branko answers 2026-07-31 Q2/Q3/Q5/Q7; Figma 11884-16885</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>Parts filters support multiple choices and can be cleared</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>Parts Page Filters</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Parts area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>1. Open a Parts filter button that shows a list of choices.
 2. Select more than one choice, then look at the filter button.
 3. Use the Clear Selection action, then look at the filter bar for a way to clear all filters.</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. More than one value can be chosen inside the filter, and the button shows what you picked.
 2. Clear Selection removes the choices for that one filter.
@@ -5264,43 +5320,43 @@
 </t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (spec v1.6 §2 Feature Overview -&gt; Parts Filters; §4 Key Decisions -&gt; "Context-specific filter sets on Parts and Reports" + "Multi-select where it makes sense"); Branko answers 2026-07-31 Q2/Q3/Q5/Q7; Figma 11884-16885</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>Every filter a page had before is still available in the new filter bar</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>Parts Page Filters</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You have a written list of the filters each Parts page and each report offers today, before the new filter bar (take screenshots of the old screens first, or ask the developers for the list).
 3. Sample data is present in the Parts area and in the Reports area.</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>1. Take your before-list for one page.
 2. Open the same page with the new filter bar.
@@ -5309,7 +5365,7 @@
 5. Repeat steps 1 to 4 for the other Parts pages and for each report.</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Every filter the page offered before is still offered - nothing has been taken away.
 2. Every choice each of those filters offered before is still available inside the new button.
@@ -5321,36 +5377,36 @@
 </t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (spec v1.6 §2 Parts Filters + Reports Filters); Branko answers 2026-07-31 Q3 + 2026-08-04 Q8 ("we should have all filters we support now per each page plus we should add new ones"); tech plan 2026-07-29 rollout rule</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>Parts and Reports filters collapse, share and work on a phone as Work Orders do</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>Parts Page Filters</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You can also open the same pages on a mobile phone (or a browser window narrowed to phone size).
@@ -5358,7 +5414,7 @@
 4. Sample data is present in the Parts area and in the Reports area.</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>1. On the Parts page, set one filter so the list is narrowed.
 2. Count the filter buttons on the page. If there is more than one, find the control that collapses the filter bar and use it, then expand it again. If there is only one filter button, check instead that there is no collapse control at all and the filter bar stays on display.
@@ -5368,7 +5424,7 @@
 6. Repeat steps 1 to 5 on a report that has a filter bar.</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. On a Parts page or a report that has more than one filter, the filter bar can be collapsed and expanded, and the table takes the freed space when it is collapsed - exactly as on the Work Orders page. On a page that has only one filter there is no collapse control at all and the filter bar is always on display; that is correct and is not a fault.
 2. Where that collapse control is present: while the bar is collapsed the filters keep working, and the collapsed control shows that filters are active - exactly as on the Work Orders page.
@@ -5383,42 +5439,42 @@
 </t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>Branko Round-3 Q5=A (2026-07-31)</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>Report filter bars appear on the reports this change covers</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>Reports Page Filters</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Reports area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>1. Open the Reports area and go to the Shop Efficiency report, and look at the filter buttons shown above the report table.
 2. Go to the Timesheet Activities report and look at its filter buttons.
@@ -5431,7 +5487,7 @@
 9. On each report above, open the Date filter and check whether a date range is already chosen when the report first opens.</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t>1. Each of the six reports in the steps shows a filter bar under the report header, with filter buttons on it.
 2. Shop Efficiency includes a Date filter button.
@@ -5458,49 +5514,49 @@
 AUTOMATION: HOLD - Branko's Parts and Reports write-up is still outstanding, so no product source states which filter buttons each report should show</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (spec v1.6 §2 Reports Filters; §4 Key Decisions "New date-range filter type" + "Multi-select where it makes sense"); Branko answers 2026-07-31 Q2/Q3/Q5/Q7; Figma 11903-10573</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>Choosing a Reports filter narrows the report results</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>Reports Page Filters</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Reports area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>1. Open the Reports area and go to any report — for example the Sales report.
 2. Open one of the filter buttons shown above the report table and choose one value.
 3. Look at the report table below.</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The report updates to show only the rows matching the chosen filter value, and the chosen value is shown on the filter button.
 2. The report narrows as soon as you pick the value - there is no Apply or Run button to press. Every filter button on every report works this way.
@@ -5511,49 +5567,49 @@
 </t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (spec v1.6 §2 Reports Filters; §4 Key Decisions "New date-range filter type" + "Multi-select where it makes sense"); Branko answers 2026-07-31 Q2/Q3/Q5/Q7; Figma 11903-10573</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr"/>
-      <c r="J93" s="2" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>New Reports filter types behave correctly (Location, Transaction Type, etc.)</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>Reports Page Filters</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Reports area of the app with some sample data present.</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>1. Open the Reports area and go to a report that uses them - for example A/R Aging Detail (Location, Transaction Type) or Notes (Mention).
 2. Look at the filter buttons shown above the report table.
 3. Open each of those filter buttons in turn, tick two choices where possible, and watch the report.</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Each of these filter buttons - Location, Transaction Type, Invoice Status, Type, User and Mention - opens a list of choices, lets you tick more than one, and narrows the report straight away with no Apply button.
 2. The choices inside each filter come from your own shop's data (for example your real vendors or categories), so there is no fixed list to compare against - check that the choices you see match the data in your shop.
@@ -5565,36 +5621,36 @@
 </t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (spec v1.6 §2 Reports Filters; §4 "Multi-select where it makes sense"); Branko answers 2026-07-31 Q3/Q5 + 2026-08-04 Q8 ("We do not have list of all filter items" - confirms no option list exists); Figma 11903-10573</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="2" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>Date range filter offers ready-made periods and a custom start/end range</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>Reports Page Filters</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. You are signed in to the ShopView App on a desktop browser.
 2. You are on a report that has a Date Range button - on the build tested that is Reports then the Timesheet Activities report.
@@ -5602,7 +5658,7 @@
 </t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Click the Date Range button.
 2. Look at what the panel offers, and at what the button already reads before you change anything.
@@ -5614,7 +5670,7 @@
 </t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The panel that opens offers a set of standard ready-made periods to choose from, plus a Custom option and a Clear Selection link. The written description does not fix which periods are offered, and it can differ per report, so do not check them against a fixed list - write down the ones your report offers.
 2. A period is already filled in when the panel first opens (on Timesheet Activities it is This month), and the button reads that period, for example "Date Range: This month".
@@ -5630,42 +5686,42 @@
 </t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (spec v1.6 §4 "New date-range filter type"; §2 Reports Filters - start/end picker; no presets; no default; applies on the second date); Branko answers 2026-07-31 Q5; tech plan 2026-07-29 D19</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr"/>
-      <c r="J95" s="2" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>Page toolbar Search expands in place and narrows the list as you type</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with several work orders listed.</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>1. Find the Search control in the page toolbar (a magnifier icon with the word Search).
 2. Click it.
@@ -5675,7 +5731,7 @@
 6. Expand it again, type text, and click somewhere else.</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The control expands in place into a small search box showing the placeholder 'Type to search'.
 2. The list narrows as you type, after a brief pause - and ONLY this page's list changes, nothing else in the app.
@@ -5687,42 +5743,42 @@
 </t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>SV-8798 (S13-R1 (placement in the toolbar action group); S13-R9 (scoped to this table only); S13-R12; S13-R15 (blur rules)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="2" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>Page search combines with filters and is cleared separately</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with work orders for several customers and statuses.</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>1. Apply one filter (for example a Status).
 2. Type a search term in the page search box.
@@ -5730,7 +5786,7 @@
 4. Re-type the search, then clear ONLY the filter.</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. With both active, the results match the filter AND the search together (both narrow the list at once).
 2. Clearing the search keeps the filter applied.
@@ -5741,43 +5797,43 @@
 </t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (S13-R10 (search and filters are additive); S13-R13 (each cleared independently); S8-R5) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="2" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>Your typed search stays in this browser tab only and is never saved</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with several work orders listed.
 3. You know how to open a second browser tab on the same page.</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>1. Type a search term in the page Search box that matches some work orders.
 2. Sort the table by a column, then move to the next page of results.
@@ -5786,7 +5842,7 @@
 5. Close every browser tab, open the browser again and go back to the Work Orders page.</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Sorting and paging keep your search applied - your text stays in the box and the list stays narrowed.
 2. Leaving the page and coming back also keeps your text in the box and the list still narrowed.
@@ -5798,49 +5854,49 @@
 </t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (S13-R14 (retained for the browser tab session); S13-R25 (never stored against the account; each tab independent); S13-N4 (not restored on a later visit); S10-R5) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>The search term is part of the shareable page link</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page.</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>1. Type a search term and copy the page address.
 2. Open the copied address in a fresh tab.
 3. Hand-edit the search part of the address into something malformed and load it.</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The address contains the search term after step 1.
 2. The fresh tab opens with the search box filled and the list already narrowed.
@@ -5852,42 +5908,42 @@
 </t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>SV-8796 (S11-R4 (query reflected in the URL); S11-R5 (URL query pre-applied with the control filled); S11-N2 (malformed query ignored with no error); S11-R8 (rationale: no saved value to overwrite)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr"/>
-      <c r="J99" s="2" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>On mobile the search expands in the toolbar and buttons make room</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile device.
 2. You are on the Work Orders page.</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>1. Tap the Search control in the page toolbar.
 2. Type a term and watch the list.
@@ -5895,7 +5951,7 @@
 4. With text in the box, tap somewhere else on the screen; then clear the text and tap somewhere else again.</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The search expands inline inside the toolbar - no separate popup window opens.
 2. The list narrows as you type, same as desktop.
@@ -5912,43 +5968,43 @@
 </t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (S13-R16 (inline expansion with no modal); S13-R17 (field fills the remaining width); S13-R18 (CTA hug width); S13-R19 (2+ icon actions -&gt; "more" kebab); S13-R20 (no active-query indicator); S12-R5) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>Every list page keeps its own search box (Parts, Reports, detail tabs)</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The page-search rollout has finished everywhere (run this sweep at the end of the rollout, not part-way through).
 3. You can reach Work Orders, Customers, Parts, Administration, Reports and the Dashboard.</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>1. Visit the Work Orders surfaces: the Work Orders list, a work order's History tab, the Work Order Log dialog opened from that tab's kebab menu, a line's Line Log dialog opened from the Lines tab, and the work order's Notes tab.
 2. Visit the customer and asset surfaces: the Customers list, then on one customer - Contacts, Assets, Invoices, Work Orders, Part Sales, Fees &amp; Discounts, Notes; then on one asset - Work Orders, Invoices, Notes.
@@ -5958,7 +6014,7 @@
 6. On each surface, find that table's own Search box and type something that matches one of its rows. Then open a work order's Parts tab and look at the search input it already has.</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Every table listed above has its own Search box - no table lost the ability to narrow by text.
 2. Each Search box narrows only its own table; nothing else in the app changes.
@@ -5970,42 +6026,42 @@
 </t>
         </is>
       </c>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (S14-R6 (audit: 42 surfaces across 39 components; Work Order Parts excluded); S14-R5 (app-wide sweep); S13-R22 (every table carries a search control); S14-N1 (verify once at the end)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>The top navigation search no longer filters page lists</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with several work orders listed.</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>1. Type a term into the TOP NAVIGATION search (the app-wide search at the top), not the page's own search box.
 2. Watch the Work Orders list while typing.
@@ -6013,7 +6069,7 @@
 4. Pick one of the results offered in the navigation search's dropdown.</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The page list does NOT narrow while you type in the navigation search - only its dropdown of matching records appears.
 2. The same holds on the other pages checked.
@@ -6024,42 +6080,42 @@
 </t>
         </is>
       </c>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>SV-8799 (S14-R1 (navigational results only); S14-R2 (the page-filtering code path is removed rather than dormant); S14-R4 (the list is left untouched); S14-R5) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="2" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>The Search box changes look as you hover over it, open it and type</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with several work orders listed.</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>1. Look at the right-hand end of the toolbar row, before the small icon buttons and before the 'Create Work Order' button.
 2. Move the mouse pointer over the 'Search' button without clicking.
@@ -6068,7 +6124,7 @@
 5. Delete what you typed and type a very long sentence instead.</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. A 'Search' button is shown with a small magnifier icon next to the word 'Search'; it is plain text on a see-through background, with no border and no fill.
 2. Hovering over it gives it a light grey background; the word 'Search' keeps its own colour.
@@ -6082,43 +6138,43 @@
 </t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>SV-8798 (S13-R2 (default text button); S13-R3 (hover fill); S13-R4 (expands in place at 180px); S13-R5 (placeholder "Type to search"); S13-R6 (typed text + X-circle clear); S13-R8 (long queries scroll)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" s="2" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>The list narrows shortly after you stop typing, with no button to press</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page with several work orders listed.
 3. You can also open the Parts Inventory page.</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>1. On the Work Orders page open the Search box and type a few letters that match some work orders. Do NOT press Enter.
 2. Watch the work order table for a second or two.
@@ -6127,7 +6183,7 @@
 5. Do the same on the Parts Inventory page.</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The list narrows on its own a moment after you stop typing (about a third of a second) - you never press Enter or any button.
 2. The matching rows appear in the table you were already looking at; no separate results page, results list or pop-up window opens.
@@ -6140,43 +6196,43 @@
 </t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>SV-8798 (S13-R7 (applies as you type; debounced 300ms; no apply/submit; Enter not required; Inventory 350ms); S13-R12 (results replace the table in place)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="2" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+      <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>One search box serves all Work Orders tabs and searches the tab you are on</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Work orders exist in several statuses, so the All, Estimates and Completed tabs each have rows.
 3. You have a word (for example part of a customer name) that matches work orders on more than one of those tabs.</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>1. On the All tab, type that word into the page Search box.
 2. Click the Estimates tab and look at the Search box and the list.
@@ -6184,7 +6240,7 @@
 4. Still on the Completed tab, clear the search with the round x, then go back to the All tab.</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. On the All tab only the rows matching your word remain.
 2. On the Estimates tab your word is still in the Search box, and the list shows only Estimates rows that match it - no rows from the other tabs appear.
@@ -6196,43 +6252,43 @@
 </t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>SV-8798 (S13-R11 (search applies within the active tab only); S13-R24 (the Work Orders tabs share a single query - views of one dataset)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="2" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>Each Report tab and each Parts view keeps its own separate search</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You can open at least two Parts views (for example Inventory and Purchase Orders).
 3. You can open a report that has more than one tab.</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>1. On a Parts view (for example Inventory) type a word into that page's Search box.
 2. Switch to another Parts view (for example Purchase Orders) and look at its Search box and list.
@@ -6240,7 +6296,7 @@
 4. Do the same on a report with tabs: search on one tab, then switch to another tab of the same report.</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The second Parts view opens with an empty Search box and its full list - the word you typed on the first view is not carried over.
 2. Going back to the first view brings its own word back and narrows its list again.
@@ -6252,42 +6308,42 @@
 </t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (S13-R24 (Reports sub-tabs and Parts views each keep their own query); S13-R11; S10-R4 (each view/tab keeps its own set)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>An old link carrying a top-search word no longer narrows the page list</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You have a Work Orders web address from BEFORE this change that still carries a word typed into the top-of-screen search (a bookmark, or a link someone sent). If you do not have one, hand-type that old search part onto the end of the Work Orders address.</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>1. Open that old web address.
 2. Look at the work order list and at the page's own Search box.
@@ -6295,7 +6351,7 @@
 4. Type a word into the top-of-screen search, then reload the page.</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The page opens with the normal list for your own saved filters - the old search word does NOT narrow the list.
 2. The page's own Search box is empty; nothing was carried into it.
@@ -6307,50 +6363,50 @@
 </t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>SV-8799 (S14-R3 (state / URL parameters / persisted values carrying a global search term into page filtering are removed with it); S14-R2; S14-R1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>Collapsing the filter bar keeps an active search working</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page and the filter bar is expanded.
 3. A word is typed in the page Search box and the list is narrowed by it.</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>1. With the search still active, click the filter button in the toolbar to collapse the filter bar.
 2. Look at the table and at the toolbar row.
 3. Expand the filter bar again.</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The list stays narrowed by your word - collapsing the filter bar does not cancel the search.
 2. The Search box stays in the toolbar row with your word still showing; it is not tucked away with the filter bar, because the search sits in the toolbar row and the chips sit in the row below.
@@ -6361,43 +6417,43 @@
 </t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>SV-8798 (S13-E1 (a collapsed filter bar keeps an active query applying and the search control stays in the toolbar); §4 Key Decisions (page search is separate from the filter bar)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="2" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>On a phone, pages with two or more icon buttons collapse them into one menu</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>Page Search Toolbar</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a mobile phone (or a browser window narrowed to phone size).
 2. You can reach the Parts area and the Reports area.
 3. You know what the same pages look like on a desktop screen, so you can tell which small icon buttons each one has.</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>1. Open Parts then Inventory. Look at the row of buttons at the top right of the table.
 2. Open Parts then Purchase Orders. Look at the same row of buttons.
@@ -6408,7 +6464,7 @@
 7. For comparison, open a page that has only ONE small icon button in its toolbar and look at its button row.</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. On each of the pages in steps 1 to 5, the small icon-only buttons are NOT all shown side by side. They are gathered into a single 'more' button.
 2. Tapping that 'more' button opens a short menu listing those actions, and each one still works from there.
@@ -6422,49 +6478,49 @@
 </t>
         </is>
       </c>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>S13-R19</t>
         </is>
       </c>
-      <c r="I109" s="2" t="inlineStr"/>
-      <c r="J109" s="2" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>The work order list request carries the active filter selections</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>API — Work Orders List Filtering</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser with developer tools open on the Network tab.
 2. You are on the Work Orders page with no filters applied.</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>1. Apply a Status selection and a Customer selection in the filter bar.
 2. In the Network tab, find the work order list request the page sends after the change.
 3. Inspect the request's parameters.</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The list request includes the active filter selections as request parameters (status values and customer identifiers).
 2. The request succeeds (HTTP 200).
@@ -6475,48 +6531,48 @@
 </t>
         </is>
       </c>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (S2-R2; S3-R6 (backend view)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="2" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+      <c r="I111" s="2" t="inlineStr"/>
+      <c r="J111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>A combined multi-filter request returns only work orders matching all filters</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>API — Work Orders List Filtering</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with developer tools open on the Network tab.
 2. Seeded ZZAUTOTEST work orders exist: customer A with an Estimate and an Approved work order, customer B with an Estimate work order.</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>1. On the Work Orders page apply Status = Estimate + Approved and Customer = customer A.
 2. Capture the resulting list request and response.</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. One request carries both filters together (both statuses and the customer).
 2. The response returns customer A's Estimate and Approved work orders only.
@@ -6528,48 +6584,48 @@
 </t>
         </is>
       </c>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (S2-R2; S3-R6; S8-R3 (backend view)) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I111" s="2" t="inlineStr"/>
-      <c r="J111" s="2" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+      <c r="I112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>A request with a deleted or unknown filter value gives no server error</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>API — Work Orders List Filtering</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in and can replay/edit the work order list request (developer tools or an API client).
 2. You have a captured filtered list request, and one of its filter values has since been deleted (for example a removed ZZAUTOTEST customer) or is a made-up identifier.</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>1. Send the list request containing the no-longer-existing (or made-up) filter value.
 2. Inspect the HTTP status and the response body.</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The backend does not fail with a server error (no HTTP 5xx).
 2. The response is a normal, successful list response - the invalid value is ignored or simply matches nothing.
@@ -6580,49 +6636,49 @@
 </t>
         </is>
       </c>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (S10-N1; S11-R3) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I112" s="2" t="inlineStr"/>
-      <c r="J112" s="2" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+      <c r="I113" s="2" t="inlineStr"/>
+      <c r="J113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>A list request with malformed filter parameters does not produce a server error</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>API — Work Orders List Filtering</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr">
+      <c r="C114" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in and can replay/edit the work order list request.
 2. You have a captured filtered list request to tamper with.</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>1. Corrupt the filter parameters (wrong types, scrambled values, nonsense text) and send the request.
 2. Inspect the HTTP status and the response body.
 3. Also open the equally malformed page URL in the browser and watch the page.</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The backend responds gracefully - no HTTP 5xx / crash; either a normal (unfiltered or empty) list or a clean validation response.
 2. In the browser the page still loads without filters and without an error message, matching the malformed-URL requirement.
@@ -6636,48 +6692,48 @@
 </t>
         </is>
       </c>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>SV-8796 (S11-N1) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I113" s="2" t="inlineStr"/>
-      <c r="J113" s="2" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+      <c r="I114" s="2" t="inlineStr"/>
+      <c r="J114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>A filter combination matching nothing returns an empty list, not an error</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>API — Work Orders List Filtering</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with developer tools open on the Network tab.
 2. A filter combination is known to match no work orders (for example a seeded customer plus a status they never have).</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>1. Apply that filter combination on the Work Orders page.
 2. Capture the list request and response.</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The request succeeds (HTTP 200).
 2. The response contains an empty result set (zero work orders) - an empty match is a normal outcome, not an error.
@@ -6688,42 +6744,42 @@
 </t>
         </is>
       </c>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>SV-8785 [epic] (S8-R3; S2-N3) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I114" s="2" t="inlineStr"/>
-      <c r="J114" s="2" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+      <c r="I115" s="2" t="inlineStr"/>
+      <c r="J115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>Saved-filters service round-trip: save, reload, and per-user isolation</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>API — Work Orders List Filtering</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser with developer tools open on the Network tab.
 2. A second user account is available.</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>1. On the Work Orders page, change a filter and watch the Network tab for the save request the page sends shortly after.
 2. Reload the page and find the load request for the saved page state.
@@ -6731,7 +6787,7 @@
 4. With an API client (or by editing the request), ask the saved-state service for a page key that was never saved.</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Changing a filter sends a save (PUT) to the per-user page-preferences service carrying the page's state, and it succeeds (HTTP 200).
 2. On reload the page requests the saved state back (GET, HTTP 200) and applies it - the filters return without you redoing them.
@@ -6744,13 +6800,13 @@
 </t>
         </is>
       </c>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>SV-8795 (S10-R2 (filters stored server-side against the user account; last write wins); S10-R3 (saved per user)) + tech plan 2026-07-29 s4-1.3 (GET/PUT per-user page preferences) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I115" s="2" t="inlineStr"/>
-      <c r="J115" s="2" t="inlineStr"/>
+      <c r="I116" s="2" t="inlineStr"/>
+      <c r="J116" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/filters-v1-testrail-import.xlsx
+++ b/testrail-import/filters-v1-testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J116"/>
+  <dimension ref="A1:J125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -490,7 +490,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Filter bar is shown below the tab row on the Work Orders page</t>
+          <t>Assigned to me is a toggle chip with no arrow that turns on and off</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -510,38 +510,36 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. At least a few work orders exist in the shop.</t>
+          <t>1. You are signed in on a desktop browser.
+2. You are on the Work Orders page.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>1. Open the Work Orders page.
-2. Look at the area directly under the tab row (All, Estimates, Completed, My Work Orders).</t>
+          <t>1. Look at the 'Assigned to me' chip in the toolbar row.
+2. Click it once, then click it a second time.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. A filter bar is visible directly below the tab row and above the work order table.
-2. The filter bar is shown by default (expanded) without having to turn anything on.
----
-This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S1-R1), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>SV-8786 (S1-R1) [spec v1.6 2026-07-28]</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1. The 'Assigned to me' chip shows a leading icon and the label 'Assigned to me'.
+2. It has NO dropdown arrow (chevron) and does not open a panel - it is a simple on/off toggle.
+3. The first click turns the filter on; the second click turns it off.
+4. It sits among the Work Orders chips in this order: Status, Assigned to me, Asset on Site.
+---
+This is the expected behaviour as per epic SV-8785, read on 17 August 2026, story SV-9271 (Assigned to Me filter), and the Filters specification at Confluence version 21 (published 14 August 2026) (S6a-R1; S6a-R2; S1-R6), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Five filter chips appear in a fixed order with an icon, name and arrow</t>
+          <t>Turning Assigned to me on highlights the chip with no value and no clear X</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -561,40 +559,37 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. You are on the Work Orders page with the filter bar visible.
-3. You are on the All tab (the Estimates and Completed tabs treat the Status chip differently - that is covered by its own tests, so do not compare the chips there).</t>
+          <t>1. You are signed in on a desktop browser.
+2. You are on the Work Orders page with 'Assigned to me' turned off.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>1. Read the filter chips in the filter bar from left to right.
-2. Look at what each chip shows.</t>
+          <t>1. Click the 'Assigned to me' chip to turn it on.
+2. Hover the mouse over the chip.
+3. Click the chip again to turn it off.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Exactly five filter chips appear, in this order: Status, Customer, Lead Technician, Service Advisor, Asset on Site.
-2. Each chip shows a leading picture icon, then the filter name, then a down arrow (chevron) showing that it opens a dropdown.
-3. The leading icon suits each filter (for example a status glyph for Status, a person for Customer, a wrench for Lead Technician, a headset for Service Advisor, a box for Asset on Site).
----
-This is the expected behaviour as per epic SV-8785, read on 11 August 2026, the owning story SV-8786, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S1-R2, S1-R3), read on 11 August 2026. Note: version 18 of the same specification asked only for the filter name and the chevron; version 19 added the leading picture icon to match the design, and this test follows the newer wording.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>SV-8786 (S1-R2; S1-R3) [spec v1.6 2026-07-28]</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1. When on, the chip takes the active (highlighted) appearance used by any selected filter.
+2. It shows NO value text after the name - it stays just 'Assigned to me'.
+3. Hovering does NOT show an X-circle clear icon - the toggle chip has no separate clear control.
+4. Clicking the chip itself is what turns the filter off; it returns to its plain appearance.
+---
+This is the expected behaviour as per epic SV-8785, read on 17 August 2026, story SV-9271 (Assigned to Me filter), and the Filters specification at Confluence version 21 (published 14 August 2026) (S6a-R3; S6a-R4; S7-R5; S7-R6), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>The filter bar still shows the other four chips on the Estimates tab</t>
+          <t>Assigned to me narrows to my work orders on top of the tab and filters</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -604,124 +599,428 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. Estimate work orders exist.
-3. You are on the Work Orders page.</t>
+          <t>1. You are signed in on a desktop browser as a user who is the assignee on some work orders.
+2. You are on the Work Orders page and other work orders (not yours) also exist.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1. Click the Estimates tab.
-2. Look at the filter bar.
-3. Look at each chip in turn.</t>
+          <t>1. Turn on 'Assigned to me'.
+2. Note which work orders remain in the list.
+3. Also apply a Status filter and switch tabs, watching the list.
+4. Navigate away from the page and return; also copy the page link.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The filter bar is still shown on this tab - it does not disappear.
-2. The Customer, Lead Technician, Service Advisor and Asset on Site chips are all shown and usable.
-3. The Status chip is shown but greyed out and already filled in with this tab's own status, and cannot be clicked or changed.
----
-This is the expected behaviour as per epic SV-8785, read on 11 August 2026, the owning story SV-8794, read on 11 August 2026, and Branko's answer of 17 July 2026 (Round 1, question 4, option B), recorded in this file: build/filters/branko-answers-2026-07-17/answers-ingested.md (https://github.com/bilalmuzamil-sketch/Manual-test-Cases/blob/HEAD/build/filters/branko-answers-2026-07-17/answers-ingested.md), read on 11 August 2026. Note: the Filters specification at Confluence version 19 says instead that the Status chip is hidden on this tab (S9-R2 and S9-R3). That sentence has not been edited since 14 May 2026, which is two and a half months before Branko's answer, so the answer is the later decision and this test follows the answer. Branko has been asked to correct the specification.
-AUTOMATION: HOLD - waiting on Branko to confirm whether the Status chip is hidden or shown greyed out on the Estimates and Completed tabs, and to correct the specification
-</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>SV-8785 [epic] (S1-N1; S9-R2; §4 Key Decisions - PRD text says "hidden"; behaviour per Branko Q4=B 2026-07-17 + QA-lead ruling 2026-07-30 = shown greyed-out/disabled) [spec v1.6 2026-07-28]</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1. The list narrows to only the work orders assigned to you (the logged-in user).
+2. It applies on top of the active tab's built-in filter and on top of any other active filter - the results match all of them together.
+3. The selection is remembered when you leave and return (persistence, Story 10).
+4. The active state is reflected in the page link so a filtered view can be shared (URL state, Story 11).
+5. If nothing is assigned to you within the current tab and filters, the empty state is shown (Story 8).
+---
+This is the expected behaviour as per epic SV-8785, read on 17 August 2026, story SV-9271 (Assigned to Me filter), and the Filters specification at Confluence version 21 (published 14 August 2026) (S6a-R5; S6a-R6; S11-R1; S10-R1), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Status chip opens a checkbox list of all nine statuses plus Clear Selection</t>
+          <t>Filter chips sit in the Work Orders toolbar row, not a separate filter bar</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>Filter Bar Layout and Visibility</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in on a desktop browser.
+2. You are on the Work Orders page.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1. Look at where the filter chips are placed on the page.
+2. Look for any separate filter bar or a control to hide the chips.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The filter chips sit in the page's main toolbar row, right-aligned, in the same row as the tabs.
+2. There is no separate filter bar row above or below the tabs.
+3. The chips are always visible - there is no button to hide, collapse or expand them.
+---
+This is the expected behaviour as per epic SV-8785, read on 17 August 2026, story SV-9268 (Filter layout in the toolbar) and SV-9269 (remove the collapse toggle), and the Filters specification at Confluence version 21 (published 14 August 2026) (S1-R1; S1-R4), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>SV-8786 (S1-R1) [spec v1.6 2026-07-28]</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Work Orders shows three filter chips: Status, Assigned to me, Asset on Site</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Filter Bar Layout and Visibility</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in on a desktop browser.
+2. You are on the Work Orders page, All tab.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1. Read the filter chips in the toolbar row, left to right.
+2. Look at each chip's parts.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. There are THREE filter chips, in this order: Status, Assigned to me, Asset on Site.
+2. Customer, Lead Technician and Service Advisor are NOT filter chips here - they were removed in the redesign.
+3. Each chip shows a leading type-icon, the filter name, and a chevron (arrow) that shows it opens a panel.
+4. The 'Assigned to me' chip is the exception: it has no chevron because it is a simple on/off toggle.
+---
+This is the expected behaviour as per epic SV-8785, read on 17 August 2026, story SV-9268 (Filter layout in the toolbar) and SV-9270 (reduce Work Orders filters), and the Filters specification at Confluence version 21 (published 14 August 2026) (S1-R5; S1-R6), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>SV-8786 (S1-R2; S1-R3) [spec v1.6 2026-07-28]</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>On the Estimates tab the Assigned to me and Asset on Site chips still show</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Filter Bar Layout and Visibility</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in on a desktop browser.
+2. You are on the Work Orders page.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1. Go to the Estimates tab.
+2. Read which filter chips are shown.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The 'Assigned to me' and 'Asset on Site' chips are shown on the Estimates tab.
+2. The Status chip is not among them on this tab, because the Estimates tab already pre-filters by status (the Status chip shows on the All tab only).
+3. Note: there is an open question on whether the Status chip should be hidden or shown greyed/pre-filled on this tab - see the tab-behaviour cases; that point is being confirmed with the QA lead and is not settled by this case.
+---
+This is the expected behaviour as per epic SV-8785, read on 17 August 2026, story SV-9272 (tab model), and the Filters specification at Confluence version 21 (published 14 August 2026) (S1-N1; S9-R5), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>SV-8785 [epic] (S1-N1; S9-R2; §4 Key Decisions - PRD text says "hidden"; behaviour per Branko Q4=B 2026-07-17 + QA-lead ruling 2026-07-30 = shown greyed-out/disabled) [spec v1.6 2026-07-28]</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Filter chips sit in the toolbar row; on pages with no tabs, the title row</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Filter Bar Layout and Visibility</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in on a desktop browser.
+2. You can reach both a page that has tabs (Work Orders) and a page that has no tabs but does have filters.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1. On the Work Orders page, note where the filter chips are placed relative to the tabs.
+2. Go to another page that has filters but no tabs (for example a Parts view or a Report).
+3. Look for any control to hide or collapse the filter chips.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The filter chips sit in the page's main toolbar row, right-aligned. There is no separate filter bar row anywhere in the application.
+2. On a page WITH tabs, the chips are in the same row as the tabs.
+3. On a page WITHOUT tabs, the chips are in the same row as the page title.
+4. The chips are always visible: there is no button to hide, collapse or expand them, on any page or screen size.
+5. Each page shows the filters that page already provides today - this change relocates and restyles existing filters; it adds none and removes none. A page with no filters today shows no chips.
+---
+This is the expected behaviour as per epic SV-8785, read on 17 August 2026, story SV-9268 (Filter layout in the toolbar) and SV-9269 (remove the collapse toggle), and the Filters specification at Confluence version 21 (published 14 August 2026) (S1-R1; S1-R4; S1-R7; S1-R8), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Toolbar order is search, filter chips, icon actions, then the main button</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Filter Bar Layout and Visibility</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in on a desktop browser.
+2. You are on the Work Orders page (which has a page search, filter chips and a 'New Work Order' button).</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1. Read the right-hand group of controls in the toolbar row, left to right.
+2. Make the browser window narrow enough that the group cannot fit on one line.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The right-hand action group is ordered, left to right: the page search, a divider, the filter chips, a divider, any icon-only actions, then the primary button (for example 'New Work Order').
+2. When the window is too narrow to fit the group on one line, the toolbar row wraps.
+3. The chips wrap together as a group and keep their order. Nothing is hidden and nothing collapses into an overflow menu.
+---
+This is the expected behaviour as per epic SV-8785, read on 17 August 2026, story SV-9268 (Filter layout in the toolbar), and the Filters specification at Confluence version 21 (published 14 August 2026) (S1-R2; S1-R3), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>A filter panel opens under its chip and stays applied when you click away</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Filter Bar Layout and Visibility</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in on a desktop browser.
+2. You are on a page that has at least one filter chip that opens a panel.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1. Click a filter chip that opens a panel and note where the panel appears.
+2. Make a selection, then click somewhere outside the panel.
+3. Re-open a panel that has a search box and type text that matches nothing.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The panel opens as a small pop-over just below its chip, lined up with the left edge of the chip.
+2. Every panel has a 'Clear selection' action in its footer that clears only that filter.
+3. Clicking outside the panel closes it. Your selection is already applied and is kept - it is not discarded.
+4. In a panel that has a search box, a search that matches nothing shows 'No matches' in the panel body.
+---
+This is the expected behaviour as per epic SV-8785, read on 17 August 2026, story SV-9276 (Filter panel types), and the Filters specification at Confluence version 21 (published 14 August 2026) (S16-R6; S16-R7; S16-N1), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Status chip opens a checkbox list of all nine statuses plus Clear selection</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>Status Filter</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. You are on the Work Orders page on the All or My Work Orders tab.
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in on a desktop browser.
+2. You are on the Work Orders page on the All tab (the Status chip is shown on the All tab only).
 3. No filters are currently selected.</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>1. Click the Status filter chip.
 2. Read the list of options from top to bottom.
-3. Look at the bottom of the dropdown panel.</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. A dropdown panel opens under the Status chip.
+3. Look at the bottom of the panel.</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. A checkbox-list panel opens under the Status chip (no search box).
 2. It lists all nine statuses as checkboxes, in this order: Estimate, Approved, In progress, Review, Complete, Invoiced, Paid, Declined, Imported.
 3. All checkboxes are unticked (nothing selected yet).
-4. A 'Clear Selection' action is shown at the bottom of the dropdown.
----
-This is the expected behaviour as per epic SV-8785, read on 11 August 2026, and the Filters specification at Confluence version 19 (published 6 August 2026) (S2-R1, S2-R4), read on 11 August 2026. Last checked against build v3.4.2-d00239b on 8/5/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+4. A 'Clear selection' action is shown at the bottom of the panel.
+---
+This is the expected behaviour as per epic SV-8785, read on 17 August 2026, story SV-8787 (Status filter) and SV-9276 (panel types), and the Filters specification at Confluence version 21 (published 14 August 2026) (S2-R1; S16-R1; S16-R6), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026
+</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>SV-8787 (S2-R1; S2-R4) [spec v1.6 2026-07-28]</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Ticking one status filters the table immediately, with no apply button</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Status Filter</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Work Orders page on the All tab.
@@ -729,7 +1028,7 @@
 </t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Click the Status filter chip.
 2. Tick the checkbox for one status (for example Estimate).
@@ -737,47 +1036,47 @@
 </t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The ticked checkbox appears filled (checked).
 2. The table updates immediately to show only work orders in the selected status - there is no co